--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="300">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -676,6 +676,9 @@
     <t>['24', '41', '67', '82']</t>
   </si>
   <si>
+    <t>['6']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -770,9 +773,6 @@
   </si>
   <si>
     <t>['24', '81']</t>
-  </si>
-  <si>
-    <t>['6']</t>
   </si>
   <si>
     <t>['4', '24']</t>
@@ -1275,7 +1275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP185"/>
+  <dimension ref="A1:BP186"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1531,7 +1531,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1612,7 +1612,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ2">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2561,7 +2561,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3385,7 +3385,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ12">
         <v>1.67</v>
@@ -3797,7 +3797,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4003,7 +4003,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4209,7 +4209,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4621,7 +4621,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4908,7 +4908,7 @@
         <v>2</v>
       </c>
       <c r="AQ18">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR18">
         <v>0.9399999999999999</v>
@@ -5239,7 +5239,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5651,7 +5651,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5857,7 +5857,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6269,7 +6269,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6681,7 +6681,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6887,7 +6887,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7093,7 +7093,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7583,7 +7583,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ31">
         <v>0.83</v>
@@ -8123,7 +8123,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8410,7 +8410,7 @@
         <v>1.82</v>
       </c>
       <c r="AQ35">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR35">
         <v>2.22</v>
@@ -8535,7 +8535,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9565,7 +9565,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9771,7 +9771,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10055,7 +10055,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
         <v>0.91</v>
@@ -10389,7 +10389,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q45">
         <v>3</v>
@@ -11007,7 +11007,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11213,7 +11213,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11419,7 +11419,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11625,7 +11625,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12530,7 +12530,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ55">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR55">
         <v>1.72</v>
@@ -12655,7 +12655,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13067,7 +13067,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13273,7 +13273,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13685,7 +13685,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14381,7 +14381,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ64">
         <v>0.5</v>
@@ -14509,7 +14509,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15002,7 +15002,7 @@
         <v>2.82</v>
       </c>
       <c r="AQ67">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR67">
         <v>1.91</v>
@@ -15127,7 +15127,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15333,7 +15333,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16157,7 +16157,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16363,7 +16363,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16775,7 +16775,7 @@
         <v>143</v>
       </c>
       <c r="P76" t="s">
-        <v>252</v>
+        <v>220</v>
       </c>
       <c r="Q76">
         <v>4.75</v>
@@ -19119,7 +19119,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ87">
         <v>1.42</v>
@@ -20152,7 +20152,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ92">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR92">
         <v>1.14</v>
@@ -21797,7 +21797,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ100">
         <v>1.91</v>
@@ -23036,7 +23036,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ106">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR106">
         <v>1.33</v>
@@ -25711,7 +25711,7 @@
         <v>0.71</v>
       </c>
       <c r="AP119">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ119">
         <v>1.33</v>
@@ -26332,7 +26332,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ122">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR122">
         <v>1.47</v>
@@ -27153,7 +27153,7 @@
         <v>1.57</v>
       </c>
       <c r="AP126">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ126">
         <v>1.64</v>
@@ -30037,7 +30037,7 @@
         <v>0.78</v>
       </c>
       <c r="AP140">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ140">
         <v>0.92</v>
@@ -30577,7 +30577,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -31276,7 +31276,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ146">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR146">
         <v>1.85</v>
@@ -33951,7 +33951,7 @@
         <v>0.11</v>
       </c>
       <c r="AP159">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ159">
         <v>0.09</v>
@@ -35315,7 +35315,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -36014,7 +36014,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ169">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR169">
         <v>1.59</v>
@@ -36345,7 +36345,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -39104,7 +39104,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ184">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AR184">
         <v>1.69</v>
@@ -39307,7 +39307,7 @@
         <v>1.27</v>
       </c>
       <c r="AP185">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ185">
         <v>1.25</v>
@@ -39385,6 +39385,212 @@
         <v>2.48</v>
       </c>
       <c r="BP185">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="186" spans="1:68">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186">
+        <v>7453611</v>
+      </c>
+      <c r="C186" t="s">
+        <v>68</v>
+      </c>
+      <c r="D186" t="s">
+        <v>69</v>
+      </c>
+      <c r="E186" s="2">
+        <v>45688.69791666666</v>
+      </c>
+      <c r="F186">
+        <v>24</v>
+      </c>
+      <c r="G186" t="s">
+        <v>80</v>
+      </c>
+      <c r="H186" t="s">
+        <v>79</v>
+      </c>
+      <c r="I186">
+        <v>1</v>
+      </c>
+      <c r="J186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>1</v>
+      </c>
+      <c r="M186">
+        <v>0</v>
+      </c>
+      <c r="N186">
+        <v>1</v>
+      </c>
+      <c r="O186" t="s">
+        <v>220</v>
+      </c>
+      <c r="P186" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q186">
+        <v>3.1</v>
+      </c>
+      <c r="R186">
+        <v>2.1</v>
+      </c>
+      <c r="S186">
+        <v>3.4</v>
+      </c>
+      <c r="T186">
+        <v>1.4</v>
+      </c>
+      <c r="U186">
+        <v>2.75</v>
+      </c>
+      <c r="V186">
+        <v>3</v>
+      </c>
+      <c r="W186">
+        <v>1.36</v>
+      </c>
+      <c r="X186">
+        <v>8</v>
+      </c>
+      <c r="Y186">
+        <v>1.08</v>
+      </c>
+      <c r="Z186">
+        <v>2.23</v>
+      </c>
+      <c r="AA186">
+        <v>3.5</v>
+      </c>
+      <c r="AB186">
+        <v>3.14</v>
+      </c>
+      <c r="AC186">
+        <v>1.05</v>
+      </c>
+      <c r="AD186">
+        <v>11</v>
+      </c>
+      <c r="AE186">
+        <v>1.28</v>
+      </c>
+      <c r="AF186">
+        <v>3.52</v>
+      </c>
+      <c r="AG186">
+        <v>1.91</v>
+      </c>
+      <c r="AH186">
+        <v>1.89</v>
+      </c>
+      <c r="AI186">
+        <v>1.7</v>
+      </c>
+      <c r="AJ186">
+        <v>2.05</v>
+      </c>
+      <c r="AK186">
+        <v>1.43</v>
+      </c>
+      <c r="AL186">
+        <v>1.3</v>
+      </c>
+      <c r="AM186">
+        <v>1.52</v>
+      </c>
+      <c r="AN186">
+        <v>1.64</v>
+      </c>
+      <c r="AO186">
+        <v>0.82</v>
+      </c>
+      <c r="AP186">
+        <v>1.75</v>
+      </c>
+      <c r="AQ186">
+        <v>0.75</v>
+      </c>
+      <c r="AR186">
+        <v>1.34</v>
+      </c>
+      <c r="AS186">
+        <v>1.33</v>
+      </c>
+      <c r="AT186">
+        <v>2.67</v>
+      </c>
+      <c r="AU186">
+        <v>2</v>
+      </c>
+      <c r="AV186">
+        <v>6</v>
+      </c>
+      <c r="AW186">
+        <v>3</v>
+      </c>
+      <c r="AX186">
+        <v>22</v>
+      </c>
+      <c r="AY186">
+        <v>6</v>
+      </c>
+      <c r="AZ186">
+        <v>30</v>
+      </c>
+      <c r="BA186">
+        <v>1</v>
+      </c>
+      <c r="BB186">
+        <v>6</v>
+      </c>
+      <c r="BC186">
+        <v>7</v>
+      </c>
+      <c r="BD186">
+        <v>1.72</v>
+      </c>
+      <c r="BE186">
+        <v>6.75</v>
+      </c>
+      <c r="BF186">
+        <v>2.33</v>
+      </c>
+      <c r="BG186">
+        <v>1.23</v>
+      </c>
+      <c r="BH186">
+        <v>3.7</v>
+      </c>
+      <c r="BI186">
+        <v>1.4</v>
+      </c>
+      <c r="BJ186">
+        <v>2.7</v>
+      </c>
+      <c r="BK186">
+        <v>1.64</v>
+      </c>
+      <c r="BL186">
+        <v>2.1</v>
+      </c>
+      <c r="BM186">
+        <v>1.85</v>
+      </c>
+      <c r="BN186">
+        <v>1.83</v>
+      </c>
+      <c r="BO186">
+        <v>2.48</v>
+      </c>
+      <c r="BP186">
         <v>1.47</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1178" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="302">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -679,6 +679,15 @@
     <t>['6']</t>
   </si>
   <si>
+    <t>['8', '17', '44', '71', '82']</t>
+  </si>
+  <si>
+    <t>['30']</t>
+  </si>
+  <si>
+    <t>['86', '90']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -731,9 +740,6 @@
   </si>
   <si>
     <t>['2', '12']</t>
-  </si>
-  <si>
-    <t>['30']</t>
   </si>
   <si>
     <t>['9', '65']</t>
@@ -1275,7 +1281,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP186"/>
+  <dimension ref="A1:BP190"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1531,7 +1537,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2433,10 +2439,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ6">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2561,7 +2567,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2845,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ8">
         <v>1.42</v>
@@ -3260,7 +3266,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ10">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3385,7 +3391,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3797,7 +3803,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4003,7 +4009,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4081,7 +4087,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14">
         <v>1.64</v>
@@ -4209,7 +4215,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4287,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ15">
         <v>0.5</v>
@@ -4496,7 +4502,7 @@
         <v>2</v>
       </c>
       <c r="AQ16">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4621,7 +4627,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4702,7 +4708,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ17">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5239,7 +5245,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5651,7 +5657,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5729,10 +5735,10 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ22">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR22">
         <v>1.58</v>
@@ -5857,7 +5863,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -5935,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ23">
         <v>0.73</v>
@@ -6141,7 +6147,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ24">
         <v>1.25</v>
@@ -6269,7 +6275,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6347,10 +6353,10 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ25">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR25">
         <v>2.16</v>
@@ -6681,7 +6687,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6887,7 +6893,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -6968,7 +6974,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
         <v>0.79</v>
@@ -7093,7 +7099,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7792,7 +7798,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ32">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -8123,7 +8129,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8407,7 +8413,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ35">
         <v>0.75</v>
@@ -8535,7 +8541,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8616,7 +8622,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ36">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR36">
         <v>0.9399999999999999</v>
@@ -9028,7 +9034,7 @@
         <v>2</v>
       </c>
       <c r="AQ38">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR38">
         <v>1.16</v>
@@ -9231,7 +9237,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39">
         <v>0.5</v>
@@ -9437,7 +9443,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ40">
         <v>0.64</v>
@@ -9565,7 +9571,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9771,7 +9777,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9852,7 +9858,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR42">
         <v>0.95</v>
@@ -10058,7 +10064,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -10389,7 +10395,7 @@
         <v>121</v>
       </c>
       <c r="P45" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="Q45">
         <v>3</v>
@@ -11007,7 +11013,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11088,7 +11094,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ48">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR48">
         <v>1.15</v>
@@ -11213,7 +11219,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11291,7 +11297,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ49">
         <v>1.67</v>
@@ -11419,7 +11425,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11500,7 +11506,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ50">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR50">
         <v>1.76</v>
@@ -11625,7 +11631,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11909,7 +11915,7 @@
         <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ52">
         <v>1.33</v>
@@ -12321,10 +12327,10 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ54">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR54">
         <v>1.56</v>
@@ -12655,7 +12661,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13067,7 +13073,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13273,7 +13279,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13685,7 +13691,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14175,10 +14181,10 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ63">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR63">
         <v>1.69</v>
@@ -14509,7 +14515,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14587,7 +14593,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ65">
         <v>1.25</v>
@@ -14793,10 +14799,10 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ66">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR66">
         <v>1.81</v>
@@ -14999,7 +15005,7 @@
         <v>1.25</v>
       </c>
       <c r="AP67">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ67">
         <v>0.75</v>
@@ -15127,7 +15133,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15333,7 +15339,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15617,10 +15623,10 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ70">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR70">
         <v>1.88</v>
@@ -16157,7 +16163,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16235,7 +16241,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ73">
         <v>0.73</v>
@@ -16363,7 +16369,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16444,7 +16450,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR74">
         <v>1.66</v>
@@ -17268,7 +17274,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ78">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR78">
         <v>1.59</v>
@@ -17471,7 +17477,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ79">
         <v>0.83</v>
@@ -18217,7 +18223,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18298,7 +18304,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ83">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR83">
         <v>1.89</v>
@@ -18501,10 +18507,10 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ84">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR84">
         <v>1.61</v>
@@ -18835,7 +18841,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -18913,7 +18919,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ86">
         <v>0.73</v>
@@ -19740,7 +19746,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ90">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR90">
         <v>1.5</v>
@@ -19865,7 +19871,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19943,7 +19949,7 @@
         <v>0.5</v>
       </c>
       <c r="AP91">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ91">
         <v>0.67</v>
@@ -20071,7 +20077,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20483,7 +20489,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20767,10 +20773,10 @@
         <v>0.8</v>
       </c>
       <c r="AP95">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ95">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR95">
         <v>1.79</v>
@@ -20895,7 +20901,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21101,7 +21107,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21388,7 +21394,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ98">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR98">
         <v>1.83</v>
@@ -21513,7 +21519,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21719,7 +21725,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21800,7 +21806,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ100">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR100">
         <v>1.3</v>
@@ -21925,7 +21931,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22209,7 +22215,7 @@
         <v>1.6</v>
       </c>
       <c r="AP102">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ102">
         <v>1.42</v>
@@ -22415,7 +22421,7 @@
         <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ103">
         <v>0.92</v>
@@ -22955,7 +22961,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23161,7 +23167,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23367,7 +23373,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23651,7 +23657,7 @@
         <v>1.17</v>
       </c>
       <c r="AP109">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ109">
         <v>0.64</v>
@@ -23779,7 +23785,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -23857,7 +23863,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ110">
         <v>1.64</v>
@@ -24066,7 +24072,7 @@
         <v>1.64</v>
       </c>
       <c r="AQ111">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR111">
         <v>1.55</v>
@@ -24397,7 +24403,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24478,7 +24484,7 @@
         <v>1</v>
       </c>
       <c r="AQ113">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR113">
         <v>0.88</v>
@@ -24681,10 +24687,10 @@
         <v>1.33</v>
       </c>
       <c r="AP114">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ114">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR114">
         <v>1.76</v>
@@ -25299,7 +25305,7 @@
         <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ117">
         <v>0.92</v>
@@ -25508,7 +25514,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ118">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR118">
         <v>1.51</v>
@@ -25633,7 +25639,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26251,7 +26257,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26538,7 +26544,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ123">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR123">
         <v>2.07</v>
@@ -26741,10 +26747,10 @@
         <v>0.57</v>
       </c>
       <c r="AP124">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ124">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR124">
         <v>1.8</v>
@@ -26869,7 +26875,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27281,7 +27287,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27693,7 +27699,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27899,7 +27905,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -27977,7 +27983,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ130">
         <v>0.5</v>
@@ -28311,7 +28317,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28392,7 +28398,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ132">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR132">
         <v>1.55</v>
@@ -28723,7 +28729,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28801,7 +28807,7 @@
         <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ134">
         <v>0.92</v>
@@ -29007,7 +29013,7 @@
         <v>0.75</v>
       </c>
       <c r="AP135">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ135">
         <v>1.33</v>
@@ -29135,7 +29141,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29216,7 +29222,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ136">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR136">
         <v>1.71</v>
@@ -29834,7 +29840,7 @@
         <v>1</v>
       </c>
       <c r="AQ139">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR139">
         <v>1.07</v>
@@ -30165,7 +30171,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30246,7 +30252,7 @@
         <v>1.18</v>
       </c>
       <c r="AQ141">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR141">
         <v>1.44</v>
@@ -30577,7 +30583,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30783,7 +30789,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31195,7 +31201,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31479,7 +31485,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP147">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ147">
         <v>0.73</v>
@@ -31607,7 +31613,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31813,7 +31819,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32097,7 +32103,7 @@
         <v>1.67</v>
       </c>
       <c r="AP150">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ150">
         <v>1.64</v>
@@ -32431,7 +32437,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32512,7 +32518,7 @@
         <v>2.18</v>
       </c>
       <c r="AQ152">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR152">
         <v>1.81</v>
@@ -32715,7 +32721,7 @@
         <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ153">
         <v>0.67</v>
@@ -32843,7 +32849,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -32921,7 +32927,7 @@
         <v>1.44</v>
       </c>
       <c r="AP154">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ154">
         <v>1.67</v>
@@ -33049,7 +33055,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33255,7 +33261,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33542,7 +33548,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ157">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR157">
         <v>1.54</v>
@@ -33667,7 +33673,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -33954,7 +33960,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ159">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34079,7 +34085,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34285,7 +34291,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34366,7 +34372,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ161">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR161">
         <v>1.75</v>
@@ -34697,7 +34703,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34981,7 +34987,7 @@
         <v>0.8</v>
       </c>
       <c r="AP164">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AQ164">
         <v>0.67</v>
@@ -35109,7 +35115,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35187,7 +35193,7 @@
         <v>1</v>
       </c>
       <c r="AP165">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ165">
         <v>1.33</v>
@@ -35315,7 +35321,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35727,7 +35733,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -35808,7 +35814,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ168">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AR168">
         <v>1.71</v>
@@ -36011,7 +36017,7 @@
         <v>1</v>
       </c>
       <c r="AP169">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AQ169">
         <v>0.75</v>
@@ -36345,7 +36351,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36551,7 +36557,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36757,7 +36763,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36838,7 +36844,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ173">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AR173">
         <v>2.04</v>
@@ -36963,7 +36969,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37375,7 +37381,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37456,7 +37462,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ176">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AR176">
         <v>1.54</v>
@@ -37581,7 +37587,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37659,7 +37665,7 @@
         <v>0.7</v>
       </c>
       <c r="AP177">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="AQ177">
         <v>0.64</v>
@@ -37993,7 +37999,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38199,7 +38205,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38277,7 +38283,7 @@
         <v>0.82</v>
       </c>
       <c r="AP180">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ180">
         <v>0.83</v>
@@ -38692,7 +38698,7 @@
         <v>2</v>
       </c>
       <c r="AQ182">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AR182">
         <v>1.21</v>
@@ -38817,7 +38823,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39023,7 +39029,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39592,6 +39598,830 @@
       </c>
       <c r="BP186">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="187" spans="1:68">
+      <c r="A187" s="1">
+        <v>186</v>
+      </c>
+      <c r="B187">
+        <v>7453612</v>
+      </c>
+      <c r="C187" t="s">
+        <v>68</v>
+      </c>
+      <c r="D187" t="s">
+        <v>69</v>
+      </c>
+      <c r="E187" s="2">
+        <v>45689.5</v>
+      </c>
+      <c r="F187">
+        <v>24</v>
+      </c>
+      <c r="G187" t="s">
+        <v>76</v>
+      </c>
+      <c r="H187" t="s">
+        <v>71</v>
+      </c>
+      <c r="I187">
+        <v>3</v>
+      </c>
+      <c r="J187">
+        <v>0</v>
+      </c>
+      <c r="K187">
+        <v>3</v>
+      </c>
+      <c r="L187">
+        <v>5</v>
+      </c>
+      <c r="M187">
+        <v>0</v>
+      </c>
+      <c r="N187">
+        <v>5</v>
+      </c>
+      <c r="O187" t="s">
+        <v>221</v>
+      </c>
+      <c r="P187" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q187">
+        <v>2.2</v>
+      </c>
+      <c r="R187">
+        <v>2.15</v>
+      </c>
+      <c r="S187">
+        <v>5</v>
+      </c>
+      <c r="T187">
+        <v>1.38</v>
+      </c>
+      <c r="U187">
+        <v>2.8</v>
+      </c>
+      <c r="V187">
+        <v>2.7</v>
+      </c>
+      <c r="W187">
+        <v>1.4</v>
+      </c>
+      <c r="X187">
+        <v>7</v>
+      </c>
+      <c r="Y187">
+        <v>1.09</v>
+      </c>
+      <c r="Z187">
+        <v>1.62</v>
+      </c>
+      <c r="AA187">
+        <v>3.6</v>
+      </c>
+      <c r="AB187">
+        <v>5.8</v>
+      </c>
+      <c r="AC187">
+        <v>1.05</v>
+      </c>
+      <c r="AD187">
+        <v>9</v>
+      </c>
+      <c r="AE187">
+        <v>1.3</v>
+      </c>
+      <c r="AF187">
+        <v>3.4</v>
+      </c>
+      <c r="AG187">
+        <v>1.91</v>
+      </c>
+      <c r="AH187">
+        <v>1.83</v>
+      </c>
+      <c r="AI187">
+        <v>1.9</v>
+      </c>
+      <c r="AJ187">
+        <v>1.78</v>
+      </c>
+      <c r="AK187">
+        <v>1.16</v>
+      </c>
+      <c r="AL187">
+        <v>1.26</v>
+      </c>
+      <c r="AM187">
+        <v>2.2</v>
+      </c>
+      <c r="AN187">
+        <v>1.64</v>
+      </c>
+      <c r="AO187">
+        <v>1.36</v>
+      </c>
+      <c r="AP187">
+        <v>1.75</v>
+      </c>
+      <c r="AQ187">
+        <v>1.25</v>
+      </c>
+      <c r="AR187">
+        <v>1.65</v>
+      </c>
+      <c r="AS187">
+        <v>1.2</v>
+      </c>
+      <c r="AT187">
+        <v>2.85</v>
+      </c>
+      <c r="AU187">
+        <v>11</v>
+      </c>
+      <c r="AV187">
+        <v>3</v>
+      </c>
+      <c r="AW187">
+        <v>8</v>
+      </c>
+      <c r="AX187">
+        <v>1</v>
+      </c>
+      <c r="AY187">
+        <v>20</v>
+      </c>
+      <c r="AZ187">
+        <v>4</v>
+      </c>
+      <c r="BA187">
+        <v>1</v>
+      </c>
+      <c r="BB187">
+        <v>3</v>
+      </c>
+      <c r="BC187">
+        <v>4</v>
+      </c>
+      <c r="BD187">
+        <v>1.5</v>
+      </c>
+      <c r="BE187">
+        <v>6.75</v>
+      </c>
+      <c r="BF187">
+        <v>2.9</v>
+      </c>
+      <c r="BG187">
+        <v>1.28</v>
+      </c>
+      <c r="BH187">
+        <v>3.3</v>
+      </c>
+      <c r="BI187">
+        <v>1.49</v>
+      </c>
+      <c r="BJ187">
+        <v>2.43</v>
+      </c>
+      <c r="BK187">
+        <v>1.75</v>
+      </c>
+      <c r="BL187">
+        <v>1.95</v>
+      </c>
+      <c r="BM187">
+        <v>2.18</v>
+      </c>
+      <c r="BN187">
+        <v>1.58</v>
+      </c>
+      <c r="BO187">
+        <v>2.8</v>
+      </c>
+      <c r="BP187">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="188" spans="1:68">
+      <c r="A188" s="1">
+        <v>187</v>
+      </c>
+      <c r="B188">
+        <v>7453610</v>
+      </c>
+      <c r="C188" t="s">
+        <v>68</v>
+      </c>
+      <c r="D188" t="s">
+        <v>69</v>
+      </c>
+      <c r="E188" s="2">
+        <v>45689.59375</v>
+      </c>
+      <c r="F188">
+        <v>24</v>
+      </c>
+      <c r="G188" t="s">
+        <v>83</v>
+      </c>
+      <c r="H188" t="s">
+        <v>84</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>1</v>
+      </c>
+      <c r="M188">
+        <v>1</v>
+      </c>
+      <c r="N188">
+        <v>2</v>
+      </c>
+      <c r="O188" t="s">
+        <v>96</v>
+      </c>
+      <c r="P188" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q188">
+        <v>2.35</v>
+      </c>
+      <c r="R188">
+        <v>2.15</v>
+      </c>
+      <c r="S188">
+        <v>4.33</v>
+      </c>
+      <c r="T188">
+        <v>1.38</v>
+      </c>
+      <c r="U188">
+        <v>2.8</v>
+      </c>
+      <c r="V188">
+        <v>2.7</v>
+      </c>
+      <c r="W188">
+        <v>1.4</v>
+      </c>
+      <c r="X188">
+        <v>7</v>
+      </c>
+      <c r="Y188">
+        <v>1.08</v>
+      </c>
+      <c r="Z188">
+        <v>1.79</v>
+      </c>
+      <c r="AA188">
+        <v>3.59</v>
+      </c>
+      <c r="AB188">
+        <v>4.3</v>
+      </c>
+      <c r="AC188">
+        <v>1.05</v>
+      </c>
+      <c r="AD188">
+        <v>9</v>
+      </c>
+      <c r="AE188">
+        <v>1.3</v>
+      </c>
+      <c r="AF188">
+        <v>3.4</v>
+      </c>
+      <c r="AG188">
+        <v>1.91</v>
+      </c>
+      <c r="AH188">
+        <v>1.83</v>
+      </c>
+      <c r="AI188">
+        <v>1.83</v>
+      </c>
+      <c r="AJ188">
+        <v>1.85</v>
+      </c>
+      <c r="AK188">
+        <v>1.22</v>
+      </c>
+      <c r="AL188">
+        <v>1.27</v>
+      </c>
+      <c r="AM188">
+        <v>1.95</v>
+      </c>
+      <c r="AN188">
+        <v>1.64</v>
+      </c>
+      <c r="AO188">
+        <v>0.91</v>
+      </c>
+      <c r="AP188">
+        <v>1.58</v>
+      </c>
+      <c r="AQ188">
+        <v>0.92</v>
+      </c>
+      <c r="AR188">
+        <v>1.65</v>
+      </c>
+      <c r="AS188">
+        <v>0.97</v>
+      </c>
+      <c r="AT188">
+        <v>2.62</v>
+      </c>
+      <c r="AU188">
+        <v>4</v>
+      </c>
+      <c r="AV188">
+        <v>4</v>
+      </c>
+      <c r="AW188">
+        <v>11</v>
+      </c>
+      <c r="AX188">
+        <v>9</v>
+      </c>
+      <c r="AY188">
+        <v>18</v>
+      </c>
+      <c r="AZ188">
+        <v>17</v>
+      </c>
+      <c r="BA188">
+        <v>4</v>
+      </c>
+      <c r="BB188">
+        <v>6</v>
+      </c>
+      <c r="BC188">
+        <v>10</v>
+      </c>
+      <c r="BD188">
+        <v>1.5</v>
+      </c>
+      <c r="BE188">
+        <v>6.75</v>
+      </c>
+      <c r="BF188">
+        <v>2.8</v>
+      </c>
+      <c r="BG188">
+        <v>1.28</v>
+      </c>
+      <c r="BH188">
+        <v>3.2</v>
+      </c>
+      <c r="BI188">
+        <v>1.49</v>
+      </c>
+      <c r="BJ188">
+        <v>2.4</v>
+      </c>
+      <c r="BK188">
+        <v>1.75</v>
+      </c>
+      <c r="BL188">
+        <v>1.95</v>
+      </c>
+      <c r="BM188">
+        <v>2.2</v>
+      </c>
+      <c r="BN188">
+        <v>1.57</v>
+      </c>
+      <c r="BO188">
+        <v>2.8</v>
+      </c>
+      <c r="BP188">
+        <v>1.36</v>
+      </c>
+    </row>
+    <row r="189" spans="1:68">
+      <c r="A189" s="1">
+        <v>188</v>
+      </c>
+      <c r="B189">
+        <v>7453606</v>
+      </c>
+      <c r="C189" t="s">
+        <v>68</v>
+      </c>
+      <c r="D189" t="s">
+        <v>69</v>
+      </c>
+      <c r="E189" s="2">
+        <v>45689.69791666666</v>
+      </c>
+      <c r="F189">
+        <v>24</v>
+      </c>
+      <c r="G189" t="s">
+        <v>74</v>
+      </c>
+      <c r="H189" t="s">
+        <v>72</v>
+      </c>
+      <c r="I189">
+        <v>1</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>1</v>
+      </c>
+      <c r="L189">
+        <v>1</v>
+      </c>
+      <c r="M189">
+        <v>0</v>
+      </c>
+      <c r="N189">
+        <v>1</v>
+      </c>
+      <c r="O189" t="s">
+        <v>222</v>
+      </c>
+      <c r="P189" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q189">
+        <v>1.73</v>
+      </c>
+      <c r="R189">
+        <v>2.65</v>
+      </c>
+      <c r="S189">
+        <v>6.25</v>
+      </c>
+      <c r="T189">
+        <v>1.23</v>
+      </c>
+      <c r="U189">
+        <v>3.7</v>
+      </c>
+      <c r="V189">
+        <v>2.1</v>
+      </c>
+      <c r="W189">
+        <v>1.65</v>
+      </c>
+      <c r="X189">
+        <v>4.5</v>
+      </c>
+      <c r="Y189">
+        <v>1.17</v>
+      </c>
+      <c r="Z189">
+        <v>1.29</v>
+      </c>
+      <c r="AA189">
+        <v>5.8</v>
+      </c>
+      <c r="AB189">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AC189">
+        <v>1.01</v>
+      </c>
+      <c r="AD189">
+        <v>17</v>
+      </c>
+      <c r="AE189">
+        <v>1.15</v>
+      </c>
+      <c r="AF189">
+        <v>5.25</v>
+      </c>
+      <c r="AG189">
+        <v>1.39</v>
+      </c>
+      <c r="AH189">
+        <v>2.86</v>
+      </c>
+      <c r="AI189">
+        <v>1.75</v>
+      </c>
+      <c r="AJ189">
+        <v>1.95</v>
+      </c>
+      <c r="AK189">
+        <v>1.08</v>
+      </c>
+      <c r="AL189">
+        <v>1.14</v>
+      </c>
+      <c r="AM189">
+        <v>3.25</v>
+      </c>
+      <c r="AN189">
+        <v>2.82</v>
+      </c>
+      <c r="AO189">
+        <v>0.09</v>
+      </c>
+      <c r="AP189">
+        <v>2.83</v>
+      </c>
+      <c r="AQ189">
+        <v>0.08</v>
+      </c>
+      <c r="AR189">
+        <v>1.74</v>
+      </c>
+      <c r="AS189">
+        <v>1.08</v>
+      </c>
+      <c r="AT189">
+        <v>2.82</v>
+      </c>
+      <c r="AU189">
+        <v>6</v>
+      </c>
+      <c r="AV189">
+        <v>0</v>
+      </c>
+      <c r="AW189">
+        <v>9</v>
+      </c>
+      <c r="AX189">
+        <v>7</v>
+      </c>
+      <c r="AY189">
+        <v>19</v>
+      </c>
+      <c r="AZ189">
+        <v>9</v>
+      </c>
+      <c r="BA189">
+        <v>7</v>
+      </c>
+      <c r="BB189">
+        <v>2</v>
+      </c>
+      <c r="BC189">
+        <v>9</v>
+      </c>
+      <c r="BD189">
+        <v>1.24</v>
+      </c>
+      <c r="BE189">
+        <v>8.5</v>
+      </c>
+      <c r="BF189">
+        <v>4.4</v>
+      </c>
+      <c r="BG189">
+        <v>1.25</v>
+      </c>
+      <c r="BH189">
+        <v>3.45</v>
+      </c>
+      <c r="BI189">
+        <v>1.44</v>
+      </c>
+      <c r="BJ189">
+        <v>2.55</v>
+      </c>
+      <c r="BK189">
+        <v>1.7</v>
+      </c>
+      <c r="BL189">
+        <v>2.05</v>
+      </c>
+      <c r="BM189">
+        <v>2.08</v>
+      </c>
+      <c r="BN189">
+        <v>1.65</v>
+      </c>
+      <c r="BO189">
+        <v>2.65</v>
+      </c>
+      <c r="BP189">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="190" spans="1:68">
+      <c r="A190" s="1">
+        <v>189</v>
+      </c>
+      <c r="B190">
+        <v>7453608</v>
+      </c>
+      <c r="C190" t="s">
+        <v>68</v>
+      </c>
+      <c r="D190" t="s">
+        <v>69</v>
+      </c>
+      <c r="E190" s="2">
+        <v>45690.39583333334</v>
+      </c>
+      <c r="F190">
+        <v>24</v>
+      </c>
+      <c r="G190" t="s">
+        <v>82</v>
+      </c>
+      <c r="H190" t="s">
+        <v>70</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>1</v>
+      </c>
+      <c r="L190">
+        <v>2</v>
+      </c>
+      <c r="M190">
+        <v>1</v>
+      </c>
+      <c r="N190">
+        <v>3</v>
+      </c>
+      <c r="O190" t="s">
+        <v>223</v>
+      </c>
+      <c r="P190" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q190">
+        <v>4.5</v>
+      </c>
+      <c r="R190">
+        <v>2.3</v>
+      </c>
+      <c r="S190">
+        <v>2.38</v>
+      </c>
+      <c r="T190">
+        <v>1.33</v>
+      </c>
+      <c r="U190">
+        <v>3.25</v>
+      </c>
+      <c r="V190">
+        <v>2.63</v>
+      </c>
+      <c r="W190">
+        <v>1.44</v>
+      </c>
+      <c r="X190">
+        <v>6.5</v>
+      </c>
+      <c r="Y190">
+        <v>1.11</v>
+      </c>
+      <c r="Z190">
+        <v>4.1</v>
+      </c>
+      <c r="AA190">
+        <v>3.82</v>
+      </c>
+      <c r="AB190">
+        <v>1.77</v>
+      </c>
+      <c r="AC190">
+        <v>1.03</v>
+      </c>
+      <c r="AD190">
+        <v>15</v>
+      </c>
+      <c r="AE190">
+        <v>1.22</v>
+      </c>
+      <c r="AF190">
+        <v>4.08</v>
+      </c>
+      <c r="AG190">
+        <v>1.65</v>
+      </c>
+      <c r="AH190">
+        <v>2.15</v>
+      </c>
+      <c r="AI190">
+        <v>1.7</v>
+      </c>
+      <c r="AJ190">
+        <v>2.05</v>
+      </c>
+      <c r="AK190">
+        <v>1.98</v>
+      </c>
+      <c r="AL190">
+        <v>1.25</v>
+      </c>
+      <c r="AM190">
+        <v>1.23</v>
+      </c>
+      <c r="AN190">
+        <v>1.82</v>
+      </c>
+      <c r="AO190">
+        <v>1.91</v>
+      </c>
+      <c r="AP190">
+        <v>1.92</v>
+      </c>
+      <c r="AQ190">
+        <v>1.75</v>
+      </c>
+      <c r="AR190">
+        <v>1.72</v>
+      </c>
+      <c r="AS190">
+        <v>1.6</v>
+      </c>
+      <c r="AT190">
+        <v>3.32</v>
+      </c>
+      <c r="AU190">
+        <v>4</v>
+      </c>
+      <c r="AV190">
+        <v>11</v>
+      </c>
+      <c r="AW190">
+        <v>4</v>
+      </c>
+      <c r="AX190">
+        <v>9</v>
+      </c>
+      <c r="AY190">
+        <v>11</v>
+      </c>
+      <c r="AZ190">
+        <v>24</v>
+      </c>
+      <c r="BA190">
+        <v>3</v>
+      </c>
+      <c r="BB190">
+        <v>6</v>
+      </c>
+      <c r="BC190">
+        <v>9</v>
+      </c>
+      <c r="BD190">
+        <v>2.4</v>
+      </c>
+      <c r="BE190">
+        <v>6.4</v>
+      </c>
+      <c r="BF190">
+        <v>1.68</v>
+      </c>
+      <c r="BG190">
+        <v>1.3</v>
+      </c>
+      <c r="BH190">
+        <v>3.15</v>
+      </c>
+      <c r="BI190">
+        <v>1.52</v>
+      </c>
+      <c r="BJ190">
+        <v>2.33</v>
+      </c>
+      <c r="BK190">
+        <v>1.85</v>
+      </c>
+      <c r="BL190">
+        <v>1.85</v>
+      </c>
+      <c r="BM190">
+        <v>2.38</v>
+      </c>
+      <c r="BN190">
+        <v>1.5</v>
+      </c>
+      <c r="BO190">
+        <v>3.05</v>
+      </c>
+      <c r="BP190">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1202" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="306">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -688,6 +688,12 @@
     <t>['86', '90']</t>
   </si>
   <si>
+    <t>['60', '90+6']</t>
+  </si>
+  <si>
+    <t>['27']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -920,6 +926,12 @@
   </si>
   <si>
     <t>['49']</t>
+  </si>
+  <si>
+    <t>['76']</t>
+  </si>
+  <si>
+    <t>['67', '89']</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1293,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP190"/>
+  <dimension ref="A1:BP193"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1537,7 +1549,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1615,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1821,10 +1833,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ3">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2027,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ4">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2233,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ5">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2439,10 +2451,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ6">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2567,7 +2579,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2645,10 +2657,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.18</v>
+        <v>0.79</v>
       </c>
       <c r="AQ7">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2851,10 +2863,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3057,10 +3069,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ9">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3257,25 +3269,25 @@
         <v>3.75</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP10">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ10">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AU10">
         <v>5</v>
@@ -3391,7 +3403,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3463,25 +3475,25 @@
         <v>1.9</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ11">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3669,25 +3681,25 @@
         <v>1.35</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ12">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3803,7 +3815,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3881,19 +3893,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="AQ13">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AU13">
         <v>4</v>
@@ -4009,7 +4021,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4081,25 +4093,25 @@
         <v>1.45</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ14">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AU14">
         <v>8</v>
@@ -4215,7 +4227,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4293,19 +4305,19 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AU15">
         <v>7</v>
@@ -4493,25 +4505,25 @@
         <v>1.15</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ16">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AU16">
         <v>3</v>
@@ -4627,7 +4639,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4699,25 +4711,25 @@
         <v>3.6</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ17">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AU17">
         <v>4</v>
@@ -4905,25 +4917,25 @@
         <v>1.67</v>
       </c>
       <c r="AN18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ18">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR18">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="AS18">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="AT18">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -5111,25 +5123,25 @@
         <v>1.57</v>
       </c>
       <c r="AN19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO19">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ19">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR19">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="AS19">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AT19">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AU19">
         <v>7</v>
@@ -5245,7 +5257,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5320,22 +5332,22 @@
         <v>3</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP20">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR20">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AS20">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AT20">
-        <v>2.85</v>
+        <v>3.09</v>
       </c>
       <c r="AU20">
         <v>10</v>
@@ -5526,22 +5538,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP21">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ21">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR21">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS21">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AT21">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="AU21">
         <v>3</v>
@@ -5657,7 +5669,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5729,25 +5741,25 @@
         <v>1.33</v>
       </c>
       <c r="AN22">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ22">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR22">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AS22">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AT22">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="AU22">
         <v>8</v>
@@ -5863,7 +5875,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -5935,25 +5947,25 @@
         <v>2.62</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ23">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR23">
-        <v>2.53</v>
+        <v>1.91</v>
       </c>
       <c r="AS23">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="AT23">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="AU23">
         <v>9</v>
@@ -6141,25 +6153,25 @@
         <v>1.38</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO24">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP24">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AS24">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AT24">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6275,7 +6287,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6350,22 +6362,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ25">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR25">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AS25">
-        <v>0.78</v>
+        <v>0.62</v>
       </c>
       <c r="AT25">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="AU25">
         <v>9</v>
@@ -6553,16 +6565,16 @@
         <v>2.4</v>
       </c>
       <c r="AN26">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP26">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ26">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
         <v>1.53</v>
@@ -6687,7 +6699,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6759,25 +6771,25 @@
         <v>1.29</v>
       </c>
       <c r="AN27">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ27">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR27">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="AS27">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="AT27">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -6893,7 +6905,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -6968,22 +6980,22 @@
         <v>0</v>
       </c>
       <c r="AO28">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR28">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="AS28">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="AT28">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="AU28">
         <v>5</v>
@@ -7099,7 +7111,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7171,25 +7183,25 @@
         <v>1.33</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO29">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ29">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR29">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="AS29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AT29">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AU29">
         <v>10</v>
@@ -7377,25 +7389,25 @@
         <v>2.05</v>
       </c>
       <c r="AN30">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP30">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AR30">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AS30">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AT30">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7583,25 +7595,25 @@
         <v>1.4</v>
       </c>
       <c r="AN31">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ31">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR31">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AS31">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="AT31">
-        <v>2.74</v>
+        <v>3.13</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7789,25 +7801,25 @@
         <v>1.45</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP32">
-        <v>1.18</v>
+        <v>0.79</v>
       </c>
       <c r="AQ32">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR32">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AS32">
-        <v>0.59</v>
+        <v>0.97</v>
       </c>
       <c r="AT32">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -7995,25 +8007,25 @@
         <v>1.91</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33">
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ33">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="AR33">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="AS33">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AT33">
-        <v>3.32</v>
+        <v>2.84</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8129,7 +8141,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8201,25 +8213,25 @@
         <v>1.85</v>
       </c>
       <c r="AN34">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO34">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ34">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR34">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AS34">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT34">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AU34">
         <v>4</v>
@@ -8410,22 +8422,22 @@
         <v>1.5</v>
       </c>
       <c r="AO35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ35">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR35">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="AS35">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="AT35">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AU35">
         <v>5</v>
@@ -8541,7 +8553,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8616,22 +8628,22 @@
         <v>2</v>
       </c>
       <c r="AO36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ36">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR36">
-        <v>0.9399999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="AS36">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AT36">
-        <v>2.59</v>
+        <v>3.09</v>
       </c>
       <c r="AU36">
         <v>6</v>
@@ -8819,25 +8831,25 @@
         <v>1.09</v>
       </c>
       <c r="AN37">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AO37">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP37">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR37">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="AS37">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AT37">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AU37">
         <v>0</v>
@@ -9025,25 +9037,25 @@
         <v>2</v>
       </c>
       <c r="AN38">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AO38">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ38">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR38">
-        <v>1.16</v>
+        <v>0.84</v>
       </c>
       <c r="AS38">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="AT38">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9237,19 +9249,19 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR39">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="AS39">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="AT39">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9437,25 +9449,25 @@
         <v>2.1</v>
       </c>
       <c r="AN40">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO40">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ40">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="AR40">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AS40">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AT40">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9571,7 +9583,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9643,25 +9655,25 @@
         <v>1.5</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO41">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ41">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR41">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AS41">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AT41">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -9777,7 +9789,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9849,25 +9861,25 @@
         <v>1.43</v>
       </c>
       <c r="AN42">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AO42">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ42">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR42">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="AS42">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AT42">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -10055,25 +10067,25 @@
         <v>1.85</v>
       </c>
       <c r="AN43">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO43">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ43">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR43">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AS43">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="AT43">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AU43">
         <v>5</v>
@@ -10261,25 +10273,25 @@
         <v>2.4</v>
       </c>
       <c r="AN44">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP44">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR44">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AS44">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AT44">
-        <v>3.29</v>
+        <v>3.49</v>
       </c>
       <c r="AU44">
         <v>11</v>
@@ -10470,22 +10482,22 @@
         <v>1.5</v>
       </c>
       <c r="AO45">
+        <v>1.2</v>
+      </c>
+      <c r="AP45">
         <v>1.5</v>
       </c>
-      <c r="AP45">
-        <v>1.64</v>
-      </c>
       <c r="AQ45">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AR45">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AS45">
-        <v>1.18</v>
+        <v>1.71</v>
       </c>
       <c r="AT45">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AU45">
         <v>9</v>
@@ -10673,25 +10685,25 @@
         <v>1.77</v>
       </c>
       <c r="AN46">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AO46">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP46">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ46">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR46">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AS46">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AT46">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="AU46">
         <v>7</v>
@@ -10879,25 +10891,25 @@
         <v>1.7</v>
       </c>
       <c r="AN47">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AO47">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AP47">
-        <v>1.18</v>
+        <v>0.79</v>
       </c>
       <c r="AQ47">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR47">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="AS47">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="AT47">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -11013,7 +11025,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11085,25 +11097,25 @@
         <v>1.7</v>
       </c>
       <c r="AN48">
+        <v>1.83</v>
+      </c>
+      <c r="AO48">
         <v>1.33</v>
       </c>
-      <c r="AO48">
-        <v>0.33</v>
-      </c>
       <c r="AP48">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ48">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR48">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AS48">
-        <v>0.51</v>
+        <v>0.79</v>
       </c>
       <c r="AT48">
-        <v>1.66</v>
+        <v>2.09</v>
       </c>
       <c r="AU48">
         <v>4</v>
@@ -11219,7 +11231,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11291,25 +11303,25 @@
         <v>1.5</v>
       </c>
       <c r="AN49">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AO49">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ49">
+        <v>2.25</v>
+      </c>
+      <c r="AR49">
         <v>1.67</v>
       </c>
-      <c r="AR49">
-        <v>2.18</v>
-      </c>
       <c r="AS49">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AT49">
-        <v>3.77</v>
+        <v>3.32</v>
       </c>
       <c r="AU49">
         <v>3</v>
@@ -11425,7 +11437,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11497,25 +11509,25 @@
         <v>1.1</v>
       </c>
       <c r="AN50">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO50">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP50">
-        <v>1.18</v>
+        <v>0.79</v>
       </c>
       <c r="AQ50">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR50">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AS50">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AT50">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11631,7 +11643,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11703,25 +11715,25 @@
         <v>2.05</v>
       </c>
       <c r="AN51">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AO51">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP51">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ51">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="AR51">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AS51">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AT51">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="AU51">
         <v>9</v>
@@ -11909,25 +11921,25 @@
         <v>1.54</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO52">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR52">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AS52">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AT52">
-        <v>3.53</v>
+        <v>3.33</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12115,25 +12127,25 @@
         <v>1.37</v>
       </c>
       <c r="AN53">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO53">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="AQ53">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR53">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="AS53">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AT53">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AU53">
         <v>5</v>
@@ -12321,25 +12333,25 @@
         <v>2.21</v>
       </c>
       <c r="AN54">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO54">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AP54">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR54">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AS54">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="AT54">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AU54">
         <v>13</v>
@@ -12527,25 +12539,25 @@
         <v>2.17</v>
       </c>
       <c r="AN55">
+        <v>1.4</v>
+      </c>
+      <c r="AO55">
         <v>1.33</v>
       </c>
-      <c r="AO55">
-        <v>1.67</v>
-      </c>
       <c r="AP55">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ55">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR55">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="AS55">
-        <v>0.98</v>
+        <v>1.24</v>
       </c>
       <c r="AT55">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AU55">
         <v>8</v>
@@ -12661,7 +12673,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -12733,25 +12745,25 @@
         <v>1.65</v>
       </c>
       <c r="AN56">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO56">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AP56">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ56">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR56">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AS56">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AT56">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AU56">
         <v>5</v>
@@ -12939,25 +12951,25 @@
         <v>1.22</v>
       </c>
       <c r="AN57">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO57">
-        <v>0.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR57">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="AS57">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AT57">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -13073,7 +13085,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13145,25 +13157,25 @@
         <v>1.55</v>
       </c>
       <c r="AN58">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AO58">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ58">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR58">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="AS58">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AT58">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AU58">
         <v>0</v>
@@ -13279,7 +13291,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13351,25 +13363,25 @@
         <v>1.38</v>
       </c>
       <c r="AN59">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO59">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP59">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ59">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AR59">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AS59">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AT59">
-        <v>3.03</v>
+        <v>3.22</v>
       </c>
       <c r="AU59">
         <v>7</v>
@@ -13557,25 +13569,25 @@
         <v>1.84</v>
       </c>
       <c r="AN60">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AP60">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ60">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR60">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AS60">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AT60">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AU60">
         <v>5</v>
@@ -13691,7 +13703,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13763,25 +13775,25 @@
         <v>2.5</v>
       </c>
       <c r="AN61">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AO61">
+        <v>1.67</v>
+      </c>
+      <c r="AP61">
+        <v>2</v>
+      </c>
+      <c r="AQ61">
         <v>1.5</v>
       </c>
-      <c r="AP61">
-        <v>2.25</v>
-      </c>
-      <c r="AQ61">
-        <v>1.25</v>
-      </c>
       <c r="AR61">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AS61">
-        <v>0.86</v>
+        <v>1.5</v>
       </c>
       <c r="AT61">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="AU61">
         <v>10</v>
@@ -13969,25 +13981,25 @@
         <v>1.51</v>
       </c>
       <c r="AN62">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AO62">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ62">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR62">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS62">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AT62">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14175,22 +14187,22 @@
         <v>2.3</v>
       </c>
       <c r="AN63">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AO63">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AP63">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ63">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR63">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AS63">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT63">
         <v>3.14</v>
@@ -14381,25 +14393,25 @@
         <v>2</v>
       </c>
       <c r="AN64">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AO64">
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ64">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR64">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS64">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AT64">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="AU64">
         <v>3</v>
@@ -14515,7 +14527,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14587,25 +14599,25 @@
         <v>1.51</v>
       </c>
       <c r="AN65">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AO65">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP65">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ65">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AS65">
-        <v>0.88</v>
+        <v>1.42</v>
       </c>
       <c r="AT65">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14793,25 +14805,25 @@
         <v>1.22</v>
       </c>
       <c r="AN66">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AO66">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AP66">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ66">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR66">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AS66">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AT66">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -14999,25 +15011,25 @@
         <v>2.5</v>
       </c>
       <c r="AN67">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AO67">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AP67">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ67">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR67">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AS67">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AT67">
-        <v>3.01</v>
+        <v>3.18</v>
       </c>
       <c r="AU67">
         <v>6</v>
@@ -15133,7 +15145,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15205,25 +15217,25 @@
         <v>1.44</v>
       </c>
       <c r="AN68">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO68">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ68">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="AR68">
-        <v>1.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS68">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AT68">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AU68">
         <v>4</v>
@@ -15339,7 +15351,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15411,25 +15423,25 @@
         <v>1.35</v>
       </c>
       <c r="AN69">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AO69">
-        <v>2.33</v>
+        <v>1.63</v>
       </c>
       <c r="AP69">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ69">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR69">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AS69">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="AT69">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15617,25 +15629,25 @@
         <v>3.75</v>
       </c>
       <c r="AN70">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AO70">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AP70">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ70">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR70">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AS70">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AT70">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="AU70">
         <v>7</v>
@@ -15823,25 +15835,25 @@
         <v>3</v>
       </c>
       <c r="AN71">
-        <v>2.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO71">
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ71">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR71">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AS71">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="AT71">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="AU71">
         <v>6</v>
@@ -16029,25 +16041,25 @@
         <v>2.2</v>
       </c>
       <c r="AN72">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO72">
-        <v>0.75</v>
+        <v>1.38</v>
       </c>
       <c r="AP72">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR72">
-        <v>1.82</v>
+        <v>1.33</v>
       </c>
       <c r="AS72">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AT72">
-        <v>3.24</v>
+        <v>2.72</v>
       </c>
       <c r="AU72">
         <v>6</v>
@@ -16163,7 +16175,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16235,25 +16247,25 @@
         <v>2.15</v>
       </c>
       <c r="AN73">
-        <v>1.5</v>
+        <v>0.88</v>
       </c>
       <c r="AO73">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP73">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ73">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR73">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AS73">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AT73">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16369,7 +16381,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16441,25 +16453,25 @@
         <v>2.75</v>
       </c>
       <c r="AN74">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AO74">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ74">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR74">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AS74">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="AT74">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AU74">
         <v>10</v>
@@ -16647,25 +16659,25 @@
         <v>1.62</v>
       </c>
       <c r="AN75">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AO75">
-        <v>0.6</v>
+        <v>1.22</v>
       </c>
       <c r="AP75">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ75">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR75">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AS75">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AT75">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16853,25 +16865,25 @@
         <v>1.15</v>
       </c>
       <c r="AN76">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AO76">
+        <v>2.44</v>
+      </c>
+      <c r="AP76">
+        <v>0.79</v>
+      </c>
+      <c r="AQ76">
         <v>2.25</v>
       </c>
-      <c r="AP76">
-        <v>1.18</v>
-      </c>
-      <c r="AQ76">
-        <v>1.67</v>
-      </c>
       <c r="AR76">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AS76">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AT76">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17059,25 +17071,25 @@
         <v>1.33</v>
       </c>
       <c r="AN77">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO77">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AP77">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ77">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR77">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AS77">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AT77">
-        <v>2.48</v>
+        <v>2.79</v>
       </c>
       <c r="AU77">
         <v>3</v>
@@ -17265,25 +17277,25 @@
         <v>2.4</v>
       </c>
       <c r="AN78">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="AO78">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP78">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ78">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR78">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AS78">
-        <v>0.58</v>
+        <v>0.89</v>
       </c>
       <c r="AT78">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17471,25 +17483,25 @@
         <v>2.25</v>
       </c>
       <c r="AN79">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AO79">
-        <v>0.25</v>
+        <v>0.89</v>
       </c>
       <c r="AP79">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ79">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR79">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AS79">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AT79">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="AU79">
         <v>6</v>
@@ -17677,25 +17689,25 @@
         <v>1.86</v>
       </c>
       <c r="AN80">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AO80">
-        <v>0.6</v>
+        <v>1.44</v>
       </c>
       <c r="AP80">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR80">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AS80">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AT80">
-        <v>3.75</v>
+        <v>3.49</v>
       </c>
       <c r="AU80">
         <v>6</v>
@@ -17883,25 +17895,25 @@
         <v>1.33</v>
       </c>
       <c r="AN81">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AO81">
+        <v>1.78</v>
+      </c>
+      <c r="AP81">
+        <v>0.96</v>
+      </c>
+      <c r="AQ81">
         <v>1.5</v>
       </c>
-      <c r="AP81">
-        <v>1.25</v>
-      </c>
-      <c r="AQ81">
-        <v>1.25</v>
-      </c>
       <c r="AR81">
-        <v>0.89</v>
+        <v>1.06</v>
       </c>
       <c r="AS81">
-        <v>0.84</v>
+        <v>1.33</v>
       </c>
       <c r="AT81">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="AU81">
         <v>13</v>
@@ -18089,25 +18101,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AO82">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ82">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR82">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AS82">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AT82">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AU82">
         <v>0</v>
@@ -18223,7 +18235,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18295,25 +18307,25 @@
         <v>1.25</v>
       </c>
       <c r="AN83">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO83">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ83">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR83">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AS83">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AT83">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18501,25 +18513,25 @@
         <v>1.96</v>
       </c>
       <c r="AN84">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AO84">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ84">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR84">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AS84">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AT84">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="AU84">
         <v>7</v>
@@ -18707,25 +18719,25 @@
         <v>2.15</v>
       </c>
       <c r="AN85">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO85">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AP85">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ85">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR85">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AS85">
-        <v>0.91</v>
+        <v>1.31</v>
       </c>
       <c r="AT85">
-        <v>2.58</v>
+        <v>2.87</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18841,7 +18853,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -18913,25 +18925,25 @@
         <v>2.65</v>
       </c>
       <c r="AN86">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AO86">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AP86">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ86">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR86">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AS86">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT86">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="AU86">
         <v>5</v>
@@ -19119,25 +19131,25 @@
         <v>1.38</v>
       </c>
       <c r="AN87">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="AO87">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AP87">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ87">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AR87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AS87">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AT87">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19325,25 +19337,25 @@
         <v>1.38</v>
       </c>
       <c r="AN88">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AO88">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ88">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR88">
-        <v>1.14</v>
+        <v>0.98</v>
       </c>
       <c r="AS88">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AT88">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AU88">
         <v>7</v>
@@ -19531,25 +19543,25 @@
         <v>2.15</v>
       </c>
       <c r="AN89">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AO89">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AP89">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR89">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS89">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AT89">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19737,25 +19749,25 @@
         <v>1.9</v>
       </c>
       <c r="AN90">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="AP90">
-        <v>1.18</v>
+        <v>0.79</v>
       </c>
       <c r="AQ90">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR90">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS90">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="AT90">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="AU90">
         <v>6</v>
@@ -19871,7 +19883,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19943,25 +19955,25 @@
         <v>0</v>
       </c>
       <c r="AN91">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="AO91">
-        <v>0.5</v>
+        <v>1.09</v>
       </c>
       <c r="AP91">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ91">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR91">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AS91">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT91">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20077,7 +20089,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20149,25 +20161,25 @@
         <v>1.45</v>
       </c>
       <c r="AN92">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AO92">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AP92">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ92">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR92">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AS92">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AT92">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="AU92">
         <v>5</v>
@@ -20355,25 +20367,25 @@
         <v>1.49</v>
       </c>
       <c r="AN93">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO93">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AP93">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="AQ93">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="AR93">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AS93">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AT93">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="AU93">
         <v>7</v>
@@ -20489,7 +20501,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20561,25 +20573,25 @@
         <v>2.4</v>
       </c>
       <c r="AN94">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AO94">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AP94">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR94">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AS94">
         <v>1.57</v>
       </c>
       <c r="AT94">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="AU94">
         <v>10</v>
@@ -20767,25 +20779,25 @@
         <v>2.4</v>
       </c>
       <c r="AN95">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AO95">
-        <v>0.8</v>
+        <v>1.36</v>
       </c>
       <c r="AP95">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ95">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR95">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AS95">
-        <v>0.82</v>
+        <v>1.01</v>
       </c>
       <c r="AT95">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AU95">
         <v>6</v>
@@ -20901,7 +20913,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -20973,25 +20985,25 @@
         <v>1.38</v>
       </c>
       <c r="AN96">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AO96">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AP96">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ96">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR96">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="AS96">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AT96">
-        <v>3.66</v>
+        <v>3.19</v>
       </c>
       <c r="AU96">
         <v>0</v>
@@ -21107,7 +21119,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21179,25 +21191,25 @@
         <v>2.7</v>
       </c>
       <c r="AN97">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AO97">
-        <v>0.2</v>
+        <v>0.82</v>
       </c>
       <c r="AP97">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ97">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR97">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AS97">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AT97">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21385,25 +21397,25 @@
         <v>1.98</v>
       </c>
       <c r="AN98">
+        <v>1.25</v>
+      </c>
+      <c r="AO98">
         <v>1.33</v>
       </c>
-      <c r="AO98">
-        <v>1.6</v>
-      </c>
       <c r="AP98">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ98">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR98">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AS98">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AT98">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="AU98">
         <v>9</v>
@@ -21519,7 +21531,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21591,25 +21603,25 @@
         <v>1.6</v>
       </c>
       <c r="AN99">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AO99">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="AP99">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ99">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR99">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS99">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AT99">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AU99">
         <v>5</v>
@@ -21725,7 +21737,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21797,25 +21809,25 @@
         <v>1.26</v>
       </c>
       <c r="AN100">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO100">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ100">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR100">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AS100">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AT100">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21931,7 +21943,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22003,25 +22015,25 @@
         <v>1.28</v>
       </c>
       <c r="AN101">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO101">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ101">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR101">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AS101">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AT101">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="AU101">
         <v>5</v>
@@ -22209,25 +22221,25 @@
         <v>1.83</v>
       </c>
       <c r="AN102">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="AO102">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AP102">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ102">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AR102">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AS102">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AT102">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="AU102">
         <v>8</v>
@@ -22415,25 +22427,25 @@
         <v>1.58</v>
       </c>
       <c r="AN103">
+        <v>1</v>
+      </c>
+      <c r="AO103">
+        <v>1.17</v>
+      </c>
+      <c r="AP103">
+        <v>1.21</v>
+      </c>
+      <c r="AQ103">
         <v>1.33</v>
       </c>
-      <c r="AO103">
-        <v>0.67</v>
-      </c>
-      <c r="AP103">
+      <c r="AR103">
+        <v>1.46</v>
+      </c>
+      <c r="AS103">
         <v>1.58</v>
       </c>
-      <c r="AQ103">
-        <v>0.92</v>
-      </c>
-      <c r="AR103">
-        <v>1.64</v>
-      </c>
-      <c r="AS103">
-        <v>1.41</v>
-      </c>
       <c r="AT103">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22621,25 +22633,25 @@
         <v>2.75</v>
       </c>
       <c r="AN104">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AO104">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ104">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR104">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AS104">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AT104">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="AU104">
         <v>7</v>
@@ -22827,25 +22839,25 @@
         <v>1.24</v>
       </c>
       <c r="AN105">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="AO105">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ105">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR105">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="AS105">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="AT105">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="AU105">
         <v>5</v>
@@ -22961,7 +22973,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23033,25 +23045,25 @@
         <v>1.5</v>
       </c>
       <c r="AN106">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AO106">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AP106">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="AQ106">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR106">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AS106">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AT106">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="AU106">
         <v>6</v>
@@ -23167,7 +23179,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23239,25 +23251,25 @@
         <v>1.22</v>
       </c>
       <c r="AN107">
+        <v>1.08</v>
+      </c>
+      <c r="AO107">
+        <v>1.77</v>
+      </c>
+      <c r="AP107">
+        <v>0.79</v>
+      </c>
+      <c r="AQ107">
         <v>1.67</v>
       </c>
-      <c r="AO107">
-        <v>1.33</v>
-      </c>
-      <c r="AP107">
-        <v>1.18</v>
-      </c>
-      <c r="AQ107">
-        <v>1.42</v>
-      </c>
       <c r="AR107">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AS107">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="AT107">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="AU107">
         <v>6</v>
@@ -23373,7 +23385,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23445,25 +23457,25 @@
         <v>1.38</v>
       </c>
       <c r="AN108">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AO108">
-        <v>0.86</v>
+        <v>1.15</v>
       </c>
       <c r="AP108">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ108">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR108">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AS108">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AT108">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23651,25 +23663,25 @@
         <v>1.8</v>
       </c>
       <c r="AN109">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="AO109">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AP109">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ109">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="AR109">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AS109">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AT109">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23785,7 +23797,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -23857,25 +23869,25 @@
         <v>1.45</v>
       </c>
       <c r="AN110">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AO110">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AP110">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ110">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR110">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AS110">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AT110">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -24063,25 +24075,25 @@
         <v>1.9</v>
       </c>
       <c r="AN111">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AO111">
-        <v>0.67</v>
+        <v>1.38</v>
       </c>
       <c r="AP111">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR111">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AS111">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AT111">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AU111">
         <v>13</v>
@@ -24269,25 +24281,25 @@
         <v>1.65</v>
       </c>
       <c r="AN112">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="AO112">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AP112">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ112">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR112">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AS112">
         <v>1.85</v>
       </c>
       <c r="AT112">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AU112">
         <v>8</v>
@@ -24403,7 +24415,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24475,25 +24487,25 @@
         <v>1.05</v>
       </c>
       <c r="AN113">
-        <v>0.83</v>
+        <v>0.46</v>
       </c>
       <c r="AO113">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AP113">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ113">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR113">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="AS113">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AT113">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="AU113">
         <v>6</v>
@@ -24681,25 +24693,25 @@
         <v>2.5</v>
       </c>
       <c r="AN114">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AO114">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AP114">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ114">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR114">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AS114">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AT114">
-        <v>2.89</v>
+        <v>2.64</v>
       </c>
       <c r="AU114">
         <v>7</v>
@@ -24887,25 +24899,25 @@
         <v>0</v>
       </c>
       <c r="AN115">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AO115">
-        <v>0.71</v>
+        <v>1.21</v>
       </c>
       <c r="AP115">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ115">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR115">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AS115">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AT115">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AU115">
         <v>6</v>
@@ -25093,25 +25105,25 @@
         <v>1.53</v>
       </c>
       <c r="AN116">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AO116">
-        <v>0.67</v>
+        <v>1.07</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ116">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR116">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AS116">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AT116">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AU116">
         <v>5</v>
@@ -25299,25 +25311,25 @@
         <v>2.5</v>
       </c>
       <c r="AN117">
-        <v>2.71</v>
+        <v>2.21</v>
       </c>
       <c r="AO117">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
       <c r="AP117">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ117">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR117">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AS117">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AT117">
-        <v>3.18</v>
+        <v>3.37</v>
       </c>
       <c r="AU117">
         <v>6</v>
@@ -25505,25 +25517,25 @@
         <v>0</v>
       </c>
       <c r="AN118">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AO118">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ118">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR118">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AS118">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="AT118">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AU118">
         <v>11</v>
@@ -25639,7 +25651,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25711,25 +25723,25 @@
         <v>0</v>
       </c>
       <c r="AN119">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AO119">
-        <v>0.71</v>
+        <v>1.36</v>
       </c>
       <c r="AP119">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ119">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR119">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AS119">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AT119">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AU119">
         <v>0</v>
@@ -25917,25 +25929,25 @@
         <v>1.88</v>
       </c>
       <c r="AN120">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AO120">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AP120">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ120">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR120">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AS120">
-        <v>0.99</v>
+        <v>1.34</v>
       </c>
       <c r="AT120">
-        <v>2.63</v>
+        <v>2.87</v>
       </c>
       <c r="AU120">
         <v>12</v>
@@ -26123,25 +26135,25 @@
         <v>2.15</v>
       </c>
       <c r="AN121">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AO121">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ121">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR121">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AS121">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AT121">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AU121">
         <v>7</v>
@@ -26257,7 +26269,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26329,25 +26341,25 @@
         <v>1.38</v>
       </c>
       <c r="AN122">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="AO122">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="AP122">
-        <v>1.18</v>
+        <v>0.79</v>
       </c>
       <c r="AQ122">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR122">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AS122">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AT122">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AU122">
         <v>6</v>
@@ -26535,25 +26547,25 @@
         <v>4</v>
       </c>
       <c r="AN123">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AO123">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AP123">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR123">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AS123">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AT123">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="AU123">
         <v>9</v>
@@ -26741,25 +26753,25 @@
         <v>1.92</v>
       </c>
       <c r="AN124">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AO124">
-        <v>0.57</v>
+        <v>1.4</v>
       </c>
       <c r="AP124">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ124">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR124">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AS124">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="AT124">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AU124">
         <v>3</v>
@@ -26875,7 +26887,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -26947,22 +26959,22 @@
         <v>1.2</v>
       </c>
       <c r="AN125">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="AO125">
-        <v>1.71</v>
+        <v>2.27</v>
       </c>
       <c r="AP125">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="AQ125">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR125">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AS125">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AT125">
         <v>3.15</v>
@@ -27153,25 +27165,25 @@
         <v>1.36</v>
       </c>
       <c r="AN126">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="AO126">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AP126">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ126">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR126">
         <v>1.26</v>
       </c>
       <c r="AS126">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AT126">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="AU126">
         <v>3</v>
@@ -27287,7 +27299,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27359,25 +27371,25 @@
         <v>1.25</v>
       </c>
       <c r="AN127">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="AO127">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ127">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR127">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="AS127">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AT127">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AU127">
         <v>9</v>
@@ -27565,25 +27577,25 @@
         <v>1.98</v>
       </c>
       <c r="AN128">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO128">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AP128">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ128">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AR128">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AS128">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AT128">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="AU128">
         <v>7</v>
@@ -27699,7 +27711,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27771,25 +27783,25 @@
         <v>1.68</v>
       </c>
       <c r="AN129">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AO129">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AP129">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ129">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR129">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AS129">
-        <v>0.99</v>
+        <v>1.31</v>
       </c>
       <c r="AT129">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AU129">
         <v>9</v>
@@ -27905,7 +27917,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -27977,25 +27989,25 @@
         <v>3.6</v>
       </c>
       <c r="AN130">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="AO130">
-        <v>0.5</v>
+        <v>1.06</v>
       </c>
       <c r="AP130">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ130">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR130">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AS130">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AT130">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AU130">
         <v>7</v>
@@ -28183,25 +28195,25 @@
         <v>1.45</v>
       </c>
       <c r="AN131">
-        <v>2.13</v>
+        <v>1.38</v>
       </c>
       <c r="AO131">
-        <v>0.88</v>
+        <v>1.13</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ131">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR131">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS131">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AT131">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28317,7 +28329,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28389,25 +28401,25 @@
         <v>1.26</v>
       </c>
       <c r="AN132">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO132">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AP132">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ132">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR132">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS132">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AT132">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="AU132">
         <v>6</v>
@@ -28595,25 +28607,25 @@
         <v>1.95</v>
       </c>
       <c r="AN133">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AO133">
-        <v>0.63</v>
+        <v>1.13</v>
       </c>
       <c r="AP133">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ133">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR133">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AS133">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AT133">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28729,7 +28741,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28801,25 +28813,25 @@
         <v>1.77</v>
       </c>
       <c r="AN134">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AO134">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AP134">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ134">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR134">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AS134">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AT134">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU134">
         <v>9</v>
@@ -29007,25 +29019,25 @@
         <v>1.22</v>
       </c>
       <c r="AN135">
-        <v>1.38</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO135">
-        <v>0.75</v>
+        <v>1.44</v>
       </c>
       <c r="AP135">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ135">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR135">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS135">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AT135">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="AU135">
         <v>8</v>
@@ -29141,7 +29153,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29213,25 +29225,25 @@
         <v>3.35</v>
       </c>
       <c r="AN136">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="AO136">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="AP136">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ136">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR136">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AS136">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AT136">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AU136">
         <v>7</v>
@@ -29422,22 +29434,22 @@
         <v>1.13</v>
       </c>
       <c r="AO137">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP137">
+        <v>1.17</v>
+      </c>
+      <c r="AQ137">
         <v>1.08</v>
       </c>
-      <c r="AQ137">
-        <v>0.64</v>
-      </c>
       <c r="AR137">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AS137">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AT137">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AU137">
         <v>2</v>
@@ -29625,25 +29637,25 @@
         <v>1.52</v>
       </c>
       <c r="AN138">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AO138">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AP138">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ138">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AR138">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AS138">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AT138">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AU138">
         <v>7</v>
@@ -29831,25 +29843,25 @@
         <v>1.36</v>
       </c>
       <c r="AN139">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="AO139">
-        <v>0.63</v>
+        <v>1.35</v>
       </c>
       <c r="AP139">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ139">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR139">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AS139">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="AT139">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AU139">
         <v>9</v>
@@ -30037,25 +30049,25 @@
         <v>1.57</v>
       </c>
       <c r="AN140">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AO140">
-        <v>0.78</v>
+        <v>1.24</v>
       </c>
       <c r="AP140">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ140">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR140">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AS140">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AT140">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="AU140">
         <v>3</v>
@@ -30171,7 +30183,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30243,25 +30255,25 @@
         <v>1.66</v>
       </c>
       <c r="AN141">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="AO141">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AP141">
-        <v>1.18</v>
+        <v>0.79</v>
       </c>
       <c r="AQ141">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR141">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AS141">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AT141">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="AU141">
         <v>2</v>
@@ -30449,25 +30461,25 @@
         <v>2.3</v>
       </c>
       <c r="AN142">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AO142">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="AP142">
+        <v>2</v>
+      </c>
+      <c r="AQ142">
         <v>2.25</v>
       </c>
-      <c r="AQ142">
-        <v>1.67</v>
-      </c>
       <c r="AR142">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="AS142">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AT142">
-        <v>3.79</v>
+        <v>3.56</v>
       </c>
       <c r="AU142">
         <v>6</v>
@@ -30583,7 +30595,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30655,25 +30667,25 @@
         <v>2.75</v>
       </c>
       <c r="AN143">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="AO143">
-        <v>0.88</v>
+        <v>1.29</v>
       </c>
       <c r="AP143">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ143">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="AR143">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AS143">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AT143">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="AU143">
         <v>14</v>
@@ -30789,7 +30801,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -30861,25 +30873,25 @@
         <v>1.3</v>
       </c>
       <c r="AN144">
+        <v>1.06</v>
+      </c>
+      <c r="AO144">
+        <v>1.76</v>
+      </c>
+      <c r="AP144">
+        <v>0.96</v>
+      </c>
+      <c r="AQ144">
         <v>1.63</v>
       </c>
-      <c r="AO144">
-        <v>1.5</v>
-      </c>
-      <c r="AP144">
-        <v>1.25</v>
-      </c>
-      <c r="AQ144">
-        <v>1.64</v>
-      </c>
       <c r="AR144">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AS144">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AT144">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AU144">
         <v>7</v>
@@ -31067,25 +31079,25 @@
         <v>2</v>
       </c>
       <c r="AN145">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AO145">
-        <v>0.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP145">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ145">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR145">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AS145">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AT145">
-        <v>2.97</v>
+        <v>2.82</v>
       </c>
       <c r="AU145">
         <v>6</v>
@@ -31201,7 +31213,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31273,25 +31285,25 @@
         <v>1.65</v>
       </c>
       <c r="AN146">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AO146">
-        <v>1</v>
+        <v>1.39</v>
       </c>
       <c r="AP146">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ146">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR146">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AS146">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AT146">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU146">
         <v>7</v>
@@ -31479,25 +31491,25 @@
         <v>1.83</v>
       </c>
       <c r="AN147">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AO147">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ147">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR147">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AS147">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AT147">
-        <v>3.09</v>
+        <v>2.98</v>
       </c>
       <c r="AU147">
         <v>8</v>
@@ -31613,7 +31625,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31688,22 +31700,22 @@
         <v>1.33</v>
       </c>
       <c r="AO148">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AP148">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ148">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AR148">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AS148">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AT148">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="AU148">
         <v>2</v>
@@ -31819,7 +31831,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31891,25 +31903,25 @@
         <v>1.48</v>
       </c>
       <c r="AN149">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
       <c r="AO149">
-        <v>0.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP149">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ149">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR149">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AS149">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AT149">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AU149">
         <v>8</v>
@@ -32097,25 +32109,25 @@
         <v>1.75</v>
       </c>
       <c r="AN150">
-        <v>2.78</v>
+        <v>2.11</v>
       </c>
       <c r="AO150">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AP150">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ150">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR150">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AS150">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AT150">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="AU150">
         <v>7</v>
@@ -32303,25 +32315,25 @@
         <v>1.45</v>
       </c>
       <c r="AN151">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO151">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ151">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR151">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AS151">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AT151">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AU151">
         <v>2</v>
@@ -32437,7 +32449,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32509,22 +32521,22 @@
         <v>1.5</v>
       </c>
       <c r="AN152">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="AO152">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AP152">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ152">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR152">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AS152">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AT152">
         <v>3.43</v>
@@ -32715,25 +32727,25 @@
         <v>1.72</v>
       </c>
       <c r="AN153">
-        <v>1.33</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO153">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AP153">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ153">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR153">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AS153">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT153">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AU153">
         <v>5</v>
@@ -32849,7 +32861,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -32921,25 +32933,25 @@
         <v>1.48</v>
       </c>
       <c r="AN154">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AO154">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AP154">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ154">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR154">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AS154">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AT154">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="AU154">
         <v>4</v>
@@ -33055,7 +33067,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33127,25 +33139,25 @@
         <v>1.38</v>
       </c>
       <c r="AN155">
-        <v>1.44</v>
+        <v>0.95</v>
       </c>
       <c r="AO155">
-        <v>0.7</v>
+        <v>1.26</v>
       </c>
       <c r="AP155">
-        <v>1.18</v>
+        <v>0.79</v>
       </c>
       <c r="AQ155">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR155">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AS155">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AT155">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33261,7 +33273,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33333,25 +33345,25 @@
         <v>3.4</v>
       </c>
       <c r="AN156">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AO156">
-        <v>0.78</v>
+        <v>1.21</v>
       </c>
       <c r="AP156">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ156">
-        <v>0.64</v>
+        <v>1.08</v>
       </c>
       <c r="AR156">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AS156">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AT156">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AU156">
         <v>10</v>
@@ -33539,22 +33551,22 @@
         <v>1.93</v>
       </c>
       <c r="AN157">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AO157">
-        <v>0.67</v>
+        <v>1.26</v>
       </c>
       <c r="AP157">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ157">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR157">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AS157">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AT157">
         <v>2.5</v>
@@ -33673,7 +33685,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -33745,25 +33757,25 @@
         <v>1.3</v>
       </c>
       <c r="AN158">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AO158">
-        <v>0.78</v>
+        <v>1.47</v>
       </c>
       <c r="AP158">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ158">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR158">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AS158">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AT158">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="AU158">
         <v>4</v>
@@ -33951,25 +33963,25 @@
         <v>2.2</v>
       </c>
       <c r="AN159">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AO159">
-        <v>0.11</v>
+        <v>0.63</v>
       </c>
       <c r="AP159">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ159">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR159">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AS159">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT159">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AU159">
         <v>11</v>
@@ -34085,7 +34097,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34157,25 +34169,25 @@
         <v>1.5</v>
       </c>
       <c r="AN160">
-        <v>1.44</v>
+        <v>0.95</v>
       </c>
       <c r="AO160">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AP160">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="AQ160">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR160">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AS160">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AT160">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AU160">
         <v>8</v>
@@ -34291,7 +34303,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34363,25 +34375,25 @@
         <v>2.95</v>
       </c>
       <c r="AN161">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AO161">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AP161">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ161">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR161">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AS161">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT161">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34569,25 +34581,25 @@
         <v>1.83</v>
       </c>
       <c r="AN162">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO162">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AP162">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ162">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR162">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS162">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AT162">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AU162">
         <v>7</v>
@@ -34703,7 +34715,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34775,25 +34787,25 @@
         <v>1.75</v>
       </c>
       <c r="AN163">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AO163">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AP163">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ163">
-        <v>0.73</v>
+        <v>0.96</v>
       </c>
       <c r="AR163">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AS163">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AT163">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AU163">
         <v>7</v>
@@ -34981,22 +34993,22 @@
         <v>2.3</v>
       </c>
       <c r="AN164">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AO164">
-        <v>0.8</v>
+        <v>1.25</v>
       </c>
       <c r="AP164">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ164">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR164">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AS164">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AT164">
         <v>3</v>
@@ -35115,7 +35127,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35187,25 +35199,25 @@
         <v>1.34</v>
       </c>
       <c r="AN165">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="AO165">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AP165">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ165">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR165">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AS165">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AT165">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="AU165">
         <v>5</v>
@@ -35321,7 +35333,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35393,25 +35405,25 @@
         <v>1.21</v>
       </c>
       <c r="AN166">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="AO166">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP166">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ166">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AR166">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AS166">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AT166">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AU166">
         <v>8</v>
@@ -35599,25 +35611,25 @@
         <v>1.33</v>
       </c>
       <c r="AN167">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AO167">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AP167">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ167">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AR167">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AS167">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AT167">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="AU167">
         <v>4</v>
@@ -35733,7 +35745,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -35805,25 +35817,25 @@
         <v>1.32</v>
       </c>
       <c r="AN168">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AO168">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AP168">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ168">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR168">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AS168">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AT168">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="AU168">
         <v>6</v>
@@ -36011,25 +36023,25 @@
         <v>1.62</v>
       </c>
       <c r="AN169">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AO169">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="AP169">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ169">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR169">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS169">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AT169">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AU169">
         <v>8</v>
@@ -36217,25 +36229,25 @@
         <v>1.72</v>
       </c>
       <c r="AN170">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AO170">
-        <v>0.91</v>
+        <v>1.29</v>
       </c>
       <c r="AP170">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AQ170">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AR170">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AS170">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AT170">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AU170">
         <v>4</v>
@@ -36351,7 +36363,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36423,25 +36435,25 @@
         <v>1.41</v>
       </c>
       <c r="AN171">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AO171">
-        <v>0.6</v>
+        <v>1.14</v>
       </c>
       <c r="AP171">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AQ171">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR171">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AS171">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AT171">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AU171">
         <v>2</v>
@@ -36557,7 +36569,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36629,25 +36641,25 @@
         <v>1.41</v>
       </c>
       <c r="AN172">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AO172">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AP172">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AQ172">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR172">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS172">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AT172">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="AU172">
         <v>3</v>
@@ -36763,7 +36775,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36835,25 +36847,25 @@
         <v>5.25</v>
       </c>
       <c r="AN173">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO173">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="AP173">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ173">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR173">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AS173">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AT173">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="AU173">
         <v>10</v>
@@ -36969,7 +36981,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37041,25 +37053,25 @@
         <v>1.26</v>
       </c>
       <c r="AN174">
-        <v>1.3</v>
+        <v>0.86</v>
       </c>
       <c r="AO174">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AP174">
-        <v>1.18</v>
+        <v>0.79</v>
       </c>
       <c r="AQ174">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AR174">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AS174">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AT174">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AU174">
         <v>4</v>
@@ -37247,25 +37259,25 @@
         <v>2.45</v>
       </c>
       <c r="AN175">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AO175">
-        <v>0.73</v>
+        <v>1.19</v>
       </c>
       <c r="AP175">
-        <v>2.18</v>
+        <v>1.79</v>
       </c>
       <c r="AQ175">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AR175">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AS175">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AT175">
-        <v>2.97</v>
+        <v>2.84</v>
       </c>
       <c r="AU175">
         <v>10</v>
@@ -37381,7 +37393,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37453,25 +37465,25 @@
         <v>1.77</v>
       </c>
       <c r="AN176">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="AO176">
-        <v>0.7</v>
+        <v>1.33</v>
       </c>
       <c r="AP176">
-        <v>1.25</v>
+        <v>0.96</v>
       </c>
       <c r="AQ176">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR176">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AS176">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AT176">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AU176">
         <v>3</v>
@@ -37587,7 +37599,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37659,25 +37671,25 @@
         <v>2.05</v>
       </c>
       <c r="AN177">
+        <v>1.57</v>
+      </c>
+      <c r="AO177">
+        <v>1.1</v>
+      </c>
+      <c r="AP177">
+        <v>1.67</v>
+      </c>
+      <c r="AQ177">
+        <v>1.08</v>
+      </c>
+      <c r="AR177">
+        <v>1.45</v>
+      </c>
+      <c r="AS177">
         <v>1.7</v>
       </c>
-      <c r="AO177">
-        <v>0.7</v>
-      </c>
-      <c r="AP177">
-        <v>1.92</v>
-      </c>
-      <c r="AQ177">
-        <v>0.64</v>
-      </c>
-      <c r="AR177">
-        <v>1.71</v>
-      </c>
-      <c r="AS177">
-        <v>1.48</v>
-      </c>
       <c r="AT177">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="AU177">
         <v>8</v>
@@ -37865,25 +37877,25 @@
         <v>1.41</v>
       </c>
       <c r="AN178">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="AO178">
+        <v>1.64</v>
+      </c>
+      <c r="AP178">
+        <v>0.96</v>
+      </c>
+      <c r="AQ178">
+        <v>1.67</v>
+      </c>
+      <c r="AR178">
         <v>1.45</v>
       </c>
-      <c r="AP178">
-        <v>1.25</v>
-      </c>
-      <c r="AQ178">
-        <v>1.42</v>
-      </c>
-      <c r="AR178">
-        <v>1.57</v>
-      </c>
       <c r="AS178">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AT178">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AU178">
         <v>5</v>
@@ -37999,7 +38011,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38071,25 +38083,25 @@
         <v>1.33</v>
       </c>
       <c r="AN179">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="AO179">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="AP179">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AQ179">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="AR179">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AS179">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AT179">
-        <v>3.67</v>
+        <v>3.48</v>
       </c>
       <c r="AU179">
         <v>6</v>
@@ -38205,7 +38217,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38277,25 +38289,25 @@
         <v>1.78</v>
       </c>
       <c r="AN180">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AO180">
-        <v>0.82</v>
+        <v>1.23</v>
       </c>
       <c r="AP180">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ180">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AR180">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AS180">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AT180">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="AU180">
         <v>5</v>
@@ -38483,25 +38495,25 @@
         <v>4.4</v>
       </c>
       <c r="AN181">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AO181">
-        <v>0.45</v>
+        <v>0.82</v>
       </c>
       <c r="AP181">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
-        <v>0.5</v>
+        <v>0.79</v>
       </c>
       <c r="AR181">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AS181">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AT181">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AU181">
         <v>8</v>
@@ -38689,25 +38701,25 @@
         <v>1.65</v>
       </c>
       <c r="AN182">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="AO182">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AP182">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="AQ182">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR182">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AS182">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AT182">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AU182">
         <v>7</v>
@@ -38823,7 +38835,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -38895,25 +38907,25 @@
         <v>1.13</v>
       </c>
       <c r="AN183">
-        <v>1.09</v>
+        <v>0.59</v>
       </c>
       <c r="AO183">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="AP183">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ183">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AR183">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AS183">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AT183">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="AU183">
         <v>5</v>
@@ -39029,7 +39041,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39104,22 +39116,22 @@
         <v>1.64</v>
       </c>
       <c r="AO184">
-        <v>0.9</v>
+        <v>1.23</v>
       </c>
       <c r="AP184">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AQ184">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR184">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AS184">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AT184">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="AU184">
         <v>7</v>
@@ -39307,25 +39319,25 @@
         <v>1.51</v>
       </c>
       <c r="AN185">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="AO185">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AP185">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ185">
+        <v>1.5</v>
+      </c>
+      <c r="AR185">
         <v>1.25</v>
       </c>
-      <c r="AR185">
-        <v>1.29</v>
-      </c>
       <c r="AS185">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AT185">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="AU185">
         <v>3</v>
@@ -39513,25 +39525,25 @@
         <v>1.52</v>
       </c>
       <c r="AN186">
-        <v>1.64</v>
+        <v>1.13</v>
       </c>
       <c r="AO186">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="AP186">
-        <v>1.75</v>
+        <v>1.21</v>
       </c>
       <c r="AQ186">
-        <v>0.75</v>
+        <v>1.13</v>
       </c>
       <c r="AR186">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AS186">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AT186">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AU186">
         <v>2</v>
@@ -39719,25 +39731,25 @@
         <v>2.2</v>
       </c>
       <c r="AN187">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AO187">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AP187">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="AQ187">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="AR187">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AS187">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AT187">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AU187">
         <v>11</v>
@@ -39853,7 +39865,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -39925,25 +39937,25 @@
         <v>1.95</v>
       </c>
       <c r="AN188">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AO188">
-        <v>0.91</v>
+        <v>1.48</v>
       </c>
       <c r="AP188">
-        <v>1.58</v>
+        <v>1.21</v>
       </c>
       <c r="AQ188">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AR188">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AS188">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AT188">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AU188">
         <v>4</v>
@@ -40131,25 +40143,25 @@
         <v>3.25</v>
       </c>
       <c r="AN189">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
       <c r="AO189">
-        <v>0.09</v>
+        <v>0.57</v>
       </c>
       <c r="AP189">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AQ189">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR189">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AS189">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AT189">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="AU189">
         <v>6</v>
@@ -40337,25 +40349,25 @@
         <v>1.23</v>
       </c>
       <c r="AN190">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AO190">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AP190">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AQ190">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AR190">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AS190">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AT190">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="AU190">
         <v>4</v>
@@ -40422,6 +40434,624 @@
       </c>
       <c r="BP190">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="191" spans="1:68">
+      <c r="A191" s="1">
+        <v>190</v>
+      </c>
+      <c r="B191">
+        <v>7453605</v>
+      </c>
+      <c r="C191" t="s">
+        <v>68</v>
+      </c>
+      <c r="D191" t="s">
+        <v>69</v>
+      </c>
+      <c r="E191" s="2">
+        <v>45690.5</v>
+      </c>
+      <c r="F191">
+        <v>24</v>
+      </c>
+      <c r="G191" t="s">
+        <v>78</v>
+      </c>
+      <c r="H191" t="s">
+        <v>81</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>0</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>2</v>
+      </c>
+      <c r="M191">
+        <v>1</v>
+      </c>
+      <c r="N191">
+        <v>3</v>
+      </c>
+      <c r="O191" t="s">
+        <v>224</v>
+      </c>
+      <c r="P191" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q191">
+        <v>1.95</v>
+      </c>
+      <c r="R191">
+        <v>2.5</v>
+      </c>
+      <c r="S191">
+        <v>6.5</v>
+      </c>
+      <c r="T191">
+        <v>1.3</v>
+      </c>
+      <c r="U191">
+        <v>3.4</v>
+      </c>
+      <c r="V191">
+        <v>2.5</v>
+      </c>
+      <c r="W191">
+        <v>1.5</v>
+      </c>
+      <c r="X191">
+        <v>6</v>
+      </c>
+      <c r="Y191">
+        <v>1.13</v>
+      </c>
+      <c r="Z191">
+        <v>1.43</v>
+      </c>
+      <c r="AA191">
+        <v>4.2</v>
+      </c>
+      <c r="AB191">
+        <v>7.4</v>
+      </c>
+      <c r="AC191">
+        <v>1.03</v>
+      </c>
+      <c r="AD191">
+        <v>15</v>
+      </c>
+      <c r="AE191">
+        <v>1.19</v>
+      </c>
+      <c r="AF191">
+        <v>4.45</v>
+      </c>
+      <c r="AG191">
+        <v>1.7</v>
+      </c>
+      <c r="AH191">
+        <v>2.05</v>
+      </c>
+      <c r="AI191">
+        <v>1.8</v>
+      </c>
+      <c r="AJ191">
+        <v>1.95</v>
+      </c>
+      <c r="AK191">
+        <v>1.11</v>
+      </c>
+      <c r="AL191">
+        <v>1.19</v>
+      </c>
+      <c r="AM191">
+        <v>2.7</v>
+      </c>
+      <c r="AN191">
+        <v>1.74</v>
+      </c>
+      <c r="AO191">
+        <v>1</v>
+      </c>
+      <c r="AP191">
+        <v>1.79</v>
+      </c>
+      <c r="AQ191">
+        <v>0.96</v>
+      </c>
+      <c r="AR191">
+        <v>1.61</v>
+      </c>
+      <c r="AS191">
+        <v>1.47</v>
+      </c>
+      <c r="AT191">
+        <v>3.08</v>
+      </c>
+      <c r="AU191">
+        <v>3</v>
+      </c>
+      <c r="AV191">
+        <v>4</v>
+      </c>
+      <c r="AW191">
+        <v>12</v>
+      </c>
+      <c r="AX191">
+        <v>5</v>
+      </c>
+      <c r="AY191">
+        <v>17</v>
+      </c>
+      <c r="AZ191">
+        <v>10</v>
+      </c>
+      <c r="BA191">
+        <v>6</v>
+      </c>
+      <c r="BB191">
+        <v>6</v>
+      </c>
+      <c r="BC191">
+        <v>12</v>
+      </c>
+      <c r="BD191">
+        <v>1.26</v>
+      </c>
+      <c r="BE191">
+        <v>8</v>
+      </c>
+      <c r="BF191">
+        <v>4.1</v>
+      </c>
+      <c r="BG191">
+        <v>1.24</v>
+      </c>
+      <c r="BH191">
+        <v>3.55</v>
+      </c>
+      <c r="BI191">
+        <v>1.43</v>
+      </c>
+      <c r="BJ191">
+        <v>2.6</v>
+      </c>
+      <c r="BK191">
+        <v>1.7</v>
+      </c>
+      <c r="BL191">
+        <v>2.05</v>
+      </c>
+      <c r="BM191">
+        <v>2.05</v>
+      </c>
+      <c r="BN191">
+        <v>1.68</v>
+      </c>
+      <c r="BO191">
+        <v>2.55</v>
+      </c>
+      <c r="BP191">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="192" spans="1:68">
+      <c r="A192" s="1">
+        <v>191</v>
+      </c>
+      <c r="B192">
+        <v>7453607</v>
+      </c>
+      <c r="C192" t="s">
+        <v>68</v>
+      </c>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" s="2">
+        <v>45690.60416666666</v>
+      </c>
+      <c r="F192">
+        <v>24</v>
+      </c>
+      <c r="G192" t="s">
+        <v>85</v>
+      </c>
+      <c r="H192" t="s">
+        <v>73</v>
+      </c>
+      <c r="I192">
+        <v>1</v>
+      </c>
+      <c r="J192">
+        <v>0</v>
+      </c>
+      <c r="K192">
+        <v>1</v>
+      </c>
+      <c r="L192">
+        <v>1</v>
+      </c>
+      <c r="M192">
+        <v>0</v>
+      </c>
+      <c r="N192">
+        <v>1</v>
+      </c>
+      <c r="O192" t="s">
+        <v>220</v>
+      </c>
+      <c r="P192" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q192">
+        <v>3</v>
+      </c>
+      <c r="R192">
+        <v>2.2</v>
+      </c>
+      <c r="S192">
+        <v>3.4</v>
+      </c>
+      <c r="T192">
+        <v>1.36</v>
+      </c>
+      <c r="U192">
+        <v>3</v>
+      </c>
+      <c r="V192">
+        <v>2.75</v>
+      </c>
+      <c r="W192">
+        <v>1.4</v>
+      </c>
+      <c r="X192">
+        <v>7</v>
+      </c>
+      <c r="Y192">
+        <v>1.1</v>
+      </c>
+      <c r="Z192">
+        <v>2.45</v>
+      </c>
+      <c r="AA192">
+        <v>3.45</v>
+      </c>
+      <c r="AB192">
+        <v>2.7</v>
+      </c>
+      <c r="AC192">
+        <v>1.05</v>
+      </c>
+      <c r="AD192">
+        <v>12</v>
+      </c>
+      <c r="AE192">
+        <v>1.26</v>
+      </c>
+      <c r="AF192">
+        <v>3.67</v>
+      </c>
+      <c r="AG192">
+        <v>1.82</v>
+      </c>
+      <c r="AH192">
+        <v>1.92</v>
+      </c>
+      <c r="AI192">
+        <v>1.67</v>
+      </c>
+      <c r="AJ192">
+        <v>2.1</v>
+      </c>
+      <c r="AK192">
+        <v>1.44</v>
+      </c>
+      <c r="AL192">
+        <v>1.29</v>
+      </c>
+      <c r="AM192">
+        <v>1.53</v>
+      </c>
+      <c r="AN192">
+        <v>1.43</v>
+      </c>
+      <c r="AO192">
+        <v>1.7</v>
+      </c>
+      <c r="AP192">
+        <v>1.5</v>
+      </c>
+      <c r="AQ192">
+        <v>1.63</v>
+      </c>
+      <c r="AR192">
+        <v>1.39</v>
+      </c>
+      <c r="AS192">
+        <v>1.54</v>
+      </c>
+      <c r="AT192">
+        <v>2.93</v>
+      </c>
+      <c r="AU192">
+        <v>8</v>
+      </c>
+      <c r="AV192">
+        <v>4</v>
+      </c>
+      <c r="AW192">
+        <v>5</v>
+      </c>
+      <c r="AX192">
+        <v>8</v>
+      </c>
+      <c r="AY192">
+        <v>14</v>
+      </c>
+      <c r="AZ192">
+        <v>15</v>
+      </c>
+      <c r="BA192">
+        <v>9</v>
+      </c>
+      <c r="BB192">
+        <v>6</v>
+      </c>
+      <c r="BC192">
+        <v>15</v>
+      </c>
+      <c r="BD192">
+        <v>1.94</v>
+      </c>
+      <c r="BE192">
+        <v>6.4</v>
+      </c>
+      <c r="BF192">
+        <v>2.07</v>
+      </c>
+      <c r="BG192">
+        <v>1.3</v>
+      </c>
+      <c r="BH192">
+        <v>3.1</v>
+      </c>
+      <c r="BI192">
+        <v>1.53</v>
+      </c>
+      <c r="BJ192">
+        <v>2.3</v>
+      </c>
+      <c r="BK192">
+        <v>1.75</v>
+      </c>
+      <c r="BL192">
+        <v>1.95</v>
+      </c>
+      <c r="BM192">
+        <v>2.35</v>
+      </c>
+      <c r="BN192">
+        <v>1.5</v>
+      </c>
+      <c r="BO192">
+        <v>3.05</v>
+      </c>
+      <c r="BP192">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="193" spans="1:68">
+      <c r="A193" s="1">
+        <v>192</v>
+      </c>
+      <c r="B193">
+        <v>7453609</v>
+      </c>
+      <c r="C193" t="s">
+        <v>68</v>
+      </c>
+      <c r="D193" t="s">
+        <v>69</v>
+      </c>
+      <c r="E193" s="2">
+        <v>45690.63541666666</v>
+      </c>
+      <c r="F193">
+        <v>24</v>
+      </c>
+      <c r="G193" t="s">
+        <v>75</v>
+      </c>
+      <c r="H193" t="s">
+        <v>77</v>
+      </c>
+      <c r="I193">
+        <v>1</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>1</v>
+      </c>
+      <c r="L193">
+        <v>1</v>
+      </c>
+      <c r="M193">
+        <v>2</v>
+      </c>
+      <c r="N193">
+        <v>3</v>
+      </c>
+      <c r="O193" t="s">
+        <v>225</v>
+      </c>
+      <c r="P193" t="s">
+        <v>305</v>
+      </c>
+      <c r="Q193">
+        <v>3.6</v>
+      </c>
+      <c r="R193">
+        <v>2.25</v>
+      </c>
+      <c r="S193">
+        <v>2.75</v>
+      </c>
+      <c r="T193">
+        <v>1.33</v>
+      </c>
+      <c r="U193">
+        <v>3.25</v>
+      </c>
+      <c r="V193">
+        <v>2.63</v>
+      </c>
+      <c r="W193">
+        <v>1.44</v>
+      </c>
+      <c r="X193">
+        <v>7</v>
+      </c>
+      <c r="Y193">
+        <v>1.1</v>
+      </c>
+      <c r="Z193">
+        <v>3.13</v>
+      </c>
+      <c r="AA193">
+        <v>3.41</v>
+      </c>
+      <c r="AB193">
+        <v>2.19</v>
+      </c>
+      <c r="AC193">
+        <v>1.04</v>
+      </c>
+      <c r="AD193">
+        <v>13</v>
+      </c>
+      <c r="AE193">
+        <v>1.24</v>
+      </c>
+      <c r="AF193">
+        <v>3.89</v>
+      </c>
+      <c r="AG193">
+        <v>1.73</v>
+      </c>
+      <c r="AH193">
+        <v>2</v>
+      </c>
+      <c r="AI193">
+        <v>1.62</v>
+      </c>
+      <c r="AJ193">
+        <v>2.2</v>
+      </c>
+      <c r="AK193">
+        <v>1.65</v>
+      </c>
+      <c r="AL193">
+        <v>1.29</v>
+      </c>
+      <c r="AM193">
+        <v>1.35</v>
+      </c>
+      <c r="AN193">
+        <v>0.83</v>
+      </c>
+      <c r="AO193">
+        <v>1</v>
+      </c>
+      <c r="AP193">
+        <v>0.79</v>
+      </c>
+      <c r="AQ193">
+        <v>1.08</v>
+      </c>
+      <c r="AR193">
+        <v>1.25</v>
+      </c>
+      <c r="AS193">
+        <v>1.73</v>
+      </c>
+      <c r="AT193">
+        <v>2.98</v>
+      </c>
+      <c r="AU193">
+        <v>4</v>
+      </c>
+      <c r="AV193">
+        <v>8</v>
+      </c>
+      <c r="AW193">
+        <v>6</v>
+      </c>
+      <c r="AX193">
+        <v>7</v>
+      </c>
+      <c r="AY193">
+        <v>10</v>
+      </c>
+      <c r="AZ193">
+        <v>17</v>
+      </c>
+      <c r="BA193">
+        <v>5</v>
+      </c>
+      <c r="BB193">
+        <v>6</v>
+      </c>
+      <c r="BC193">
+        <v>11</v>
+      </c>
+      <c r="BD193">
+        <v>2.05</v>
+      </c>
+      <c r="BE193">
+        <v>6.75</v>
+      </c>
+      <c r="BF193">
+        <v>1.92</v>
+      </c>
+      <c r="BG193">
+        <v>1.24</v>
+      </c>
+      <c r="BH193">
+        <v>3.55</v>
+      </c>
+      <c r="BI193">
+        <v>1.43</v>
+      </c>
+      <c r="BJ193">
+        <v>2.63</v>
+      </c>
+      <c r="BK193">
+        <v>1.7</v>
+      </c>
+      <c r="BL193">
+        <v>2.02</v>
+      </c>
+      <c r="BM193">
+        <v>2.05</v>
+      </c>
+      <c r="BN193">
+        <v>1.7</v>
+      </c>
+      <c r="BO193">
+        <v>2.65</v>
+      </c>
+      <c r="BP193">
+        <v>1.41</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -1627,10 +1627,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ2">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1833,10 +1833,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ3">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2039,10 +2039,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ5">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2451,10 +2451,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ6">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2657,10 +2657,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2863,10 +2863,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ8">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3069,10 +3069,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ9">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3269,25 +3269,25 @@
         <v>3.75</v>
       </c>
       <c r="AN10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ10">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR10">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>5</v>
@@ -3475,25 +3475,25 @@
         <v>1.9</v>
       </c>
       <c r="AN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AQ11">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AR11">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3681,25 +3681,25 @@
         <v>1.35</v>
       </c>
       <c r="AN12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ12">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR12">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3893,19 +3893,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR13">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>4</v>
@@ -4093,25 +4093,25 @@
         <v>1.45</v>
       </c>
       <c r="AN14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ14">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AU14">
         <v>8</v>
@@ -4305,19 +4305,19 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ15">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR15">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AU15">
         <v>7</v>
@@ -4505,25 +4505,25 @@
         <v>1.15</v>
       </c>
       <c r="AN16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR16">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AU16">
         <v>3</v>
@@ -4711,25 +4711,25 @@
         <v>3.6</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ17">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR17">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AU17">
         <v>4</v>
@@ -4917,25 +4917,25 @@
         <v>1.67</v>
       </c>
       <c r="AN18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ18">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR18">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS18">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="AT18">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -5123,25 +5123,25 @@
         <v>1.57</v>
       </c>
       <c r="AN19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO19">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ19">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR19">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="AS19">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AT19">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AU19">
         <v>7</v>
@@ -5332,22 +5332,22 @@
         <v>3</v>
       </c>
       <c r="AO20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ20">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR20">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AS20">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AT20">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="AU20">
         <v>10</v>
@@ -5538,22 +5538,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ21">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR21">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS21">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AT21">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="AU21">
         <v>3</v>
@@ -5741,25 +5741,25 @@
         <v>1.33</v>
       </c>
       <c r="AN22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR22">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AS22">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AT22">
-        <v>3.86</v>
+        <v>3.22</v>
       </c>
       <c r="AU22">
         <v>8</v>
@@ -5947,25 +5947,25 @@
         <v>2.62</v>
       </c>
       <c r="AN23">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ23">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR23">
-        <v>1.91</v>
+        <v>2.53</v>
       </c>
       <c r="AS23">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="AT23">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AU23">
         <v>9</v>
@@ -6153,25 +6153,25 @@
         <v>1.38</v>
       </c>
       <c r="AN24">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR24">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AS24">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AT24">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6362,22 +6362,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ25">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR25">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AS25">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AT25">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="AU25">
         <v>9</v>
@@ -6565,16 +6565,16 @@
         <v>2.4</v>
       </c>
       <c r="AN26">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR26">
         <v>1.53</v>
@@ -6771,25 +6771,25 @@
         <v>1.29</v>
       </c>
       <c r="AN27">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR27">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="AS27">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="AT27">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -6980,22 +6980,22 @@
         <v>0</v>
       </c>
       <c r="AO28">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ28">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR28">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AS28">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="AT28">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="AU28">
         <v>5</v>
@@ -7183,25 +7183,25 @@
         <v>1.33</v>
       </c>
       <c r="AN29">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO29">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AQ29">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="AS29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AT29">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AU29">
         <v>10</v>
@@ -7389,25 +7389,25 @@
         <v>2.05</v>
       </c>
       <c r="AN30">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ30">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR30">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AS30">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AT30">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7595,25 +7595,25 @@
         <v>1.4</v>
       </c>
       <c r="AN31">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AO31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ31">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR31">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AS31">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="AT31">
-        <v>3.13</v>
+        <v>2.74</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7801,25 +7801,25 @@
         <v>1.45</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO32">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP32">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AQ32">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR32">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AS32">
-        <v>0.97</v>
+        <v>0.59</v>
       </c>
       <c r="AT32">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -8007,25 +8007,25 @@
         <v>1.91</v>
       </c>
       <c r="AN33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO33">
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ33">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AR33">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="AS33">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AT33">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8213,25 +8213,25 @@
         <v>1.85</v>
       </c>
       <c r="AN34">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AO34">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ34">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR34">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS34">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AT34">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AU34">
         <v>4</v>
@@ -8422,22 +8422,22 @@
         <v>1.5</v>
       </c>
       <c r="AO35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ35">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR35">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="AS35">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
       <c r="AT35">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="AU35">
         <v>5</v>
@@ -8628,22 +8628,22 @@
         <v>2</v>
       </c>
       <c r="AO36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR36">
-        <v>1.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS36">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AT36">
-        <v>3.09</v>
+        <v>2.59</v>
       </c>
       <c r="AU36">
         <v>6</v>
@@ -8831,25 +8831,25 @@
         <v>1.09</v>
       </c>
       <c r="AN37">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO37">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR37">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="AS37">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AT37">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AU37">
         <v>0</v>
@@ -9037,25 +9037,25 @@
         <v>2</v>
       </c>
       <c r="AN38">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AO38">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ38">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR38">
-        <v>0.84</v>
+        <v>1.16</v>
       </c>
       <c r="AS38">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="AT38">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9249,19 +9249,19 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ39">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR39">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AS39">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="AT39">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9449,25 +9449,25 @@
         <v>2.1</v>
       </c>
       <c r="AN40">
+        <v>2</v>
+      </c>
+      <c r="AO40">
+        <v>1.5</v>
+      </c>
+      <c r="AP40">
+        <v>2.83</v>
+      </c>
+      <c r="AQ40">
+        <v>0.83</v>
+      </c>
+      <c r="AR40">
+        <v>1.69</v>
+      </c>
+      <c r="AS40">
         <v>1.75</v>
       </c>
-      <c r="AO40">
-        <v>2</v>
-      </c>
-      <c r="AP40">
-        <v>2.25</v>
-      </c>
-      <c r="AQ40">
-        <v>1.08</v>
-      </c>
-      <c r="AR40">
-        <v>1.64</v>
-      </c>
-      <c r="AS40">
-        <v>1.67</v>
-      </c>
       <c r="AT40">
-        <v>3.31</v>
+        <v>3.44</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9655,25 +9655,25 @@
         <v>1.5</v>
       </c>
       <c r="AN41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO41">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AQ41">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR41">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AS41">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AT41">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -9861,25 +9861,25 @@
         <v>1.43</v>
       </c>
       <c r="AN42">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AO42">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP42">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR42">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="AS42">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AT42">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -10067,25 +10067,25 @@
         <v>1.85</v>
       </c>
       <c r="AN43">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR43">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AS43">
-        <v>0.86</v>
+        <v>0.52</v>
       </c>
       <c r="AT43">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="AU43">
         <v>5</v>
@@ -10273,25 +10273,25 @@
         <v>2.4</v>
       </c>
       <c r="AN44">
+        <v>2</v>
+      </c>
+      <c r="AO44">
+        <v>0.5</v>
+      </c>
+      <c r="AP44">
+        <v>2.25</v>
+      </c>
+      <c r="AQ44">
+        <v>0.83</v>
+      </c>
+      <c r="AR44">
+        <v>1.89</v>
+      </c>
+      <c r="AS44">
         <v>1.4</v>
       </c>
-      <c r="AO44">
-        <v>1</v>
-      </c>
-      <c r="AP44">
-        <v>2</v>
-      </c>
-      <c r="AQ44">
-        <v>1.21</v>
-      </c>
-      <c r="AR44">
-        <v>1.7</v>
-      </c>
-      <c r="AS44">
-        <v>1.79</v>
-      </c>
       <c r="AT44">
-        <v>3.49</v>
+        <v>3.29</v>
       </c>
       <c r="AU44">
         <v>11</v>
@@ -10482,22 +10482,22 @@
         <v>1.5</v>
       </c>
       <c r="AO45">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ45">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR45">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AS45">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="AT45">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="AU45">
         <v>9</v>
@@ -10685,25 +10685,25 @@
         <v>1.77</v>
       </c>
       <c r="AN46">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="AO46">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ46">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR46">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AS46">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AT46">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="AU46">
         <v>7</v>
@@ -10891,25 +10891,25 @@
         <v>1.7</v>
       </c>
       <c r="AN47">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AO47">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AQ47">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR47">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="AS47">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="AT47">
-        <v>2.22</v>
+        <v>2.65</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -11097,25 +11097,25 @@
         <v>1.7</v>
       </c>
       <c r="AN48">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AO48">
-        <v>1.33</v>
+        <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ48">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR48">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AS48">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="AT48">
-        <v>2.09</v>
+        <v>1.66</v>
       </c>
       <c r="AU48">
         <v>4</v>
@@ -11303,25 +11303,25 @@
         <v>1.5</v>
       </c>
       <c r="AN49">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AO49">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ49">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR49">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="AS49">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AT49">
-        <v>3.32</v>
+        <v>3.77</v>
       </c>
       <c r="AU49">
         <v>3</v>
@@ -11509,25 +11509,25 @@
         <v>1.1</v>
       </c>
       <c r="AN50">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP50">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AQ50">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR50">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AS50">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AT50">
-        <v>3.23</v>
+        <v>3.33</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11715,25 +11715,25 @@
         <v>2.05</v>
       </c>
       <c r="AN51">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AO51">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ51">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AR51">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AS51">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT51">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="AU51">
         <v>9</v>
@@ -11921,25 +11921,25 @@
         <v>1.54</v>
       </c>
       <c r="AN52">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ52">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR52">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AS52">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AT52">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12127,25 +12127,25 @@
         <v>1.37</v>
       </c>
       <c r="AN53">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO53">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP53">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ53">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR53">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="AS53">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AT53">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AU53">
         <v>5</v>
@@ -12333,25 +12333,25 @@
         <v>2.21</v>
       </c>
       <c r="AN54">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO54">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ54">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR54">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AS54">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT54">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AU54">
         <v>13</v>
@@ -12539,25 +12539,25 @@
         <v>2.17</v>
       </c>
       <c r="AN55">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AO55">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP55">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ55">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR55">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="AS55">
-        <v>1.24</v>
+        <v>0.98</v>
       </c>
       <c r="AT55">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AU55">
         <v>8</v>
@@ -12745,25 +12745,25 @@
         <v>1.65</v>
       </c>
       <c r="AN56">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO56">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ56">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR56">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AS56">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AT56">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AU56">
         <v>5</v>
@@ -12951,25 +12951,25 @@
         <v>1.22</v>
       </c>
       <c r="AN57">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AO57">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ57">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR57">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="AS57">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AT57">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -13157,25 +13157,25 @@
         <v>1.55</v>
       </c>
       <c r="AN58">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="AO58">
-        <v>0.86</v>
+        <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR58">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS58">
         <v>0.93</v>
       </c>
-      <c r="AS58">
-        <v>0.9</v>
-      </c>
       <c r="AT58">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AU58">
         <v>0</v>
@@ -13363,25 +13363,25 @@
         <v>1.38</v>
       </c>
       <c r="AN59">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AO59">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ59">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR59">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AS59">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="AT59">
-        <v>3.22</v>
+        <v>3.03</v>
       </c>
       <c r="AU59">
         <v>7</v>
@@ -13569,25 +13569,25 @@
         <v>1.84</v>
       </c>
       <c r="AN60">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="AO60">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ60">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR60">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AS60">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AT60">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AU60">
         <v>5</v>
@@ -13775,25 +13775,25 @@
         <v>2.5</v>
       </c>
       <c r="AN61">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AO61">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ61">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR61">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AS61">
-        <v>1.5</v>
+        <v>0.86</v>
       </c>
       <c r="AT61">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="AU61">
         <v>10</v>
@@ -13981,25 +13981,25 @@
         <v>1.51</v>
       </c>
       <c r="AN62">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AO62">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AQ62">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR62">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AS62">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AT62">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14187,22 +14187,22 @@
         <v>2.3</v>
       </c>
       <c r="AN63">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AO63">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ63">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR63">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AS63">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AT63">
         <v>3.14</v>
@@ -14393,25 +14393,25 @@
         <v>2</v>
       </c>
       <c r="AN64">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="AO64">
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ64">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR64">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS64">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AT64">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="AU64">
         <v>3</v>
@@ -14599,25 +14599,25 @@
         <v>1.51</v>
       </c>
       <c r="AN65">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AO65">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ65">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR65">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AS65">
-        <v>1.42</v>
+        <v>0.88</v>
       </c>
       <c r="AT65">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14805,25 +14805,25 @@
         <v>1.22</v>
       </c>
       <c r="AN66">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AO66">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ66">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR66">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AS66">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AT66">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -15011,25 +15011,25 @@
         <v>2.5</v>
       </c>
       <c r="AN67">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AO67">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AP67">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ67">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR67">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AS67">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AT67">
-        <v>3.18</v>
+        <v>3.01</v>
       </c>
       <c r="AU67">
         <v>6</v>
@@ -15217,25 +15217,25 @@
         <v>1.44</v>
       </c>
       <c r="AN68">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO68">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ68">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AR68">
-        <v>0.8100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="AS68">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AT68">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AU68">
         <v>4</v>
@@ -15423,25 +15423,25 @@
         <v>1.35</v>
       </c>
       <c r="AN69">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AO69">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ69">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR69">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AS69">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AT69">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15629,25 +15629,25 @@
         <v>3.75</v>
       </c>
       <c r="AN70">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AO70">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ70">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR70">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AS70">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AT70">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="AU70">
         <v>7</v>
@@ -15835,25 +15835,25 @@
         <v>3</v>
       </c>
       <c r="AN71">
-        <v>1.25</v>
+        <v>2.33</v>
       </c>
       <c r="AO71">
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ71">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR71">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AS71">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="AT71">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="AU71">
         <v>6</v>
@@ -16041,25 +16041,25 @@
         <v>2.2</v>
       </c>
       <c r="AN72">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO72">
-        <v>1.38</v>
+        <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ72">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR72">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="AS72">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AT72">
-        <v>2.72</v>
+        <v>3.24</v>
       </c>
       <c r="AU72">
         <v>6</v>
@@ -16247,25 +16247,25 @@
         <v>2.15</v>
       </c>
       <c r="AN73">
-        <v>0.88</v>
+        <v>1.5</v>
       </c>
       <c r="AO73">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ73">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR73">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AS73">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AT73">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16453,25 +16453,25 @@
         <v>2.75</v>
       </c>
       <c r="AN74">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AO74">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ74">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR74">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AS74">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AT74">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AU74">
         <v>10</v>
@@ -16659,25 +16659,25 @@
         <v>1.62</v>
       </c>
       <c r="AN75">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AO75">
-        <v>1.22</v>
+        <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AQ75">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR75">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AS75">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AT75">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16865,25 +16865,25 @@
         <v>1.15</v>
       </c>
       <c r="AN76">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AO76">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AQ76">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR76">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AS76">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AT76">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17071,25 +17071,25 @@
         <v>1.33</v>
       </c>
       <c r="AN77">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO77">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ77">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR77">
+        <v>1.23</v>
+      </c>
+      <c r="AS77">
         <v>1.25</v>
       </c>
-      <c r="AS77">
-        <v>1.54</v>
-      </c>
       <c r="AT77">
-        <v>2.79</v>
+        <v>2.48</v>
       </c>
       <c r="AU77">
         <v>3</v>
@@ -17277,25 +17277,25 @@
         <v>2.4</v>
       </c>
       <c r="AN78">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="AO78">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ78">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR78">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AS78">
-        <v>0.89</v>
+        <v>0.58</v>
       </c>
       <c r="AT78">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17483,25 +17483,25 @@
         <v>2.25</v>
       </c>
       <c r="AN79">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AO79">
-        <v>0.89</v>
+        <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ79">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR79">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AS79">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AT79">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="AU79">
         <v>6</v>
@@ -17689,25 +17689,25 @@
         <v>1.86</v>
       </c>
       <c r="AN80">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AO80">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ80">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR80">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AS80">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AT80">
-        <v>3.49</v>
+        <v>3.75</v>
       </c>
       <c r="AU80">
         <v>6</v>
@@ -17895,25 +17895,25 @@
         <v>1.33</v>
       </c>
       <c r="AN81">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AO81">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR81">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="AS81">
-        <v>1.33</v>
+        <v>0.84</v>
       </c>
       <c r="AT81">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="AU81">
         <v>13</v>
@@ -18101,25 +18101,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AO82">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ82">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR82">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="AS82">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AT82">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AU82">
         <v>0</v>
@@ -18307,25 +18307,25 @@
         <v>1.25</v>
       </c>
       <c r="AN83">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AO83">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP83">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ83">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR83">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AS83">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AT83">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18513,25 +18513,25 @@
         <v>1.96</v>
       </c>
       <c r="AN84">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AO84">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ84">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR84">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AS84">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AT84">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="AU84">
         <v>7</v>
@@ -18719,25 +18719,25 @@
         <v>2.15</v>
       </c>
       <c r="AN85">
+        <v>2.5</v>
+      </c>
+      <c r="AO85">
         <v>1.4</v>
       </c>
-      <c r="AO85">
-        <v>1.7</v>
-      </c>
       <c r="AP85">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ85">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR85">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AS85">
-        <v>1.31</v>
+        <v>0.91</v>
       </c>
       <c r="AT85">
-        <v>2.87</v>
+        <v>2.58</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18925,25 +18925,25 @@
         <v>2.65</v>
       </c>
       <c r="AN86">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AO86">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ86">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR86">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AS86">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT86">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="AU86">
         <v>5</v>
@@ -19131,25 +19131,25 @@
         <v>1.38</v>
       </c>
       <c r="AN87">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AO87">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ87">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR87">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AS87">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="AT87">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19337,25 +19337,25 @@
         <v>1.38</v>
       </c>
       <c r="AN88">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AO88">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AP88">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR88">
-        <v>0.98</v>
+        <v>1.14</v>
       </c>
       <c r="AS88">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT88">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AU88">
         <v>7</v>
@@ -19543,25 +19543,25 @@
         <v>2.15</v>
       </c>
       <c r="AN89">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AO89">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AP89">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AQ89">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR89">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AS89">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AT89">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19749,25 +19749,25 @@
         <v>1.9</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO90">
-        <v>0.45</v>
+        <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AQ90">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR90">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AS90">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AT90">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="AU90">
         <v>6</v>
@@ -19955,25 +19955,25 @@
         <v>0</v>
       </c>
       <c r="AN91">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="AO91">
-        <v>1.09</v>
+        <v>0.5</v>
       </c>
       <c r="AP91">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ91">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR91">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AS91">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AT91">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20161,25 +20161,25 @@
         <v>1.45</v>
       </c>
       <c r="AN92">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AO92">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ92">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR92">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AS92">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AT92">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="AU92">
         <v>5</v>
@@ -20367,25 +20367,25 @@
         <v>1.49</v>
       </c>
       <c r="AN93">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AO93">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AP93">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ93">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AR93">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AS93">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AT93">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="AU93">
         <v>7</v>
@@ -20573,25 +20573,25 @@
         <v>2.4</v>
       </c>
       <c r="AN94">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AO94">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ94">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR94">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AS94">
         <v>1.57</v>
       </c>
       <c r="AT94">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="AU94">
         <v>10</v>
@@ -20779,25 +20779,25 @@
         <v>2.4</v>
       </c>
       <c r="AN95">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AO95">
-        <v>1.36</v>
+        <v>0.8</v>
       </c>
       <c r="AP95">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ95">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR95">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AS95">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="AT95">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AU95">
         <v>6</v>
@@ -20985,25 +20985,25 @@
         <v>1.38</v>
       </c>
       <c r="AN96">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AO96">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ96">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR96">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="AS96">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AT96">
-        <v>3.19</v>
+        <v>3.66</v>
       </c>
       <c r="AU96">
         <v>0</v>
@@ -21191,25 +21191,25 @@
         <v>2.7</v>
       </c>
       <c r="AN97">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AO97">
-        <v>0.82</v>
+        <v>0.2</v>
       </c>
       <c r="AP97">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ97">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR97">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AS97">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AT97">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21397,25 +21397,25 @@
         <v>1.98</v>
       </c>
       <c r="AN98">
+        <v>1.33</v>
+      </c>
+      <c r="AO98">
+        <v>1.6</v>
+      </c>
+      <c r="AP98">
+        <v>1.33</v>
+      </c>
+      <c r="AQ98">
         <v>1.25</v>
       </c>
-      <c r="AO98">
-        <v>1.33</v>
-      </c>
-      <c r="AP98">
-        <v>1.08</v>
-      </c>
-      <c r="AQ98">
-        <v>1.17</v>
-      </c>
       <c r="AR98">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AS98">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AT98">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="AU98">
         <v>9</v>
@@ -21603,25 +21603,25 @@
         <v>1.6</v>
       </c>
       <c r="AN99">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AO99">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="AP99">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ99">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR99">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS99">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AT99">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AU99">
         <v>5</v>
@@ -21809,25 +21809,25 @@
         <v>1.26</v>
       </c>
       <c r="AN100">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AO100">
+        <v>1.67</v>
+      </c>
+      <c r="AP100">
         <v>1.75</v>
       </c>
-      <c r="AP100">
-        <v>1.21</v>
-      </c>
       <c r="AQ100">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR100">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AS100">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AT100">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -22015,25 +22015,25 @@
         <v>1.28</v>
       </c>
       <c r="AN101">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO101">
-        <v>1.25</v>
+        <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AQ101">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR101">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AS101">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AT101">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="AU101">
         <v>5</v>
@@ -22221,25 +22221,25 @@
         <v>1.83</v>
       </c>
       <c r="AN102">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="AO102">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AP102">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ102">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR102">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AS102">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AT102">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="AU102">
         <v>8</v>
@@ -22427,25 +22427,25 @@
         <v>1.58</v>
       </c>
       <c r="AN103">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO103">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ103">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR103">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AS103">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AT103">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22633,25 +22633,25 @@
         <v>2.75</v>
       </c>
       <c r="AN104">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AO104">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AP104">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ104">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR104">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AS104">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AT104">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AU104">
         <v>7</v>
@@ -22839,25 +22839,25 @@
         <v>1.24</v>
       </c>
       <c r="AN105">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="AO105">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP105">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR105">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="AS105">
-        <v>1.24</v>
+        <v>0.93</v>
       </c>
       <c r="AT105">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="AU105">
         <v>5</v>
@@ -23045,25 +23045,25 @@
         <v>1.5</v>
       </c>
       <c r="AN106">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AO106">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AP106">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ106">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR106">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS106">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AT106">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="AU106">
         <v>6</v>
@@ -23251,25 +23251,25 @@
         <v>1.22</v>
       </c>
       <c r="AN107">
+        <v>1.67</v>
+      </c>
+      <c r="AO107">
+        <v>1.33</v>
+      </c>
+      <c r="AP107">
         <v>1.08</v>
       </c>
-      <c r="AO107">
-        <v>1.77</v>
-      </c>
-      <c r="AP107">
-        <v>0.79</v>
-      </c>
       <c r="AQ107">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR107">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AS107">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="AT107">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AU107">
         <v>6</v>
@@ -23457,25 +23457,25 @@
         <v>1.38</v>
       </c>
       <c r="AN108">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AO108">
-        <v>1.15</v>
+        <v>0.86</v>
       </c>
       <c r="AP108">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ108">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR108">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AS108">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AT108">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23663,25 +23663,25 @@
         <v>1.8</v>
       </c>
       <c r="AN109">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AO109">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AP109">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ109">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AR109">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AS109">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AT109">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23869,25 +23869,25 @@
         <v>1.45</v>
       </c>
       <c r="AN110">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="AO110">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ110">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR110">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AS110">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AT110">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -24075,25 +24075,25 @@
         <v>1.9</v>
       </c>
       <c r="AN111">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AO111">
-        <v>1.38</v>
+        <v>0.67</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ111">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR111">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AS111">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AT111">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AU111">
         <v>13</v>
@@ -24281,25 +24281,25 @@
         <v>1.65</v>
       </c>
       <c r="AN112">
-        <v>1.23</v>
+        <v>1.83</v>
       </c>
       <c r="AO112">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AP112">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ112">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR112">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AS112">
         <v>1.85</v>
       </c>
       <c r="AT112">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="AU112">
         <v>8</v>
@@ -24487,25 +24487,25 @@
         <v>1.05</v>
       </c>
       <c r="AN113">
-        <v>0.46</v>
+        <v>0.83</v>
       </c>
       <c r="AO113">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AP113">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ113">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR113">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="AS113">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AT113">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="AU113">
         <v>6</v>
@@ -24693,25 +24693,25 @@
         <v>2.5</v>
       </c>
       <c r="AN114">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AO114">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AP114">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ114">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR114">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS114">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT114">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="AU114">
         <v>7</v>
@@ -24899,25 +24899,25 @@
         <v>0</v>
       </c>
       <c r="AN115">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AO115">
-        <v>1.21</v>
+        <v>0.71</v>
       </c>
       <c r="AP115">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ115">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR115">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AS115">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AT115">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AU115">
         <v>6</v>
@@ -25105,25 +25105,25 @@
         <v>1.53</v>
       </c>
       <c r="AN116">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AO116">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ116">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR116">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AS116">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AT116">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AU116">
         <v>5</v>
@@ -25311,25 +25311,25 @@
         <v>2.5</v>
       </c>
       <c r="AN117">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AO117">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ117">
+        <v>0.92</v>
+      </c>
+      <c r="AR117">
+        <v>1.85</v>
+      </c>
+      <c r="AS117">
         <v>1.33</v>
       </c>
-      <c r="AR117">
-        <v>1.81</v>
-      </c>
-      <c r="AS117">
-        <v>1.56</v>
-      </c>
       <c r="AT117">
-        <v>3.37</v>
+        <v>3.18</v>
       </c>
       <c r="AU117">
         <v>6</v>
@@ -25517,25 +25517,25 @@
         <v>0</v>
       </c>
       <c r="AN118">
+        <v>1.86</v>
+      </c>
+      <c r="AO118">
+        <v>0.14</v>
+      </c>
+      <c r="AP118">
         <v>1.5</v>
       </c>
-      <c r="AO118">
-        <v>0.5</v>
-      </c>
-      <c r="AP118">
-        <v>1.13</v>
-      </c>
       <c r="AQ118">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR118">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AS118">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="AT118">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AU118">
         <v>11</v>
@@ -25723,25 +25723,25 @@
         <v>0</v>
       </c>
       <c r="AN119">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AO119">
-        <v>1.36</v>
+        <v>0.71</v>
       </c>
       <c r="AP119">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ119">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR119">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AS119">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AT119">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AU119">
         <v>0</v>
@@ -25929,25 +25929,25 @@
         <v>1.88</v>
       </c>
       <c r="AN120">
+        <v>1.71</v>
+      </c>
+      <c r="AO120">
+        <v>1.29</v>
+      </c>
+      <c r="AP120">
+        <v>1.75</v>
+      </c>
+      <c r="AQ120">
+        <v>1.25</v>
+      </c>
+      <c r="AR120">
         <v>1.64</v>
       </c>
-      <c r="AO120">
-        <v>1.57</v>
-      </c>
-      <c r="AP120">
-        <v>1.63</v>
-      </c>
-      <c r="AQ120">
-        <v>1.5</v>
-      </c>
-      <c r="AR120">
-        <v>1.53</v>
-      </c>
       <c r="AS120">
-        <v>1.34</v>
+        <v>0.99</v>
       </c>
       <c r="AT120">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="AU120">
         <v>12</v>
@@ -26135,25 +26135,25 @@
         <v>2.15</v>
       </c>
       <c r="AN121">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AO121">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AP121">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ121">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR121">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AS121">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AT121">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AU121">
         <v>7</v>
@@ -26341,25 +26341,25 @@
         <v>1.38</v>
       </c>
       <c r="AN122">
-        <v>0.93</v>
+        <v>1.43</v>
       </c>
       <c r="AO122">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AQ122">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR122">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AS122">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT122">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AU122">
         <v>6</v>
@@ -26547,25 +26547,25 @@
         <v>4</v>
       </c>
       <c r="AN123">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AO123">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ123">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR123">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AS123">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT123">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU123">
         <v>9</v>
@@ -26753,25 +26753,25 @@
         <v>1.92</v>
       </c>
       <c r="AN124">
-        <v>1.13</v>
+        <v>1.86</v>
       </c>
       <c r="AO124">
-        <v>1.4</v>
+        <v>0.57</v>
       </c>
       <c r="AP124">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ124">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR124">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AS124">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="AT124">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AU124">
         <v>3</v>
@@ -26959,22 +26959,22 @@
         <v>1.2</v>
       </c>
       <c r="AN125">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="AO125">
-        <v>2.27</v>
+        <v>1.71</v>
       </c>
       <c r="AP125">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ125">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR125">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AS125">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AT125">
         <v>3.15</v>
@@ -27165,25 +27165,25 @@
         <v>1.36</v>
       </c>
       <c r="AN126">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AO126">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AP126">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ126">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR126">
         <v>1.26</v>
       </c>
       <c r="AS126">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AT126">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="AU126">
         <v>3</v>
@@ -27371,25 +27371,25 @@
         <v>1.25</v>
       </c>
       <c r="AN127">
-        <v>0.47</v>
+        <v>0.86</v>
       </c>
       <c r="AO127">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AP127">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR127">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AS127">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT127">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AU127">
         <v>9</v>
@@ -27577,25 +27577,25 @@
         <v>1.98</v>
       </c>
       <c r="AN128">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO128">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AP128">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ128">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR128">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AS128">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AT128">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="AU128">
         <v>7</v>
@@ -27783,25 +27783,25 @@
         <v>1.68</v>
       </c>
       <c r="AN129">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AO129">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AP129">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ129">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR129">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AS129">
-        <v>1.31</v>
+        <v>0.99</v>
       </c>
       <c r="AT129">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="AU129">
         <v>9</v>
@@ -27989,25 +27989,25 @@
         <v>3.6</v>
       </c>
       <c r="AN130">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="AO130">
-        <v>1.06</v>
+        <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ130">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR130">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AS130">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AT130">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AU130">
         <v>7</v>
@@ -28195,25 +28195,25 @@
         <v>1.45</v>
       </c>
       <c r="AN131">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="AO131">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AP131">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ131">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR131">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AS131">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AT131">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28401,25 +28401,25 @@
         <v>1.26</v>
       </c>
       <c r="AN132">
+        <v>2</v>
+      </c>
+      <c r="AO132">
+        <v>1.75</v>
+      </c>
+      <c r="AP132">
         <v>1.5</v>
       </c>
-      <c r="AO132">
-        <v>1.94</v>
-      </c>
-      <c r="AP132">
-        <v>1.13</v>
-      </c>
       <c r="AQ132">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR132">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AS132">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AT132">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="AU132">
         <v>6</v>
@@ -28607,25 +28607,25 @@
         <v>1.95</v>
       </c>
       <c r="AN133">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="AO133">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="AP133">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ133">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR133">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AS133">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT133">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28813,25 +28813,25 @@
         <v>1.77</v>
       </c>
       <c r="AN134">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AO134">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ134">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR134">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS134">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AT134">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU134">
         <v>9</v>
@@ -29019,25 +29019,25 @@
         <v>1.22</v>
       </c>
       <c r="AN135">
-        <v>0.9399999999999999</v>
+        <v>1.38</v>
       </c>
       <c r="AO135">
-        <v>1.44</v>
+        <v>0.75</v>
       </c>
       <c r="AP135">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ135">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR135">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AS135">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AT135">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="AU135">
         <v>8</v>
@@ -29225,25 +29225,25 @@
         <v>3.35</v>
       </c>
       <c r="AN136">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AO136">
-        <v>0.63</v>
+        <v>0.13</v>
       </c>
       <c r="AP136">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ136">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR136">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AS136">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AT136">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AU136">
         <v>7</v>
@@ -29434,22 +29434,22 @@
         <v>1.13</v>
       </c>
       <c r="AO137">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP137">
+        <v>1.08</v>
+      </c>
+      <c r="AQ137">
+        <v>0.83</v>
+      </c>
+      <c r="AR137">
         <v>1.17</v>
       </c>
-      <c r="AQ137">
-        <v>1.08</v>
-      </c>
-      <c r="AR137">
-        <v>1.13</v>
-      </c>
       <c r="AS137">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AT137">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="AU137">
         <v>2</v>
@@ -29637,25 +29637,25 @@
         <v>1.52</v>
       </c>
       <c r="AN138">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AO138">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AP138">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AQ138">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR138">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AS138">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AT138">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="AU138">
         <v>7</v>
@@ -29843,25 +29843,25 @@
         <v>1.36</v>
       </c>
       <c r="AN139">
-        <v>0.59</v>
+        <v>1.13</v>
       </c>
       <c r="AO139">
-        <v>1.35</v>
+        <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ139">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR139">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AS139">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
       <c r="AT139">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AU139">
         <v>9</v>
@@ -30049,25 +30049,25 @@
         <v>1.57</v>
       </c>
       <c r="AN140">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AO140">
-        <v>1.24</v>
+        <v>0.78</v>
       </c>
       <c r="AP140">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ140">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR140">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AS140">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AT140">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="AU140">
         <v>3</v>
@@ -30255,25 +30255,25 @@
         <v>1.66</v>
       </c>
       <c r="AN141">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="AO141">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AQ141">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR141">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AS141">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AT141">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="AU141">
         <v>2</v>
@@ -30461,25 +30461,25 @@
         <v>2.3</v>
       </c>
       <c r="AN142">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AO142">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ142">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR142">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AS142">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AT142">
-        <v>3.56</v>
+        <v>3.79</v>
       </c>
       <c r="AU142">
         <v>6</v>
@@ -30667,25 +30667,25 @@
         <v>2.75</v>
       </c>
       <c r="AN143">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="AO143">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="AP143">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ143">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AR143">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AS143">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AT143">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="AU143">
         <v>14</v>
@@ -30873,25 +30873,25 @@
         <v>1.3</v>
       </c>
       <c r="AN144">
-        <v>1.06</v>
+        <v>1.63</v>
       </c>
       <c r="AO144">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AP144">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ144">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR144">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AS144">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AT144">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AU144">
         <v>7</v>
@@ -31079,25 +31079,25 @@
         <v>2</v>
       </c>
       <c r="AN145">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AO145">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ145">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR145">
+        <v>1.64</v>
+      </c>
+      <c r="AS145">
         <v>1.33</v>
       </c>
-      <c r="AS145">
-        <v>1.49</v>
-      </c>
       <c r="AT145">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="AU145">
         <v>6</v>
@@ -31285,25 +31285,25 @@
         <v>1.65</v>
       </c>
       <c r="AN146">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AO146">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ146">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR146">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AS146">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AT146">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU146">
         <v>7</v>
@@ -31491,25 +31491,25 @@
         <v>1.83</v>
       </c>
       <c r="AN147">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AO147">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP147">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ147">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR147">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AS147">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AT147">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="AU147">
         <v>8</v>
@@ -31700,22 +31700,22 @@
         <v>1.33</v>
       </c>
       <c r="AO148">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ148">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR148">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AS148">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AT148">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AU148">
         <v>2</v>
@@ -31903,25 +31903,25 @@
         <v>1.48</v>
       </c>
       <c r="AN149">
-        <v>0.61</v>
+        <v>1.11</v>
       </c>
       <c r="AO149">
-        <v>0.9399999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="AP149">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ149">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR149">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AS149">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AT149">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AU149">
         <v>8</v>
@@ -32109,25 +32109,25 @@
         <v>1.75</v>
       </c>
       <c r="AN150">
-        <v>2.11</v>
+        <v>2.78</v>
       </c>
       <c r="AO150">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AP150">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ150">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR150">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AS150">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AT150">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="AU150">
         <v>7</v>
@@ -32315,25 +32315,25 @@
         <v>1.45</v>
       </c>
       <c r="AN151">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO151">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AP151">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ151">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR151">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AS151">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AT151">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AU151">
         <v>2</v>
@@ -32521,22 +32521,22 @@
         <v>1.5</v>
       </c>
       <c r="AN152">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="AO152">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AP152">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ152">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR152">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AS152">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AT152">
         <v>3.43</v>
@@ -32727,25 +32727,25 @@
         <v>1.72</v>
       </c>
       <c r="AN153">
-        <v>0.9399999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="AO153">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ153">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR153">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AS153">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AT153">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="AU153">
         <v>5</v>
@@ -32933,25 +32933,25 @@
         <v>1.48</v>
       </c>
       <c r="AN154">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AO154">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="AP154">
+        <v>1.92</v>
+      </c>
+      <c r="AQ154">
         <v>1.67</v>
       </c>
-      <c r="AQ154">
-        <v>2.25</v>
-      </c>
       <c r="AR154">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AS154">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AT154">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="AU154">
         <v>4</v>
@@ -33139,25 +33139,25 @@
         <v>1.38</v>
       </c>
       <c r="AN155">
-        <v>0.95</v>
+        <v>1.44</v>
       </c>
       <c r="AO155">
-        <v>1.26</v>
+        <v>0.7</v>
       </c>
       <c r="AP155">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AQ155">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR155">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AS155">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AT155">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33345,25 +33345,25 @@
         <v>3.4</v>
       </c>
       <c r="AN156">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AO156">
-        <v>1.21</v>
+        <v>0.78</v>
       </c>
       <c r="AP156">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ156">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AR156">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AS156">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AT156">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="AU156">
         <v>10</v>
@@ -33551,22 +33551,22 @@
         <v>1.93</v>
       </c>
       <c r="AN157">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AO157">
-        <v>1.26</v>
+        <v>0.67</v>
       </c>
       <c r="AP157">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AQ157">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR157">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AS157">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AT157">
         <v>2.5</v>
@@ -33757,25 +33757,25 @@
         <v>1.3</v>
       </c>
       <c r="AN158">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AO158">
-        <v>1.47</v>
+        <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ158">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR158">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AS158">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AT158">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="AU158">
         <v>4</v>
@@ -33963,25 +33963,25 @@
         <v>2.2</v>
       </c>
       <c r="AN159">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AO159">
-        <v>0.63</v>
+        <v>0.11</v>
       </c>
       <c r="AP159">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ159">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR159">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AS159">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT159">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AU159">
         <v>11</v>
@@ -34169,25 +34169,25 @@
         <v>1.5</v>
       </c>
       <c r="AN160">
-        <v>0.95</v>
+        <v>1.44</v>
       </c>
       <c r="AO160">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP160">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ160">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR160">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AS160">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AT160">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AU160">
         <v>8</v>
@@ -34375,25 +34375,25 @@
         <v>2.95</v>
       </c>
       <c r="AN161">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AO161">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ161">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR161">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AS161">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AT161">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34581,25 +34581,25 @@
         <v>1.83</v>
       </c>
       <c r="AN162">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AO162">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ162">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR162">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AS162">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AT162">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AU162">
         <v>7</v>
@@ -34787,25 +34787,25 @@
         <v>1.75</v>
       </c>
       <c r="AN163">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="AO163">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AP163">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ163">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AR163">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AS163">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AT163">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="AU163">
         <v>7</v>
@@ -34993,22 +34993,22 @@
         <v>2.3</v>
       </c>
       <c r="AN164">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AO164">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="AP164">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ164">
+        <v>0.67</v>
+      </c>
+      <c r="AR164">
+        <v>1.79</v>
+      </c>
+      <c r="AS164">
         <v>1.21</v>
-      </c>
-      <c r="AR164">
-        <v>1.75</v>
-      </c>
-      <c r="AS164">
-        <v>1.25</v>
       </c>
       <c r="AT164">
         <v>3</v>
@@ -35199,25 +35199,25 @@
         <v>1.34</v>
       </c>
       <c r="AN165">
-        <v>1.35</v>
+        <v>1.89</v>
       </c>
       <c r="AO165">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="AP165">
+        <v>1.75</v>
+      </c>
+      <c r="AQ165">
         <v>1.33</v>
       </c>
-      <c r="AQ165">
-        <v>1.79</v>
-      </c>
       <c r="AR165">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AS165">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AT165">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="AU165">
         <v>5</v>
@@ -35405,25 +35405,25 @@
         <v>1.21</v>
       </c>
       <c r="AN166">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="AO166">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ166">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR166">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AS166">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AT166">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AU166">
         <v>8</v>
@@ -35611,25 +35611,25 @@
         <v>1.33</v>
       </c>
       <c r="AN167">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AO167">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AP167">
+        <v>1.08</v>
+      </c>
+      <c r="AQ167">
+        <v>1.25</v>
+      </c>
+      <c r="AR167">
+        <v>1.07</v>
+      </c>
+      <c r="AS167">
         <v>1.17</v>
       </c>
-      <c r="AQ167">
-        <v>1.5</v>
-      </c>
-      <c r="AR167">
-        <v>1.09</v>
-      </c>
-      <c r="AS167">
-        <v>1.35</v>
-      </c>
       <c r="AT167">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="AU167">
         <v>4</v>
@@ -35817,25 +35817,25 @@
         <v>1.32</v>
       </c>
       <c r="AN168">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AO168">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AP168">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ168">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR168">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="AS168">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AT168">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="AU168">
         <v>6</v>
@@ -36023,25 +36023,25 @@
         <v>1.62</v>
       </c>
       <c r="AN169">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AO169">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AP169">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ169">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR169">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AS169">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AT169">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="AU169">
         <v>8</v>
@@ -36229,25 +36229,25 @@
         <v>1.72</v>
       </c>
       <c r="AN170">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AO170">
-        <v>1.29</v>
+        <v>0.91</v>
       </c>
       <c r="AP170">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AQ170">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AR170">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AS170">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AT170">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AU170">
         <v>4</v>
@@ -36435,25 +36435,25 @@
         <v>1.41</v>
       </c>
       <c r="AN171">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AO171">
-        <v>1.14</v>
+        <v>0.6</v>
       </c>
       <c r="AP171">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AQ171">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR171">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AS171">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AT171">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AU171">
         <v>2</v>
@@ -36641,25 +36641,25 @@
         <v>1.41</v>
       </c>
       <c r="AN172">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AO172">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AQ172">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR172">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AS172">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AT172">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="AU172">
         <v>3</v>
@@ -36847,25 +36847,25 @@
         <v>5.25</v>
       </c>
       <c r="AN173">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AO173">
-        <v>0.62</v>
+        <v>0.1</v>
       </c>
       <c r="AP173">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ173">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR173">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AS173">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AT173">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="AU173">
         <v>10</v>
@@ -37053,25 +37053,25 @@
         <v>1.26</v>
       </c>
       <c r="AN174">
-        <v>0.86</v>
+        <v>1.3</v>
       </c>
       <c r="AO174">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AQ174">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AR174">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AS174">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AT174">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AU174">
         <v>4</v>
@@ -37259,25 +37259,25 @@
         <v>2.45</v>
       </c>
       <c r="AN175">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AO175">
-        <v>1.19</v>
+        <v>0.73</v>
       </c>
       <c r="AP175">
-        <v>1.79</v>
+        <v>2.25</v>
       </c>
       <c r="AQ175">
-        <v>1.21</v>
+        <v>0.67</v>
       </c>
       <c r="AR175">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AS175">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AT175">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="AU175">
         <v>10</v>
@@ -37465,25 +37465,25 @@
         <v>1.77</v>
       </c>
       <c r="AN176">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AO176">
-        <v>1.33</v>
+        <v>0.7</v>
       </c>
       <c r="AP176">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ176">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR176">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AS176">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AT176">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AU176">
         <v>3</v>
@@ -37671,25 +37671,25 @@
         <v>2.05</v>
       </c>
       <c r="AN177">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AO177">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="AP177">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ177">
-        <v>1.08</v>
+        <v>0.83</v>
       </c>
       <c r="AR177">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="AS177">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AT177">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AU177">
         <v>8</v>
@@ -37877,25 +37877,25 @@
         <v>1.41</v>
       </c>
       <c r="AN178">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="AO178">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AP178">
-        <v>0.96</v>
+        <v>1.25</v>
       </c>
       <c r="AQ178">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AR178">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AS178">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="AT178">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="AU178">
         <v>5</v>
@@ -38083,25 +38083,25 @@
         <v>1.33</v>
       </c>
       <c r="AN179">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="AO179">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AQ179">
-        <v>2.25</v>
+        <v>1.67</v>
       </c>
       <c r="AR179">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AS179">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AT179">
-        <v>3.48</v>
+        <v>3.67</v>
       </c>
       <c r="AU179">
         <v>6</v>
@@ -38289,25 +38289,25 @@
         <v>1.78</v>
       </c>
       <c r="AN180">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AO180">
-        <v>1.23</v>
+        <v>0.82</v>
       </c>
       <c r="AP180">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ180">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AR180">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AS180">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT180">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="AU180">
         <v>5</v>
@@ -38495,25 +38495,25 @@
         <v>4.4</v>
       </c>
       <c r="AN181">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AO181">
-        <v>0.82</v>
+        <v>0.45</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ181">
-        <v>0.79</v>
+        <v>0.5</v>
       </c>
       <c r="AR181">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AS181">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AT181">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AU181">
         <v>8</v>
@@ -38701,25 +38701,25 @@
         <v>1.65</v>
       </c>
       <c r="AN182">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="AO182">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AP182">
-        <v>1.46</v>
+        <v>2</v>
       </c>
       <c r="AQ182">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR182">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AS182">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AT182">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AU182">
         <v>7</v>
@@ -38907,25 +38907,25 @@
         <v>1.13</v>
       </c>
       <c r="AN183">
-        <v>0.59</v>
+        <v>1.09</v>
       </c>
       <c r="AO183">
-        <v>1.68</v>
+        <v>1.18</v>
       </c>
       <c r="AP183">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ183">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AR183">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AS183">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AT183">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AU183">
         <v>5</v>
@@ -39116,22 +39116,22 @@
         <v>1.64</v>
       </c>
       <c r="AO184">
-        <v>1.23</v>
+        <v>0.9</v>
       </c>
       <c r="AP184">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AQ184">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR184">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AS184">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AT184">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="AU184">
         <v>7</v>
@@ -39319,25 +39319,25 @@
         <v>1.51</v>
       </c>
       <c r="AN185">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="AO185">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AP185">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ185">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AR185">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AS185">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AT185">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="AU185">
         <v>3</v>
@@ -39525,25 +39525,25 @@
         <v>1.52</v>
       </c>
       <c r="AN186">
-        <v>1.13</v>
+        <v>1.64</v>
       </c>
       <c r="AO186">
-        <v>1.17</v>
+        <v>0.82</v>
       </c>
       <c r="AP186">
-        <v>1.21</v>
+        <v>1.75</v>
       </c>
       <c r="AQ186">
-        <v>1.13</v>
+        <v>0.75</v>
       </c>
       <c r="AR186">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AS186">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AT186">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AU186">
         <v>2</v>
@@ -39731,25 +39731,25 @@
         <v>2.2</v>
       </c>
       <c r="AN187">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AO187">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AP187">
-        <v>1.33</v>
+        <v>1.75</v>
       </c>
       <c r="AQ187">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AR187">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AS187">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AT187">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="AU187">
         <v>11</v>
@@ -39937,25 +39937,25 @@
         <v>1.95</v>
       </c>
       <c r="AN188">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="AO188">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="AP188">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="AQ188">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AR188">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AS188">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT188">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AU188">
         <v>4</v>
@@ -40143,25 +40143,25 @@
         <v>3.25</v>
       </c>
       <c r="AN189">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="AO189">
-        <v>0.57</v>
+        <v>0.09</v>
       </c>
       <c r="AP189">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AQ189">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR189">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AS189">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AT189">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="AU189">
         <v>6</v>
@@ -40349,25 +40349,25 @@
         <v>1.23</v>
       </c>
       <c r="AN190">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AO190">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AP190">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AQ190">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AR190">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="AS190">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AT190">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="AU190">
         <v>4</v>
@@ -40555,25 +40555,25 @@
         <v>2.7</v>
       </c>
       <c r="AN191">
-        <v>1.74</v>
+        <v>2.18</v>
       </c>
       <c r="AO191">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AP191">
+        <v>2.25</v>
+      </c>
+      <c r="AQ191">
+        <v>0.67</v>
+      </c>
+      <c r="AR191">
         <v>1.79</v>
       </c>
-      <c r="AQ191">
-        <v>0.96</v>
-      </c>
-      <c r="AR191">
-        <v>1.61</v>
-      </c>
       <c r="AS191">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AT191">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="AU191">
         <v>3</v>
@@ -40761,25 +40761,25 @@
         <v>1.53</v>
       </c>
       <c r="AN192">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AO192">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AP192">
+        <v>1.75</v>
+      </c>
+      <c r="AQ192">
         <v>1.5</v>
       </c>
-      <c r="AQ192">
-        <v>1.63</v>
-      </c>
       <c r="AR192">
+        <v>1.52</v>
+      </c>
+      <c r="AS192">
         <v>1.39</v>
       </c>
-      <c r="AS192">
-        <v>1.54</v>
-      </c>
       <c r="AT192">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="AU192">
         <v>8</v>
@@ -40967,25 +40967,25 @@
         <v>1.35</v>
       </c>
       <c r="AN193">
+        <v>1.18</v>
+      </c>
+      <c r="AO193">
+        <v>0.64</v>
+      </c>
+      <c r="AP193">
+        <v>1.08</v>
+      </c>
+      <c r="AQ193">
         <v>0.83</v>
       </c>
-      <c r="AO193">
-        <v>1</v>
-      </c>
-      <c r="AP193">
-        <v>0.79</v>
-      </c>
-      <c r="AQ193">
-        <v>1.08</v>
-      </c>
       <c r="AR193">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AS193">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AT193">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="AU193">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1220" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="308">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -694,6 +694,9 @@
     <t>['27']</t>
   </si>
   <si>
+    <t>['14', '46', '54']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -932,6 +935,9 @@
   </si>
   <si>
     <t>['67', '89']</t>
+  </si>
+  <si>
+    <t>['28', '84', '90+4']</t>
   </si>
 </sst>
 </file>
@@ -1293,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP193"/>
+  <dimension ref="A1:BP194"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1549,7 +1555,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2579,7 +2585,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2660,7 +2666,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ7">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3403,7 +3409,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3481,7 +3487,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11">
         <v>0.83</v>
@@ -3815,7 +3821,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4021,7 +4027,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4227,7 +4233,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4639,7 +4645,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5257,7 +5263,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5669,7 +5675,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5875,7 +5881,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6162,7 +6168,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ24">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR24">
         <v>1.65</v>
@@ -6287,7 +6293,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6699,7 +6705,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6905,7 +6911,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7111,7 +7117,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7189,7 +7195,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ29">
         <v>1.5</v>
@@ -8141,7 +8147,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8553,7 +8559,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9583,7 +9589,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9661,7 +9667,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ41">
         <v>0.92</v>
@@ -9789,7 +9795,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -11025,7 +11031,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11231,7 +11237,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11437,7 +11443,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11643,7 +11649,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12673,7 +12679,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13085,7 +13091,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13291,7 +13297,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13703,7 +13709,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13784,7 +13790,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ61">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR61">
         <v>2.01</v>
@@ -13987,7 +13993,7 @@
         <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ62">
         <v>0.83</v>
@@ -14527,7 +14533,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14608,7 +14614,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ65">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR65">
         <v>1.79</v>
@@ -15145,7 +15151,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15351,7 +15357,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16175,7 +16181,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16381,7 +16387,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16665,7 +16671,7 @@
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ75">
         <v>0.67</v>
@@ -17904,7 +17910,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ81">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR81">
         <v>0.89</v>
@@ -18235,7 +18241,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18728,7 +18734,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ85">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR85">
         <v>1.67</v>
@@ -18853,7 +18859,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19549,7 +19555,7 @@
         <v>0.8</v>
       </c>
       <c r="AP89">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ89">
         <v>0.5</v>
@@ -19883,7 +19889,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20089,7 +20095,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20501,7 +20507,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20913,7 +20919,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21119,7 +21125,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21531,7 +21537,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21737,7 +21743,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21943,7 +21949,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22021,7 +22027,7 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ101">
         <v>1.33</v>
@@ -22848,7 +22854,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR105">
         <v>0.83</v>
@@ -22973,7 +22979,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23179,7 +23185,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23385,7 +23391,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23797,7 +23803,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24415,7 +24421,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -25523,7 +25529,7 @@
         <v>0.14</v>
       </c>
       <c r="AP118">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ118">
         <v>0.08</v>
@@ -25651,7 +25657,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25938,7 +25944,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ120">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR120">
         <v>1.64</v>
@@ -26269,7 +26275,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26887,7 +26893,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27299,7 +27305,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27711,7 +27717,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27792,7 +27798,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ129">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR129">
         <v>1.82</v>
@@ -27917,7 +27923,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28329,7 +28335,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28407,7 +28413,7 @@
         <v>1.75</v>
       </c>
       <c r="AP132">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ132">
         <v>1.75</v>
@@ -28741,7 +28747,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29153,7 +29159,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29643,7 +29649,7 @@
         <v>1.38</v>
       </c>
       <c r="AP138">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ138">
         <v>1.42</v>
@@ -30183,7 +30189,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30595,7 +30601,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30801,7 +30807,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31213,7 +31219,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31625,7 +31631,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31831,7 +31837,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32324,7 +32330,7 @@
         <v>2</v>
       </c>
       <c r="AQ151">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR151">
         <v>1.23</v>
@@ -32449,7 +32455,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32861,7 +32867,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33067,7 +33073,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33273,7 +33279,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33557,7 +33563,7 @@
         <v>0.67</v>
       </c>
       <c r="AP157">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ157">
         <v>0.92</v>
@@ -33685,7 +33691,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34097,7 +34103,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34303,7 +34309,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34715,7 +34721,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35127,7 +35133,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35333,7 +35339,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35620,7 +35626,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ167">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR167">
         <v>1.07</v>
@@ -35745,7 +35751,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36363,7 +36369,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36569,7 +36575,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36647,7 +36653,7 @@
         <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AQ172">
         <v>1.67</v>
@@ -36775,7 +36781,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36981,7 +36987,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37393,7 +37399,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37599,7 +37605,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38011,7 +38017,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38217,7 +38223,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38835,7 +38841,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39041,7 +39047,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39328,7 +39334,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ185">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AR185">
         <v>1.29</v>
@@ -39865,7 +39871,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40483,7 +40489,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40895,7 +40901,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41052,6 +41058,212 @@
       </c>
       <c r="BP193">
         <v>1.41</v>
+      </c>
+    </row>
+    <row r="194" spans="1:68">
+      <c r="A194" s="1">
+        <v>193</v>
+      </c>
+      <c r="B194">
+        <v>7454761</v>
+      </c>
+      <c r="C194" t="s">
+        <v>68</v>
+      </c>
+      <c r="D194" t="s">
+        <v>69</v>
+      </c>
+      <c r="E194" s="2">
+        <v>45695.69791666666</v>
+      </c>
+      <c r="F194">
+        <v>25</v>
+      </c>
+      <c r="G194" t="s">
+        <v>79</v>
+      </c>
+      <c r="H194" t="s">
+        <v>85</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194">
+        <v>1</v>
+      </c>
+      <c r="K194">
+        <v>2</v>
+      </c>
+      <c r="L194">
+        <v>3</v>
+      </c>
+      <c r="M194">
+        <v>3</v>
+      </c>
+      <c r="N194">
+        <v>6</v>
+      </c>
+      <c r="O194" t="s">
+        <v>226</v>
+      </c>
+      <c r="P194" t="s">
+        <v>307</v>
+      </c>
+      <c r="Q194">
+        <v>3</v>
+      </c>
+      <c r="R194">
+        <v>2.2</v>
+      </c>
+      <c r="S194">
+        <v>3.4</v>
+      </c>
+      <c r="T194">
+        <v>1.36</v>
+      </c>
+      <c r="U194">
+        <v>3</v>
+      </c>
+      <c r="V194">
+        <v>2.63</v>
+      </c>
+      <c r="W194">
+        <v>1.44</v>
+      </c>
+      <c r="X194">
+        <v>7</v>
+      </c>
+      <c r="Y194">
+        <v>1.1</v>
+      </c>
+      <c r="Z194">
+        <v>2.37</v>
+      </c>
+      <c r="AA194">
+        <v>3.35</v>
+      </c>
+      <c r="AB194">
+        <v>2.86</v>
+      </c>
+      <c r="AC194">
+        <v>1.05</v>
+      </c>
+      <c r="AD194">
+        <v>9.5</v>
+      </c>
+      <c r="AE194">
+        <v>1.25</v>
+      </c>
+      <c r="AF194">
+        <v>3.7</v>
+      </c>
+      <c r="AG194">
+        <v>1.79</v>
+      </c>
+      <c r="AH194">
+        <v>1.95</v>
+      </c>
+      <c r="AI194">
+        <v>1.62</v>
+      </c>
+      <c r="AJ194">
+        <v>2.2</v>
+      </c>
+      <c r="AK194">
+        <v>1.41</v>
+      </c>
+      <c r="AL194">
+        <v>1.29</v>
+      </c>
+      <c r="AM194">
+        <v>1.55</v>
+      </c>
+      <c r="AN194">
+        <v>1.5</v>
+      </c>
+      <c r="AO194">
+        <v>1.25</v>
+      </c>
+      <c r="AP194">
+        <v>1.46</v>
+      </c>
+      <c r="AQ194">
+        <v>1.23</v>
+      </c>
+      <c r="AR194">
+        <v>1.52</v>
+      </c>
+      <c r="AS194">
+        <v>1.27</v>
+      </c>
+      <c r="AT194">
+        <v>2.79</v>
+      </c>
+      <c r="AU194">
+        <v>8</v>
+      </c>
+      <c r="AV194">
+        <v>7</v>
+      </c>
+      <c r="AW194">
+        <v>9</v>
+      </c>
+      <c r="AX194">
+        <v>9</v>
+      </c>
+      <c r="AY194">
+        <v>17</v>
+      </c>
+      <c r="AZ194">
+        <v>18</v>
+      </c>
+      <c r="BA194">
+        <v>9</v>
+      </c>
+      <c r="BB194">
+        <v>2</v>
+      </c>
+      <c r="BC194">
+        <v>11</v>
+      </c>
+      <c r="BD194">
+        <v>1.82</v>
+      </c>
+      <c r="BE194">
+        <v>6.5</v>
+      </c>
+      <c r="BF194">
+        <v>2.17</v>
+      </c>
+      <c r="BG194">
+        <v>1.27</v>
+      </c>
+      <c r="BH194">
+        <v>3.3</v>
+      </c>
+      <c r="BI194">
+        <v>1.47</v>
+      </c>
+      <c r="BJ194">
+        <v>2.48</v>
+      </c>
+      <c r="BK194">
+        <v>1.75</v>
+      </c>
+      <c r="BL194">
+        <v>1.95</v>
+      </c>
+      <c r="BM194">
+        <v>2.18</v>
+      </c>
+      <c r="BN194">
+        <v>1.58</v>
+      </c>
+      <c r="BO194">
+        <v>2.8</v>
+      </c>
+      <c r="BP194">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="311">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -697,6 +697,15 @@
     <t>['14', '46', '54']</t>
   </si>
   <si>
+    <t>['31']</t>
+  </si>
+  <si>
+    <t>['39', '53']</t>
+  </si>
+  <si>
+    <t>['18', '40']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1299,7 +1308,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP194"/>
+  <dimension ref="A1:BP197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1555,7 +1564,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1633,7 +1642,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ2">
         <v>0.75</v>
@@ -1839,7 +1848,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ3">
         <v>1.33</v>
@@ -2048,7 +2057,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2254,7 +2263,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ5">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2457,7 +2466,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ6">
         <v>0.92</v>
@@ -2585,7 +2594,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3078,7 +3087,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ9">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3409,7 +3418,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3821,7 +3830,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4027,7 +4036,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4233,7 +4242,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4645,7 +4654,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5135,7 +5144,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ19">
         <v>0.5</v>
@@ -5263,7 +5272,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5550,7 +5559,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ21">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR21">
         <v>1.37</v>
@@ -5675,7 +5684,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5753,7 +5762,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ22">
         <v>1.75</v>
@@ -5881,7 +5890,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -5962,7 +5971,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ23">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR23">
         <v>2.53</v>
@@ -6293,7 +6302,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6705,7 +6714,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6911,7 +6920,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7117,7 +7126,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7401,7 +7410,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ30">
         <v>1.42</v>
@@ -7610,7 +7619,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ31">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR31">
         <v>1.23</v>
@@ -8147,7 +8156,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8228,7 +8237,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ34">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR34">
         <v>1.74</v>
@@ -8559,7 +8568,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8637,7 +8646,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ36">
         <v>1.75</v>
@@ -9461,7 +9470,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ40">
         <v>0.83</v>
@@ -9589,7 +9598,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9795,7 +9804,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10285,10 +10294,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ44">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR44">
         <v>1.89</v>
@@ -10906,7 +10915,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ47">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR47">
         <v>1.76</v>
@@ -11031,7 +11040,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11109,7 +11118,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ48">
         <v>0.92</v>
@@ -11237,7 +11246,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11443,7 +11452,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11649,7 +11658,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12142,7 +12151,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ53">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR53">
         <v>0.82</v>
@@ -12679,7 +12688,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13091,7 +13100,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13172,7 +13181,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR58">
         <v>0.9399999999999999</v>
@@ -13297,7 +13306,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13709,7 +13718,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13787,7 +13796,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ61">
         <v>1.23</v>
@@ -13996,7 +14005,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ62">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR62">
         <v>1.5</v>
@@ -14199,7 +14208,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ63">
         <v>1.25</v>
@@ -14533,7 +14542,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15023,7 +15032,7 @@
         <v>1.25</v>
       </c>
       <c r="AP67">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ67">
         <v>0.75</v>
@@ -15151,7 +15160,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15357,7 +15366,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15435,7 +15444,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ69">
         <v>1.5</v>
@@ -16056,7 +16065,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ72">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR72">
         <v>1.82</v>
@@ -16181,7 +16190,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16262,7 +16271,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ73">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR73">
         <v>1.73</v>
@@ -16387,7 +16396,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16674,7 +16683,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ75">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR75">
         <v>1.41</v>
@@ -17083,7 +17092,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ77">
         <v>0.92</v>
@@ -17498,7 +17507,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ79">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR79">
         <v>1.88</v>
@@ -17701,7 +17710,7 @@
         <v>0.6</v>
       </c>
       <c r="AP80">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ80">
         <v>1.33</v>
@@ -18241,7 +18250,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18859,7 +18868,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -18937,10 +18946,10 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ86">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR86">
         <v>1.86</v>
@@ -19889,7 +19898,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -19970,7 +19979,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ91">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR91">
         <v>1.77</v>
@@ -20095,7 +20104,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20173,7 +20182,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ92">
         <v>0.75</v>
@@ -20507,7 +20516,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20585,7 +20594,7 @@
         <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ94">
         <v>1.5</v>
@@ -20919,7 +20928,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21125,7 +21134,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21206,7 +21215,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ97">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -21537,7 +21546,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21618,7 +21627,7 @@
         <v>2</v>
       </c>
       <c r="AQ99">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR99">
         <v>1.16</v>
@@ -21743,7 +21752,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21949,7 +21958,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22233,7 +22242,7 @@
         <v>1.6</v>
       </c>
       <c r="AP102">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ102">
         <v>1.42</v>
@@ -22979,7 +22988,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23185,7 +23194,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23391,7 +23400,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23469,10 +23478,10 @@
         <v>0.86</v>
       </c>
       <c r="AP108">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ108">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR108">
         <v>1.16</v>
@@ -23803,7 +23812,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24421,7 +24430,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24911,10 +24920,10 @@
         <v>0.71</v>
       </c>
       <c r="AP115">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ115">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR115">
         <v>2.07</v>
@@ -25120,7 +25129,7 @@
         <v>2</v>
       </c>
       <c r="AQ116">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR116">
         <v>1.18</v>
@@ -25323,7 +25332,7 @@
         <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ117">
         <v>0.92</v>
@@ -25657,7 +25666,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26275,7 +26284,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26559,7 +26568,7 @@
         <v>1.29</v>
       </c>
       <c r="AP123">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ123">
         <v>1.25</v>
@@ -26893,7 +26902,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27305,7 +27314,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27386,7 +27395,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR127">
         <v>0.92</v>
@@ -27717,7 +27726,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27923,7 +27932,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28001,7 +28010,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ130">
         <v>0.5</v>
@@ -28210,7 +28219,7 @@
         <v>2</v>
       </c>
       <c r="AQ131">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR131">
         <v>1.18</v>
@@ -28335,7 +28344,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28622,7 +28631,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ133">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR133">
         <v>1.68</v>
@@ -28747,7 +28756,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29159,7 +29168,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29443,7 +29452,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ137">
         <v>0.83</v>
@@ -30189,7 +30198,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30473,7 +30482,7 @@
         <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ142">
         <v>1.67</v>
@@ -30601,7 +30610,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30807,7 +30816,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31094,7 +31103,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ145">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR145">
         <v>1.64</v>
@@ -31219,7 +31228,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31506,7 +31515,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ147">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR147">
         <v>1.75</v>
@@ -31631,7 +31640,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31709,7 +31718,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ148">
         <v>1.42</v>
@@ -31837,7 +31846,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32121,7 +32130,7 @@
         <v>1.67</v>
       </c>
       <c r="AP150">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ150">
         <v>1.5</v>
@@ -32455,7 +32464,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32742,7 +32751,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ153">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR153">
         <v>1.62</v>
@@ -32867,7 +32876,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33073,7 +33082,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33279,7 +33288,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33357,7 +33366,7 @@
         <v>0.78</v>
       </c>
       <c r="AP156">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ156">
         <v>0.83</v>
@@ -33691,7 +33700,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34103,7 +34112,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34184,7 +34193,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ160">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR160">
         <v>1.47</v>
@@ -34309,7 +34318,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34721,7 +34730,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34802,7 +34811,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ163">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR163">
         <v>1.85</v>
@@ -35005,10 +35014,10 @@
         <v>0.8</v>
       </c>
       <c r="AP164">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ164">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR164">
         <v>1.79</v>
@@ -35133,7 +35142,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35339,7 +35348,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35623,7 +35632,7 @@
         <v>1.3</v>
       </c>
       <c r="AP167">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ167">
         <v>1.23</v>
@@ -35751,7 +35760,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36369,7 +36378,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36447,10 +36456,10 @@
         <v>0.6</v>
       </c>
       <c r="AP171">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="AQ171">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR171">
         <v>1.08</v>
@@ -36575,7 +36584,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36781,7 +36790,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36859,7 +36868,7 @@
         <v>0.1</v>
       </c>
       <c r="AP173">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ173">
         <v>0.08</v>
@@ -36987,7 +36996,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37274,7 +37283,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ175">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR175">
         <v>1.74</v>
@@ -37399,7 +37408,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37605,7 +37614,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38017,7 +38026,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38223,7 +38232,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38304,7 +38313,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ180">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AR180">
         <v>1.69</v>
@@ -38507,7 +38516,7 @@
         <v>0.45</v>
       </c>
       <c r="AP181">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="AQ181">
         <v>0.5</v>
@@ -38841,7 +38850,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39047,7 +39056,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39871,7 +39880,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40155,7 +40164,7 @@
         <v>0.09</v>
       </c>
       <c r="AP189">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="AQ189">
         <v>0.08</v>
@@ -40489,7 +40498,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40570,7 +40579,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ191">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AR191">
         <v>1.79</v>
@@ -40901,7 +40910,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41107,7 +41116,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41264,6 +41273,624 @@
       </c>
       <c r="BP194">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="195" spans="1:68">
+      <c r="A195" s="1">
+        <v>194</v>
+      </c>
+      <c r="B195">
+        <v>7453613</v>
+      </c>
+      <c r="C195" t="s">
+        <v>68</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195" s="2">
+        <v>45696.5</v>
+      </c>
+      <c r="F195">
+        <v>25</v>
+      </c>
+      <c r="G195" t="s">
+        <v>70</v>
+      </c>
+      <c r="H195" t="s">
+        <v>80</v>
+      </c>
+      <c r="I195">
+        <v>1</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>1</v>
+      </c>
+      <c r="L195">
+        <v>1</v>
+      </c>
+      <c r="M195">
+        <v>0</v>
+      </c>
+      <c r="N195">
+        <v>1</v>
+      </c>
+      <c r="O195" t="s">
+        <v>227</v>
+      </c>
+      <c r="P195" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q195">
+        <v>1.73</v>
+      </c>
+      <c r="R195">
+        <v>2.5</v>
+      </c>
+      <c r="S195">
+        <v>6.75</v>
+      </c>
+      <c r="T195">
+        <v>1.28</v>
+      </c>
+      <c r="U195">
+        <v>3.4</v>
+      </c>
+      <c r="V195">
+        <v>2.25</v>
+      </c>
+      <c r="W195">
+        <v>1.57</v>
+      </c>
+      <c r="X195">
+        <v>5</v>
+      </c>
+      <c r="Y195">
+        <v>1.14</v>
+      </c>
+      <c r="Z195">
+        <v>1.32</v>
+      </c>
+      <c r="AA195">
+        <v>5.2</v>
+      </c>
+      <c r="AB195">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="AC195">
+        <v>1.02</v>
+      </c>
+      <c r="AD195">
+        <v>21</v>
+      </c>
+      <c r="AE195">
+        <v>1.16</v>
+      </c>
+      <c r="AF195">
+        <v>4.87</v>
+      </c>
+      <c r="AG195">
+        <v>1.57</v>
+      </c>
+      <c r="AH195">
+        <v>2.25</v>
+      </c>
+      <c r="AI195">
+        <v>1.93</v>
+      </c>
+      <c r="AJ195">
+        <v>1.77</v>
+      </c>
+      <c r="AK195">
+        <v>1.07</v>
+      </c>
+      <c r="AL195">
+        <v>1.15</v>
+      </c>
+      <c r="AM195">
+        <v>3.25</v>
+      </c>
+      <c r="AN195">
+        <v>2.25</v>
+      </c>
+      <c r="AO195">
+        <v>0.67</v>
+      </c>
+      <c r="AP195">
+        <v>2.31</v>
+      </c>
+      <c r="AQ195">
+        <v>0.62</v>
+      </c>
+      <c r="AR195">
+        <v>2.09</v>
+      </c>
+      <c r="AS195">
+        <v>1.21</v>
+      </c>
+      <c r="AT195">
+        <v>3.3</v>
+      </c>
+      <c r="AU195">
+        <v>5</v>
+      </c>
+      <c r="AV195">
+        <v>3</v>
+      </c>
+      <c r="AW195">
+        <v>11</v>
+      </c>
+      <c r="AX195">
+        <v>4</v>
+      </c>
+      <c r="AY195">
+        <v>22</v>
+      </c>
+      <c r="AZ195">
+        <v>11</v>
+      </c>
+      <c r="BA195">
+        <v>8</v>
+      </c>
+      <c r="BB195">
+        <v>1</v>
+      </c>
+      <c r="BC195">
+        <v>9</v>
+      </c>
+      <c r="BD195">
+        <v>1.26</v>
+      </c>
+      <c r="BE195">
+        <v>8</v>
+      </c>
+      <c r="BF195">
+        <v>4.1</v>
+      </c>
+      <c r="BG195">
+        <v>1.22</v>
+      </c>
+      <c r="BH195">
+        <v>3.8</v>
+      </c>
+      <c r="BI195">
+        <v>1.38</v>
+      </c>
+      <c r="BJ195">
+        <v>2.75</v>
+      </c>
+      <c r="BK195">
+        <v>1.63</v>
+      </c>
+      <c r="BL195">
+        <v>2.12</v>
+      </c>
+      <c r="BM195">
+        <v>1.98</v>
+      </c>
+      <c r="BN195">
+        <v>1.74</v>
+      </c>
+      <c r="BO195">
+        <v>2.48</v>
+      </c>
+      <c r="BP195">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="196" spans="1:68">
+      <c r="A196" s="1">
+        <v>195</v>
+      </c>
+      <c r="B196">
+        <v>7453619</v>
+      </c>
+      <c r="C196" t="s">
+        <v>68</v>
+      </c>
+      <c r="D196" t="s">
+        <v>69</v>
+      </c>
+      <c r="E196" s="2">
+        <v>45696.59375</v>
+      </c>
+      <c r="F196">
+        <v>25</v>
+      </c>
+      <c r="G196" t="s">
+        <v>71</v>
+      </c>
+      <c r="H196" t="s">
+        <v>81</v>
+      </c>
+      <c r="I196">
+        <v>1</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+      <c r="L196">
+        <v>2</v>
+      </c>
+      <c r="M196">
+        <v>1</v>
+      </c>
+      <c r="N196">
+        <v>3</v>
+      </c>
+      <c r="O196" t="s">
+        <v>228</v>
+      </c>
+      <c r="P196" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q196">
+        <v>3.2</v>
+      </c>
+      <c r="R196">
+        <v>2.05</v>
+      </c>
+      <c r="S196">
+        <v>3</v>
+      </c>
+      <c r="T196">
+        <v>1.38</v>
+      </c>
+      <c r="U196">
+        <v>2.8</v>
+      </c>
+      <c r="V196">
+        <v>2.65</v>
+      </c>
+      <c r="W196">
+        <v>1.41</v>
+      </c>
+      <c r="X196">
+        <v>6.75</v>
+      </c>
+      <c r="Y196">
+        <v>1.09</v>
+      </c>
+      <c r="Z196">
+        <v>2.57</v>
+      </c>
+      <c r="AA196">
+        <v>3.21</v>
+      </c>
+      <c r="AB196">
+        <v>2.71</v>
+      </c>
+      <c r="AC196">
+        <v>1.05</v>
+      </c>
+      <c r="AD196">
+        <v>9</v>
+      </c>
+      <c r="AE196">
+        <v>1.3</v>
+      </c>
+      <c r="AF196">
+        <v>3.45</v>
+      </c>
+      <c r="AG196">
+        <v>1.89</v>
+      </c>
+      <c r="AH196">
+        <v>1.81</v>
+      </c>
+      <c r="AI196">
+        <v>1.66</v>
+      </c>
+      <c r="AJ196">
+        <v>2.05</v>
+      </c>
+      <c r="AK196">
+        <v>1.5</v>
+      </c>
+      <c r="AL196">
+        <v>1.31</v>
+      </c>
+      <c r="AM196">
+        <v>1.44</v>
+      </c>
+      <c r="AN196">
+        <v>1.08</v>
+      </c>
+      <c r="AO196">
+        <v>0.67</v>
+      </c>
+      <c r="AP196">
+        <v>1.23</v>
+      </c>
+      <c r="AQ196">
+        <v>0.62</v>
+      </c>
+      <c r="AR196">
+        <v>1.08</v>
+      </c>
+      <c r="AS196">
+        <v>1.29</v>
+      </c>
+      <c r="AT196">
+        <v>2.37</v>
+      </c>
+      <c r="AU196">
+        <v>5</v>
+      </c>
+      <c r="AV196">
+        <v>2</v>
+      </c>
+      <c r="AW196">
+        <v>7</v>
+      </c>
+      <c r="AX196">
+        <v>4</v>
+      </c>
+      <c r="AY196">
+        <v>17</v>
+      </c>
+      <c r="AZ196">
+        <v>10</v>
+      </c>
+      <c r="BA196">
+        <v>3</v>
+      </c>
+      <c r="BB196">
+        <v>5</v>
+      </c>
+      <c r="BC196">
+        <v>8</v>
+      </c>
+      <c r="BD196">
+        <v>1.97</v>
+      </c>
+      <c r="BE196">
+        <v>6.5</v>
+      </c>
+      <c r="BF196">
+        <v>2</v>
+      </c>
+      <c r="BG196">
+        <v>1.29</v>
+      </c>
+      <c r="BH196">
+        <v>3.2</v>
+      </c>
+      <c r="BI196">
+        <v>1.5</v>
+      </c>
+      <c r="BJ196">
+        <v>2.38</v>
+      </c>
+      <c r="BK196">
+        <v>1.81</v>
+      </c>
+      <c r="BL196">
+        <v>1.88</v>
+      </c>
+      <c r="BM196">
+        <v>2.23</v>
+      </c>
+      <c r="BN196">
+        <v>1.56</v>
+      </c>
+      <c r="BO196">
+        <v>2.9</v>
+      </c>
+      <c r="BP196">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="197" spans="1:68">
+      <c r="A197" s="1">
+        <v>196</v>
+      </c>
+      <c r="B197">
+        <v>7453615</v>
+      </c>
+      <c r="C197" t="s">
+        <v>68</v>
+      </c>
+      <c r="D197" t="s">
+        <v>69</v>
+      </c>
+      <c r="E197" s="2">
+        <v>45696.69791666666</v>
+      </c>
+      <c r="F197">
+        <v>25</v>
+      </c>
+      <c r="G197" t="s">
+        <v>74</v>
+      </c>
+      <c r="H197" t="s">
+        <v>83</v>
+      </c>
+      <c r="I197">
+        <v>2</v>
+      </c>
+      <c r="J197">
+        <v>1</v>
+      </c>
+      <c r="K197">
+        <v>3</v>
+      </c>
+      <c r="L197">
+        <v>2</v>
+      </c>
+      <c r="M197">
+        <v>1</v>
+      </c>
+      <c r="N197">
+        <v>3</v>
+      </c>
+      <c r="O197" t="s">
+        <v>229</v>
+      </c>
+      <c r="P197" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q197">
+        <v>2.1</v>
+      </c>
+      <c r="R197">
+        <v>2.35</v>
+      </c>
+      <c r="S197">
+        <v>4.6</v>
+      </c>
+      <c r="T197">
+        <v>1.29</v>
+      </c>
+      <c r="U197">
+        <v>3.3</v>
+      </c>
+      <c r="V197">
+        <v>2.3</v>
+      </c>
+      <c r="W197">
+        <v>1.53</v>
+      </c>
+      <c r="X197">
+        <v>5.25</v>
+      </c>
+      <c r="Y197">
+        <v>1.13</v>
+      </c>
+      <c r="Z197">
+        <v>1.62</v>
+      </c>
+      <c r="AA197">
+        <v>4.1</v>
+      </c>
+      <c r="AB197">
+        <v>4.8</v>
+      </c>
+      <c r="AC197">
+        <v>1.03</v>
+      </c>
+      <c r="AD197">
+        <v>17</v>
+      </c>
+      <c r="AE197">
+        <v>1.19</v>
+      </c>
+      <c r="AF197">
+        <v>4.45</v>
+      </c>
+      <c r="AG197">
+        <v>1.6</v>
+      </c>
+      <c r="AH197">
+        <v>2.2</v>
+      </c>
+      <c r="AI197">
+        <v>1.66</v>
+      </c>
+      <c r="AJ197">
+        <v>2.05</v>
+      </c>
+      <c r="AK197">
+        <v>1.17</v>
+      </c>
+      <c r="AL197">
+        <v>1.22</v>
+      </c>
+      <c r="AM197">
+        <v>2.25</v>
+      </c>
+      <c r="AN197">
+        <v>2.83</v>
+      </c>
+      <c r="AO197">
+        <v>0.83</v>
+      </c>
+      <c r="AP197">
+        <v>2.85</v>
+      </c>
+      <c r="AQ197">
+        <v>0.77</v>
+      </c>
+      <c r="AR197">
+        <v>1.75</v>
+      </c>
+      <c r="AS197">
+        <v>1.42</v>
+      </c>
+      <c r="AT197">
+        <v>3.17</v>
+      </c>
+      <c r="AU197">
+        <v>7</v>
+      </c>
+      <c r="AV197">
+        <v>5</v>
+      </c>
+      <c r="AW197">
+        <v>10</v>
+      </c>
+      <c r="AX197">
+        <v>7</v>
+      </c>
+      <c r="AY197">
+        <v>20</v>
+      </c>
+      <c r="AZ197">
+        <v>14</v>
+      </c>
+      <c r="BA197">
+        <v>2</v>
+      </c>
+      <c r="BB197">
+        <v>3</v>
+      </c>
+      <c r="BC197">
+        <v>5</v>
+      </c>
+      <c r="BD197">
+        <v>1.45</v>
+      </c>
+      <c r="BE197">
+        <v>7</v>
+      </c>
+      <c r="BF197">
+        <v>3.05</v>
+      </c>
+      <c r="BG197">
+        <v>1.28</v>
+      </c>
+      <c r="BH197">
+        <v>3.2</v>
+      </c>
+      <c r="BI197">
+        <v>1.49</v>
+      </c>
+      <c r="BJ197">
+        <v>2.4</v>
+      </c>
+      <c r="BK197">
+        <v>1.79</v>
+      </c>
+      <c r="BL197">
+        <v>1.9</v>
+      </c>
+      <c r="BM197">
+        <v>2.25</v>
+      </c>
+      <c r="BN197">
+        <v>1.56</v>
+      </c>
+      <c r="BO197">
+        <v>2.9</v>
+      </c>
+      <c r="BP197">
+        <v>1.35</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1244" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="316">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -706,6 +706,15 @@
     <t>['18', '40']</t>
   </si>
   <si>
+    <t>['58', '64']</t>
+  </si>
+  <si>
+    <t>['17', '31', '46', '89']</t>
+  </si>
+  <si>
+    <t>['32']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -947,6 +956,12 @@
   </si>
   <si>
     <t>['28', '84', '90+4']</t>
+  </si>
+  <si>
+    <t>['34', '66']</t>
+  </si>
+  <si>
+    <t>['10', '90+3']</t>
   </si>
 </sst>
 </file>
@@ -1308,7 +1323,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP197"/>
+  <dimension ref="A1:BP201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1564,7 +1579,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1851,7 +1866,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ3">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2260,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ5">
         <v>0.62</v>
@@ -2469,7 +2484,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ6">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2594,7 +2609,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2672,7 +2687,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
         <v>1.23</v>
@@ -2881,7 +2896,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ8">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3084,7 +3099,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ9">
         <v>0.77</v>
@@ -3418,7 +3433,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3830,7 +3845,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4036,7 +4051,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4242,7 +4257,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4654,7 +4669,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5272,7 +5287,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5350,10 +5365,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR20">
         <v>1.27</v>
@@ -5556,7 +5571,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ21">
         <v>0.62</v>
@@ -5684,7 +5699,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5890,7 +5905,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6302,7 +6317,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6714,7 +6729,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6920,7 +6935,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7126,7 +7141,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7413,7 +7428,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ30">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR30">
         <v>2.35</v>
@@ -7822,10 +7837,10 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ32">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -8156,7 +8171,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8234,7 +8249,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ34">
         <v>0.62</v>
@@ -8568,7 +8583,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8855,7 +8870,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ37">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR37">
         <v>1.03</v>
@@ -9598,7 +9613,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9804,7 +9819,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10091,7 +10106,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ43">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -10503,7 +10518,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ45">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR45">
         <v>1.63</v>
@@ -10912,7 +10927,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
         <v>0.62</v>
@@ -11040,7 +11055,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11121,7 +11136,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ48">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR48">
         <v>1.15</v>
@@ -11246,7 +11261,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11452,7 +11467,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11530,7 +11545,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ50">
         <v>1.75</v>
@@ -11658,7 +11673,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11736,7 +11751,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ51">
         <v>0.83</v>
@@ -11945,7 +11960,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ52">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR52">
         <v>2.07</v>
@@ -12688,7 +12703,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -12766,7 +12781,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ56">
         <v>1.67</v>
@@ -12975,7 +12990,7 @@
         <v>2</v>
       </c>
       <c r="AQ57">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR57">
         <v>1.08</v>
@@ -13100,7 +13115,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13306,7 +13321,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13384,10 +13399,10 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ59">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13590,7 +13605,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ60">
         <v>0.92</v>
@@ -13718,7 +13733,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14542,7 +14557,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15160,7 +15175,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15366,7 +15381,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16190,7 +16205,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16396,7 +16411,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16474,7 +16489,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ74">
         <v>0.08</v>
@@ -16886,7 +16901,7 @@
         <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
         <v>1.67</v>
@@ -17298,10 +17313,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ78">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR78">
         <v>1.59</v>
@@ -17713,7 +17728,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ80">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR80">
         <v>2.17</v>
@@ -18250,7 +18265,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18328,7 +18343,7 @@
         <v>1.4</v>
       </c>
       <c r="AP83">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ83">
         <v>1.75</v>
@@ -18868,7 +18883,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19155,7 +19170,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ87">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR87">
         <v>1.36</v>
@@ -19770,7 +19785,7 @@
         <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
         <v>0.08</v>
@@ -19898,7 +19913,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20104,7 +20119,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20516,7 +20531,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20803,7 +20818,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ95">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR95">
         <v>1.79</v>
@@ -20928,7 +20943,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21134,7 +21149,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21418,7 +21433,7 @@
         <v>1.6</v>
       </c>
       <c r="AP98">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ98">
         <v>1.25</v>
@@ -21546,7 +21561,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21752,7 +21767,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21958,7 +21973,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22039,7 +22054,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ101">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR101">
         <v>1.52</v>
@@ -22245,7 +22260,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ102">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR102">
         <v>1.86</v>
@@ -22654,7 +22669,7 @@
         <v>0.67</v>
       </c>
       <c r="AP104">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ104">
         <v>0.5</v>
@@ -22988,7 +23003,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23194,7 +23209,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23272,10 +23287,10 @@
         <v>1.33</v>
       </c>
       <c r="AP107">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ107">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR107">
         <v>1.5</v>
@@ -23400,7 +23415,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23812,7 +23827,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24099,7 +24114,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ111">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR111">
         <v>1.55</v>
@@ -24430,7 +24445,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -25666,7 +25681,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25747,7 +25762,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ119">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -25950,7 +25965,7 @@
         <v>1.29</v>
       </c>
       <c r="AP120">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ120">
         <v>1.23</v>
@@ -26156,7 +26171,7 @@
         <v>0.57</v>
       </c>
       <c r="AP121">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ121">
         <v>0.5</v>
@@ -26284,7 +26299,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26362,7 +26377,7 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ122">
         <v>0.75</v>
@@ -26777,7 +26792,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ124">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR124">
         <v>1.8</v>
@@ -26902,7 +26917,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27314,7 +27329,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27601,7 +27616,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ128">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR128">
         <v>1.7</v>
@@ -27726,7 +27741,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27804,7 +27819,7 @@
         <v>1.13</v>
       </c>
       <c r="AP129">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ129">
         <v>1.23</v>
@@ -27932,7 +27947,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28344,7 +28359,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28756,7 +28771,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29043,7 +29058,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ135">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR135">
         <v>1.6</v>
@@ -29168,7 +29183,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29246,7 +29261,7 @@
         <v>0.13</v>
       </c>
       <c r="AP136">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ136">
         <v>0.08</v>
@@ -29661,7 +29676,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ138">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR138">
         <v>1.55</v>
@@ -29867,7 +29882,7 @@
         <v>1</v>
       </c>
       <c r="AQ139">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR139">
         <v>1.07</v>
@@ -30198,7 +30213,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30276,7 +30291,7 @@
         <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ141">
         <v>1.25</v>
@@ -30610,7 +30625,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30816,7 +30831,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31228,7 +31243,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31306,7 +31321,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ146">
         <v>0.75</v>
@@ -31640,7 +31655,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31721,7 +31736,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ148">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR148">
         <v>1.11</v>
@@ -31846,7 +31861,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32464,7 +32479,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32876,7 +32891,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33082,7 +33097,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33160,7 +33175,7 @@
         <v>0.7</v>
       </c>
       <c r="AP155">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ155">
         <v>0.92</v>
@@ -33288,7 +33303,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33575,7 +33590,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ157">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR157">
         <v>1.54</v>
@@ -33700,7 +33715,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -33781,7 +33796,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ158">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR158">
         <v>1.6</v>
@@ -34112,7 +34127,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34318,7 +34333,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34396,7 +34411,7 @@
         <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ161">
         <v>1.25</v>
@@ -34730,7 +34745,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34808,7 +34823,7 @@
         <v>0.5</v>
       </c>
       <c r="AP163">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ163">
         <v>0.62</v>
@@ -35142,7 +35157,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35223,7 +35238,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ165">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR165">
         <v>1.75</v>
@@ -35348,7 +35363,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35429,7 +35444,7 @@
         <v>1</v>
       </c>
       <c r="AQ166">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR166">
         <v>1.26</v>
@@ -35760,7 +35775,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -35838,7 +35853,7 @@
         <v>1.8</v>
       </c>
       <c r="AP168">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ168">
         <v>1.75</v>
@@ -36378,7 +36393,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36584,7 +36599,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36790,7 +36805,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36996,7 +37011,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37074,7 +37089,7 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ174">
         <v>1.5</v>
@@ -37408,7 +37423,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37489,7 +37504,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ176">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR176">
         <v>1.54</v>
@@ -37614,7 +37629,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37901,7 +37916,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ178">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AR178">
         <v>1.57</v>
@@ -38026,7 +38041,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38104,7 +38119,7 @@
         <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AQ179">
         <v>1.67</v>
@@ -38232,7 +38247,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38850,7 +38865,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -38931,7 +38946,7 @@
         <v>1</v>
       </c>
       <c r="AQ183">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AR183">
         <v>1.3</v>
@@ -39056,7 +39071,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39134,7 +39149,7 @@
         <v>0.9</v>
       </c>
       <c r="AP184">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ184">
         <v>0.75</v>
@@ -39880,7 +39895,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -39961,7 +39976,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ188">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AR188">
         <v>1.65</v>
@@ -40498,7 +40513,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40910,7 +40925,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -40988,7 +41003,7 @@
         <v>0.64</v>
       </c>
       <c r="AP193">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AQ193">
         <v>0.83</v>
@@ -41116,7 +41131,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41891,6 +41906,830 @@
       </c>
       <c r="BP197">
         <v>1.35</v>
+      </c>
+    </row>
+    <row r="198" spans="1:68">
+      <c r="A198" s="1">
+        <v>197</v>
+      </c>
+      <c r="B198">
+        <v>7453614</v>
+      </c>
+      <c r="C198" t="s">
+        <v>68</v>
+      </c>
+      <c r="D198" t="s">
+        <v>69</v>
+      </c>
+      <c r="E198" s="2">
+        <v>45697.39583333334</v>
+      </c>
+      <c r="F198">
+        <v>25</v>
+      </c>
+      <c r="G198" t="s">
+        <v>73</v>
+      </c>
+      <c r="H198" t="s">
+        <v>82</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>2</v>
+      </c>
+      <c r="M198">
+        <v>0</v>
+      </c>
+      <c r="N198">
+        <v>2</v>
+      </c>
+      <c r="O198" t="s">
+        <v>230</v>
+      </c>
+      <c r="P198" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q198">
+        <v>2.88</v>
+      </c>
+      <c r="R198">
+        <v>2.1</v>
+      </c>
+      <c r="S198">
+        <v>3.75</v>
+      </c>
+      <c r="T198">
+        <v>1.4</v>
+      </c>
+      <c r="U198">
+        <v>2.75</v>
+      </c>
+      <c r="V198">
+        <v>3</v>
+      </c>
+      <c r="W198">
+        <v>1.36</v>
+      </c>
+      <c r="X198">
+        <v>8</v>
+      </c>
+      <c r="Y198">
+        <v>1.08</v>
+      </c>
+      <c r="Z198">
+        <v>2.1</v>
+      </c>
+      <c r="AA198">
+        <v>3.47</v>
+      </c>
+      <c r="AB198">
+        <v>3.27</v>
+      </c>
+      <c r="AC198">
+        <v>1.04</v>
+      </c>
+      <c r="AD198">
+        <v>13</v>
+      </c>
+      <c r="AE198">
+        <v>1.26</v>
+      </c>
+      <c r="AF198">
+        <v>3.67</v>
+      </c>
+      <c r="AG198">
+        <v>1.8</v>
+      </c>
+      <c r="AH198">
+        <v>1.94</v>
+      </c>
+      <c r="AI198">
+        <v>1.75</v>
+      </c>
+      <c r="AJ198">
+        <v>2</v>
+      </c>
+      <c r="AK198">
+        <v>1.33</v>
+      </c>
+      <c r="AL198">
+        <v>1.28</v>
+      </c>
+      <c r="AM198">
+        <v>1.68</v>
+      </c>
+      <c r="AN198">
+        <v>1.75</v>
+      </c>
+      <c r="AO198">
+        <v>1.42</v>
+      </c>
+      <c r="AP198">
+        <v>1.85</v>
+      </c>
+      <c r="AQ198">
+        <v>1.31</v>
+      </c>
+      <c r="AR198">
+        <v>1.68</v>
+      </c>
+      <c r="AS198">
+        <v>1.25</v>
+      </c>
+      <c r="AT198">
+        <v>2.93</v>
+      </c>
+      <c r="AU198">
+        <v>5</v>
+      </c>
+      <c r="AV198">
+        <v>4</v>
+      </c>
+      <c r="AW198">
+        <v>9</v>
+      </c>
+      <c r="AX198">
+        <v>5</v>
+      </c>
+      <c r="AY198">
+        <v>19</v>
+      </c>
+      <c r="AZ198">
+        <v>9</v>
+      </c>
+      <c r="BA198">
+        <v>9</v>
+      </c>
+      <c r="BB198">
+        <v>2</v>
+      </c>
+      <c r="BC198">
+        <v>11</v>
+      </c>
+      <c r="BD198">
+        <v>1.84</v>
+      </c>
+      <c r="BE198">
+        <v>6.75</v>
+      </c>
+      <c r="BF198">
+        <v>2.15</v>
+      </c>
+      <c r="BG198">
+        <v>1.28</v>
+      </c>
+      <c r="BH198">
+        <v>3.2</v>
+      </c>
+      <c r="BI198">
+        <v>1.5</v>
+      </c>
+      <c r="BJ198">
+        <v>2.4</v>
+      </c>
+      <c r="BK198">
+        <v>1.83</v>
+      </c>
+      <c r="BL198">
+        <v>1.85</v>
+      </c>
+      <c r="BM198">
+        <v>2.23</v>
+      </c>
+      <c r="BN198">
+        <v>1.56</v>
+      </c>
+      <c r="BO198">
+        <v>2.9</v>
+      </c>
+      <c r="BP198">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="199" spans="1:68">
+      <c r="A199" s="1">
+        <v>198</v>
+      </c>
+      <c r="B199">
+        <v>7453616</v>
+      </c>
+      <c r="C199" t="s">
+        <v>68</v>
+      </c>
+      <c r="D199" t="s">
+        <v>69</v>
+      </c>
+      <c r="E199" s="2">
+        <v>45697.5</v>
+      </c>
+      <c r="F199">
+        <v>25</v>
+      </c>
+      <c r="G199" t="s">
+        <v>75</v>
+      </c>
+      <c r="H199" t="s">
+        <v>78</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>1</v>
+      </c>
+      <c r="K199">
+        <v>1</v>
+      </c>
+      <c r="L199">
+        <v>1</v>
+      </c>
+      <c r="M199">
+        <v>2</v>
+      </c>
+      <c r="N199">
+        <v>3</v>
+      </c>
+      <c r="O199" t="s">
+        <v>188</v>
+      </c>
+      <c r="P199" t="s">
+        <v>314</v>
+      </c>
+      <c r="Q199">
+        <v>6</v>
+      </c>
+      <c r="R199">
+        <v>2.25</v>
+      </c>
+      <c r="S199">
+        <v>2.1</v>
+      </c>
+      <c r="T199">
+        <v>1.36</v>
+      </c>
+      <c r="U199">
+        <v>3</v>
+      </c>
+      <c r="V199">
+        <v>2.75</v>
+      </c>
+      <c r="W199">
+        <v>1.4</v>
+      </c>
+      <c r="X199">
+        <v>7</v>
+      </c>
+      <c r="Y199">
+        <v>1.1</v>
+      </c>
+      <c r="Z199">
+        <v>4.8</v>
+      </c>
+      <c r="AA199">
+        <v>4.1</v>
+      </c>
+      <c r="AB199">
+        <v>1.62</v>
+      </c>
+      <c r="AC199">
+        <v>1.03</v>
+      </c>
+      <c r="AD199">
+        <v>15</v>
+      </c>
+      <c r="AE199">
+        <v>1.24</v>
+      </c>
+      <c r="AF199">
+        <v>3.89</v>
+      </c>
+      <c r="AG199">
+        <v>1.83</v>
+      </c>
+      <c r="AH199">
+        <v>1.91</v>
+      </c>
+      <c r="AI199">
+        <v>1.95</v>
+      </c>
+      <c r="AJ199">
+        <v>1.8</v>
+      </c>
+      <c r="AK199">
+        <v>2.25</v>
+      </c>
+      <c r="AL199">
+        <v>1.24</v>
+      </c>
+      <c r="AM199">
+        <v>1.16</v>
+      </c>
+      <c r="AN199">
+        <v>1.08</v>
+      </c>
+      <c r="AO199">
+        <v>1.33</v>
+      </c>
+      <c r="AP199">
+        <v>1</v>
+      </c>
+      <c r="AQ199">
+        <v>1.46</v>
+      </c>
+      <c r="AR199">
+        <v>1.34</v>
+      </c>
+      <c r="AS199">
+        <v>1.44</v>
+      </c>
+      <c r="AT199">
+        <v>2.78</v>
+      </c>
+      <c r="AU199">
+        <v>3</v>
+      </c>
+      <c r="AV199">
+        <v>7</v>
+      </c>
+      <c r="AW199">
+        <v>8</v>
+      </c>
+      <c r="AX199">
+        <v>8</v>
+      </c>
+      <c r="AY199">
+        <v>12</v>
+      </c>
+      <c r="AZ199">
+        <v>16</v>
+      </c>
+      <c r="BA199">
+        <v>7</v>
+      </c>
+      <c r="BB199">
+        <v>5</v>
+      </c>
+      <c r="BC199">
+        <v>12</v>
+      </c>
+      <c r="BD199">
+        <v>2.8</v>
+      </c>
+      <c r="BE199">
+        <v>7</v>
+      </c>
+      <c r="BF199">
+        <v>1.52</v>
+      </c>
+      <c r="BG199">
+        <v>1.22</v>
+      </c>
+      <c r="BH199">
+        <v>3.7</v>
+      </c>
+      <c r="BI199">
+        <v>1.4</v>
+      </c>
+      <c r="BJ199">
+        <v>2.7</v>
+      </c>
+      <c r="BK199">
+        <v>1.65</v>
+      </c>
+      <c r="BL199">
+        <v>2.08</v>
+      </c>
+      <c r="BM199">
+        <v>2</v>
+      </c>
+      <c r="BN199">
+        <v>1.73</v>
+      </c>
+      <c r="BO199">
+        <v>2.55</v>
+      </c>
+      <c r="BP199">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="200" spans="1:68">
+      <c r="A200" s="1">
+        <v>199</v>
+      </c>
+      <c r="B200">
+        <v>7453618</v>
+      </c>
+      <c r="C200" t="s">
+        <v>68</v>
+      </c>
+      <c r="D200" t="s">
+        <v>69</v>
+      </c>
+      <c r="E200" s="2">
+        <v>45697.60416666666</v>
+      </c>
+      <c r="F200">
+        <v>25</v>
+      </c>
+      <c r="G200" t="s">
+        <v>77</v>
+      </c>
+      <c r="H200" t="s">
+        <v>84</v>
+      </c>
+      <c r="I200">
+        <v>2</v>
+      </c>
+      <c r="J200">
+        <v>1</v>
+      </c>
+      <c r="K200">
+        <v>3</v>
+      </c>
+      <c r="L200">
+        <v>4</v>
+      </c>
+      <c r="M200">
+        <v>2</v>
+      </c>
+      <c r="N200">
+        <v>6</v>
+      </c>
+      <c r="O200" t="s">
+        <v>231</v>
+      </c>
+      <c r="P200" t="s">
+        <v>315</v>
+      </c>
+      <c r="Q200">
+        <v>2.25</v>
+      </c>
+      <c r="R200">
+        <v>2.38</v>
+      </c>
+      <c r="S200">
+        <v>4.75</v>
+      </c>
+      <c r="T200">
+        <v>1.33</v>
+      </c>
+      <c r="U200">
+        <v>3.25</v>
+      </c>
+      <c r="V200">
+        <v>2.5</v>
+      </c>
+      <c r="W200">
+        <v>1.5</v>
+      </c>
+      <c r="X200">
+        <v>6.5</v>
+      </c>
+      <c r="Y200">
+        <v>1.11</v>
+      </c>
+      <c r="Z200">
+        <v>1.7</v>
+      </c>
+      <c r="AA200">
+        <v>3.96</v>
+      </c>
+      <c r="AB200">
+        <v>4.4</v>
+      </c>
+      <c r="AC200">
+        <v>1.03</v>
+      </c>
+      <c r="AD200">
+        <v>15</v>
+      </c>
+      <c r="AE200">
+        <v>1.19</v>
+      </c>
+      <c r="AF200">
+        <v>4.45</v>
+      </c>
+      <c r="AG200">
+        <v>1.65</v>
+      </c>
+      <c r="AH200">
+        <v>2.15</v>
+      </c>
+      <c r="AI200">
+        <v>1.7</v>
+      </c>
+      <c r="AJ200">
+        <v>2.05</v>
+      </c>
+      <c r="AK200">
+        <v>1.2</v>
+      </c>
+      <c r="AL200">
+        <v>1.24</v>
+      </c>
+      <c r="AM200">
+        <v>2.05</v>
+      </c>
+      <c r="AN200">
+        <v>1.33</v>
+      </c>
+      <c r="AO200">
+        <v>0.92</v>
+      </c>
+      <c r="AP200">
+        <v>1.46</v>
+      </c>
+      <c r="AQ200">
+        <v>0.85</v>
+      </c>
+      <c r="AR200">
+        <v>1.89</v>
+      </c>
+      <c r="AS200">
+        <v>1.02</v>
+      </c>
+      <c r="AT200">
+        <v>2.91</v>
+      </c>
+      <c r="AU200">
+        <v>10</v>
+      </c>
+      <c r="AV200">
+        <v>3</v>
+      </c>
+      <c r="AW200">
+        <v>11</v>
+      </c>
+      <c r="AX200">
+        <v>10</v>
+      </c>
+      <c r="AY200">
+        <v>28</v>
+      </c>
+      <c r="AZ200">
+        <v>14</v>
+      </c>
+      <c r="BA200">
+        <v>5</v>
+      </c>
+      <c r="BB200">
+        <v>4</v>
+      </c>
+      <c r="BC200">
+        <v>9</v>
+      </c>
+      <c r="BD200">
+        <v>1.41</v>
+      </c>
+      <c r="BE200">
+        <v>7</v>
+      </c>
+      <c r="BF200">
+        <v>3.2</v>
+      </c>
+      <c r="BG200">
+        <v>1.21</v>
+      </c>
+      <c r="BH200">
+        <v>3.9</v>
+      </c>
+      <c r="BI200">
+        <v>1.36</v>
+      </c>
+      <c r="BJ200">
+        <v>2.8</v>
+      </c>
+      <c r="BK200">
+        <v>1.58</v>
+      </c>
+      <c r="BL200">
+        <v>2.18</v>
+      </c>
+      <c r="BM200">
+        <v>1.95</v>
+      </c>
+      <c r="BN200">
+        <v>1.75</v>
+      </c>
+      <c r="BO200">
+        <v>2.4</v>
+      </c>
+      <c r="BP200">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="201" spans="1:68">
+      <c r="A201" s="1">
+        <v>200</v>
+      </c>
+      <c r="B201">
+        <v>7453617</v>
+      </c>
+      <c r="C201" t="s">
+        <v>68</v>
+      </c>
+      <c r="D201" t="s">
+        <v>69</v>
+      </c>
+      <c r="E201" s="2">
+        <v>45697.63541666666</v>
+      </c>
+      <c r="F201">
+        <v>25</v>
+      </c>
+      <c r="G201" t="s">
+        <v>72</v>
+      </c>
+      <c r="H201" t="s">
+        <v>76</v>
+      </c>
+      <c r="I201">
+        <v>1</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>1</v>
+      </c>
+      <c r="L201">
+        <v>1</v>
+      </c>
+      <c r="M201">
+        <v>1</v>
+      </c>
+      <c r="N201">
+        <v>2</v>
+      </c>
+      <c r="O201" t="s">
+        <v>232</v>
+      </c>
+      <c r="P201" t="s">
+        <v>192</v>
+      </c>
+      <c r="Q201">
+        <v>4.5</v>
+      </c>
+      <c r="R201">
+        <v>2.2</v>
+      </c>
+      <c r="S201">
+        <v>2.5</v>
+      </c>
+      <c r="T201">
+        <v>1.4</v>
+      </c>
+      <c r="U201">
+        <v>2.75</v>
+      </c>
+      <c r="V201">
+        <v>2.75</v>
+      </c>
+      <c r="W201">
+        <v>1.4</v>
+      </c>
+      <c r="X201">
+        <v>8</v>
+      </c>
+      <c r="Y201">
+        <v>1.08</v>
+      </c>
+      <c r="Z201">
+        <v>4.1</v>
+      </c>
+      <c r="AA201">
+        <v>3.61</v>
+      </c>
+      <c r="AB201">
+        <v>1.82</v>
+      </c>
+      <c r="AC201">
+        <v>1.05</v>
+      </c>
+      <c r="AD201">
+        <v>12</v>
+      </c>
+      <c r="AE201">
+        <v>1.28</v>
+      </c>
+      <c r="AF201">
+        <v>3.52</v>
+      </c>
+      <c r="AG201">
+        <v>1.87</v>
+      </c>
+      <c r="AH201">
+        <v>1.87</v>
+      </c>
+      <c r="AI201">
+        <v>1.8</v>
+      </c>
+      <c r="AJ201">
+        <v>1.95</v>
+      </c>
+      <c r="AK201">
+        <v>1.9</v>
+      </c>
+      <c r="AL201">
+        <v>1.28</v>
+      </c>
+      <c r="AM201">
+        <v>1.22</v>
+      </c>
+      <c r="AN201">
+        <v>1</v>
+      </c>
+      <c r="AO201">
+        <v>0.92</v>
+      </c>
+      <c r="AP201">
+        <v>1</v>
+      </c>
+      <c r="AQ201">
+        <v>0.92</v>
+      </c>
+      <c r="AR201">
+        <v>1.28</v>
+      </c>
+      <c r="AS201">
+        <v>1.44</v>
+      </c>
+      <c r="AT201">
+        <v>2.72</v>
+      </c>
+      <c r="AU201">
+        <v>4</v>
+      </c>
+      <c r="AV201">
+        <v>2</v>
+      </c>
+      <c r="AW201">
+        <v>8</v>
+      </c>
+      <c r="AX201">
+        <v>6</v>
+      </c>
+      <c r="AY201">
+        <v>16</v>
+      </c>
+      <c r="AZ201">
+        <v>11</v>
+      </c>
+      <c r="BA201">
+        <v>4</v>
+      </c>
+      <c r="BB201">
+        <v>5</v>
+      </c>
+      <c r="BC201">
+        <v>9</v>
+      </c>
+      <c r="BD201">
+        <v>2.33</v>
+      </c>
+      <c r="BE201">
+        <v>6.5</v>
+      </c>
+      <c r="BF201">
+        <v>1.73</v>
+      </c>
+      <c r="BG201">
+        <v>1.29</v>
+      </c>
+      <c r="BH201">
+        <v>3.15</v>
+      </c>
+      <c r="BI201">
+        <v>1.5</v>
+      </c>
+      <c r="BJ201">
+        <v>2.38</v>
+      </c>
+      <c r="BK201">
+        <v>1.82</v>
+      </c>
+      <c r="BL201">
+        <v>1.86</v>
+      </c>
+      <c r="BM201">
+        <v>2</v>
+      </c>
+      <c r="BN201">
+        <v>1.73</v>
+      </c>
+      <c r="BO201">
+        <v>2.9</v>
+      </c>
+      <c r="BP201">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -42066,13 +42066,13 @@
         <v>9</v>
       </c>
       <c r="BA198">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB198">
         <v>2</v>
       </c>
       <c r="BC198">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD198">
         <v>1.84</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="318">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -715,6 +715,9 @@
     <t>['32']</t>
   </si>
   <si>
+    <t>['90+9']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -962,6 +965,9 @@
   </si>
   <si>
     <t>['10', '90+3']</t>
+  </si>
+  <si>
+    <t>['35', '78']</t>
   </si>
 </sst>
 </file>
@@ -1323,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP201"/>
+  <dimension ref="A1:BP202"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1579,7 +1585,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2609,7 +2615,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3433,7 +3439,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3720,7 +3726,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ12">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3845,7 +3851,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4051,7 +4057,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4257,7 +4263,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4541,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ16">
         <v>1.75</v>
@@ -4669,7 +4675,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4953,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ18">
         <v>0.75</v>
@@ -5287,7 +5293,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5699,7 +5705,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5905,7 +5911,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6317,7 +6323,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6729,7 +6735,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6810,7 +6816,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR27">
         <v>0.45</v>
@@ -6935,7 +6941,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7141,7 +7147,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -8171,7 +8177,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8583,7 +8589,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9073,7 +9079,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ38">
         <v>0.08</v>
@@ -9613,7 +9619,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9819,7 +9825,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -11055,7 +11061,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11261,7 +11267,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11342,7 +11348,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ49">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR49">
         <v>2.18</v>
@@ -11467,7 +11473,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11673,7 +11679,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12703,7 +12709,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -12784,7 +12790,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ56">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR56">
         <v>1.68</v>
@@ -12987,7 +12993,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ57">
         <v>1.46</v>
@@ -13115,7 +13121,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13321,7 +13327,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13733,7 +13739,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14557,7 +14563,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15175,7 +15181,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15253,7 +15259,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ68">
         <v>0.83</v>
@@ -15381,7 +15387,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16205,7 +16211,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16411,7 +16417,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16904,7 +16910,7 @@
         <v>1</v>
       </c>
       <c r="AQ76">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -18265,7 +18271,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18883,7 +18889,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19373,7 +19379,7 @@
         <v>0.8</v>
       </c>
       <c r="AP88">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ88">
         <v>0.92</v>
@@ -19913,7 +19919,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20119,7 +20125,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20531,7 +20537,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20943,7 +20949,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21024,7 +21030,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ96">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR96">
         <v>1.72</v>
@@ -21149,7 +21155,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21561,7 +21567,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21639,7 +21645,7 @@
         <v>0.83</v>
       </c>
       <c r="AP99">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ99">
         <v>0.62</v>
@@ -21767,7 +21773,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21973,7 +21979,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -23003,7 +23009,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23209,7 +23215,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23415,7 +23421,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23827,7 +23833,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24320,7 +24326,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ112">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR112">
         <v>1.71</v>
@@ -24445,7 +24451,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -25141,7 +25147,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ116">
         <v>0.77</v>
@@ -25681,7 +25687,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26299,7 +26305,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26917,7 +26923,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -26998,7 +27004,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ125">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR125">
         <v>1.37</v>
@@ -27329,7 +27335,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27741,7 +27747,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27947,7 +27953,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28231,7 +28237,7 @@
         <v>0.88</v>
       </c>
       <c r="AP131">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ131">
         <v>0.62</v>
@@ -28359,7 +28365,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28771,7 +28777,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29183,7 +29189,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -30213,7 +30219,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30500,7 +30506,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ142">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR142">
         <v>2.07</v>
@@ -30625,7 +30631,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30831,7 +30837,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31243,7 +31249,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31655,7 +31661,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31861,7 +31867,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32351,7 +32357,7 @@
         <v>1.11</v>
       </c>
       <c r="AP151">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ151">
         <v>1.23</v>
@@ -32479,7 +32485,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32891,7 +32897,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -32972,7 +32978,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ154">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR154">
         <v>1.81</v>
@@ -33097,7 +33103,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33303,7 +33309,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33715,7 +33721,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34127,7 +34133,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34333,7 +34339,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34617,7 +34623,7 @@
         <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ162">
         <v>0.5</v>
@@ -34745,7 +34751,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35157,7 +35163,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35363,7 +35369,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35775,7 +35781,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36393,7 +36399,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36599,7 +36605,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36680,7 +36686,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ172">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR172">
         <v>1.56</v>
@@ -36805,7 +36811,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -37011,7 +37017,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37423,7 +37429,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37629,7 +37635,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38041,7 +38047,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38122,7 +38128,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ179">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="AR179">
         <v>1.9</v>
@@ -38247,7 +38253,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38737,7 +38743,7 @@
         <v>1.5</v>
       </c>
       <c r="AP182">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AQ182">
         <v>1.25</v>
@@ -38865,7 +38871,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39071,7 +39077,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39895,7 +39901,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40513,7 +40519,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40925,7 +40931,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41131,7 +41137,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -42161,7 +42167,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42367,7 +42373,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42730,6 +42736,212 @@
       </c>
       <c r="BP201">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="202" spans="1:68">
+      <c r="A202" s="1">
+        <v>201</v>
+      </c>
+      <c r="B202">
+        <v>7453622</v>
+      </c>
+      <c r="C202" t="s">
+        <v>68</v>
+      </c>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" s="2">
+        <v>45702.69791666666</v>
+      </c>
+      <c r="F202">
+        <v>26</v>
+      </c>
+      <c r="G202" t="s">
+        <v>84</v>
+      </c>
+      <c r="H202" t="s">
+        <v>74</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>1</v>
+      </c>
+      <c r="K202">
+        <v>1</v>
+      </c>
+      <c r="L202">
+        <v>1</v>
+      </c>
+      <c r="M202">
+        <v>2</v>
+      </c>
+      <c r="N202">
+        <v>3</v>
+      </c>
+      <c r="O202" t="s">
+        <v>233</v>
+      </c>
+      <c r="P202" t="s">
+        <v>317</v>
+      </c>
+      <c r="Q202">
+        <v>5</v>
+      </c>
+      <c r="R202">
+        <v>2.25</v>
+      </c>
+      <c r="S202">
+        <v>2.3</v>
+      </c>
+      <c r="T202">
+        <v>1.36</v>
+      </c>
+      <c r="U202">
+        <v>3</v>
+      </c>
+      <c r="V202">
+        <v>2.75</v>
+      </c>
+      <c r="W202">
+        <v>1.4</v>
+      </c>
+      <c r="X202">
+        <v>8</v>
+      </c>
+      <c r="Y202">
+        <v>1.08</v>
+      </c>
+      <c r="Z202">
+        <v>4.9</v>
+      </c>
+      <c r="AA202">
+        <v>3.62</v>
+      </c>
+      <c r="AB202">
+        <v>1.69</v>
+      </c>
+      <c r="AC202">
+        <v>1.04</v>
+      </c>
+      <c r="AD202">
+        <v>13</v>
+      </c>
+      <c r="AE202">
+        <v>1.26</v>
+      </c>
+      <c r="AF202">
+        <v>3.67</v>
+      </c>
+      <c r="AG202">
+        <v>1.87</v>
+      </c>
+      <c r="AH202">
+        <v>1.87</v>
+      </c>
+      <c r="AI202">
+        <v>1.8</v>
+      </c>
+      <c r="AJ202">
+        <v>1.95</v>
+      </c>
+      <c r="AK202">
+        <v>2.1</v>
+      </c>
+      <c r="AL202">
+        <v>1.26</v>
+      </c>
+      <c r="AM202">
+        <v>1.18</v>
+      </c>
+      <c r="AN202">
+        <v>2</v>
+      </c>
+      <c r="AO202">
+        <v>1.67</v>
+      </c>
+      <c r="AP202">
+        <v>1.85</v>
+      </c>
+      <c r="AQ202">
+        <v>1.77</v>
+      </c>
+      <c r="AR202">
+        <v>1.22</v>
+      </c>
+      <c r="AS202">
+        <v>1.69</v>
+      </c>
+      <c r="AT202">
+        <v>2.91</v>
+      </c>
+      <c r="AU202">
+        <v>4</v>
+      </c>
+      <c r="AV202">
+        <v>5</v>
+      </c>
+      <c r="AW202">
+        <v>7</v>
+      </c>
+      <c r="AX202">
+        <v>12</v>
+      </c>
+      <c r="AY202">
+        <v>14</v>
+      </c>
+      <c r="AZ202">
+        <v>22</v>
+      </c>
+      <c r="BA202">
+        <v>6</v>
+      </c>
+      <c r="BB202">
+        <v>4</v>
+      </c>
+      <c r="BC202">
+        <v>10</v>
+      </c>
+      <c r="BD202">
+        <v>2.9</v>
+      </c>
+      <c r="BE202">
+        <v>6.75</v>
+      </c>
+      <c r="BF202">
+        <v>1.49</v>
+      </c>
+      <c r="BG202">
+        <v>1.34</v>
+      </c>
+      <c r="BH202">
+        <v>2.9</v>
+      </c>
+      <c r="BI202">
+        <v>1.56</v>
+      </c>
+      <c r="BJ202">
+        <v>2.23</v>
+      </c>
+      <c r="BK202">
+        <v>1.95</v>
+      </c>
+      <c r="BL202">
+        <v>1.75</v>
+      </c>
+      <c r="BM202">
+        <v>2.43</v>
+      </c>
+      <c r="BN202">
+        <v>1.48</v>
+      </c>
+      <c r="BO202">
+        <v>3.2</v>
+      </c>
+      <c r="BP202">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="324">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -718,6 +718,15 @@
     <t>['90+9']</t>
   </si>
   <si>
+    <t>['30', '89', '90+2']</t>
+  </si>
+  <si>
+    <t>['22', '42']</t>
+  </si>
+  <si>
+    <t>['10', '20']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -968,6 +977,15 @@
   </si>
   <si>
     <t>['35', '78']</t>
+  </si>
+  <si>
+    <t>['9', '39']</t>
+  </si>
+  <si>
+    <t>['53']</t>
+  </si>
+  <si>
+    <t>['72', '90+1']</t>
   </si>
 </sst>
 </file>
@@ -1329,7 +1347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP202"/>
+  <dimension ref="A1:BP205"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1585,7 +1603,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2615,7 +2633,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3439,7 +3457,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3723,7 +3741,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ12">
         <v>1.77</v>
@@ -3851,7 +3869,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3929,7 +3947,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ13">
         <v>0.92</v>
@@ -4057,7 +4075,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4135,7 +4153,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
         <v>1.5</v>
@@ -4263,7 +4281,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4344,7 +4362,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ15">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4550,7 +4568,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ16">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4675,7 +4693,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4756,7 +4774,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ17">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5168,7 +5186,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ19">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR19">
         <v>0.45</v>
@@ -5293,7 +5311,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5705,7 +5723,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5786,7 +5804,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ22">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR22">
         <v>1.58</v>
@@ -5911,7 +5929,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -5989,7 +6007,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
         <v>0.62</v>
@@ -6323,7 +6341,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6735,7 +6753,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6941,7 +6959,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7019,10 +7037,10 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ28">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR28">
         <v>0.79</v>
@@ -7147,7 +7165,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7637,7 +7655,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ31">
         <v>0.77</v>
@@ -8177,7 +8195,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8461,7 +8479,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
         <v>0.75</v>
@@ -8589,7 +8607,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8670,7 +8688,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ36">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR36">
         <v>0.9399999999999999</v>
@@ -8873,7 +8891,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ37">
         <v>1.46</v>
@@ -9288,7 +9306,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ39">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR39">
         <v>1.72</v>
@@ -9619,7 +9637,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9825,7 +9843,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9906,7 +9924,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR42">
         <v>0.95</v>
@@ -10109,7 +10127,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ43">
         <v>0.85</v>
@@ -11061,7 +11079,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11267,7 +11285,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11473,7 +11491,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11554,7 +11572,7 @@
         <v>1</v>
       </c>
       <c r="AQ50">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR50">
         <v>1.76</v>
@@ -11679,7 +11697,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11963,7 +11981,7 @@
         <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
         <v>1.46</v>
@@ -12169,7 +12187,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ53">
         <v>0.62</v>
@@ -12709,7 +12727,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13121,7 +13139,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13327,7 +13345,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13739,7 +13757,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14232,7 +14250,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ63">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR63">
         <v>1.69</v>
@@ -14435,10 +14453,10 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ64">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR64">
         <v>1.33</v>
@@ -14563,7 +14581,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14850,7 +14868,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ66">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR66">
         <v>1.81</v>
@@ -15181,7 +15199,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15387,7 +15405,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15671,7 +15689,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
         <v>0.08</v>
@@ -15880,7 +15898,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ71">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -16211,7 +16229,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16417,7 +16435,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -17525,7 +17543,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
         <v>0.77</v>
@@ -17937,7 +17955,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ81">
         <v>1.23</v>
@@ -18271,7 +18289,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18352,7 +18370,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ83">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR83">
         <v>1.89</v>
@@ -18558,7 +18576,7 @@
         <v>1.58</v>
       </c>
       <c r="AQ84">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR84">
         <v>1.61</v>
@@ -18889,7 +18907,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19173,7 +19191,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ87">
         <v>1.31</v>
@@ -19588,7 +19606,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ89">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19919,7 +19937,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20125,7 +20143,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20409,7 +20427,7 @@
         <v>1.4</v>
       </c>
       <c r="AP93">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ93">
         <v>0.83</v>
@@ -20537,7 +20555,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20821,7 +20839,7 @@
         <v>0.8</v>
       </c>
       <c r="AP95">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
         <v>0.85</v>
@@ -20949,7 +20967,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21155,7 +21173,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21442,7 +21460,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ98">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR98">
         <v>1.83</v>
@@ -21567,7 +21585,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21773,7 +21791,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21851,10 +21869,10 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ100">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR100">
         <v>1.3</v>
@@ -21979,7 +21997,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22678,7 +22696,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ104">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23009,7 +23027,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23087,7 +23105,7 @@
         <v>1.33</v>
       </c>
       <c r="AP106">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ106">
         <v>0.75</v>
@@ -23215,7 +23233,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23421,7 +23439,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23833,7 +23851,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24451,7 +24469,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24532,7 +24550,7 @@
         <v>1</v>
       </c>
       <c r="AQ113">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR113">
         <v>0.88</v>
@@ -24735,10 +24753,10 @@
         <v>1.33</v>
       </c>
       <c r="AP114">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR114">
         <v>1.76</v>
@@ -25687,7 +25705,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25765,7 +25783,7 @@
         <v>0.71</v>
       </c>
       <c r="AP119">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ119">
         <v>1.46</v>
@@ -26180,7 +26198,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ121">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR121">
         <v>1.8</v>
@@ -26305,7 +26323,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26592,7 +26610,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ123">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR123">
         <v>2.07</v>
@@ -26923,7 +26941,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27001,7 +27019,7 @@
         <v>1.71</v>
       </c>
       <c r="AP125">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ125">
         <v>1.77</v>
@@ -27207,7 +27225,7 @@
         <v>1.57</v>
       </c>
       <c r="AP126">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ126">
         <v>1.5</v>
@@ -27335,7 +27353,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27747,7 +27765,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27953,7 +27971,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28034,7 +28052,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ130">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR130">
         <v>1.84</v>
@@ -28365,7 +28383,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28446,7 +28464,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ132">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR132">
         <v>1.55</v>
@@ -28777,7 +28795,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28855,7 +28873,7 @@
         <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
         <v>0.92</v>
@@ -29189,7 +29207,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -30091,7 +30109,7 @@
         <v>0.78</v>
       </c>
       <c r="AP140">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ140">
         <v>0.92</v>
@@ -30219,7 +30237,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30300,7 +30318,7 @@
         <v>1</v>
       </c>
       <c r="AQ141">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR141">
         <v>1.44</v>
@@ -30631,7 +30649,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30837,7 +30855,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -30915,7 +30933,7 @@
         <v>1.5</v>
       </c>
       <c r="AP144">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ144">
         <v>1.5</v>
@@ -31249,7 +31267,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31661,7 +31679,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31867,7 +31885,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31948,7 +31966,7 @@
         <v>1</v>
       </c>
       <c r="AQ149">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR149">
         <v>1.18</v>
@@ -32485,7 +32503,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32566,7 +32584,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ152">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR152">
         <v>1.81</v>
@@ -32897,7 +32915,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -32975,7 +32993,7 @@
         <v>1.44</v>
       </c>
       <c r="AP154">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ154">
         <v>1.77</v>
@@ -33103,7 +33121,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33309,7 +33327,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33721,7 +33739,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34005,7 +34023,7 @@
         <v>0.11</v>
       </c>
       <c r="AP159">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ159">
         <v>0.08</v>
@@ -34133,7 +34151,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34211,7 +34229,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP160">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ160">
         <v>0.77</v>
@@ -34339,7 +34357,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34420,7 +34438,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ161">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR161">
         <v>1.75</v>
@@ -34626,7 +34644,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ162">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR162">
         <v>1.18</v>
@@ -34751,7 +34769,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35163,7 +35181,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35369,7 +35387,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35781,7 +35799,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -35862,7 +35880,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ168">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR168">
         <v>1.71</v>
@@ -36399,7 +36417,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36605,7 +36623,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36811,7 +36829,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -37017,7 +37035,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37429,7 +37447,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37507,7 +37525,7 @@
         <v>0.7</v>
       </c>
       <c r="AP176">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ176">
         <v>0.85</v>
@@ -37635,7 +37653,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37713,7 +37731,7 @@
         <v>0.7</v>
       </c>
       <c r="AP177">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ177">
         <v>0.83</v>
@@ -37919,7 +37937,7 @@
         <v>1.45</v>
       </c>
       <c r="AP178">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AQ178">
         <v>1.31</v>
@@ -38047,7 +38065,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38253,7 +38271,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38540,7 +38558,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ181">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AR181">
         <v>2.05</v>
@@ -38746,7 +38764,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ182">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR182">
         <v>1.21</v>
@@ -38871,7 +38889,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39077,7 +39095,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39361,7 +39379,7 @@
         <v>1.27</v>
       </c>
       <c r="AP185">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ185">
         <v>1.23</v>
@@ -39567,7 +39585,7 @@
         <v>0.82</v>
       </c>
       <c r="AP186">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AQ186">
         <v>0.75</v>
@@ -39776,7 +39794,7 @@
         <v>1.75</v>
       </c>
       <c r="AQ187">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AR187">
         <v>1.65</v>
@@ -39901,7 +39919,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40391,10 +40409,10 @@
         <v>1.91</v>
       </c>
       <c r="AP190">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ190">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AR190">
         <v>1.72</v>
@@ -40519,7 +40537,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40931,7 +40949,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41137,7 +41155,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -42167,7 +42185,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42373,7 +42391,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42785,7 +42803,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -42942,6 +42960,624 @@
       </c>
       <c r="BP202">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="203" spans="1:68">
+      <c r="A203" s="1">
+        <v>202</v>
+      </c>
+      <c r="B203">
+        <v>7453624</v>
+      </c>
+      <c r="C203" t="s">
+        <v>68</v>
+      </c>
+      <c r="D203" t="s">
+        <v>69</v>
+      </c>
+      <c r="E203" s="2">
+        <v>45703.5</v>
+      </c>
+      <c r="F203">
+        <v>26</v>
+      </c>
+      <c r="G203" t="s">
+        <v>80</v>
+      </c>
+      <c r="H203" t="s">
+        <v>71</v>
+      </c>
+      <c r="I203">
+        <v>1</v>
+      </c>
+      <c r="J203">
+        <v>2</v>
+      </c>
+      <c r="K203">
+        <v>3</v>
+      </c>
+      <c r="L203">
+        <v>3</v>
+      </c>
+      <c r="M203">
+        <v>2</v>
+      </c>
+      <c r="N203">
+        <v>5</v>
+      </c>
+      <c r="O203" t="s">
+        <v>234</v>
+      </c>
+      <c r="P203" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q203">
+        <v>2.6</v>
+      </c>
+      <c r="R203">
+        <v>2.05</v>
+      </c>
+      <c r="S203">
+        <v>4</v>
+      </c>
+      <c r="T203">
+        <v>1.41</v>
+      </c>
+      <c r="U203">
+        <v>2.65</v>
+      </c>
+      <c r="V203">
+        <v>2.87</v>
+      </c>
+      <c r="W203">
+        <v>1.36</v>
+      </c>
+      <c r="X203">
+        <v>7.5</v>
+      </c>
+      <c r="Y203">
+        <v>1.07</v>
+      </c>
+      <c r="Z203">
+        <v>1.85</v>
+      </c>
+      <c r="AA203">
+        <v>3.5</v>
+      </c>
+      <c r="AB203">
+        <v>4.1</v>
+      </c>
+      <c r="AC203">
+        <v>1.06</v>
+      </c>
+      <c r="AD203">
+        <v>8.6</v>
+      </c>
+      <c r="AE203">
+        <v>1.36</v>
+      </c>
+      <c r="AF203">
+        <v>3.04</v>
+      </c>
+      <c r="AG203">
+        <v>2</v>
+      </c>
+      <c r="AH203">
+        <v>1.75</v>
+      </c>
+      <c r="AI203">
+        <v>1.85</v>
+      </c>
+      <c r="AJ203">
+        <v>1.82</v>
+      </c>
+      <c r="AK203">
+        <v>1.27</v>
+      </c>
+      <c r="AL203">
+        <v>1.3</v>
+      </c>
+      <c r="AM203">
+        <v>1.77</v>
+      </c>
+      <c r="AN203">
+        <v>1.75</v>
+      </c>
+      <c r="AO203">
+        <v>1.25</v>
+      </c>
+      <c r="AP203">
+        <v>1.85</v>
+      </c>
+      <c r="AQ203">
+        <v>1.15</v>
+      </c>
+      <c r="AR203">
+        <v>1.28</v>
+      </c>
+      <c r="AS203">
+        <v>1.15</v>
+      </c>
+      <c r="AT203">
+        <v>2.43</v>
+      </c>
+      <c r="AU203">
+        <v>5</v>
+      </c>
+      <c r="AV203">
+        <v>7</v>
+      </c>
+      <c r="AW203">
+        <v>9</v>
+      </c>
+      <c r="AX203">
+        <v>14</v>
+      </c>
+      <c r="AY203">
+        <v>18</v>
+      </c>
+      <c r="AZ203">
+        <v>27</v>
+      </c>
+      <c r="BA203">
+        <v>2</v>
+      </c>
+      <c r="BB203">
+        <v>8</v>
+      </c>
+      <c r="BC203">
+        <v>10</v>
+      </c>
+      <c r="BD203">
+        <v>1.63</v>
+      </c>
+      <c r="BE203">
+        <v>6.75</v>
+      </c>
+      <c r="BF203">
+        <v>2.55</v>
+      </c>
+      <c r="BG203">
+        <v>1.29</v>
+      </c>
+      <c r="BH203">
+        <v>3.15</v>
+      </c>
+      <c r="BI203">
+        <v>1.49</v>
+      </c>
+      <c r="BJ203">
+        <v>2.4</v>
+      </c>
+      <c r="BK203">
+        <v>1.82</v>
+      </c>
+      <c r="BL203">
+        <v>1.86</v>
+      </c>
+      <c r="BM203">
+        <v>2.25</v>
+      </c>
+      <c r="BN203">
+        <v>1.55</v>
+      </c>
+      <c r="BO203">
+        <v>2.9</v>
+      </c>
+      <c r="BP203">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="204" spans="1:68">
+      <c r="A204" s="1">
+        <v>203</v>
+      </c>
+      <c r="B204">
+        <v>7453621</v>
+      </c>
+      <c r="C204" t="s">
+        <v>68</v>
+      </c>
+      <c r="D204" t="s">
+        <v>69</v>
+      </c>
+      <c r="E204" s="2">
+        <v>45703.59375</v>
+      </c>
+      <c r="F204">
+        <v>26</v>
+      </c>
+      <c r="G204" t="s">
+        <v>82</v>
+      </c>
+      <c r="H204" t="s">
+        <v>75</v>
+      </c>
+      <c r="I204">
+        <v>2</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>2</v>
+      </c>
+      <c r="L204">
+        <v>2</v>
+      </c>
+      <c r="M204">
+        <v>1</v>
+      </c>
+      <c r="N204">
+        <v>3</v>
+      </c>
+      <c r="O204" t="s">
+        <v>235</v>
+      </c>
+      <c r="P204" t="s">
+        <v>322</v>
+      </c>
+      <c r="Q204">
+        <v>2.15</v>
+      </c>
+      <c r="R204">
+        <v>2.3</v>
+      </c>
+      <c r="S204">
+        <v>4.5</v>
+      </c>
+      <c r="T204">
+        <v>1.31</v>
+      </c>
+      <c r="U204">
+        <v>3.1</v>
+      </c>
+      <c r="V204">
+        <v>2.4</v>
+      </c>
+      <c r="W204">
+        <v>1.49</v>
+      </c>
+      <c r="X204">
+        <v>5.75</v>
+      </c>
+      <c r="Y204">
+        <v>1.12</v>
+      </c>
+      <c r="Z204">
+        <v>1.67</v>
+      </c>
+      <c r="AA204">
+        <v>4</v>
+      </c>
+      <c r="AB204">
+        <v>4.5</v>
+      </c>
+      <c r="AC204">
+        <v>1.04</v>
+      </c>
+      <c r="AD204">
+        <v>10</v>
+      </c>
+      <c r="AE204">
+        <v>1.22</v>
+      </c>
+      <c r="AF204">
+        <v>4.2</v>
+      </c>
+      <c r="AG204">
+        <v>1.7</v>
+      </c>
+      <c r="AH204">
+        <v>2.05</v>
+      </c>
+      <c r="AI204">
+        <v>1.71</v>
+      </c>
+      <c r="AJ204">
+        <v>2</v>
+      </c>
+      <c r="AK204">
+        <v>1.19</v>
+      </c>
+      <c r="AL204">
+        <v>1.23</v>
+      </c>
+      <c r="AM204">
+        <v>2.15</v>
+      </c>
+      <c r="AN204">
+        <v>1.92</v>
+      </c>
+      <c r="AO204">
+        <v>0.5</v>
+      </c>
+      <c r="AP204">
+        <v>2</v>
+      </c>
+      <c r="AQ204">
+        <v>0.46</v>
+      </c>
+      <c r="AR204">
+        <v>1.66</v>
+      </c>
+      <c r="AS204">
+        <v>1.13</v>
+      </c>
+      <c r="AT204">
+        <v>2.79</v>
+      </c>
+      <c r="AU204">
+        <v>10</v>
+      </c>
+      <c r="AV204">
+        <v>3</v>
+      </c>
+      <c r="AW204">
+        <v>8</v>
+      </c>
+      <c r="AX204">
+        <v>9</v>
+      </c>
+      <c r="AY204">
+        <v>20</v>
+      </c>
+      <c r="AZ204">
+        <v>14</v>
+      </c>
+      <c r="BA204">
+        <v>4</v>
+      </c>
+      <c r="BB204">
+        <v>5</v>
+      </c>
+      <c r="BC204">
+        <v>9</v>
+      </c>
+      <c r="BD204">
+        <v>1.36</v>
+      </c>
+      <c r="BE204">
+        <v>7.5</v>
+      </c>
+      <c r="BF204">
+        <v>3.4</v>
+      </c>
+      <c r="BG204">
+        <v>1.21</v>
+      </c>
+      <c r="BH204">
+        <v>3.9</v>
+      </c>
+      <c r="BI204">
+        <v>1.36</v>
+      </c>
+      <c r="BJ204">
+        <v>2.8</v>
+      </c>
+      <c r="BK204">
+        <v>1.58</v>
+      </c>
+      <c r="BL204">
+        <v>2.18</v>
+      </c>
+      <c r="BM204">
+        <v>1.92</v>
+      </c>
+      <c r="BN204">
+        <v>1.77</v>
+      </c>
+      <c r="BO204">
+        <v>2.38</v>
+      </c>
+      <c r="BP204">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:68">
+      <c r="A205" s="1">
+        <v>204</v>
+      </c>
+      <c r="B205">
+        <v>7453625</v>
+      </c>
+      <c r="C205" t="s">
+        <v>68</v>
+      </c>
+      <c r="D205" t="s">
+        <v>69</v>
+      </c>
+      <c r="E205" s="2">
+        <v>45703.69791666666</v>
+      </c>
+      <c r="F205">
+        <v>26</v>
+      </c>
+      <c r="G205" t="s">
+        <v>81</v>
+      </c>
+      <c r="H205" t="s">
+        <v>70</v>
+      </c>
+      <c r="I205">
+        <v>2</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>2</v>
+      </c>
+      <c r="L205">
+        <v>2</v>
+      </c>
+      <c r="M205">
+        <v>2</v>
+      </c>
+      <c r="N205">
+        <v>4</v>
+      </c>
+      <c r="O205" t="s">
+        <v>236</v>
+      </c>
+      <c r="P205" t="s">
+        <v>323</v>
+      </c>
+      <c r="Q205">
+        <v>4.6</v>
+      </c>
+      <c r="R205">
+        <v>2.4</v>
+      </c>
+      <c r="S205">
+        <v>2.05</v>
+      </c>
+      <c r="T205">
+        <v>1.28</v>
+      </c>
+      <c r="U205">
+        <v>3.4</v>
+      </c>
+      <c r="V205">
+        <v>2.3</v>
+      </c>
+      <c r="W205">
+        <v>1.55</v>
+      </c>
+      <c r="X205">
+        <v>5.25</v>
+      </c>
+      <c r="Y205">
+        <v>1.13</v>
+      </c>
+      <c r="Z205">
+        <v>5.3</v>
+      </c>
+      <c r="AA205">
+        <v>4.33</v>
+      </c>
+      <c r="AB205">
+        <v>1.54</v>
+      </c>
+      <c r="AC205">
+        <v>1.02</v>
+      </c>
+      <c r="AD205">
+        <v>17</v>
+      </c>
+      <c r="AE205">
+        <v>1.18</v>
+      </c>
+      <c r="AF205">
+        <v>4.65</v>
+      </c>
+      <c r="AG205">
+        <v>1.57</v>
+      </c>
+      <c r="AH205">
+        <v>2.3</v>
+      </c>
+      <c r="AI205">
+        <v>1.66</v>
+      </c>
+      <c r="AJ205">
+        <v>2.05</v>
+      </c>
+      <c r="AK205">
+        <v>2.3</v>
+      </c>
+      <c r="AL205">
+        <v>1.2</v>
+      </c>
+      <c r="AM205">
+        <v>1.17</v>
+      </c>
+      <c r="AN205">
+        <v>1.25</v>
+      </c>
+      <c r="AO205">
+        <v>1.75</v>
+      </c>
+      <c r="AP205">
+        <v>1.23</v>
+      </c>
+      <c r="AQ205">
+        <v>1.69</v>
+      </c>
+      <c r="AR205">
+        <v>1.6</v>
+      </c>
+      <c r="AS205">
+        <v>1.67</v>
+      </c>
+      <c r="AT205">
+        <v>3.27</v>
+      </c>
+      <c r="AU205">
+        <v>4</v>
+      </c>
+      <c r="AV205">
+        <v>7</v>
+      </c>
+      <c r="AW205">
+        <v>2</v>
+      </c>
+      <c r="AX205">
+        <v>11</v>
+      </c>
+      <c r="AY205">
+        <v>7</v>
+      </c>
+      <c r="AZ205">
+        <v>25</v>
+      </c>
+      <c r="BA205">
+        <v>3</v>
+      </c>
+      <c r="BB205">
+        <v>14</v>
+      </c>
+      <c r="BC205">
+        <v>17</v>
+      </c>
+      <c r="BD205">
+        <v>2.8</v>
+      </c>
+      <c r="BE205">
+        <v>6.4</v>
+      </c>
+      <c r="BF205">
+        <v>1.54</v>
+      </c>
+      <c r="BG205">
+        <v>1.34</v>
+      </c>
+      <c r="BH205">
+        <v>2.9</v>
+      </c>
+      <c r="BI205">
+        <v>1.58</v>
+      </c>
+      <c r="BJ205">
+        <v>2.18</v>
+      </c>
+      <c r="BK205">
+        <v>1.96</v>
+      </c>
+      <c r="BL205">
+        <v>1.74</v>
+      </c>
+      <c r="BM205">
+        <v>2.48</v>
+      </c>
+      <c r="BN205">
+        <v>1.47</v>
+      </c>
+      <c r="BO205">
+        <v>3.15</v>
+      </c>
+      <c r="BP205">
+        <v>1.29</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1292" uniqueCount="324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="326">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -727,6 +727,9 @@
     <t>['10', '20']</t>
   </si>
   <si>
+    <t>['10', '67', '90']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -986,6 +989,9 @@
   </si>
   <si>
     <t>['72', '90+1']</t>
+  </si>
+  <si>
+    <t>['6', '55']</t>
   </si>
 </sst>
 </file>
@@ -1347,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP205"/>
+  <dimension ref="A1:BP209"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1603,7 +1609,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1681,10 +1687,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ2">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1887,10 +1893,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2093,10 +2099,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ4">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2299,10 +2305,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ5">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2505,10 +2511,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ6">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2633,7 +2639,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2711,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ7">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2917,10 +2923,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ8">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3123,10 +3129,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ9">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3323,25 +3329,25 @@
         <v>3.75</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP10">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ10">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AU10">
         <v>5</v>
@@ -3457,7 +3463,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3529,25 +3535,25 @@
         <v>1.9</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ11">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3735,25 +3741,25 @@
         <v>1.35</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ12">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3869,7 +3875,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3947,19 +3953,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ13">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AU13">
         <v>4</v>
@@ -4075,7 +4081,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4147,25 +4153,25 @@
         <v>1.45</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ14">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AU14">
         <v>8</v>
@@ -4281,7 +4287,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4359,19 +4365,19 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ15">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AU15">
         <v>7</v>
@@ -4559,25 +4565,25 @@
         <v>1.15</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP16">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ16">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AU16">
         <v>3</v>
@@ -4693,7 +4699,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4765,25 +4771,25 @@
         <v>3.6</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ17">
+        <v>1.19</v>
+      </c>
+      <c r="AR17">
         <v>1.15</v>
       </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
       <c r="AS17">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AU17">
         <v>4</v>
@@ -4971,25 +4977,25 @@
         <v>1.67</v>
       </c>
       <c r="AN18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ18">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR18">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="AS18">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="AT18">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -5177,25 +5183,25 @@
         <v>1.57</v>
       </c>
       <c r="AN19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO19">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ19">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR19">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="AS19">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AT19">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AU19">
         <v>7</v>
@@ -5311,7 +5317,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5386,22 +5392,22 @@
         <v>3</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP20">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ20">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR20">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AS20">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AT20">
-        <v>2.85</v>
+        <v>3.09</v>
       </c>
       <c r="AU20">
         <v>10</v>
@@ -5592,22 +5598,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP21">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ21">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR21">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS21">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AT21">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="AU21">
         <v>3</v>
@@ -5723,7 +5729,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5795,25 +5801,25 @@
         <v>1.33</v>
       </c>
       <c r="AN22">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ22">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR22">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AS22">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AT22">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="AU22">
         <v>8</v>
@@ -5929,7 +5935,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6001,25 +6007,25 @@
         <v>2.62</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ23">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR23">
-        <v>2.53</v>
+        <v>1.91</v>
       </c>
       <c r="AS23">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="AT23">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="AU23">
         <v>9</v>
@@ -6207,25 +6213,25 @@
         <v>1.38</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO24">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP24">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ24">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR24">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AS24">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AT24">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6341,7 +6347,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6416,22 +6422,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ25">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR25">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AS25">
-        <v>0.78</v>
+        <v>0.62</v>
       </c>
       <c r="AT25">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="AU25">
         <v>9</v>
@@ -6619,16 +6625,16 @@
         <v>2.4</v>
       </c>
       <c r="AN26">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP26">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ26">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR26">
         <v>1.53</v>
@@ -6753,7 +6759,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6825,25 +6831,25 @@
         <v>1.29</v>
       </c>
       <c r="AN27">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ27">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR27">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="AS27">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="AT27">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -6959,7 +6965,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7034,22 +7040,22 @@
         <v>0</v>
       </c>
       <c r="AO28">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ28">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR28">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="AS28">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="AT28">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="AU28">
         <v>5</v>
@@ -7165,7 +7171,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7237,25 +7243,25 @@
         <v>1.33</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO29">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP29">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ29">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR29">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="AS29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AT29">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AU29">
         <v>10</v>
@@ -7443,25 +7449,25 @@
         <v>2.05</v>
       </c>
       <c r="AN30">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP30">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ30">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR30">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AS30">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AT30">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7649,25 +7655,25 @@
         <v>1.4</v>
       </c>
       <c r="AN31">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ31">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR31">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AS31">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="AT31">
-        <v>2.74</v>
+        <v>3.13</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7855,25 +7861,25 @@
         <v>1.45</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ32">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR32">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AS32">
-        <v>0.59</v>
+        <v>0.97</v>
       </c>
       <c r="AT32">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -8061,25 +8067,25 @@
         <v>1.91</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33">
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ33">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR33">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="AS33">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AT33">
-        <v>3.32</v>
+        <v>2.84</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8195,7 +8201,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8267,25 +8273,25 @@
         <v>1.85</v>
       </c>
       <c r="AN34">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO34">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ34">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR34">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AS34">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT34">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AU34">
         <v>4</v>
@@ -8476,22 +8482,22 @@
         <v>1.5</v>
       </c>
       <c r="AO35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ35">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR35">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="AS35">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="AT35">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AU35">
         <v>5</v>
@@ -8607,7 +8613,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8682,22 +8688,22 @@
         <v>2</v>
       </c>
       <c r="AO36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ36">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR36">
-        <v>0.9399999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="AS36">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AT36">
-        <v>2.59</v>
+        <v>3.09</v>
       </c>
       <c r="AU36">
         <v>6</v>
@@ -8885,25 +8891,25 @@
         <v>1.09</v>
       </c>
       <c r="AN37">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AO37">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP37">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ37">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR37">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="AS37">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AT37">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AU37">
         <v>0</v>
@@ -9091,25 +9097,25 @@
         <v>2</v>
       </c>
       <c r="AN38">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AO38">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP38">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ38">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR38">
-        <v>1.16</v>
+        <v>0.84</v>
       </c>
       <c r="AS38">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="AT38">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9303,19 +9309,19 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ39">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR39">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="AS39">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="AT39">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9503,25 +9509,25 @@
         <v>2.1</v>
       </c>
       <c r="AN40">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO40">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ40">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR40">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AS40">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AT40">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9637,7 +9643,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9709,25 +9715,25 @@
         <v>1.5</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO41">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP41">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ41">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR41">
-        <v>1.62</v>
+        <v>1.23</v>
       </c>
       <c r="AS41">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="AT41">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -9843,7 +9849,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9915,25 +9921,25 @@
         <v>1.43</v>
       </c>
       <c r="AN42">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AO42">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ42">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR42">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="AS42">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AT42">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -10121,25 +10127,25 @@
         <v>1.85</v>
       </c>
       <c r="AN43">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO43">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP43">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ43">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR43">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AS43">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="AT43">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AU43">
         <v>5</v>
@@ -10327,25 +10333,25 @@
         <v>2.4</v>
       </c>
       <c r="AN44">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP44">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ44">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR44">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AS44">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AT44">
-        <v>3.29</v>
+        <v>3.49</v>
       </c>
       <c r="AU44">
         <v>11</v>
@@ -10536,22 +10542,22 @@
         <v>1.5</v>
       </c>
       <c r="AO45">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP45">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ45">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR45">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AS45">
-        <v>1.18</v>
+        <v>1.71</v>
       </c>
       <c r="AT45">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AU45">
         <v>9</v>
@@ -10739,25 +10745,25 @@
         <v>1.77</v>
       </c>
       <c r="AN46">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AO46">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP46">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ46">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR46">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AS46">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AT46">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="AU46">
         <v>7</v>
@@ -10945,25 +10951,25 @@
         <v>1.7</v>
       </c>
       <c r="AN47">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AO47">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ47">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR47">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="AS47">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="AT47">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -11079,7 +11085,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11151,25 +11157,25 @@
         <v>1.7</v>
       </c>
       <c r="AN48">
+        <v>1.83</v>
+      </c>
+      <c r="AO48">
         <v>1.33</v>
       </c>
-      <c r="AO48">
-        <v>0.33</v>
-      </c>
       <c r="AP48">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ48">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR48">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AS48">
-        <v>0.51</v>
+        <v>0.79</v>
       </c>
       <c r="AT48">
-        <v>1.66</v>
+        <v>2.09</v>
       </c>
       <c r="AU48">
         <v>4</v>
@@ -11285,7 +11291,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11357,25 +11363,25 @@
         <v>1.5</v>
       </c>
       <c r="AN49">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AO49">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ49">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR49">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="AS49">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AT49">
-        <v>3.77</v>
+        <v>3.32</v>
       </c>
       <c r="AU49">
         <v>3</v>
@@ -11491,7 +11497,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11563,25 +11569,25 @@
         <v>1.1</v>
       </c>
       <c r="AN50">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO50">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP50">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ50">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR50">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AS50">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AT50">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11697,7 +11703,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11769,25 +11775,25 @@
         <v>2.05</v>
       </c>
       <c r="AN51">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AO51">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP51">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ51">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR51">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AS51">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AT51">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="AU51">
         <v>9</v>
@@ -11975,25 +11981,25 @@
         <v>1.54</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO52">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ52">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR52">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AS52">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AT52">
-        <v>3.53</v>
+        <v>3.33</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12181,25 +12187,25 @@
         <v>1.37</v>
       </c>
       <c r="AN53">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO53">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP53">
+        <v>0.92</v>
+      </c>
+      <c r="AQ53">
         <v>1.23</v>
       </c>
-      <c r="AQ53">
-        <v>0.62</v>
-      </c>
       <c r="AR53">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="AS53">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AT53">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AU53">
         <v>5</v>
@@ -12387,25 +12393,25 @@
         <v>2.21</v>
       </c>
       <c r="AN54">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO54">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AP54">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ54">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR54">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AS54">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="AT54">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AU54">
         <v>13</v>
@@ -12593,25 +12599,25 @@
         <v>2.17</v>
       </c>
       <c r="AN55">
+        <v>1.4</v>
+      </c>
+      <c r="AO55">
         <v>1.33</v>
       </c>
-      <c r="AO55">
-        <v>1.67</v>
-      </c>
       <c r="AP55">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ55">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR55">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="AS55">
-        <v>0.98</v>
+        <v>1.24</v>
       </c>
       <c r="AT55">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AU55">
         <v>8</v>
@@ -12727,7 +12733,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -12799,25 +12805,25 @@
         <v>1.65</v>
       </c>
       <c r="AN56">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO56">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="AP56">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ56">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR56">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AS56">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AT56">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AU56">
         <v>5</v>
@@ -13005,25 +13011,25 @@
         <v>1.22</v>
       </c>
       <c r="AN57">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO57">
-        <v>0.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP57">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ57">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR57">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="AS57">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AT57">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -13139,7 +13145,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13211,25 +13217,25 @@
         <v>1.55</v>
       </c>
       <c r="AN58">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AO58">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ58">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR58">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="AS58">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AT58">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AU58">
         <v>0</v>
@@ -13345,7 +13351,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13417,25 +13423,25 @@
         <v>1.38</v>
       </c>
       <c r="AN59">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO59">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP59">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ59">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR59">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AS59">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AT59">
-        <v>3.03</v>
+        <v>3.22</v>
       </c>
       <c r="AU59">
         <v>7</v>
@@ -13623,25 +13629,25 @@
         <v>1.84</v>
       </c>
       <c r="AN60">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AP60">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ60">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR60">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AS60">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AT60">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AU60">
         <v>5</v>
@@ -13757,7 +13763,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13829,25 +13835,25 @@
         <v>2.5</v>
       </c>
       <c r="AN61">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AO61">
+        <v>1.67</v>
+      </c>
+      <c r="AP61">
+        <v>2</v>
+      </c>
+      <c r="AQ61">
+        <v>1.54</v>
+      </c>
+      <c r="AR61">
+        <v>1.8</v>
+      </c>
+      <c r="AS61">
         <v>1.5</v>
       </c>
-      <c r="AP61">
-        <v>2.31</v>
-      </c>
-      <c r="AQ61">
-        <v>1.23</v>
-      </c>
-      <c r="AR61">
-        <v>2.01</v>
-      </c>
-      <c r="AS61">
-        <v>0.86</v>
-      </c>
       <c r="AT61">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="AU61">
         <v>10</v>
@@ -14035,25 +14041,25 @@
         <v>1.51</v>
       </c>
       <c r="AN62">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AO62">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ62">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR62">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS62">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AT62">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14241,22 +14247,22 @@
         <v>2.3</v>
       </c>
       <c r="AN63">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AO63">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AP63">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ63">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR63">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AS63">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT63">
         <v>3.14</v>
@@ -14447,25 +14453,25 @@
         <v>2</v>
       </c>
       <c r="AN64">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AO64">
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ64">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR64">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS64">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AT64">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="AU64">
         <v>3</v>
@@ -14581,7 +14587,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14653,25 +14659,25 @@
         <v>1.51</v>
       </c>
       <c r="AN65">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AO65">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP65">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ65">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR65">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AS65">
-        <v>0.88</v>
+        <v>1.42</v>
       </c>
       <c r="AT65">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14859,25 +14865,25 @@
         <v>1.22</v>
       </c>
       <c r="AN66">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AO66">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AP66">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ66">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR66">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AS66">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AT66">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -15065,25 +15071,25 @@
         <v>2.5</v>
       </c>
       <c r="AN67">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AO67">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AP67">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ67">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR67">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AS67">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AT67">
-        <v>3.01</v>
+        <v>3.18</v>
       </c>
       <c r="AU67">
         <v>6</v>
@@ -15199,7 +15205,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15271,25 +15277,25 @@
         <v>1.44</v>
       </c>
       <c r="AN68">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO68">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP68">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ68">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR68">
-        <v>1.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS68">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AT68">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AU68">
         <v>4</v>
@@ -15405,7 +15411,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15477,25 +15483,25 @@
         <v>1.35</v>
       </c>
       <c r="AN69">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AO69">
-        <v>2.33</v>
+        <v>1.63</v>
       </c>
       <c r="AP69">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ69">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR69">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AS69">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="AT69">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15683,25 +15689,25 @@
         <v>3.75</v>
       </c>
       <c r="AN70">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AO70">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ70">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR70">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AS70">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AT70">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="AU70">
         <v>7</v>
@@ -15889,25 +15895,25 @@
         <v>3</v>
       </c>
       <c r="AN71">
-        <v>2.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO71">
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ71">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR71">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AS71">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="AT71">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="AU71">
         <v>6</v>
@@ -16095,25 +16101,25 @@
         <v>2.2</v>
       </c>
       <c r="AN72">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO72">
-        <v>0.75</v>
+        <v>1.38</v>
       </c>
       <c r="AP72">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ72">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR72">
-        <v>1.82</v>
+        <v>1.33</v>
       </c>
       <c r="AS72">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AT72">
-        <v>3.24</v>
+        <v>2.72</v>
       </c>
       <c r="AU72">
         <v>6</v>
@@ -16229,7 +16235,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16301,25 +16307,25 @@
         <v>2.15</v>
       </c>
       <c r="AN73">
-        <v>1.5</v>
+        <v>0.88</v>
       </c>
       <c r="AO73">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP73">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ73">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR73">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AS73">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AT73">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16435,7 +16441,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16507,25 +16513,25 @@
         <v>2.75</v>
       </c>
       <c r="AN74">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AO74">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AP74">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ74">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR74">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AS74">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="AT74">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AU74">
         <v>10</v>
@@ -16713,25 +16719,25 @@
         <v>1.62</v>
       </c>
       <c r="AN75">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AO75">
-        <v>0.6</v>
+        <v>1.22</v>
       </c>
       <c r="AP75">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ75">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR75">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AS75">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AT75">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16919,25 +16925,25 @@
         <v>1.15</v>
       </c>
       <c r="AN76">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AO76">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ76">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR76">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AS76">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AT76">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17125,25 +17131,25 @@
         <v>1.33</v>
       </c>
       <c r="AN77">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO77">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AP77">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ77">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR77">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AS77">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AT77">
-        <v>2.48</v>
+        <v>2.79</v>
       </c>
       <c r="AU77">
         <v>3</v>
@@ -17331,25 +17337,25 @@
         <v>2.4</v>
       </c>
       <c r="AN78">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="AO78">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP78">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ78">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR78">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AS78">
-        <v>0.58</v>
+        <v>0.89</v>
       </c>
       <c r="AT78">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17537,25 +17543,25 @@
         <v>2.25</v>
       </c>
       <c r="AN79">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AO79">
-        <v>0.25</v>
+        <v>0.89</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ79">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR79">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AS79">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AT79">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="AU79">
         <v>6</v>
@@ -17743,25 +17749,25 @@
         <v>1.86</v>
       </c>
       <c r="AN80">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AO80">
-        <v>0.6</v>
+        <v>1.44</v>
       </c>
       <c r="AP80">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ80">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR80">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AS80">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AT80">
-        <v>3.75</v>
+        <v>3.49</v>
       </c>
       <c r="AU80">
         <v>6</v>
@@ -17949,25 +17955,25 @@
         <v>1.33</v>
       </c>
       <c r="AN81">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AO81">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AP81">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ81">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR81">
-        <v>0.89</v>
+        <v>1.06</v>
       </c>
       <c r="AS81">
-        <v>0.84</v>
+        <v>1.33</v>
       </c>
       <c r="AT81">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="AU81">
         <v>13</v>
@@ -18155,25 +18161,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AO82">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ82">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR82">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AS82">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AT82">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AU82">
         <v>0</v>
@@ -18289,7 +18295,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18361,25 +18367,25 @@
         <v>1.25</v>
       </c>
       <c r="AN83">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO83">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ83">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR83">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AS83">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AT83">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18567,25 +18573,25 @@
         <v>1.96</v>
       </c>
       <c r="AN84">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AO84">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ84">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR84">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AS84">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AT84">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="AU84">
         <v>7</v>
@@ -18773,25 +18779,25 @@
         <v>2.15</v>
       </c>
       <c r="AN85">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO85">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AP85">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ85">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR85">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AS85">
-        <v>0.91</v>
+        <v>1.31</v>
       </c>
       <c r="AT85">
-        <v>2.58</v>
+        <v>2.87</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18907,7 +18913,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -18979,25 +18985,25 @@
         <v>2.65</v>
       </c>
       <c r="AN86">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AO86">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AP86">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ86">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR86">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AS86">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT86">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="AU86">
         <v>5</v>
@@ -19185,25 +19191,25 @@
         <v>1.38</v>
       </c>
       <c r="AN87">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="AO87">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AP87">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ87">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AS87">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AT87">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19391,25 +19397,25 @@
         <v>1.38</v>
       </c>
       <c r="AN88">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AO88">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP88">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ88">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR88">
-        <v>1.14</v>
+        <v>0.98</v>
       </c>
       <c r="AS88">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AT88">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AU88">
         <v>7</v>
@@ -19597,25 +19603,25 @@
         <v>2.15</v>
       </c>
       <c r="AN89">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AO89">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AP89">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ89">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR89">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS89">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AT89">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19803,25 +19809,25 @@
         <v>1.9</v>
       </c>
       <c r="AN90">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ90">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR90">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS90">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="AT90">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="AU90">
         <v>6</v>
@@ -19937,7 +19943,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20009,25 +20015,25 @@
         <v>0</v>
       </c>
       <c r="AN91">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="AO91">
-        <v>0.5</v>
+        <v>1.09</v>
       </c>
       <c r="AP91">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ91">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR91">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AS91">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT91">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20143,7 +20149,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20215,25 +20221,25 @@
         <v>1.45</v>
       </c>
       <c r="AN92">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AO92">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AP92">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ92">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR92">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AS92">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AT92">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="AU92">
         <v>5</v>
@@ -20421,25 +20427,25 @@
         <v>1.49</v>
       </c>
       <c r="AN93">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO93">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AP93">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ93">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR93">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AS93">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AT93">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="AU93">
         <v>7</v>
@@ -20555,7 +20561,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20627,25 +20633,25 @@
         <v>2.4</v>
       </c>
       <c r="AN94">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AO94">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AP94">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ94">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR94">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AS94">
         <v>1.57</v>
       </c>
       <c r="AT94">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="AU94">
         <v>10</v>
@@ -20833,25 +20839,25 @@
         <v>2.4</v>
       </c>
       <c r="AN95">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AO95">
-        <v>0.8</v>
+        <v>1.36</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ95">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR95">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AS95">
-        <v>0.82</v>
+        <v>1.01</v>
       </c>
       <c r="AT95">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AU95">
         <v>6</v>
@@ -20967,7 +20973,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21039,25 +21045,25 @@
         <v>1.38</v>
       </c>
       <c r="AN96">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AO96">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AP96">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ96">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR96">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="AS96">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AT96">
-        <v>3.66</v>
+        <v>3.19</v>
       </c>
       <c r="AU96">
         <v>0</v>
@@ -21173,7 +21179,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21245,25 +21251,25 @@
         <v>2.7</v>
       </c>
       <c r="AN97">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AO97">
-        <v>0.2</v>
+        <v>0.82</v>
       </c>
       <c r="AP97">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ97">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR97">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AS97">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AT97">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21451,25 +21457,25 @@
         <v>1.98</v>
       </c>
       <c r="AN98">
+        <v>1.25</v>
+      </c>
+      <c r="AO98">
         <v>1.33</v>
       </c>
-      <c r="AO98">
-        <v>1.6</v>
-      </c>
       <c r="AP98">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ98">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR98">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AS98">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AT98">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="AU98">
         <v>9</v>
@@ -21585,7 +21591,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21657,25 +21663,25 @@
         <v>1.6</v>
       </c>
       <c r="AN99">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AO99">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="AP99">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ99">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR99">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS99">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AT99">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AU99">
         <v>5</v>
@@ -21791,7 +21797,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21863,25 +21869,25 @@
         <v>1.26</v>
       </c>
       <c r="AN100">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO100">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ100">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR100">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AS100">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AT100">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -21997,7 +22003,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22069,25 +22075,25 @@
         <v>1.28</v>
       </c>
       <c r="AN101">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO101">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ101">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR101">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AS101">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AT101">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="AU101">
         <v>5</v>
@@ -22275,25 +22281,25 @@
         <v>1.83</v>
       </c>
       <c r="AN102">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="AO102">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AP102">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ102">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR102">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AS102">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AT102">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="AU102">
         <v>8</v>
@@ -22481,25 +22487,25 @@
         <v>1.58</v>
       </c>
       <c r="AN103">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO103">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AP103">
+        <v>1.15</v>
+      </c>
+      <c r="AQ103">
+        <v>1.27</v>
+      </c>
+      <c r="AR103">
+        <v>1.46</v>
+      </c>
+      <c r="AS103">
         <v>1.58</v>
       </c>
-      <c r="AQ103">
-        <v>0.92</v>
-      </c>
-      <c r="AR103">
-        <v>1.64</v>
-      </c>
-      <c r="AS103">
-        <v>1.41</v>
-      </c>
       <c r="AT103">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22687,25 +22693,25 @@
         <v>2.75</v>
       </c>
       <c r="AN104">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AO104">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ104">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR104">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AS104">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AT104">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="AU104">
         <v>7</v>
@@ -22893,25 +22899,25 @@
         <v>1.24</v>
       </c>
       <c r="AN105">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="AO105">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ105">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR105">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="AS105">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="AT105">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="AU105">
         <v>5</v>
@@ -23027,7 +23033,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23099,25 +23105,25 @@
         <v>1.5</v>
       </c>
       <c r="AN106">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AO106">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AP106">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ106">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR106">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AS106">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AT106">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="AU106">
         <v>6</v>
@@ -23233,7 +23239,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23305,25 +23311,25 @@
         <v>1.22</v>
       </c>
       <c r="AN107">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="AO107">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AP107">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ107">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR107">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AS107">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="AT107">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="AU107">
         <v>6</v>
@@ -23439,7 +23445,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23511,25 +23517,25 @@
         <v>1.38</v>
       </c>
       <c r="AN108">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AO108">
-        <v>0.86</v>
+        <v>1.15</v>
       </c>
       <c r="AP108">
+        <v>1.19</v>
+      </c>
+      <c r="AQ108">
         <v>1.23</v>
       </c>
-      <c r="AQ108">
-        <v>0.62</v>
-      </c>
       <c r="AR108">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AS108">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AT108">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23717,25 +23723,25 @@
         <v>1.8</v>
       </c>
       <c r="AN109">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="AO109">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AP109">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ109">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR109">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AS109">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AT109">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23851,7 +23857,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -23923,25 +23929,25 @@
         <v>1.45</v>
       </c>
       <c r="AN110">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AO110">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AP110">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ110">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR110">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AS110">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AT110">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -24129,25 +24135,25 @@
         <v>1.9</v>
       </c>
       <c r="AN111">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AO111">
-        <v>0.67</v>
+        <v>1.38</v>
       </c>
       <c r="AP111">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ111">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR111">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AS111">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AT111">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AU111">
         <v>13</v>
@@ -24335,25 +24341,25 @@
         <v>1.65</v>
       </c>
       <c r="AN112">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="AO112">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AP112">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ112">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR112">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AS112">
         <v>1.85</v>
       </c>
       <c r="AT112">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AU112">
         <v>8</v>
@@ -24469,7 +24475,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24541,25 +24547,25 @@
         <v>1.05</v>
       </c>
       <c r="AN113">
-        <v>0.83</v>
+        <v>0.46</v>
       </c>
       <c r="AO113">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AP113">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ113">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR113">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="AS113">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AT113">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="AU113">
         <v>6</v>
@@ -24747,25 +24753,25 @@
         <v>2.5</v>
       </c>
       <c r="AN114">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AO114">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ114">
+        <v>1.19</v>
+      </c>
+      <c r="AR114">
+        <v>1.49</v>
+      </c>
+      <c r="AS114">
         <v>1.15</v>
       </c>
-      <c r="AR114">
-        <v>1.76</v>
-      </c>
-      <c r="AS114">
-        <v>1.13</v>
-      </c>
       <c r="AT114">
-        <v>2.89</v>
+        <v>2.64</v>
       </c>
       <c r="AU114">
         <v>7</v>
@@ -24953,25 +24959,25 @@
         <v>0</v>
       </c>
       <c r="AN115">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AO115">
-        <v>0.71</v>
+        <v>1.21</v>
       </c>
       <c r="AP115">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ115">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR115">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AS115">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AT115">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AU115">
         <v>6</v>
@@ -25159,25 +25165,25 @@
         <v>1.53</v>
       </c>
       <c r="AN116">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AO116">
-        <v>0.67</v>
+        <v>1.07</v>
       </c>
       <c r="AP116">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ116">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR116">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AS116">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AT116">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AU116">
         <v>5</v>
@@ -25365,25 +25371,25 @@
         <v>2.5</v>
       </c>
       <c r="AN117">
-        <v>2.71</v>
+        <v>2.21</v>
       </c>
       <c r="AO117">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
       <c r="AP117">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ117">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR117">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AS117">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AT117">
-        <v>3.18</v>
+        <v>3.37</v>
       </c>
       <c r="AU117">
         <v>6</v>
@@ -25571,25 +25577,25 @@
         <v>0</v>
       </c>
       <c r="AN118">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AO118">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ118">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR118">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AS118">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="AT118">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AU118">
         <v>11</v>
@@ -25705,7 +25711,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25777,25 +25783,25 @@
         <v>0</v>
       </c>
       <c r="AN119">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AO119">
-        <v>0.71</v>
+        <v>1.36</v>
       </c>
       <c r="AP119">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ119">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR119">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AS119">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AT119">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AU119">
         <v>0</v>
@@ -25983,25 +25989,25 @@
         <v>1.88</v>
       </c>
       <c r="AN120">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AO120">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AP120">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ120">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR120">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AS120">
-        <v>0.99</v>
+        <v>1.34</v>
       </c>
       <c r="AT120">
-        <v>2.63</v>
+        <v>2.87</v>
       </c>
       <c r="AU120">
         <v>12</v>
@@ -26189,25 +26195,25 @@
         <v>2.15</v>
       </c>
       <c r="AN121">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AO121">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ121">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR121">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AS121">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AT121">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AU121">
         <v>7</v>
@@ -26323,7 +26329,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26395,25 +26401,25 @@
         <v>1.38</v>
       </c>
       <c r="AN122">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="AO122">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="AP122">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ122">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR122">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AS122">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AT122">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AU122">
         <v>6</v>
@@ -26601,25 +26607,25 @@
         <v>4</v>
       </c>
       <c r="AN123">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AO123">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AP123">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ123">
+        <v>1.19</v>
+      </c>
+      <c r="AR123">
+        <v>1.86</v>
+      </c>
+      <c r="AS123">
         <v>1.15</v>
       </c>
-      <c r="AR123">
-        <v>2.07</v>
-      </c>
-      <c r="AS123">
-        <v>1.13</v>
-      </c>
       <c r="AT123">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="AU123">
         <v>9</v>
@@ -26807,25 +26813,25 @@
         <v>1.92</v>
       </c>
       <c r="AN124">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AO124">
-        <v>0.57</v>
+        <v>1.4</v>
       </c>
       <c r="AP124">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ124">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR124">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AS124">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="AT124">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AU124">
         <v>3</v>
@@ -26941,7 +26947,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27013,22 +27019,22 @@
         <v>1.2</v>
       </c>
       <c r="AN125">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="AO125">
-        <v>1.71</v>
+        <v>2.27</v>
       </c>
       <c r="AP125">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ125">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR125">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AS125">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AT125">
         <v>3.15</v>
@@ -27219,25 +27225,25 @@
         <v>1.36</v>
       </c>
       <c r="AN126">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="AO126">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AP126">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ126">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR126">
         <v>1.26</v>
       </c>
       <c r="AS126">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AT126">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="AU126">
         <v>3</v>
@@ -27353,7 +27359,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27425,25 +27431,25 @@
         <v>1.25</v>
       </c>
       <c r="AN127">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="AO127">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ127">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR127">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="AS127">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AT127">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AU127">
         <v>9</v>
@@ -27631,25 +27637,25 @@
         <v>1.98</v>
       </c>
       <c r="AN128">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO128">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AP128">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ128">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR128">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AS128">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AT128">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="AU128">
         <v>7</v>
@@ -27765,7 +27771,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27837,25 +27843,25 @@
         <v>1.68</v>
       </c>
       <c r="AN129">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AO129">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AP129">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ129">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR129">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AS129">
-        <v>0.99</v>
+        <v>1.31</v>
       </c>
       <c r="AT129">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AU129">
         <v>9</v>
@@ -27971,7 +27977,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28043,25 +28049,25 @@
         <v>3.6</v>
       </c>
       <c r="AN130">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="AO130">
-        <v>0.5</v>
+        <v>1.06</v>
       </c>
       <c r="AP130">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ130">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR130">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AS130">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AT130">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AU130">
         <v>7</v>
@@ -28249,25 +28255,25 @@
         <v>1.45</v>
       </c>
       <c r="AN131">
-        <v>2.13</v>
+        <v>1.38</v>
       </c>
       <c r="AO131">
-        <v>0.88</v>
+        <v>1.13</v>
       </c>
       <c r="AP131">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ131">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR131">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS131">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AT131">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28383,7 +28389,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28455,25 +28461,25 @@
         <v>1.26</v>
       </c>
       <c r="AN132">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO132">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AP132">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ132">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR132">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS132">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AT132">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="AU132">
         <v>6</v>
@@ -28661,25 +28667,25 @@
         <v>1.95</v>
       </c>
       <c r="AN133">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AO133">
-        <v>0.63</v>
+        <v>1.13</v>
       </c>
       <c r="AP133">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ133">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR133">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AS133">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AT133">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28795,7 +28801,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28867,25 +28873,25 @@
         <v>1.77</v>
       </c>
       <c r="AN134">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AO134">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ134">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR134">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AS134">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AT134">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU134">
         <v>9</v>
@@ -29073,25 +29079,25 @@
         <v>1.22</v>
       </c>
       <c r="AN135">
-        <v>1.38</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO135">
-        <v>0.75</v>
+        <v>1.44</v>
       </c>
       <c r="AP135">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ135">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR135">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS135">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AT135">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="AU135">
         <v>8</v>
@@ -29207,7 +29213,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29279,25 +29285,25 @@
         <v>3.35</v>
       </c>
       <c r="AN136">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="AO136">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="AP136">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ136">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR136">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AS136">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AT136">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AU136">
         <v>7</v>
@@ -29488,22 +29494,22 @@
         <v>1.13</v>
       </c>
       <c r="AO137">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP137">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ137">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR137">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AS137">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AT137">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AU137">
         <v>2</v>
@@ -29691,25 +29697,25 @@
         <v>1.52</v>
       </c>
       <c r="AN138">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AO138">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AP138">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ138">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR138">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="AS138">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AT138">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AU138">
         <v>7</v>
@@ -29897,25 +29903,25 @@
         <v>1.36</v>
       </c>
       <c r="AN139">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="AO139">
-        <v>0.63</v>
+        <v>1.35</v>
       </c>
       <c r="AP139">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ139">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR139">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AS139">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="AT139">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AU139">
         <v>9</v>
@@ -30103,25 +30109,25 @@
         <v>1.57</v>
       </c>
       <c r="AN140">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AO140">
-        <v>0.78</v>
+        <v>1.24</v>
       </c>
       <c r="AP140">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ140">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR140">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AS140">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AT140">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="AU140">
         <v>3</v>
@@ -30237,7 +30243,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30309,25 +30315,25 @@
         <v>1.66</v>
       </c>
       <c r="AN141">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="AO141">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ141">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR141">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AS141">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AT141">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="AU141">
         <v>2</v>
@@ -30515,25 +30521,25 @@
         <v>2.3</v>
       </c>
       <c r="AN142">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AO142">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="AP142">
+        <v>2</v>
+      </c>
+      <c r="AQ142">
         <v>2.31</v>
       </c>
-      <c r="AQ142">
-        <v>1.77</v>
-      </c>
       <c r="AR142">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="AS142">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AT142">
-        <v>3.79</v>
+        <v>3.56</v>
       </c>
       <c r="AU142">
         <v>6</v>
@@ -30649,7 +30655,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30721,25 +30727,25 @@
         <v>2.75</v>
       </c>
       <c r="AN143">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="AO143">
-        <v>0.88</v>
+        <v>1.29</v>
       </c>
       <c r="AP143">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ143">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR143">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AS143">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AT143">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="AU143">
         <v>14</v>
@@ -30855,7 +30861,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -30927,25 +30933,25 @@
         <v>1.3</v>
       </c>
       <c r="AN144">
-        <v>1.63</v>
+        <v>1.06</v>
       </c>
       <c r="AO144">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AP144">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ144">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR144">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AS144">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AT144">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AU144">
         <v>7</v>
@@ -31133,25 +31139,25 @@
         <v>2</v>
       </c>
       <c r="AN145">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AO145">
-        <v>0.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP145">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ145">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR145">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AS145">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AT145">
-        <v>2.97</v>
+        <v>2.82</v>
       </c>
       <c r="AU145">
         <v>6</v>
@@ -31267,7 +31273,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31339,25 +31345,25 @@
         <v>1.65</v>
       </c>
       <c r="AN146">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AO146">
-        <v>1</v>
+        <v>1.39</v>
       </c>
       <c r="AP146">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ146">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR146">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AS146">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AT146">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU146">
         <v>7</v>
@@ -31545,25 +31551,25 @@
         <v>1.83</v>
       </c>
       <c r="AN147">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AO147">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ147">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR147">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AS147">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AT147">
-        <v>3.09</v>
+        <v>2.98</v>
       </c>
       <c r="AU147">
         <v>8</v>
@@ -31679,7 +31685,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31754,22 +31760,22 @@
         <v>1.33</v>
       </c>
       <c r="AO148">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AP148">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ148">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR148">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AS148">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AT148">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="AU148">
         <v>2</v>
@@ -31885,7 +31891,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31957,25 +31963,25 @@
         <v>1.48</v>
       </c>
       <c r="AN149">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
       <c r="AO149">
-        <v>0.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP149">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ149">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR149">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AS149">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AT149">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AU149">
         <v>8</v>
@@ -32163,25 +32169,25 @@
         <v>1.75</v>
       </c>
       <c r="AN150">
-        <v>2.78</v>
+        <v>2.11</v>
       </c>
       <c r="AO150">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AP150">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ150">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR150">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AS150">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AT150">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="AU150">
         <v>7</v>
@@ -32369,25 +32375,25 @@
         <v>1.45</v>
       </c>
       <c r="AN151">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO151">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AP151">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ151">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR151">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AS151">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AT151">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AU151">
         <v>2</v>
@@ -32503,7 +32509,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32575,22 +32581,22 @@
         <v>1.5</v>
       </c>
       <c r="AN152">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="AO152">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AP152">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ152">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR152">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AS152">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AT152">
         <v>3.43</v>
@@ -32781,25 +32787,25 @@
         <v>1.72</v>
       </c>
       <c r="AN153">
-        <v>1.33</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO153">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AP153">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ153">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR153">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AS153">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT153">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AU153">
         <v>5</v>
@@ -32915,7 +32921,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -32987,25 +32993,25 @@
         <v>1.48</v>
       </c>
       <c r="AN154">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AO154">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AP154">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ154">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR154">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AS154">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AT154">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="AU154">
         <v>4</v>
@@ -33121,7 +33127,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33193,25 +33199,25 @@
         <v>1.38</v>
       </c>
       <c r="AN155">
-        <v>1.44</v>
+        <v>0.95</v>
       </c>
       <c r="AO155">
-        <v>0.7</v>
+        <v>1.26</v>
       </c>
       <c r="AP155">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ155">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR155">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AS155">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AT155">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33327,7 +33333,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33399,25 +33405,25 @@
         <v>3.4</v>
       </c>
       <c r="AN156">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AO156">
-        <v>0.78</v>
+        <v>1.21</v>
       </c>
       <c r="AP156">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ156">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR156">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AS156">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AT156">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AU156">
         <v>10</v>
@@ -33605,22 +33611,22 @@
         <v>1.93</v>
       </c>
       <c r="AN157">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AO157">
-        <v>0.67</v>
+        <v>1.26</v>
       </c>
       <c r="AP157">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ157">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR157">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AS157">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AT157">
         <v>2.5</v>
@@ -33739,7 +33745,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -33811,25 +33817,25 @@
         <v>1.3</v>
       </c>
       <c r="AN158">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AO158">
-        <v>0.78</v>
+        <v>1.47</v>
       </c>
       <c r="AP158">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ158">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR158">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AS158">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AT158">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="AU158">
         <v>4</v>
@@ -34017,25 +34023,25 @@
         <v>2.2</v>
       </c>
       <c r="AN159">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AO159">
-        <v>0.11</v>
+        <v>0.63</v>
       </c>
       <c r="AP159">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ159">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR159">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AS159">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT159">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AU159">
         <v>11</v>
@@ -34151,7 +34157,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34223,25 +34229,25 @@
         <v>1.5</v>
       </c>
       <c r="AN160">
-        <v>1.44</v>
+        <v>0.95</v>
       </c>
       <c r="AO160">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AP160">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ160">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR160">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AS160">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AT160">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AU160">
         <v>8</v>
@@ -34357,7 +34363,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34429,25 +34435,25 @@
         <v>2.95</v>
       </c>
       <c r="AN161">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AO161">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AP161">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ161">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR161">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AS161">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT161">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34635,25 +34641,25 @@
         <v>1.83</v>
       </c>
       <c r="AN162">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO162">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AP162">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ162">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR162">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS162">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AT162">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AU162">
         <v>7</v>
@@ -34769,7 +34775,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34841,25 +34847,25 @@
         <v>1.75</v>
       </c>
       <c r="AN163">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AO163">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AP163">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ163">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR163">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AS163">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AT163">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AU163">
         <v>7</v>
@@ -35047,22 +35053,22 @@
         <v>2.3</v>
       </c>
       <c r="AN164">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AO164">
-        <v>0.8</v>
+        <v>1.25</v>
       </c>
       <c r="AP164">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ164">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR164">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AS164">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AT164">
         <v>3</v>
@@ -35181,7 +35187,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35253,25 +35259,25 @@
         <v>1.34</v>
       </c>
       <c r="AN165">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="AO165">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AP165">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ165">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR165">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AS165">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AT165">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="AU165">
         <v>5</v>
@@ -35387,7 +35393,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35459,25 +35465,25 @@
         <v>1.21</v>
       </c>
       <c r="AN166">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="AO166">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP166">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ166">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR166">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AS166">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AT166">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AU166">
         <v>8</v>
@@ -35665,25 +35671,25 @@
         <v>1.33</v>
       </c>
       <c r="AN167">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AO167">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AP167">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ167">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR167">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AS167">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AT167">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="AU167">
         <v>4</v>
@@ -35799,7 +35805,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -35871,25 +35877,25 @@
         <v>1.32</v>
       </c>
       <c r="AN168">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AO168">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AP168">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ168">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR168">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AS168">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AT168">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="AU168">
         <v>6</v>
@@ -36077,25 +36083,25 @@
         <v>1.62</v>
       </c>
       <c r="AN169">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AO169">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="AP169">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ169">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR169">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS169">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AT169">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AU169">
         <v>8</v>
@@ -36283,25 +36289,25 @@
         <v>1.72</v>
       </c>
       <c r="AN170">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AO170">
-        <v>0.91</v>
+        <v>1.29</v>
       </c>
       <c r="AP170">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ170">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR170">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AS170">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AT170">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AU170">
         <v>4</v>
@@ -36417,7 +36423,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36489,25 +36495,25 @@
         <v>1.41</v>
       </c>
       <c r="AN171">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AO171">
-        <v>0.6</v>
+        <v>1.14</v>
       </c>
       <c r="AP171">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ171">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR171">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AS171">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AT171">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AU171">
         <v>2</v>
@@ -36623,7 +36629,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36695,25 +36701,25 @@
         <v>1.41</v>
       </c>
       <c r="AN172">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AO172">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AP172">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ172">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR172">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="AS172">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AT172">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="AU172">
         <v>3</v>
@@ -36829,7 +36835,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36901,25 +36907,25 @@
         <v>5.25</v>
       </c>
       <c r="AN173">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO173">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="AP173">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ173">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR173">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AS173">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AT173">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="AU173">
         <v>10</v>
@@ -37035,7 +37041,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37107,25 +37113,25 @@
         <v>1.26</v>
       </c>
       <c r="AN174">
-        <v>1.3</v>
+        <v>0.86</v>
       </c>
       <c r="AO174">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AP174">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ174">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR174">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AS174">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AT174">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AU174">
         <v>4</v>
@@ -37313,25 +37319,25 @@
         <v>2.45</v>
       </c>
       <c r="AN175">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AO175">
-        <v>0.73</v>
+        <v>1.19</v>
       </c>
       <c r="AP175">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ175">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR175">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AS175">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AT175">
-        <v>2.97</v>
+        <v>2.84</v>
       </c>
       <c r="AU175">
         <v>10</v>
@@ -37447,7 +37453,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37519,25 +37525,25 @@
         <v>1.77</v>
       </c>
       <c r="AN176">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="AO176">
-        <v>0.7</v>
+        <v>1.33</v>
       </c>
       <c r="AP176">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ176">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR176">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AS176">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AT176">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AU176">
         <v>3</v>
@@ -37653,7 +37659,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37725,25 +37731,25 @@
         <v>2.05</v>
       </c>
       <c r="AN177">
+        <v>1.57</v>
+      </c>
+      <c r="AO177">
+        <v>1.1</v>
+      </c>
+      <c r="AP177">
+        <v>1.65</v>
+      </c>
+      <c r="AQ177">
+        <v>1.15</v>
+      </c>
+      <c r="AR177">
+        <v>1.45</v>
+      </c>
+      <c r="AS177">
         <v>1.7</v>
       </c>
-      <c r="AO177">
-        <v>0.7</v>
-      </c>
-      <c r="AP177">
-        <v>2</v>
-      </c>
-      <c r="AQ177">
-        <v>0.83</v>
-      </c>
-      <c r="AR177">
-        <v>1.71</v>
-      </c>
-      <c r="AS177">
-        <v>1.48</v>
-      </c>
       <c r="AT177">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="AU177">
         <v>8</v>
@@ -37931,25 +37937,25 @@
         <v>1.41</v>
       </c>
       <c r="AN178">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="AO178">
+        <v>1.64</v>
+      </c>
+      <c r="AP178">
+        <v>0.92</v>
+      </c>
+      <c r="AQ178">
+        <v>1.65</v>
+      </c>
+      <c r="AR178">
         <v>1.45</v>
       </c>
-      <c r="AP178">
-        <v>1.23</v>
-      </c>
-      <c r="AQ178">
-        <v>1.31</v>
-      </c>
-      <c r="AR178">
-        <v>1.57</v>
-      </c>
       <c r="AS178">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AT178">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AU178">
         <v>5</v>
@@ -38065,7 +38071,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38137,25 +38143,25 @@
         <v>1.33</v>
       </c>
       <c r="AN179">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="AO179">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="AP179">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ179">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR179">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AS179">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AT179">
-        <v>3.67</v>
+        <v>3.48</v>
       </c>
       <c r="AU179">
         <v>6</v>
@@ -38271,7 +38277,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38343,25 +38349,25 @@
         <v>1.78</v>
       </c>
       <c r="AN180">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AO180">
-        <v>0.82</v>
+        <v>1.23</v>
       </c>
       <c r="AP180">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ180">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR180">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AS180">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AT180">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="AU180">
         <v>5</v>
@@ -38549,25 +38555,25 @@
         <v>4.4</v>
       </c>
       <c r="AN181">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AO181">
-        <v>0.45</v>
+        <v>0.82</v>
       </c>
       <c r="AP181">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ181">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR181">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AS181">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AT181">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AU181">
         <v>8</v>
@@ -38755,25 +38761,25 @@
         <v>1.65</v>
       </c>
       <c r="AN182">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="AO182">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AP182">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ182">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR182">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AS182">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AT182">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AU182">
         <v>7</v>
@@ -38889,7 +38895,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -38961,25 +38967,25 @@
         <v>1.13</v>
       </c>
       <c r="AN183">
-        <v>1.09</v>
+        <v>0.59</v>
       </c>
       <c r="AO183">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="AP183">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ183">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR183">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AS183">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AT183">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="AU183">
         <v>5</v>
@@ -39095,7 +39101,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39170,22 +39176,22 @@
         <v>1.64</v>
       </c>
       <c r="AO184">
-        <v>0.9</v>
+        <v>1.23</v>
       </c>
       <c r="AP184">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ184">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR184">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AS184">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AT184">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="AU184">
         <v>7</v>
@@ -39373,25 +39379,25 @@
         <v>1.51</v>
       </c>
       <c r="AN185">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="AO185">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AP185">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ185">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR185">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AS185">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AT185">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="AU185">
         <v>3</v>
@@ -39579,25 +39585,25 @@
         <v>1.52</v>
       </c>
       <c r="AN186">
-        <v>1.64</v>
+        <v>1.13</v>
       </c>
       <c r="AO186">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="AP186">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ186">
-        <v>0.75</v>
+        <v>1.19</v>
       </c>
       <c r="AR186">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AS186">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AT186">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AU186">
         <v>2</v>
@@ -39785,25 +39791,25 @@
         <v>2.2</v>
       </c>
       <c r="AN187">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AO187">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AP187">
-        <v>1.75</v>
+        <v>1.27</v>
       </c>
       <c r="AQ187">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR187">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AS187">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AT187">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AU187">
         <v>11</v>
@@ -39919,7 +39925,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -39991,25 +39997,25 @@
         <v>1.95</v>
       </c>
       <c r="AN188">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AO188">
-        <v>0.91</v>
+        <v>1.48</v>
       </c>
       <c r="AP188">
-        <v>1.58</v>
+        <v>1.15</v>
       </c>
       <c r="AQ188">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR188">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AS188">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AT188">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AU188">
         <v>4</v>
@@ -40197,25 +40203,25 @@
         <v>3.25</v>
       </c>
       <c r="AN189">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
       <c r="AO189">
-        <v>0.09</v>
+        <v>0.57</v>
       </c>
       <c r="AP189">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ189">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AR189">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AS189">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AT189">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="AU189">
         <v>6</v>
@@ -40403,25 +40409,25 @@
         <v>1.23</v>
       </c>
       <c r="AN190">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AO190">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AP190">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ190">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR190">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AS190">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AT190">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="AU190">
         <v>4</v>
@@ -40537,7 +40543,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40609,25 +40615,25 @@
         <v>2.7</v>
       </c>
       <c r="AN191">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="AO191">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AP191">
-        <v>2.25</v>
+        <v>1.77</v>
       </c>
       <c r="AQ191">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR191">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AS191">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AT191">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AU191">
         <v>3</v>
@@ -40815,25 +40821,25 @@
         <v>1.53</v>
       </c>
       <c r="AN192">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AO192">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AP192">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="AQ192">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="AR192">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS192">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AT192">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AU192">
         <v>8</v>
@@ -40949,7 +40955,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41021,25 +41027,25 @@
         <v>1.35</v>
       </c>
       <c r="AN193">
-        <v>1.18</v>
+        <v>0.83</v>
       </c>
       <c r="AO193">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="AP193">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ193">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="AR193">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AS193">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AT193">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="AU193">
         <v>4</v>
@@ -41155,7 +41161,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41227,25 +41233,25 @@
         <v>1.55</v>
       </c>
       <c r="AN194">
+        <v>1.13</v>
+      </c>
+      <c r="AO194">
         <v>1.5</v>
       </c>
-      <c r="AO194">
-        <v>1.25</v>
-      </c>
       <c r="AP194">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AQ194">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AR194">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AS194">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AT194">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="AU194">
         <v>8</v>
@@ -41433,25 +41439,25 @@
         <v>3.25</v>
       </c>
       <c r="AN195">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO195">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AP195">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AQ195">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AR195">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AS195">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AT195">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="AU195">
         <v>5</v>
@@ -41639,25 +41645,25 @@
         <v>1.44</v>
       </c>
       <c r="AN196">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AO196">
-        <v>0.67</v>
+        <v>0.96</v>
       </c>
       <c r="AP196">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AQ196">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AR196">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AS196">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AT196">
-        <v>2.37</v>
+        <v>2.58</v>
       </c>
       <c r="AU196">
         <v>5</v>
@@ -41845,25 +41851,25 @@
         <v>2.25</v>
       </c>
       <c r="AN197">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AO197">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AP197">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AQ197">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AR197">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AS197">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AT197">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="AU197">
         <v>7</v>
@@ -42051,25 +42057,25 @@
         <v>1.68</v>
       </c>
       <c r="AN198">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO198">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AP198">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AQ198">
-        <v>1.31</v>
+        <v>1.65</v>
       </c>
       <c r="AR198">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AS198">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AT198">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="AU198">
         <v>5</v>
@@ -42185,7 +42191,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42257,25 +42263,25 @@
         <v>1.16</v>
       </c>
       <c r="AN199">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="AO199">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AP199">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AQ199">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AR199">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AS199">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AT199">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="AU199">
         <v>3</v>
@@ -42391,7 +42397,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42463,25 +42469,25 @@
         <v>2.05</v>
       </c>
       <c r="AN200">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AO200">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AP200">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AQ200">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AR200">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AS200">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AT200">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AU200">
         <v>10</v>
@@ -42669,25 +42675,25 @@
         <v>1.22</v>
       </c>
       <c r="AN201">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AO201">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AP201">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AQ201">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AR201">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AS201">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AT201">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AU201">
         <v>4</v>
@@ -42803,7 +42809,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -42875,25 +42881,25 @@
         <v>1.18</v>
       </c>
       <c r="AN202">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO202">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="AP202">
-        <v>1.85</v>
+        <v>1.35</v>
       </c>
       <c r="AQ202">
-        <v>1.77</v>
+        <v>2.31</v>
       </c>
       <c r="AR202">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AS202">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AT202">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AU202">
         <v>4</v>
@@ -43009,7 +43015,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43081,25 +43087,25 @@
         <v>1.77</v>
       </c>
       <c r="AN203">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="AO203">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AP203">
-        <v>1.85</v>
+        <v>1.23</v>
       </c>
       <c r="AQ203">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR203">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AS203">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT203">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="AU203">
         <v>5</v>
@@ -43215,7 +43221,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43287,25 +43293,25 @@
         <v>2.15</v>
       </c>
       <c r="AN204">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AO204">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AP204">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AQ204">
-        <v>0.46</v>
+        <v>0.73</v>
       </c>
       <c r="AR204">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AS204">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AT204">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="AU204">
         <v>10</v>
@@ -43421,7 +43427,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43493,25 +43499,25 @@
         <v>1.17</v>
       </c>
       <c r="AN205">
-        <v>1.25</v>
+        <v>0.92</v>
       </c>
       <c r="AO205">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AP205">
-        <v>1.23</v>
+        <v>0.92</v>
       </c>
       <c r="AQ205">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AR205">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AS205">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AT205">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="AU205">
         <v>4</v>
@@ -43578,6 +43584,830 @@
       </c>
       <c r="BP205">
         <v>1.29</v>
+      </c>
+    </row>
+    <row r="206" spans="1:68">
+      <c r="A206" s="1">
+        <v>205</v>
+      </c>
+      <c r="B206">
+        <v>7454762</v>
+      </c>
+      <c r="C206" t="s">
+        <v>68</v>
+      </c>
+      <c r="D206" t="s">
+        <v>69</v>
+      </c>
+      <c r="E206" s="2">
+        <v>45704.39583333334</v>
+      </c>
+      <c r="F206">
+        <v>26</v>
+      </c>
+      <c r="G206" t="s">
+        <v>85</v>
+      </c>
+      <c r="H206" t="s">
+        <v>72</v>
+      </c>
+      <c r="I206">
+        <v>1</v>
+      </c>
+      <c r="J206">
+        <v>1</v>
+      </c>
+      <c r="K206">
+        <v>2</v>
+      </c>
+      <c r="L206">
+        <v>3</v>
+      </c>
+      <c r="M206">
+        <v>2</v>
+      </c>
+      <c r="N206">
+        <v>5</v>
+      </c>
+      <c r="O206" t="s">
+        <v>237</v>
+      </c>
+      <c r="P206" t="s">
+        <v>325</v>
+      </c>
+      <c r="Q206">
+        <v>1.95</v>
+      </c>
+      <c r="R206">
+        <v>2.4</v>
+      </c>
+      <c r="S206">
+        <v>6.5</v>
+      </c>
+      <c r="T206">
+        <v>1.33</v>
+      </c>
+      <c r="U206">
+        <v>3.25</v>
+      </c>
+      <c r="V206">
+        <v>2.5</v>
+      </c>
+      <c r="W206">
+        <v>1.5</v>
+      </c>
+      <c r="X206">
+        <v>6.5</v>
+      </c>
+      <c r="Y206">
+        <v>1.11</v>
+      </c>
+      <c r="Z206">
+        <v>1.45</v>
+      </c>
+      <c r="AA206">
+        <v>4.4</v>
+      </c>
+      <c r="AB206">
+        <v>6.5</v>
+      </c>
+      <c r="AC206">
+        <v>1.04</v>
+      </c>
+      <c r="AD206">
+        <v>10</v>
+      </c>
+      <c r="AE206">
+        <v>1.2</v>
+      </c>
+      <c r="AF206">
+        <v>4.33</v>
+      </c>
+      <c r="AG206">
+        <v>1.55</v>
+      </c>
+      <c r="AH206">
+        <v>2.3</v>
+      </c>
+      <c r="AI206">
+        <v>1.91</v>
+      </c>
+      <c r="AJ206">
+        <v>1.91</v>
+      </c>
+      <c r="AK206">
+        <v>1.12</v>
+      </c>
+      <c r="AL206">
+        <v>1.19</v>
+      </c>
+      <c r="AM206">
+        <v>2.65</v>
+      </c>
+      <c r="AN206">
+        <v>1.48</v>
+      </c>
+      <c r="AO206">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AP206">
+        <v>1.54</v>
+      </c>
+      <c r="AQ206">
+        <v>0.54</v>
+      </c>
+      <c r="AR206">
+        <v>1.42</v>
+      </c>
+      <c r="AS206">
+        <v>1.17</v>
+      </c>
+      <c r="AT206">
+        <v>2.59</v>
+      </c>
+      <c r="AU206">
+        <v>4</v>
+      </c>
+      <c r="AV206">
+        <v>6</v>
+      </c>
+      <c r="AW206">
+        <v>18</v>
+      </c>
+      <c r="AX206">
+        <v>8</v>
+      </c>
+      <c r="AY206">
+        <v>28</v>
+      </c>
+      <c r="AZ206">
+        <v>18</v>
+      </c>
+      <c r="BA206">
+        <v>8</v>
+      </c>
+      <c r="BB206">
+        <v>6</v>
+      </c>
+      <c r="BC206">
+        <v>14</v>
+      </c>
+      <c r="BD206">
+        <v>1.33</v>
+      </c>
+      <c r="BE206">
+        <v>7.5</v>
+      </c>
+      <c r="BF206">
+        <v>3.55</v>
+      </c>
+      <c r="BG206">
+        <v>1.25</v>
+      </c>
+      <c r="BH206">
+        <v>3.4</v>
+      </c>
+      <c r="BI206">
+        <v>1.44</v>
+      </c>
+      <c r="BJ206">
+        <v>2.55</v>
+      </c>
+      <c r="BK206">
+        <v>1.72</v>
+      </c>
+      <c r="BL206">
+        <v>1.98</v>
+      </c>
+      <c r="BM206">
+        <v>2.08</v>
+      </c>
+      <c r="BN206">
+        <v>1.65</v>
+      </c>
+      <c r="BO206">
+        <v>2.65</v>
+      </c>
+      <c r="BP206">
+        <v>1.41</v>
+      </c>
+    </row>
+    <row r="207" spans="1:68">
+      <c r="A207" s="1">
+        <v>206</v>
+      </c>
+      <c r="B207">
+        <v>7453620</v>
+      </c>
+      <c r="C207" t="s">
+        <v>68</v>
+      </c>
+      <c r="D207" t="s">
+        <v>69</v>
+      </c>
+      <c r="E207" s="2">
+        <v>45704.5</v>
+      </c>
+      <c r="F207">
+        <v>26</v>
+      </c>
+      <c r="G207" t="s">
+        <v>78</v>
+      </c>
+      <c r="H207" t="s">
+        <v>79</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>1</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>0</v>
+      </c>
+      <c r="M207">
+        <v>1</v>
+      </c>
+      <c r="N207">
+        <v>1</v>
+      </c>
+      <c r="O207" t="s">
+        <v>87</v>
+      </c>
+      <c r="P207" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q207">
+        <v>2.1</v>
+      </c>
+      <c r="R207">
+        <v>2.38</v>
+      </c>
+      <c r="S207">
+        <v>5.5</v>
+      </c>
+      <c r="T207">
+        <v>1.33</v>
+      </c>
+      <c r="U207">
+        <v>3.25</v>
+      </c>
+      <c r="V207">
+        <v>2.5</v>
+      </c>
+      <c r="W207">
+        <v>1.5</v>
+      </c>
+      <c r="X207">
+        <v>6.5</v>
+      </c>
+      <c r="Y207">
+        <v>1.11</v>
+      </c>
+      <c r="Z207">
+        <v>1.6</v>
+      </c>
+      <c r="AA207">
+        <v>4.1</v>
+      </c>
+      <c r="AB207">
+        <v>5.1</v>
+      </c>
+      <c r="AC207">
+        <v>1.03</v>
+      </c>
+      <c r="AD207">
+        <v>15</v>
+      </c>
+      <c r="AE207">
+        <v>1.21</v>
+      </c>
+      <c r="AF207">
+        <v>4.25</v>
+      </c>
+      <c r="AG207">
+        <v>1.67</v>
+      </c>
+      <c r="AH207">
+        <v>2.1</v>
+      </c>
+      <c r="AI207">
+        <v>1.75</v>
+      </c>
+      <c r="AJ207">
+        <v>2</v>
+      </c>
+      <c r="AK207">
+        <v>1.17</v>
+      </c>
+      <c r="AL207">
+        <v>1.23</v>
+      </c>
+      <c r="AM207">
+        <v>2.25</v>
+      </c>
+      <c r="AN207">
+        <v>1.84</v>
+      </c>
+      <c r="AO207">
+        <v>1.12</v>
+      </c>
+      <c r="AP207">
+        <v>1.77</v>
+      </c>
+      <c r="AQ207">
+        <v>1.19</v>
+      </c>
+      <c r="AR207">
+        <v>1.61</v>
+      </c>
+      <c r="AS207">
+        <v>1.51</v>
+      </c>
+      <c r="AT207">
+        <v>3.12</v>
+      </c>
+      <c r="AU207">
+        <v>9</v>
+      </c>
+      <c r="AV207">
+        <v>5</v>
+      </c>
+      <c r="AW207">
+        <v>11</v>
+      </c>
+      <c r="AX207">
+        <v>7</v>
+      </c>
+      <c r="AY207">
+        <v>20</v>
+      </c>
+      <c r="AZ207">
+        <v>12</v>
+      </c>
+      <c r="BA207">
+        <v>9</v>
+      </c>
+      <c r="BB207">
+        <v>5</v>
+      </c>
+      <c r="BC207">
+        <v>14</v>
+      </c>
+      <c r="BD207">
+        <v>1.36</v>
+      </c>
+      <c r="BE207">
+        <v>7.5</v>
+      </c>
+      <c r="BF207">
+        <v>3.4</v>
+      </c>
+      <c r="BG207">
+        <v>1.24</v>
+      </c>
+      <c r="BH207">
+        <v>3.65</v>
+      </c>
+      <c r="BI207">
+        <v>1.42</v>
+      </c>
+      <c r="BJ207">
+        <v>2.65</v>
+      </c>
+      <c r="BK207">
+        <v>1.67</v>
+      </c>
+      <c r="BL207">
+        <v>2.07</v>
+      </c>
+      <c r="BM207">
+        <v>2.02</v>
+      </c>
+      <c r="BN207">
+        <v>1.7</v>
+      </c>
+      <c r="BO207">
+        <v>2.55</v>
+      </c>
+      <c r="BP207">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="208" spans="1:68">
+      <c r="A208" s="1">
+        <v>207</v>
+      </c>
+      <c r="B208">
+        <v>7453626</v>
+      </c>
+      <c r="C208" t="s">
+        <v>68</v>
+      </c>
+      <c r="D208" t="s">
+        <v>69</v>
+      </c>
+      <c r="E208" s="2">
+        <v>45704.60416666666</v>
+      </c>
+      <c r="F208">
+        <v>26</v>
+      </c>
+      <c r="G208" t="s">
+        <v>76</v>
+      </c>
+      <c r="H208" t="s">
+        <v>73</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+      <c r="M208">
+        <v>1</v>
+      </c>
+      <c r="N208">
+        <v>1</v>
+      </c>
+      <c r="O208" t="s">
+        <v>87</v>
+      </c>
+      <c r="P208" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q208">
+        <v>3.2</v>
+      </c>
+      <c r="R208">
+        <v>2.1</v>
+      </c>
+      <c r="S208">
+        <v>3.25</v>
+      </c>
+      <c r="T208">
+        <v>1.4</v>
+      </c>
+      <c r="U208">
+        <v>2.75</v>
+      </c>
+      <c r="V208">
+        <v>3</v>
+      </c>
+      <c r="W208">
+        <v>1.36</v>
+      </c>
+      <c r="X208">
+        <v>8</v>
+      </c>
+      <c r="Y208">
+        <v>1.08</v>
+      </c>
+      <c r="Z208">
+        <v>2.68</v>
+      </c>
+      <c r="AA208">
+        <v>3.32</v>
+      </c>
+      <c r="AB208">
+        <v>2.53</v>
+      </c>
+      <c r="AC208">
+        <v>1.04</v>
+      </c>
+      <c r="AD208">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AE208">
+        <v>1.31</v>
+      </c>
+      <c r="AF208">
+        <v>3.32</v>
+      </c>
+      <c r="AG208">
+        <v>1.83</v>
+      </c>
+      <c r="AH208">
+        <v>1.91</v>
+      </c>
+      <c r="AI208">
+        <v>1.75</v>
+      </c>
+      <c r="AJ208">
+        <v>2</v>
+      </c>
+      <c r="AK208">
+        <v>1.46</v>
+      </c>
+      <c r="AL208">
+        <v>1.3</v>
+      </c>
+      <c r="AM208">
+        <v>1.49</v>
+      </c>
+      <c r="AN208">
+        <v>1.32</v>
+      </c>
+      <c r="AO208">
+        <v>1.68</v>
+      </c>
+      <c r="AP208">
+        <v>1.27</v>
+      </c>
+      <c r="AQ208">
+        <v>1.73</v>
+      </c>
+      <c r="AR208">
+        <v>1.55</v>
+      </c>
+      <c r="AS208">
+        <v>1.53</v>
+      </c>
+      <c r="AT208">
+        <v>3.08</v>
+      </c>
+      <c r="AU208">
+        <v>6</v>
+      </c>
+      <c r="AV208">
+        <v>2</v>
+      </c>
+      <c r="AW208">
+        <v>9</v>
+      </c>
+      <c r="AX208">
+        <v>4</v>
+      </c>
+      <c r="AY208">
+        <v>16</v>
+      </c>
+      <c r="AZ208">
+        <v>7</v>
+      </c>
+      <c r="BA208">
+        <v>3</v>
+      </c>
+      <c r="BB208">
+        <v>6</v>
+      </c>
+      <c r="BC208">
+        <v>9</v>
+      </c>
+      <c r="BD208">
+        <v>1.97</v>
+      </c>
+      <c r="BE208">
+        <v>6.5</v>
+      </c>
+      <c r="BF208">
+        <v>2</v>
+      </c>
+      <c r="BG208">
+        <v>1.3</v>
+      </c>
+      <c r="BH208">
+        <v>3.15</v>
+      </c>
+      <c r="BI208">
+        <v>1.5</v>
+      </c>
+      <c r="BJ208">
+        <v>2.33</v>
+      </c>
+      <c r="BK208">
+        <v>1.84</v>
+      </c>
+      <c r="BL208">
+        <v>1.84</v>
+      </c>
+      <c r="BM208">
+        <v>2.32</v>
+      </c>
+      <c r="BN208">
+        <v>1.53</v>
+      </c>
+      <c r="BO208">
+        <v>2.95</v>
+      </c>
+      <c r="BP208">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="209" spans="1:68">
+      <c r="A209" s="1">
+        <v>208</v>
+      </c>
+      <c r="B209">
+        <v>7453623</v>
+      </c>
+      <c r="C209" t="s">
+        <v>68</v>
+      </c>
+      <c r="D209" t="s">
+        <v>69</v>
+      </c>
+      <c r="E209" s="2">
+        <v>45704.63541666666</v>
+      </c>
+      <c r="F209">
+        <v>26</v>
+      </c>
+      <c r="G209" t="s">
+        <v>83</v>
+      </c>
+      <c r="H209" t="s">
+        <v>77</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+      <c r="L209">
+        <v>1</v>
+      </c>
+      <c r="M209">
+        <v>1</v>
+      </c>
+      <c r="N209">
+        <v>2</v>
+      </c>
+      <c r="O209" t="s">
+        <v>115</v>
+      </c>
+      <c r="P209" t="s">
+        <v>225</v>
+      </c>
+      <c r="Q209">
+        <v>2.88</v>
+      </c>
+      <c r="R209">
+        <v>2.25</v>
+      </c>
+      <c r="S209">
+        <v>3.5</v>
+      </c>
+      <c r="T209">
+        <v>1.33</v>
+      </c>
+      <c r="U209">
+        <v>3.25</v>
+      </c>
+      <c r="V209">
+        <v>2.63</v>
+      </c>
+      <c r="W209">
+        <v>1.44</v>
+      </c>
+      <c r="X209">
+        <v>6.5</v>
+      </c>
+      <c r="Y209">
+        <v>1.11</v>
+      </c>
+      <c r="Z209">
+        <v>2.23</v>
+      </c>
+      <c r="AA209">
+        <v>3.4</v>
+      </c>
+      <c r="AB209">
+        <v>3.05</v>
+      </c>
+      <c r="AC209">
+        <v>1.03</v>
+      </c>
+      <c r="AD209">
+        <v>13</v>
+      </c>
+      <c r="AE209">
+        <v>1.21</v>
+      </c>
+      <c r="AF209">
+        <v>4.25</v>
+      </c>
+      <c r="AG209">
+        <v>1.67</v>
+      </c>
+      <c r="AH209">
+        <v>2.1</v>
+      </c>
+      <c r="AI209">
+        <v>1.57</v>
+      </c>
+      <c r="AJ209">
+        <v>2.25</v>
+      </c>
+      <c r="AK209">
+        <v>1.38</v>
+      </c>
+      <c r="AL209">
+        <v>1.28</v>
+      </c>
+      <c r="AM209">
+        <v>1.62</v>
+      </c>
+      <c r="AN209">
+        <v>1.16</v>
+      </c>
+      <c r="AO209">
+        <v>1.16</v>
+      </c>
+      <c r="AP209">
+        <v>1.15</v>
+      </c>
+      <c r="AQ209">
+        <v>1.15</v>
+      </c>
+      <c r="AR209">
+        <v>1.53</v>
+      </c>
+      <c r="AS209">
+        <v>1.77</v>
+      </c>
+      <c r="AT209">
+        <v>3.3</v>
+      </c>
+      <c r="AU209">
+        <v>10</v>
+      </c>
+      <c r="AV209">
+        <v>6</v>
+      </c>
+      <c r="AW209">
+        <v>12</v>
+      </c>
+      <c r="AX209">
+        <v>3</v>
+      </c>
+      <c r="AY209">
+        <v>27</v>
+      </c>
+      <c r="AZ209">
+        <v>9</v>
+      </c>
+      <c r="BA209">
+        <v>8</v>
+      </c>
+      <c r="BB209">
+        <v>1</v>
+      </c>
+      <c r="BC209">
+        <v>9</v>
+      </c>
+      <c r="BD209">
+        <v>1.71</v>
+      </c>
+      <c r="BE209">
+        <v>6.5</v>
+      </c>
+      <c r="BF209">
+        <v>2.38</v>
+      </c>
+      <c r="BG209">
+        <v>1.25</v>
+      </c>
+      <c r="BH209">
+        <v>3.45</v>
+      </c>
+      <c r="BI209">
+        <v>1.44</v>
+      </c>
+      <c r="BJ209">
+        <v>2.55</v>
+      </c>
+      <c r="BK209">
+        <v>1.72</v>
+      </c>
+      <c r="BL209">
+        <v>1.98</v>
+      </c>
+      <c r="BM209">
+        <v>2.1</v>
+      </c>
+      <c r="BN209">
+        <v>1.64</v>
+      </c>
+      <c r="BO209">
+        <v>2.65</v>
+      </c>
+      <c r="BP209">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -1687,10 +1687,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ2">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1893,10 +1893,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ3">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2099,10 +2099,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2305,10 +2305,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ5">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2511,10 +2511,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ6">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2717,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2923,10 +2923,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ8">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3129,10 +3129,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ9">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3329,25 +3329,25 @@
         <v>3.75</v>
       </c>
       <c r="AN10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ10">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR10">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>5</v>
@@ -3535,25 +3535,25 @@
         <v>1.9</v>
       </c>
       <c r="AN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR11">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3741,25 +3741,25 @@
         <v>1.35</v>
       </c>
       <c r="AN12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ12">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR12">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3953,19 +3953,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
+        <v>1.23</v>
+      </c>
+      <c r="AQ13">
         <v>0.92</v>
       </c>
-      <c r="AQ13">
-        <v>1.27</v>
-      </c>
       <c r="AR13">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>4</v>
@@ -4153,25 +4153,25 @@
         <v>1.45</v>
       </c>
       <c r="AN14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ14">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR14">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AU14">
         <v>8</v>
@@ -4365,19 +4365,19 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ15">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR15">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AU15">
         <v>7</v>
@@ -4565,25 +4565,25 @@
         <v>1.15</v>
       </c>
       <c r="AN16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ16">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR16">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AU16">
         <v>3</v>
@@ -4771,25 +4771,25 @@
         <v>3.6</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ17">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR17">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AU17">
         <v>4</v>
@@ -4977,25 +4977,25 @@
         <v>1.67</v>
       </c>
       <c r="AN18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ18">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR18">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS18">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="AT18">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -5183,25 +5183,25 @@
         <v>1.57</v>
       </c>
       <c r="AN19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO19">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ19">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR19">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="AS19">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AT19">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AU19">
         <v>7</v>
@@ -5392,22 +5392,22 @@
         <v>3</v>
       </c>
       <c r="AO20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ20">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR20">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AS20">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AT20">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="AU20">
         <v>10</v>
@@ -5598,22 +5598,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ21">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AR21">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS21">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AT21">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="AU21">
         <v>3</v>
@@ -5801,25 +5801,25 @@
         <v>1.33</v>
       </c>
       <c r="AN22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ22">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR22">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AS22">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AT22">
-        <v>3.86</v>
+        <v>3.22</v>
       </c>
       <c r="AU22">
         <v>8</v>
@@ -6007,25 +6007,25 @@
         <v>2.62</v>
       </c>
       <c r="AN23">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ23">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR23">
-        <v>1.91</v>
+        <v>2.53</v>
       </c>
       <c r="AS23">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="AT23">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AU23">
         <v>9</v>
@@ -6213,25 +6213,25 @@
         <v>1.38</v>
       </c>
       <c r="AN24">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ24">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR24">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AS24">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AT24">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6422,22 +6422,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ25">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR25">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AS25">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AT25">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="AU25">
         <v>9</v>
@@ -6625,16 +6625,16 @@
         <v>2.4</v>
       </c>
       <c r="AN26">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ26">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR26">
         <v>1.53</v>
@@ -6831,25 +6831,25 @@
         <v>1.29</v>
       </c>
       <c r="AN27">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR27">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="AS27">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="AT27">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -7040,22 +7040,22 @@
         <v>0</v>
       </c>
       <c r="AO28">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP28">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ28">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR28">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AS28">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="AT28">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="AU28">
         <v>5</v>
@@ -7243,25 +7243,25 @@
         <v>1.33</v>
       </c>
       <c r="AN29">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO29">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ29">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR29">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="AS29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AT29">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AU29">
         <v>10</v>
@@ -7449,25 +7449,25 @@
         <v>2.05</v>
       </c>
       <c r="AN30">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP30">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ30">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR30">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AS30">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AT30">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7655,25 +7655,25 @@
         <v>1.4</v>
       </c>
       <c r="AN31">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AO31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP31">
+        <v>1.85</v>
+      </c>
+      <c r="AQ31">
+        <v>0.77</v>
+      </c>
+      <c r="AR31">
         <v>1.23</v>
       </c>
-      <c r="AQ31">
-        <v>1.15</v>
-      </c>
-      <c r="AR31">
-        <v>1.17</v>
-      </c>
       <c r="AS31">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="AT31">
-        <v>3.13</v>
+        <v>2.74</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7861,25 +7861,25 @@
         <v>1.45</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO32">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP32">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ32">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR32">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AS32">
-        <v>0.97</v>
+        <v>0.59</v>
       </c>
       <c r="AT32">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -8067,25 +8067,25 @@
         <v>1.91</v>
       </c>
       <c r="AN33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO33">
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ33">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR33">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="AS33">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AT33">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8273,25 +8273,25 @@
         <v>1.85</v>
       </c>
       <c r="AN34">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AO34">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ34">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AR34">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS34">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AT34">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AU34">
         <v>4</v>
@@ -8482,22 +8482,22 @@
         <v>1.5</v>
       </c>
       <c r="AO35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ35">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR35">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="AS35">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
       <c r="AT35">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="AU35">
         <v>5</v>
@@ -8688,22 +8688,22 @@
         <v>2</v>
       </c>
       <c r="AO36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ36">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR36">
-        <v>1.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS36">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AT36">
-        <v>3.09</v>
+        <v>2.59</v>
       </c>
       <c r="AU36">
         <v>6</v>
@@ -8891,25 +8891,25 @@
         <v>1.09</v>
       </c>
       <c r="AN37">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO37">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ37">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR37">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="AS37">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AT37">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AU37">
         <v>0</v>
@@ -9097,25 +9097,25 @@
         <v>2</v>
       </c>
       <c r="AN38">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AO38">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ38">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR38">
-        <v>0.84</v>
+        <v>1.16</v>
       </c>
       <c r="AS38">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="AT38">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9309,19 +9309,19 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ39">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR39">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AS39">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="AT39">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9509,25 +9509,25 @@
         <v>2.1</v>
       </c>
       <c r="AN40">
+        <v>2</v>
+      </c>
+      <c r="AO40">
+        <v>1.5</v>
+      </c>
+      <c r="AP40">
+        <v>2.85</v>
+      </c>
+      <c r="AQ40">
+        <v>0.85</v>
+      </c>
+      <c r="AR40">
+        <v>1.69</v>
+      </c>
+      <c r="AS40">
         <v>1.75</v>
       </c>
-      <c r="AO40">
-        <v>2</v>
-      </c>
-      <c r="AP40">
-        <v>2.31</v>
-      </c>
-      <c r="AQ40">
-        <v>1.15</v>
-      </c>
-      <c r="AR40">
-        <v>1.64</v>
-      </c>
-      <c r="AS40">
-        <v>1.67</v>
-      </c>
       <c r="AT40">
-        <v>3.31</v>
+        <v>3.44</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9715,25 +9715,25 @@
         <v>1.5</v>
       </c>
       <c r="AN41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO41">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ41">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR41">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AS41">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AT41">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -9921,25 +9921,25 @@
         <v>1.43</v>
       </c>
       <c r="AN42">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AO42">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP42">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR42">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="AS42">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AT42">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -10127,25 +10127,25 @@
         <v>1.85</v>
       </c>
       <c r="AN43">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ43">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR43">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AS43">
-        <v>0.86</v>
+        <v>0.52</v>
       </c>
       <c r="AT43">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="AU43">
         <v>5</v>
@@ -10333,25 +10333,25 @@
         <v>2.4</v>
       </c>
       <c r="AN44">
+        <v>2</v>
+      </c>
+      <c r="AO44">
+        <v>0.5</v>
+      </c>
+      <c r="AP44">
+        <v>2.31</v>
+      </c>
+      <c r="AQ44">
+        <v>0.77</v>
+      </c>
+      <c r="AR44">
+        <v>1.89</v>
+      </c>
+      <c r="AS44">
         <v>1.4</v>
       </c>
-      <c r="AO44">
-        <v>1</v>
-      </c>
-      <c r="AP44">
-        <v>2</v>
-      </c>
-      <c r="AQ44">
-        <v>1.15</v>
-      </c>
-      <c r="AR44">
-        <v>1.7</v>
-      </c>
-      <c r="AS44">
-        <v>1.79</v>
-      </c>
       <c r="AT44">
-        <v>3.49</v>
+        <v>3.29</v>
       </c>
       <c r="AU44">
         <v>11</v>
@@ -10542,22 +10542,22 @@
         <v>1.5</v>
       </c>
       <c r="AO45">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ45">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR45">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AS45">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="AT45">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="AU45">
         <v>9</v>
@@ -10745,25 +10745,25 @@
         <v>1.77</v>
       </c>
       <c r="AN46">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="AO46">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ46">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR46">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AS46">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AT46">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="AU46">
         <v>7</v>
@@ -10951,25 +10951,25 @@
         <v>1.7</v>
       </c>
       <c r="AN47">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AO47">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR47">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="AS47">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="AT47">
-        <v>2.22</v>
+        <v>2.65</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -11157,25 +11157,25 @@
         <v>1.7</v>
       </c>
       <c r="AN48">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AO48">
-        <v>1.33</v>
+        <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ48">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR48">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AS48">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="AT48">
-        <v>2.09</v>
+        <v>1.66</v>
       </c>
       <c r="AU48">
         <v>4</v>
@@ -11363,25 +11363,25 @@
         <v>1.5</v>
       </c>
       <c r="AN49">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AO49">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ49">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR49">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="AS49">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AT49">
-        <v>3.32</v>
+        <v>3.77</v>
       </c>
       <c r="AU49">
         <v>3</v>
@@ -11569,25 +11569,25 @@
         <v>1.1</v>
       </c>
       <c r="AN50">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP50">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ50">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR50">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AS50">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AT50">
-        <v>3.23</v>
+        <v>3.33</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11775,25 +11775,25 @@
         <v>2.05</v>
       </c>
       <c r="AN51">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AO51">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ51">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR51">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AS51">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT51">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="AU51">
         <v>9</v>
@@ -11981,25 +11981,25 @@
         <v>1.54</v>
       </c>
       <c r="AN52">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ52">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR52">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AS52">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AT52">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12187,25 +12187,25 @@
         <v>1.37</v>
       </c>
       <c r="AN53">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO53">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP53">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ53">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AR53">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="AS53">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AT53">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AU53">
         <v>5</v>
@@ -12393,25 +12393,25 @@
         <v>2.21</v>
       </c>
       <c r="AN54">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO54">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ54">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR54">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AS54">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT54">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AU54">
         <v>13</v>
@@ -12599,25 +12599,25 @@
         <v>2.17</v>
       </c>
       <c r="AN55">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AO55">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP55">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ55">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR55">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="AS55">
-        <v>1.24</v>
+        <v>0.98</v>
       </c>
       <c r="AT55">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AU55">
         <v>8</v>
@@ -12805,25 +12805,25 @@
         <v>1.65</v>
       </c>
       <c r="AN56">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO56">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ56">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR56">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AS56">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AT56">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AU56">
         <v>5</v>
@@ -13011,25 +13011,25 @@
         <v>1.22</v>
       </c>
       <c r="AN57">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AO57">
-        <v>1.29</v>
+        <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ57">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR57">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="AS57">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AT57">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -13217,25 +13217,25 @@
         <v>1.55</v>
       </c>
       <c r="AN58">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="AO58">
-        <v>0.86</v>
+        <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR58">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS58">
         <v>0.93</v>
       </c>
-      <c r="AS58">
-        <v>0.9</v>
-      </c>
       <c r="AT58">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AU58">
         <v>0</v>
@@ -13423,25 +13423,25 @@
         <v>1.38</v>
       </c>
       <c r="AN59">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AO59">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ59">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR59">
-        <v>1.54</v>
+        <v>1.61</v>
       </c>
       <c r="AS59">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="AT59">
-        <v>3.22</v>
+        <v>3.03</v>
       </c>
       <c r="AU59">
         <v>7</v>
@@ -13629,25 +13629,25 @@
         <v>1.84</v>
       </c>
       <c r="AN60">
-        <v>1.71</v>
+        <v>1.25</v>
       </c>
       <c r="AO60">
-        <v>1.71</v>
+        <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ60">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR60">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AS60">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AT60">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AU60">
         <v>5</v>
@@ -13835,25 +13835,25 @@
         <v>2.5</v>
       </c>
       <c r="AN61">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AO61">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ61">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR61">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AS61">
-        <v>1.5</v>
+        <v>0.86</v>
       </c>
       <c r="AT61">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="AU61">
         <v>10</v>
@@ -14041,25 +14041,25 @@
         <v>1.51</v>
       </c>
       <c r="AN62">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AO62">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ62">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR62">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AS62">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AT62">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14247,22 +14247,22 @@
         <v>2.3</v>
       </c>
       <c r="AN63">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AO63">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ63">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR63">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AS63">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AT63">
         <v>3.14</v>
@@ -14453,25 +14453,25 @@
         <v>2</v>
       </c>
       <c r="AN64">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="AO64">
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ64">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR64">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS64">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AT64">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="AU64">
         <v>3</v>
@@ -14659,25 +14659,25 @@
         <v>1.51</v>
       </c>
       <c r="AN65">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AO65">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ65">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR65">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AS65">
-        <v>1.42</v>
+        <v>0.88</v>
       </c>
       <c r="AT65">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14865,25 +14865,25 @@
         <v>1.22</v>
       </c>
       <c r="AN66">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AO66">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ66">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR66">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AS66">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AT66">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -15071,25 +15071,25 @@
         <v>2.5</v>
       </c>
       <c r="AN67">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AO67">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AP67">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ67">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR67">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AS67">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AT67">
-        <v>3.18</v>
+        <v>3.01</v>
       </c>
       <c r="AU67">
         <v>6</v>
@@ -15277,25 +15277,25 @@
         <v>1.44</v>
       </c>
       <c r="AN68">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO68">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ68">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR68">
-        <v>0.8100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="AS68">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AT68">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AU68">
         <v>4</v>
@@ -15483,25 +15483,25 @@
         <v>1.35</v>
       </c>
       <c r="AN69">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AO69">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ69">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR69">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AS69">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AT69">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15689,25 +15689,25 @@
         <v>3.75</v>
       </c>
       <c r="AN70">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AO70">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ70">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR70">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AS70">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AT70">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="AU70">
         <v>7</v>
@@ -15895,25 +15895,25 @@
         <v>3</v>
       </c>
       <c r="AN71">
-        <v>1.25</v>
+        <v>2.33</v>
       </c>
       <c r="AO71">
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ71">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR71">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AS71">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="AT71">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="AU71">
         <v>6</v>
@@ -16101,25 +16101,25 @@
         <v>2.2</v>
       </c>
       <c r="AN72">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO72">
-        <v>1.38</v>
+        <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ72">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AR72">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="AS72">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AT72">
-        <v>2.72</v>
+        <v>3.24</v>
       </c>
       <c r="AU72">
         <v>6</v>
@@ -16307,25 +16307,25 @@
         <v>2.15</v>
       </c>
       <c r="AN73">
-        <v>0.88</v>
+        <v>1.5</v>
       </c>
       <c r="AO73">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ73">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR73">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AS73">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AT73">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16513,25 +16513,25 @@
         <v>2.75</v>
       </c>
       <c r="AN74">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AO74">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ74">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR74">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AS74">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AT74">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AU74">
         <v>10</v>
@@ -16719,25 +16719,25 @@
         <v>1.62</v>
       </c>
       <c r="AN75">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AO75">
-        <v>1.22</v>
+        <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ75">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AR75">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AS75">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AT75">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16925,25 +16925,25 @@
         <v>1.15</v>
       </c>
       <c r="AN76">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AO76">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR76">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AS76">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AT76">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17131,25 +17131,25 @@
         <v>1.33</v>
       </c>
       <c r="AN77">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO77">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ77">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR77">
+        <v>1.23</v>
+      </c>
+      <c r="AS77">
         <v>1.25</v>
       </c>
-      <c r="AS77">
-        <v>1.54</v>
-      </c>
       <c r="AT77">
-        <v>2.79</v>
+        <v>2.48</v>
       </c>
       <c r="AU77">
         <v>3</v>
@@ -17337,25 +17337,25 @@
         <v>2.4</v>
       </c>
       <c r="AN78">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="AO78">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ78">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR78">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AS78">
-        <v>0.89</v>
+        <v>0.58</v>
       </c>
       <c r="AT78">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17543,25 +17543,25 @@
         <v>2.25</v>
       </c>
       <c r="AN79">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AO79">
-        <v>0.89</v>
+        <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ79">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR79">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AS79">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AT79">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="AU79">
         <v>6</v>
@@ -17749,25 +17749,25 @@
         <v>1.86</v>
       </c>
       <c r="AN80">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AO80">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="AP80">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ80">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR80">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AS80">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AT80">
-        <v>3.49</v>
+        <v>3.75</v>
       </c>
       <c r="AU80">
         <v>6</v>
@@ -17955,25 +17955,25 @@
         <v>1.33</v>
       </c>
       <c r="AN81">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AO81">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ81">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR81">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="AS81">
-        <v>1.33</v>
+        <v>0.84</v>
       </c>
       <c r="AT81">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="AU81">
         <v>13</v>
@@ -18161,25 +18161,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AO82">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ82">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR82">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="AS82">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AT82">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AU82">
         <v>0</v>
@@ -18367,25 +18367,25 @@
         <v>1.25</v>
       </c>
       <c r="AN83">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AO83">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP83">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ83">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR83">
-        <v>1.65</v>
+        <v>1.89</v>
       </c>
       <c r="AS83">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AT83">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18573,25 +18573,25 @@
         <v>1.96</v>
       </c>
       <c r="AN84">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AO84">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP84">
+        <v>1.54</v>
+      </c>
+      <c r="AQ84">
         <v>1.15</v>
       </c>
-      <c r="AQ84">
-        <v>1.19</v>
-      </c>
       <c r="AR84">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AS84">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AT84">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="AU84">
         <v>7</v>
@@ -18779,25 +18779,25 @@
         <v>2.15</v>
       </c>
       <c r="AN85">
+        <v>2.5</v>
+      </c>
+      <c r="AO85">
         <v>1.4</v>
       </c>
-      <c r="AO85">
-        <v>1.7</v>
-      </c>
       <c r="AP85">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ85">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR85">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AS85">
-        <v>1.31</v>
+        <v>0.91</v>
       </c>
       <c r="AT85">
-        <v>2.87</v>
+        <v>2.58</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -18985,25 +18985,25 @@
         <v>2.65</v>
       </c>
       <c r="AN86">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AO86">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ86">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR86">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AS86">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT86">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="AU86">
         <v>5</v>
@@ -19191,25 +19191,25 @@
         <v>1.38</v>
       </c>
       <c r="AN87">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AO87">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ87">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR87">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AS87">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="AT87">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19397,25 +19397,25 @@
         <v>1.38</v>
       </c>
       <c r="AN88">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AO88">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AP88">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ88">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR88">
-        <v>0.98</v>
+        <v>1.14</v>
       </c>
       <c r="AS88">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT88">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AU88">
         <v>7</v>
@@ -19603,25 +19603,25 @@
         <v>2.15</v>
       </c>
       <c r="AN89">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AO89">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AP89">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ89">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR89">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AS89">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AT89">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19809,25 +19809,25 @@
         <v>1.9</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO90">
-        <v>0.45</v>
+        <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR90">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AS90">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AT90">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="AU90">
         <v>6</v>
@@ -20015,25 +20015,25 @@
         <v>0</v>
       </c>
       <c r="AN91">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="AO91">
-        <v>1.09</v>
+        <v>0.5</v>
       </c>
       <c r="AP91">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ91">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AR91">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="AS91">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AT91">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20221,25 +20221,25 @@
         <v>1.45</v>
       </c>
       <c r="AN92">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AO92">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ92">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR92">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AS92">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AT92">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="AU92">
         <v>5</v>
@@ -20427,25 +20427,25 @@
         <v>1.49</v>
       </c>
       <c r="AN93">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AO93">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AP93">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ93">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR93">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AS93">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AT93">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="AU93">
         <v>7</v>
@@ -20633,25 +20633,25 @@
         <v>2.4</v>
       </c>
       <c r="AN94">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AO94">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ94">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR94">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AS94">
         <v>1.57</v>
       </c>
       <c r="AT94">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="AU94">
         <v>10</v>
@@ -20839,25 +20839,25 @@
         <v>2.4</v>
       </c>
       <c r="AN95">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AO95">
-        <v>1.36</v>
+        <v>0.8</v>
       </c>
       <c r="AP95">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ95">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR95">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AS95">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="AT95">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AU95">
         <v>6</v>
@@ -21045,25 +21045,25 @@
         <v>1.38</v>
       </c>
       <c r="AN96">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AO96">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ96">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR96">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="AS96">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AT96">
-        <v>3.19</v>
+        <v>3.66</v>
       </c>
       <c r="AU96">
         <v>0</v>
@@ -21251,25 +21251,25 @@
         <v>2.7</v>
       </c>
       <c r="AN97">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AO97">
-        <v>0.82</v>
+        <v>0.2</v>
       </c>
       <c r="AP97">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ97">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR97">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AS97">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AT97">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21457,25 +21457,25 @@
         <v>1.98</v>
       </c>
       <c r="AN98">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO98">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AP98">
+        <v>1.46</v>
+      </c>
+      <c r="AQ98">
         <v>1.15</v>
       </c>
-      <c r="AQ98">
-        <v>1.19</v>
-      </c>
       <c r="AR98">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AS98">
-        <v>1.14</v>
+        <v>1.11</v>
       </c>
       <c r="AT98">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="AU98">
         <v>9</v>
@@ -21663,25 +21663,25 @@
         <v>1.6</v>
       </c>
       <c r="AN99">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AO99">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="AP99">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ99">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR99">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS99">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AT99">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AU99">
         <v>5</v>
@@ -21869,25 +21869,25 @@
         <v>1.26</v>
       </c>
       <c r="AN100">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AO100">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ100">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR100">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AS100">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AT100">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -22075,25 +22075,25 @@
         <v>1.28</v>
       </c>
       <c r="AN101">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO101">
-        <v>1.25</v>
+        <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ101">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR101">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AS101">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AT101">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="AU101">
         <v>5</v>
@@ -22281,25 +22281,25 @@
         <v>1.83</v>
       </c>
       <c r="AN102">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="AO102">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AP102">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ102">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR102">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AS102">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AT102">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="AU102">
         <v>8</v>
@@ -22487,25 +22487,25 @@
         <v>1.58</v>
       </c>
       <c r="AN103">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO103">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ103">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR103">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AS103">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AT103">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22693,25 +22693,25 @@
         <v>2.75</v>
       </c>
       <c r="AN104">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AO104">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AP104">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ104">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR104">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AS104">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AT104">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AU104">
         <v>7</v>
@@ -22899,25 +22899,25 @@
         <v>1.24</v>
       </c>
       <c r="AN105">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="AO105">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP105">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR105">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="AS105">
-        <v>1.24</v>
+        <v>0.93</v>
       </c>
       <c r="AT105">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="AU105">
         <v>5</v>
@@ -23105,25 +23105,25 @@
         <v>1.5</v>
       </c>
       <c r="AN106">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AO106">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AP106">
+        <v>1.23</v>
+      </c>
+      <c r="AQ106">
         <v>0.92</v>
       </c>
-      <c r="AQ106">
-        <v>1.19</v>
-      </c>
       <c r="AR106">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS106">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AT106">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="AU106">
         <v>6</v>
@@ -23311,25 +23311,25 @@
         <v>1.22</v>
       </c>
       <c r="AN107">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AO107">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AP107">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ107">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR107">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AS107">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="AT107">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AU107">
         <v>6</v>
@@ -23517,25 +23517,25 @@
         <v>1.38</v>
       </c>
       <c r="AN108">
+        <v>1.14</v>
+      </c>
+      <c r="AO108">
+        <v>0.86</v>
+      </c>
+      <c r="AP108">
         <v>1.23</v>
       </c>
-      <c r="AO108">
-        <v>1.15</v>
-      </c>
-      <c r="AP108">
-        <v>1.19</v>
-      </c>
       <c r="AQ108">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AR108">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AS108">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AT108">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23723,25 +23723,25 @@
         <v>1.8</v>
       </c>
       <c r="AN109">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AO109">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AP109">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ109">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR109">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AS109">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AT109">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23929,25 +23929,25 @@
         <v>1.45</v>
       </c>
       <c r="AN110">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="AO110">
+        <v>1.33</v>
+      </c>
+      <c r="AP110">
         <v>1.54</v>
       </c>
-      <c r="AP110">
-        <v>1.15</v>
-      </c>
       <c r="AQ110">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR110">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AS110">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AT110">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -24135,25 +24135,25 @@
         <v>1.9</v>
       </c>
       <c r="AN111">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AO111">
-        <v>1.38</v>
+        <v>0.67</v>
       </c>
       <c r="AP111">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ111">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR111">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AS111">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AT111">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AU111">
         <v>13</v>
@@ -24341,25 +24341,25 @@
         <v>1.65</v>
       </c>
       <c r="AN112">
-        <v>1.23</v>
+        <v>1.83</v>
       </c>
       <c r="AO112">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AP112">
+        <v>2.08</v>
+      </c>
+      <c r="AQ112">
         <v>1.77</v>
       </c>
-      <c r="AQ112">
-        <v>2.31</v>
-      </c>
       <c r="AR112">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AS112">
         <v>1.85</v>
       </c>
       <c r="AT112">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="AU112">
         <v>8</v>
@@ -24547,25 +24547,25 @@
         <v>1.05</v>
       </c>
       <c r="AN113">
-        <v>0.46</v>
+        <v>0.83</v>
       </c>
       <c r="AO113">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AP113">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ113">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR113">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="AS113">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AT113">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="AU113">
         <v>6</v>
@@ -24753,25 +24753,25 @@
         <v>2.5</v>
       </c>
       <c r="AN114">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AO114">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AP114">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ114">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR114">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS114">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT114">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="AU114">
         <v>7</v>
@@ -24959,25 +24959,25 @@
         <v>0</v>
       </c>
       <c r="AN115">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AO115">
-        <v>1.21</v>
+        <v>0.71</v>
       </c>
       <c r="AP115">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ115">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR115">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AS115">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AT115">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AU115">
         <v>6</v>
@@ -25165,25 +25165,25 @@
         <v>1.53</v>
       </c>
       <c r="AN116">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AO116">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ116">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR116">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AS116">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AT116">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AU116">
         <v>5</v>
@@ -25371,25 +25371,25 @@
         <v>2.5</v>
       </c>
       <c r="AN117">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AO117">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ117">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR117">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AS117">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AT117">
-        <v>3.37</v>
+        <v>3.18</v>
       </c>
       <c r="AU117">
         <v>6</v>
@@ -25577,25 +25577,25 @@
         <v>0</v>
       </c>
       <c r="AN118">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AO118">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="AP118">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ118">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR118">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AS118">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="AT118">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AU118">
         <v>11</v>
@@ -25783,25 +25783,25 @@
         <v>0</v>
       </c>
       <c r="AN119">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AO119">
-        <v>1.36</v>
+        <v>0.71</v>
       </c>
       <c r="AP119">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ119">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR119">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AS119">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AT119">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AU119">
         <v>0</v>
@@ -25989,25 +25989,25 @@
         <v>1.88</v>
       </c>
       <c r="AN120">
+        <v>1.71</v>
+      </c>
+      <c r="AO120">
+        <v>1.29</v>
+      </c>
+      <c r="AP120">
+        <v>1.85</v>
+      </c>
+      <c r="AQ120">
+        <v>1.23</v>
+      </c>
+      <c r="AR120">
         <v>1.64</v>
       </c>
-      <c r="AO120">
-        <v>1.57</v>
-      </c>
-      <c r="AP120">
-        <v>1.73</v>
-      </c>
-      <c r="AQ120">
-        <v>1.54</v>
-      </c>
-      <c r="AR120">
-        <v>1.53</v>
-      </c>
       <c r="AS120">
-        <v>1.34</v>
+        <v>0.99</v>
       </c>
       <c r="AT120">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="AU120">
         <v>12</v>
@@ -26195,25 +26195,25 @@
         <v>2.15</v>
       </c>
       <c r="AN121">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AO121">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AP121">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ121">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR121">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AS121">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AT121">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AU121">
         <v>7</v>
@@ -26401,25 +26401,25 @@
         <v>1.38</v>
       </c>
       <c r="AN122">
-        <v>0.93</v>
+        <v>1.43</v>
       </c>
       <c r="AO122">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ122">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR122">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AS122">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT122">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AU122">
         <v>6</v>
@@ -26607,25 +26607,25 @@
         <v>4</v>
       </c>
       <c r="AN123">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AO123">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AP123">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ123">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR123">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AS123">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT123">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU123">
         <v>9</v>
@@ -26813,25 +26813,25 @@
         <v>1.92</v>
       </c>
       <c r="AN124">
-        <v>1.13</v>
+        <v>1.86</v>
       </c>
       <c r="AO124">
-        <v>1.4</v>
+        <v>0.57</v>
       </c>
       <c r="AP124">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ124">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR124">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AS124">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="AT124">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AU124">
         <v>3</v>
@@ -27019,22 +27019,22 @@
         <v>1.2</v>
       </c>
       <c r="AN125">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="AO125">
-        <v>2.27</v>
+        <v>1.71</v>
       </c>
       <c r="AP125">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ125">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR125">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AS125">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AT125">
         <v>3.15</v>
@@ -27225,25 +27225,25 @@
         <v>1.36</v>
       </c>
       <c r="AN126">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AO126">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AP126">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ126">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR126">
         <v>1.26</v>
       </c>
       <c r="AS126">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AT126">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="AU126">
         <v>3</v>
@@ -27431,25 +27431,25 @@
         <v>1.25</v>
       </c>
       <c r="AN127">
-        <v>0.47</v>
+        <v>0.86</v>
       </c>
       <c r="AO127">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AP127">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR127">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AS127">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT127">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AU127">
         <v>9</v>
@@ -27637,25 +27637,25 @@
         <v>1.98</v>
       </c>
       <c r="AN128">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO128">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AP128">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ128">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR128">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AS128">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AT128">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="AU128">
         <v>7</v>
@@ -27843,25 +27843,25 @@
         <v>1.68</v>
       </c>
       <c r="AN129">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AO129">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AP129">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ129">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR129">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AS129">
-        <v>1.31</v>
+        <v>0.99</v>
       </c>
       <c r="AT129">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="AU129">
         <v>9</v>
@@ -28049,25 +28049,25 @@
         <v>3.6</v>
       </c>
       <c r="AN130">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="AO130">
-        <v>1.06</v>
+        <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ130">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR130">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AS130">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AT130">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AU130">
         <v>7</v>
@@ -28255,25 +28255,25 @@
         <v>1.45</v>
       </c>
       <c r="AN131">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="AO131">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AP131">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ131">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AR131">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AS131">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AT131">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28461,25 +28461,25 @@
         <v>1.26</v>
       </c>
       <c r="AN132">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO132">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AP132">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ132">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR132">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AS132">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AT132">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="AU132">
         <v>6</v>
@@ -28667,25 +28667,25 @@
         <v>1.95</v>
       </c>
       <c r="AN133">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="AO133">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="AP133">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ133">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR133">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AS133">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT133">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28873,25 +28873,25 @@
         <v>1.77</v>
       </c>
       <c r="AN134">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AO134">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ134">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR134">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS134">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AT134">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU134">
         <v>9</v>
@@ -29079,25 +29079,25 @@
         <v>1.22</v>
       </c>
       <c r="AN135">
-        <v>0.9399999999999999</v>
+        <v>1.38</v>
       </c>
       <c r="AO135">
-        <v>1.44</v>
+        <v>0.75</v>
       </c>
       <c r="AP135">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ135">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR135">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AS135">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AT135">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="AU135">
         <v>8</v>
@@ -29285,25 +29285,25 @@
         <v>3.35</v>
       </c>
       <c r="AN136">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AO136">
-        <v>0.63</v>
+        <v>0.13</v>
       </c>
       <c r="AP136">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ136">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR136">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AS136">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AT136">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AU136">
         <v>7</v>
@@ -29494,22 +29494,22 @@
         <v>1.13</v>
       </c>
       <c r="AO137">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ137">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR137">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AS137">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AT137">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="AU137">
         <v>2</v>
@@ -29697,25 +29697,25 @@
         <v>1.52</v>
       </c>
       <c r="AN138">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AO138">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AP138">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ138">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR138">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AS138">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AT138">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="AU138">
         <v>7</v>
@@ -29903,25 +29903,25 @@
         <v>1.36</v>
       </c>
       <c r="AN139">
-        <v>0.59</v>
+        <v>1.13</v>
       </c>
       <c r="AO139">
-        <v>1.35</v>
+        <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ139">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR139">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AS139">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
       <c r="AT139">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AU139">
         <v>9</v>
@@ -30109,25 +30109,25 @@
         <v>1.57</v>
       </c>
       <c r="AN140">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AO140">
-        <v>1.24</v>
+        <v>0.78</v>
       </c>
       <c r="AP140">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ140">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR140">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AS140">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AT140">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="AU140">
         <v>3</v>
@@ -30315,25 +30315,25 @@
         <v>1.66</v>
       </c>
       <c r="AN141">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="AO141">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ141">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR141">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AS141">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AT141">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="AU141">
         <v>2</v>
@@ -30521,25 +30521,25 @@
         <v>2.3</v>
       </c>
       <c r="AN142">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AO142">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ142">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR142">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AS142">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AT142">
-        <v>3.56</v>
+        <v>3.79</v>
       </c>
       <c r="AU142">
         <v>6</v>
@@ -30727,25 +30727,25 @@
         <v>2.75</v>
       </c>
       <c r="AN143">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="AO143">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="AP143">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ143">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR143">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AS143">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AT143">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="AU143">
         <v>14</v>
@@ -30933,25 +30933,25 @@
         <v>1.3</v>
       </c>
       <c r="AN144">
-        <v>1.06</v>
+        <v>1.63</v>
       </c>
       <c r="AO144">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AP144">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ144">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR144">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AS144">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AT144">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AU144">
         <v>7</v>
@@ -31139,25 +31139,25 @@
         <v>2</v>
       </c>
       <c r="AN145">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AO145">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ145">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR145">
+        <v>1.64</v>
+      </c>
+      <c r="AS145">
         <v>1.33</v>
       </c>
-      <c r="AS145">
-        <v>1.49</v>
-      </c>
       <c r="AT145">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="AU145">
         <v>6</v>
@@ -31345,25 +31345,25 @@
         <v>1.65</v>
       </c>
       <c r="AN146">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AO146">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ146">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR146">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AS146">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AT146">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU146">
         <v>7</v>
@@ -31551,25 +31551,25 @@
         <v>1.83</v>
       </c>
       <c r="AN147">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AO147">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP147">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ147">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR147">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AS147">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AT147">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="AU147">
         <v>8</v>
@@ -31760,22 +31760,22 @@
         <v>1.33</v>
       </c>
       <c r="AO148">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ148">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR148">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AS148">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AT148">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AU148">
         <v>2</v>
@@ -31963,25 +31963,25 @@
         <v>1.48</v>
       </c>
       <c r="AN149">
-        <v>0.61</v>
+        <v>1.11</v>
       </c>
       <c r="AO149">
-        <v>0.9399999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="AP149">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ149">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR149">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AS149">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AT149">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AU149">
         <v>8</v>
@@ -32169,25 +32169,25 @@
         <v>1.75</v>
       </c>
       <c r="AN150">
-        <v>2.11</v>
+        <v>2.78</v>
       </c>
       <c r="AO150">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AP150">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ150">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR150">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AS150">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AT150">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="AU150">
         <v>7</v>
@@ -32375,25 +32375,25 @@
         <v>1.45</v>
       </c>
       <c r="AN151">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO151">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AP151">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ151">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR151">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AS151">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AT151">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AU151">
         <v>2</v>
@@ -32581,22 +32581,22 @@
         <v>1.5</v>
       </c>
       <c r="AN152">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="AO152">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AP152">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ152">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR152">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AS152">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AT152">
         <v>3.43</v>
@@ -32787,25 +32787,25 @@
         <v>1.72</v>
       </c>
       <c r="AN153">
-        <v>0.9399999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="AO153">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ153">
+        <v>0.62</v>
+      </c>
+      <c r="AR153">
+        <v>1.62</v>
+      </c>
+      <c r="AS153">
         <v>1.23</v>
       </c>
-      <c r="AR153">
-        <v>1.5</v>
-      </c>
-      <c r="AS153">
-        <v>1.21</v>
-      </c>
       <c r="AT153">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="AU153">
         <v>5</v>
@@ -32993,25 +32993,25 @@
         <v>1.48</v>
       </c>
       <c r="AN154">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AO154">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="AP154">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ154">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR154">
-        <v>1.48</v>
+        <v>1.81</v>
       </c>
       <c r="AS154">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="AT154">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="AU154">
         <v>4</v>
@@ -33199,25 +33199,25 @@
         <v>1.38</v>
       </c>
       <c r="AN155">
-        <v>0.95</v>
+        <v>1.44</v>
       </c>
       <c r="AO155">
-        <v>1.26</v>
+        <v>0.7</v>
       </c>
       <c r="AP155">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ155">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR155">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AS155">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AT155">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33405,25 +33405,25 @@
         <v>3.4</v>
       </c>
       <c r="AN156">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AO156">
-        <v>1.21</v>
+        <v>0.78</v>
       </c>
       <c r="AP156">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ156">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR156">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AS156">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AT156">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="AU156">
         <v>10</v>
@@ -33611,22 +33611,22 @@
         <v>1.93</v>
       </c>
       <c r="AN157">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AO157">
-        <v>1.26</v>
+        <v>0.67</v>
       </c>
       <c r="AP157">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ157">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR157">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AS157">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AT157">
         <v>2.5</v>
@@ -33817,25 +33817,25 @@
         <v>1.3</v>
       </c>
       <c r="AN158">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AO158">
-        <v>1.47</v>
+        <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ158">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR158">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AS158">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AT158">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="AU158">
         <v>4</v>
@@ -34023,25 +34023,25 @@
         <v>2.2</v>
       </c>
       <c r="AN159">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AO159">
-        <v>0.63</v>
+        <v>0.11</v>
       </c>
       <c r="AP159">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ159">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR159">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AS159">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT159">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AU159">
         <v>11</v>
@@ -34229,25 +34229,25 @@
         <v>1.5</v>
       </c>
       <c r="AN160">
-        <v>0.95</v>
+        <v>1.44</v>
       </c>
       <c r="AO160">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP160">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ160">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR160">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AS160">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AT160">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AU160">
         <v>8</v>
@@ -34435,25 +34435,25 @@
         <v>2.95</v>
       </c>
       <c r="AN161">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AO161">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ161">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR161">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AS161">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AT161">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34641,25 +34641,25 @@
         <v>1.83</v>
       </c>
       <c r="AN162">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AO162">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ162">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR162">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AS162">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AT162">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AU162">
         <v>7</v>
@@ -34847,25 +34847,25 @@
         <v>1.75</v>
       </c>
       <c r="AN163">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="AO163">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AP163">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ163">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR163">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AS163">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AT163">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="AU163">
         <v>7</v>
@@ -35053,22 +35053,22 @@
         <v>2.3</v>
       </c>
       <c r="AN164">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AO164">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="AP164">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ164">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AR164">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AS164">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AT164">
         <v>3</v>
@@ -35259,25 +35259,25 @@
         <v>1.34</v>
       </c>
       <c r="AN165">
-        <v>1.35</v>
+        <v>1.89</v>
       </c>
       <c r="AO165">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="AP165">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ165">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR165">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AS165">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AT165">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="AU165">
         <v>5</v>
@@ -35465,25 +35465,25 @@
         <v>1.21</v>
       </c>
       <c r="AN166">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="AO166">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ166">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR166">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AS166">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AT166">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AU166">
         <v>8</v>
@@ -35671,25 +35671,25 @@
         <v>1.33</v>
       </c>
       <c r="AN167">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AO167">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AP167">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ167">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR167">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AS167">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AT167">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="AU167">
         <v>4</v>
@@ -35877,25 +35877,25 @@
         <v>1.32</v>
       </c>
       <c r="AN168">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AO168">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AP168">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ168">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR168">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="AS168">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AT168">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="AU168">
         <v>6</v>
@@ -36083,25 +36083,25 @@
         <v>1.62</v>
       </c>
       <c r="AN169">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AO169">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AP169">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ169">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR169">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AS169">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AT169">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="AU169">
         <v>8</v>
@@ -36289,25 +36289,25 @@
         <v>1.72</v>
       </c>
       <c r="AN170">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AO170">
-        <v>1.29</v>
+        <v>0.91</v>
       </c>
       <c r="AP170">
+        <v>1.85</v>
+      </c>
+      <c r="AQ170">
+        <v>0.92</v>
+      </c>
+      <c r="AR170">
         <v>1.54</v>
       </c>
-      <c r="AQ170">
-        <v>1.27</v>
-      </c>
-      <c r="AR170">
-        <v>1.34</v>
-      </c>
       <c r="AS170">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AT170">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AU170">
         <v>4</v>
@@ -36495,25 +36495,25 @@
         <v>1.41</v>
       </c>
       <c r="AN171">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AO171">
-        <v>1.14</v>
+        <v>0.6</v>
       </c>
       <c r="AP171">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ171">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR171">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AS171">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AT171">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AU171">
         <v>2</v>
@@ -36701,25 +36701,25 @@
         <v>1.41</v>
       </c>
       <c r="AN172">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AO172">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ172">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR172">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AS172">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AT172">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="AU172">
         <v>3</v>
@@ -36907,25 +36907,25 @@
         <v>5.25</v>
       </c>
       <c r="AN173">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AO173">
-        <v>0.62</v>
+        <v>0.1</v>
       </c>
       <c r="AP173">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ173">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR173">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AS173">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AT173">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="AU173">
         <v>10</v>
@@ -37113,25 +37113,25 @@
         <v>1.26</v>
       </c>
       <c r="AN174">
-        <v>0.86</v>
+        <v>1.3</v>
       </c>
       <c r="AO174">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ174">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR174">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AS174">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AT174">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AU174">
         <v>4</v>
@@ -37319,25 +37319,25 @@
         <v>2.45</v>
       </c>
       <c r="AN175">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AO175">
-        <v>1.19</v>
+        <v>0.73</v>
       </c>
       <c r="AP175">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ175">
+        <v>0.62</v>
+      </c>
+      <c r="AR175">
+        <v>1.74</v>
+      </c>
+      <c r="AS175">
         <v>1.23</v>
       </c>
-      <c r="AR175">
-        <v>1.58</v>
-      </c>
-      <c r="AS175">
-        <v>1.26</v>
-      </c>
       <c r="AT175">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="AU175">
         <v>10</v>
@@ -37525,25 +37525,25 @@
         <v>1.77</v>
       </c>
       <c r="AN176">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AO176">
-        <v>1.33</v>
+        <v>0.7</v>
       </c>
       <c r="AP176">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ176">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR176">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AS176">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AT176">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AU176">
         <v>3</v>
@@ -37731,25 +37731,25 @@
         <v>2.05</v>
       </c>
       <c r="AN177">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AO177">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="AP177">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ177">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR177">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="AS177">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AT177">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AU177">
         <v>8</v>
@@ -37937,25 +37937,25 @@
         <v>1.41</v>
       </c>
       <c r="AN178">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="AO178">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AP178">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ178">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR178">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AS178">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="AT178">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="AU178">
         <v>5</v>
@@ -38143,25 +38143,25 @@
         <v>1.33</v>
       </c>
       <c r="AN179">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="AO179">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AQ179">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR179">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AS179">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AT179">
-        <v>3.48</v>
+        <v>3.67</v>
       </c>
       <c r="AU179">
         <v>6</v>
@@ -38349,25 +38349,25 @@
         <v>1.78</v>
       </c>
       <c r="AN180">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AO180">
-        <v>1.23</v>
+        <v>0.82</v>
       </c>
       <c r="AP180">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ180">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR180">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AS180">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT180">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="AU180">
         <v>5</v>
@@ -38555,25 +38555,25 @@
         <v>4.4</v>
       </c>
       <c r="AN181">
-        <v>2.14</v>
+        <v>2.36</v>
       </c>
       <c r="AO181">
-        <v>0.82</v>
+        <v>0.45</v>
       </c>
       <c r="AP181">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AQ181">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR181">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AS181">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AT181">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AU181">
         <v>8</v>
@@ -38761,25 +38761,25 @@
         <v>1.65</v>
       </c>
       <c r="AN182">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="AO182">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AP182">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ182">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR182">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AS182">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AT182">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AU182">
         <v>7</v>
@@ -38967,25 +38967,25 @@
         <v>1.13</v>
       </c>
       <c r="AN183">
-        <v>0.59</v>
+        <v>1.09</v>
       </c>
       <c r="AO183">
-        <v>1.68</v>
+        <v>1.18</v>
       </c>
       <c r="AP183">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ183">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR183">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AS183">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AT183">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AU183">
         <v>5</v>
@@ -39176,22 +39176,22 @@
         <v>1.64</v>
       </c>
       <c r="AO184">
-        <v>1.23</v>
+        <v>0.9</v>
       </c>
       <c r="AP184">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ184">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR184">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AS184">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AT184">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="AU184">
         <v>7</v>
@@ -39379,25 +39379,25 @@
         <v>1.51</v>
       </c>
       <c r="AN185">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="AO185">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AP185">
+        <v>1.85</v>
+      </c>
+      <c r="AQ185">
         <v>1.23</v>
       </c>
-      <c r="AQ185">
-        <v>1.54</v>
-      </c>
       <c r="AR185">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AS185">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AT185">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="AU185">
         <v>3</v>
@@ -39585,25 +39585,25 @@
         <v>1.52</v>
       </c>
       <c r="AN186">
-        <v>1.13</v>
+        <v>1.64</v>
       </c>
       <c r="AO186">
-        <v>1.17</v>
+        <v>0.82</v>
       </c>
       <c r="AP186">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ186">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR186">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AS186">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AT186">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AU186">
         <v>2</v>
@@ -39791,25 +39791,25 @@
         <v>2.2</v>
       </c>
       <c r="AN187">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AO187">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AP187">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ187">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR187">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AS187">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AT187">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="AU187">
         <v>11</v>
@@ -39997,25 +39997,25 @@
         <v>1.95</v>
       </c>
       <c r="AN188">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="AO188">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="AP188">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ188">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR188">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AS188">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT188">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AU188">
         <v>4</v>
@@ -40203,25 +40203,25 @@
         <v>3.25</v>
       </c>
       <c r="AN189">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="AO189">
-        <v>0.57</v>
+        <v>0.09</v>
       </c>
       <c r="AP189">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ189">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AR189">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AS189">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AT189">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="AU189">
         <v>6</v>
@@ -40409,25 +40409,25 @@
         <v>1.23</v>
       </c>
       <c r="AN190">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AO190">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AP190">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ190">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR190">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="AS190">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AT190">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="AU190">
         <v>4</v>
@@ -40615,25 +40615,25 @@
         <v>2.7</v>
       </c>
       <c r="AN191">
-        <v>1.74</v>
+        <v>2.18</v>
       </c>
       <c r="AO191">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AP191">
-        <v>1.77</v>
+        <v>2.08</v>
       </c>
       <c r="AQ191">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR191">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AS191">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AT191">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="AU191">
         <v>3</v>
@@ -40821,25 +40821,25 @@
         <v>1.53</v>
       </c>
       <c r="AN192">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AO192">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.54</v>
+        <v>1.85</v>
       </c>
       <c r="AQ192">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR192">
+        <v>1.52</v>
+      </c>
+      <c r="AS192">
         <v>1.39</v>
       </c>
-      <c r="AS192">
-        <v>1.54</v>
-      </c>
       <c r="AT192">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="AU192">
         <v>8</v>
@@ -41027,25 +41027,25 @@
         <v>1.35</v>
       </c>
       <c r="AN193">
-        <v>0.83</v>
+        <v>1.18</v>
       </c>
       <c r="AO193">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AP193">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ193">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR193">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AS193">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AT193">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="AU193">
         <v>4</v>
@@ -41233,25 +41233,25 @@
         <v>1.55</v>
       </c>
       <c r="AN194">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AO194">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP194">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AQ194">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AR194">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AS194">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT194">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="AU194">
         <v>8</v>
@@ -41439,25 +41439,25 @@
         <v>3.25</v>
       </c>
       <c r="AN195">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO195">
+        <v>0.67</v>
+      </c>
+      <c r="AP195">
+        <v>2.31</v>
+      </c>
+      <c r="AQ195">
+        <v>0.62</v>
+      </c>
+      <c r="AR195">
+        <v>2.09</v>
+      </c>
+      <c r="AS195">
         <v>1.21</v>
       </c>
-      <c r="AP195">
-        <v>2</v>
-      </c>
-      <c r="AQ195">
-        <v>1.23</v>
-      </c>
-      <c r="AR195">
-        <v>1.87</v>
-      </c>
-      <c r="AS195">
-        <v>1.24</v>
-      </c>
       <c r="AT195">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="AU195">
         <v>5</v>
@@ -41645,25 +41645,25 @@
         <v>1.44</v>
       </c>
       <c r="AN196">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AO196">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AP196">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AQ196">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AR196">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AS196">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AT196">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
       <c r="AU196">
         <v>5</v>
@@ -41851,25 +41851,25 @@
         <v>2.25</v>
       </c>
       <c r="AN197">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AO197">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AP197">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AQ197">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AR197">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AS197">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AT197">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AU197">
         <v>7</v>
@@ -42057,25 +42057,25 @@
         <v>1.68</v>
       </c>
       <c r="AN198">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO198">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AP198">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AQ198">
-        <v>1.65</v>
+        <v>1.31</v>
       </c>
       <c r="AR198">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AS198">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AT198">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="AU198">
         <v>5</v>
@@ -42263,25 +42263,25 @@
         <v>1.16</v>
       </c>
       <c r="AN199">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AO199">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AP199">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AQ199">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AR199">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AS199">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AT199">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="AU199">
         <v>3</v>
@@ -42469,25 +42469,25 @@
         <v>2.05</v>
       </c>
       <c r="AN200">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AO200">
+        <v>0.92</v>
+      </c>
+      <c r="AP200">
         <v>1.46</v>
       </c>
-      <c r="AP200">
-        <v>1.15</v>
-      </c>
       <c r="AQ200">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AR200">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AS200">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AT200">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="AU200">
         <v>10</v>
@@ -42675,25 +42675,25 @@
         <v>1.22</v>
       </c>
       <c r="AN201">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AO201">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AP201">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AQ201">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AR201">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AS201">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AT201">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="AU201">
         <v>4</v>
@@ -42881,25 +42881,25 @@
         <v>1.18</v>
       </c>
       <c r="AN202">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO202">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AP202">
-        <v>1.35</v>
+        <v>1.85</v>
       </c>
       <c r="AQ202">
-        <v>2.31</v>
+        <v>1.77</v>
       </c>
       <c r="AR202">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AS202">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AT202">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="AU202">
         <v>4</v>
@@ -43087,25 +43087,25 @@
         <v>1.77</v>
       </c>
       <c r="AN203">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="AO203">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AP203">
-        <v>1.23</v>
+        <v>1.85</v>
       </c>
       <c r="AQ203">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AR203">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AS203">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AT203">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="AU203">
         <v>5</v>
@@ -43293,25 +43293,25 @@
         <v>2.15</v>
       </c>
       <c r="AN204">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AO204">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="AP204">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AQ204">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="AR204">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="AS204">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AT204">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="AU204">
         <v>10</v>
@@ -43499,25 +43499,25 @@
         <v>1.17</v>
       </c>
       <c r="AN205">
-        <v>0.92</v>
+        <v>1.25</v>
       </c>
       <c r="AO205">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AP205">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="AQ205">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AR205">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AS205">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AT205">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="AU205">
         <v>4</v>
@@ -43705,25 +43705,25 @@
         <v>2.65</v>
       </c>
       <c r="AN206">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AO206">
-        <v>0.5600000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AP206">
+        <v>1.85</v>
+      </c>
+      <c r="AQ206">
+        <v>0.08</v>
+      </c>
+      <c r="AR206">
         <v>1.54</v>
       </c>
-      <c r="AQ206">
-        <v>0.54</v>
-      </c>
-      <c r="AR206">
-        <v>1.42</v>
-      </c>
       <c r="AS206">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT206">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AU206">
         <v>4</v>
@@ -43911,25 +43911,25 @@
         <v>2.25</v>
       </c>
       <c r="AN207">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="AO207">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="AP207">
+        <v>2.08</v>
+      </c>
+      <c r="AQ207">
+        <v>0.92</v>
+      </c>
+      <c r="AR207">
         <v>1.77</v>
       </c>
-      <c r="AQ207">
-        <v>1.19</v>
-      </c>
-      <c r="AR207">
-        <v>1.61</v>
-      </c>
       <c r="AS207">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AT207">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AU207">
         <v>9</v>
@@ -44117,25 +44117,25 @@
         <v>1.49</v>
       </c>
       <c r="AN208">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AO208">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AP208">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="AQ208">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AR208">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AS208">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AT208">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AU208">
         <v>6</v>
@@ -44323,25 +44323,25 @@
         <v>1.62</v>
       </c>
       <c r="AN209">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="AO209">
-        <v>1.16</v>
+        <v>0.83</v>
       </c>
       <c r="AP209">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AQ209">
-        <v>1.15</v>
+        <v>0.85</v>
       </c>
       <c r="AR209">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AS209">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AT209">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="AU209">
         <v>10</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1316" uniqueCount="326">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="327">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -730,6 +730,9 @@
     <t>['10', '67', '90']</t>
   </si>
   <si>
+    <t>['26']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1353,7 +1356,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP209"/>
+  <dimension ref="A1:BP210"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1609,7 +1612,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2308,7 +2311,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ5">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2639,7 +2642,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3463,7 +3466,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3541,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ11">
         <v>0.85</v>
@@ -3875,7 +3878,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4081,7 +4084,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4287,7 +4290,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4699,7 +4702,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5317,7 +5320,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5729,7 +5732,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5935,7 +5938,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6016,7 +6019,7 @@
         <v>2</v>
       </c>
       <c r="AQ23">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR23">
         <v>2.53</v>
@@ -6347,7 +6350,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6759,7 +6762,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6965,7 +6968,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7171,7 +7174,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7249,7 +7252,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ29">
         <v>1.62</v>
@@ -8201,7 +8204,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8613,7 +8616,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9643,7 +9646,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9721,7 +9724,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ41">
         <v>0.92</v>
@@ -9849,7 +9852,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10960,7 +10963,7 @@
         <v>1</v>
       </c>
       <c r="AQ47">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR47">
         <v>1.76</v>
@@ -11085,7 +11088,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11291,7 +11294,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11497,7 +11500,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11703,7 +11706,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12733,7 +12736,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13145,7 +13148,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13226,7 +13229,7 @@
         <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR58">
         <v>0.9399999999999999</v>
@@ -13351,7 +13354,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13763,7 +13766,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14047,7 +14050,7 @@
         <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ62">
         <v>0.77</v>
@@ -14587,7 +14590,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15205,7 +15208,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15411,7 +15414,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16235,7 +16238,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16316,7 +16319,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ73">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR73">
         <v>1.73</v>
@@ -16441,7 +16444,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16725,7 +16728,7 @@
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ75">
         <v>0.62</v>
@@ -18295,7 +18298,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18913,7 +18916,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -18994,7 +18997,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ86">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR86">
         <v>1.86</v>
@@ -19609,7 +19612,7 @@
         <v>0.8</v>
       </c>
       <c r="AP89">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ89">
         <v>0.46</v>
@@ -19943,7 +19946,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20149,7 +20152,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20561,7 +20564,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20973,7 +20976,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21179,7 +21182,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21591,7 +21594,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21672,7 +21675,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ99">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR99">
         <v>1.16</v>
@@ -21797,7 +21800,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -22003,7 +22006,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22081,7 +22084,7 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ101">
         <v>1.46</v>
@@ -23033,7 +23036,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23239,7 +23242,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23445,7 +23448,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23857,7 +23860,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24475,7 +24478,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24968,7 +24971,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ115">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR115">
         <v>2.07</v>
@@ -25583,7 +25586,7 @@
         <v>0.14</v>
       </c>
       <c r="AP118">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ118">
         <v>0.08</v>
@@ -25711,7 +25714,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26329,7 +26332,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26947,7 +26950,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27359,7 +27362,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27771,7 +27774,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27977,7 +27980,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28389,7 +28392,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28467,7 +28470,7 @@
         <v>1.75</v>
       </c>
       <c r="AP132">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ132">
         <v>1.69</v>
@@ -28676,7 +28679,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ133">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR133">
         <v>1.68</v>
@@ -28801,7 +28804,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29213,7 +29216,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29703,7 +29706,7 @@
         <v>1.38</v>
       </c>
       <c r="AP138">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ138">
         <v>1.31</v>
@@ -30243,7 +30246,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30655,7 +30658,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30861,7 +30864,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31273,7 +31276,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31560,7 +31563,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ147">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR147">
         <v>1.75</v>
@@ -31685,7 +31688,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31891,7 +31894,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32509,7 +32512,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32921,7 +32924,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33127,7 +33130,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33333,7 +33336,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33617,7 +33620,7 @@
         <v>0.67</v>
       </c>
       <c r="AP157">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ157">
         <v>0.85</v>
@@ -33745,7 +33748,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34157,7 +34160,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34363,7 +34366,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34775,7 +34778,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34856,7 +34859,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ163">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR163">
         <v>1.85</v>
@@ -35187,7 +35190,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35393,7 +35396,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35805,7 +35808,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36423,7 +36426,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36629,7 +36632,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36707,7 +36710,7 @@
         <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ172">
         <v>1.77</v>
@@ -36835,7 +36838,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -37041,7 +37044,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37453,7 +37456,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37659,7 +37662,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38071,7 +38074,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38277,7 +38280,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38895,7 +38898,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39101,7 +39104,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39925,7 +39928,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40543,7 +40546,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40624,7 +40627,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ191">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR191">
         <v>1.79</v>
@@ -40955,7 +40958,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41161,7 +41164,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41239,7 +41242,7 @@
         <v>1.25</v>
       </c>
       <c r="AP194">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="AQ194">
         <v>1.23</v>
@@ -41654,7 +41657,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ196">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR196">
         <v>1.08</v>
@@ -42191,7 +42194,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42397,7 +42400,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42809,7 +42812,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -43015,7 +43018,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43221,7 +43224,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43427,7 +43430,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43633,7 +43636,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -44408,6 +44411,212 @@
       </c>
       <c r="BP209">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:68">
+      <c r="A210" s="1">
+        <v>209</v>
+      </c>
+      <c r="B210">
+        <v>7453632</v>
+      </c>
+      <c r="C210" t="s">
+        <v>68</v>
+      </c>
+      <c r="D210" t="s">
+        <v>69</v>
+      </c>
+      <c r="E210" s="2">
+        <v>45709.69791666666</v>
+      </c>
+      <c r="F210">
+        <v>27</v>
+      </c>
+      <c r="G210" t="s">
+        <v>79</v>
+      </c>
+      <c r="H210" t="s">
+        <v>81</v>
+      </c>
+      <c r="I210">
+        <v>1</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>1</v>
+      </c>
+      <c r="L210">
+        <v>1</v>
+      </c>
+      <c r="M210">
+        <v>1</v>
+      </c>
+      <c r="N210">
+        <v>2</v>
+      </c>
+      <c r="O210" t="s">
+        <v>238</v>
+      </c>
+      <c r="P210" t="s">
+        <v>188</v>
+      </c>
+      <c r="Q210">
+        <v>2.5</v>
+      </c>
+      <c r="R210">
+        <v>2.25</v>
+      </c>
+      <c r="S210">
+        <v>3.6</v>
+      </c>
+      <c r="T210">
+        <v>1.3</v>
+      </c>
+      <c r="U210">
+        <v>3.2</v>
+      </c>
+      <c r="V210">
+        <v>2.35</v>
+      </c>
+      <c r="W210">
+        <v>1.52</v>
+      </c>
+      <c r="X210">
+        <v>5.5</v>
+      </c>
+      <c r="Y210">
+        <v>1.13</v>
+      </c>
+      <c r="Z210">
+        <v>1.91</v>
+      </c>
+      <c r="AA210">
+        <v>3.72</v>
+      </c>
+      <c r="AB210">
+        <v>3.61</v>
+      </c>
+      <c r="AC210">
+        <v>1.04</v>
+      </c>
+      <c r="AD210">
+        <v>10</v>
+      </c>
+      <c r="AE210">
+        <v>1.22</v>
+      </c>
+      <c r="AF210">
+        <v>4.2</v>
+      </c>
+      <c r="AG210">
+        <v>1.61</v>
+      </c>
+      <c r="AH210">
+        <v>2.2</v>
+      </c>
+      <c r="AI210">
+        <v>1.57</v>
+      </c>
+      <c r="AJ210">
+        <v>2.25</v>
+      </c>
+      <c r="AK210">
+        <v>1.3</v>
+      </c>
+      <c r="AL210">
+        <v>1.27</v>
+      </c>
+      <c r="AM210">
+        <v>1.77</v>
+      </c>
+      <c r="AN210">
+        <v>1.46</v>
+      </c>
+      <c r="AO210">
+        <v>0.62</v>
+      </c>
+      <c r="AP210">
+        <v>1.43</v>
+      </c>
+      <c r="AQ210">
+        <v>0.64</v>
+      </c>
+      <c r="AR210">
+        <v>1.55</v>
+      </c>
+      <c r="AS210">
+        <v>1.25</v>
+      </c>
+      <c r="AT210">
+        <v>2.8</v>
+      </c>
+      <c r="AU210">
+        <v>2</v>
+      </c>
+      <c r="AV210">
+        <v>4</v>
+      </c>
+      <c r="AW210">
+        <v>4</v>
+      </c>
+      <c r="AX210">
+        <v>6</v>
+      </c>
+      <c r="AY210">
+        <v>7</v>
+      </c>
+      <c r="AZ210">
+        <v>12</v>
+      </c>
+      <c r="BA210">
+        <v>4</v>
+      </c>
+      <c r="BB210">
+        <v>0</v>
+      </c>
+      <c r="BC210">
+        <v>4</v>
+      </c>
+      <c r="BD210">
+        <v>1.72</v>
+      </c>
+      <c r="BE210">
+        <v>6.5</v>
+      </c>
+      <c r="BF210">
+        <v>2.35</v>
+      </c>
+      <c r="BG210">
+        <v>1.26</v>
+      </c>
+      <c r="BH210">
+        <v>3.4</v>
+      </c>
+      <c r="BI210">
+        <v>1.47</v>
+      </c>
+      <c r="BJ210">
+        <v>2.48</v>
+      </c>
+      <c r="BK210">
+        <v>1.75</v>
+      </c>
+      <c r="BL210">
+        <v>1.95</v>
+      </c>
+      <c r="BM210">
+        <v>2.17</v>
+      </c>
+      <c r="BN210">
+        <v>1.6</v>
+      </c>
+      <c r="BO210">
+        <v>2.75</v>
+      </c>
+      <c r="BP210">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1322" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="330">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -733,6 +733,9 @@
     <t>['26']</t>
   </si>
   <si>
+    <t>['47', '58']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -995,6 +998,12 @@
   </si>
   <si>
     <t>['6', '55']</t>
+  </si>
+  <si>
+    <t>['56', '62', '90+3']</t>
+  </si>
+  <si>
+    <t>['56', '90+6']</t>
   </si>
 </sst>
 </file>
@@ -1356,7 +1365,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP210"/>
+  <dimension ref="A1:BP213"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1612,7 +1621,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1896,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ3">
         <v>1.46</v>
@@ -2105,7 +2114,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2642,7 +2651,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3132,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9">
         <v>0.77</v>
@@ -3341,7 +3350,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ10">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3466,7 +3475,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3878,7 +3887,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3959,7 +3968,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ13">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4084,7 +4093,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4162,7 +4171,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ14">
         <v>1.62</v>
@@ -4290,7 +4299,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4702,7 +4711,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5192,7 +5201,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ19">
         <v>0.46</v>
@@ -5320,7 +5329,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5398,7 +5407,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ20">
         <v>1.46</v>
@@ -5607,7 +5616,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ21">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR21">
         <v>1.37</v>
@@ -5732,7 +5741,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5938,7 +5947,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6016,7 +6025,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ23">
         <v>0.64</v>
@@ -6350,7 +6359,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6431,7 +6440,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ25">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR25">
         <v>2.16</v>
@@ -6637,7 +6646,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ26">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR26">
         <v>1.53</v>
@@ -6762,7 +6771,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6968,7 +6977,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7174,7 +7183,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -8204,7 +8213,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8282,10 +8291,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR34">
         <v>1.74</v>
@@ -8488,7 +8497,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ35">
         <v>0.92</v>
@@ -8616,7 +8625,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8694,7 +8703,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ36">
         <v>1.69</v>
@@ -9109,7 +9118,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ38">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR38">
         <v>1.16</v>
@@ -9646,7 +9655,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9727,7 +9736,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ41">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR41">
         <v>1.62</v>
@@ -9852,7 +9861,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -11088,7 +11097,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11166,7 +11175,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ48">
         <v>0.85</v>
@@ -11294,7 +11303,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11500,7 +11509,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11706,7 +11715,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11990,7 +11999,7 @@
         <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ52">
         <v>1.46</v>
@@ -12199,7 +12208,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ53">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR53">
         <v>0.82</v>
@@ -12405,7 +12414,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ54">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR54">
         <v>1.56</v>
@@ -12736,7 +12745,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13148,7 +13157,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13354,7 +13363,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13432,7 +13441,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
         <v>1.31</v>
@@ -13641,7 +13650,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ60">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR60">
         <v>1.66</v>
@@ -13766,7 +13775,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14590,7 +14599,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15208,7 +15217,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15414,7 +15423,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15492,7 +15501,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ69">
         <v>1.62</v>
@@ -15698,10 +15707,10 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ70">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR70">
         <v>1.88</v>
@@ -16113,7 +16122,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ72">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR72">
         <v>1.82</v>
@@ -16238,7 +16247,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16444,7 +16453,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16522,10 +16531,10 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ74">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR74">
         <v>1.66</v>
@@ -16731,7 +16740,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ75">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR75">
         <v>1.41</v>
@@ -17140,10 +17149,10 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ77">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR77">
         <v>1.23</v>
@@ -17552,7 +17561,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ79">
         <v>0.77</v>
@@ -18298,7 +18307,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18376,7 +18385,7 @@
         <v>1.4</v>
       </c>
       <c r="AP83">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ83">
         <v>1.69</v>
@@ -18916,7 +18925,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19409,7 +19418,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ88">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR88">
         <v>1.14</v>
@@ -19821,7 +19830,7 @@
         <v>1</v>
       </c>
       <c r="AQ90">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR90">
         <v>1.5</v>
@@ -19946,7 +19955,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20027,7 +20036,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ91">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR91">
         <v>1.77</v>
@@ -20152,7 +20161,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20230,7 +20239,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ92">
         <v>0.92</v>
@@ -20564,7 +20573,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20848,7 +20857,7 @@
         <v>0.8</v>
       </c>
       <c r="AP95">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ95">
         <v>0.85</v>
@@ -20976,7 +20985,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21182,7 +21191,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21466,7 +21475,7 @@
         <v>1.6</v>
       </c>
       <c r="AP98">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ98">
         <v>1.15</v>
@@ -21594,7 +21603,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21800,7 +21809,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -22006,7 +22015,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22499,7 +22508,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ103">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR103">
         <v>1.64</v>
@@ -23036,7 +23045,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23242,7 +23251,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23448,7 +23457,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23526,10 +23535,10 @@
         <v>0.86</v>
       </c>
       <c r="AP108">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ108">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR108">
         <v>1.16</v>
@@ -23860,7 +23869,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24478,7 +24487,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24762,7 +24771,7 @@
         <v>1.33</v>
       </c>
       <c r="AP114">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ114">
         <v>1.15</v>
@@ -25383,7 +25392,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ117">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR117">
         <v>1.85</v>
@@ -25589,7 +25598,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ118">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR118">
         <v>1.51</v>
@@ -25714,7 +25723,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26204,7 +26213,7 @@
         <v>0.57</v>
       </c>
       <c r="AP121">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ121">
         <v>0.46</v>
@@ -26332,7 +26341,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26950,7 +26959,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27362,7 +27371,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27774,7 +27783,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27852,7 +27861,7 @@
         <v>1.13</v>
       </c>
       <c r="AP129">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ129">
         <v>1.23</v>
@@ -27980,7 +27989,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28267,7 +28276,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ131">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR131">
         <v>1.18</v>
@@ -28392,7 +28401,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28804,7 +28813,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28882,10 +28891,10 @@
         <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ134">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR134">
         <v>1.76</v>
@@ -29216,7 +29225,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29297,7 +29306,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ136">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR136">
         <v>1.71</v>
@@ -29500,7 +29509,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ137">
         <v>0.85</v>
@@ -30121,7 +30130,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ140">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR140">
         <v>1.25</v>
@@ -30246,7 +30255,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30658,7 +30667,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30864,7 +30873,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31276,7 +31285,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31354,7 +31363,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ146">
         <v>0.92</v>
@@ -31688,7 +31697,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31766,7 +31775,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ148">
         <v>1.31</v>
@@ -31894,7 +31903,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32512,7 +32521,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32799,7 +32808,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ153">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR153">
         <v>1.62</v>
@@ -32924,7 +32933,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33002,7 +33011,7 @@
         <v>1.44</v>
       </c>
       <c r="AP154">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ154">
         <v>1.77</v>
@@ -33130,7 +33139,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33211,7 +33220,7 @@
         <v>1</v>
       </c>
       <c r="AQ155">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR155">
         <v>1.43</v>
@@ -33336,7 +33345,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33748,7 +33757,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34035,7 +34044,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ159">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34160,7 +34169,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34366,7 +34375,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34778,7 +34787,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34856,7 +34865,7 @@
         <v>0.5</v>
       </c>
       <c r="AP163">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ163">
         <v>0.64</v>
@@ -35065,7 +35074,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ164">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR164">
         <v>1.79</v>
@@ -35190,7 +35199,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35396,7 +35405,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35680,7 +35689,7 @@
         <v>1.3</v>
       </c>
       <c r="AP167">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ167">
         <v>1.23</v>
@@ -35808,7 +35817,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36301,7 +36310,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ170">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR170">
         <v>1.54</v>
@@ -36426,7 +36435,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36504,7 +36513,7 @@
         <v>0.6</v>
       </c>
       <c r="AP171">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ171">
         <v>0.77</v>
@@ -36632,7 +36641,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36838,7 +36847,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36919,7 +36928,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ173">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR173">
         <v>2.04</v>
@@ -37044,7 +37053,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37331,7 +37340,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ175">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR175">
         <v>1.74</v>
@@ -37456,7 +37465,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37662,7 +37671,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37740,7 +37749,7 @@
         <v>0.7</v>
       </c>
       <c r="AP177">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ177">
         <v>0.85</v>
@@ -38074,7 +38083,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38152,7 +38161,7 @@
         <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ179">
         <v>1.77</v>
@@ -38280,7 +38289,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38898,7 +38907,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39104,7 +39113,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39928,7 +39937,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40215,7 +40224,7 @@
         <v>2.85</v>
       </c>
       <c r="AQ189">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR189">
         <v>1.74</v>
@@ -40418,7 +40427,7 @@
         <v>1.91</v>
       </c>
       <c r="AP190">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ190">
         <v>1.69</v>
@@ -40546,7 +40555,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40958,7 +40967,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41164,7 +41173,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41451,7 +41460,7 @@
         <v>2.31</v>
       </c>
       <c r="AQ195">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="AR195">
         <v>2.09</v>
@@ -41654,7 +41663,7 @@
         <v>0.67</v>
       </c>
       <c r="AP196">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AQ196">
         <v>0.64</v>
@@ -42194,7 +42203,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42400,7 +42409,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42478,7 +42487,7 @@
         <v>0.92</v>
       </c>
       <c r="AP200">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="AQ200">
         <v>0.85</v>
@@ -42687,7 +42696,7 @@
         <v>1</v>
       </c>
       <c r="AQ201">
-        <v>0.92</v>
+        <v>1.07</v>
       </c>
       <c r="AR201">
         <v>1.28</v>
@@ -42812,7 +42821,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -43018,7 +43027,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43224,7 +43233,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43302,7 +43311,7 @@
         <v>0.5</v>
       </c>
       <c r="AP204">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AQ204">
         <v>0.46</v>
@@ -43430,7 +43439,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43636,7 +43645,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -43717,7 +43726,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ206">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="AR206">
         <v>1.54</v>
@@ -44617,6 +44626,624 @@
       </c>
       <c r="BP210">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="211" spans="1:68">
+      <c r="A211" s="1">
+        <v>210</v>
+      </c>
+      <c r="B211">
+        <v>7453634</v>
+      </c>
+      <c r="C211" t="s">
+        <v>68</v>
+      </c>
+      <c r="D211" t="s">
+        <v>69</v>
+      </c>
+      <c r="E211" s="2">
+        <v>45710.5</v>
+      </c>
+      <c r="F211">
+        <v>27</v>
+      </c>
+      <c r="G211" t="s">
+        <v>71</v>
+      </c>
+      <c r="H211" t="s">
+        <v>72</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+      <c r="M211">
+        <v>0</v>
+      </c>
+      <c r="N211">
+        <v>0</v>
+      </c>
+      <c r="O211" t="s">
+        <v>87</v>
+      </c>
+      <c r="P211" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q211">
+        <v>2.5</v>
+      </c>
+      <c r="R211">
+        <v>2.15</v>
+      </c>
+      <c r="S211">
+        <v>4.75</v>
+      </c>
+      <c r="T211">
+        <v>1.42</v>
+      </c>
+      <c r="U211">
+        <v>2.85</v>
+      </c>
+      <c r="V211">
+        <v>3</v>
+      </c>
+      <c r="W211">
+        <v>1.38</v>
+      </c>
+      <c r="X211">
+        <v>7.5</v>
+      </c>
+      <c r="Y211">
+        <v>1.08</v>
+      </c>
+      <c r="Z211">
+        <v>1.83</v>
+      </c>
+      <c r="AA211">
+        <v>3.65</v>
+      </c>
+      <c r="AB211">
+        <v>4</v>
+      </c>
+      <c r="AC211">
+        <v>1.04</v>
+      </c>
+      <c r="AD211">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AE211">
+        <v>1.31</v>
+      </c>
+      <c r="AF211">
+        <v>3.32</v>
+      </c>
+      <c r="AG211">
+        <v>1.79</v>
+      </c>
+      <c r="AH211">
+        <v>1.95</v>
+      </c>
+      <c r="AI211">
+        <v>1.88</v>
+      </c>
+      <c r="AJ211">
+        <v>1.92</v>
+      </c>
+      <c r="AK211">
+        <v>1.22</v>
+      </c>
+      <c r="AL211">
+        <v>1.25</v>
+      </c>
+      <c r="AM211">
+        <v>2</v>
+      </c>
+      <c r="AN211">
+        <v>1.23</v>
+      </c>
+      <c r="AO211">
+        <v>0.08</v>
+      </c>
+      <c r="AP211">
+        <v>1.21</v>
+      </c>
+      <c r="AQ211">
+        <v>0.14</v>
+      </c>
+      <c r="AR211">
+        <v>1.1</v>
+      </c>
+      <c r="AS211">
+        <v>1.09</v>
+      </c>
+      <c r="AT211">
+        <v>2.19</v>
+      </c>
+      <c r="AU211">
+        <v>3</v>
+      </c>
+      <c r="AV211">
+        <v>3</v>
+      </c>
+      <c r="AW211">
+        <v>7</v>
+      </c>
+      <c r="AX211">
+        <v>14</v>
+      </c>
+      <c r="AY211">
+        <v>10</v>
+      </c>
+      <c r="AZ211">
+        <v>17</v>
+      </c>
+      <c r="BA211">
+        <v>1</v>
+      </c>
+      <c r="BB211">
+        <v>9</v>
+      </c>
+      <c r="BC211">
+        <v>10</v>
+      </c>
+      <c r="BD211">
+        <v>1.47</v>
+      </c>
+      <c r="BE211">
+        <v>7</v>
+      </c>
+      <c r="BF211">
+        <v>2.95</v>
+      </c>
+      <c r="BG211">
+        <v>1.3</v>
+      </c>
+      <c r="BH211">
+        <v>3.05</v>
+      </c>
+      <c r="BI211">
+        <v>1.54</v>
+      </c>
+      <c r="BJ211">
+        <v>2.3</v>
+      </c>
+      <c r="BK211">
+        <v>1.89</v>
+      </c>
+      <c r="BL211">
+        <v>1.8</v>
+      </c>
+      <c r="BM211">
+        <v>2.38</v>
+      </c>
+      <c r="BN211">
+        <v>1.5</v>
+      </c>
+      <c r="BO211">
+        <v>3.05</v>
+      </c>
+      <c r="BP211">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="212" spans="1:68">
+      <c r="A212" s="1">
+        <v>211</v>
+      </c>
+      <c r="B212">
+        <v>7453633</v>
+      </c>
+      <c r="C212" t="s">
+        <v>68</v>
+      </c>
+      <c r="D212" t="s">
+        <v>69</v>
+      </c>
+      <c r="E212" s="2">
+        <v>45710.59375</v>
+      </c>
+      <c r="F212">
+        <v>27</v>
+      </c>
+      <c r="G212" t="s">
+        <v>77</v>
+      </c>
+      <c r="H212" t="s">
+        <v>76</v>
+      </c>
+      <c r="I212">
+        <v>1</v>
+      </c>
+      <c r="J212">
+        <v>0</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212">
+        <v>1</v>
+      </c>
+      <c r="M212">
+        <v>3</v>
+      </c>
+      <c r="N212">
+        <v>4</v>
+      </c>
+      <c r="O212" t="s">
+        <v>227</v>
+      </c>
+      <c r="P212" t="s">
+        <v>328</v>
+      </c>
+      <c r="Q212">
+        <v>2.75</v>
+      </c>
+      <c r="R212">
+        <v>2.3</v>
+      </c>
+      <c r="S212">
+        <v>3.5</v>
+      </c>
+      <c r="T212">
+        <v>1.33</v>
+      </c>
+      <c r="U212">
+        <v>3.25</v>
+      </c>
+      <c r="V212">
+        <v>2.5</v>
+      </c>
+      <c r="W212">
+        <v>1.5</v>
+      </c>
+      <c r="X212">
+        <v>6.5</v>
+      </c>
+      <c r="Y212">
+        <v>1.11</v>
+      </c>
+      <c r="Z212">
+        <v>2.32</v>
+      </c>
+      <c r="AA212">
+        <v>3.53</v>
+      </c>
+      <c r="AB212">
+        <v>2.81</v>
+      </c>
+      <c r="AC212">
+        <v>1.02</v>
+      </c>
+      <c r="AD212">
+        <v>17</v>
+      </c>
+      <c r="AE212">
+        <v>1.18</v>
+      </c>
+      <c r="AF212">
+        <v>4.65</v>
+      </c>
+      <c r="AG212">
+        <v>1.67</v>
+      </c>
+      <c r="AH212">
+        <v>2.1</v>
+      </c>
+      <c r="AI212">
+        <v>1.57</v>
+      </c>
+      <c r="AJ212">
+        <v>2.25</v>
+      </c>
+      <c r="AK212">
+        <v>1.35</v>
+      </c>
+      <c r="AL212">
+        <v>1.26</v>
+      </c>
+      <c r="AM212">
+        <v>1.68</v>
+      </c>
+      <c r="AN212">
+        <v>1.46</v>
+      </c>
+      <c r="AO212">
+        <v>0.92</v>
+      </c>
+      <c r="AP212">
+        <v>1.36</v>
+      </c>
+      <c r="AQ212">
+        <v>1.07</v>
+      </c>
+      <c r="AR212">
+        <v>1.93</v>
+      </c>
+      <c r="AS212">
+        <v>1.4</v>
+      </c>
+      <c r="AT212">
+        <v>3.33</v>
+      </c>
+      <c r="AU212">
+        <v>5</v>
+      </c>
+      <c r="AV212">
+        <v>5</v>
+      </c>
+      <c r="AW212">
+        <v>4</v>
+      </c>
+      <c r="AX212">
+        <v>9</v>
+      </c>
+      <c r="AY212">
+        <v>12</v>
+      </c>
+      <c r="AZ212">
+        <v>17</v>
+      </c>
+      <c r="BA212">
+        <v>2</v>
+      </c>
+      <c r="BB212">
+        <v>9</v>
+      </c>
+      <c r="BC212">
+        <v>11</v>
+      </c>
+      <c r="BD212">
+        <v>1.66</v>
+      </c>
+      <c r="BE212">
+        <v>6.75</v>
+      </c>
+      <c r="BF212">
+        <v>2.45</v>
+      </c>
+      <c r="BG212">
+        <v>1.21</v>
+      </c>
+      <c r="BH212">
+        <v>3.8</v>
+      </c>
+      <c r="BI212">
+        <v>1.38</v>
+      </c>
+      <c r="BJ212">
+        <v>2.8</v>
+      </c>
+      <c r="BK212">
+        <v>1.61</v>
+      </c>
+      <c r="BL212">
+        <v>2.15</v>
+      </c>
+      <c r="BM212">
+        <v>1.98</v>
+      </c>
+      <c r="BN212">
+        <v>1.74</v>
+      </c>
+      <c r="BO212">
+        <v>2.48</v>
+      </c>
+      <c r="BP212">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="213" spans="1:68">
+      <c r="A213" s="1">
+        <v>212</v>
+      </c>
+      <c r="B213">
+        <v>7453630</v>
+      </c>
+      <c r="C213" t="s">
+        <v>68</v>
+      </c>
+      <c r="D213" t="s">
+        <v>69</v>
+      </c>
+      <c r="E213" s="2">
+        <v>45710.69791666666</v>
+      </c>
+      <c r="F213">
+        <v>27</v>
+      </c>
+      <c r="G213" t="s">
+        <v>82</v>
+      </c>
+      <c r="H213" t="s">
+        <v>80</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>2</v>
+      </c>
+      <c r="M213">
+        <v>2</v>
+      </c>
+      <c r="N213">
+        <v>4</v>
+      </c>
+      <c r="O213" t="s">
+        <v>239</v>
+      </c>
+      <c r="P213" t="s">
+        <v>329</v>
+      </c>
+      <c r="Q213">
+        <v>2.5</v>
+      </c>
+      <c r="R213">
+        <v>2.15</v>
+      </c>
+      <c r="S213">
+        <v>3.9</v>
+      </c>
+      <c r="T213">
+        <v>1.36</v>
+      </c>
+      <c r="U213">
+        <v>2.9</v>
+      </c>
+      <c r="V213">
+        <v>2.6</v>
+      </c>
+      <c r="W213">
+        <v>1.43</v>
+      </c>
+      <c r="X213">
+        <v>6.5</v>
+      </c>
+      <c r="Y213">
+        <v>1.1</v>
+      </c>
+      <c r="Z213">
+        <v>1.93</v>
+      </c>
+      <c r="AA213">
+        <v>3.53</v>
+      </c>
+      <c r="AB213">
+        <v>3.75</v>
+      </c>
+      <c r="AC213">
+        <v>1.04</v>
+      </c>
+      <c r="AD213">
+        <v>13</v>
+      </c>
+      <c r="AE213">
+        <v>1.26</v>
+      </c>
+      <c r="AF213">
+        <v>3.67</v>
+      </c>
+      <c r="AG213">
+        <v>1.82</v>
+      </c>
+      <c r="AH213">
+        <v>1.92</v>
+      </c>
+      <c r="AI213">
+        <v>1.72</v>
+      </c>
+      <c r="AJ213">
+        <v>1.98</v>
+      </c>
+      <c r="AK213">
+        <v>1.27</v>
+      </c>
+      <c r="AL213">
+        <v>1.28</v>
+      </c>
+      <c r="AM213">
+        <v>1.82</v>
+      </c>
+      <c r="AN213">
+        <v>2</v>
+      </c>
+      <c r="AO213">
+        <v>0.62</v>
+      </c>
+      <c r="AP213">
+        <v>1.93</v>
+      </c>
+      <c r="AQ213">
+        <v>0.64</v>
+      </c>
+      <c r="AR213">
+        <v>1.7</v>
+      </c>
+      <c r="AS213">
+        <v>1.18</v>
+      </c>
+      <c r="AT213">
+        <v>2.88</v>
+      </c>
+      <c r="AU213">
+        <v>10</v>
+      </c>
+      <c r="AV213">
+        <v>7</v>
+      </c>
+      <c r="AW213">
+        <v>12</v>
+      </c>
+      <c r="AX213">
+        <v>3</v>
+      </c>
+      <c r="AY213">
+        <v>23</v>
+      </c>
+      <c r="AZ213">
+        <v>11</v>
+      </c>
+      <c r="BA213">
+        <v>7</v>
+      </c>
+      <c r="BB213">
+        <v>4</v>
+      </c>
+      <c r="BC213">
+        <v>11</v>
+      </c>
+      <c r="BD213">
+        <v>1.48</v>
+      </c>
+      <c r="BE213">
+        <v>7</v>
+      </c>
+      <c r="BF213">
+        <v>2.9</v>
+      </c>
+      <c r="BG213">
+        <v>1.21</v>
+      </c>
+      <c r="BH213">
+        <v>3.9</v>
+      </c>
+      <c r="BI213">
+        <v>1.36</v>
+      </c>
+      <c r="BJ213">
+        <v>2.8</v>
+      </c>
+      <c r="BK213">
+        <v>1.58</v>
+      </c>
+      <c r="BL213">
+        <v>2.18</v>
+      </c>
+      <c r="BM213">
+        <v>1.93</v>
+      </c>
+      <c r="BN213">
+        <v>1.77</v>
+      </c>
+      <c r="BO213">
+        <v>2.4</v>
+      </c>
+      <c r="BP213">
+        <v>1.49</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1340" uniqueCount="330">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="332">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1005,6 +1005,12 @@
   <si>
     <t>['56', '90+6']</t>
   </si>
+  <si>
+    <t>['67', '85']</t>
+  </si>
+  <si>
+    <t>['33', '70']</t>
+  </si>
 </sst>
 </file>
 
@@ -1365,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1699,7 +1705,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ2">
         <v>0.92</v>
@@ -1908,7 +1914,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ3">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2317,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ5">
         <v>0.64</v>
@@ -2523,10 +2529,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ6">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2732,7 +2738,7 @@
         <v>1</v>
       </c>
       <c r="AQ7">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3144,7 +3150,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ9">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -5410,7 +5416,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ20">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR20">
         <v>1.27</v>
@@ -5613,7 +5619,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ21">
         <v>0.64</v>
@@ -5819,7 +5825,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ22">
         <v>1.69</v>
@@ -6234,7 +6240,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ24">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR24">
         <v>1.65</v>
@@ -7467,7 +7473,7 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ30">
         <v>1.31</v>
@@ -7676,7 +7682,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ31">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR31">
         <v>1.23</v>
@@ -7882,7 +7888,7 @@
         <v>1</v>
       </c>
       <c r="AQ32">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -8912,7 +8918,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ37">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR37">
         <v>1.03</v>
@@ -9527,7 +9533,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ40">
         <v>0.85</v>
@@ -10148,7 +10154,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ43">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -10351,10 +10357,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ44">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR44">
         <v>1.89</v>
@@ -11178,7 +11184,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ48">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR48">
         <v>1.15</v>
@@ -11793,7 +11799,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ51">
         <v>0.85</v>
@@ -12002,7 +12008,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ52">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR52">
         <v>2.07</v>
@@ -12823,7 +12829,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ56">
         <v>1.77</v>
@@ -13032,7 +13038,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ57">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR57">
         <v>1.08</v>
@@ -13647,7 +13653,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ60">
         <v>1.07</v>
@@ -13853,10 +13859,10 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ61">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR61">
         <v>2.01</v>
@@ -14062,7 +14068,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ62">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR62">
         <v>1.5</v>
@@ -14265,7 +14271,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ63">
         <v>1.15</v>
@@ -14680,7 +14686,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ65">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR65">
         <v>1.79</v>
@@ -15089,7 +15095,7 @@
         <v>1.25</v>
       </c>
       <c r="AP67">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ67">
         <v>0.92</v>
@@ -17355,10 +17361,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ78">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR78">
         <v>1.59</v>
@@ -17564,7 +17570,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ79">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR79">
         <v>1.88</v>
@@ -17767,10 +17773,10 @@
         <v>0.6</v>
       </c>
       <c r="AP80">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ80">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR80">
         <v>2.17</v>
@@ -17976,7 +17982,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ81">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR81">
         <v>0.89</v>
@@ -18800,7 +18806,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ85">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR85">
         <v>1.67</v>
@@ -19003,7 +19009,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ86">
         <v>0.64</v>
@@ -20651,7 +20657,7 @@
         <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ94">
         <v>1.62</v>
@@ -20860,7 +20866,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ95">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR95">
         <v>1.79</v>
@@ -21272,7 +21278,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ97">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -22096,7 +22102,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ101">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR101">
         <v>1.52</v>
@@ -22299,7 +22305,7 @@
         <v>1.6</v>
       </c>
       <c r="AP102">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ102">
         <v>1.31</v>
@@ -22711,7 +22717,7 @@
         <v>0.67</v>
       </c>
       <c r="AP104">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ104">
         <v>0.46</v>
@@ -22920,7 +22926,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR105">
         <v>0.83</v>
@@ -24156,7 +24162,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ111">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR111">
         <v>1.55</v>
@@ -24977,7 +24983,7 @@
         <v>0.71</v>
       </c>
       <c r="AP115">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ115">
         <v>0.64</v>
@@ -25186,7 +25192,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ116">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR116">
         <v>1.18</v>
@@ -25389,7 +25395,7 @@
         <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ117">
         <v>1.07</v>
@@ -25804,7 +25810,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ119">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -26007,10 +26013,10 @@
         <v>1.29</v>
       </c>
       <c r="AP120">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ120">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR120">
         <v>1.64</v>
@@ -26625,7 +26631,7 @@
         <v>1.29</v>
       </c>
       <c r="AP123">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ123">
         <v>1.15</v>
@@ -26834,7 +26840,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ124">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR124">
         <v>1.8</v>
@@ -27452,7 +27458,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR127">
         <v>0.92</v>
@@ -27864,7 +27870,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ129">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR129">
         <v>1.82</v>
@@ -28067,7 +28073,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ130">
         <v>0.46</v>
@@ -29100,7 +29106,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ135">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR135">
         <v>1.6</v>
@@ -29303,7 +29309,7 @@
         <v>0.13</v>
       </c>
       <c r="AP136">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ136">
         <v>0.14</v>
@@ -29924,7 +29930,7 @@
         <v>1</v>
       </c>
       <c r="AQ139">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR139">
         <v>1.07</v>
@@ -30539,7 +30545,7 @@
         <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ142">
         <v>1.77</v>
@@ -31160,7 +31166,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ145">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR145">
         <v>1.64</v>
@@ -32187,7 +32193,7 @@
         <v>1.67</v>
       </c>
       <c r="AP150">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ150">
         <v>1.62</v>
@@ -32396,7 +32402,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ151">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR151">
         <v>1.23</v>
@@ -33423,7 +33429,7 @@
         <v>0.78</v>
       </c>
       <c r="AP156">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ156">
         <v>0.85</v>
@@ -33632,7 +33638,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ157">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR157">
         <v>1.54</v>
@@ -33838,7 +33844,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ158">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR158">
         <v>1.6</v>
@@ -34250,7 +34256,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ160">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR160">
         <v>1.47</v>
@@ -34453,7 +34459,7 @@
         <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ161">
         <v>1.15</v>
@@ -35071,7 +35077,7 @@
         <v>0.8</v>
       </c>
       <c r="AP164">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ164">
         <v>0.64</v>
@@ -35280,7 +35286,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ165">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR165">
         <v>1.75</v>
@@ -35692,7 +35698,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ167">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR167">
         <v>1.07</v>
@@ -35895,7 +35901,7 @@
         <v>1.8</v>
       </c>
       <c r="AP168">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ168">
         <v>1.69</v>
@@ -36516,7 +36522,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ171">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR171">
         <v>1.08</v>
@@ -36925,7 +36931,7 @@
         <v>0.1</v>
       </c>
       <c r="AP173">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ173">
         <v>0.14</v>
@@ -37546,7 +37552,7 @@
         <v>1.23</v>
       </c>
       <c r="AQ176">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR176">
         <v>1.54</v>
@@ -38370,7 +38376,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ180">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR180">
         <v>1.69</v>
@@ -38573,7 +38579,7 @@
         <v>0.45</v>
       </c>
       <c r="AP181">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ181">
         <v>0.46</v>
@@ -38988,7 +38994,7 @@
         <v>1</v>
       </c>
       <c r="AQ183">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR183">
         <v>1.3</v>
@@ -39191,7 +39197,7 @@
         <v>0.9</v>
       </c>
       <c r="AP184">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ184">
         <v>0.92</v>
@@ -39400,7 +39406,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ185">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR185">
         <v>1.29</v>
@@ -40018,7 +40024,7 @@
         <v>1.54</v>
       </c>
       <c r="AQ188">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR188">
         <v>1.65</v>
@@ -40221,7 +40227,7 @@
         <v>0.09</v>
       </c>
       <c r="AP189">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ189">
         <v>0.14</v>
@@ -41254,7 +41260,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ194">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AR194">
         <v>1.52</v>
@@ -41457,7 +41463,7 @@
         <v>0.67</v>
       </c>
       <c r="AP195">
-        <v>2.31</v>
+        <v>2.14</v>
       </c>
       <c r="AQ195">
         <v>0.64</v>
@@ -41869,10 +41875,10 @@
         <v>0.83</v>
       </c>
       <c r="AP197">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AQ197">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AR197">
         <v>1.75</v>
@@ -42075,7 +42081,7 @@
         <v>1.42</v>
       </c>
       <c r="AP198">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ198">
         <v>1.31</v>
@@ -42284,7 +42290,7 @@
         <v>1</v>
       </c>
       <c r="AQ199">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="AR199">
         <v>1.34</v>
@@ -42490,7 +42496,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ200">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="AR200">
         <v>1.89</v>
@@ -45244,6 +45250,830 @@
       </c>
       <c r="BP213">
         <v>1.49</v>
+      </c>
+    </row>
+    <row r="214" spans="1:68">
+      <c r="A214" s="1">
+        <v>213</v>
+      </c>
+      <c r="B214">
+        <v>7453627</v>
+      </c>
+      <c r="C214" t="s">
+        <v>68</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214" s="2">
+        <v>45711.39583333334</v>
+      </c>
+      <c r="F214">
+        <v>27</v>
+      </c>
+      <c r="G214" t="s">
+        <v>70</v>
+      </c>
+      <c r="H214" t="s">
+        <v>84</v>
+      </c>
+      <c r="I214">
+        <v>0</v>
+      </c>
+      <c r="J214">
+        <v>0</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>1</v>
+      </c>
+      <c r="M214">
+        <v>2</v>
+      </c>
+      <c r="N214">
+        <v>3</v>
+      </c>
+      <c r="O214" t="s">
+        <v>86</v>
+      </c>
+      <c r="P214" t="s">
+        <v>330</v>
+      </c>
+      <c r="Q214">
+        <v>1.71</v>
+      </c>
+      <c r="R214">
+        <v>2.55</v>
+      </c>
+      <c r="S214">
+        <v>7</v>
+      </c>
+      <c r="T214">
+        <v>1.27</v>
+      </c>
+      <c r="U214">
+        <v>3.4</v>
+      </c>
+      <c r="V214">
+        <v>2.2</v>
+      </c>
+      <c r="W214">
+        <v>1.57</v>
+      </c>
+      <c r="X214">
+        <v>5</v>
+      </c>
+      <c r="Y214">
+        <v>1.15</v>
+      </c>
+      <c r="Z214">
+        <v>1.28</v>
+      </c>
+      <c r="AA214">
+        <v>5.7</v>
+      </c>
+      <c r="AB214">
+        <v>8.9</v>
+      </c>
+      <c r="AC214">
+        <v>1.01</v>
+      </c>
+      <c r="AD214">
+        <v>21</v>
+      </c>
+      <c r="AE214">
+        <v>1.16</v>
+      </c>
+      <c r="AF214">
+        <v>4.87</v>
+      </c>
+      <c r="AG214">
+        <v>1.64</v>
+      </c>
+      <c r="AH214">
+        <v>2.26</v>
+      </c>
+      <c r="AI214">
+        <v>1.93</v>
+      </c>
+      <c r="AJ214">
+        <v>1.75</v>
+      </c>
+      <c r="AK214">
+        <v>1.06</v>
+      </c>
+      <c r="AL214">
+        <v>1.14</v>
+      </c>
+      <c r="AM214">
+        <v>3.4</v>
+      </c>
+      <c r="AN214">
+        <v>2.31</v>
+      </c>
+      <c r="AO214">
+        <v>0.85</v>
+      </c>
+      <c r="AP214">
+        <v>2.14</v>
+      </c>
+      <c r="AQ214">
+        <v>1</v>
+      </c>
+      <c r="AR214">
+        <v>2.08</v>
+      </c>
+      <c r="AS214">
+        <v>1.05</v>
+      </c>
+      <c r="AT214">
+        <v>3.13</v>
+      </c>
+      <c r="AU214">
+        <v>7</v>
+      </c>
+      <c r="AV214">
+        <v>4</v>
+      </c>
+      <c r="AW214">
+        <v>7</v>
+      </c>
+      <c r="AX214">
+        <v>9</v>
+      </c>
+      <c r="AY214">
+        <v>16</v>
+      </c>
+      <c r="AZ214">
+        <v>16</v>
+      </c>
+      <c r="BA214">
+        <v>7</v>
+      </c>
+      <c r="BB214">
+        <v>8</v>
+      </c>
+      <c r="BC214">
+        <v>15</v>
+      </c>
+      <c r="BD214">
+        <v>1.18</v>
+      </c>
+      <c r="BE214">
+        <v>9</v>
+      </c>
+      <c r="BF214">
+        <v>5.1</v>
+      </c>
+      <c r="BG214">
+        <v>1.28</v>
+      </c>
+      <c r="BH214">
+        <v>3.3</v>
+      </c>
+      <c r="BI214">
+        <v>1.48</v>
+      </c>
+      <c r="BJ214">
+        <v>2.48</v>
+      </c>
+      <c r="BK214">
+        <v>1.75</v>
+      </c>
+      <c r="BL214">
+        <v>1.95</v>
+      </c>
+      <c r="BM214">
+        <v>2.15</v>
+      </c>
+      <c r="BN214">
+        <v>1.61</v>
+      </c>
+      <c r="BO214">
+        <v>2.7</v>
+      </c>
+      <c r="BP214">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="215" spans="1:68">
+      <c r="A215" s="1">
+        <v>214</v>
+      </c>
+      <c r="B215">
+        <v>7453629</v>
+      </c>
+      <c r="C215" t="s">
+        <v>68</v>
+      </c>
+      <c r="D215" t="s">
+        <v>69</v>
+      </c>
+      <c r="E215" s="2">
+        <v>45711.5</v>
+      </c>
+      <c r="F215">
+        <v>27</v>
+      </c>
+      <c r="G215" t="s">
+        <v>74</v>
+      </c>
+      <c r="H215" t="s">
+        <v>85</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>0</v>
+      </c>
+      <c r="K215">
+        <v>0</v>
+      </c>
+      <c r="L215">
+        <v>0</v>
+      </c>
+      <c r="M215">
+        <v>0</v>
+      </c>
+      <c r="N215">
+        <v>0</v>
+      </c>
+      <c r="O215" t="s">
+        <v>87</v>
+      </c>
+      <c r="P215" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q215">
+        <v>2.1</v>
+      </c>
+      <c r="R215">
+        <v>2.3</v>
+      </c>
+      <c r="S215">
+        <v>4.6</v>
+      </c>
+      <c r="T215">
+        <v>1.29</v>
+      </c>
+      <c r="U215">
+        <v>3.3</v>
+      </c>
+      <c r="V215">
+        <v>2.25</v>
+      </c>
+      <c r="W215">
+        <v>1.55</v>
+      </c>
+      <c r="X215">
+        <v>5.25</v>
+      </c>
+      <c r="Y215">
+        <v>1.14</v>
+      </c>
+      <c r="Z215">
+        <v>1.63</v>
+      </c>
+      <c r="AA215">
+        <v>3.84</v>
+      </c>
+      <c r="AB215">
+        <v>5.1</v>
+      </c>
+      <c r="AC215">
+        <v>1.04</v>
+      </c>
+      <c r="AD215">
+        <v>10</v>
+      </c>
+      <c r="AE215">
+        <v>1.2</v>
+      </c>
+      <c r="AF215">
+        <v>4.33</v>
+      </c>
+      <c r="AG215">
+        <v>1.57</v>
+      </c>
+      <c r="AH215">
+        <v>2.25</v>
+      </c>
+      <c r="AI215">
+        <v>1.62</v>
+      </c>
+      <c r="AJ215">
+        <v>2.15</v>
+      </c>
+      <c r="AK215">
+        <v>1.18</v>
+      </c>
+      <c r="AL215">
+        <v>1.23</v>
+      </c>
+      <c r="AM215">
+        <v>2.2</v>
+      </c>
+      <c r="AN215">
+        <v>2.85</v>
+      </c>
+      <c r="AO215">
+        <v>1.23</v>
+      </c>
+      <c r="AP215">
+        <v>2.71</v>
+      </c>
+      <c r="AQ215">
+        <v>1.21</v>
+      </c>
+      <c r="AR215">
+        <v>1.77</v>
+      </c>
+      <c r="AS215">
+        <v>1.3</v>
+      </c>
+      <c r="AT215">
+        <v>3.07</v>
+      </c>
+      <c r="AU215">
+        <v>3</v>
+      </c>
+      <c r="AV215">
+        <v>4</v>
+      </c>
+      <c r="AW215">
+        <v>16</v>
+      </c>
+      <c r="AX215">
+        <v>8</v>
+      </c>
+      <c r="AY215">
+        <v>20</v>
+      </c>
+      <c r="AZ215">
+        <v>15</v>
+      </c>
+      <c r="BA215">
+        <v>7</v>
+      </c>
+      <c r="BB215">
+        <v>5</v>
+      </c>
+      <c r="BC215">
+        <v>12</v>
+      </c>
+      <c r="BD215">
+        <v>1.44</v>
+      </c>
+      <c r="BE215">
+        <v>7</v>
+      </c>
+      <c r="BF215">
+        <v>3.15</v>
+      </c>
+      <c r="BG215">
+        <v>1.29</v>
+      </c>
+      <c r="BH215">
+        <v>3.2</v>
+      </c>
+      <c r="BI215">
+        <v>1.49</v>
+      </c>
+      <c r="BJ215">
+        <v>2.4</v>
+      </c>
+      <c r="BK215">
+        <v>1.8</v>
+      </c>
+      <c r="BL215">
+        <v>1.89</v>
+      </c>
+      <c r="BM215">
+        <v>2.23</v>
+      </c>
+      <c r="BN215">
+        <v>1.56</v>
+      </c>
+      <c r="BO215">
+        <v>2.9</v>
+      </c>
+      <c r="BP215">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="216" spans="1:68">
+      <c r="A216" s="1">
+        <v>215</v>
+      </c>
+      <c r="B216">
+        <v>7453628</v>
+      </c>
+      <c r="C216" t="s">
+        <v>68</v>
+      </c>
+      <c r="D216" t="s">
+        <v>69</v>
+      </c>
+      <c r="E216" s="2">
+        <v>45711.60416666666</v>
+      </c>
+      <c r="F216">
+        <v>27</v>
+      </c>
+      <c r="G216" t="s">
+        <v>73</v>
+      </c>
+      <c r="H216" t="s">
+        <v>78</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>1</v>
+      </c>
+      <c r="K216">
+        <v>1</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+      <c r="M216">
+        <v>2</v>
+      </c>
+      <c r="N216">
+        <v>2</v>
+      </c>
+      <c r="O216" t="s">
+        <v>87</v>
+      </c>
+      <c r="P216" t="s">
+        <v>331</v>
+      </c>
+      <c r="Q216">
+        <v>3.25</v>
+      </c>
+      <c r="R216">
+        <v>2.2</v>
+      </c>
+      <c r="S216">
+        <v>3.2</v>
+      </c>
+      <c r="T216">
+        <v>1.4</v>
+      </c>
+      <c r="U216">
+        <v>2.75</v>
+      </c>
+      <c r="V216">
+        <v>2.75</v>
+      </c>
+      <c r="W216">
+        <v>1.4</v>
+      </c>
+      <c r="X216">
+        <v>8</v>
+      </c>
+      <c r="Y216">
+        <v>1.08</v>
+      </c>
+      <c r="Z216">
+        <v>2.49</v>
+      </c>
+      <c r="AA216">
+        <v>3.62</v>
+      </c>
+      <c r="AB216">
+        <v>2.55</v>
+      </c>
+      <c r="AC216">
+        <v>1.04</v>
+      </c>
+      <c r="AD216">
+        <v>13</v>
+      </c>
+      <c r="AE216">
+        <v>1.28</v>
+      </c>
+      <c r="AF216">
+        <v>3.52</v>
+      </c>
+      <c r="AG216">
+        <v>1.79</v>
+      </c>
+      <c r="AH216">
+        <v>1.95</v>
+      </c>
+      <c r="AI216">
+        <v>1.7</v>
+      </c>
+      <c r="AJ216">
+        <v>2.05</v>
+      </c>
+      <c r="AK216">
+        <v>1.5</v>
+      </c>
+      <c r="AL216">
+        <v>1.3</v>
+      </c>
+      <c r="AM216">
+        <v>1.46</v>
+      </c>
+      <c r="AN216">
+        <v>1.85</v>
+      </c>
+      <c r="AO216">
+        <v>1.46</v>
+      </c>
+      <c r="AP216">
+        <v>1.71</v>
+      </c>
+      <c r="AQ216">
+        <v>1.57</v>
+      </c>
+      <c r="AR216">
+        <v>1.66</v>
+      </c>
+      <c r="AS216">
+        <v>1.46</v>
+      </c>
+      <c r="AT216">
+        <v>3.12</v>
+      </c>
+      <c r="AU216">
+        <v>6</v>
+      </c>
+      <c r="AV216">
+        <v>5</v>
+      </c>
+      <c r="AW216">
+        <v>6</v>
+      </c>
+      <c r="AX216">
+        <v>1</v>
+      </c>
+      <c r="AY216">
+        <v>14</v>
+      </c>
+      <c r="AZ216">
+        <v>7</v>
+      </c>
+      <c r="BA216">
+        <v>7</v>
+      </c>
+      <c r="BB216">
+        <v>2</v>
+      </c>
+      <c r="BC216">
+        <v>9</v>
+      </c>
+      <c r="BD216">
+        <v>1.94</v>
+      </c>
+      <c r="BE216">
+        <v>6.5</v>
+      </c>
+      <c r="BF216">
+        <v>2.05</v>
+      </c>
+      <c r="BG216">
+        <v>1.28</v>
+      </c>
+      <c r="BH216">
+        <v>3.3</v>
+      </c>
+      <c r="BI216">
+        <v>1.49</v>
+      </c>
+      <c r="BJ216">
+        <v>2.4</v>
+      </c>
+      <c r="BK216">
+        <v>1.79</v>
+      </c>
+      <c r="BL216">
+        <v>1.91</v>
+      </c>
+      <c r="BM216">
+        <v>2.23</v>
+      </c>
+      <c r="BN216">
+        <v>1.56</v>
+      </c>
+      <c r="BO216">
+        <v>2.88</v>
+      </c>
+      <c r="BP216">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="217" spans="1:68">
+      <c r="A217" s="1">
+        <v>216</v>
+      </c>
+      <c r="B217">
+        <v>7453631</v>
+      </c>
+      <c r="C217" t="s">
+        <v>68</v>
+      </c>
+      <c r="D217" t="s">
+        <v>69</v>
+      </c>
+      <c r="E217" s="2">
+        <v>45711.63541666666</v>
+      </c>
+      <c r="F217">
+        <v>27</v>
+      </c>
+      <c r="G217" t="s">
+        <v>75</v>
+      </c>
+      <c r="H217" t="s">
+        <v>83</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>1</v>
+      </c>
+      <c r="L217">
+        <v>1</v>
+      </c>
+      <c r="M217">
+        <v>1</v>
+      </c>
+      <c r="N217">
+        <v>2</v>
+      </c>
+      <c r="O217" t="s">
+        <v>144</v>
+      </c>
+      <c r="P217" t="s">
+        <v>269</v>
+      </c>
+      <c r="Q217">
+        <v>3.75</v>
+      </c>
+      <c r="R217">
+        <v>2.1</v>
+      </c>
+      <c r="S217">
+        <v>3</v>
+      </c>
+      <c r="T217">
+        <v>1.44</v>
+      </c>
+      <c r="U217">
+        <v>2.63</v>
+      </c>
+      <c r="V217">
+        <v>3</v>
+      </c>
+      <c r="W217">
+        <v>1.36</v>
+      </c>
+      <c r="X217">
+        <v>9</v>
+      </c>
+      <c r="Y217">
+        <v>1.07</v>
+      </c>
+      <c r="Z217">
+        <v>3.11</v>
+      </c>
+      <c r="AA217">
+        <v>3.23</v>
+      </c>
+      <c r="AB217">
+        <v>2.28</v>
+      </c>
+      <c r="AC217">
+        <v>1.05</v>
+      </c>
+      <c r="AD217">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AE217">
+        <v>1.32</v>
+      </c>
+      <c r="AF217">
+        <v>3.26</v>
+      </c>
+      <c r="AG217">
+        <v>1.98</v>
+      </c>
+      <c r="AH217">
+        <v>1.77</v>
+      </c>
+      <c r="AI217">
+        <v>1.8</v>
+      </c>
+      <c r="AJ217">
+        <v>1.95</v>
+      </c>
+      <c r="AK217">
+        <v>1.6</v>
+      </c>
+      <c r="AL217">
+        <v>1.32</v>
+      </c>
+      <c r="AM217">
+        <v>1.35</v>
+      </c>
+      <c r="AN217">
+        <v>1</v>
+      </c>
+      <c r="AO217">
+        <v>0.77</v>
+      </c>
+      <c r="AP217">
+        <v>1</v>
+      </c>
+      <c r="AQ217">
+        <v>0.79</v>
+      </c>
+      <c r="AR217">
+        <v>1.34</v>
+      </c>
+      <c r="AS217">
+        <v>1.43</v>
+      </c>
+      <c r="AT217">
+        <v>2.77</v>
+      </c>
+      <c r="AU217">
+        <v>6</v>
+      </c>
+      <c r="AV217">
+        <v>4</v>
+      </c>
+      <c r="AW217">
+        <v>7</v>
+      </c>
+      <c r="AX217">
+        <v>2</v>
+      </c>
+      <c r="AY217">
+        <v>15</v>
+      </c>
+      <c r="AZ217">
+        <v>7</v>
+      </c>
+      <c r="BA217">
+        <v>5</v>
+      </c>
+      <c r="BB217">
+        <v>3</v>
+      </c>
+      <c r="BC217">
+        <v>8</v>
+      </c>
+      <c r="BD217">
+        <v>2.15</v>
+      </c>
+      <c r="BE217">
+        <v>6.5</v>
+      </c>
+      <c r="BF217">
+        <v>1.84</v>
+      </c>
+      <c r="BG217">
+        <v>1.27</v>
+      </c>
+      <c r="BH217">
+        <v>3.3</v>
+      </c>
+      <c r="BI217">
+        <v>1.48</v>
+      </c>
+      <c r="BJ217">
+        <v>2.45</v>
+      </c>
+      <c r="BK217">
+        <v>1.77</v>
+      </c>
+      <c r="BL217">
+        <v>1.93</v>
+      </c>
+      <c r="BM217">
+        <v>2.2</v>
+      </c>
+      <c r="BN217">
+        <v>1.58</v>
+      </c>
+      <c r="BO217">
+        <v>2.8</v>
+      </c>
+      <c r="BP217">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -1705,10 +1705,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ2">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1911,10 +1911,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ3">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2117,10 +2117,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ4">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2323,10 +2323,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ5">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2529,10 +2529,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2735,10 +2735,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ7">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2941,10 +2941,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ8">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3147,10 +3147,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ9">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3347,25 +3347,25 @@
         <v>3.75</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP10">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ10">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AU10">
         <v>5</v>
@@ -3553,25 +3553,25 @@
         <v>1.9</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP11">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ11">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3759,25 +3759,25 @@
         <v>1.35</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ12">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3971,19 +3971,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ13">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR13">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="AS13">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AT13">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AU13">
         <v>4</v>
@@ -4171,25 +4171,25 @@
         <v>1.45</v>
       </c>
       <c r="AN14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ14">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR14">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS14">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AT14">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AU14">
         <v>8</v>
@@ -4383,19 +4383,19 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ15">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR15">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AS15">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AT15">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AU15">
         <v>7</v>
@@ -4583,25 +4583,25 @@
         <v>1.15</v>
       </c>
       <c r="AN16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP16">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ16">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR16">
-        <v>0</v>
+        <v>0.59</v>
       </c>
       <c r="AS16">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AT16">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AU16">
         <v>3</v>
@@ -4789,25 +4789,25 @@
         <v>3.6</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ17">
+        <v>1.19</v>
+      </c>
+      <c r="AR17">
         <v>1.15</v>
       </c>
-      <c r="AR17">
-        <v>0</v>
-      </c>
       <c r="AS17">
-        <v>0</v>
+        <v>0.45</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AU17">
         <v>4</v>
@@ -4995,25 +4995,25 @@
         <v>1.67</v>
       </c>
       <c r="AN18">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO18">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP18">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ18">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR18">
-        <v>0.9399999999999999</v>
+        <v>0.76</v>
       </c>
       <c r="AS18">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
       <c r="AT18">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -5201,25 +5201,25 @@
         <v>1.57</v>
       </c>
       <c r="AN19">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO19">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ19">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR19">
-        <v>0.45</v>
+        <v>0.96</v>
       </c>
       <c r="AS19">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AT19">
-        <v>1.85</v>
+        <v>2.38</v>
       </c>
       <c r="AU19">
         <v>7</v>
@@ -5410,22 +5410,22 @@
         <v>3</v>
       </c>
       <c r="AO20">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP20">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ20">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR20">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AS20">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AT20">
-        <v>2.85</v>
+        <v>3.09</v>
       </c>
       <c r="AU20">
         <v>10</v>
@@ -5616,22 +5616,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AP21">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ21">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR21">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="AS21">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="AT21">
-        <v>2.44</v>
+        <v>2.51</v>
       </c>
       <c r="AU21">
         <v>3</v>
@@ -5819,25 +5819,25 @@
         <v>1.33</v>
       </c>
       <c r="AN22">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AO22">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ22">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR22">
-        <v>1.58</v>
+        <v>1.86</v>
       </c>
       <c r="AS22">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AT22">
-        <v>3.22</v>
+        <v>3.86</v>
       </c>
       <c r="AU22">
         <v>8</v>
@@ -6025,25 +6025,25 @@
         <v>2.62</v>
       </c>
       <c r="AN23">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ23">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR23">
-        <v>2.53</v>
+        <v>1.91</v>
       </c>
       <c r="AS23">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="AT23">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="AU23">
         <v>9</v>
@@ -6231,25 +6231,25 @@
         <v>1.38</v>
       </c>
       <c r="AN24">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO24">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="AP24">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ24">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR24">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AS24">
-        <v>1.15</v>
+        <v>1.34</v>
       </c>
       <c r="AT24">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6440,22 +6440,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ25">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR25">
-        <v>2.16</v>
+        <v>1.83</v>
       </c>
       <c r="AS25">
-        <v>0.78</v>
+        <v>0.62</v>
       </c>
       <c r="AT25">
-        <v>2.94</v>
+        <v>2.45</v>
       </c>
       <c r="AU25">
         <v>9</v>
@@ -6643,16 +6643,16 @@
         <v>2.4</v>
       </c>
       <c r="AN26">
-        <v>3</v>
+        <v>1.33</v>
       </c>
       <c r="AO26">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP26">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ26">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR26">
         <v>1.53</v>
@@ -6849,25 +6849,25 @@
         <v>1.29</v>
       </c>
       <c r="AN27">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO27">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ27">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR27">
-        <v>0.45</v>
+        <v>0.65</v>
       </c>
       <c r="AS27">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="AT27">
-        <v>2.59</v>
+        <v>2.49</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -7058,22 +7058,22 @@
         <v>0</v>
       </c>
       <c r="AO28">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ28">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR28">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="AS28">
-        <v>1.47</v>
+        <v>1.12</v>
       </c>
       <c r="AT28">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="AU28">
         <v>5</v>
@@ -7261,25 +7261,25 @@
         <v>1.33</v>
       </c>
       <c r="AN29">
-        <v>0</v>
+        <v>0.67</v>
       </c>
       <c r="AO29">
-        <v>3</v>
+        <v>2.33</v>
       </c>
       <c r="AP29">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ29">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR29">
-        <v>0.96</v>
+        <v>0.87</v>
       </c>
       <c r="AS29">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="AT29">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="AU29">
         <v>10</v>
@@ -7467,25 +7467,25 @@
         <v>2.05</v>
       </c>
       <c r="AN30">
-        <v>1</v>
+        <v>0.33</v>
       </c>
       <c r="AO30">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP30">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ30">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR30">
-        <v>2.35</v>
+        <v>1.89</v>
       </c>
       <c r="AS30">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AT30">
-        <v>3.64</v>
+        <v>3.8</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7673,25 +7673,25 @@
         <v>1.4</v>
       </c>
       <c r="AN31">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="AO31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP31">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ31">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR31">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AS31">
-        <v>1.51</v>
+        <v>1.96</v>
       </c>
       <c r="AT31">
-        <v>2.74</v>
+        <v>3.13</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7879,25 +7879,25 @@
         <v>1.45</v>
       </c>
       <c r="AN32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO32">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR32">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="AS32">
-        <v>0.59</v>
+        <v>0.97</v>
       </c>
       <c r="AT32">
-        <v>2.02</v>
+        <v>2.32</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -8085,25 +8085,25 @@
         <v>1.91</v>
       </c>
       <c r="AN33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO33">
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ33">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR33">
-        <v>1.52</v>
+        <v>1.08</v>
       </c>
       <c r="AS33">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AT33">
-        <v>3.32</v>
+        <v>2.84</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8291,25 +8291,25 @@
         <v>1.85</v>
       </c>
       <c r="AN34">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="AO34">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="AP34">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ34">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR34">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="AS34">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="AT34">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AU34">
         <v>4</v>
@@ -8500,22 +8500,22 @@
         <v>1.5</v>
       </c>
       <c r="AO35">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ35">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR35">
-        <v>2.22</v>
+        <v>1.7</v>
       </c>
       <c r="AS35">
-        <v>0.83</v>
+        <v>1.23</v>
       </c>
       <c r="AT35">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="AU35">
         <v>5</v>
@@ -8706,22 +8706,22 @@
         <v>2</v>
       </c>
       <c r="AO36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ36">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR36">
-        <v>0.9399999999999999</v>
+        <v>1.32</v>
       </c>
       <c r="AS36">
-        <v>1.65</v>
+        <v>1.77</v>
       </c>
       <c r="AT36">
-        <v>2.59</v>
+        <v>3.09</v>
       </c>
       <c r="AU36">
         <v>6</v>
@@ -8909,25 +8909,25 @@
         <v>1.09</v>
       </c>
       <c r="AN37">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="AO37">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="AP37">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ37">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR37">
-        <v>1.03</v>
+        <v>0.96</v>
       </c>
       <c r="AS37">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="AT37">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="AU37">
         <v>0</v>
@@ -9115,25 +9115,25 @@
         <v>2</v>
       </c>
       <c r="AN38">
-        <v>2</v>
+        <v>1.25</v>
       </c>
       <c r="AO38">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AP38">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ38">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR38">
-        <v>1.16</v>
+        <v>0.84</v>
       </c>
       <c r="AS38">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="AT38">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9327,19 +9327,19 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ39">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR39">
-        <v>1.72</v>
+        <v>1.48</v>
       </c>
       <c r="AS39">
-        <v>1.31</v>
+        <v>1.54</v>
       </c>
       <c r="AT39">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9527,25 +9527,25 @@
         <v>2.1</v>
       </c>
       <c r="AN40">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AO40">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ40">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR40">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="AS40">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AT40">
-        <v>3.44</v>
+        <v>3.31</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9733,25 +9733,25 @@
         <v>1.5</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO41">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="AP41">
+        <v>1.19</v>
+      </c>
+      <c r="AQ41">
+        <v>1.33</v>
+      </c>
+      <c r="AR41">
+        <v>1.23</v>
+      </c>
+      <c r="AS41">
         <v>1.43</v>
       </c>
-      <c r="AQ41">
-        <v>1.07</v>
-      </c>
-      <c r="AR41">
-        <v>1.62</v>
-      </c>
-      <c r="AS41">
-        <v>1.25</v>
-      </c>
       <c r="AT41">
-        <v>2.87</v>
+        <v>2.66</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -9939,25 +9939,25 @@
         <v>1.43</v>
       </c>
       <c r="AN42">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AO42">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ42">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR42">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="AS42">
-        <v>1.71</v>
+        <v>1.38</v>
       </c>
       <c r="AT42">
-        <v>2.66</v>
+        <v>2.25</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -10145,25 +10145,25 @@
         <v>1.85</v>
       </c>
       <c r="AN43">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO43">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP43">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR43">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AS43">
-        <v>0.52</v>
+        <v>0.86</v>
       </c>
       <c r="AT43">
-        <v>1.85</v>
+        <v>2.16</v>
       </c>
       <c r="AU43">
         <v>5</v>
@@ -10351,25 +10351,25 @@
         <v>2.4</v>
       </c>
       <c r="AN44">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO44">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP44">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ44">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR44">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="AS44">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="AT44">
-        <v>3.29</v>
+        <v>3.49</v>
       </c>
       <c r="AU44">
         <v>11</v>
@@ -10560,22 +10560,22 @@
         <v>1.5</v>
       </c>
       <c r="AO45">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AP45">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ45">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR45">
-        <v>1.63</v>
+        <v>1.25</v>
       </c>
       <c r="AS45">
-        <v>1.18</v>
+        <v>1.71</v>
       </c>
       <c r="AT45">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AU45">
         <v>9</v>
@@ -10763,25 +10763,25 @@
         <v>1.77</v>
       </c>
       <c r="AN46">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="AO46">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="AP46">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ46">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR46">
-        <v>1.58</v>
+        <v>1.51</v>
       </c>
       <c r="AS46">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="AT46">
-        <v>3.04</v>
+        <v>2.95</v>
       </c>
       <c r="AU46">
         <v>7</v>
@@ -10969,25 +10969,25 @@
         <v>1.7</v>
       </c>
       <c r="AN47">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AO47">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ47">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR47">
-        <v>1.76</v>
+        <v>1.38</v>
       </c>
       <c r="AS47">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="AT47">
-        <v>2.65</v>
+        <v>2.22</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -11175,25 +11175,25 @@
         <v>1.7</v>
       </c>
       <c r="AN48">
+        <v>1.83</v>
+      </c>
+      <c r="AO48">
         <v>1.33</v>
       </c>
-      <c r="AO48">
-        <v>0.33</v>
-      </c>
       <c r="AP48">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR48">
-        <v>1.15</v>
+        <v>1.3</v>
       </c>
       <c r="AS48">
-        <v>0.51</v>
+        <v>0.79</v>
       </c>
       <c r="AT48">
-        <v>1.66</v>
+        <v>2.09</v>
       </c>
       <c r="AU48">
         <v>4</v>
@@ -11381,25 +11381,25 @@
         <v>1.5</v>
       </c>
       <c r="AN49">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="AO49">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ49">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR49">
-        <v>2.18</v>
+        <v>1.67</v>
       </c>
       <c r="AS49">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AT49">
-        <v>3.77</v>
+        <v>3.32</v>
       </c>
       <c r="AU49">
         <v>3</v>
@@ -11587,25 +11587,25 @@
         <v>1.1</v>
       </c>
       <c r="AN50">
-        <v>1.33</v>
+        <v>1.17</v>
       </c>
       <c r="AO50">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP50">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ50">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR50">
-        <v>1.76</v>
+        <v>1.44</v>
       </c>
       <c r="AS50">
-        <v>1.57</v>
+        <v>1.79</v>
       </c>
       <c r="AT50">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11793,25 +11793,25 @@
         <v>2.05</v>
       </c>
       <c r="AN51">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AO51">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP51">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ51">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR51">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AS51">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AT51">
-        <v>2.77</v>
+        <v>2.87</v>
       </c>
       <c r="AU51">
         <v>9</v>
@@ -11999,25 +11999,25 @@
         <v>1.54</v>
       </c>
       <c r="AN52">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="AO52">
-        <v>0.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ52">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR52">
-        <v>2.07</v>
+        <v>1.75</v>
       </c>
       <c r="AS52">
-        <v>1.46</v>
+        <v>1.58</v>
       </c>
       <c r="AT52">
-        <v>3.53</v>
+        <v>3.33</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12205,25 +12205,25 @@
         <v>1.37</v>
       </c>
       <c r="AN53">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="AO53">
-        <v>1</v>
+        <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ53">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR53">
-        <v>0.82</v>
+        <v>0.87</v>
       </c>
       <c r="AS53">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AT53">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AU53">
         <v>5</v>
@@ -12411,25 +12411,25 @@
         <v>2.21</v>
       </c>
       <c r="AN54">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO54">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AP54">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ54">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR54">
-        <v>1.56</v>
+        <v>1.45</v>
       </c>
       <c r="AS54">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="AT54">
-        <v>2.37</v>
+        <v>2.33</v>
       </c>
       <c r="AU54">
         <v>13</v>
@@ -12617,25 +12617,25 @@
         <v>2.17</v>
       </c>
       <c r="AN55">
+        <v>1.4</v>
+      </c>
+      <c r="AO55">
         <v>1.33</v>
       </c>
-      <c r="AO55">
-        <v>1.67</v>
-      </c>
       <c r="AP55">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ55">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR55">
-        <v>1.72</v>
+        <v>1.38</v>
       </c>
       <c r="AS55">
-        <v>0.98</v>
+        <v>1.24</v>
       </c>
       <c r="AT55">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="AU55">
         <v>8</v>
@@ -12823,25 +12823,25 @@
         <v>1.65</v>
       </c>
       <c r="AN56">
+        <v>2</v>
+      </c>
+      <c r="AO56">
+        <v>2.17</v>
+      </c>
+      <c r="AP56">
         <v>1.67</v>
       </c>
-      <c r="AO56">
-        <v>2</v>
-      </c>
-      <c r="AP56">
-        <v>1.71</v>
-      </c>
       <c r="AQ56">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR56">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AS56">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AT56">
-        <v>3.6</v>
+        <v>3.34</v>
       </c>
       <c r="AU56">
         <v>5</v>
@@ -13029,25 +13029,25 @@
         <v>1.22</v>
       </c>
       <c r="AN57">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO57">
-        <v>0.5</v>
+        <v>1.29</v>
       </c>
       <c r="AP57">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ57">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR57">
-        <v>1.08</v>
+        <v>0.8</v>
       </c>
       <c r="AS57">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="AT57">
-        <v>2.56</v>
+        <v>2.38</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -13235,25 +13235,25 @@
         <v>1.55</v>
       </c>
       <c r="AN58">
-        <v>0.33</v>
+        <v>0.14</v>
       </c>
       <c r="AO58">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ58">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR58">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="AS58">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="AT58">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="AU58">
         <v>0</v>
@@ -13441,25 +13441,25 @@
         <v>1.38</v>
       </c>
       <c r="AN59">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AO59">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AP59">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ59">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR59">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="AS59">
-        <v>1.42</v>
+        <v>1.68</v>
       </c>
       <c r="AT59">
-        <v>3.03</v>
+        <v>3.22</v>
       </c>
       <c r="AU59">
         <v>7</v>
@@ -13647,25 +13647,25 @@
         <v>1.84</v>
       </c>
       <c r="AN60">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="AO60">
-        <v>1</v>
+        <v>1.71</v>
       </c>
       <c r="AP60">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ60">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR60">
-        <v>1.66</v>
+        <v>1.54</v>
       </c>
       <c r="AS60">
-        <v>1.34</v>
+        <v>1.61</v>
       </c>
       <c r="AT60">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="AU60">
         <v>5</v>
@@ -13853,25 +13853,25 @@
         <v>2.5</v>
       </c>
       <c r="AN61">
-        <v>2.33</v>
+        <v>1.86</v>
       </c>
       <c r="AO61">
+        <v>1.67</v>
+      </c>
+      <c r="AP61">
+        <v>1.93</v>
+      </c>
+      <c r="AQ61">
+        <v>1.52</v>
+      </c>
+      <c r="AR61">
+        <v>1.8</v>
+      </c>
+      <c r="AS61">
         <v>1.5</v>
       </c>
-      <c r="AP61">
-        <v>2.14</v>
-      </c>
-      <c r="AQ61">
-        <v>1.21</v>
-      </c>
-      <c r="AR61">
-        <v>2.01</v>
-      </c>
-      <c r="AS61">
-        <v>0.86</v>
-      </c>
       <c r="AT61">
-        <v>2.87</v>
+        <v>3.3</v>
       </c>
       <c r="AU61">
         <v>10</v>
@@ -14059,25 +14059,25 @@
         <v>1.51</v>
       </c>
       <c r="AN62">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AO62">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="AP62">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ62">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR62">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS62">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="AT62">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14265,22 +14265,22 @@
         <v>2.3</v>
       </c>
       <c r="AN63">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AO63">
-        <v>2.33</v>
+        <v>1.57</v>
       </c>
       <c r="AP63">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ63">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR63">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AS63">
-        <v>1.45</v>
+        <v>1.31</v>
       </c>
       <c r="AT63">
         <v>3.14</v>
@@ -14471,25 +14471,25 @@
         <v>2</v>
       </c>
       <c r="AN64">
-        <v>2.33</v>
+        <v>1.43</v>
       </c>
       <c r="AO64">
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ64">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR64">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AS64">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AT64">
-        <v>2.45</v>
+        <v>2.76</v>
       </c>
       <c r="AU64">
         <v>3</v>
@@ -14677,25 +14677,25 @@
         <v>1.51</v>
       </c>
       <c r="AN65">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AO65">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="AP65">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ65">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR65">
-        <v>1.79</v>
+        <v>1.48</v>
       </c>
       <c r="AS65">
-        <v>0.88</v>
+        <v>1.42</v>
       </c>
       <c r="AT65">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14883,25 +14883,25 @@
         <v>1.22</v>
       </c>
       <c r="AN66">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="AO66">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AP66">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ66">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR66">
-        <v>1.81</v>
+        <v>1.53</v>
       </c>
       <c r="AS66">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AT66">
-        <v>3.45</v>
+        <v>3.43</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -15089,25 +15089,25 @@
         <v>2.5</v>
       </c>
       <c r="AN67">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AO67">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AP67">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ67">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR67">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AS67">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="AT67">
-        <v>3.01</v>
+        <v>3.18</v>
       </c>
       <c r="AU67">
         <v>6</v>
@@ -15295,25 +15295,25 @@
         <v>1.44</v>
       </c>
       <c r="AN68">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO68">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP68">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ68">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR68">
-        <v>1.04</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AS68">
-        <v>1.48</v>
+        <v>1.57</v>
       </c>
       <c r="AT68">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="AU68">
         <v>4</v>
@@ -15501,25 +15501,25 @@
         <v>1.35</v>
       </c>
       <c r="AN69">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AO69">
-        <v>2.33</v>
+        <v>1.63</v>
       </c>
       <c r="AP69">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ69">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR69">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AS69">
-        <v>1.37</v>
+        <v>1.51</v>
       </c>
       <c r="AT69">
-        <v>2.58</v>
+        <v>2.76</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15707,25 +15707,25 @@
         <v>3.75</v>
       </c>
       <c r="AN70">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AO70">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="AP70">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ70">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR70">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="AS70">
-        <v>0.93</v>
+        <v>0.92</v>
       </c>
       <c r="AT70">
-        <v>2.81</v>
+        <v>2.55</v>
       </c>
       <c r="AU70">
         <v>7</v>
@@ -15913,25 +15913,25 @@
         <v>3</v>
       </c>
       <c r="AN71">
-        <v>2.33</v>
+        <v>1.25</v>
       </c>
       <c r="AO71">
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ71">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR71">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AS71">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="AT71">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="AU71">
         <v>6</v>
@@ -16119,25 +16119,25 @@
         <v>2.2</v>
       </c>
       <c r="AN72">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO72">
-        <v>0.75</v>
+        <v>1.38</v>
       </c>
       <c r="AP72">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ72">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR72">
-        <v>1.82</v>
+        <v>1.33</v>
       </c>
       <c r="AS72">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AT72">
-        <v>3.24</v>
+        <v>2.72</v>
       </c>
       <c r="AU72">
         <v>6</v>
@@ -16325,25 +16325,25 @@
         <v>2.15</v>
       </c>
       <c r="AN73">
-        <v>1.5</v>
+        <v>0.88</v>
       </c>
       <c r="AO73">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AP73">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ73">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR73">
-        <v>1.73</v>
+        <v>1.49</v>
       </c>
       <c r="AS73">
-        <v>1.26</v>
+        <v>1.08</v>
       </c>
       <c r="AT73">
-        <v>2.99</v>
+        <v>2.57</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16531,25 +16531,25 @@
         <v>2.75</v>
       </c>
       <c r="AN74">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AO74">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AP74">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ74">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR74">
-        <v>1.66</v>
+        <v>1.52</v>
       </c>
       <c r="AS74">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="AT74">
-        <v>2.51</v>
+        <v>2.4</v>
       </c>
       <c r="AU74">
         <v>10</v>
@@ -16737,25 +16737,25 @@
         <v>1.62</v>
       </c>
       <c r="AN75">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AO75">
-        <v>0.6</v>
+        <v>1.22</v>
       </c>
       <c r="AP75">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ75">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR75">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="AS75">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AT75">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16943,25 +16943,25 @@
         <v>1.15</v>
       </c>
       <c r="AN76">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AO76">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ76">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR76">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AS76">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AT76">
-        <v>3.5</v>
+        <v>3.18</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17149,25 +17149,25 @@
         <v>1.33</v>
       </c>
       <c r="AN77">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO77">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="AP77">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ77">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR77">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AS77">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="AT77">
-        <v>2.48</v>
+        <v>2.79</v>
       </c>
       <c r="AU77">
         <v>3</v>
@@ -17355,25 +17355,25 @@
         <v>2.4</v>
       </c>
       <c r="AN78">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="AO78">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AP78">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ78">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR78">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AS78">
-        <v>0.58</v>
+        <v>0.89</v>
       </c>
       <c r="AT78">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17561,25 +17561,25 @@
         <v>2.25</v>
       </c>
       <c r="AN79">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AO79">
-        <v>0.25</v>
+        <v>0.89</v>
       </c>
       <c r="AP79">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ79">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR79">
-        <v>1.88</v>
+        <v>1.66</v>
       </c>
       <c r="AS79">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AT79">
-        <v>3.13</v>
+        <v>3.11</v>
       </c>
       <c r="AU79">
         <v>6</v>
@@ -17767,25 +17767,25 @@
         <v>1.86</v>
       </c>
       <c r="AN80">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AO80">
-        <v>0.6</v>
+        <v>1.44</v>
       </c>
       <c r="AP80">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ80">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR80">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="AS80">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AT80">
-        <v>3.75</v>
+        <v>3.49</v>
       </c>
       <c r="AU80">
         <v>6</v>
@@ -17973,25 +17973,25 @@
         <v>1.33</v>
       </c>
       <c r="AN81">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AO81">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="AP81">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ81">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR81">
-        <v>0.89</v>
+        <v>1.06</v>
       </c>
       <c r="AS81">
-        <v>0.84</v>
+        <v>1.33</v>
       </c>
       <c r="AT81">
-        <v>1.73</v>
+        <v>2.39</v>
       </c>
       <c r="AU81">
         <v>13</v>
@@ -18179,25 +18179,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>0.25</v>
+        <v>0.2</v>
       </c>
       <c r="AO82">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ82">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR82">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="AS82">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="AT82">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="AU82">
         <v>0</v>
@@ -18385,25 +18385,25 @@
         <v>1.25</v>
       </c>
       <c r="AN83">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AO83">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AP83">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ83">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR83">
-        <v>1.89</v>
+        <v>1.65</v>
       </c>
       <c r="AS83">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AT83">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18591,25 +18591,25 @@
         <v>1.96</v>
       </c>
       <c r="AN84">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AO84">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ84">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR84">
-        <v>1.61</v>
+        <v>1.47</v>
       </c>
       <c r="AS84">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AT84">
-        <v>2.89</v>
+        <v>2.67</v>
       </c>
       <c r="AU84">
         <v>7</v>
@@ -18797,25 +18797,25 @@
         <v>2.15</v>
       </c>
       <c r="AN85">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="AO85">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="AP85">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ85">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR85">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AS85">
-        <v>0.91</v>
+        <v>1.31</v>
       </c>
       <c r="AT85">
-        <v>2.58</v>
+        <v>2.87</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -19003,25 +19003,25 @@
         <v>2.65</v>
       </c>
       <c r="AN86">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="AO86">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="AP86">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ86">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR86">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="AS86">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AT86">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="AU86">
         <v>5</v>
@@ -19209,25 +19209,25 @@
         <v>1.38</v>
       </c>
       <c r="AN87">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="AO87">
-        <v>1.75</v>
+        <v>1.9</v>
       </c>
       <c r="AP87">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ87">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR87">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AS87">
-        <v>1.39</v>
+        <v>1.63</v>
       </c>
       <c r="AT87">
-        <v>2.75</v>
+        <v>2.96</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19415,25 +19415,25 @@
         <v>1.38</v>
       </c>
       <c r="AN88">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="AO88">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AP88">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ88">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR88">
-        <v>1.14</v>
+        <v>0.98</v>
       </c>
       <c r="AS88">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="AT88">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="AU88">
         <v>7</v>
@@ -19621,25 +19621,25 @@
         <v>2.15</v>
       </c>
       <c r="AN89">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AO89">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="AP89">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ89">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR89">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AS89">
-        <v>1.07</v>
+        <v>1.29</v>
       </c>
       <c r="AT89">
-        <v>2.55</v>
+        <v>2.64</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19827,25 +19827,25 @@
         <v>1.9</v>
       </c>
       <c r="AN90">
-        <v>1.4</v>
+        <v>1</v>
       </c>
       <c r="AO90">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ90">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR90">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AS90">
-        <v>0.86</v>
+        <v>0.84</v>
       </c>
       <c r="AT90">
-        <v>2.36</v>
+        <v>2.11</v>
       </c>
       <c r="AU90">
         <v>6</v>
@@ -20033,25 +20033,25 @@
         <v>0</v>
       </c>
       <c r="AN91">
-        <v>2</v>
+        <v>1.27</v>
       </c>
       <c r="AO91">
-        <v>0.5</v>
+        <v>1.09</v>
       </c>
       <c r="AP91">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ91">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR91">
-        <v>1.77</v>
+        <v>1.57</v>
       </c>
       <c r="AS91">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AT91">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20239,25 +20239,25 @@
         <v>1.45</v>
       </c>
       <c r="AN92">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AO92">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AP92">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ92">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR92">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="AS92">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="AT92">
-        <v>2.36</v>
+        <v>2.51</v>
       </c>
       <c r="AU92">
         <v>5</v>
@@ -20445,25 +20445,25 @@
         <v>1.49</v>
       </c>
       <c r="AN93">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="AO93">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AP93">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ93">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR93">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="AS93">
-        <v>1.41</v>
+        <v>1.64</v>
       </c>
       <c r="AT93">
-        <v>2.64</v>
+        <v>2.86</v>
       </c>
       <c r="AU93">
         <v>7</v>
@@ -20651,25 +20651,25 @@
         <v>2.4</v>
       </c>
       <c r="AN94">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AO94">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="AP94">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ94">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR94">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AS94">
         <v>1.57</v>
       </c>
       <c r="AT94">
-        <v>3.6</v>
+        <v>3.39</v>
       </c>
       <c r="AU94">
         <v>10</v>
@@ -20857,25 +20857,25 @@
         <v>2.4</v>
       </c>
       <c r="AN95">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AO95">
-        <v>0.8</v>
+        <v>1.36</v>
       </c>
       <c r="AP95">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR95">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
       <c r="AS95">
-        <v>0.82</v>
+        <v>1.01</v>
       </c>
       <c r="AT95">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="AU95">
         <v>6</v>
@@ -21063,25 +21063,25 @@
         <v>1.38</v>
       </c>
       <c r="AN96">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AO96">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AP96">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ96">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR96">
-        <v>1.72</v>
+        <v>1.29</v>
       </c>
       <c r="AS96">
-        <v>1.94</v>
+        <v>1.9</v>
       </c>
       <c r="AT96">
-        <v>3.66</v>
+        <v>3.19</v>
       </c>
       <c r="AU96">
         <v>0</v>
@@ -21269,25 +21269,25 @@
         <v>2.7</v>
       </c>
       <c r="AN97">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="AO97">
-        <v>0.2</v>
+        <v>0.82</v>
       </c>
       <c r="AP97">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ97">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR97">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AS97">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AT97">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21475,25 +21475,25 @@
         <v>1.98</v>
       </c>
       <c r="AN98">
+        <v>1.25</v>
+      </c>
+      <c r="AO98">
         <v>1.33</v>
       </c>
-      <c r="AO98">
-        <v>1.6</v>
-      </c>
       <c r="AP98">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ98">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR98">
-        <v>1.83</v>
+        <v>1.65</v>
       </c>
       <c r="AS98">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AT98">
-        <v>2.94</v>
+        <v>2.79</v>
       </c>
       <c r="AU98">
         <v>9</v>
@@ -21681,25 +21681,25 @@
         <v>1.6</v>
       </c>
       <c r="AN99">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="AO99">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="AP99">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ99">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR99">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="AS99">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AT99">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="AU99">
         <v>5</v>
@@ -21887,25 +21887,25 @@
         <v>1.26</v>
       </c>
       <c r="AN100">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO100">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AP100">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ100">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR100">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AS100">
-        <v>1.65</v>
+        <v>1.86</v>
       </c>
       <c r="AT100">
-        <v>2.95</v>
+        <v>3.14</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -22093,25 +22093,25 @@
         <v>1.28</v>
       </c>
       <c r="AN101">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO101">
-        <v>0.67</v>
+        <v>1.25</v>
       </c>
       <c r="AP101">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ101">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR101">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AS101">
-        <v>1.49</v>
+        <v>1.6</v>
       </c>
       <c r="AT101">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="AU101">
         <v>5</v>
@@ -22299,25 +22299,25 @@
         <v>1.83</v>
       </c>
       <c r="AN102">
-        <v>2.67</v>
+        <v>2.33</v>
       </c>
       <c r="AO102">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AP102">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ102">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR102">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AS102">
-        <v>1.29</v>
+        <v>1.56</v>
       </c>
       <c r="AT102">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="AU102">
         <v>8</v>
@@ -22505,25 +22505,25 @@
         <v>1.58</v>
       </c>
       <c r="AN103">
+        <v>1</v>
+      </c>
+      <c r="AO103">
+        <v>1.17</v>
+      </c>
+      <c r="AP103">
+        <v>1.15</v>
+      </c>
+      <c r="AQ103">
         <v>1.33</v>
       </c>
-      <c r="AO103">
-        <v>0.67</v>
-      </c>
-      <c r="AP103">
-        <v>1.54</v>
-      </c>
-      <c r="AQ103">
-        <v>1.07</v>
-      </c>
       <c r="AR103">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AS103">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AT103">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22711,25 +22711,25 @@
         <v>2.75</v>
       </c>
       <c r="AN104">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AO104">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="AP104">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ104">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR104">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AS104">
-        <v>1.08</v>
+        <v>1.29</v>
       </c>
       <c r="AT104">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="AU104">
         <v>7</v>
@@ -22917,25 +22917,25 @@
         <v>1.24</v>
       </c>
       <c r="AN105">
-        <v>0.8</v>
+        <v>0.42</v>
       </c>
       <c r="AO105">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ105">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR105">
-        <v>0.83</v>
+        <v>0.9</v>
       </c>
       <c r="AS105">
-        <v>0.93</v>
+        <v>1.24</v>
       </c>
       <c r="AT105">
-        <v>1.76</v>
+        <v>2.14</v>
       </c>
       <c r="AU105">
         <v>5</v>
@@ -23123,25 +23123,25 @@
         <v>1.5</v>
       </c>
       <c r="AN106">
-        <v>1.5</v>
+        <v>1.08</v>
       </c>
       <c r="AO106">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AP106">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ106">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR106">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AS106">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AT106">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="AU106">
         <v>6</v>
@@ -23329,25 +23329,25 @@
         <v>1.22</v>
       </c>
       <c r="AN107">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="AO107">
-        <v>1.33</v>
+        <v>1.77</v>
       </c>
       <c r="AP107">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ107">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR107">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AS107">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="AT107">
-        <v>2.67</v>
+        <v>2.73</v>
       </c>
       <c r="AU107">
         <v>6</v>
@@ -23535,25 +23535,25 @@
         <v>1.38</v>
       </c>
       <c r="AN108">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="AO108">
-        <v>0.86</v>
+        <v>1.15</v>
       </c>
       <c r="AP108">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ108">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR108">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="AS108">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AT108">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23741,25 +23741,25 @@
         <v>1.8</v>
       </c>
       <c r="AN109">
-        <v>1.67</v>
+        <v>1.08</v>
       </c>
       <c r="AO109">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AP109">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ109">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR109">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AS109">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AT109">
-        <v>3.23</v>
+        <v>3.17</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23947,25 +23947,25 @@
         <v>1.45</v>
       </c>
       <c r="AN110">
-        <v>1.57</v>
+        <v>1.15</v>
       </c>
       <c r="AO110">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="AP110">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ110">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR110">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AS110">
-        <v>1.46</v>
+        <v>1.56</v>
       </c>
       <c r="AT110">
-        <v>3.11</v>
+        <v>3.04</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -24153,25 +24153,25 @@
         <v>1.9</v>
       </c>
       <c r="AN111">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AO111">
-        <v>0.67</v>
+        <v>1.38</v>
       </c>
       <c r="AP111">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR111">
-        <v>1.55</v>
+        <v>1.25</v>
       </c>
       <c r="AS111">
-        <v>0.9</v>
+        <v>1.05</v>
       </c>
       <c r="AT111">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AU111">
         <v>13</v>
@@ -24359,25 +24359,25 @@
         <v>1.65</v>
       </c>
       <c r="AN112">
-        <v>1.83</v>
+        <v>1.23</v>
       </c>
       <c r="AO112">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AP112">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ112">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR112">
-        <v>1.71</v>
+        <v>1.55</v>
       </c>
       <c r="AS112">
         <v>1.85</v>
       </c>
       <c r="AT112">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AU112">
         <v>8</v>
@@ -24565,25 +24565,25 @@
         <v>1.05</v>
       </c>
       <c r="AN113">
-        <v>0.83</v>
+        <v>0.46</v>
       </c>
       <c r="AO113">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AP113">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ113">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR113">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="AS113">
-        <v>1.63</v>
+        <v>1.84</v>
       </c>
       <c r="AT113">
-        <v>2.51</v>
+        <v>2.75</v>
       </c>
       <c r="AU113">
         <v>6</v>
@@ -24771,25 +24771,25 @@
         <v>2.5</v>
       </c>
       <c r="AN114">
-        <v>2.14</v>
+        <v>1.86</v>
       </c>
       <c r="AO114">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="AP114">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ114">
+        <v>1.19</v>
+      </c>
+      <c r="AR114">
+        <v>1.49</v>
+      </c>
+      <c r="AS114">
         <v>1.15</v>
       </c>
-      <c r="AR114">
-        <v>1.76</v>
-      </c>
-      <c r="AS114">
-        <v>1.13</v>
-      </c>
       <c r="AT114">
-        <v>2.89</v>
+        <v>2.64</v>
       </c>
       <c r="AU114">
         <v>7</v>
@@ -24977,25 +24977,25 @@
         <v>0</v>
       </c>
       <c r="AN115">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="AO115">
-        <v>0.71</v>
+        <v>1.21</v>
       </c>
       <c r="AP115">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ115">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR115">
-        <v>2.07</v>
+        <v>1.86</v>
       </c>
       <c r="AS115">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AT115">
-        <v>3.38</v>
+        <v>3.2</v>
       </c>
       <c r="AU115">
         <v>6</v>
@@ -25183,25 +25183,25 @@
         <v>1.53</v>
       </c>
       <c r="AN116">
-        <v>2</v>
+        <v>1.29</v>
       </c>
       <c r="AO116">
-        <v>0.67</v>
+        <v>1.07</v>
       </c>
       <c r="AP116">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ116">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR116">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AS116">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="AT116">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="AU116">
         <v>5</v>
@@ -25389,25 +25389,25 @@
         <v>2.5</v>
       </c>
       <c r="AN117">
-        <v>2.71</v>
+        <v>2.21</v>
       </c>
       <c r="AO117">
-        <v>0.57</v>
+        <v>1.21</v>
       </c>
       <c r="AP117">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ117">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR117">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AS117">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AT117">
-        <v>3.18</v>
+        <v>3.37</v>
       </c>
       <c r="AU117">
         <v>6</v>
@@ -25595,25 +25595,25 @@
         <v>0</v>
       </c>
       <c r="AN118">
-        <v>1.86</v>
+        <v>1.5</v>
       </c>
       <c r="AO118">
-        <v>0.14</v>
+        <v>0.5</v>
       </c>
       <c r="AP118">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ118">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR118">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AS118">
-        <v>0.95</v>
+        <v>0.93</v>
       </c>
       <c r="AT118">
-        <v>2.46</v>
+        <v>2.33</v>
       </c>
       <c r="AU118">
         <v>11</v>
@@ -25801,25 +25801,25 @@
         <v>0</v>
       </c>
       <c r="AN119">
-        <v>1.5</v>
+        <v>1.14</v>
       </c>
       <c r="AO119">
-        <v>0.71</v>
+        <v>1.36</v>
       </c>
       <c r="AP119">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ119">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR119">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AS119">
-        <v>1.42</v>
+        <v>1.56</v>
       </c>
       <c r="AT119">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="AU119">
         <v>0</v>
@@ -26007,25 +26007,25 @@
         <v>1.88</v>
       </c>
       <c r="AN120">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="AO120">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AP120">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ120">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR120">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AS120">
-        <v>0.99</v>
+        <v>1.34</v>
       </c>
       <c r="AT120">
-        <v>2.63</v>
+        <v>2.87</v>
       </c>
       <c r="AU120">
         <v>12</v>
@@ -26213,25 +26213,25 @@
         <v>2.15</v>
       </c>
       <c r="AN121">
-        <v>1.57</v>
+        <v>1.29</v>
       </c>
       <c r="AO121">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AP121">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ121">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR121">
-        <v>1.8</v>
+        <v>1.63</v>
       </c>
       <c r="AS121">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="AT121">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="AU121">
         <v>7</v>
@@ -26419,25 +26419,25 @@
         <v>1.38</v>
       </c>
       <c r="AN122">
-        <v>1.43</v>
+        <v>0.93</v>
       </c>
       <c r="AO122">
-        <v>1.14</v>
+        <v>1.6</v>
       </c>
       <c r="AP122">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ122">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR122">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AS122">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="AT122">
-        <v>2.75</v>
+        <v>2.64</v>
       </c>
       <c r="AU122">
         <v>6</v>
@@ -26625,25 +26625,25 @@
         <v>4</v>
       </c>
       <c r="AN123">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AO123">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AP123">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ123">
+        <v>1.19</v>
+      </c>
+      <c r="AR123">
+        <v>1.86</v>
+      </c>
+      <c r="AS123">
         <v>1.15</v>
       </c>
-      <c r="AR123">
-        <v>2.07</v>
-      </c>
-      <c r="AS123">
-        <v>1.13</v>
-      </c>
       <c r="AT123">
-        <v>3.2</v>
+        <v>3.01</v>
       </c>
       <c r="AU123">
         <v>9</v>
@@ -26831,25 +26831,25 @@
         <v>1.92</v>
       </c>
       <c r="AN124">
-        <v>1.86</v>
+        <v>1.13</v>
       </c>
       <c r="AO124">
-        <v>0.57</v>
+        <v>1.4</v>
       </c>
       <c r="AP124">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR124">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AS124">
-        <v>0.91</v>
+        <v>1.05</v>
       </c>
       <c r="AT124">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AU124">
         <v>3</v>
@@ -27037,22 +27037,22 @@
         <v>1.2</v>
       </c>
       <c r="AN125">
-        <v>1.71</v>
+        <v>1.13</v>
       </c>
       <c r="AO125">
-        <v>1.71</v>
+        <v>2.27</v>
       </c>
       <c r="AP125">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ125">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR125">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="AS125">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="AT125">
         <v>3.15</v>
@@ -27243,25 +27243,25 @@
         <v>1.36</v>
       </c>
       <c r="AN126">
-        <v>1.43</v>
+        <v>1.13</v>
       </c>
       <c r="AO126">
-        <v>1.57</v>
+        <v>1.73</v>
       </c>
       <c r="AP126">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ126">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR126">
         <v>1.26</v>
       </c>
       <c r="AS126">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AT126">
-        <v>2.69</v>
+        <v>2.84</v>
       </c>
       <c r="AU126">
         <v>3</v>
@@ -27449,25 +27449,25 @@
         <v>1.25</v>
       </c>
       <c r="AN127">
-        <v>0.86</v>
+        <v>0.47</v>
       </c>
       <c r="AO127">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ127">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR127">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="AS127">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AT127">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="AU127">
         <v>9</v>
@@ -27655,25 +27655,25 @@
         <v>1.98</v>
       </c>
       <c r="AN128">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO128">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AP128">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ128">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR128">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AS128">
-        <v>1.23</v>
+        <v>1.49</v>
       </c>
       <c r="AT128">
-        <v>2.93</v>
+        <v>3.04</v>
       </c>
       <c r="AU128">
         <v>7</v>
@@ -27861,25 +27861,25 @@
         <v>1.68</v>
       </c>
       <c r="AN129">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="AO129">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AP129">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ129">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR129">
-        <v>1.82</v>
+        <v>1.65</v>
       </c>
       <c r="AS129">
-        <v>0.99</v>
+        <v>1.31</v>
       </c>
       <c r="AT129">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AU129">
         <v>9</v>
@@ -28067,25 +28067,25 @@
         <v>3.6</v>
       </c>
       <c r="AN130">
-        <v>2.75</v>
+        <v>2.19</v>
       </c>
       <c r="AO130">
-        <v>0.5</v>
+        <v>1.06</v>
       </c>
       <c r="AP130">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ130">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR130">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="AS130">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="AT130">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AU130">
         <v>7</v>
@@ -28273,25 +28273,25 @@
         <v>1.45</v>
       </c>
       <c r="AN131">
-        <v>2.13</v>
+        <v>1.38</v>
       </c>
       <c r="AO131">
-        <v>0.88</v>
+        <v>1.13</v>
       </c>
       <c r="AP131">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ131">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR131">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS131">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AT131">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28479,25 +28479,25 @@
         <v>1.26</v>
       </c>
       <c r="AN132">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AO132">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AP132">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ132">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR132">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AS132">
-        <v>1.69</v>
+        <v>1.87</v>
       </c>
       <c r="AT132">
-        <v>3.24</v>
+        <v>3.29</v>
       </c>
       <c r="AU132">
         <v>6</v>
@@ -28685,25 +28685,25 @@
         <v>1.95</v>
       </c>
       <c r="AN133">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="AO133">
-        <v>0.63</v>
+        <v>1.13</v>
       </c>
       <c r="AP133">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ133">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR133">
-        <v>1.68</v>
+        <v>1.33</v>
       </c>
       <c r="AS133">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AT133">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28891,25 +28891,25 @@
         <v>1.77</v>
       </c>
       <c r="AN134">
-        <v>2</v>
+        <v>1.69</v>
       </c>
       <c r="AO134">
-        <v>0.5</v>
+        <v>1.13</v>
       </c>
       <c r="AP134">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ134">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR134">
-        <v>1.76</v>
+        <v>1.49</v>
       </c>
       <c r="AS134">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="AT134">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU134">
         <v>9</v>
@@ -29097,25 +29097,25 @@
         <v>1.22</v>
       </c>
       <c r="AN135">
-        <v>1.38</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO135">
-        <v>0.75</v>
+        <v>1.44</v>
       </c>
       <c r="AP135">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ135">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR135">
-        <v>1.6</v>
+        <v>1.47</v>
       </c>
       <c r="AS135">
-        <v>1.41</v>
+        <v>1.55</v>
       </c>
       <c r="AT135">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="AU135">
         <v>8</v>
@@ -29303,25 +29303,25 @@
         <v>3.35</v>
       </c>
       <c r="AN136">
-        <v>1.88</v>
+        <v>1.69</v>
       </c>
       <c r="AO136">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="AP136">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ136">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR136">
-        <v>1.71</v>
+        <v>1.57</v>
       </c>
       <c r="AS136">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="AT136">
-        <v>2.71</v>
+        <v>2.6</v>
       </c>
       <c r="AU136">
         <v>7</v>
@@ -29512,22 +29512,22 @@
         <v>1.13</v>
       </c>
       <c r="AO137">
-        <v>1</v>
+        <v>1.38</v>
       </c>
       <c r="AP137">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ137">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR137">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AS137">
-        <v>1.46</v>
+        <v>1.68</v>
       </c>
       <c r="AT137">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AU137">
         <v>2</v>
@@ -29715,25 +29715,25 @@
         <v>1.52</v>
       </c>
       <c r="AN138">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="AO138">
-        <v>1.38</v>
+        <v>1.59</v>
       </c>
       <c r="AP138">
+        <v>1.19</v>
+      </c>
+      <c r="AQ138">
+        <v>1.63</v>
+      </c>
+      <c r="AR138">
         <v>1.43</v>
       </c>
-      <c r="AQ138">
-        <v>1.31</v>
-      </c>
-      <c r="AR138">
-        <v>1.55</v>
-      </c>
       <c r="AS138">
-        <v>1.26</v>
+        <v>1.53</v>
       </c>
       <c r="AT138">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="AU138">
         <v>7</v>
@@ -29921,25 +29921,25 @@
         <v>1.36</v>
       </c>
       <c r="AN139">
-        <v>1.13</v>
+        <v>0.59</v>
       </c>
       <c r="AO139">
-        <v>0.63</v>
+        <v>1.35</v>
       </c>
       <c r="AP139">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ139">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR139">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="AS139">
-        <v>0.93</v>
+        <v>1.09</v>
       </c>
       <c r="AT139">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AU139">
         <v>9</v>
@@ -30127,25 +30127,25 @@
         <v>1.57</v>
       </c>
       <c r="AN140">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AO140">
-        <v>0.78</v>
+        <v>1.24</v>
       </c>
       <c r="AP140">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ140">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR140">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AS140">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="AT140">
-        <v>2.68</v>
+        <v>2.82</v>
       </c>
       <c r="AU140">
         <v>3</v>
@@ -30333,25 +30333,25 @@
         <v>1.66</v>
       </c>
       <c r="AN141">
-        <v>1.63</v>
+        <v>1</v>
       </c>
       <c r="AO141">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ141">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR141">
-        <v>1.44</v>
+        <v>1.24</v>
       </c>
       <c r="AS141">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AT141">
-        <v>2.53</v>
+        <v>2.34</v>
       </c>
       <c r="AU141">
         <v>2</v>
@@ -30539,25 +30539,25 @@
         <v>2.3</v>
       </c>
       <c r="AN142">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AO142">
-        <v>1.63</v>
+        <v>2.24</v>
       </c>
       <c r="AP142">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ142">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR142">
-        <v>2.07</v>
+        <v>1.81</v>
       </c>
       <c r="AS142">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AT142">
-        <v>3.79</v>
+        <v>3.56</v>
       </c>
       <c r="AU142">
         <v>6</v>
@@ -30745,25 +30745,25 @@
         <v>2.75</v>
       </c>
       <c r="AN143">
-        <v>2.13</v>
+        <v>1.41</v>
       </c>
       <c r="AO143">
-        <v>0.88</v>
+        <v>1.29</v>
       </c>
       <c r="AP143">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ143">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR143">
-        <v>1.68</v>
+        <v>1.54</v>
       </c>
       <c r="AS143">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AT143">
-        <v>3.14</v>
+        <v>3.21</v>
       </c>
       <c r="AU143">
         <v>14</v>
@@ -30951,25 +30951,25 @@
         <v>1.3</v>
       </c>
       <c r="AN144">
-        <v>1.63</v>
+        <v>1.06</v>
       </c>
       <c r="AO144">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AP144">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ144">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR144">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="AS144">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AT144">
-        <v>2.83</v>
+        <v>2.97</v>
       </c>
       <c r="AU144">
         <v>7</v>
@@ -31157,25 +31157,25 @@
         <v>2</v>
       </c>
       <c r="AN145">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AO145">
-        <v>0.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP145">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ145">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR145">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="AS145">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AT145">
-        <v>2.97</v>
+        <v>2.82</v>
       </c>
       <c r="AU145">
         <v>6</v>
@@ -31363,25 +31363,25 @@
         <v>1.65</v>
       </c>
       <c r="AN146">
-        <v>1.67</v>
+        <v>1.22</v>
       </c>
       <c r="AO146">
-        <v>1</v>
+        <v>1.39</v>
       </c>
       <c r="AP146">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ146">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR146">
-        <v>1.85</v>
+        <v>1.63</v>
       </c>
       <c r="AS146">
-        <v>1.29</v>
+        <v>1.43</v>
       </c>
       <c r="AT146">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="AU146">
         <v>7</v>
@@ -31569,25 +31569,25 @@
         <v>1.83</v>
       </c>
       <c r="AN147">
-        <v>1.75</v>
+        <v>1.17</v>
       </c>
       <c r="AO147">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ147">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR147">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AS147">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="AT147">
-        <v>3.09</v>
+        <v>2.98</v>
       </c>
       <c r="AU147">
         <v>8</v>
@@ -31778,22 +31778,22 @@
         <v>1.33</v>
       </c>
       <c r="AO148">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="AP148">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ148">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR148">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AS148">
-        <v>1.23</v>
+        <v>1.5</v>
       </c>
       <c r="AT148">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="AU148">
         <v>2</v>
@@ -31981,25 +31981,25 @@
         <v>1.48</v>
       </c>
       <c r="AN149">
-        <v>1.11</v>
+        <v>0.61</v>
       </c>
       <c r="AO149">
-        <v>0.44</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AP149">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ149">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR149">
-        <v>1.18</v>
+        <v>1.1</v>
       </c>
       <c r="AS149">
-        <v>1.07</v>
+        <v>1.25</v>
       </c>
       <c r="AT149">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AU149">
         <v>8</v>
@@ -32187,25 +32187,25 @@
         <v>1.75</v>
       </c>
       <c r="AN150">
-        <v>2.78</v>
+        <v>2.11</v>
       </c>
       <c r="AO150">
+        <v>1.83</v>
+      </c>
+      <c r="AP150">
+        <v>2.26</v>
+      </c>
+      <c r="AQ150">
         <v>1.67</v>
       </c>
-      <c r="AP150">
-        <v>2.71</v>
-      </c>
-      <c r="AQ150">
-        <v>1.62</v>
-      </c>
       <c r="AR150">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="AS150">
-        <v>1.42</v>
+        <v>1.59</v>
       </c>
       <c r="AT150">
-        <v>3.21</v>
+        <v>3.28</v>
       </c>
       <c r="AU150">
         <v>7</v>
@@ -32393,25 +32393,25 @@
         <v>1.45</v>
       </c>
       <c r="AN151">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AO151">
-        <v>1.11</v>
+        <v>1.5</v>
       </c>
       <c r="AP151">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ151">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR151">
-        <v>1.23</v>
+        <v>1.09</v>
       </c>
       <c r="AS151">
-        <v>1.05</v>
+        <v>1.33</v>
       </c>
       <c r="AT151">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="AU151">
         <v>2</v>
@@ -32599,22 +32599,22 @@
         <v>1.5</v>
       </c>
       <c r="AN152">
-        <v>2.22</v>
+        <v>1.5</v>
       </c>
       <c r="AO152">
-        <v>1.89</v>
+        <v>2.06</v>
       </c>
       <c r="AP152">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ152">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR152">
-        <v>1.81</v>
+        <v>1.61</v>
       </c>
       <c r="AS152">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AT152">
         <v>3.43</v>
@@ -32805,25 +32805,25 @@
         <v>1.72</v>
       </c>
       <c r="AN153">
-        <v>1.33</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AO153">
-        <v>0.89</v>
+        <v>1.22</v>
       </c>
       <c r="AP153">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ153">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR153">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AS153">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="AT153">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AU153">
         <v>5</v>
@@ -33011,25 +33011,25 @@
         <v>1.48</v>
       </c>
       <c r="AN154">
-        <v>1.78</v>
+        <v>1.63</v>
       </c>
       <c r="AO154">
-        <v>1.44</v>
+        <v>2.16</v>
       </c>
       <c r="AP154">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ154">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR154">
-        <v>1.81</v>
+        <v>1.48</v>
       </c>
       <c r="AS154">
-        <v>1.61</v>
+        <v>1.7</v>
       </c>
       <c r="AT154">
-        <v>3.42</v>
+        <v>3.18</v>
       </c>
       <c r="AU154">
         <v>4</v>
@@ -33217,25 +33217,25 @@
         <v>1.38</v>
       </c>
       <c r="AN155">
-        <v>1.44</v>
+        <v>0.95</v>
       </c>
       <c r="AO155">
-        <v>0.7</v>
+        <v>1.26</v>
       </c>
       <c r="AP155">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ155">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR155">
-        <v>1.43</v>
+        <v>1.24</v>
       </c>
       <c r="AS155">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AT155">
-        <v>2.83</v>
+        <v>2.81</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33423,25 +33423,25 @@
         <v>3.4</v>
       </c>
       <c r="AN156">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="AO156">
-        <v>0.78</v>
+        <v>1.21</v>
       </c>
       <c r="AP156">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ156">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR156">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AS156">
-        <v>1.41</v>
+        <v>1.65</v>
       </c>
       <c r="AT156">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="AU156">
         <v>10</v>
@@ -33629,22 +33629,22 @@
         <v>1.93</v>
       </c>
       <c r="AN157">
-        <v>1.7</v>
+        <v>1.37</v>
       </c>
       <c r="AO157">
-        <v>0.67</v>
+        <v>1.26</v>
       </c>
       <c r="AP157">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR157">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AS157">
-        <v>0.96</v>
+        <v>1.08</v>
       </c>
       <c r="AT157">
         <v>2.5</v>
@@ -33835,25 +33835,25 @@
         <v>1.3</v>
       </c>
       <c r="AN158">
-        <v>1.89</v>
+        <v>1.58</v>
       </c>
       <c r="AO158">
-        <v>0.78</v>
+        <v>1.47</v>
       </c>
       <c r="AP158">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ158">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR158">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="AS158">
-        <v>1.41</v>
+        <v>1.58</v>
       </c>
       <c r="AT158">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="AU158">
         <v>4</v>
@@ -34041,25 +34041,25 @@
         <v>2.2</v>
       </c>
       <c r="AN159">
-        <v>1.56</v>
+        <v>1.16</v>
       </c>
       <c r="AO159">
-        <v>0.11</v>
+        <v>0.63</v>
       </c>
       <c r="AP159">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ159">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR159">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AS159">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT159">
-        <v>2.2</v>
+        <v>2.34</v>
       </c>
       <c r="AU159">
         <v>11</v>
@@ -34247,25 +34247,25 @@
         <v>1.5</v>
       </c>
       <c r="AN160">
-        <v>1.44</v>
+        <v>0.95</v>
       </c>
       <c r="AO160">
-        <v>0.5600000000000001</v>
+        <v>1.05</v>
       </c>
       <c r="AP160">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ160">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR160">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="AS160">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="AT160">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="AU160">
         <v>8</v>
@@ -34453,25 +34453,25 @@
         <v>2.95</v>
       </c>
       <c r="AN161">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="AO161">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AP161">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ161">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR161">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AS161">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AT161">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34659,25 +34659,25 @@
         <v>1.83</v>
       </c>
       <c r="AN162">
-        <v>1.8</v>
+        <v>1.25</v>
       </c>
       <c r="AO162">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="AP162">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ162">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR162">
-        <v>1.18</v>
+        <v>1.05</v>
       </c>
       <c r="AS162">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AT162">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="AU162">
         <v>7</v>
@@ -34865,25 +34865,25 @@
         <v>1.75</v>
       </c>
       <c r="AN163">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="AO163">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="AP163">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ163">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR163">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AS163">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="AT163">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AU163">
         <v>7</v>
@@ -35071,22 +35071,22 @@
         <v>2.3</v>
       </c>
       <c r="AN164">
-        <v>2.8</v>
+        <v>2.1</v>
       </c>
       <c r="AO164">
-        <v>0.8</v>
+        <v>1.25</v>
       </c>
       <c r="AP164">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ164">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR164">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="AS164">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="AT164">
         <v>3</v>
@@ -35277,25 +35277,25 @@
         <v>1.34</v>
       </c>
       <c r="AN165">
-        <v>1.89</v>
+        <v>1.35</v>
       </c>
       <c r="AO165">
-        <v>1</v>
+        <v>1.55</v>
       </c>
       <c r="AP165">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ165">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR165">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AS165">
-        <v>1.44</v>
+        <v>1.59</v>
       </c>
       <c r="AT165">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="AU165">
         <v>5</v>
@@ -35483,25 +35483,25 @@
         <v>1.21</v>
       </c>
       <c r="AN166">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="AO166">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AP166">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ166">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR166">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AS166">
-        <v>1.22</v>
+        <v>1.45</v>
       </c>
       <c r="AT166">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AU166">
         <v>8</v>
@@ -35689,25 +35689,25 @@
         <v>1.33</v>
       </c>
       <c r="AN167">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AO167">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AP167">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ167">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR167">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AS167">
-        <v>1.17</v>
+        <v>1.35</v>
       </c>
       <c r="AT167">
-        <v>2.24</v>
+        <v>2.44</v>
       </c>
       <c r="AU167">
         <v>4</v>
@@ -35895,25 +35895,25 @@
         <v>1.32</v>
       </c>
       <c r="AN168">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AO168">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AP168">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ168">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR168">
-        <v>1.71</v>
+        <v>1.54</v>
       </c>
       <c r="AS168">
-        <v>1.6</v>
+        <v>1.81</v>
       </c>
       <c r="AT168">
-        <v>3.31</v>
+        <v>3.35</v>
       </c>
       <c r="AU168">
         <v>6</v>
@@ -36101,25 +36101,25 @@
         <v>1.62</v>
       </c>
       <c r="AN169">
-        <v>1.5</v>
+        <v>1.05</v>
       </c>
       <c r="AO169">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="AP169">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ169">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR169">
-        <v>1.59</v>
+        <v>1.46</v>
       </c>
       <c r="AS169">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
       <c r="AT169">
-        <v>2.87</v>
+        <v>2.89</v>
       </c>
       <c r="AU169">
         <v>8</v>
@@ -36307,25 +36307,25 @@
         <v>1.72</v>
       </c>
       <c r="AN170">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AO170">
-        <v>0.91</v>
+        <v>1.29</v>
       </c>
       <c r="AP170">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ170">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR170">
-        <v>1.54</v>
+        <v>1.34</v>
       </c>
       <c r="AS170">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="AT170">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="AU170">
         <v>4</v>
@@ -36513,25 +36513,25 @@
         <v>1.41</v>
       </c>
       <c r="AN171">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AO171">
-        <v>0.6</v>
+        <v>1.14</v>
       </c>
       <c r="AP171">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ171">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR171">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="AS171">
-        <v>1.34</v>
+        <v>1.5</v>
       </c>
       <c r="AT171">
-        <v>2.42</v>
+        <v>2.6</v>
       </c>
       <c r="AU171">
         <v>2</v>
@@ -36719,25 +36719,25 @@
         <v>1.41</v>
       </c>
       <c r="AN172">
-        <v>1.64</v>
+        <v>1.29</v>
       </c>
       <c r="AO172">
-        <v>1.4</v>
+        <v>2.14</v>
       </c>
       <c r="AP172">
+        <v>1.19</v>
+      </c>
+      <c r="AQ172">
+        <v>2.26</v>
+      </c>
+      <c r="AR172">
         <v>1.43</v>
       </c>
-      <c r="AQ172">
-        <v>1.77</v>
-      </c>
-      <c r="AR172">
-        <v>1.56</v>
-      </c>
       <c r="AS172">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AT172">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="AU172">
         <v>3</v>
@@ -36925,25 +36925,25 @@
         <v>5.25</v>
       </c>
       <c r="AN173">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO173">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="AP173">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ173">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR173">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AS173">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AT173">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="AU173">
         <v>10</v>
@@ -37131,25 +37131,25 @@
         <v>1.26</v>
       </c>
       <c r="AN174">
-        <v>1.3</v>
+        <v>0.86</v>
       </c>
       <c r="AO174">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AP174">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ174">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR174">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
       <c r="AS174">
-        <v>1.37</v>
+        <v>1.54</v>
       </c>
       <c r="AT174">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AU174">
         <v>4</v>
@@ -37337,25 +37337,25 @@
         <v>2.45</v>
       </c>
       <c r="AN175">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="AO175">
-        <v>0.73</v>
+        <v>1.19</v>
       </c>
       <c r="AP175">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ175">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR175">
-        <v>1.74</v>
+        <v>1.58</v>
       </c>
       <c r="AS175">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="AT175">
-        <v>2.97</v>
+        <v>2.84</v>
       </c>
       <c r="AU175">
         <v>10</v>
@@ -37543,25 +37543,25 @@
         <v>1.77</v>
       </c>
       <c r="AN176">
-        <v>1.4</v>
+        <v>1.05</v>
       </c>
       <c r="AO176">
-        <v>0.7</v>
+        <v>1.33</v>
       </c>
       <c r="AP176">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ176">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR176">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AS176">
-        <v>0.93</v>
+        <v>1.07</v>
       </c>
       <c r="AT176">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="AU176">
         <v>3</v>
@@ -37749,25 +37749,25 @@
         <v>2.05</v>
       </c>
       <c r="AN177">
+        <v>1.57</v>
+      </c>
+      <c r="AO177">
+        <v>1.1</v>
+      </c>
+      <c r="AP177">
+        <v>1.63</v>
+      </c>
+      <c r="AQ177">
+        <v>1.11</v>
+      </c>
+      <c r="AR177">
+        <v>1.45</v>
+      </c>
+      <c r="AS177">
         <v>1.7</v>
       </c>
-      <c r="AO177">
-        <v>0.7</v>
-      </c>
-      <c r="AP177">
-        <v>1.93</v>
-      </c>
-      <c r="AQ177">
-        <v>0.85</v>
-      </c>
-      <c r="AR177">
-        <v>1.71</v>
-      </c>
-      <c r="AS177">
-        <v>1.48</v>
-      </c>
       <c r="AT177">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="AU177">
         <v>8</v>
@@ -37955,25 +37955,25 @@
         <v>1.41</v>
       </c>
       <c r="AN178">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="AO178">
+        <v>1.64</v>
+      </c>
+      <c r="AP178">
+        <v>0.93</v>
+      </c>
+      <c r="AQ178">
+        <v>1.63</v>
+      </c>
+      <c r="AR178">
         <v>1.45</v>
       </c>
-      <c r="AP178">
-        <v>1.23</v>
-      </c>
-      <c r="AQ178">
-        <v>1.31</v>
-      </c>
-      <c r="AR178">
-        <v>1.57</v>
-      </c>
       <c r="AS178">
-        <v>1.23</v>
+        <v>1.46</v>
       </c>
       <c r="AT178">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="AU178">
         <v>5</v>
@@ -38161,25 +38161,25 @@
         <v>1.33</v>
       </c>
       <c r="AN179">
-        <v>1.45</v>
+        <v>1.05</v>
       </c>
       <c r="AO179">
-        <v>1.55</v>
+        <v>2.18</v>
       </c>
       <c r="AP179">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ179">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR179">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AS179">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="AT179">
-        <v>3.67</v>
+        <v>3.48</v>
       </c>
       <c r="AU179">
         <v>6</v>
@@ -38367,25 +38367,25 @@
         <v>1.78</v>
       </c>
       <c r="AN180">
-        <v>1.7</v>
+        <v>1.27</v>
       </c>
       <c r="AO180">
-        <v>0.82</v>
+        <v>1.23</v>
       </c>
       <c r="AP180">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ180">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR180">
-        <v>1.69</v>
+        <v>1.55</v>
       </c>
       <c r="AS180">
-        <v>1.39</v>
+        <v>1.52</v>
       </c>
       <c r="AT180">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="AU180">
         <v>5</v>
@@ -38573,25 +38573,25 @@
         <v>4.4</v>
       </c>
       <c r="AN181">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="AO181">
-        <v>0.45</v>
+        <v>0.82</v>
       </c>
       <c r="AP181">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ181">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR181">
-        <v>2.05</v>
+        <v>1.82</v>
       </c>
       <c r="AS181">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AT181">
-        <v>3.2</v>
+        <v>3.08</v>
       </c>
       <c r="AU181">
         <v>8</v>
@@ -38779,25 +38779,25 @@
         <v>1.65</v>
       </c>
       <c r="AN182">
-        <v>1.91</v>
+        <v>1.41</v>
       </c>
       <c r="AO182">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AP182">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ182">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR182">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AS182">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AT182">
-        <v>2.33</v>
+        <v>2.19</v>
       </c>
       <c r="AU182">
         <v>7</v>
@@ -38985,25 +38985,25 @@
         <v>1.13</v>
       </c>
       <c r="AN183">
-        <v>1.09</v>
+        <v>0.59</v>
       </c>
       <c r="AO183">
-        <v>1.18</v>
+        <v>1.68</v>
       </c>
       <c r="AP183">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ183">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR183">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="AS183">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="AT183">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="AU183">
         <v>5</v>
@@ -39194,22 +39194,22 @@
         <v>1.64</v>
       </c>
       <c r="AO184">
-        <v>0.9</v>
+        <v>1.23</v>
       </c>
       <c r="AP184">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ184">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR184">
-        <v>1.69</v>
+        <v>1.54</v>
       </c>
       <c r="AS184">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="AT184">
-        <v>2.98</v>
+        <v>2.95</v>
       </c>
       <c r="AU184">
         <v>7</v>
@@ -39397,25 +39397,25 @@
         <v>1.51</v>
       </c>
       <c r="AN185">
-        <v>1.7</v>
+        <v>1.14</v>
       </c>
       <c r="AO185">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="AP185">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ185">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR185">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AS185">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="AT185">
-        <v>2.44</v>
+        <v>2.58</v>
       </c>
       <c r="AU185">
         <v>3</v>
@@ -39603,25 +39603,25 @@
         <v>1.52</v>
       </c>
       <c r="AN186">
-        <v>1.64</v>
+        <v>1.13</v>
       </c>
       <c r="AO186">
-        <v>0.82</v>
+        <v>1.17</v>
       </c>
       <c r="AP186">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ186">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR186">
-        <v>1.34</v>
+        <v>1.27</v>
       </c>
       <c r="AS186">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AT186">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AU186">
         <v>2</v>
@@ -39809,25 +39809,25 @@
         <v>2.2</v>
       </c>
       <c r="AN187">
-        <v>1.64</v>
+        <v>1.26</v>
       </c>
       <c r="AO187">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AP187">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ187">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR187">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="AS187">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AT187">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="AU187">
         <v>11</v>
@@ -40015,25 +40015,25 @@
         <v>1.95</v>
       </c>
       <c r="AN188">
-        <v>1.64</v>
+        <v>1.22</v>
       </c>
       <c r="AO188">
-        <v>0.91</v>
+        <v>1.48</v>
       </c>
       <c r="AP188">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ188">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR188">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AS188">
-        <v>0.97</v>
+        <v>1.1</v>
       </c>
       <c r="AT188">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="AU188">
         <v>4</v>
@@ -40221,25 +40221,25 @@
         <v>3.25</v>
       </c>
       <c r="AN189">
-        <v>2.82</v>
+        <v>2.22</v>
       </c>
       <c r="AO189">
-        <v>0.09</v>
+        <v>0.57</v>
       </c>
       <c r="AP189">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ189">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR189">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AS189">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="AT189">
-        <v>2.82</v>
+        <v>2.89</v>
       </c>
       <c r="AU189">
         <v>6</v>
@@ -40427,25 +40427,25 @@
         <v>1.23</v>
       </c>
       <c r="AN190">
-        <v>1.82</v>
+        <v>1.61</v>
       </c>
       <c r="AO190">
-        <v>1.91</v>
+        <v>2.09</v>
       </c>
       <c r="AP190">
+        <v>1.63</v>
+      </c>
+      <c r="AQ190">
         <v>1.93</v>
       </c>
-      <c r="AQ190">
-        <v>1.69</v>
-      </c>
       <c r="AR190">
-        <v>1.72</v>
+        <v>1.47</v>
       </c>
       <c r="AS190">
-        <v>1.6</v>
+        <v>1.84</v>
       </c>
       <c r="AT190">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="AU190">
         <v>4</v>
@@ -40633,25 +40633,25 @@
         <v>2.7</v>
       </c>
       <c r="AN191">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="AO191">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AP191">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ191">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR191">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AS191">
-        <v>1.3</v>
+        <v>1.47</v>
       </c>
       <c r="AT191">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="AU191">
         <v>3</v>
@@ -40839,25 +40839,25 @@
         <v>1.53</v>
       </c>
       <c r="AN192">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="AO192">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AP192">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ192">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR192">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AS192">
-        <v>1.39</v>
+        <v>1.54</v>
       </c>
       <c r="AT192">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="AU192">
         <v>8</v>
@@ -41045,25 +41045,25 @@
         <v>1.35</v>
       </c>
       <c r="AN193">
-        <v>1.18</v>
+        <v>0.83</v>
       </c>
       <c r="AO193">
-        <v>0.64</v>
+        <v>1</v>
       </c>
       <c r="AP193">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ193">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR193">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AS193">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="AT193">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="AU193">
         <v>4</v>
@@ -41251,25 +41251,25 @@
         <v>1.55</v>
       </c>
       <c r="AN194">
+        <v>1.13</v>
+      </c>
+      <c r="AO194">
         <v>1.5</v>
       </c>
-      <c r="AO194">
-        <v>1.25</v>
-      </c>
       <c r="AP194">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ194">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR194">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="AS194">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="AT194">
-        <v>2.79</v>
+        <v>2.89</v>
       </c>
       <c r="AU194">
         <v>8</v>
@@ -41457,25 +41457,25 @@
         <v>3.25</v>
       </c>
       <c r="AN195">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AO195">
-        <v>0.67</v>
+        <v>1.21</v>
       </c>
       <c r="AP195">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ195">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR195">
-        <v>2.09</v>
+        <v>1.87</v>
       </c>
       <c r="AS195">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="AT195">
-        <v>3.3</v>
+        <v>3.11</v>
       </c>
       <c r="AU195">
         <v>5</v>
@@ -41663,25 +41663,25 @@
         <v>1.44</v>
       </c>
       <c r="AN196">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="AO196">
-        <v>0.67</v>
+        <v>0.96</v>
       </c>
       <c r="AP196">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ196">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR196">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="AS196">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AT196">
-        <v>2.37</v>
+        <v>2.58</v>
       </c>
       <c r="AU196">
         <v>5</v>
@@ -41869,25 +41869,25 @@
         <v>2.25</v>
       </c>
       <c r="AN197">
-        <v>2.83</v>
+        <v>2.25</v>
       </c>
       <c r="AO197">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="AP197">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ197">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR197">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AS197">
-        <v>1.42</v>
+        <v>1.53</v>
       </c>
       <c r="AT197">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="AU197">
         <v>7</v>
@@ -42075,25 +42075,25 @@
         <v>1.68</v>
       </c>
       <c r="AN198">
-        <v>1.75</v>
+        <v>1.63</v>
       </c>
       <c r="AO198">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AP198">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ198">
-        <v>1.31</v>
+        <v>1.63</v>
       </c>
       <c r="AR198">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AS198">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AT198">
-        <v>2.93</v>
+        <v>2.98</v>
       </c>
       <c r="AU198">
         <v>5</v>
@@ -42281,25 +42281,25 @@
         <v>1.16</v>
       </c>
       <c r="AN199">
-        <v>1.08</v>
+        <v>0.79</v>
       </c>
       <c r="AO199">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AP199">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ199">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR199">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AS199">
-        <v>1.44</v>
+        <v>1.61</v>
       </c>
       <c r="AT199">
-        <v>2.78</v>
+        <v>2.85</v>
       </c>
       <c r="AU199">
         <v>3</v>
@@ -42487,25 +42487,25 @@
         <v>2.05</v>
       </c>
       <c r="AN200">
-        <v>1.33</v>
+        <v>1.08</v>
       </c>
       <c r="AO200">
-        <v>0.92</v>
+        <v>1.46</v>
       </c>
       <c r="AP200">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ200">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR200">
-        <v>1.89</v>
+        <v>1.74</v>
       </c>
       <c r="AS200">
-        <v>1.02</v>
+        <v>1.12</v>
       </c>
       <c r="AT200">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AU200">
         <v>10</v>
@@ -42693,25 +42693,25 @@
         <v>1.22</v>
       </c>
       <c r="AN201">
-        <v>1</v>
+        <v>0.54</v>
       </c>
       <c r="AO201">
-        <v>0.92</v>
+        <v>1.33</v>
       </c>
       <c r="AP201">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AQ201">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR201">
-        <v>1.28</v>
+        <v>1.16</v>
       </c>
       <c r="AS201">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AT201">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="AU201">
         <v>4</v>
@@ -42899,25 +42899,25 @@
         <v>1.18</v>
       </c>
       <c r="AN202">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="AO202">
-        <v>1.67</v>
+        <v>2.28</v>
       </c>
       <c r="AP202">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AQ202">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="AR202">
-        <v>1.22</v>
+        <v>1.13</v>
       </c>
       <c r="AS202">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="AT202">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="AU202">
         <v>4</v>
@@ -43105,25 +43105,25 @@
         <v>1.77</v>
       </c>
       <c r="AN203">
-        <v>1.75</v>
+        <v>1.16</v>
       </c>
       <c r="AO203">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AP203">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="AQ203">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="AR203">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AS203">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT203">
-        <v>2.43</v>
+        <v>2.36</v>
       </c>
       <c r="AU203">
         <v>5</v>
@@ -43311,25 +43311,25 @@
         <v>2.15</v>
       </c>
       <c r="AN204">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AO204">
-        <v>0.5</v>
+        <v>0.76</v>
       </c>
       <c r="AP204">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ204">
-        <v>0.46</v>
+        <v>0.74</v>
       </c>
       <c r="AR204">
-        <v>1.66</v>
+        <v>1.43</v>
       </c>
       <c r="AS204">
-        <v>1.13</v>
+        <v>1.24</v>
       </c>
       <c r="AT204">
-        <v>2.79</v>
+        <v>2.67</v>
       </c>
       <c r="AU204">
         <v>10</v>
@@ -43517,25 +43517,25 @@
         <v>1.17</v>
       </c>
       <c r="AN205">
-        <v>1.25</v>
+        <v>0.92</v>
       </c>
       <c r="AO205">
-        <v>1.75</v>
+        <v>2.04</v>
       </c>
       <c r="AP205">
-        <v>1.23</v>
+        <v>0.93</v>
       </c>
       <c r="AQ205">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="AR205">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AS205">
-        <v>1.67</v>
+        <v>1.88</v>
       </c>
       <c r="AT205">
-        <v>3.27</v>
+        <v>3.31</v>
       </c>
       <c r="AU205">
         <v>4</v>
@@ -43723,25 +43723,25 @@
         <v>2.65</v>
       </c>
       <c r="AN206">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AO206">
-        <v>0.08</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP206">
-        <v>1.85</v>
+        <v>1.52</v>
       </c>
       <c r="AQ206">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR206">
-        <v>1.54</v>
+        <v>1.42</v>
       </c>
       <c r="AS206">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="AT206">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="AU206">
         <v>4</v>
@@ -43929,25 +43929,25 @@
         <v>2.25</v>
       </c>
       <c r="AN207">
-        <v>2.25</v>
+        <v>1.84</v>
       </c>
       <c r="AO207">
-        <v>0.75</v>
+        <v>1.12</v>
       </c>
       <c r="AP207">
-        <v>2.08</v>
+        <v>1.81</v>
       </c>
       <c r="AQ207">
-        <v>0.92</v>
+        <v>1.19</v>
       </c>
       <c r="AR207">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="AS207">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="AT207">
-        <v>3.24</v>
+        <v>3.12</v>
       </c>
       <c r="AU207">
         <v>9</v>
@@ -44135,25 +44135,25 @@
         <v>1.49</v>
       </c>
       <c r="AN208">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="AO208">
-        <v>1.5</v>
+        <v>1.68</v>
       </c>
       <c r="AP208">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AQ208">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AR208">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AS208">
-        <v>1.39</v>
+        <v>1.53</v>
       </c>
       <c r="AT208">
-        <v>3.11</v>
+        <v>3.08</v>
       </c>
       <c r="AU208">
         <v>6</v>
@@ -44341,25 +44341,25 @@
         <v>1.62</v>
       </c>
       <c r="AN209">
-        <v>1.58</v>
+        <v>1.16</v>
       </c>
       <c r="AO209">
-        <v>0.83</v>
+        <v>1.16</v>
       </c>
       <c r="AP209">
-        <v>1.54</v>
+        <v>1.15</v>
       </c>
       <c r="AQ209">
-        <v>0.85</v>
+        <v>1.11</v>
       </c>
       <c r="AR209">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AS209">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AT209">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AU209">
         <v>10</v>
@@ -44547,25 +44547,25 @@
         <v>1.77</v>
       </c>
       <c r="AN210">
-        <v>1.46</v>
+        <v>1.19</v>
       </c>
       <c r="AO210">
-        <v>0.62</v>
+        <v>0.92</v>
       </c>
       <c r="AP210">
-        <v>1.43</v>
+        <v>1.19</v>
       </c>
       <c r="AQ210">
-        <v>0.64</v>
+        <v>0.93</v>
       </c>
       <c r="AR210">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="AS210">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="AT210">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AU210">
         <v>2</v>
@@ -44753,25 +44753,25 @@
         <v>2</v>
       </c>
       <c r="AN211">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="AO211">
-        <v>0.08</v>
+        <v>0.54</v>
       </c>
       <c r="AP211">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AQ211">
-        <v>0.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AR211">
-        <v>1.1</v>
+        <v>1.17</v>
       </c>
       <c r="AS211">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
       <c r="AT211">
-        <v>2.19</v>
+        <v>2.36</v>
       </c>
       <c r="AU211">
         <v>3</v>
@@ -44959,25 +44959,25 @@
         <v>1.68</v>
       </c>
       <c r="AN212">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AO212">
-        <v>0.92</v>
+        <v>1.27</v>
       </c>
       <c r="AP212">
-        <v>1.36</v>
+        <v>1.11</v>
       </c>
       <c r="AQ212">
-        <v>1.07</v>
+        <v>1.33</v>
       </c>
       <c r="AR212">
-        <v>1.93</v>
+        <v>1.74</v>
       </c>
       <c r="AS212">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="AT212">
-        <v>3.33</v>
+        <v>3.3</v>
       </c>
       <c r="AU212">
         <v>5</v>
@@ -45165,25 +45165,25 @@
         <v>1.82</v>
       </c>
       <c r="AN213">
-        <v>2</v>
+        <v>1.65</v>
       </c>
       <c r="AO213">
-        <v>0.62</v>
+        <v>1.23</v>
       </c>
       <c r="AP213">
-        <v>1.93</v>
+        <v>1.63</v>
       </c>
       <c r="AQ213">
-        <v>0.64</v>
+        <v>1.22</v>
       </c>
       <c r="AR213">
-        <v>1.7</v>
+        <v>1.46</v>
       </c>
       <c r="AS213">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AT213">
-        <v>2.88</v>
+        <v>2.71</v>
       </c>
       <c r="AU213">
         <v>10</v>
@@ -45371,25 +45371,25 @@
         <v>3.4</v>
       </c>
       <c r="AN214">
-        <v>2.31</v>
+        <v>2</v>
       </c>
       <c r="AO214">
-        <v>0.85</v>
+        <v>1.35</v>
       </c>
       <c r="AP214">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AQ214">
-        <v>1</v>
+        <v>1.41</v>
       </c>
       <c r="AR214">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="AS214">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="AT214">
-        <v>3.13</v>
+        <v>3.02</v>
       </c>
       <c r="AU214">
         <v>7</v>
@@ -45577,25 +45577,25 @@
         <v>2.2</v>
       </c>
       <c r="AN215">
-        <v>2.85</v>
+        <v>2.31</v>
       </c>
       <c r="AO215">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AP215">
-        <v>2.71</v>
+        <v>2.26</v>
       </c>
       <c r="AQ215">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
       <c r="AR215">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AS215">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AT215">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
       <c r="AU215">
         <v>3</v>
@@ -45783,25 +45783,25 @@
         <v>1.46</v>
       </c>
       <c r="AN216">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="AO216">
-        <v>1.46</v>
+        <v>1.77</v>
       </c>
       <c r="AP216">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ216">
-        <v>1.57</v>
+        <v>1.81</v>
       </c>
       <c r="AR216">
-        <v>1.66</v>
+        <v>1.51</v>
       </c>
       <c r="AS216">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AT216">
-        <v>3.12</v>
+        <v>3.15</v>
       </c>
       <c r="AU216">
         <v>6</v>
@@ -45989,25 +45989,25 @@
         <v>1.35</v>
       </c>
       <c r="AN217">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AO217">
-        <v>0.77</v>
+        <v>1.15</v>
       </c>
       <c r="AP217">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="AQ217">
-        <v>0.79</v>
+        <v>1.15</v>
       </c>
       <c r="AR217">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="AS217">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AT217">
-        <v>2.77</v>
+        <v>2.81</v>
       </c>
       <c r="AU217">
         <v>6</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1364" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="332">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -736,6 +736,9 @@
     <t>['47', '58']</t>
   </si>
   <si>
+    <t>['89']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -821,9 +824,6 @@
   </si>
   <si>
     <t>['28']</t>
-  </si>
-  <si>
-    <t>['89']</t>
   </si>
   <si>
     <t>['24', '81']</t>
@@ -1371,7 +1371,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1627,7 +1627,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ6">
         <v>1.41</v>
@@ -2657,7 +2657,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ8">
         <v>1.63</v>
@@ -3481,7 +3481,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3768,7 +3768,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ12">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR12">
         <v>1.07</v>
@@ -3893,7 +3893,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3974,7 +3974,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ13">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR13">
         <v>0.27</v>
@@ -4099,7 +4099,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4305,7 +4305,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4717,7 +4717,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5335,7 +5335,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5747,7 +5747,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5825,7 +5825,7 @@
         <v>0.5</v>
       </c>
       <c r="AP22">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ22">
         <v>1.93</v>
@@ -5953,7 +5953,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6237,7 +6237,7 @@
         <v>1.5</v>
       </c>
       <c r="AP24">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ24">
         <v>1.52</v>
@@ -6365,7 +6365,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6652,7 +6652,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ26">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR26">
         <v>1.53</v>
@@ -6777,7 +6777,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6858,7 +6858,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ27">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR27">
         <v>0.65</v>
@@ -6983,7 +6983,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7189,7 +7189,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -8219,7 +8219,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8631,7 +8631,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9327,7 +9327,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ39">
         <v>0.74</v>
@@ -9533,7 +9533,7 @@
         <v>2</v>
       </c>
       <c r="AP40">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ40">
         <v>1.11</v>
@@ -9661,7 +9661,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9742,7 +9742,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ41">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR41">
         <v>1.23</v>
@@ -9867,7 +9867,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -11103,7 +11103,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11309,7 +11309,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11390,7 +11390,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ49">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR49">
         <v>1.67</v>
@@ -11515,7 +11515,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11721,7 +11721,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12417,7 +12417,7 @@
         <v>0.17</v>
       </c>
       <c r="AP54">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ54">
         <v>0.5600000000000001</v>
@@ -12751,7 +12751,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -12832,7 +12832,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ56">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR56">
         <v>1.53</v>
@@ -13163,7 +13163,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13369,7 +13369,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13656,7 +13656,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ60">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR60">
         <v>1.54</v>
@@ -13781,7 +13781,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14271,7 +14271,7 @@
         <v>1.57</v>
       </c>
       <c r="AP63">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ63">
         <v>1.19</v>
@@ -14605,7 +14605,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14889,7 +14889,7 @@
         <v>1.63</v>
       </c>
       <c r="AP66">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ66">
         <v>1.93</v>
@@ -15095,7 +15095,7 @@
         <v>1.38</v>
       </c>
       <c r="AP67">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ67">
         <v>1.19</v>
@@ -15223,7 +15223,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15429,7 +15429,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16253,7 +16253,7 @@
         <v>94</v>
       </c>
       <c r="P73" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="Q73">
         <v>2.27</v>
@@ -16952,7 +16952,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ76">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR76">
         <v>1.29</v>
@@ -17158,7 +17158,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ77">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR77">
         <v>1.25</v>
@@ -19009,7 +19009,7 @@
         <v>1.1</v>
       </c>
       <c r="AP86">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ86">
         <v>0.93</v>
@@ -19424,7 +19424,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ88">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR88">
         <v>0.98</v>
@@ -20039,7 +20039,7 @@
         <v>1.09</v>
       </c>
       <c r="AP91">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ91">
         <v>1.22</v>
@@ -21072,7 +21072,7 @@
         <v>1.52</v>
       </c>
       <c r="AQ96">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR96">
         <v>1.29</v>
@@ -22305,7 +22305,7 @@
         <v>1.92</v>
       </c>
       <c r="AP102">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ102">
         <v>1.63</v>
@@ -22514,7 +22514,7 @@
         <v>1.15</v>
       </c>
       <c r="AQ103">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR103">
         <v>1.46</v>
@@ -23747,7 +23747,7 @@
         <v>1.38</v>
       </c>
       <c r="AP109">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ109">
         <v>1.11</v>
@@ -24368,7 +24368,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ112">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR112">
         <v>1.55</v>
@@ -25395,10 +25395,10 @@
         <v>1.21</v>
       </c>
       <c r="AP117">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ117">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR117">
         <v>1.81</v>
@@ -26837,7 +26837,7 @@
         <v>1.4</v>
       </c>
       <c r="AP124">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ124">
         <v>1.41</v>
@@ -27046,7 +27046,7 @@
         <v>0.93</v>
       </c>
       <c r="AQ125">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR125">
         <v>1.34</v>
@@ -28073,7 +28073,7 @@
         <v>1.06</v>
       </c>
       <c r="AP130">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ130">
         <v>0.74</v>
@@ -28900,7 +28900,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ134">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR134">
         <v>1.49</v>
@@ -30136,7 +30136,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ140">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR140">
         <v>1.24</v>
@@ -30548,7 +30548,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ142">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR142">
         <v>1.81</v>
@@ -30673,7 +30673,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -31575,7 +31575,7 @@
         <v>1</v>
       </c>
       <c r="AP147">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ147">
         <v>0.93</v>
@@ -32193,7 +32193,7 @@
         <v>1.83</v>
       </c>
       <c r="AP150">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ150">
         <v>1.67</v>
@@ -33020,7 +33020,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ154">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR154">
         <v>1.48</v>
@@ -33226,7 +33226,7 @@
         <v>0.74</v>
       </c>
       <c r="AQ155">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR155">
         <v>1.24</v>
@@ -35077,7 +35077,7 @@
         <v>1.25</v>
       </c>
       <c r="AP164">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ164">
         <v>1.22</v>
@@ -35283,7 +35283,7 @@
         <v>1.55</v>
       </c>
       <c r="AP165">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ165">
         <v>1.81</v>
@@ -35411,7 +35411,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -36316,7 +36316,7 @@
         <v>1.52</v>
       </c>
       <c r="AQ170">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR170">
         <v>1.34</v>
@@ -36441,7 +36441,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36728,7 +36728,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ172">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR172">
         <v>1.43</v>
@@ -38170,7 +38170,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ179">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR179">
         <v>1.73</v>
@@ -38373,7 +38373,7 @@
         <v>1.23</v>
       </c>
       <c r="AP180">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ180">
         <v>1.15</v>
@@ -39815,7 +39815,7 @@
         <v>1.22</v>
       </c>
       <c r="AP187">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ187">
         <v>1.19</v>
@@ -39943,7 +39943,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40227,7 +40227,7 @@
         <v>0.57</v>
       </c>
       <c r="AP189">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ189">
         <v>0.5600000000000001</v>
@@ -41875,7 +41875,7 @@
         <v>1.21</v>
       </c>
       <c r="AP197">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ197">
         <v>1.15</v>
@@ -42702,7 +42702,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ201">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR201">
         <v>1.16</v>
@@ -42908,7 +42908,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ202">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AR202">
         <v>1.13</v>
@@ -44141,7 +44141,7 @@
         <v>1.68</v>
       </c>
       <c r="AP208">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AQ208">
         <v>1.67</v>
@@ -44968,7 +44968,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ212">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AR212">
         <v>1.74</v>
@@ -45583,7 +45583,7 @@
         <v>1.54</v>
       </c>
       <c r="AP215">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="AQ215">
         <v>1.52</v>
@@ -45917,7 +45917,7 @@
         <v>144</v>
       </c>
       <c r="P217" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="Q217">
         <v>3.75</v>
@@ -46074,6 +46074,212 @@
       </c>
       <c r="BP217">
         <v>1.37</v>
+      </c>
+    </row>
+    <row r="218" spans="1:68">
+      <c r="A218" s="1">
+        <v>217</v>
+      </c>
+      <c r="B218">
+        <v>7453641</v>
+      </c>
+      <c r="C218" t="s">
+        <v>68</v>
+      </c>
+      <c r="D218" t="s">
+        <v>69</v>
+      </c>
+      <c r="E218" s="2">
+        <v>45716.69791666666</v>
+      </c>
+      <c r="F218">
+        <v>28</v>
+      </c>
+      <c r="G218" t="s">
+        <v>76</v>
+      </c>
+      <c r="H218" t="s">
+        <v>74</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>1</v>
+      </c>
+      <c r="M218">
+        <v>1</v>
+      </c>
+      <c r="N218">
+        <v>2</v>
+      </c>
+      <c r="O218" t="s">
+        <v>240</v>
+      </c>
+      <c r="P218" t="s">
+        <v>118</v>
+      </c>
+      <c r="Q218">
+        <v>3.3</v>
+      </c>
+      <c r="R218">
+        <v>2.15</v>
+      </c>
+      <c r="S218">
+        <v>2.85</v>
+      </c>
+      <c r="T218">
+        <v>1.34</v>
+      </c>
+      <c r="U218">
+        <v>2.95</v>
+      </c>
+      <c r="V218">
+        <v>2.5</v>
+      </c>
+      <c r="W218">
+        <v>1.46</v>
+      </c>
+      <c r="X218">
+        <v>6</v>
+      </c>
+      <c r="Y218">
+        <v>1.11</v>
+      </c>
+      <c r="Z218">
+        <v>2.63</v>
+      </c>
+      <c r="AA218">
+        <v>3.45</v>
+      </c>
+      <c r="AB218">
+        <v>2.51</v>
+      </c>
+      <c r="AC218">
+        <v>1.02</v>
+      </c>
+      <c r="AD218">
+        <v>9</v>
+      </c>
+      <c r="AE218">
+        <v>1.21</v>
+      </c>
+      <c r="AF218">
+        <v>3.74</v>
+      </c>
+      <c r="AG218">
+        <v>1.8</v>
+      </c>
+      <c r="AH218">
+        <v>1.94</v>
+      </c>
+      <c r="AI218">
+        <v>1.62</v>
+      </c>
+      <c r="AJ218">
+        <v>2.15</v>
+      </c>
+      <c r="AK218">
+        <v>1.57</v>
+      </c>
+      <c r="AL218">
+        <v>1.3</v>
+      </c>
+      <c r="AM218">
+        <v>1.4</v>
+      </c>
+      <c r="AN218">
+        <v>1.33</v>
+      </c>
+      <c r="AO218">
+        <v>2.26</v>
+      </c>
+      <c r="AP218">
+        <v>1.32</v>
+      </c>
+      <c r="AQ218">
+        <v>2.21</v>
+      </c>
+      <c r="AR218">
+        <v>1.57</v>
+      </c>
+      <c r="AS218">
+        <v>1.74</v>
+      </c>
+      <c r="AT218">
+        <v>3.31</v>
+      </c>
+      <c r="AU218">
+        <v>7</v>
+      </c>
+      <c r="AV218">
+        <v>4</v>
+      </c>
+      <c r="AW218">
+        <v>6</v>
+      </c>
+      <c r="AX218">
+        <v>8</v>
+      </c>
+      <c r="AY218">
+        <v>13</v>
+      </c>
+      <c r="AZ218">
+        <v>13</v>
+      </c>
+      <c r="BA218">
+        <v>3</v>
+      </c>
+      <c r="BB218">
+        <v>4</v>
+      </c>
+      <c r="BC218">
+        <v>7</v>
+      </c>
+      <c r="BD218">
+        <v>2.02</v>
+      </c>
+      <c r="BE218">
+        <v>6.4</v>
+      </c>
+      <c r="BF218">
+        <v>1.97</v>
+      </c>
+      <c r="BG218">
+        <v>1.34</v>
+      </c>
+      <c r="BH218">
+        <v>2.9</v>
+      </c>
+      <c r="BI218">
+        <v>1.58</v>
+      </c>
+      <c r="BJ218">
+        <v>2.18</v>
+      </c>
+      <c r="BK218">
+        <v>1.95</v>
+      </c>
+      <c r="BL218">
+        <v>1.74</v>
+      </c>
+      <c r="BM218">
+        <v>2.45</v>
+      </c>
+      <c r="BN218">
+        <v>1.48</v>
+      </c>
+      <c r="BO218">
+        <v>3.2</v>
+      </c>
+      <c r="BP218">
+        <v>1.28</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="336">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -739,6 +739,12 @@
     <t>['89']</t>
   </si>
   <si>
+    <t>['11', '20', '75', '81']</t>
+  </si>
+  <si>
+    <t>['28', '32', '53', '86']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1010,6 +1016,12 @@
   </si>
   <si>
     <t>['33', '70']</t>
+  </si>
+  <si>
+    <t>['29']</t>
+  </si>
+  <si>
+    <t>['45', '70']</t>
   </si>
 </sst>
 </file>
@@ -1371,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP218"/>
+  <dimension ref="A1:BP222"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1627,7 +1639,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1705,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ2">
         <v>1.19</v>
@@ -1911,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ3">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2326,7 +2338,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ5">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2657,7 +2669,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2735,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ7">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2944,7 +2956,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ8">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3150,7 +3162,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ9">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3353,7 +3365,7 @@
         <v>1</v>
       </c>
       <c r="AP10">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ10">
         <v>0.5600000000000001</v>
@@ -3481,7 +3493,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3893,7 +3905,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3971,7 +3983,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ13">
         <v>1.32</v>
@@ -4099,7 +4111,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4177,7 +4189,7 @@
         <v>3</v>
       </c>
       <c r="AP14">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ14">
         <v>1.67</v>
@@ -4305,7 +4317,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4383,10 +4395,10 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ15">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR15">
         <v>1.51</v>
@@ -4592,7 +4604,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ16">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR16">
         <v>0.59</v>
@@ -4717,7 +4729,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4795,10 +4807,10 @@
         <v>1</v>
       </c>
       <c r="AP17">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ17">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR17">
         <v>1.15</v>
@@ -5207,10 +5219,10 @@
         <v>1.5</v>
       </c>
       <c r="AP19">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ19">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR19">
         <v>0.96</v>
@@ -5335,7 +5347,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5416,7 +5428,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ20">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR20">
         <v>1.54</v>
@@ -5747,7 +5759,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5828,7 +5840,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ22">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR22">
         <v>1.86</v>
@@ -5953,7 +5965,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6031,10 +6043,10 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ23">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR23">
         <v>1.91</v>
@@ -6240,7 +6252,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ24">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR24">
         <v>1.69</v>
@@ -6365,7 +6377,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6443,7 +6455,7 @@
         <v>0.5</v>
       </c>
       <c r="AP25">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ25">
         <v>0.5600000000000001</v>
@@ -6649,7 +6661,7 @@
         <v>2</v>
       </c>
       <c r="AP26">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ26">
         <v>1.32</v>
@@ -6777,7 +6789,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6983,7 +6995,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7061,10 +7073,10 @@
         <v>2.33</v>
       </c>
       <c r="AP28">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ28">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR28">
         <v>0.85</v>
@@ -7189,7 +7201,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7473,10 +7485,10 @@
         <v>2</v>
       </c>
       <c r="AP30">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ30">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR30">
         <v>1.89</v>
@@ -7682,7 +7694,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ31">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR31">
         <v>1.17</v>
@@ -7885,7 +7897,7 @@
         <v>1.67</v>
       </c>
       <c r="AP32">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ32">
         <v>1.41</v>
@@ -8091,7 +8103,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ33">
         <v>1.11</v>
@@ -8219,7 +8231,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8503,7 +8515,7 @@
         <v>0.5</v>
       </c>
       <c r="AP35">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ35">
         <v>1.19</v>
@@ -8631,7 +8643,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8709,10 +8721,10 @@
         <v>1</v>
       </c>
       <c r="AP36">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ36">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR36">
         <v>1.32</v>
@@ -8915,10 +8927,10 @@
         <v>1.75</v>
       </c>
       <c r="AP37">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ37">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR37">
         <v>0.96</v>
@@ -9330,7 +9342,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ39">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR39">
         <v>1.48</v>
@@ -9661,7 +9673,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9867,7 +9879,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9948,7 +9960,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ42">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR42">
         <v>0.87</v>
@@ -10357,10 +10369,10 @@
         <v>1</v>
       </c>
       <c r="AP44">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ44">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR44">
         <v>1.7</v>
@@ -10563,10 +10575,10 @@
         <v>1.2</v>
       </c>
       <c r="AP45">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ45">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR45">
         <v>1.25</v>
@@ -10769,7 +10781,7 @@
         <v>2.5</v>
       </c>
       <c r="AP46">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ46">
         <v>1.67</v>
@@ -10975,10 +10987,10 @@
         <v>0.4</v>
       </c>
       <c r="AP47">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ47">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR47">
         <v>1.38</v>
@@ -11103,7 +11115,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11181,7 +11193,7 @@
         <v>1.33</v>
       </c>
       <c r="AP48">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ48">
         <v>1.41</v>
@@ -11309,7 +11321,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11387,7 +11399,7 @@
         <v>2</v>
       </c>
       <c r="AP49">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ49">
         <v>2.21</v>
@@ -11515,7 +11527,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11593,10 +11605,10 @@
         <v>1.67</v>
       </c>
       <c r="AP50">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ50">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR50">
         <v>1.44</v>
@@ -11721,7 +11733,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12005,10 +12017,10 @@
         <v>1.5</v>
       </c>
       <c r="AP52">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ52">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR52">
         <v>1.75</v>
@@ -12211,7 +12223,7 @@
         <v>1.67</v>
       </c>
       <c r="AP53">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ53">
         <v>1.22</v>
@@ -12623,7 +12635,7 @@
         <v>1.33</v>
       </c>
       <c r="AP55">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ55">
         <v>1.19</v>
@@ -12751,7 +12763,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13038,7 +13050,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ57">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR57">
         <v>0.8</v>
@@ -13163,7 +13175,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13244,7 +13256,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ58">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR58">
         <v>0.93</v>
@@ -13369,7 +13381,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13450,7 +13462,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ59">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR59">
         <v>1.54</v>
@@ -13781,7 +13793,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13859,10 +13871,10 @@
         <v>1.67</v>
       </c>
       <c r="AP61">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ61">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR61">
         <v>1.8</v>
@@ -14068,7 +14080,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ62">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR62">
         <v>1.27</v>
@@ -14274,7 +14286,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ63">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR63">
         <v>1.83</v>
@@ -14480,7 +14492,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ64">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR64">
         <v>1.38</v>
@@ -14605,7 +14617,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14683,10 +14695,10 @@
         <v>1.86</v>
       </c>
       <c r="AP65">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ65">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR65">
         <v>1.48</v>
@@ -14892,7 +14904,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ66">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR66">
         <v>1.53</v>
@@ -15223,7 +15235,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15429,7 +15441,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15507,7 +15519,7 @@
         <v>1.63</v>
       </c>
       <c r="AP69">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ69">
         <v>1.67</v>
@@ -15713,7 +15725,7 @@
         <v>0.13</v>
       </c>
       <c r="AP70">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ70">
         <v>0.5600000000000001</v>
@@ -15919,10 +15931,10 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ71">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR71">
         <v>1.62</v>
@@ -16125,7 +16137,7 @@
         <v>1.38</v>
       </c>
       <c r="AP72">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ72">
         <v>1.22</v>
@@ -16331,10 +16343,10 @@
         <v>1.13</v>
       </c>
       <c r="AP73">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ73">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR73">
         <v>1.49</v>
@@ -16459,7 +16471,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16949,7 +16961,7 @@
         <v>2.44</v>
       </c>
       <c r="AP76">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ76">
         <v>2.21</v>
@@ -17155,7 +17167,7 @@
         <v>1.56</v>
       </c>
       <c r="AP77">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ77">
         <v>1.32</v>
@@ -17567,10 +17579,10 @@
         <v>0.89</v>
       </c>
       <c r="AP79">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ79">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR79">
         <v>1.66</v>
@@ -17773,10 +17785,10 @@
         <v>1.44</v>
       </c>
       <c r="AP80">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ80">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR80">
         <v>1.87</v>
@@ -17979,10 +17991,10 @@
         <v>1.78</v>
       </c>
       <c r="AP81">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ81">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR81">
         <v>1.06</v>
@@ -18313,7 +18325,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18394,7 +18406,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ83">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR83">
         <v>1.65</v>
@@ -18597,10 +18609,10 @@
         <v>1.5</v>
       </c>
       <c r="AP84">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ84">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR84">
         <v>1.47</v>
@@ -18803,10 +18815,10 @@
         <v>1.7</v>
       </c>
       <c r="AP85">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ85">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR85">
         <v>1.56</v>
@@ -18931,7 +18943,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19012,7 +19024,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ86">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR86">
         <v>1.9</v>
@@ -19218,7 +19230,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ87">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR87">
         <v>1.33</v>
@@ -19630,7 +19642,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ89">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR89">
         <v>1.35</v>
@@ -19833,7 +19845,7 @@
         <v>0.45</v>
       </c>
       <c r="AP90">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ90">
         <v>0.5600000000000001</v>
@@ -19961,7 +19973,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20167,7 +20179,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20245,7 +20257,7 @@
         <v>1.55</v>
       </c>
       <c r="AP92">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ92">
         <v>1.19</v>
@@ -20451,7 +20463,7 @@
         <v>1.36</v>
       </c>
       <c r="AP93">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ93">
         <v>1.11</v>
@@ -20579,7 +20591,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20657,7 +20669,7 @@
         <v>1.55</v>
       </c>
       <c r="AP94">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ94">
         <v>1.67</v>
@@ -20863,7 +20875,7 @@
         <v>1.36</v>
       </c>
       <c r="AP95">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ95">
         <v>1.41</v>
@@ -20991,7 +21003,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21069,7 +21081,7 @@
         <v>2.27</v>
       </c>
       <c r="AP96">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ96">
         <v>2.21</v>
@@ -21197,7 +21209,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21275,10 +21287,10 @@
         <v>0.82</v>
       </c>
       <c r="AP97">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ97">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR97">
         <v>1.58</v>
@@ -21484,7 +21496,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ98">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR98">
         <v>1.65</v>
@@ -21609,7 +21621,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21690,7 +21702,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ99">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR99">
         <v>1.03</v>
@@ -21815,7 +21827,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21896,7 +21908,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ100">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR100">
         <v>1.28</v>
@@ -22021,7 +22033,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22102,7 +22114,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ101">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR101">
         <v>1.44</v>
@@ -22308,7 +22320,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ102">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR102">
         <v>1.85</v>
@@ -22511,7 +22523,7 @@
         <v>1.17</v>
       </c>
       <c r="AP103">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ103">
         <v>1.32</v>
@@ -22720,7 +22732,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ104">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR104">
         <v>1.52</v>
@@ -22926,7 +22938,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ105">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR105">
         <v>0.9</v>
@@ -23051,7 +23063,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23129,7 +23141,7 @@
         <v>1.62</v>
       </c>
       <c r="AP106">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ106">
         <v>1.19</v>
@@ -23257,7 +23269,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23335,10 +23347,10 @@
         <v>1.77</v>
       </c>
       <c r="AP107">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ107">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR107">
         <v>1.24</v>
@@ -23463,7 +23475,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23541,7 +23553,7 @@
         <v>1.15</v>
       </c>
       <c r="AP108">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ108">
         <v>1.22</v>
@@ -23875,7 +23887,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -23953,7 +23965,7 @@
         <v>1.54</v>
       </c>
       <c r="AP110">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ110">
         <v>1.67</v>
@@ -24159,7 +24171,7 @@
         <v>1.38</v>
       </c>
       <c r="AP111">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ111">
         <v>1.41</v>
@@ -24365,7 +24377,7 @@
         <v>2.38</v>
       </c>
       <c r="AP112">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ112">
         <v>2.21</v>
@@ -24493,7 +24505,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24574,7 +24586,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ113">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR113">
         <v>0.91</v>
@@ -24777,10 +24789,10 @@
         <v>1.21</v>
       </c>
       <c r="AP114">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ114">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR114">
         <v>1.49</v>
@@ -24983,10 +24995,10 @@
         <v>1.21</v>
       </c>
       <c r="AP115">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ115">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR115">
         <v>1.86</v>
@@ -25192,7 +25204,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ116">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR116">
         <v>1.04</v>
@@ -25729,7 +25741,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25810,7 +25822,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ119">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR119">
         <v>1.29</v>
@@ -26016,7 +26028,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ120">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR120">
         <v>1.53</v>
@@ -26222,7 +26234,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ121">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR121">
         <v>1.63</v>
@@ -26347,7 +26359,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26425,7 +26437,7 @@
         <v>1.6</v>
       </c>
       <c r="AP122">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ122">
         <v>1.19</v>
@@ -26631,10 +26643,10 @@
         <v>1.2</v>
       </c>
       <c r="AP123">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ123">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR123">
         <v>1.86</v>
@@ -26965,7 +26977,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27043,7 +27055,7 @@
         <v>2.27</v>
       </c>
       <c r="AP125">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ125">
         <v>2.21</v>
@@ -27377,7 +27389,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27458,7 +27470,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ127">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR127">
         <v>0.96</v>
@@ -27661,10 +27673,10 @@
         <v>1.8</v>
       </c>
       <c r="AP128">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ128">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR128">
         <v>1.55</v>
@@ -27789,7 +27801,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27870,7 +27882,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ129">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR129">
         <v>1.65</v>
@@ -27995,7 +28007,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28076,7 +28088,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ130">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR130">
         <v>1.78</v>
@@ -28407,7 +28419,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28488,7 +28500,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ132">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR132">
         <v>1.42</v>
@@ -28691,10 +28703,10 @@
         <v>1.13</v>
       </c>
       <c r="AP133">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ133">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR133">
         <v>1.33</v>
@@ -28819,7 +28831,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28897,7 +28909,7 @@
         <v>1.13</v>
       </c>
       <c r="AP134">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ134">
         <v>1.32</v>
@@ -29103,10 +29115,10 @@
         <v>1.44</v>
       </c>
       <c r="AP135">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ135">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR135">
         <v>1.47</v>
@@ -29231,7 +29243,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29515,7 +29527,7 @@
         <v>1.38</v>
       </c>
       <c r="AP137">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ137">
         <v>1.11</v>
@@ -29724,7 +29736,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ138">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR138">
         <v>1.43</v>
@@ -30261,7 +30273,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30339,10 +30351,10 @@
         <v>1.24</v>
       </c>
       <c r="AP141">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ141">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR141">
         <v>1.24</v>
@@ -30545,7 +30557,7 @@
         <v>2.24</v>
       </c>
       <c r="AP142">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ142">
         <v>2.21</v>
@@ -30673,7 +30685,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30751,7 +30763,7 @@
         <v>1.29</v>
       </c>
       <c r="AP143">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ143">
         <v>1.11</v>
@@ -30879,7 +30891,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -30957,7 +30969,7 @@
         <v>1.76</v>
       </c>
       <c r="AP144">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ144">
         <v>1.67</v>
@@ -31163,10 +31175,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="AP145">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ145">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR145">
         <v>1.33</v>
@@ -31291,7 +31303,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31578,7 +31590,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ147">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR147">
         <v>1.56</v>
@@ -31703,7 +31715,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31781,10 +31793,10 @@
         <v>1.56</v>
       </c>
       <c r="AP148">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ148">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR148">
         <v>1.1</v>
@@ -31909,7 +31921,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -31990,7 +32002,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ149">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR149">
         <v>1.1</v>
@@ -32402,7 +32414,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ151">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR151">
         <v>1.09</v>
@@ -32527,7 +32539,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32605,10 +32617,10 @@
         <v>2.06</v>
       </c>
       <c r="AP152">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ152">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR152">
         <v>1.61</v>
@@ -32811,7 +32823,7 @@
         <v>1.22</v>
       </c>
       <c r="AP153">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ153">
         <v>1.22</v>
@@ -32939,7 +32951,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33017,7 +33029,7 @@
         <v>2.16</v>
       </c>
       <c r="AP154">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ154">
         <v>2.21</v>
@@ -33145,7 +33157,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33223,7 +33235,7 @@
         <v>1.26</v>
       </c>
       <c r="AP155">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ155">
         <v>1.32</v>
@@ -33351,7 +33363,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33429,7 +33441,7 @@
         <v>1.21</v>
       </c>
       <c r="AP156">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ156">
         <v>1.11</v>
@@ -33763,7 +33775,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -33841,10 +33853,10 @@
         <v>1.47</v>
       </c>
       <c r="AP158">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ158">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR158">
         <v>1.38</v>
@@ -34175,7 +34187,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34253,10 +34265,10 @@
         <v>1.05</v>
       </c>
       <c r="AP160">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ160">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR160">
         <v>1.41</v>
@@ -34381,7 +34393,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34462,7 +34474,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ161">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR161">
         <v>1.55</v>
@@ -34668,7 +34680,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ162">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR162">
         <v>1.05</v>
@@ -34793,7 +34805,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34874,7 +34886,7 @@
         <v>1.11</v>
       </c>
       <c r="AQ163">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR163">
         <v>1.67</v>
@@ -35205,7 +35217,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35286,7 +35298,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ165">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR165">
         <v>1.58</v>
@@ -35411,7 +35423,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35492,7 +35504,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ166">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR166">
         <v>1.15</v>
@@ -35695,10 +35707,10 @@
         <v>1.5</v>
       </c>
       <c r="AP167">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ167">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR167">
         <v>1.09</v>
@@ -35823,7 +35835,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -35904,7 +35916,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ168">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR168">
         <v>1.54</v>
@@ -36107,7 +36119,7 @@
         <v>1.35</v>
       </c>
       <c r="AP169">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ169">
         <v>1.19</v>
@@ -36313,7 +36325,7 @@
         <v>1.29</v>
       </c>
       <c r="AP170">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ170">
         <v>1.32</v>
@@ -36441,7 +36453,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36519,10 +36531,10 @@
         <v>1.14</v>
       </c>
       <c r="AP171">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ171">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR171">
         <v>1.1</v>
@@ -36647,7 +36659,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36853,7 +36865,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36931,7 +36943,7 @@
         <v>0.62</v>
       </c>
       <c r="AP173">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ173">
         <v>0.5600000000000001</v>
@@ -37059,7 +37071,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37137,7 +37149,7 @@
         <v>1.57</v>
       </c>
       <c r="AP174">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ174">
         <v>1.67</v>
@@ -37343,7 +37355,7 @@
         <v>1.19</v>
       </c>
       <c r="AP175">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ175">
         <v>1.22</v>
@@ -37471,7 +37483,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37549,7 +37561,7 @@
         <v>1.33</v>
       </c>
       <c r="AP176">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ176">
         <v>1.41</v>
@@ -37677,7 +37689,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37755,7 +37767,7 @@
         <v>1.1</v>
       </c>
       <c r="AP177">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ177">
         <v>1.11</v>
@@ -37961,10 +37973,10 @@
         <v>1.64</v>
       </c>
       <c r="AP178">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ178">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR178">
         <v>1.45</v>
@@ -38089,7 +38101,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38295,7 +38307,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38376,7 +38388,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ180">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR180">
         <v>1.55</v>
@@ -38579,10 +38591,10 @@
         <v>0.82</v>
       </c>
       <c r="AP181">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ181">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR181">
         <v>1.82</v>
@@ -38788,7 +38800,7 @@
         <v>1.41</v>
       </c>
       <c r="AQ182">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR182">
         <v>1.09</v>
@@ -38913,7 +38925,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -38994,7 +39006,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AQ183">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR183">
         <v>1.19</v>
@@ -39119,7 +39131,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39406,7 +39418,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ185">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR185">
         <v>1.25</v>
@@ -39818,7 +39830,7 @@
         <v>1.32</v>
       </c>
       <c r="AQ187">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR187">
         <v>1.54</v>
@@ -39943,7 +39955,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40021,7 +40033,7 @@
         <v>1.48</v>
       </c>
       <c r="AP188">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ188">
         <v>1.41</v>
@@ -40433,10 +40445,10 @@
         <v>2.09</v>
       </c>
       <c r="AP190">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ190">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR190">
         <v>1.47</v>
@@ -40561,7 +40573,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40639,10 +40651,10 @@
         <v>1</v>
       </c>
       <c r="AP191">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ191">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR191">
         <v>1.61</v>
@@ -40845,7 +40857,7 @@
         <v>1.7</v>
       </c>
       <c r="AP192">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ192">
         <v>1.67</v>
@@ -40973,7 +40985,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41051,7 +41063,7 @@
         <v>1</v>
       </c>
       <c r="AP193">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ193">
         <v>1.11</v>
@@ -41179,7 +41191,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41260,7 +41272,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ194">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR194">
         <v>1.49</v>
@@ -41463,7 +41475,7 @@
         <v>1.21</v>
       </c>
       <c r="AP195">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ195">
         <v>1.22</v>
@@ -41669,10 +41681,10 @@
         <v>0.96</v>
       </c>
       <c r="AP196">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ196">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR196">
         <v>1.12</v>
@@ -41878,7 +41890,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ197">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR197">
         <v>1.72</v>
@@ -42084,7 +42096,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ198">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AR198">
         <v>1.53</v>
@@ -42209,7 +42221,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42287,10 +42299,10 @@
         <v>1.79</v>
       </c>
       <c r="AP199">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ199">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR199">
         <v>1.24</v>
@@ -42415,7 +42427,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42827,7 +42839,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -43033,7 +43045,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43114,7 +43126,7 @@
         <v>1.22</v>
       </c>
       <c r="AQ203">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AR203">
         <v>1.23</v>
@@ -43239,7 +43251,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43317,10 +43329,10 @@
         <v>0.76</v>
       </c>
       <c r="AP204">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ204">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AR204">
         <v>1.43</v>
@@ -43445,7 +43457,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43523,10 +43535,10 @@
         <v>2.04</v>
       </c>
       <c r="AP205">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AQ205">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AR205">
         <v>1.43</v>
@@ -43651,7 +43663,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -43729,7 +43741,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP206">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AQ206">
         <v>0.5600000000000001</v>
@@ -43935,7 +43947,7 @@
         <v>1.12</v>
       </c>
       <c r="AP207">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AQ207">
         <v>1.19</v>
@@ -44347,7 +44359,7 @@
         <v>1.16</v>
       </c>
       <c r="AP209">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AQ209">
         <v>1.11</v>
@@ -44556,7 +44568,7 @@
         <v>1.19</v>
       </c>
       <c r="AQ210">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="AR210">
         <v>1.51</v>
@@ -44759,7 +44771,7 @@
         <v>0.54</v>
       </c>
       <c r="AP211">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AQ211">
         <v>0.5600000000000001</v>
@@ -44887,7 +44899,7 @@
         <v>227</v>
       </c>
       <c r="P212" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q212">
         <v>2.75</v>
@@ -45093,7 +45105,7 @@
         <v>239</v>
       </c>
       <c r="P213" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -45171,7 +45183,7 @@
         <v>1.23</v>
       </c>
       <c r="AP213">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AQ213">
         <v>1.22</v>
@@ -45299,7 +45311,7 @@
         <v>86</v>
       </c>
       <c r="P214" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q214">
         <v>1.71</v>
@@ -45377,7 +45389,7 @@
         <v>1.35</v>
       </c>
       <c r="AP214">
-        <v>1.93</v>
+        <v>1.89</v>
       </c>
       <c r="AQ214">
         <v>1.41</v>
@@ -45586,7 +45598,7 @@
         <v>2.21</v>
       </c>
       <c r="AQ215">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AR215">
         <v>1.73</v>
@@ -45711,7 +45723,7 @@
         <v>87</v>
       </c>
       <c r="P216" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q216">
         <v>3.25</v>
@@ -45792,7 +45804,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ216">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AR216">
         <v>1.51</v>
@@ -45995,10 +46007,10 @@
         <v>1.15</v>
       </c>
       <c r="AP217">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="AQ217">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AR217">
         <v>1.24</v>
@@ -46280,6 +46292,830 @@
       </c>
       <c r="BP218">
         <v>1.28</v>
+      </c>
+    </row>
+    <row r="219" spans="1:68">
+      <c r="A219" s="1">
+        <v>218</v>
+      </c>
+      <c r="B219">
+        <v>7454763</v>
+      </c>
+      <c r="C219" t="s">
+        <v>68</v>
+      </c>
+      <c r="D219" t="s">
+        <v>69</v>
+      </c>
+      <c r="E219" s="2">
+        <v>45717.5</v>
+      </c>
+      <c r="F219">
+        <v>28</v>
+      </c>
+      <c r="G219" t="s">
+        <v>85</v>
+      </c>
+      <c r="H219" t="s">
+        <v>70</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>1</v>
+      </c>
+      <c r="K219">
+        <v>1</v>
+      </c>
+      <c r="L219">
+        <v>1</v>
+      </c>
+      <c r="M219">
+        <v>1</v>
+      </c>
+      <c r="N219">
+        <v>2</v>
+      </c>
+      <c r="O219" t="s">
+        <v>88</v>
+      </c>
+      <c r="P219" t="s">
+        <v>334</v>
+      </c>
+      <c r="Q219">
+        <v>4.33</v>
+      </c>
+      <c r="R219">
+        <v>2.38</v>
+      </c>
+      <c r="S219">
+        <v>2.38</v>
+      </c>
+      <c r="T219">
+        <v>1.3</v>
+      </c>
+      <c r="U219">
+        <v>3.4</v>
+      </c>
+      <c r="V219">
+        <v>2.5</v>
+      </c>
+      <c r="W219">
+        <v>1.5</v>
+      </c>
+      <c r="X219">
+        <v>6</v>
+      </c>
+      <c r="Y219">
+        <v>1.13</v>
+      </c>
+      <c r="Z219">
+        <v>3.56</v>
+      </c>
+      <c r="AA219">
+        <v>3.65</v>
+      </c>
+      <c r="AB219">
+        <v>1.94</v>
+      </c>
+      <c r="AC219">
+        <v>1.04</v>
+      </c>
+      <c r="AD219">
+        <v>10</v>
+      </c>
+      <c r="AE219">
+        <v>1.22</v>
+      </c>
+      <c r="AF219">
+        <v>4.2</v>
+      </c>
+      <c r="AG219">
+        <v>1.82</v>
+      </c>
+      <c r="AH219">
+        <v>1.92</v>
+      </c>
+      <c r="AI219">
+        <v>1.62</v>
+      </c>
+      <c r="AJ219">
+        <v>2.2</v>
+      </c>
+      <c r="AK219">
+        <v>1.98</v>
+      </c>
+      <c r="AL219">
+        <v>1.26</v>
+      </c>
+      <c r="AM219">
+        <v>1.22</v>
+      </c>
+      <c r="AN219">
+        <v>1.52</v>
+      </c>
+      <c r="AO219">
+        <v>1.93</v>
+      </c>
+      <c r="AP219">
+        <v>1.5</v>
+      </c>
+      <c r="AQ219">
+        <v>1.89</v>
+      </c>
+      <c r="AR219">
+        <v>1.44</v>
+      </c>
+      <c r="AS219">
+        <v>1.89</v>
+      </c>
+      <c r="AT219">
+        <v>3.33</v>
+      </c>
+      <c r="AU219">
+        <v>7</v>
+      </c>
+      <c r="AV219">
+        <v>4</v>
+      </c>
+      <c r="AW219">
+        <v>11</v>
+      </c>
+      <c r="AX219">
+        <v>7</v>
+      </c>
+      <c r="AY219">
+        <v>23</v>
+      </c>
+      <c r="AZ219">
+        <v>13</v>
+      </c>
+      <c r="BA219">
+        <v>6</v>
+      </c>
+      <c r="BB219">
+        <v>7</v>
+      </c>
+      <c r="BC219">
+        <v>13</v>
+      </c>
+      <c r="BD219">
+        <v>2.65</v>
+      </c>
+      <c r="BE219">
+        <v>6.75</v>
+      </c>
+      <c r="BF219">
+        <v>1.58</v>
+      </c>
+      <c r="BG219">
+        <v>1.33</v>
+      </c>
+      <c r="BH219">
+        <v>2.95</v>
+      </c>
+      <c r="BI219">
+        <v>1.57</v>
+      </c>
+      <c r="BJ219">
+        <v>2.23</v>
+      </c>
+      <c r="BK219">
+        <v>1.94</v>
+      </c>
+      <c r="BL219">
+        <v>1.76</v>
+      </c>
+      <c r="BM219">
+        <v>2.43</v>
+      </c>
+      <c r="BN219">
+        <v>1.49</v>
+      </c>
+      <c r="BO219">
+        <v>3.15</v>
+      </c>
+      <c r="BP219">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:68">
+      <c r="A220" s="1">
+        <v>219</v>
+      </c>
+      <c r="B220">
+        <v>7453638</v>
+      </c>
+      <c r="C220" t="s">
+        <v>68</v>
+      </c>
+      <c r="D220" t="s">
+        <v>69</v>
+      </c>
+      <c r="E220" s="2">
+        <v>45717.5</v>
+      </c>
+      <c r="F220">
+        <v>28</v>
+      </c>
+      <c r="G220" t="s">
+        <v>83</v>
+      </c>
+      <c r="H220" t="s">
+        <v>82</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>0</v>
+      </c>
+      <c r="K220">
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>0</v>
+      </c>
+      <c r="M220">
+        <v>0</v>
+      </c>
+      <c r="N220">
+        <v>0</v>
+      </c>
+      <c r="O220" t="s">
+        <v>87</v>
+      </c>
+      <c r="P220" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q220">
+        <v>2.95</v>
+      </c>
+      <c r="R220">
+        <v>2.1</v>
+      </c>
+      <c r="S220">
+        <v>3.3</v>
+      </c>
+      <c r="T220">
+        <v>1.38</v>
+      </c>
+      <c r="U220">
+        <v>2.8</v>
+      </c>
+      <c r="V220">
+        <v>2.75</v>
+      </c>
+      <c r="W220">
+        <v>1.39</v>
+      </c>
+      <c r="X220">
+        <v>7</v>
+      </c>
+      <c r="Y220">
+        <v>1.08</v>
+      </c>
+      <c r="Z220">
+        <v>2.35</v>
+      </c>
+      <c r="AA220">
+        <v>3.39</v>
+      </c>
+      <c r="AB220">
+        <v>2.86</v>
+      </c>
+      <c r="AC220">
+        <v>1.06</v>
+      </c>
+      <c r="AD220">
+        <v>8.5</v>
+      </c>
+      <c r="AE220">
+        <v>1.33</v>
+      </c>
+      <c r="AF220">
+        <v>3.25</v>
+      </c>
+      <c r="AG220">
+        <v>1.89</v>
+      </c>
+      <c r="AH220">
+        <v>1.85</v>
+      </c>
+      <c r="AI220">
+        <v>1.73</v>
+      </c>
+      <c r="AJ220">
+        <v>1.95</v>
+      </c>
+      <c r="AK220">
+        <v>1.41</v>
+      </c>
+      <c r="AL220">
+        <v>1.31</v>
+      </c>
+      <c r="AM220">
+        <v>1.53</v>
+      </c>
+      <c r="AN220">
+        <v>1.15</v>
+      </c>
+      <c r="AO220">
+        <v>1.63</v>
+      </c>
+      <c r="AP220">
+        <v>1.14</v>
+      </c>
+      <c r="AQ220">
+        <v>1.61</v>
+      </c>
+      <c r="AR220">
+        <v>1.56</v>
+      </c>
+      <c r="AS220">
+        <v>1.5</v>
+      </c>
+      <c r="AT220">
+        <v>3.06</v>
+      </c>
+      <c r="AU220">
+        <v>11</v>
+      </c>
+      <c r="AV220">
+        <v>5</v>
+      </c>
+      <c r="AW220">
+        <v>11</v>
+      </c>
+      <c r="AX220">
+        <v>4</v>
+      </c>
+      <c r="AY220">
+        <v>23</v>
+      </c>
+      <c r="AZ220">
+        <v>11</v>
+      </c>
+      <c r="BA220">
+        <v>2</v>
+      </c>
+      <c r="BB220">
+        <v>5</v>
+      </c>
+      <c r="BC220">
+        <v>7</v>
+      </c>
+      <c r="BD220">
+        <v>1.98</v>
+      </c>
+      <c r="BE220">
+        <v>6.4</v>
+      </c>
+      <c r="BF220">
+        <v>1.98</v>
+      </c>
+      <c r="BG220">
+        <v>1.29</v>
+      </c>
+      <c r="BH220">
+        <v>3.15</v>
+      </c>
+      <c r="BI220">
+        <v>1.5</v>
+      </c>
+      <c r="BJ220">
+        <v>2.35</v>
+      </c>
+      <c r="BK220">
+        <v>1.84</v>
+      </c>
+      <c r="BL220">
+        <v>1.84</v>
+      </c>
+      <c r="BM220">
+        <v>2.3</v>
+      </c>
+      <c r="BN220">
+        <v>1.54</v>
+      </c>
+      <c r="BO220">
+        <v>2.95</v>
+      </c>
+      <c r="BP220">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="221" spans="1:68">
+      <c r="A221" s="1">
+        <v>220</v>
+      </c>
+      <c r="B221">
+        <v>7453640</v>
+      </c>
+      <c r="C221" t="s">
+        <v>68</v>
+      </c>
+      <c r="D221" t="s">
+        <v>69</v>
+      </c>
+      <c r="E221" s="2">
+        <v>45717.59375</v>
+      </c>
+      <c r="F221">
+        <v>28</v>
+      </c>
+      <c r="G221" t="s">
+        <v>81</v>
+      </c>
+      <c r="H221" t="s">
+        <v>75</v>
+      </c>
+      <c r="I221">
+        <v>2</v>
+      </c>
+      <c r="J221">
+        <v>1</v>
+      </c>
+      <c r="K221">
+        <v>3</v>
+      </c>
+      <c r="L221">
+        <v>4</v>
+      </c>
+      <c r="M221">
+        <v>2</v>
+      </c>
+      <c r="N221">
+        <v>6</v>
+      </c>
+      <c r="O221" t="s">
+        <v>241</v>
+      </c>
+      <c r="P221" t="s">
+        <v>335</v>
+      </c>
+      <c r="Q221">
+        <v>2.25</v>
+      </c>
+      <c r="R221">
+        <v>2.2</v>
+      </c>
+      <c r="S221">
+        <v>4.5</v>
+      </c>
+      <c r="T221">
+        <v>1.35</v>
+      </c>
+      <c r="U221">
+        <v>2.95</v>
+      </c>
+      <c r="V221">
+        <v>2.5</v>
+      </c>
+      <c r="W221">
+        <v>1.46</v>
+      </c>
+      <c r="X221">
+        <v>6.25</v>
+      </c>
+      <c r="Y221">
+        <v>1.1</v>
+      </c>
+      <c r="Z221">
+        <v>1.77</v>
+      </c>
+      <c r="AA221">
+        <v>3.8</v>
+      </c>
+      <c r="AB221">
+        <v>4.1</v>
+      </c>
+      <c r="AC221">
+        <v>1.05</v>
+      </c>
+      <c r="AD221">
+        <v>9.5</v>
+      </c>
+      <c r="AE221">
+        <v>1.25</v>
+      </c>
+      <c r="AF221">
+        <v>3.75</v>
+      </c>
+      <c r="AG221">
+        <v>1.8</v>
+      </c>
+      <c r="AH221">
+        <v>1.94</v>
+      </c>
+      <c r="AI221">
+        <v>1.73</v>
+      </c>
+      <c r="AJ221">
+        <v>1.95</v>
+      </c>
+      <c r="AK221">
+        <v>1.2</v>
+      </c>
+      <c r="AL221">
+        <v>1.26</v>
+      </c>
+      <c r="AM221">
+        <v>2.05</v>
+      </c>
+      <c r="AN221">
+        <v>0.93</v>
+      </c>
+      <c r="AO221">
+        <v>0.74</v>
+      </c>
+      <c r="AP221">
+        <v>1</v>
+      </c>
+      <c r="AQ221">
+        <v>0.71</v>
+      </c>
+      <c r="AR221">
+        <v>1.4</v>
+      </c>
+      <c r="AS221">
+        <v>1.26</v>
+      </c>
+      <c r="AT221">
+        <v>2.66</v>
+      </c>
+      <c r="AU221">
+        <v>5</v>
+      </c>
+      <c r="AV221">
+        <v>8</v>
+      </c>
+      <c r="AW221">
+        <v>5</v>
+      </c>
+      <c r="AX221">
+        <v>8</v>
+      </c>
+      <c r="AY221">
+        <v>10</v>
+      </c>
+      <c r="AZ221">
+        <v>18</v>
+      </c>
+      <c r="BA221">
+        <v>3</v>
+      </c>
+      <c r="BB221">
+        <v>4</v>
+      </c>
+      <c r="BC221">
+        <v>7</v>
+      </c>
+      <c r="BD221">
+        <v>1.47</v>
+      </c>
+      <c r="BE221">
+        <v>7</v>
+      </c>
+      <c r="BF221">
+        <v>2.95</v>
+      </c>
+      <c r="BG221">
+        <v>1.21</v>
+      </c>
+      <c r="BH221">
+        <v>3.9</v>
+      </c>
+      <c r="BI221">
+        <v>1.38</v>
+      </c>
+      <c r="BJ221">
+        <v>2.8</v>
+      </c>
+      <c r="BK221">
+        <v>1.63</v>
+      </c>
+      <c r="BL221">
+        <v>2.15</v>
+      </c>
+      <c r="BM221">
+        <v>1.98</v>
+      </c>
+      <c r="BN221">
+        <v>1.73</v>
+      </c>
+      <c r="BO221">
+        <v>2.48</v>
+      </c>
+      <c r="BP221">
+        <v>1.47</v>
+      </c>
+    </row>
+    <row r="222" spans="1:68">
+      <c r="A222" s="1">
+        <v>221</v>
+      </c>
+      <c r="B222">
+        <v>7453635</v>
+      </c>
+      <c r="C222" t="s">
+        <v>68</v>
+      </c>
+      <c r="D222" t="s">
+        <v>69</v>
+      </c>
+      <c r="E222" s="2">
+        <v>45717.69791666666</v>
+      </c>
+      <c r="F222">
+        <v>28</v>
+      </c>
+      <c r="G222" t="s">
+        <v>78</v>
+      </c>
+      <c r="H222" t="s">
+        <v>71</v>
+      </c>
+      <c r="I222">
+        <v>2</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>2</v>
+      </c>
+      <c r="L222">
+        <v>4</v>
+      </c>
+      <c r="M222">
+        <v>1</v>
+      </c>
+      <c r="N222">
+        <v>5</v>
+      </c>
+      <c r="O222" t="s">
+        <v>242</v>
+      </c>
+      <c r="P222" t="s">
+        <v>196</v>
+      </c>
+      <c r="Q222">
+        <v>1.78</v>
+      </c>
+      <c r="R222">
+        <v>2.45</v>
+      </c>
+      <c r="S222">
+        <v>6.5</v>
+      </c>
+      <c r="T222">
+        <v>1.3</v>
+      </c>
+      <c r="U222">
+        <v>3.25</v>
+      </c>
+      <c r="V222">
+        <v>2.35</v>
+      </c>
+      <c r="W222">
+        <v>1.52</v>
+      </c>
+      <c r="X222">
+        <v>5.5</v>
+      </c>
+      <c r="Y222">
+        <v>1.13</v>
+      </c>
+      <c r="Z222">
+        <v>1.33</v>
+      </c>
+      <c r="AA222">
+        <v>5.2</v>
+      </c>
+      <c r="AB222">
+        <v>8.1</v>
+      </c>
+      <c r="AC222">
+        <v>1.03</v>
+      </c>
+      <c r="AD222">
+        <v>11</v>
+      </c>
+      <c r="AE222">
+        <v>1.2</v>
+      </c>
+      <c r="AF222">
+        <v>4.33</v>
+      </c>
+      <c r="AG222">
+        <v>1.66</v>
+      </c>
+      <c r="AH222">
+        <v>2.22</v>
+      </c>
+      <c r="AI222">
+        <v>1.95</v>
+      </c>
+      <c r="AJ222">
+        <v>1.73</v>
+      </c>
+      <c r="AK222">
+        <v>1.08</v>
+      </c>
+      <c r="AL222">
+        <v>1.16</v>
+      </c>
+      <c r="AM222">
+        <v>3.1</v>
+      </c>
+      <c r="AN222">
+        <v>1.81</v>
+      </c>
+      <c r="AO222">
+        <v>1.19</v>
+      </c>
+      <c r="AP222">
+        <v>1.86</v>
+      </c>
+      <c r="AQ222">
+        <v>1.14</v>
+      </c>
+      <c r="AR222">
+        <v>1.62</v>
+      </c>
+      <c r="AS222">
+        <v>1.17</v>
+      </c>
+      <c r="AT222">
+        <v>2.79</v>
+      </c>
+      <c r="AU222">
+        <v>14</v>
+      </c>
+      <c r="AV222">
+        <v>3</v>
+      </c>
+      <c r="AW222">
+        <v>7</v>
+      </c>
+      <c r="AX222">
+        <v>2</v>
+      </c>
+      <c r="AY222">
+        <v>25</v>
+      </c>
+      <c r="AZ222">
+        <v>5</v>
+      </c>
+      <c r="BA222">
+        <v>2</v>
+      </c>
+      <c r="BB222">
+        <v>5</v>
+      </c>
+      <c r="BC222">
+        <v>7</v>
+      </c>
+      <c r="BD222">
+        <v>1.27</v>
+      </c>
+      <c r="BE222">
+        <v>8</v>
+      </c>
+      <c r="BF222">
+        <v>3.95</v>
+      </c>
+      <c r="BG222">
+        <v>1.3</v>
+      </c>
+      <c r="BH222">
+        <v>3.15</v>
+      </c>
+      <c r="BI222">
+        <v>1.5</v>
+      </c>
+      <c r="BJ222">
+        <v>2.33</v>
+      </c>
+      <c r="BK222">
+        <v>1.83</v>
+      </c>
+      <c r="BL222">
+        <v>1.85</v>
+      </c>
+      <c r="BM222">
+        <v>2.3</v>
+      </c>
+      <c r="BN222">
+        <v>1.53</v>
+      </c>
+      <c r="BO222">
+        <v>2.9</v>
+      </c>
+      <c r="BP222">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -1717,10 +1717,10 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ2">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1923,10 +1923,10 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ3">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2129,10 +2129,10 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2335,10 +2335,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ5">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2541,10 +2541,10 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ6">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2747,10 +2747,10 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ7">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -2953,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ8">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3159,10 +3159,10 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ9">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3359,25 +3359,25 @@
         <v>3.75</v>
       </c>
       <c r="AN10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP10">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ10">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR10">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AS10">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="AT10">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AU10">
         <v>5</v>
@@ -3565,25 +3565,25 @@
         <v>1.9</v>
       </c>
       <c r="AN11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ11">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR11">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AS11">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AT11">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AU11">
         <v>5</v>
@@ -3771,25 +3771,25 @@
         <v>1.35</v>
       </c>
       <c r="AN12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ12">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR12">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AS12">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AT12">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AU12">
         <v>6</v>
@@ -3983,19 +3983,19 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ13">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR13">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="AS13">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AT13">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AU13">
         <v>4</v>
@@ -4183,25 +4183,25 @@
         <v>1.45</v>
       </c>
       <c r="AN14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ14">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR14">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AU14">
         <v>8</v>
@@ -4395,19 +4395,19 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR15">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AU15">
         <v>7</v>
@@ -4595,25 +4595,25 @@
         <v>1.15</v>
       </c>
       <c r="AN16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ16">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR16">
-        <v>0.59</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AU16">
         <v>3</v>
@@ -4801,25 +4801,25 @@
         <v>3.6</v>
       </c>
       <c r="AN17">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ17">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR17">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>0.45</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AU17">
         <v>4</v>
@@ -5007,25 +5007,25 @@
         <v>1.67</v>
       </c>
       <c r="AN18">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO18">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ18">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR18">
-        <v>0.76</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS18">
-        <v>0.87</v>
+        <v>0.78</v>
       </c>
       <c r="AT18">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="AU18">
         <v>5</v>
@@ -5213,25 +5213,25 @@
         <v>1.57</v>
       </c>
       <c r="AN19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO19">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ19">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR19">
-        <v>0.96</v>
+        <v>0.45</v>
       </c>
       <c r="AS19">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="AT19">
-        <v>2.38</v>
+        <v>1.85</v>
       </c>
       <c r="AU19">
         <v>7</v>
@@ -5422,22 +5422,22 @@
         <v>3</v>
       </c>
       <c r="AO20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ20">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR20">
-        <v>1.54</v>
+        <v>1.27</v>
       </c>
       <c r="AS20">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AT20">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="AU20">
         <v>10</v>
@@ -5628,22 +5628,22 @@
         <v>3</v>
       </c>
       <c r="AO21">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ21">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR21">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AS21">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AT21">
-        <v>2.51</v>
+        <v>2.44</v>
       </c>
       <c r="AU21">
         <v>3</v>
@@ -5831,25 +5831,25 @@
         <v>1.33</v>
       </c>
       <c r="AN22">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AO22">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ22">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR22">
-        <v>1.86</v>
+        <v>1.58</v>
       </c>
       <c r="AS22">
-        <v>2</v>
+        <v>1.64</v>
       </c>
       <c r="AT22">
-        <v>3.86</v>
+        <v>3.22</v>
       </c>
       <c r="AU22">
         <v>8</v>
@@ -6037,25 +6037,25 @@
         <v>2.62</v>
       </c>
       <c r="AN23">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO23">
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ23">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR23">
-        <v>1.91</v>
+        <v>2.53</v>
       </c>
       <c r="AS23">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="AT23">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="AU23">
         <v>9</v>
@@ -6243,25 +6243,25 @@
         <v>1.38</v>
       </c>
       <c r="AN24">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AO24">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ24">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR24">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="AS24">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="AT24">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="AU24">
         <v>6</v>
@@ -6452,22 +6452,22 @@
         <v>0</v>
       </c>
       <c r="AO25">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR25">
-        <v>1.83</v>
+        <v>2.16</v>
       </c>
       <c r="AS25">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AT25">
-        <v>2.45</v>
+        <v>2.94</v>
       </c>
       <c r="AU25">
         <v>9</v>
@@ -6655,16 +6655,16 @@
         <v>2.4</v>
       </c>
       <c r="AN26">
-        <v>1.33</v>
+        <v>3</v>
       </c>
       <c r="AO26">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP26">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ26">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR26">
         <v>1.53</v>
@@ -6861,25 +6861,25 @@
         <v>1.29</v>
       </c>
       <c r="AN27">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO27">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR27">
-        <v>0.65</v>
+        <v>0.45</v>
       </c>
       <c r="AS27">
-        <v>1.84</v>
+        <v>2.14</v>
       </c>
       <c r="AT27">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
       <c r="AU27">
         <v>8</v>
@@ -7070,22 +7070,22 @@
         <v>0</v>
       </c>
       <c r="AO28">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP28">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ28">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR28">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="AS28">
-        <v>1.12</v>
+        <v>1.47</v>
       </c>
       <c r="AT28">
-        <v>1.97</v>
+        <v>2.26</v>
       </c>
       <c r="AU28">
         <v>5</v>
@@ -7273,25 +7273,25 @@
         <v>1.33</v>
       </c>
       <c r="AN29">
-        <v>0.67</v>
+        <v>0</v>
       </c>
       <c r="AO29">
-        <v>2.33</v>
+        <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ29">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR29">
-        <v>0.87</v>
+        <v>0.96</v>
       </c>
       <c r="AS29">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AT29">
-        <v>2.27</v>
+        <v>2.32</v>
       </c>
       <c r="AU29">
         <v>10</v>
@@ -7479,25 +7479,25 @@
         <v>2.05</v>
       </c>
       <c r="AN30">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="AO30">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP30">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ30">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR30">
-        <v>1.89</v>
+        <v>2.35</v>
       </c>
       <c r="AS30">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AT30">
-        <v>3.8</v>
+        <v>3.64</v>
       </c>
       <c r="AU30">
         <v>6</v>
@@ -7685,25 +7685,25 @@
         <v>1.4</v>
       </c>
       <c r="AN31">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="AO31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ31">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR31">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="AS31">
-        <v>1.96</v>
+        <v>1.51</v>
       </c>
       <c r="AT31">
-        <v>3.13</v>
+        <v>2.74</v>
       </c>
       <c r="AU31">
         <v>7</v>
@@ -7891,25 +7891,25 @@
         <v>1.45</v>
       </c>
       <c r="AN32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO32">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP32">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ32">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR32">
-        <v>1.35</v>
+        <v>1.43</v>
       </c>
       <c r="AS32">
-        <v>0.97</v>
+        <v>0.59</v>
       </c>
       <c r="AT32">
-        <v>2.32</v>
+        <v>2.02</v>
       </c>
       <c r="AU32">
         <v>9</v>
@@ -8097,25 +8097,25 @@
         <v>1.91</v>
       </c>
       <c r="AN33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO33">
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ33">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR33">
-        <v>1.08</v>
+        <v>1.52</v>
       </c>
       <c r="AS33">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AT33">
-        <v>2.84</v>
+        <v>3.32</v>
       </c>
       <c r="AU33">
         <v>9</v>
@@ -8303,25 +8303,25 @@
         <v>1.85</v>
       </c>
       <c r="AN34">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="AO34">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ34">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR34">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="AS34">
-        <v>1.24</v>
+        <v>1.14</v>
       </c>
       <c r="AT34">
-        <v>2.99</v>
+        <v>2.88</v>
       </c>
       <c r="AU34">
         <v>4</v>
@@ -8512,22 +8512,22 @@
         <v>1.5</v>
       </c>
       <c r="AO35">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ35">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR35">
-        <v>1.7</v>
+        <v>2.22</v>
       </c>
       <c r="AS35">
-        <v>1.23</v>
+        <v>0.83</v>
       </c>
       <c r="AT35">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="AU35">
         <v>5</v>
@@ -8718,22 +8718,22 @@
         <v>2</v>
       </c>
       <c r="AO36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ36">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR36">
-        <v>1.32</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AS36">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="AT36">
-        <v>3.09</v>
+        <v>2.59</v>
       </c>
       <c r="AU36">
         <v>6</v>
@@ -8921,25 +8921,25 @@
         <v>1.09</v>
       </c>
       <c r="AN37">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="AO37">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ37">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR37">
-        <v>0.96</v>
+        <v>1.03</v>
       </c>
       <c r="AS37">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="AT37">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="AU37">
         <v>0</v>
@@ -9127,25 +9127,25 @@
         <v>2</v>
       </c>
       <c r="AN38">
-        <v>1.25</v>
+        <v>2</v>
       </c>
       <c r="AO38">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ38">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR38">
-        <v>0.84</v>
+        <v>1.16</v>
       </c>
       <c r="AS38">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="AT38">
-        <v>1.69</v>
+        <v>1.91</v>
       </c>
       <c r="AU38">
         <v>4</v>
@@ -9339,19 +9339,19 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ39">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR39">
-        <v>1.48</v>
+        <v>1.72</v>
       </c>
       <c r="AS39">
-        <v>1.54</v>
+        <v>1.31</v>
       </c>
       <c r="AT39">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="AU39">
         <v>4</v>
@@ -9539,25 +9539,25 @@
         <v>2.1</v>
       </c>
       <c r="AN40">
+        <v>2</v>
+      </c>
+      <c r="AO40">
+        <v>1.5</v>
+      </c>
+      <c r="AP40">
+        <v>2.71</v>
+      </c>
+      <c r="AQ40">
+        <v>0.85</v>
+      </c>
+      <c r="AR40">
+        <v>1.69</v>
+      </c>
+      <c r="AS40">
         <v>1.75</v>
       </c>
-      <c r="AO40">
-        <v>2</v>
-      </c>
-      <c r="AP40">
-        <v>2.21</v>
-      </c>
-      <c r="AQ40">
-        <v>1.11</v>
-      </c>
-      <c r="AR40">
-        <v>1.64</v>
-      </c>
-      <c r="AS40">
-        <v>1.67</v>
-      </c>
       <c r="AT40">
-        <v>3.31</v>
+        <v>3.44</v>
       </c>
       <c r="AU40">
         <v>6</v>
@@ -9745,25 +9745,25 @@
         <v>1.5</v>
       </c>
       <c r="AN41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO41">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ41">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR41">
-        <v>1.23</v>
+        <v>1.62</v>
       </c>
       <c r="AS41">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AT41">
-        <v>2.66</v>
+        <v>2.87</v>
       </c>
       <c r="AU41">
         <v>8</v>
@@ -9951,25 +9951,25 @@
         <v>1.43</v>
       </c>
       <c r="AN42">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="AO42">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="AP42">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR42">
-        <v>0.87</v>
+        <v>0.95</v>
       </c>
       <c r="AS42">
-        <v>1.38</v>
+        <v>1.71</v>
       </c>
       <c r="AT42">
-        <v>2.25</v>
+        <v>2.66</v>
       </c>
       <c r="AU42">
         <v>5</v>
@@ -10157,25 +10157,25 @@
         <v>1.85</v>
       </c>
       <c r="AN43">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO43">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ43">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR43">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AS43">
-        <v>0.86</v>
+        <v>0.52</v>
       </c>
       <c r="AT43">
-        <v>2.16</v>
+        <v>1.85</v>
       </c>
       <c r="AU43">
         <v>5</v>
@@ -10363,25 +10363,25 @@
         <v>2.4</v>
       </c>
       <c r="AN44">
+        <v>2</v>
+      </c>
+      <c r="AO44">
+        <v>0.5</v>
+      </c>
+      <c r="AP44">
+        <v>2.14</v>
+      </c>
+      <c r="AQ44">
+        <v>0.79</v>
+      </c>
+      <c r="AR44">
+        <v>1.89</v>
+      </c>
+      <c r="AS44">
         <v>1.4</v>
       </c>
-      <c r="AO44">
-        <v>1</v>
-      </c>
-      <c r="AP44">
-        <v>1.89</v>
-      </c>
-      <c r="AQ44">
-        <v>1.14</v>
-      </c>
-      <c r="AR44">
-        <v>1.7</v>
-      </c>
-      <c r="AS44">
-        <v>1.79</v>
-      </c>
       <c r="AT44">
-        <v>3.49</v>
+        <v>3.29</v>
       </c>
       <c r="AU44">
         <v>11</v>
@@ -10572,22 +10572,22 @@
         <v>1.5</v>
       </c>
       <c r="AO45">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ45">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR45">
-        <v>1.25</v>
+        <v>1.63</v>
       </c>
       <c r="AS45">
-        <v>1.71</v>
+        <v>1.18</v>
       </c>
       <c r="AT45">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="AU45">
         <v>9</v>
@@ -10775,25 +10775,25 @@
         <v>1.77</v>
       </c>
       <c r="AN46">
-        <v>1.6</v>
+        <v>3</v>
       </c>
       <c r="AO46">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AP46">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ46">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR46">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="AS46">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AT46">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="AU46">
         <v>7</v>
@@ -10981,25 +10981,25 @@
         <v>1.7</v>
       </c>
       <c r="AN47">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AO47">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="AP47">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ47">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR47">
-        <v>1.38</v>
+        <v>1.76</v>
       </c>
       <c r="AS47">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
       <c r="AT47">
-        <v>2.22</v>
+        <v>2.65</v>
       </c>
       <c r="AU47">
         <v>5</v>
@@ -11187,25 +11187,25 @@
         <v>1.7</v>
       </c>
       <c r="AN48">
-        <v>1.83</v>
+        <v>1.33</v>
       </c>
       <c r="AO48">
-        <v>1.33</v>
+        <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ48">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR48">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="AS48">
-        <v>0.79</v>
+        <v>0.51</v>
       </c>
       <c r="AT48">
-        <v>2.09</v>
+        <v>1.66</v>
       </c>
       <c r="AU48">
         <v>4</v>
@@ -11393,25 +11393,25 @@
         <v>1.5</v>
       </c>
       <c r="AN49">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="AO49">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR49">
-        <v>1.67</v>
+        <v>2.18</v>
       </c>
       <c r="AS49">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AT49">
-        <v>3.32</v>
+        <v>3.77</v>
       </c>
       <c r="AU49">
         <v>3</v>
@@ -11599,25 +11599,25 @@
         <v>1.1</v>
       </c>
       <c r="AN50">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="AO50">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP50">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ50">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR50">
-        <v>1.44</v>
+        <v>1.76</v>
       </c>
       <c r="AS50">
-        <v>1.79</v>
+        <v>1.57</v>
       </c>
       <c r="AT50">
-        <v>3.23</v>
+        <v>3.33</v>
       </c>
       <c r="AU50">
         <v>3</v>
@@ -11805,25 +11805,25 @@
         <v>2.05</v>
       </c>
       <c r="AN51">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AO51">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ51">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR51">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AS51">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT51">
-        <v>2.87</v>
+        <v>2.77</v>
       </c>
       <c r="AU51">
         <v>9</v>
@@ -12011,25 +12011,25 @@
         <v>1.54</v>
       </c>
       <c r="AN52">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AO52">
-        <v>1.5</v>
+        <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ52">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR52">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AS52">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AT52">
-        <v>3.33</v>
+        <v>3.53</v>
       </c>
       <c r="AU52">
         <v>5</v>
@@ -12217,25 +12217,25 @@
         <v>1.37</v>
       </c>
       <c r="AN53">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AO53">
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="AP53">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ53">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR53">
-        <v>0.87</v>
+        <v>0.82</v>
       </c>
       <c r="AS53">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AT53">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AU53">
         <v>5</v>
@@ -12423,25 +12423,25 @@
         <v>2.21</v>
       </c>
       <c r="AN54">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO54">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ54">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR54">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
       <c r="AS54">
-        <v>0.88</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="AT54">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="AU54">
         <v>13</v>
@@ -12629,25 +12629,25 @@
         <v>2.17</v>
       </c>
       <c r="AN55">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AO55">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AP55">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ55">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR55">
-        <v>1.38</v>
+        <v>1.72</v>
       </c>
       <c r="AS55">
-        <v>1.24</v>
+        <v>0.98</v>
       </c>
       <c r="AT55">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AU55">
         <v>8</v>
@@ -12835,25 +12835,25 @@
         <v>1.65</v>
       </c>
       <c r="AN56">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AO56">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ56">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR56">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AS56">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AT56">
-        <v>3.34</v>
+        <v>3.6</v>
       </c>
       <c r="AU56">
         <v>5</v>
@@ -13041,25 +13041,25 @@
         <v>1.22</v>
       </c>
       <c r="AN57">
+        <v>2.33</v>
+      </c>
+      <c r="AO57">
+        <v>0.5</v>
+      </c>
+      <c r="AP57">
+        <v>1.85</v>
+      </c>
+      <c r="AQ57">
         <v>1.57</v>
       </c>
-      <c r="AO57">
-        <v>1.29</v>
-      </c>
-      <c r="AP57">
-        <v>1.41</v>
-      </c>
-      <c r="AQ57">
-        <v>1.86</v>
-      </c>
       <c r="AR57">
-        <v>0.8</v>
+        <v>1.08</v>
       </c>
       <c r="AS57">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="AT57">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AU57">
         <v>4</v>
@@ -13247,25 +13247,25 @@
         <v>1.55</v>
       </c>
       <c r="AN58">
-        <v>0.14</v>
+        <v>0.33</v>
       </c>
       <c r="AO58">
-        <v>0.86</v>
+        <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR58">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AS58">
         <v>0.93</v>
       </c>
-      <c r="AS58">
-        <v>0.9</v>
-      </c>
       <c r="AT58">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="AU58">
         <v>0</v>
@@ -13453,25 +13453,25 @@
         <v>1.38</v>
       </c>
       <c r="AN59">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AO59">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ59">
+        <v>1.29</v>
+      </c>
+      <c r="AR59">
         <v>1.61</v>
       </c>
-      <c r="AR59">
-        <v>1.54</v>
-      </c>
       <c r="AS59">
-        <v>1.68</v>
+        <v>1.42</v>
       </c>
       <c r="AT59">
-        <v>3.22</v>
+        <v>3.03</v>
       </c>
       <c r="AU59">
         <v>7</v>
@@ -13659,25 +13659,25 @@
         <v>1.84</v>
       </c>
       <c r="AN60">
+        <v>1.25</v>
+      </c>
+      <c r="AO60">
+        <v>1</v>
+      </c>
+      <c r="AP60">
         <v>1.71</v>
       </c>
-      <c r="AO60">
-        <v>1.71</v>
-      </c>
-      <c r="AP60">
-        <v>1.67</v>
-      </c>
       <c r="AQ60">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR60">
-        <v>1.54</v>
+        <v>1.66</v>
       </c>
       <c r="AS60">
-        <v>1.61</v>
+        <v>1.34</v>
       </c>
       <c r="AT60">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="AU60">
         <v>5</v>
@@ -13865,25 +13865,25 @@
         <v>2.5</v>
       </c>
       <c r="AN61">
-        <v>1.86</v>
+        <v>2.33</v>
       </c>
       <c r="AO61">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ61">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR61">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="AS61">
-        <v>1.5</v>
+        <v>0.86</v>
       </c>
       <c r="AT61">
-        <v>3.3</v>
+        <v>2.87</v>
       </c>
       <c r="AU61">
         <v>10</v>
@@ -14071,25 +14071,25 @@
         <v>1.51</v>
       </c>
       <c r="AN62">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AO62">
-        <v>0.67</v>
+        <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ62">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR62">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AS62">
-        <v>1.56</v>
+        <v>1.32</v>
       </c>
       <c r="AT62">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="AU62">
         <v>6</v>
@@ -14277,22 +14277,22 @@
         <v>2.3</v>
       </c>
       <c r="AN63">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="AO63">
-        <v>1.57</v>
+        <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ63">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR63">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="AS63">
-        <v>1.31</v>
+        <v>1.45</v>
       </c>
       <c r="AT63">
         <v>3.14</v>
@@ -14483,25 +14483,25 @@
         <v>2</v>
       </c>
       <c r="AN64">
-        <v>1.43</v>
+        <v>2.33</v>
       </c>
       <c r="AO64">
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ64">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR64">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AS64">
-        <v>1.38</v>
+        <v>1.12</v>
       </c>
       <c r="AT64">
-        <v>2.76</v>
+        <v>2.45</v>
       </c>
       <c r="AU64">
         <v>3</v>
@@ -14689,25 +14689,25 @@
         <v>1.51</v>
       </c>
       <c r="AN65">
-        <v>0.57</v>
+        <v>1</v>
       </c>
       <c r="AO65">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR65">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AS65">
-        <v>1.42</v>
+        <v>0.88</v>
       </c>
       <c r="AT65">
-        <v>2.9</v>
+        <v>2.67</v>
       </c>
       <c r="AU65">
         <v>6</v>
@@ -14895,25 +14895,25 @@
         <v>1.22</v>
       </c>
       <c r="AN66">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="AO66">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ66">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR66">
-        <v>1.53</v>
+        <v>1.81</v>
       </c>
       <c r="AS66">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AT66">
-        <v>3.43</v>
+        <v>3.45</v>
       </c>
       <c r="AU66">
         <v>6</v>
@@ -15101,25 +15101,25 @@
         <v>2.5</v>
       </c>
       <c r="AN67">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AO67">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AP67">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ67">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR67">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AS67">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="AT67">
-        <v>3.18</v>
+        <v>3.01</v>
       </c>
       <c r="AU67">
         <v>6</v>
@@ -15307,25 +15307,25 @@
         <v>1.44</v>
       </c>
       <c r="AN68">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO68">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ68">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR68">
-        <v>0.8100000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="AS68">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AT68">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="AU68">
         <v>4</v>
@@ -15513,25 +15513,25 @@
         <v>1.35</v>
       </c>
       <c r="AN69">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AO69">
-        <v>1.63</v>
+        <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ69">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR69">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AS69">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="AT69">
-        <v>2.76</v>
+        <v>2.58</v>
       </c>
       <c r="AU69">
         <v>5</v>
@@ -15719,25 +15719,25 @@
         <v>3.75</v>
       </c>
       <c r="AN70">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AO70">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ70">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR70">
-        <v>1.63</v>
+        <v>1.88</v>
       </c>
       <c r="AS70">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="AT70">
-        <v>2.55</v>
+        <v>2.81</v>
       </c>
       <c r="AU70">
         <v>7</v>
@@ -15925,25 +15925,25 @@
         <v>3</v>
       </c>
       <c r="AN71">
-        <v>1.25</v>
+        <v>2.33</v>
       </c>
       <c r="AO71">
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ71">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR71">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AS71">
-        <v>1.34</v>
+        <v>1.12</v>
       </c>
       <c r="AT71">
-        <v>2.96</v>
+        <v>2.82</v>
       </c>
       <c r="AU71">
         <v>6</v>
@@ -16131,25 +16131,25 @@
         <v>2.2</v>
       </c>
       <c r="AN72">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO72">
-        <v>1.38</v>
+        <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ72">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR72">
-        <v>1.33</v>
+        <v>1.82</v>
       </c>
       <c r="AS72">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AT72">
-        <v>2.72</v>
+        <v>3.24</v>
       </c>
       <c r="AU72">
         <v>6</v>
@@ -16337,25 +16337,25 @@
         <v>2.15</v>
       </c>
       <c r="AN73">
-        <v>0.88</v>
+        <v>1.5</v>
       </c>
       <c r="AO73">
-        <v>1.13</v>
+        <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ73">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR73">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="AS73">
-        <v>1.08</v>
+        <v>1.26</v>
       </c>
       <c r="AT73">
-        <v>2.57</v>
+        <v>2.99</v>
       </c>
       <c r="AU73">
         <v>3</v>
@@ -16543,25 +16543,25 @@
         <v>2.75</v>
       </c>
       <c r="AN74">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AO74">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ74">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR74">
-        <v>1.52</v>
+        <v>1.66</v>
       </c>
       <c r="AS74">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="AT74">
-        <v>2.4</v>
+        <v>2.51</v>
       </c>
       <c r="AU74">
         <v>10</v>
@@ -16749,25 +16749,25 @@
         <v>1.62</v>
       </c>
       <c r="AN75">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AO75">
-        <v>1.22</v>
+        <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ75">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR75">
-        <v>1.31</v>
+        <v>1.41</v>
       </c>
       <c r="AS75">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AT75">
-        <v>2.68</v>
+        <v>2.8</v>
       </c>
       <c r="AU75">
         <v>7</v>
@@ -16955,25 +16955,25 @@
         <v>1.15</v>
       </c>
       <c r="AN76">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AO76">
-        <v>2.44</v>
+        <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ76">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR76">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AS76">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="AT76">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AU76">
         <v>5</v>
@@ -17161,25 +17161,25 @@
         <v>1.33</v>
       </c>
       <c r="AN77">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AO77">
-        <v>1.56</v>
+        <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ77">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR77">
+        <v>1.23</v>
+      </c>
+      <c r="AS77">
         <v>1.25</v>
       </c>
-      <c r="AS77">
-        <v>1.54</v>
-      </c>
       <c r="AT77">
-        <v>2.79</v>
+        <v>2.48</v>
       </c>
       <c r="AU77">
         <v>3</v>
@@ -17367,25 +17367,25 @@
         <v>2.4</v>
       </c>
       <c r="AN78">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="AO78">
-        <v>1.33</v>
+        <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ78">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR78">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AS78">
-        <v>0.89</v>
+        <v>0.58</v>
       </c>
       <c r="AT78">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="AU78">
         <v>8</v>
@@ -17573,25 +17573,25 @@
         <v>2.25</v>
       </c>
       <c r="AN79">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AO79">
-        <v>0.89</v>
+        <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ79">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR79">
-        <v>1.66</v>
+        <v>1.88</v>
       </c>
       <c r="AS79">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AT79">
-        <v>3.11</v>
+        <v>3.13</v>
       </c>
       <c r="AU79">
         <v>6</v>
@@ -17779,25 +17779,25 @@
         <v>1.86</v>
       </c>
       <c r="AN80">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AO80">
-        <v>1.44</v>
+        <v>0.6</v>
       </c>
       <c r="AP80">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ80">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR80">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="AS80">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="AT80">
-        <v>3.49</v>
+        <v>3.75</v>
       </c>
       <c r="AU80">
         <v>6</v>
@@ -17985,25 +17985,25 @@
         <v>1.33</v>
       </c>
       <c r="AN81">
-        <v>1.11</v>
+        <v>1.25</v>
       </c>
       <c r="AO81">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ81">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR81">
-        <v>1.06</v>
+        <v>0.89</v>
       </c>
       <c r="AS81">
-        <v>1.33</v>
+        <v>0.84</v>
       </c>
       <c r="AT81">
-        <v>2.39</v>
+        <v>1.73</v>
       </c>
       <c r="AU81">
         <v>13</v>
@@ -18191,25 +18191,25 @@
         <v>0</v>
       </c>
       <c r="AN82">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="AO82">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AP82">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ82">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR82">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="AS82">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="AT82">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="AU82">
         <v>0</v>
@@ -18397,25 +18397,25 @@
         <v>1.25</v>
       </c>
       <c r="AN83">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="AO83">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AP83">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ83">
+        <v>1.64</v>
+      </c>
+      <c r="AR83">
         <v>1.89</v>
       </c>
-      <c r="AR83">
-        <v>1.65</v>
-      </c>
       <c r="AS83">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AT83">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="AU83">
         <v>7</v>
@@ -18603,25 +18603,25 @@
         <v>1.96</v>
       </c>
       <c r="AN84">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="AO84">
+        <v>1.75</v>
+      </c>
+      <c r="AP84">
         <v>1.5</v>
       </c>
-      <c r="AP84">
-        <v>1.14</v>
-      </c>
       <c r="AQ84">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR84">
-        <v>1.47</v>
+        <v>1.61</v>
       </c>
       <c r="AS84">
-        <v>1.2</v>
+        <v>1.28</v>
       </c>
       <c r="AT84">
-        <v>2.67</v>
+        <v>2.89</v>
       </c>
       <c r="AU84">
         <v>7</v>
@@ -18809,25 +18809,25 @@
         <v>2.15</v>
       </c>
       <c r="AN85">
+        <v>2.5</v>
+      </c>
+      <c r="AO85">
         <v>1.4</v>
       </c>
-      <c r="AO85">
-        <v>1.7</v>
-      </c>
       <c r="AP85">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ85">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR85">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AS85">
-        <v>1.31</v>
+        <v>0.91</v>
       </c>
       <c r="AT85">
-        <v>2.87</v>
+        <v>2.58</v>
       </c>
       <c r="AU85">
         <v>6</v>
@@ -19015,25 +19015,25 @@
         <v>2.65</v>
       </c>
       <c r="AN86">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="AO86">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ86">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR86">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AS86">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AT86">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="AU86">
         <v>5</v>
@@ -19221,25 +19221,25 @@
         <v>1.38</v>
       </c>
       <c r="AN87">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="AO87">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ87">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR87">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AS87">
-        <v>1.63</v>
+        <v>1.39</v>
       </c>
       <c r="AT87">
-        <v>2.96</v>
+        <v>2.75</v>
       </c>
       <c r="AU87">
         <v>3</v>
@@ -19427,25 +19427,25 @@
         <v>1.38</v>
       </c>
       <c r="AN88">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="AO88">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="AP88">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ88">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR88">
-        <v>0.98</v>
+        <v>1.14</v>
       </c>
       <c r="AS88">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="AT88">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AU88">
         <v>7</v>
@@ -19633,25 +19633,25 @@
         <v>2.15</v>
       </c>
       <c r="AN89">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AO89">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="AP89">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ89">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR89">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AS89">
-        <v>1.29</v>
+        <v>1.07</v>
       </c>
       <c r="AT89">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="AU89">
         <v>8</v>
@@ -19839,25 +19839,25 @@
         <v>1.9</v>
       </c>
       <c r="AN90">
-        <v>1</v>
+        <v>1.4</v>
       </c>
       <c r="AO90">
-        <v>0.45</v>
+        <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ90">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR90">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AS90">
-        <v>0.84</v>
+        <v>0.86</v>
       </c>
       <c r="AT90">
-        <v>2.11</v>
+        <v>2.36</v>
       </c>
       <c r="AU90">
         <v>6</v>
@@ -20045,25 +20045,25 @@
         <v>0</v>
       </c>
       <c r="AN91">
-        <v>1.27</v>
+        <v>2</v>
       </c>
       <c r="AO91">
-        <v>1.09</v>
+        <v>0.5</v>
       </c>
       <c r="AP91">
+        <v>1.57</v>
+      </c>
+      <c r="AQ91">
+        <v>0.64</v>
+      </c>
+      <c r="AR91">
+        <v>1.77</v>
+      </c>
+      <c r="AS91">
         <v>1.32</v>
       </c>
-      <c r="AQ91">
-        <v>1.22</v>
-      </c>
-      <c r="AR91">
-        <v>1.57</v>
-      </c>
-      <c r="AS91">
-        <v>1.31</v>
-      </c>
       <c r="AT91">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="AU91">
         <v>5</v>
@@ -20251,25 +20251,25 @@
         <v>1.45</v>
       </c>
       <c r="AN92">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AO92">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="AP92">
+        <v>1.21</v>
+      </c>
+      <c r="AQ92">
+        <v>0.92</v>
+      </c>
+      <c r="AR92">
         <v>1.14</v>
       </c>
-      <c r="AQ92">
-        <v>1.19</v>
-      </c>
-      <c r="AR92">
-        <v>1.13</v>
-      </c>
       <c r="AS92">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AT92">
-        <v>2.51</v>
+        <v>2.36</v>
       </c>
       <c r="AU92">
         <v>5</v>
@@ -20457,25 +20457,25 @@
         <v>1.49</v>
       </c>
       <c r="AN93">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AO93">
+        <v>1.4</v>
+      </c>
+      <c r="AP93">
         <v>1.36</v>
       </c>
-      <c r="AP93">
-        <v>1</v>
-      </c>
       <c r="AQ93">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR93">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AS93">
-        <v>1.64</v>
+        <v>1.41</v>
       </c>
       <c r="AT93">
-        <v>2.86</v>
+        <v>2.64</v>
       </c>
       <c r="AU93">
         <v>7</v>
@@ -20663,25 +20663,25 @@
         <v>2.4</v>
       </c>
       <c r="AN94">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AO94">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ94">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR94">
-        <v>1.82</v>
+        <v>2.03</v>
       </c>
       <c r="AS94">
         <v>1.57</v>
       </c>
       <c r="AT94">
-        <v>3.39</v>
+        <v>3.6</v>
       </c>
       <c r="AU94">
         <v>10</v>
@@ -20869,25 +20869,25 @@
         <v>2.4</v>
       </c>
       <c r="AN95">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AO95">
-        <v>1.36</v>
+        <v>0.8</v>
       </c>
       <c r="AP95">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ95">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR95">
-        <v>1.56</v>
+        <v>1.79</v>
       </c>
       <c r="AS95">
-        <v>1.01</v>
+        <v>0.82</v>
       </c>
       <c r="AT95">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="AU95">
         <v>6</v>
@@ -21075,25 +21075,25 @@
         <v>1.38</v>
       </c>
       <c r="AN96">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AO96">
-        <v>2.27</v>
+        <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ96">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR96">
-        <v>1.29</v>
+        <v>1.72</v>
       </c>
       <c r="AS96">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="AT96">
-        <v>3.19</v>
+        <v>3.66</v>
       </c>
       <c r="AU96">
         <v>0</v>
@@ -21281,25 +21281,25 @@
         <v>2.7</v>
       </c>
       <c r="AN97">
-        <v>1.36</v>
+        <v>2.2</v>
       </c>
       <c r="AO97">
-        <v>0.82</v>
+        <v>0.2</v>
       </c>
       <c r="AP97">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ97">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR97">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AS97">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AT97">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="AU97">
         <v>6</v>
@@ -21487,25 +21487,25 @@
         <v>1.98</v>
       </c>
       <c r="AN98">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AO98">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AP98">
+        <v>1.36</v>
+      </c>
+      <c r="AQ98">
+        <v>1.07</v>
+      </c>
+      <c r="AR98">
+        <v>1.83</v>
+      </c>
+      <c r="AS98">
         <v>1.11</v>
       </c>
-      <c r="AQ98">
-        <v>1.14</v>
-      </c>
-      <c r="AR98">
-        <v>1.65</v>
-      </c>
-      <c r="AS98">
-        <v>1.14</v>
-      </c>
       <c r="AT98">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="AU98">
         <v>9</v>
@@ -21693,25 +21693,25 @@
         <v>1.6</v>
       </c>
       <c r="AN99">
-        <v>1.25</v>
+        <v>1.83</v>
       </c>
       <c r="AO99">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="AP99">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ99">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR99">
-        <v>1.03</v>
+        <v>1.16</v>
       </c>
       <c r="AS99">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
       <c r="AT99">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="AU99">
         <v>5</v>
@@ -21899,25 +21899,25 @@
         <v>1.26</v>
       </c>
       <c r="AN100">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AO100">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ100">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR100">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AS100">
-        <v>1.86</v>
+        <v>1.65</v>
       </c>
       <c r="AT100">
-        <v>3.14</v>
+        <v>2.95</v>
       </c>
       <c r="AU100">
         <v>5</v>
@@ -22105,25 +22105,25 @@
         <v>1.28</v>
       </c>
       <c r="AN101">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="AO101">
-        <v>1.25</v>
+        <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ101">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR101">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="AS101">
-        <v>1.6</v>
+        <v>1.49</v>
       </c>
       <c r="AT101">
-        <v>3.04</v>
+        <v>3.01</v>
       </c>
       <c r="AU101">
         <v>5</v>
@@ -22311,25 +22311,25 @@
         <v>1.83</v>
       </c>
       <c r="AN102">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="AO102">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AP102">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ102">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR102">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AS102">
-        <v>1.56</v>
+        <v>1.29</v>
       </c>
       <c r="AT102">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="AU102">
         <v>8</v>
@@ -22517,25 +22517,25 @@
         <v>1.58</v>
       </c>
       <c r="AN103">
-        <v>1</v>
+        <v>1.33</v>
       </c>
       <c r="AO103">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ103">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR103">
-        <v>1.46</v>
+        <v>1.64</v>
       </c>
       <c r="AS103">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AT103">
-        <v>3.04</v>
+        <v>3.05</v>
       </c>
       <c r="AU103">
         <v>8</v>
@@ -22723,25 +22723,25 @@
         <v>2.75</v>
       </c>
       <c r="AN104">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="AO104">
-        <v>1.17</v>
+        <v>0.67</v>
       </c>
       <c r="AP104">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ104">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR104">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AS104">
-        <v>1.29</v>
+        <v>1.08</v>
       </c>
       <c r="AT104">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="AU104">
         <v>7</v>
@@ -22929,25 +22929,25 @@
         <v>1.24</v>
       </c>
       <c r="AN105">
-        <v>0.42</v>
+        <v>0.8</v>
       </c>
       <c r="AO105">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP105">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR105">
-        <v>0.9</v>
+        <v>0.83</v>
       </c>
       <c r="AS105">
-        <v>1.24</v>
+        <v>0.93</v>
       </c>
       <c r="AT105">
-        <v>2.14</v>
+        <v>1.76</v>
       </c>
       <c r="AU105">
         <v>5</v>
@@ -23135,25 +23135,25 @@
         <v>1.5</v>
       </c>
       <c r="AN106">
-        <v>1.08</v>
+        <v>1.5</v>
       </c>
       <c r="AO106">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AP106">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ106">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR106">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AS106">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="AT106">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="AU106">
         <v>6</v>
@@ -23341,25 +23341,25 @@
         <v>1.22</v>
       </c>
       <c r="AN107">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AO107">
-        <v>1.77</v>
+        <v>1.33</v>
       </c>
       <c r="AP107">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ107">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR107">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AS107">
-        <v>1.49</v>
+        <v>1.17</v>
       </c>
       <c r="AT107">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AU107">
         <v>6</v>
@@ -23547,25 +23547,25 @@
         <v>1.38</v>
       </c>
       <c r="AN108">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AO108">
-        <v>1.15</v>
+        <v>0.86</v>
       </c>
       <c r="AP108">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ108">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR108">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AS108">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AT108">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="AU108">
         <v>4</v>
@@ -23753,25 +23753,25 @@
         <v>1.8</v>
       </c>
       <c r="AN109">
-        <v>1.08</v>
+        <v>1.67</v>
       </c>
       <c r="AO109">
-        <v>1.38</v>
+        <v>1.17</v>
       </c>
       <c r="AP109">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ109">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR109">
-        <v>1.52</v>
+        <v>1.75</v>
       </c>
       <c r="AS109">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AT109">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="AU109">
         <v>8</v>
@@ -23959,25 +23959,25 @@
         <v>1.45</v>
       </c>
       <c r="AN110">
-        <v>1.15</v>
+        <v>1.57</v>
       </c>
       <c r="AO110">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ110">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR110">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="AS110">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="AT110">
-        <v>3.04</v>
+        <v>3.11</v>
       </c>
       <c r="AU110">
         <v>4</v>
@@ -24165,25 +24165,25 @@
         <v>1.9</v>
       </c>
       <c r="AN111">
-        <v>1.46</v>
+        <v>1.67</v>
       </c>
       <c r="AO111">
-        <v>1.38</v>
+        <v>0.67</v>
       </c>
       <c r="AP111">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ111">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR111">
-        <v>1.25</v>
+        <v>1.55</v>
       </c>
       <c r="AS111">
-        <v>1.05</v>
+        <v>0.9</v>
       </c>
       <c r="AT111">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="AU111">
         <v>13</v>
@@ -24371,25 +24371,25 @@
         <v>1.65</v>
       </c>
       <c r="AN112">
-        <v>1.23</v>
+        <v>1.83</v>
       </c>
       <c r="AO112">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AP112">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ112">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR112">
-        <v>1.55</v>
+        <v>1.71</v>
       </c>
       <c r="AS112">
         <v>1.85</v>
       </c>
       <c r="AT112">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="AU112">
         <v>8</v>
@@ -24577,25 +24577,25 @@
         <v>1.05</v>
       </c>
       <c r="AN113">
-        <v>0.46</v>
+        <v>0.83</v>
       </c>
       <c r="AO113">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AP113">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ113">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR113">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="AS113">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="AT113">
-        <v>2.75</v>
+        <v>2.51</v>
       </c>
       <c r="AU113">
         <v>6</v>
@@ -24783,25 +24783,25 @@
         <v>2.5</v>
       </c>
       <c r="AN114">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AO114">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AP114">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ114">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR114">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS114">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT114">
-        <v>2.64</v>
+        <v>2.89</v>
       </c>
       <c r="AU114">
         <v>7</v>
@@ -24989,25 +24989,25 @@
         <v>0</v>
       </c>
       <c r="AN115">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AO115">
-        <v>1.21</v>
+        <v>0.71</v>
       </c>
       <c r="AP115">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ115">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR115">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AS115">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AT115">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AU115">
         <v>6</v>
@@ -25195,25 +25195,25 @@
         <v>1.53</v>
       </c>
       <c r="AN116">
-        <v>1.29</v>
+        <v>2</v>
       </c>
       <c r="AO116">
-        <v>1.07</v>
+        <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ116">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR116">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="AS116">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="AT116">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="AU116">
         <v>5</v>
@@ -25401,25 +25401,25 @@
         <v>2.5</v>
       </c>
       <c r="AN117">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AO117">
-        <v>1.21</v>
+        <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ117">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR117">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AS117">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AT117">
-        <v>3.37</v>
+        <v>3.18</v>
       </c>
       <c r="AU117">
         <v>6</v>
@@ -25607,25 +25607,25 @@
         <v>0</v>
       </c>
       <c r="AN118">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="AO118">
-        <v>0.5</v>
+        <v>0.14</v>
       </c>
       <c r="AP118">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ118">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR118">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AS118">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="AT118">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AU118">
         <v>11</v>
@@ -25813,25 +25813,25 @@
         <v>0</v>
       </c>
       <c r="AN119">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AO119">
-        <v>1.36</v>
+        <v>0.71</v>
       </c>
       <c r="AP119">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ119">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR119">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AS119">
-        <v>1.56</v>
+        <v>1.42</v>
       </c>
       <c r="AT119">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="AU119">
         <v>0</v>
@@ -26019,25 +26019,25 @@
         <v>1.88</v>
       </c>
       <c r="AN120">
+        <v>1.71</v>
+      </c>
+      <c r="AO120">
+        <v>1.29</v>
+      </c>
+      <c r="AP120">
+        <v>1.71</v>
+      </c>
+      <c r="AQ120">
+        <v>1.21</v>
+      </c>
+      <c r="AR120">
         <v>1.64</v>
       </c>
-      <c r="AO120">
-        <v>1.57</v>
-      </c>
-      <c r="AP120">
-        <v>1.67</v>
-      </c>
-      <c r="AQ120">
-        <v>1.5</v>
-      </c>
-      <c r="AR120">
-        <v>1.53</v>
-      </c>
       <c r="AS120">
-        <v>1.34</v>
+        <v>0.99</v>
       </c>
       <c r="AT120">
-        <v>2.87</v>
+        <v>2.63</v>
       </c>
       <c r="AU120">
         <v>12</v>
@@ -26225,25 +26225,25 @@
         <v>2.15</v>
       </c>
       <c r="AN121">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AO121">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AP121">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ121">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR121">
-        <v>1.63</v>
+        <v>1.8</v>
       </c>
       <c r="AS121">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="AT121">
-        <v>2.87</v>
+        <v>2.81</v>
       </c>
       <c r="AU121">
         <v>7</v>
@@ -26431,25 +26431,25 @@
         <v>1.38</v>
       </c>
       <c r="AN122">
-        <v>0.93</v>
+        <v>1.43</v>
       </c>
       <c r="AO122">
-        <v>1.6</v>
+        <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ122">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR122">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="AS122">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="AT122">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="AU122">
         <v>6</v>
@@ -26637,25 +26637,25 @@
         <v>4</v>
       </c>
       <c r="AN123">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AO123">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AP123">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ123">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR123">
-        <v>1.86</v>
+        <v>2.07</v>
       </c>
       <c r="AS123">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="AT123">
-        <v>3.01</v>
+        <v>3.2</v>
       </c>
       <c r="AU123">
         <v>9</v>
@@ -26843,25 +26843,25 @@
         <v>1.92</v>
       </c>
       <c r="AN124">
-        <v>1.13</v>
+        <v>1.86</v>
       </c>
       <c r="AO124">
-        <v>1.4</v>
+        <v>0.57</v>
       </c>
       <c r="AP124">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ124">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR124">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AS124">
-        <v>1.05</v>
+        <v>0.91</v>
       </c>
       <c r="AT124">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="AU124">
         <v>3</v>
@@ -27049,22 +27049,22 @@
         <v>1.2</v>
       </c>
       <c r="AN125">
-        <v>1.13</v>
+        <v>1.71</v>
       </c>
       <c r="AO125">
-        <v>2.27</v>
+        <v>1.71</v>
       </c>
       <c r="AP125">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ125">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR125">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AS125">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="AT125">
         <v>3.15</v>
@@ -27255,25 +27255,25 @@
         <v>1.36</v>
       </c>
       <c r="AN126">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AO126">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AP126">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ126">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR126">
         <v>1.26</v>
       </c>
       <c r="AS126">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AT126">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
       <c r="AU126">
         <v>3</v>
@@ -27461,25 +27461,25 @@
         <v>1.25</v>
       </c>
       <c r="AN127">
-        <v>0.47</v>
+        <v>0.86</v>
       </c>
       <c r="AO127">
-        <v>1</v>
+        <v>0.57</v>
       </c>
       <c r="AP127">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR127">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="AS127">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="AT127">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AU127">
         <v>9</v>
@@ -27667,25 +27667,25 @@
         <v>1.98</v>
       </c>
       <c r="AN128">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO128">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AP128">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ128">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR128">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AS128">
-        <v>1.49</v>
+        <v>1.23</v>
       </c>
       <c r="AT128">
-        <v>3.04</v>
+        <v>2.93</v>
       </c>
       <c r="AU128">
         <v>7</v>
@@ -27873,25 +27873,25 @@
         <v>1.68</v>
       </c>
       <c r="AN129">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="AO129">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AP129">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ129">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR129">
-        <v>1.65</v>
+        <v>1.82</v>
       </c>
       <c r="AS129">
-        <v>1.31</v>
+        <v>0.99</v>
       </c>
       <c r="AT129">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="AU129">
         <v>9</v>
@@ -28079,25 +28079,25 @@
         <v>3.6</v>
       </c>
       <c r="AN130">
-        <v>2.19</v>
+        <v>2.75</v>
       </c>
       <c r="AO130">
-        <v>1.06</v>
+        <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ130">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR130">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="AS130">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="AT130">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="AU130">
         <v>7</v>
@@ -28285,25 +28285,25 @@
         <v>1.45</v>
       </c>
       <c r="AN131">
-        <v>1.38</v>
+        <v>2.13</v>
       </c>
       <c r="AO131">
-        <v>1.13</v>
+        <v>0.88</v>
       </c>
       <c r="AP131">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ131">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR131">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AS131">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AT131">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="AU131">
         <v>5</v>
@@ -28491,25 +28491,25 @@
         <v>1.26</v>
       </c>
       <c r="AN132">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="AO132">
-        <v>1.94</v>
+        <v>1.75</v>
       </c>
       <c r="AP132">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ132">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR132">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="AS132">
-        <v>1.87</v>
+        <v>1.69</v>
       </c>
       <c r="AT132">
-        <v>3.29</v>
+        <v>3.24</v>
       </c>
       <c r="AU132">
         <v>6</v>
@@ -28697,25 +28697,25 @@
         <v>1.95</v>
       </c>
       <c r="AN133">
-        <v>1.44</v>
+        <v>1.86</v>
       </c>
       <c r="AO133">
-        <v>1.13</v>
+        <v>0.63</v>
       </c>
       <c r="AP133">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ133">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR133">
-        <v>1.33</v>
+        <v>1.68</v>
       </c>
       <c r="AS133">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AT133">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
       <c r="AU133">
         <v>4</v>
@@ -28903,25 +28903,25 @@
         <v>1.77</v>
       </c>
       <c r="AN134">
-        <v>1.69</v>
+        <v>2</v>
       </c>
       <c r="AO134">
-        <v>1.13</v>
+        <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ134">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR134">
-        <v>1.49</v>
+        <v>1.76</v>
       </c>
       <c r="AS134">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AT134">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU134">
         <v>9</v>
@@ -29109,25 +29109,25 @@
         <v>1.22</v>
       </c>
       <c r="AN135">
-        <v>0.9399999999999999</v>
+        <v>1.38</v>
       </c>
       <c r="AO135">
-        <v>1.44</v>
+        <v>0.75</v>
       </c>
       <c r="AP135">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ135">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR135">
-        <v>1.47</v>
+        <v>1.6</v>
       </c>
       <c r="AS135">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AT135">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="AU135">
         <v>8</v>
@@ -29315,25 +29315,25 @@
         <v>3.35</v>
       </c>
       <c r="AN136">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="AO136">
-        <v>0.63</v>
+        <v>0.13</v>
       </c>
       <c r="AP136">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ136">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR136">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AS136">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AT136">
-        <v>2.6</v>
+        <v>2.71</v>
       </c>
       <c r="AU136">
         <v>7</v>
@@ -29524,22 +29524,22 @@
         <v>1.13</v>
       </c>
       <c r="AO137">
-        <v>1.38</v>
+        <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ137">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR137">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="AS137">
-        <v>1.68</v>
+        <v>1.46</v>
       </c>
       <c r="AT137">
-        <v>2.81</v>
+        <v>2.63</v>
       </c>
       <c r="AU137">
         <v>2</v>
@@ -29727,25 +29727,25 @@
         <v>1.52</v>
       </c>
       <c r="AN138">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="AO138">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="AP138">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ138">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR138">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AS138">
-        <v>1.53</v>
+        <v>1.26</v>
       </c>
       <c r="AT138">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="AU138">
         <v>7</v>
@@ -29933,25 +29933,25 @@
         <v>1.36</v>
       </c>
       <c r="AN139">
-        <v>0.59</v>
+        <v>1.13</v>
       </c>
       <c r="AO139">
-        <v>1.35</v>
+        <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ139">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR139">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="AS139">
-        <v>1.09</v>
+        <v>0.93</v>
       </c>
       <c r="AT139">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AU139">
         <v>9</v>
@@ -30139,25 +30139,25 @@
         <v>1.57</v>
       </c>
       <c r="AN140">
-        <v>1.12</v>
+        <v>1.38</v>
       </c>
       <c r="AO140">
-        <v>1.24</v>
+        <v>0.78</v>
       </c>
       <c r="AP140">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ140">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR140">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AS140">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="AT140">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="AU140">
         <v>3</v>
@@ -30345,25 +30345,25 @@
         <v>1.66</v>
       </c>
       <c r="AN141">
-        <v>1</v>
+        <v>1.63</v>
       </c>
       <c r="AO141">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ141">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR141">
-        <v>1.24</v>
+        <v>1.44</v>
       </c>
       <c r="AS141">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AT141">
-        <v>2.34</v>
+        <v>2.53</v>
       </c>
       <c r="AU141">
         <v>2</v>
@@ -30551,25 +30551,25 @@
         <v>2.3</v>
       </c>
       <c r="AN142">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AO142">
-        <v>2.24</v>
+        <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ142">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR142">
-        <v>1.81</v>
+        <v>2.07</v>
       </c>
       <c r="AS142">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="AT142">
-        <v>3.56</v>
+        <v>3.79</v>
       </c>
       <c r="AU142">
         <v>6</v>
@@ -30757,25 +30757,25 @@
         <v>2.75</v>
       </c>
       <c r="AN143">
-        <v>1.41</v>
+        <v>2.13</v>
       </c>
       <c r="AO143">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="AP143">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ143">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR143">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="AS143">
-        <v>1.67</v>
+        <v>1.46</v>
       </c>
       <c r="AT143">
-        <v>3.21</v>
+        <v>3.14</v>
       </c>
       <c r="AU143">
         <v>14</v>
@@ -30963,25 +30963,25 @@
         <v>1.3</v>
       </c>
       <c r="AN144">
-        <v>1.06</v>
+        <v>1.63</v>
       </c>
       <c r="AO144">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AP144">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ144">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR144">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="AS144">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AT144">
-        <v>2.97</v>
+        <v>2.83</v>
       </c>
       <c r="AU144">
         <v>7</v>
@@ -31169,25 +31169,25 @@
         <v>2</v>
       </c>
       <c r="AN145">
-        <v>1.53</v>
+        <v>2</v>
       </c>
       <c r="AO145">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ145">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR145">
+        <v>1.64</v>
+      </c>
+      <c r="AS145">
         <v>1.33</v>
       </c>
-      <c r="AS145">
-        <v>1.49</v>
-      </c>
       <c r="AT145">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="AU145">
         <v>6</v>
@@ -31375,25 +31375,25 @@
         <v>1.65</v>
       </c>
       <c r="AN146">
-        <v>1.22</v>
+        <v>1.67</v>
       </c>
       <c r="AO146">
-        <v>1.39</v>
+        <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ146">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR146">
-        <v>1.63</v>
+        <v>1.85</v>
       </c>
       <c r="AS146">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AT146">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="AU146">
         <v>7</v>
@@ -31581,25 +31581,25 @@
         <v>1.83</v>
       </c>
       <c r="AN147">
-        <v>1.17</v>
+        <v>1.75</v>
       </c>
       <c r="AO147">
-        <v>1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP147">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ147">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR147">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="AS147">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="AT147">
-        <v>2.98</v>
+        <v>3.09</v>
       </c>
       <c r="AU147">
         <v>8</v>
@@ -31790,22 +31790,22 @@
         <v>1.33</v>
       </c>
       <c r="AO148">
-        <v>1.56</v>
+        <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ148">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR148">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AS148">
-        <v>1.5</v>
+        <v>1.23</v>
       </c>
       <c r="AT148">
-        <v>2.6</v>
+        <v>2.34</v>
       </c>
       <c r="AU148">
         <v>2</v>
@@ -31993,25 +31993,25 @@
         <v>1.48</v>
       </c>
       <c r="AN149">
-        <v>0.61</v>
+        <v>1.11</v>
       </c>
       <c r="AO149">
-        <v>0.9399999999999999</v>
+        <v>0.44</v>
       </c>
       <c r="AP149">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ149">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR149">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AS149">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="AT149">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AU149">
         <v>8</v>
@@ -32199,25 +32199,25 @@
         <v>1.75</v>
       </c>
       <c r="AN150">
-        <v>2.11</v>
+        <v>2.78</v>
       </c>
       <c r="AO150">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="AP150">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ150">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR150">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
       <c r="AS150">
-        <v>1.59</v>
+        <v>1.42</v>
       </c>
       <c r="AT150">
-        <v>3.28</v>
+        <v>3.21</v>
       </c>
       <c r="AU150">
         <v>7</v>
@@ -32405,25 +32405,25 @@
         <v>1.45</v>
       </c>
       <c r="AN151">
-        <v>1.33</v>
+        <v>2</v>
       </c>
       <c r="AO151">
-        <v>1.5</v>
+        <v>1.11</v>
       </c>
       <c r="AP151">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ151">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR151">
-        <v>1.09</v>
+        <v>1.23</v>
       </c>
       <c r="AS151">
-        <v>1.33</v>
+        <v>1.05</v>
       </c>
       <c r="AT151">
-        <v>2.42</v>
+        <v>2.28</v>
       </c>
       <c r="AU151">
         <v>2</v>
@@ -32611,22 +32611,22 @@
         <v>1.5</v>
       </c>
       <c r="AN152">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="AO152">
-        <v>2.06</v>
+        <v>1.89</v>
       </c>
       <c r="AP152">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ152">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR152">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AS152">
-        <v>1.82</v>
+        <v>1.62</v>
       </c>
       <c r="AT152">
         <v>3.43</v>
@@ -32817,25 +32817,25 @@
         <v>1.72</v>
       </c>
       <c r="AN153">
-        <v>0.9399999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="AO153">
-        <v>1.22</v>
+        <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR153">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AS153">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="AT153">
-        <v>2.71</v>
+        <v>2.85</v>
       </c>
       <c r="AU153">
         <v>5</v>
@@ -33023,25 +33023,25 @@
         <v>1.48</v>
       </c>
       <c r="AN154">
-        <v>1.63</v>
+        <v>1.78</v>
       </c>
       <c r="AO154">
-        <v>2.16</v>
+        <v>1.44</v>
       </c>
       <c r="AP154">
+        <v>1.93</v>
+      </c>
+      <c r="AQ154">
+        <v>1.71</v>
+      </c>
+      <c r="AR154">
+        <v>1.81</v>
+      </c>
+      <c r="AS154">
         <v>1.61</v>
       </c>
-      <c r="AQ154">
-        <v>2.21</v>
-      </c>
-      <c r="AR154">
-        <v>1.48</v>
-      </c>
-      <c r="AS154">
-        <v>1.7</v>
-      </c>
       <c r="AT154">
-        <v>3.18</v>
+        <v>3.42</v>
       </c>
       <c r="AU154">
         <v>4</v>
@@ -33229,25 +33229,25 @@
         <v>1.38</v>
       </c>
       <c r="AN155">
-        <v>0.95</v>
+        <v>1.44</v>
       </c>
       <c r="AO155">
-        <v>1.26</v>
+        <v>0.7</v>
       </c>
       <c r="AP155">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ155">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR155">
-        <v>1.24</v>
+        <v>1.43</v>
       </c>
       <c r="AS155">
-        <v>1.57</v>
+        <v>1.4</v>
       </c>
       <c r="AT155">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="AU155">
         <v>3</v>
@@ -33435,25 +33435,25 @@
         <v>3.4</v>
       </c>
       <c r="AN156">
-        <v>2</v>
+        <v>2.22</v>
       </c>
       <c r="AO156">
-        <v>1.21</v>
+        <v>0.78</v>
       </c>
       <c r="AP156">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ156">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR156">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AS156">
-        <v>1.65</v>
+        <v>1.41</v>
       </c>
       <c r="AT156">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="AU156">
         <v>10</v>
@@ -33641,22 +33641,22 @@
         <v>1.93</v>
       </c>
       <c r="AN157">
-        <v>1.37</v>
+        <v>1.7</v>
       </c>
       <c r="AO157">
-        <v>1.26</v>
+        <v>0.67</v>
       </c>
       <c r="AP157">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ157">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR157">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AS157">
-        <v>1.08</v>
+        <v>0.96</v>
       </c>
       <c r="AT157">
         <v>2.5</v>
@@ -33847,25 +33847,25 @@
         <v>1.3</v>
       </c>
       <c r="AN158">
-        <v>1.58</v>
+        <v>1.89</v>
       </c>
       <c r="AO158">
-        <v>1.47</v>
+        <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ158">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR158">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="AS158">
-        <v>1.58</v>
+        <v>1.41</v>
       </c>
       <c r="AT158">
-        <v>2.96</v>
+        <v>3.01</v>
       </c>
       <c r="AU158">
         <v>4</v>
@@ -34053,25 +34053,25 @@
         <v>2.2</v>
       </c>
       <c r="AN159">
-        <v>1.16</v>
+        <v>1.56</v>
       </c>
       <c r="AO159">
-        <v>0.63</v>
+        <v>0.11</v>
       </c>
       <c r="AP159">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ159">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR159">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AS159">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="AT159">
-        <v>2.34</v>
+        <v>2.2</v>
       </c>
       <c r="AU159">
         <v>11</v>
@@ -34259,25 +34259,25 @@
         <v>1.5</v>
       </c>
       <c r="AN160">
-        <v>0.95</v>
+        <v>1.44</v>
       </c>
       <c r="AO160">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP160">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ160">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR160">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="AS160">
-        <v>1.49</v>
+        <v>1.39</v>
       </c>
       <c r="AT160">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AU160">
         <v>8</v>
@@ -34465,25 +34465,25 @@
         <v>2.95</v>
       </c>
       <c r="AN161">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="AO161">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ161">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR161">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AS161">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AT161">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AU161">
         <v>6</v>
@@ -34671,25 +34671,25 @@
         <v>1.83</v>
       </c>
       <c r="AN162">
-        <v>1.25</v>
+        <v>1.8</v>
       </c>
       <c r="AO162">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ162">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR162">
-        <v>1.05</v>
+        <v>1.18</v>
       </c>
       <c r="AS162">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AT162">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AU162">
         <v>7</v>
@@ -34877,25 +34877,25 @@
         <v>1.75</v>
       </c>
       <c r="AN163">
-        <v>1.15</v>
+        <v>1.6</v>
       </c>
       <c r="AO163">
-        <v>0.95</v>
+        <v>0.5</v>
       </c>
       <c r="AP163">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ163">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR163">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AS163">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AT163">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="AU163">
         <v>7</v>
@@ -35083,22 +35083,22 @@
         <v>2.3</v>
       </c>
       <c r="AN164">
-        <v>2.1</v>
+        <v>2.8</v>
       </c>
       <c r="AO164">
-        <v>1.25</v>
+        <v>0.8</v>
       </c>
       <c r="AP164">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ164">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR164">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="AS164">
-        <v>1.25</v>
+        <v>1.21</v>
       </c>
       <c r="AT164">
         <v>3</v>
@@ -35289,25 +35289,25 @@
         <v>1.34</v>
       </c>
       <c r="AN165">
-        <v>1.35</v>
+        <v>1.89</v>
       </c>
       <c r="AO165">
-        <v>1.55</v>
+        <v>1</v>
       </c>
       <c r="AP165">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ165">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR165">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AS165">
-        <v>1.59</v>
+        <v>1.44</v>
       </c>
       <c r="AT165">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="AU165">
         <v>5</v>
@@ -35495,25 +35495,25 @@
         <v>1.21</v>
       </c>
       <c r="AN166">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="AO166">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ166">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR166">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AS166">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="AT166">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="AU166">
         <v>8</v>
@@ -35701,25 +35701,25 @@
         <v>1.33</v>
       </c>
       <c r="AN167">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AO167">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AP167">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ167">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR167">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="AS167">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="AT167">
-        <v>2.44</v>
+        <v>2.24</v>
       </c>
       <c r="AU167">
         <v>4</v>
@@ -35907,25 +35907,25 @@
         <v>1.32</v>
       </c>
       <c r="AN168">
-        <v>1.65</v>
+        <v>1.8</v>
       </c>
       <c r="AO168">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AP168">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ168">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR168">
-        <v>1.54</v>
+        <v>1.71</v>
       </c>
       <c r="AS168">
-        <v>1.81</v>
+        <v>1.6</v>
       </c>
       <c r="AT168">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="AU168">
         <v>6</v>
@@ -36113,25 +36113,25 @@
         <v>1.62</v>
       </c>
       <c r="AN169">
-        <v>1.05</v>
+        <v>1.5</v>
       </c>
       <c r="AO169">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="AP169">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ169">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR169">
-        <v>1.46</v>
+        <v>1.59</v>
       </c>
       <c r="AS169">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
       <c r="AT169">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="AU169">
         <v>8</v>
@@ -36319,25 +36319,25 @@
         <v>1.72</v>
       </c>
       <c r="AN170">
-        <v>1.48</v>
+        <v>1.7</v>
       </c>
       <c r="AO170">
-        <v>1.29</v>
+        <v>0.91</v>
       </c>
       <c r="AP170">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ170">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR170">
-        <v>1.34</v>
+        <v>1.54</v>
       </c>
       <c r="AS170">
-        <v>1.56</v>
+        <v>1.44</v>
       </c>
       <c r="AT170">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="AU170">
         <v>4</v>
@@ -36525,25 +36525,25 @@
         <v>1.41</v>
       </c>
       <c r="AN171">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AO171">
-        <v>1.14</v>
+        <v>0.6</v>
       </c>
       <c r="AP171">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ171">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR171">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="AS171">
-        <v>1.5</v>
+        <v>1.34</v>
       </c>
       <c r="AT171">
-        <v>2.6</v>
+        <v>2.42</v>
       </c>
       <c r="AU171">
         <v>2</v>
@@ -36731,25 +36731,25 @@
         <v>1.41</v>
       </c>
       <c r="AN172">
-        <v>1.29</v>
+        <v>1.64</v>
       </c>
       <c r="AO172">
-        <v>2.14</v>
+        <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ172">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR172">
-        <v>1.43</v>
+        <v>1.56</v>
       </c>
       <c r="AS172">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AT172">
-        <v>3.16</v>
+        <v>3.28</v>
       </c>
       <c r="AU172">
         <v>3</v>
@@ -36937,25 +36937,25 @@
         <v>5.25</v>
       </c>
       <c r="AN173">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AO173">
-        <v>0.62</v>
+        <v>0.1</v>
       </c>
       <c r="AP173">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ173">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR173">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AS173">
-        <v>1.18</v>
+        <v>1.04</v>
       </c>
       <c r="AT173">
-        <v>2.98</v>
+        <v>3.08</v>
       </c>
       <c r="AU173">
         <v>10</v>
@@ -37143,25 +37143,25 @@
         <v>1.26</v>
       </c>
       <c r="AN174">
-        <v>0.86</v>
+        <v>1.3</v>
       </c>
       <c r="AO174">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ174">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR174">
-        <v>1.26</v>
+        <v>1.38</v>
       </c>
       <c r="AS174">
-        <v>1.54</v>
+        <v>1.37</v>
       </c>
       <c r="AT174">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="AU174">
         <v>4</v>
@@ -37349,25 +37349,25 @@
         <v>2.45</v>
       </c>
       <c r="AN175">
-        <v>1.62</v>
+        <v>2.1</v>
       </c>
       <c r="AO175">
-        <v>1.19</v>
+        <v>0.73</v>
       </c>
       <c r="AP175">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ175">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR175">
-        <v>1.58</v>
+        <v>1.74</v>
       </c>
       <c r="AS175">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AT175">
-        <v>2.84</v>
+        <v>2.97</v>
       </c>
       <c r="AU175">
         <v>10</v>
@@ -37555,25 +37555,25 @@
         <v>1.77</v>
       </c>
       <c r="AN176">
-        <v>1.05</v>
+        <v>1.4</v>
       </c>
       <c r="AO176">
-        <v>1.33</v>
+        <v>0.7</v>
       </c>
       <c r="AP176">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ176">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR176">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AS176">
-        <v>1.07</v>
+        <v>0.93</v>
       </c>
       <c r="AT176">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="AU176">
         <v>3</v>
@@ -37761,25 +37761,25 @@
         <v>2.05</v>
       </c>
       <c r="AN177">
-        <v>1.57</v>
+        <v>1.7</v>
       </c>
       <c r="AO177">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="AP177">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ177">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR177">
-        <v>1.45</v>
+        <v>1.71</v>
       </c>
       <c r="AS177">
-        <v>1.7</v>
+        <v>1.48</v>
       </c>
       <c r="AT177">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="AU177">
         <v>8</v>
@@ -37967,25 +37967,25 @@
         <v>1.41</v>
       </c>
       <c r="AN178">
-        <v>1</v>
+        <v>1.27</v>
       </c>
       <c r="AO178">
-        <v>1.64</v>
+        <v>1.45</v>
       </c>
       <c r="AP178">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ178">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR178">
-        <v>1.45</v>
+        <v>1.57</v>
       </c>
       <c r="AS178">
-        <v>1.46</v>
+        <v>1.23</v>
       </c>
       <c r="AT178">
-        <v>2.91</v>
+        <v>2.8</v>
       </c>
       <c r="AU178">
         <v>5</v>
@@ -38173,25 +38173,25 @@
         <v>1.33</v>
       </c>
       <c r="AN179">
-        <v>1.05</v>
+        <v>1.45</v>
       </c>
       <c r="AO179">
-        <v>2.18</v>
+        <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ179">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR179">
-        <v>1.73</v>
+        <v>1.9</v>
       </c>
       <c r="AS179">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AT179">
-        <v>3.48</v>
+        <v>3.67</v>
       </c>
       <c r="AU179">
         <v>6</v>
@@ -38379,25 +38379,25 @@
         <v>1.78</v>
       </c>
       <c r="AN180">
-        <v>1.27</v>
+        <v>1.7</v>
       </c>
       <c r="AO180">
-        <v>1.23</v>
+        <v>0.82</v>
       </c>
       <c r="AP180">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ180">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR180">
-        <v>1.55</v>
+        <v>1.69</v>
       </c>
       <c r="AS180">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="AT180">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="AU180">
         <v>5</v>
@@ -38585,25 +38585,25 @@
         <v>4.4</v>
       </c>
       <c r="AN181">
+        <v>2.36</v>
+      </c>
+      <c r="AO181">
+        <v>0.45</v>
+      </c>
+      <c r="AP181">
         <v>2.14</v>
       </c>
-      <c r="AO181">
-        <v>0.82</v>
-      </c>
-      <c r="AP181">
-        <v>1.89</v>
-      </c>
       <c r="AQ181">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR181">
-        <v>1.82</v>
+        <v>2.05</v>
       </c>
       <c r="AS181">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AT181">
-        <v>3.08</v>
+        <v>3.2</v>
       </c>
       <c r="AU181">
         <v>8</v>
@@ -38791,25 +38791,25 @@
         <v>1.65</v>
       </c>
       <c r="AN182">
-        <v>1.41</v>
+        <v>1.91</v>
       </c>
       <c r="AO182">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="AP182">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ182">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR182">
-        <v>1.09</v>
+        <v>1.21</v>
       </c>
       <c r="AS182">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AT182">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="AU182">
         <v>7</v>
@@ -38997,25 +38997,25 @@
         <v>1.13</v>
       </c>
       <c r="AN183">
-        <v>0.59</v>
+        <v>1.09</v>
       </c>
       <c r="AO183">
-        <v>1.68</v>
+        <v>1.18</v>
       </c>
       <c r="AP183">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ183">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR183">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="AS183">
-        <v>1.61</v>
+        <v>1.43</v>
       </c>
       <c r="AT183">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AU183">
         <v>5</v>
@@ -39206,22 +39206,22 @@
         <v>1.64</v>
       </c>
       <c r="AO184">
-        <v>1.23</v>
+        <v>0.9</v>
       </c>
       <c r="AP184">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ184">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR184">
-        <v>1.54</v>
+        <v>1.69</v>
       </c>
       <c r="AS184">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="AT184">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="AU184">
         <v>7</v>
@@ -39409,25 +39409,25 @@
         <v>1.51</v>
       </c>
       <c r="AN185">
-        <v>1.14</v>
+        <v>1.7</v>
       </c>
       <c r="AO185">
-        <v>1.45</v>
+        <v>1.27</v>
       </c>
       <c r="AP185">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ185">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR185">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AS185">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AT185">
-        <v>2.58</v>
+        <v>2.44</v>
       </c>
       <c r="AU185">
         <v>3</v>
@@ -39615,25 +39615,25 @@
         <v>1.52</v>
       </c>
       <c r="AN186">
-        <v>1.13</v>
+        <v>1.64</v>
       </c>
       <c r="AO186">
-        <v>1.17</v>
+        <v>0.82</v>
       </c>
       <c r="AP186">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ186">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR186">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AS186">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="AT186">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="AU186">
         <v>2</v>
@@ -39821,25 +39821,25 @@
         <v>2.2</v>
       </c>
       <c r="AN187">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="AO187">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AP187">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ187">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR187">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="AS187">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AT187">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="AU187">
         <v>11</v>
@@ -40027,25 +40027,25 @@
         <v>1.95</v>
       </c>
       <c r="AN188">
-        <v>1.22</v>
+        <v>1.64</v>
       </c>
       <c r="AO188">
-        <v>1.48</v>
+        <v>0.91</v>
       </c>
       <c r="AP188">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ188">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR188">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AS188">
-        <v>1.1</v>
+        <v>0.97</v>
       </c>
       <c r="AT188">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AU188">
         <v>4</v>
@@ -40233,25 +40233,25 @@
         <v>3.25</v>
       </c>
       <c r="AN189">
-        <v>2.22</v>
+        <v>2.82</v>
       </c>
       <c r="AO189">
-        <v>0.57</v>
+        <v>0.09</v>
       </c>
       <c r="AP189">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ189">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR189">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AS189">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AT189">
-        <v>2.89</v>
+        <v>2.82</v>
       </c>
       <c r="AU189">
         <v>6</v>
@@ -40439,25 +40439,25 @@
         <v>1.23</v>
       </c>
       <c r="AN190">
-        <v>1.61</v>
+        <v>1.82</v>
       </c>
       <c r="AO190">
-        <v>2.09</v>
+        <v>1.91</v>
       </c>
       <c r="AP190">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ190">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR190">
-        <v>1.47</v>
+        <v>1.72</v>
       </c>
       <c r="AS190">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AT190">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="AU190">
         <v>4</v>
@@ -40645,25 +40645,25 @@
         <v>2.7</v>
       </c>
       <c r="AN191">
-        <v>1.74</v>
+        <v>2.18</v>
       </c>
       <c r="AO191">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AP191">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ191">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR191">
-        <v>1.61</v>
+        <v>1.79</v>
       </c>
       <c r="AS191">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="AT191">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="AU191">
         <v>3</v>
@@ -40851,25 +40851,25 @@
         <v>1.53</v>
       </c>
       <c r="AN192">
-        <v>1.43</v>
+        <v>1.64</v>
       </c>
       <c r="AO192">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ192">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR192">
+        <v>1.52</v>
+      </c>
+      <c r="AS192">
         <v>1.39</v>
       </c>
-      <c r="AS192">
-        <v>1.54</v>
-      </c>
       <c r="AT192">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="AU192">
         <v>8</v>
@@ -41057,25 +41057,25 @@
         <v>1.35</v>
       </c>
       <c r="AN193">
-        <v>0.83</v>
+        <v>1.18</v>
       </c>
       <c r="AO193">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AP193">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ193">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR193">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AS193">
-        <v>1.73</v>
+        <v>1.56</v>
       </c>
       <c r="AT193">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="AU193">
         <v>4</v>
@@ -41263,25 +41263,25 @@
         <v>1.55</v>
       </c>
       <c r="AN194">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AO194">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AP194">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ194">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR194">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AS194">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AT194">
-        <v>2.89</v>
+        <v>2.79</v>
       </c>
       <c r="AU194">
         <v>8</v>
@@ -41469,25 +41469,25 @@
         <v>3.25</v>
       </c>
       <c r="AN195">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AO195">
+        <v>0.67</v>
+      </c>
+      <c r="AP195">
+        <v>2.14</v>
+      </c>
+      <c r="AQ195">
+        <v>0.64</v>
+      </c>
+      <c r="AR195">
+        <v>2.09</v>
+      </c>
+      <c r="AS195">
         <v>1.21</v>
       </c>
-      <c r="AP195">
-        <v>1.89</v>
-      </c>
-      <c r="AQ195">
-        <v>1.22</v>
-      </c>
-      <c r="AR195">
-        <v>1.87</v>
-      </c>
-      <c r="AS195">
-        <v>1.24</v>
-      </c>
       <c r="AT195">
-        <v>3.11</v>
+        <v>3.3</v>
       </c>
       <c r="AU195">
         <v>5</v>
@@ -41675,25 +41675,25 @@
         <v>1.44</v>
       </c>
       <c r="AN196">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AO196">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="AP196">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ196">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR196">
-        <v>1.12</v>
+        <v>1.08</v>
       </c>
       <c r="AS196">
-        <v>1.46</v>
+        <v>1.29</v>
       </c>
       <c r="AT196">
-        <v>2.58</v>
+        <v>2.37</v>
       </c>
       <c r="AU196">
         <v>5</v>
@@ -41881,25 +41881,25 @@
         <v>2.25</v>
       </c>
       <c r="AN197">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="AO197">
-        <v>1.21</v>
+        <v>0.83</v>
       </c>
       <c r="AP197">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ197">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR197">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AS197">
-        <v>1.53</v>
+        <v>1.42</v>
       </c>
       <c r="AT197">
-        <v>3.25</v>
+        <v>3.17</v>
       </c>
       <c r="AU197">
         <v>7</v>
@@ -42087,25 +42087,25 @@
         <v>1.68</v>
       </c>
       <c r="AN198">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="AO198">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AP198">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ198">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR198">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AS198">
-        <v>1.45</v>
+        <v>1.25</v>
       </c>
       <c r="AT198">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="AU198">
         <v>5</v>
@@ -42293,25 +42293,25 @@
         <v>1.16</v>
       </c>
       <c r="AN199">
-        <v>0.79</v>
+        <v>1.08</v>
       </c>
       <c r="AO199">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AP199">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ199">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR199">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AS199">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="AT199">
-        <v>2.85</v>
+        <v>2.78</v>
       </c>
       <c r="AU199">
         <v>3</v>
@@ -42499,25 +42499,25 @@
         <v>2.05</v>
       </c>
       <c r="AN200">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
       <c r="AO200">
-        <v>1.46</v>
+        <v>0.92</v>
       </c>
       <c r="AP200">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ200">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR200">
-        <v>1.74</v>
+        <v>1.89</v>
       </c>
       <c r="AS200">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="AT200">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="AU200">
         <v>10</v>
@@ -42705,25 +42705,25 @@
         <v>1.22</v>
       </c>
       <c r="AN201">
-        <v>0.54</v>
+        <v>1</v>
       </c>
       <c r="AO201">
-        <v>1.33</v>
+        <v>0.92</v>
       </c>
       <c r="AP201">
-        <v>0.5600000000000001</v>
+        <v>1</v>
       </c>
       <c r="AQ201">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR201">
-        <v>1.16</v>
+        <v>1.28</v>
       </c>
       <c r="AS201">
-        <v>1.58</v>
+        <v>1.44</v>
       </c>
       <c r="AT201">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="AU201">
         <v>4</v>
@@ -42911,25 +42911,25 @@
         <v>1.18</v>
       </c>
       <c r="AN202">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="AO202">
-        <v>2.28</v>
+        <v>1.67</v>
       </c>
       <c r="AP202">
-        <v>1.41</v>
+        <v>1.85</v>
       </c>
       <c r="AQ202">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR202">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="AS202">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="AT202">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="AU202">
         <v>4</v>
@@ -43117,25 +43117,25 @@
         <v>1.77</v>
       </c>
       <c r="AN203">
-        <v>1.16</v>
+        <v>1.75</v>
       </c>
       <c r="AO203">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AP203">
-        <v>1.22</v>
+        <v>1.85</v>
       </c>
       <c r="AQ203">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR203">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="AS203">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="AT203">
-        <v>2.36</v>
+        <v>2.43</v>
       </c>
       <c r="AU203">
         <v>5</v>
@@ -43323,25 +43323,25 @@
         <v>2.15</v>
       </c>
       <c r="AN204">
-        <v>1.6</v>
+        <v>1.92</v>
       </c>
       <c r="AO204">
-        <v>0.76</v>
+        <v>0.5</v>
       </c>
       <c r="AP204">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ204">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR204">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="AS204">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="AT204">
-        <v>2.67</v>
+        <v>2.79</v>
       </c>
       <c r="AU204">
         <v>10</v>
@@ -43529,25 +43529,25 @@
         <v>1.17</v>
       </c>
       <c r="AN205">
-        <v>0.92</v>
+        <v>1.25</v>
       </c>
       <c r="AO205">
-        <v>2.04</v>
+        <v>1.75</v>
       </c>
       <c r="AP205">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ205">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR205">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="AS205">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AT205">
-        <v>3.31</v>
+        <v>3.27</v>
       </c>
       <c r="AU205">
         <v>4</v>
@@ -43735,25 +43735,25 @@
         <v>2.65</v>
       </c>
       <c r="AN206">
-        <v>1.48</v>
+        <v>1.75</v>
       </c>
       <c r="AO206">
-        <v>0.5600000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AP206">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ206">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR206">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AS206">
-        <v>1.17</v>
+        <v>1.04</v>
       </c>
       <c r="AT206">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="AU206">
         <v>4</v>
@@ -43941,25 +43941,25 @@
         <v>2.25</v>
       </c>
       <c r="AN207">
-        <v>1.84</v>
+        <v>2.25</v>
       </c>
       <c r="AO207">
-        <v>1.12</v>
+        <v>0.75</v>
       </c>
       <c r="AP207">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ207">
-        <v>1.19</v>
+        <v>0.92</v>
       </c>
       <c r="AR207">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="AS207">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="AT207">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="AU207">
         <v>9</v>
@@ -44147,25 +44147,25 @@
         <v>1.49</v>
       </c>
       <c r="AN208">
-        <v>1.32</v>
+        <v>1.75</v>
       </c>
       <c r="AO208">
-        <v>1.68</v>
+        <v>1.5</v>
       </c>
       <c r="AP208">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ208">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR208">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="AS208">
-        <v>1.53</v>
+        <v>1.39</v>
       </c>
       <c r="AT208">
-        <v>3.08</v>
+        <v>3.11</v>
       </c>
       <c r="AU208">
         <v>6</v>
@@ -44353,25 +44353,25 @@
         <v>1.62</v>
       </c>
       <c r="AN209">
-        <v>1.16</v>
+        <v>1.58</v>
       </c>
       <c r="AO209">
-        <v>1.16</v>
+        <v>0.83</v>
       </c>
       <c r="AP209">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ209">
-        <v>1.11</v>
+        <v>0.85</v>
       </c>
       <c r="AR209">
-        <v>1.53</v>
+        <v>1.64</v>
       </c>
       <c r="AS209">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AT209">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="AU209">
         <v>10</v>
@@ -44559,25 +44559,25 @@
         <v>1.77</v>
       </c>
       <c r="AN210">
-        <v>1.19</v>
+        <v>1.46</v>
       </c>
       <c r="AO210">
-        <v>0.92</v>
+        <v>0.62</v>
       </c>
       <c r="AP210">
-        <v>1.19</v>
+        <v>1.43</v>
       </c>
       <c r="AQ210">
-        <v>1</v>
+        <v>0.64</v>
       </c>
       <c r="AR210">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="AS210">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="AT210">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AU210">
         <v>2</v>
@@ -44765,25 +44765,25 @@
         <v>2</v>
       </c>
       <c r="AN211">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AO211">
-        <v>0.54</v>
+        <v>0.08</v>
       </c>
       <c r="AP211">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="AQ211">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="AR211">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AS211">
-        <v>1.19</v>
+        <v>1.09</v>
       </c>
       <c r="AT211">
-        <v>2.36</v>
+        <v>2.19</v>
       </c>
       <c r="AU211">
         <v>3</v>
@@ -44971,25 +44971,25 @@
         <v>1.68</v>
       </c>
       <c r="AN212">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AO212">
-        <v>1.27</v>
+        <v>0.92</v>
       </c>
       <c r="AP212">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="AQ212">
-        <v>1.32</v>
+        <v>1.07</v>
       </c>
       <c r="AR212">
-        <v>1.74</v>
+        <v>1.93</v>
       </c>
       <c r="AS212">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="AT212">
-        <v>3.3</v>
+        <v>3.33</v>
       </c>
       <c r="AU212">
         <v>5</v>
@@ -45177,25 +45177,25 @@
         <v>1.82</v>
       </c>
       <c r="AN213">
-        <v>1.65</v>
+        <v>2</v>
       </c>
       <c r="AO213">
-        <v>1.23</v>
+        <v>0.62</v>
       </c>
       <c r="AP213">
-        <v>1.61</v>
+        <v>1.93</v>
       </c>
       <c r="AQ213">
-        <v>1.22</v>
+        <v>0.64</v>
       </c>
       <c r="AR213">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="AS213">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="AT213">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="AU213">
         <v>10</v>
@@ -45383,25 +45383,25 @@
         <v>3.4</v>
       </c>
       <c r="AN214">
-        <v>2</v>
+        <v>2.31</v>
       </c>
       <c r="AO214">
-        <v>1.35</v>
+        <v>0.85</v>
       </c>
       <c r="AP214">
-        <v>1.89</v>
+        <v>2.14</v>
       </c>
       <c r="AQ214">
-        <v>1.41</v>
+        <v>1</v>
       </c>
       <c r="AR214">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="AS214">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="AT214">
-        <v>3.02</v>
+        <v>3.13</v>
       </c>
       <c r="AU214">
         <v>7</v>
@@ -45589,25 +45589,25 @@
         <v>2.2</v>
       </c>
       <c r="AN215">
-        <v>2.31</v>
+        <v>2.85</v>
       </c>
       <c r="AO215">
-        <v>1.54</v>
+        <v>1.23</v>
       </c>
       <c r="AP215">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="AQ215">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AR215">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="AS215">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AT215">
-        <v>3.17</v>
+        <v>3.07</v>
       </c>
       <c r="AU215">
         <v>3</v>
@@ -45795,25 +45795,25 @@
         <v>1.46</v>
       </c>
       <c r="AN216">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AO216">
-        <v>1.77</v>
+        <v>1.46</v>
       </c>
       <c r="AP216">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ216">
-        <v>1.86</v>
+        <v>1.57</v>
       </c>
       <c r="AR216">
-        <v>1.51</v>
+        <v>1.66</v>
       </c>
       <c r="AS216">
-        <v>1.64</v>
+        <v>1.46</v>
       </c>
       <c r="AT216">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="AU216">
         <v>6</v>
@@ -46001,25 +46001,25 @@
         <v>1.35</v>
       </c>
       <c r="AN217">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AO217">
-        <v>1.15</v>
+        <v>0.77</v>
       </c>
       <c r="AP217">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AQ217">
-        <v>1.14</v>
+        <v>0.79</v>
       </c>
       <c r="AR217">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AS217">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AT217">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="AU217">
         <v>6</v>
@@ -46207,25 +46207,25 @@
         <v>1.4</v>
       </c>
       <c r="AN218">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AO218">
-        <v>2.26</v>
+        <v>1.77</v>
       </c>
       <c r="AP218">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="AQ218">
-        <v>2.21</v>
+        <v>1.71</v>
       </c>
       <c r="AR218">
-        <v>1.57</v>
+        <v>1.71</v>
       </c>
       <c r="AS218">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="AT218">
-        <v>3.31</v>
+        <v>3.41</v>
       </c>
       <c r="AU218">
         <v>7</v>
@@ -46413,25 +46413,25 @@
         <v>1.22</v>
       </c>
       <c r="AN219">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="AO219">
-        <v>1.93</v>
+        <v>1.69</v>
       </c>
       <c r="AP219">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AQ219">
-        <v>1.89</v>
+        <v>1.64</v>
       </c>
       <c r="AR219">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="AS219">
-        <v>1.89</v>
+        <v>1.71</v>
       </c>
       <c r="AT219">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AU219">
         <v>7</v>
@@ -46619,25 +46619,25 @@
         <v>1.53</v>
       </c>
       <c r="AN220">
-        <v>1.15</v>
+        <v>1.54</v>
       </c>
       <c r="AO220">
-        <v>1.63</v>
+        <v>1.31</v>
       </c>
       <c r="AP220">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AQ220">
-        <v>1.61</v>
+        <v>1.29</v>
       </c>
       <c r="AR220">
-        <v>1.56</v>
+        <v>1.72</v>
       </c>
       <c r="AS220">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AT220">
-        <v>3.06</v>
+        <v>2.96</v>
       </c>
       <c r="AU220">
         <v>11</v>
@@ -46825,25 +46825,25 @@
         <v>2.05</v>
       </c>
       <c r="AN221">
-        <v>0.93</v>
+        <v>1.23</v>
       </c>
       <c r="AO221">
-        <v>0.74</v>
+        <v>0.46</v>
       </c>
       <c r="AP221">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AQ221">
-        <v>0.71</v>
+        <v>0.43</v>
       </c>
       <c r="AR221">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AS221">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="AT221">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="AU221">
         <v>5</v>
@@ -47031,25 +47031,25 @@
         <v>3.1</v>
       </c>
       <c r="AN222">
-        <v>1.81</v>
+        <v>2.08</v>
       </c>
       <c r="AO222">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="AP222">
-        <v>1.86</v>
+        <v>2.14</v>
       </c>
       <c r="AQ222">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AR222">
-        <v>1.62</v>
+        <v>1.82</v>
       </c>
       <c r="AS222">
-        <v>1.17</v>
+        <v>1.24</v>
       </c>
       <c r="AT222">
-        <v>2.79</v>
+        <v>3.06</v>
       </c>
       <c r="AU222">
         <v>14</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1394" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="336">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1383,7 +1383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP222"/>
+  <dimension ref="A1:BP223"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1720,7 +1720,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ2">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ4">
         <v>0.64</v>
@@ -5016,7 +5016,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ18">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR18">
         <v>0.9399999999999999</v>
@@ -6867,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ27">
         <v>1.71</v>
@@ -8518,7 +8518,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ35">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR35">
         <v>2.22</v>
@@ -9957,7 +9957,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ42">
         <v>1.07</v>
@@ -12638,7 +12638,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ55">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR55">
         <v>1.72</v>
@@ -13253,7 +13253,7 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ58">
         <v>0.64</v>
@@ -15110,7 +15110,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ67">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR67">
         <v>1.91</v>
@@ -18197,7 +18197,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ82">
         <v>1.62</v>
@@ -20260,7 +20260,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ92">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR92">
         <v>1.14</v>
@@ -22935,7 +22935,7 @@
         <v>1.33</v>
       </c>
       <c r="AP105">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ105">
         <v>1.21</v>
@@ -23144,7 +23144,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ106">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR106">
         <v>1.33</v>
@@ -24583,7 +24583,7 @@
         <v>1.86</v>
       </c>
       <c r="AP113">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ113">
         <v>1.64</v>
@@ -26440,7 +26440,7 @@
         <v>1</v>
       </c>
       <c r="AQ122">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR122">
         <v>1.47</v>
@@ -27467,7 +27467,7 @@
         <v>0.57</v>
       </c>
       <c r="AP127">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ127">
         <v>0.79</v>
@@ -29939,7 +29939,7 @@
         <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ139">
         <v>1</v>
@@ -31384,7 +31384,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ146">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR146">
         <v>1.85</v>
@@ -31999,7 +31999,7 @@
         <v>0.44</v>
       </c>
       <c r="AP149">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ149">
         <v>0.43</v>
@@ -35501,7 +35501,7 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ166">
         <v>1.29</v>
@@ -36122,7 +36122,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ169">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR169">
         <v>1.59</v>
@@ -39003,7 +39003,7 @@
         <v>1.18</v>
       </c>
       <c r="AP183">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ183">
         <v>1.57</v>
@@ -39212,7 +39212,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ184">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR184">
         <v>1.69</v>
@@ -39624,7 +39624,7 @@
         <v>1.85</v>
       </c>
       <c r="AQ186">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR186">
         <v>1.34</v>
@@ -42711,7 +42711,7 @@
         <v>0.92</v>
       </c>
       <c r="AP201">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AQ201">
         <v>1.07</v>
@@ -43950,7 +43950,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ207">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="AR207">
         <v>1.77</v>
@@ -47116,6 +47116,212 @@
       </c>
       <c r="BP222">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="223" spans="1:68">
+      <c r="A223" s="1">
+        <v>222</v>
+      </c>
+      <c r="B223">
+        <v>7453637</v>
+      </c>
+      <c r="C223" t="s">
+        <v>68</v>
+      </c>
+      <c r="D223" t="s">
+        <v>69</v>
+      </c>
+      <c r="E223" s="2">
+        <v>45718.5</v>
+      </c>
+      <c r="F223">
+        <v>28</v>
+      </c>
+      <c r="G223" t="s">
+        <v>72</v>
+      </c>
+      <c r="H223" t="s">
+        <v>79</v>
+      </c>
+      <c r="I223">
+        <v>1</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+      <c r="L223">
+        <v>1</v>
+      </c>
+      <c r="M223">
+        <v>0</v>
+      </c>
+      <c r="N223">
+        <v>1</v>
+      </c>
+      <c r="O223" t="s">
+        <v>95</v>
+      </c>
+      <c r="P223" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q223">
+        <v>4.33</v>
+      </c>
+      <c r="R223">
+        <v>2.25</v>
+      </c>
+      <c r="S223">
+        <v>2.5</v>
+      </c>
+      <c r="T223">
+        <v>1.33</v>
+      </c>
+      <c r="U223">
+        <v>3.25</v>
+      </c>
+      <c r="V223">
+        <v>2.63</v>
+      </c>
+      <c r="W223">
+        <v>1.44</v>
+      </c>
+      <c r="X223">
+        <v>6.5</v>
+      </c>
+      <c r="Y223">
+        <v>1.11</v>
+      </c>
+      <c r="Z223">
+        <v>3.09</v>
+      </c>
+      <c r="AA223">
+        <v>3.39</v>
+      </c>
+      <c r="AB223">
+        <v>2.21</v>
+      </c>
+      <c r="AC223">
+        <v>1.03</v>
+      </c>
+      <c r="AD223">
+        <v>13</v>
+      </c>
+      <c r="AE223">
+        <v>1.24</v>
+      </c>
+      <c r="AF223">
+        <v>3.89</v>
+      </c>
+      <c r="AG223">
+        <v>1.8</v>
+      </c>
+      <c r="AH223">
+        <v>1.94</v>
+      </c>
+      <c r="AI223">
+        <v>1.67</v>
+      </c>
+      <c r="AJ223">
+        <v>2.1</v>
+      </c>
+      <c r="AK223">
+        <v>1.87</v>
+      </c>
+      <c r="AL223">
+        <v>1.27</v>
+      </c>
+      <c r="AM223">
+        <v>1.25</v>
+      </c>
+      <c r="AN223">
+        <v>1</v>
+      </c>
+      <c r="AO223">
+        <v>0.92</v>
+      </c>
+      <c r="AP223">
+        <v>1.14</v>
+      </c>
+      <c r="AQ223">
+        <v>0.86</v>
+      </c>
+      <c r="AR223">
+        <v>1.28</v>
+      </c>
+      <c r="AS223">
+        <v>1.48</v>
+      </c>
+      <c r="AT223">
+        <v>2.76</v>
+      </c>
+      <c r="AU223">
+        <v>5</v>
+      </c>
+      <c r="AV223">
+        <v>8</v>
+      </c>
+      <c r="AW223">
+        <v>9</v>
+      </c>
+      <c r="AX223">
+        <v>9</v>
+      </c>
+      <c r="AY223">
+        <v>15</v>
+      </c>
+      <c r="AZ223">
+        <v>18</v>
+      </c>
+      <c r="BA223">
+        <v>4</v>
+      </c>
+      <c r="BB223">
+        <v>9</v>
+      </c>
+      <c r="BC223">
+        <v>13</v>
+      </c>
+      <c r="BD223">
+        <v>2.33</v>
+      </c>
+      <c r="BE223">
+        <v>6.75</v>
+      </c>
+      <c r="BF223">
+        <v>1.73</v>
+      </c>
+      <c r="BG223">
+        <v>1.24</v>
+      </c>
+      <c r="BH223">
+        <v>3.55</v>
+      </c>
+      <c r="BI223">
+        <v>1.42</v>
+      </c>
+      <c r="BJ223">
+        <v>2.65</v>
+      </c>
+      <c r="BK223">
+        <v>1.68</v>
+      </c>
+      <c r="BL223">
+        <v>2.05</v>
+      </c>
+      <c r="BM223">
+        <v>2.05</v>
+      </c>
+      <c r="BN223">
+        <v>1.68</v>
+      </c>
+      <c r="BO223">
+        <v>2.55</v>
+      </c>
+      <c r="BP223">
+        <v>1.43</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="337">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1023,6 +1023,9 @@
   <si>
     <t>['45', '70']</t>
   </si>
+  <si>
+    <t>['63', '88']</t>
+  </si>
 </sst>
 </file>
 
@@ -1383,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP223"/>
+  <dimension ref="A1:BP225"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3574,7 +3577,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ11">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3777,7 +3780,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ12">
         <v>1.71</v>
@@ -4192,7 +4195,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ14">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4601,7 +4604,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ16">
         <v>1.64</v>
@@ -5013,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ18">
         <v>0.86</v>
@@ -7282,7 +7285,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ29">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR29">
         <v>0.96</v>
@@ -7691,7 +7694,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ31">
         <v>0.79</v>
@@ -8106,7 +8109,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ33">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR33">
         <v>1.52</v>
@@ -9133,7 +9136,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ38">
         <v>0.14</v>
@@ -9548,7 +9551,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ40">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR40">
         <v>1.69</v>
@@ -10163,7 +10166,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ43">
         <v>1</v>
@@ -10784,7 +10787,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ46">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR46">
         <v>1.58</v>
@@ -11814,7 +11817,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ51">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR51">
         <v>1.42</v>
@@ -13047,7 +13050,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ57">
         <v>1.57</v>
@@ -14489,7 +14492,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ64">
         <v>0.43</v>
@@ -15313,10 +15316,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ68">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR68">
         <v>1.04</v>
@@ -15522,7 +15525,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ69">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR69">
         <v>1.21</v>
@@ -18200,7 +18203,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ82">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR82">
         <v>0.92</v>
@@ -19227,7 +19230,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ87">
         <v>1.29</v>
@@ -19433,7 +19436,7 @@
         <v>0.8</v>
       </c>
       <c r="AP88">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ88">
         <v>1.07</v>
@@ -20466,7 +20469,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ93">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR93">
         <v>1.23</v>
@@ -20672,7 +20675,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ94">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR94">
         <v>2.03</v>
@@ -21699,7 +21702,7 @@
         <v>0.83</v>
       </c>
       <c r="AP99">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ99">
         <v>0.64</v>
@@ -21905,7 +21908,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ100">
         <v>1.64</v>
@@ -23762,7 +23765,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ109">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR109">
         <v>1.75</v>
@@ -23968,7 +23971,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ110">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR110">
         <v>1.65</v>
@@ -25201,7 +25204,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ116">
         <v>0.79</v>
@@ -25819,7 +25822,7 @@
         <v>0.71</v>
       </c>
       <c r="AP119">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ119">
         <v>1.57</v>
@@ -27261,10 +27264,10 @@
         <v>1.57</v>
       </c>
       <c r="AP126">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ126">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR126">
         <v>1.26</v>
@@ -28291,7 +28294,7 @@
         <v>0.88</v>
       </c>
       <c r="AP131">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ131">
         <v>0.64</v>
@@ -29530,7 +29533,7 @@
         <v>1.21</v>
       </c>
       <c r="AQ137">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR137">
         <v>1.17</v>
@@ -30145,7 +30148,7 @@
         <v>0.78</v>
       </c>
       <c r="AP140">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ140">
         <v>1.07</v>
@@ -30766,7 +30769,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ143">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR143">
         <v>1.68</v>
@@ -30972,7 +30975,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ144">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR144">
         <v>1.4</v>
@@ -32208,7 +32211,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ150">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR150">
         <v>1.79</v>
@@ -32411,7 +32414,7 @@
         <v>1.11</v>
       </c>
       <c r="AP151">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ151">
         <v>1.21</v>
@@ -33444,7 +33447,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ156">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR156">
         <v>2.05</v>
@@ -34059,7 +34062,7 @@
         <v>0.11</v>
       </c>
       <c r="AP159">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ159">
         <v>0.14</v>
@@ -34677,7 +34680,7 @@
         <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ162">
         <v>0.43</v>
@@ -37152,7 +37155,7 @@
         <v>1</v>
       </c>
       <c r="AQ174">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR174">
         <v>1.38</v>
@@ -37770,7 +37773,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ177">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR177">
         <v>1.71</v>
@@ -38797,7 +38800,7 @@
         <v>1.5</v>
       </c>
       <c r="AP182">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ182">
         <v>1.07</v>
@@ -39415,7 +39418,7 @@
         <v>1.27</v>
       </c>
       <c r="AP185">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ185">
         <v>1.21</v>
@@ -39621,7 +39624,7 @@
         <v>0.82</v>
       </c>
       <c r="AP186">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ186">
         <v>0.86</v>
@@ -40860,7 +40863,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ192">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR192">
         <v>1.52</v>
@@ -41066,7 +41069,7 @@
         <v>1</v>
       </c>
       <c r="AQ193">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR193">
         <v>1.37</v>
@@ -42917,7 +42920,7 @@
         <v>1.67</v>
       </c>
       <c r="AP202">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AQ202">
         <v>1.71</v>
@@ -43123,7 +43126,7 @@
         <v>1.25</v>
       </c>
       <c r="AP203">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AQ203">
         <v>1.07</v>
@@ -44156,7 +44159,7 @@
         <v>1.57</v>
       </c>
       <c r="AQ208">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="AR208">
         <v>1.72</v>
@@ -44362,7 +44365,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ209">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="AR209">
         <v>1.64</v>
@@ -47322,6 +47325,418 @@
       </c>
       <c r="BP223">
         <v>1.43</v>
+      </c>
+    </row>
+    <row r="224" spans="1:68">
+      <c r="A224" s="1">
+        <v>223</v>
+      </c>
+      <c r="B224">
+        <v>7453636</v>
+      </c>
+      <c r="C224" t="s">
+        <v>68</v>
+      </c>
+      <c r="D224" t="s">
+        <v>69</v>
+      </c>
+      <c r="E224" s="2">
+        <v>45718.60416666666</v>
+      </c>
+      <c r="F224">
+        <v>28</v>
+      </c>
+      <c r="G224" t="s">
+        <v>84</v>
+      </c>
+      <c r="H224" t="s">
+        <v>73</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+      <c r="M224">
+        <v>2</v>
+      </c>
+      <c r="N224">
+        <v>2</v>
+      </c>
+      <c r="O224" t="s">
+        <v>87</v>
+      </c>
+      <c r="P224" t="s">
+        <v>336</v>
+      </c>
+      <c r="Q224">
+        <v>4.33</v>
+      </c>
+      <c r="R224">
+        <v>2.1</v>
+      </c>
+      <c r="S224">
+        <v>2.63</v>
+      </c>
+      <c r="T224">
+        <v>1.44</v>
+      </c>
+      <c r="U224">
+        <v>2.63</v>
+      </c>
+      <c r="V224">
+        <v>3.25</v>
+      </c>
+      <c r="W224">
+        <v>1.33</v>
+      </c>
+      <c r="X224">
+        <v>9</v>
+      </c>
+      <c r="Y224">
+        <v>1.07</v>
+      </c>
+      <c r="Z224">
+        <v>3.95</v>
+      </c>
+      <c r="AA224">
+        <v>3.47</v>
+      </c>
+      <c r="AB224">
+        <v>1.89</v>
+      </c>
+      <c r="AC224">
+        <v>1.05</v>
+      </c>
+      <c r="AD224">
+        <v>8.91</v>
+      </c>
+      <c r="AE224">
+        <v>1.34</v>
+      </c>
+      <c r="AF224">
+        <v>3.14</v>
+      </c>
+      <c r="AG224">
+        <v>1.91</v>
+      </c>
+      <c r="AH224">
+        <v>1.83</v>
+      </c>
+      <c r="AI224">
+        <v>1.95</v>
+      </c>
+      <c r="AJ224">
+        <v>1.8</v>
+      </c>
+      <c r="AK224">
+        <v>1.8</v>
+      </c>
+      <c r="AL224">
+        <v>1.3</v>
+      </c>
+      <c r="AM224">
+        <v>1.26</v>
+      </c>
+      <c r="AN224">
+        <v>1.85</v>
+      </c>
+      <c r="AO224">
+        <v>1.62</v>
+      </c>
+      <c r="AP224">
+        <v>1.71</v>
+      </c>
+      <c r="AQ224">
+        <v>1.71</v>
+      </c>
+      <c r="AR224">
+        <v>1.22</v>
+      </c>
+      <c r="AS224">
+        <v>1.35</v>
+      </c>
+      <c r="AT224">
+        <v>2.57</v>
+      </c>
+      <c r="AU224">
+        <v>5</v>
+      </c>
+      <c r="AV224">
+        <v>4</v>
+      </c>
+      <c r="AW224">
+        <v>7</v>
+      </c>
+      <c r="AX224">
+        <v>5</v>
+      </c>
+      <c r="AY224">
+        <v>13</v>
+      </c>
+      <c r="AZ224">
+        <v>12</v>
+      </c>
+      <c r="BA224">
+        <v>3</v>
+      </c>
+      <c r="BB224">
+        <v>4</v>
+      </c>
+      <c r="BC224">
+        <v>7</v>
+      </c>
+      <c r="BD224">
+        <v>2.4</v>
+      </c>
+      <c r="BE224">
+        <v>6.75</v>
+      </c>
+      <c r="BF224">
+        <v>1.68</v>
+      </c>
+      <c r="BG224">
+        <v>1.34</v>
+      </c>
+      <c r="BH224">
+        <v>2.9</v>
+      </c>
+      <c r="BI224">
+        <v>1.58</v>
+      </c>
+      <c r="BJ224">
+        <v>2.18</v>
+      </c>
+      <c r="BK224">
+        <v>1.96</v>
+      </c>
+      <c r="BL224">
+        <v>1.74</v>
+      </c>
+      <c r="BM224">
+        <v>2.48</v>
+      </c>
+      <c r="BN224">
+        <v>1.47</v>
+      </c>
+      <c r="BO224">
+        <v>3.2</v>
+      </c>
+      <c r="BP224">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="225" spans="1:68">
+      <c r="A225" s="1">
+        <v>224</v>
+      </c>
+      <c r="B225">
+        <v>7453639</v>
+      </c>
+      <c r="C225" t="s">
+        <v>68</v>
+      </c>
+      <c r="D225" t="s">
+        <v>69</v>
+      </c>
+      <c r="E225" s="2">
+        <v>45718.63541666666</v>
+      </c>
+      <c r="F225">
+        <v>28</v>
+      </c>
+      <c r="G225" t="s">
+        <v>80</v>
+      </c>
+      <c r="H225" t="s">
+        <v>77</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>0</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+      <c r="M225">
+        <v>0</v>
+      </c>
+      <c r="N225">
+        <v>0</v>
+      </c>
+      <c r="O225" t="s">
+        <v>87</v>
+      </c>
+      <c r="P225" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q225">
+        <v>3</v>
+      </c>
+      <c r="R225">
+        <v>2.3</v>
+      </c>
+      <c r="S225">
+        <v>3.2</v>
+      </c>
+      <c r="T225">
+        <v>1.3</v>
+      </c>
+      <c r="U225">
+        <v>3.4</v>
+      </c>
+      <c r="V225">
+        <v>2.5</v>
+      </c>
+      <c r="W225">
+        <v>1.5</v>
+      </c>
+      <c r="X225">
+        <v>6</v>
+      </c>
+      <c r="Y225">
+        <v>1.13</v>
+      </c>
+      <c r="Z225">
+        <v>2.46</v>
+      </c>
+      <c r="AA225">
+        <v>3.53</v>
+      </c>
+      <c r="AB225">
+        <v>2.63</v>
+      </c>
+      <c r="AC225">
+        <v>1.03</v>
+      </c>
+      <c r="AD225">
+        <v>15</v>
+      </c>
+      <c r="AE225">
+        <v>1.19</v>
+      </c>
+      <c r="AF225">
+        <v>4.45</v>
+      </c>
+      <c r="AG225">
+        <v>1.61</v>
+      </c>
+      <c r="AH225">
+        <v>2.15</v>
+      </c>
+      <c r="AI225">
+        <v>1.53</v>
+      </c>
+      <c r="AJ225">
+        <v>2.38</v>
+      </c>
+      <c r="AK225">
+        <v>1.46</v>
+      </c>
+      <c r="AL225">
+        <v>1.27</v>
+      </c>
+      <c r="AM225">
+        <v>1.52</v>
+      </c>
+      <c r="AN225">
+        <v>1.85</v>
+      </c>
+      <c r="AO225">
+        <v>0.85</v>
+      </c>
+      <c r="AP225">
+        <v>1.79</v>
+      </c>
+      <c r="AQ225">
+        <v>0.86</v>
+      </c>
+      <c r="AR225">
+        <v>1.31</v>
+      </c>
+      <c r="AS225">
+        <v>1.55</v>
+      </c>
+      <c r="AT225">
+        <v>2.86</v>
+      </c>
+      <c r="AU225">
+        <v>2</v>
+      </c>
+      <c r="AV225">
+        <v>4</v>
+      </c>
+      <c r="AW225">
+        <v>6</v>
+      </c>
+      <c r="AX225">
+        <v>15</v>
+      </c>
+      <c r="AY225">
+        <v>10</v>
+      </c>
+      <c r="AZ225">
+        <v>23</v>
+      </c>
+      <c r="BA225">
+        <v>2</v>
+      </c>
+      <c r="BB225">
+        <v>9</v>
+      </c>
+      <c r="BC225">
+        <v>11</v>
+      </c>
+      <c r="BD225">
+        <v>1.94</v>
+      </c>
+      <c r="BE225">
+        <v>6.75</v>
+      </c>
+      <c r="BF225">
+        <v>2.05</v>
+      </c>
+      <c r="BG225">
+        <v>1.2</v>
+      </c>
+      <c r="BH225">
+        <v>3.95</v>
+      </c>
+      <c r="BI225">
+        <v>1.35</v>
+      </c>
+      <c r="BJ225">
+        <v>2.9</v>
+      </c>
+      <c r="BK225">
+        <v>1.58</v>
+      </c>
+      <c r="BL225">
+        <v>2.18</v>
+      </c>
+      <c r="BM225">
+        <v>1.93</v>
+      </c>
+      <c r="BN225">
+        <v>1.77</v>
+      </c>
+      <c r="BO225">
+        <v>2.4</v>
+      </c>
+      <c r="BP225">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1412" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="339">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -745,6 +745,12 @@
     <t>['28', '32', '53', '86']</t>
   </si>
   <si>
+    <t>['17', '90+6']</t>
+  </si>
+  <si>
+    <t>['44', '63']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1386,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP225"/>
+  <dimension ref="A1:BP229"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1642,7 +1648,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1723,7 +1729,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ2">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR2">
         <v>0</v>
@@ -1926,7 +1932,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ3">
         <v>1.57</v>
@@ -2135,7 +2141,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ4">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2672,7 +2678,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2750,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="AP7">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ7">
         <v>1.21</v>
@@ -2956,7 +2962,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ8">
         <v>1.29</v>
@@ -3371,7 +3377,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ10">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR10">
         <v>0</v>
@@ -3496,7 +3502,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3783,7 +3789,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ12">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -3908,7 +3914,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3986,7 +3992,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ13">
         <v>1.07</v>
@@ -4114,7 +4120,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4320,7 +4326,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4732,7 +4738,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5019,7 +5025,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ18">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR18">
         <v>0.9399999999999999</v>
@@ -5222,7 +5228,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ19">
         <v>0.43</v>
@@ -5350,7 +5356,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5637,7 +5643,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ21">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR21">
         <v>1.37</v>
@@ -5762,7 +5768,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5968,7 +5974,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6252,7 +6258,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ24">
         <v>1.21</v>
@@ -6380,7 +6386,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6461,7 +6467,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ25">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR25">
         <v>2.16</v>
@@ -6792,7 +6798,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6873,7 +6879,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ27">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR27">
         <v>0.45</v>
@@ -6998,7 +7004,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7076,7 +7082,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ28">
         <v>1.07</v>
@@ -7204,7 +7210,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7900,7 +7906,7 @@
         <v>1</v>
       </c>
       <c r="AP32">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ32">
         <v>1</v>
@@ -8234,7 +8240,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8315,7 +8321,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ34">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR34">
         <v>1.74</v>
@@ -8521,7 +8527,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ35">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR35">
         <v>2.22</v>
@@ -8646,7 +8652,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8724,7 +8730,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ36">
         <v>1.64</v>
@@ -8930,7 +8936,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ37">
         <v>1.57</v>
@@ -9139,7 +9145,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ38">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR38">
         <v>1.16</v>
@@ -9342,7 +9348,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ39">
         <v>0.43</v>
@@ -9676,7 +9682,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9882,7 +9888,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10990,7 +10996,7 @@
         <v>0</v>
       </c>
       <c r="AP47">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ47">
         <v>0.64</v>
@@ -11118,7 +11124,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11196,7 +11202,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ48">
         <v>1</v>
@@ -11324,7 +11330,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11405,7 +11411,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR49">
         <v>2.18</v>
@@ -11530,7 +11536,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11608,7 +11614,7 @@
         <v>1</v>
       </c>
       <c r="AP50">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ50">
         <v>1.64</v>
@@ -11736,7 +11742,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12226,10 +12232,10 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ53">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR53">
         <v>0.82</v>
@@ -12432,10 +12438,10 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ54">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR54">
         <v>1.56</v>
@@ -12641,7 +12647,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ55">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR55">
         <v>1.72</v>
@@ -12766,7 +12772,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -12847,7 +12853,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ56">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR56">
         <v>1.68</v>
@@ -13178,7 +13184,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13384,7 +13390,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13796,7 +13802,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14620,7 +14626,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14904,7 +14910,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ66">
         <v>1.64</v>
@@ -15113,7 +15119,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ67">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR67">
         <v>1.91</v>
@@ -15238,7 +15244,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15444,7 +15450,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15522,7 +15528,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ69">
         <v>1.71</v>
@@ -15731,7 +15737,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ70">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR70">
         <v>1.88</v>
@@ -16143,7 +16149,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ72">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR72">
         <v>1.82</v>
@@ -16474,7 +16480,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16555,7 +16561,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ74">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR74">
         <v>1.66</v>
@@ -16761,7 +16767,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ75">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR75">
         <v>1.41</v>
@@ -16964,10 +16970,10 @@
         <v>2.25</v>
       </c>
       <c r="AP76">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ76">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -17170,7 +17176,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ77">
         <v>1.07</v>
@@ -17994,7 +18000,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ81">
         <v>1.21</v>
@@ -18328,7 +18334,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18946,7 +18952,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19848,10 +19854,10 @@
         <v>0.17</v>
       </c>
       <c r="AP90">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ90">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR90">
         <v>1.5</v>
@@ -19976,7 +19982,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20054,10 +20060,10 @@
         <v>0.5</v>
       </c>
       <c r="AP91">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ91">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR91">
         <v>1.77</v>
@@ -20182,7 +20188,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20260,10 +20266,10 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ92">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR92">
         <v>1.14</v>
@@ -20466,7 +20472,7 @@
         <v>1.4</v>
       </c>
       <c r="AP93">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ93">
         <v>0.86</v>
@@ -20594,7 +20600,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -21006,7 +21012,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21087,7 +21093,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ96">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR96">
         <v>1.72</v>
@@ -21212,7 +21218,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21624,7 +21630,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21830,7 +21836,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -22036,7 +22042,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -23066,7 +23072,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23144,10 +23150,10 @@
         <v>1.33</v>
       </c>
       <c r="AP106">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ106">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR106">
         <v>1.33</v>
@@ -23272,7 +23278,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23350,7 +23356,7 @@
         <v>1.33</v>
       </c>
       <c r="AP107">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ107">
         <v>1.29</v>
@@ -23478,7 +23484,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23556,10 +23562,10 @@
         <v>0.86</v>
       </c>
       <c r="AP108">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ108">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR108">
         <v>1.16</v>
@@ -23762,7 +23768,7 @@
         <v>1.17</v>
       </c>
       <c r="AP109">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ109">
         <v>0.86</v>
@@ -23890,7 +23896,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24383,7 +24389,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ112">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR112">
         <v>1.71</v>
@@ -24508,7 +24514,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -25619,7 +25625,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ118">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR118">
         <v>1.51</v>
@@ -25744,7 +25750,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26362,7 +26368,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26440,10 +26446,10 @@
         <v>1.14</v>
       </c>
       <c r="AP122">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ122">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR122">
         <v>1.47</v>
@@ -26852,7 +26858,7 @@
         <v>0.57</v>
       </c>
       <c r="AP124">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ124">
         <v>1</v>
@@ -26980,7 +26986,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27058,10 +27064,10 @@
         <v>1.71</v>
       </c>
       <c r="AP125">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ125">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR125">
         <v>1.37</v>
@@ -27392,7 +27398,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27804,7 +27810,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -28010,7 +28016,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28297,7 +28303,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ131">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR131">
         <v>1.18</v>
@@ -28422,7 +28428,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28834,7 +28840,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29246,7 +29252,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29327,7 +29333,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ136">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR136">
         <v>1.71</v>
@@ -29530,7 +29536,7 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ137">
         <v>0.86</v>
@@ -30276,7 +30282,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30354,7 +30360,7 @@
         <v>1.13</v>
       </c>
       <c r="AP141">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ141">
         <v>1.07</v>
@@ -30563,7 +30569,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ142">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR142">
         <v>2.07</v>
@@ -30688,7 +30694,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30894,7 +30900,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -30972,7 +30978,7 @@
         <v>1.5</v>
       </c>
       <c r="AP144">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ144">
         <v>1.71</v>
@@ -31306,7 +31312,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31387,7 +31393,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ146">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR146">
         <v>1.85</v>
@@ -31590,7 +31596,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP147">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ147">
         <v>0.64</v>
@@ -31718,7 +31724,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31796,7 +31802,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ148">
         <v>1.29</v>
@@ -31924,7 +31930,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32542,7 +32548,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32829,7 +32835,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ153">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR153">
         <v>1.62</v>
@@ -32954,7 +32960,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33035,7 +33041,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ154">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR154">
         <v>1.81</v>
@@ -33160,7 +33166,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33238,7 +33244,7 @@
         <v>0.7</v>
       </c>
       <c r="AP155">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ155">
         <v>1.07</v>
@@ -33366,7 +33372,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33778,7 +33784,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34065,7 +34071,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ159">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR159">
         <v>1.19</v>
@@ -34190,7 +34196,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34268,7 +34274,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP160">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ160">
         <v>0.79</v>
@@ -34396,7 +34402,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34808,7 +34814,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35095,7 +35101,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ164">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR164">
         <v>1.79</v>
@@ -35220,7 +35226,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35298,7 +35304,7 @@
         <v>1</v>
       </c>
       <c r="AP165">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ165">
         <v>1.57</v>
@@ -35426,7 +35432,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35710,7 +35716,7 @@
         <v>1.3</v>
       </c>
       <c r="AP167">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ167">
         <v>1.21</v>
@@ -35838,7 +35844,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36125,7 +36131,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ169">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR169">
         <v>1.59</v>
@@ -36456,7 +36462,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36534,7 +36540,7 @@
         <v>0.6</v>
       </c>
       <c r="AP171">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ171">
         <v>0.79</v>
@@ -36662,7 +36668,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36743,7 +36749,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ172">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR172">
         <v>1.56</v>
@@ -36868,7 +36874,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36949,7 +36955,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ173">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR173">
         <v>2.04</v>
@@ -37074,7 +37080,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37152,7 +37158,7 @@
         <v>1.5</v>
       </c>
       <c r="AP174">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ174">
         <v>1.71</v>
@@ -37361,7 +37367,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ175">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR175">
         <v>1.74</v>
@@ -37486,7 +37492,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37564,7 +37570,7 @@
         <v>0.7</v>
       </c>
       <c r="AP176">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ176">
         <v>1</v>
@@ -37692,7 +37698,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37976,7 +37982,7 @@
         <v>1.45</v>
       </c>
       <c r="AP178">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ178">
         <v>1.29</v>
@@ -38104,7 +38110,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38185,7 +38191,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ179">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR179">
         <v>1.9</v>
@@ -38310,7 +38316,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38388,7 +38394,7 @@
         <v>0.82</v>
       </c>
       <c r="AP180">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ180">
         <v>0.79</v>
@@ -38928,7 +38934,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39134,7 +39140,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39215,7 +39221,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ184">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR184">
         <v>1.69</v>
@@ -39627,7 +39633,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ186">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR186">
         <v>1.34</v>
@@ -39830,7 +39836,7 @@
         <v>1.36</v>
       </c>
       <c r="AP187">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ187">
         <v>1.07</v>
@@ -39958,7 +39964,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40245,7 +40251,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ189">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR189">
         <v>1.74</v>
@@ -40576,7 +40582,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40988,7 +40994,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41066,7 +41072,7 @@
         <v>0.64</v>
       </c>
       <c r="AP193">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ193">
         <v>0.86</v>
@@ -41194,7 +41200,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41481,7 +41487,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ195">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR195">
         <v>2.09</v>
@@ -41684,7 +41690,7 @@
         <v>0.67</v>
       </c>
       <c r="AP196">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ196">
         <v>0.64</v>
@@ -42224,7 +42230,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42302,7 +42308,7 @@
         <v>1.33</v>
       </c>
       <c r="AP199">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ199">
         <v>1.57</v>
@@ -42430,7 +42436,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42842,7 +42848,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -42923,7 +42929,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ202">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR202">
         <v>1.22</v>
@@ -43048,7 +43054,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43254,7 +43260,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43460,7 +43466,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43538,7 +43544,7 @@
         <v>1.75</v>
       </c>
       <c r="AP205">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ205">
         <v>1.64</v>
@@ -43666,7 +43672,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -43747,7 +43753,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ206">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR206">
         <v>1.54</v>
@@ -43953,7 +43959,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ207">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR207">
         <v>1.77</v>
@@ -44156,7 +44162,7 @@
         <v>1.5</v>
       </c>
       <c r="AP208">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ208">
         <v>1.71</v>
@@ -44774,10 +44780,10 @@
         <v>0.08</v>
       </c>
       <c r="AP211">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="AQ211">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AR211">
         <v>1.1</v>
@@ -44902,7 +44908,7 @@
         <v>227</v>
       </c>
       <c r="P212" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q212">
         <v>2.75</v>
@@ -45108,7 +45114,7 @@
         <v>239</v>
       </c>
       <c r="P213" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -45189,7 +45195,7 @@
         <v>1.93</v>
       </c>
       <c r="AQ213">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR213">
         <v>1.7</v>
@@ -45314,7 +45320,7 @@
         <v>86</v>
       </c>
       <c r="P214" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q214">
         <v>1.71</v>
@@ -45726,7 +45732,7 @@
         <v>87</v>
       </c>
       <c r="P216" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q216">
         <v>3.25</v>
@@ -46010,7 +46016,7 @@
         <v>0.77</v>
       </c>
       <c r="AP217">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="AQ217">
         <v>0.79</v>
@@ -46216,10 +46222,10 @@
         <v>1.77</v>
       </c>
       <c r="AP218">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AQ218">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AR218">
         <v>1.71</v>
@@ -46344,7 +46350,7 @@
         <v>88</v>
       </c>
       <c r="P219" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46756,7 +46762,7 @@
         <v>241</v>
       </c>
       <c r="P221" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q221">
         <v>2.25</v>
@@ -46834,7 +46840,7 @@
         <v>0.46</v>
       </c>
       <c r="AP221">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ221">
         <v>0.43</v>
@@ -47249,7 +47255,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ223">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR223">
         <v>1.28</v>
@@ -47374,7 +47380,7 @@
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q224">
         <v>4.33</v>
@@ -47737,6 +47743,830 @@
       </c>
       <c r="BP225">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:68">
+      <c r="A226" s="1">
+        <v>225</v>
+      </c>
+      <c r="B226">
+        <v>7453646</v>
+      </c>
+      <c r="C226" t="s">
+        <v>68</v>
+      </c>
+      <c r="D226" t="s">
+        <v>69</v>
+      </c>
+      <c r="E226" s="2">
+        <v>45723.69791666666</v>
+      </c>
+      <c r="F226">
+        <v>29</v>
+      </c>
+      <c r="G226" t="s">
+        <v>81</v>
+      </c>
+      <c r="H226" t="s">
+        <v>72</v>
+      </c>
+      <c r="I226">
+        <v>1</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>1</v>
+      </c>
+      <c r="L226">
+        <v>2</v>
+      </c>
+      <c r="M226">
+        <v>0</v>
+      </c>
+      <c r="N226">
+        <v>2</v>
+      </c>
+      <c r="O226" t="s">
+        <v>243</v>
+      </c>
+      <c r="P226" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q226">
+        <v>2</v>
+      </c>
+      <c r="R226">
+        <v>2.38</v>
+      </c>
+      <c r="S226">
+        <v>5</v>
+      </c>
+      <c r="T226">
+        <v>1.3</v>
+      </c>
+      <c r="U226">
+        <v>3.25</v>
+      </c>
+      <c r="V226">
+        <v>2.35</v>
+      </c>
+      <c r="W226">
+        <v>1.53</v>
+      </c>
+      <c r="X226">
+        <v>5.85</v>
+      </c>
+      <c r="Y226">
+        <v>1.07</v>
+      </c>
+      <c r="Z226">
+        <v>1.62</v>
+      </c>
+      <c r="AA226">
+        <v>4.2</v>
+      </c>
+      <c r="AB226">
+        <v>4.7</v>
+      </c>
+      <c r="AC226">
+        <v>1.04</v>
+      </c>
+      <c r="AD226">
+        <v>10</v>
+      </c>
+      <c r="AE226">
+        <v>1.2</v>
+      </c>
+      <c r="AF226">
+        <v>4.33</v>
+      </c>
+      <c r="AG226">
+        <v>1.61</v>
+      </c>
+      <c r="AH226">
+        <v>2.2</v>
+      </c>
+      <c r="AI226">
+        <v>1.65</v>
+      </c>
+      <c r="AJ226">
+        <v>2.05</v>
+      </c>
+      <c r="AK226">
+        <v>1.15</v>
+      </c>
+      <c r="AL226">
+        <v>1.18</v>
+      </c>
+      <c r="AM226">
+        <v>2.3</v>
+      </c>
+      <c r="AN226">
+        <v>1.36</v>
+      </c>
+      <c r="AO226">
+        <v>0.14</v>
+      </c>
+      <c r="AP226">
+        <v>1.47</v>
+      </c>
+      <c r="AQ226">
+        <v>0.13</v>
+      </c>
+      <c r="AR226">
+        <v>1.52</v>
+      </c>
+      <c r="AS226">
+        <v>1.14</v>
+      </c>
+      <c r="AT226">
+        <v>2.66</v>
+      </c>
+      <c r="AU226">
+        <v>7</v>
+      </c>
+      <c r="AV226">
+        <v>4</v>
+      </c>
+      <c r="AW226">
+        <v>8</v>
+      </c>
+      <c r="AX226">
+        <v>8</v>
+      </c>
+      <c r="AY226">
+        <v>18</v>
+      </c>
+      <c r="AZ226">
+        <v>13</v>
+      </c>
+      <c r="BA226">
+        <v>4</v>
+      </c>
+      <c r="BB226">
+        <v>8</v>
+      </c>
+      <c r="BC226">
+        <v>12</v>
+      </c>
+      <c r="BD226">
+        <v>1.36</v>
+      </c>
+      <c r="BE226">
+        <v>7.5</v>
+      </c>
+      <c r="BF226">
+        <v>3.4</v>
+      </c>
+      <c r="BG226">
+        <v>1.22</v>
+      </c>
+      <c r="BH226">
+        <v>3.7</v>
+      </c>
+      <c r="BI226">
+        <v>1.38</v>
+      </c>
+      <c r="BJ226">
+        <v>2.7</v>
+      </c>
+      <c r="BK226">
+        <v>1.64</v>
+      </c>
+      <c r="BL226">
+        <v>2.12</v>
+      </c>
+      <c r="BM226">
+        <v>1.98</v>
+      </c>
+      <c r="BN226">
+        <v>1.73</v>
+      </c>
+      <c r="BO226">
+        <v>2.48</v>
+      </c>
+      <c r="BP226">
+        <v>1.48</v>
+      </c>
+    </row>
+    <row r="227" spans="1:68">
+      <c r="A227" s="1">
+        <v>226</v>
+      </c>
+      <c r="B227">
+        <v>7453644</v>
+      </c>
+      <c r="C227" t="s">
+        <v>68</v>
+      </c>
+      <c r="D227" t="s">
+        <v>69</v>
+      </c>
+      <c r="E227" s="2">
+        <v>45724.5</v>
+      </c>
+      <c r="F227">
+        <v>29</v>
+      </c>
+      <c r="G227" t="s">
+        <v>75</v>
+      </c>
+      <c r="H227" t="s">
+        <v>80</v>
+      </c>
+      <c r="I227">
+        <v>1</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+      <c r="L227">
+        <v>2</v>
+      </c>
+      <c r="M227">
+        <v>0</v>
+      </c>
+      <c r="N227">
+        <v>2</v>
+      </c>
+      <c r="O227" t="s">
+        <v>244</v>
+      </c>
+      <c r="P227" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q227">
+        <v>2.75</v>
+      </c>
+      <c r="R227">
+        <v>2.1</v>
+      </c>
+      <c r="S227">
+        <v>3.4</v>
+      </c>
+      <c r="T227">
+        <v>1.37</v>
+      </c>
+      <c r="U227">
+        <v>2.85</v>
+      </c>
+      <c r="V227">
+        <v>2.7</v>
+      </c>
+      <c r="W227">
+        <v>1.4</v>
+      </c>
+      <c r="X227">
+        <v>6.75</v>
+      </c>
+      <c r="Y227">
+        <v>1.09</v>
+      </c>
+      <c r="Z227">
+        <v>2.71</v>
+      </c>
+      <c r="AA227">
+        <v>3.23</v>
+      </c>
+      <c r="AB227">
+        <v>2.55</v>
+      </c>
+      <c r="AC227">
+        <v>1.05</v>
+      </c>
+      <c r="AD227">
+        <v>9</v>
+      </c>
+      <c r="AE227">
+        <v>1.3</v>
+      </c>
+      <c r="AF227">
+        <v>3.45</v>
+      </c>
+      <c r="AG227">
+        <v>1.89</v>
+      </c>
+      <c r="AH227">
+        <v>1.85</v>
+      </c>
+      <c r="AI227">
+        <v>1.75</v>
+      </c>
+      <c r="AJ227">
+        <v>1.93</v>
+      </c>
+      <c r="AK227">
+        <v>1.36</v>
+      </c>
+      <c r="AL227">
+        <v>1.29</v>
+      </c>
+      <c r="AM227">
+        <v>1.62</v>
+      </c>
+      <c r="AN227">
+        <v>1</v>
+      </c>
+      <c r="AO227">
+        <v>0.64</v>
+      </c>
+      <c r="AP227">
+        <v>1.13</v>
+      </c>
+      <c r="AQ227">
+        <v>0.6</v>
+      </c>
+      <c r="AR227">
+        <v>1.36</v>
+      </c>
+      <c r="AS227">
+        <v>1.19</v>
+      </c>
+      <c r="AT227">
+        <v>2.55</v>
+      </c>
+      <c r="AU227">
+        <v>7</v>
+      </c>
+      <c r="AV227">
+        <v>4</v>
+      </c>
+      <c r="AW227">
+        <v>16</v>
+      </c>
+      <c r="AX227">
+        <v>6</v>
+      </c>
+      <c r="AY227">
+        <v>26</v>
+      </c>
+      <c r="AZ227">
+        <v>11</v>
+      </c>
+      <c r="BA227">
+        <v>5</v>
+      </c>
+      <c r="BB227">
+        <v>4</v>
+      </c>
+      <c r="BC227">
+        <v>9</v>
+      </c>
+      <c r="BD227">
+        <v>1.71</v>
+      </c>
+      <c r="BE227">
+        <v>6.75</v>
+      </c>
+      <c r="BF227">
+        <v>2.35</v>
+      </c>
+      <c r="BG227">
+        <v>1.24</v>
+      </c>
+      <c r="BH227">
+        <v>3.65</v>
+      </c>
+      <c r="BI227">
+        <v>1.42</v>
+      </c>
+      <c r="BJ227">
+        <v>2.65</v>
+      </c>
+      <c r="BK227">
+        <v>1.7</v>
+      </c>
+      <c r="BL227">
+        <v>2.02</v>
+      </c>
+      <c r="BM227">
+        <v>2.07</v>
+      </c>
+      <c r="BN227">
+        <v>1.67</v>
+      </c>
+      <c r="BO227">
+        <v>2.6</v>
+      </c>
+      <c r="BP227">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="228" spans="1:68">
+      <c r="A228" s="1">
+        <v>227</v>
+      </c>
+      <c r="B228">
+        <v>7453648</v>
+      </c>
+      <c r="C228" t="s">
+        <v>68</v>
+      </c>
+      <c r="D228" t="s">
+        <v>69</v>
+      </c>
+      <c r="E228" s="2">
+        <v>45724.59375</v>
+      </c>
+      <c r="F228">
+        <v>29</v>
+      </c>
+      <c r="G228" t="s">
+        <v>76</v>
+      </c>
+      <c r="H228" t="s">
+        <v>79</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>1</v>
+      </c>
+      <c r="K228">
+        <v>1</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+      <c r="M228">
+        <v>1</v>
+      </c>
+      <c r="N228">
+        <v>1</v>
+      </c>
+      <c r="O228" t="s">
+        <v>87</v>
+      </c>
+      <c r="P228" t="s">
+        <v>209</v>
+      </c>
+      <c r="Q228">
+        <v>2.7</v>
+      </c>
+      <c r="R228">
+        <v>2.15</v>
+      </c>
+      <c r="S228">
+        <v>3.5</v>
+      </c>
+      <c r="T228">
+        <v>1.35</v>
+      </c>
+      <c r="U228">
+        <v>2.9</v>
+      </c>
+      <c r="V228">
+        <v>2.6</v>
+      </c>
+      <c r="W228">
+        <v>1.43</v>
+      </c>
+      <c r="X228">
+        <v>6.5</v>
+      </c>
+      <c r="Y228">
+        <v>1.1</v>
+      </c>
+      <c r="Z228">
+        <v>2.2</v>
+      </c>
+      <c r="AA228">
+        <v>3.36</v>
+      </c>
+      <c r="AB228">
+        <v>3.14</v>
+      </c>
+      <c r="AC228">
+        <v>1.06</v>
+      </c>
+      <c r="AD228">
+        <v>8.5</v>
+      </c>
+      <c r="AE228">
+        <v>1.3</v>
+      </c>
+      <c r="AF228">
+        <v>3.45</v>
+      </c>
+      <c r="AG228">
+        <v>1.79</v>
+      </c>
+      <c r="AH228">
+        <v>1.95</v>
+      </c>
+      <c r="AI228">
+        <v>1.66</v>
+      </c>
+      <c r="AJ228">
+        <v>2.05</v>
+      </c>
+      <c r="AK228">
+        <v>1.35</v>
+      </c>
+      <c r="AL228">
+        <v>1.29</v>
+      </c>
+      <c r="AM228">
+        <v>1.65</v>
+      </c>
+      <c r="AN228">
+        <v>1.57</v>
+      </c>
+      <c r="AO228">
+        <v>0.86</v>
+      </c>
+      <c r="AP228">
+        <v>1.47</v>
+      </c>
+      <c r="AQ228">
+        <v>1</v>
+      </c>
+      <c r="AR228">
+        <v>1.7</v>
+      </c>
+      <c r="AS228">
+        <v>1.52</v>
+      </c>
+      <c r="AT228">
+        <v>3.22</v>
+      </c>
+      <c r="AU228">
+        <v>3</v>
+      </c>
+      <c r="AV228">
+        <v>6</v>
+      </c>
+      <c r="AW228">
+        <v>9</v>
+      </c>
+      <c r="AX228">
+        <v>4</v>
+      </c>
+      <c r="AY228">
+        <v>14</v>
+      </c>
+      <c r="AZ228">
+        <v>10</v>
+      </c>
+      <c r="BA228">
+        <v>6</v>
+      </c>
+      <c r="BB228">
+        <v>3</v>
+      </c>
+      <c r="BC228">
+        <v>9</v>
+      </c>
+      <c r="BD228">
+        <v>1.77</v>
+      </c>
+      <c r="BE228">
+        <v>6.75</v>
+      </c>
+      <c r="BF228">
+        <v>2.23</v>
+      </c>
+      <c r="BG228">
+        <v>1.24</v>
+      </c>
+      <c r="BH228">
+        <v>3.55</v>
+      </c>
+      <c r="BI228">
+        <v>1.43</v>
+      </c>
+      <c r="BJ228">
+        <v>2.55</v>
+      </c>
+      <c r="BK228">
+        <v>1.7</v>
+      </c>
+      <c r="BL228">
+        <v>2.02</v>
+      </c>
+      <c r="BM228">
+        <v>2.07</v>
+      </c>
+      <c r="BN228">
+        <v>1.66</v>
+      </c>
+      <c r="BO228">
+        <v>2.65</v>
+      </c>
+      <c r="BP228">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="229" spans="1:68">
+      <c r="A229" s="1">
+        <v>228</v>
+      </c>
+      <c r="B229">
+        <v>7453649</v>
+      </c>
+      <c r="C229" t="s">
+        <v>68</v>
+      </c>
+      <c r="D229" t="s">
+        <v>69</v>
+      </c>
+      <c r="E229" s="2">
+        <v>45724.69791666666</v>
+      </c>
+      <c r="F229">
+        <v>29</v>
+      </c>
+      <c r="G229" t="s">
+        <v>71</v>
+      </c>
+      <c r="H229" t="s">
+        <v>74</v>
+      </c>
+      <c r="I229">
+        <v>0</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+      <c r="M229">
+        <v>1</v>
+      </c>
+      <c r="N229">
+        <v>1</v>
+      </c>
+      <c r="O229" t="s">
+        <v>87</v>
+      </c>
+      <c r="P229" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q229">
+        <v>4.1</v>
+      </c>
+      <c r="R229">
+        <v>2.25</v>
+      </c>
+      <c r="S229">
+        <v>2.3</v>
+      </c>
+      <c r="T229">
+        <v>1.3</v>
+      </c>
+      <c r="U229">
+        <v>3.2</v>
+      </c>
+      <c r="V229">
+        <v>2.37</v>
+      </c>
+      <c r="W229">
+        <v>1.51</v>
+      </c>
+      <c r="X229">
+        <v>5.5</v>
+      </c>
+      <c r="Y229">
+        <v>1.12</v>
+      </c>
+      <c r="Z229">
+        <v>4.1</v>
+      </c>
+      <c r="AA229">
+        <v>3.87</v>
+      </c>
+      <c r="AB229">
+        <v>1.76</v>
+      </c>
+      <c r="AC229">
+        <v>1.04</v>
+      </c>
+      <c r="AD229">
+        <v>10</v>
+      </c>
+      <c r="AE229">
+        <v>1.22</v>
+      </c>
+      <c r="AF229">
+        <v>4.2</v>
+      </c>
+      <c r="AG229">
+        <v>1.85</v>
+      </c>
+      <c r="AH229">
+        <v>1.85</v>
+      </c>
+      <c r="AI229">
+        <v>1.62</v>
+      </c>
+      <c r="AJ229">
+        <v>2.15</v>
+      </c>
+      <c r="AK229">
+        <v>1.98</v>
+      </c>
+      <c r="AL229">
+        <v>1.24</v>
+      </c>
+      <c r="AM229">
+        <v>1.23</v>
+      </c>
+      <c r="AN229">
+        <v>1.21</v>
+      </c>
+      <c r="AO229">
+        <v>1.71</v>
+      </c>
+      <c r="AP229">
+        <v>1.13</v>
+      </c>
+      <c r="AQ229">
+        <v>1.8</v>
+      </c>
+      <c r="AR229">
+        <v>1.11</v>
+      </c>
+      <c r="AS229">
+        <v>1.67</v>
+      </c>
+      <c r="AT229">
+        <v>2.78</v>
+      </c>
+      <c r="AU229">
+        <v>5</v>
+      </c>
+      <c r="AV229">
+        <v>6</v>
+      </c>
+      <c r="AW229">
+        <v>11</v>
+      </c>
+      <c r="AX229">
+        <v>11</v>
+      </c>
+      <c r="AY229">
+        <v>20</v>
+      </c>
+      <c r="AZ229">
+        <v>24</v>
+      </c>
+      <c r="BA229">
+        <v>2</v>
+      </c>
+      <c r="BB229">
+        <v>6</v>
+      </c>
+      <c r="BC229">
+        <v>8</v>
+      </c>
+      <c r="BD229">
+        <v>2.55</v>
+      </c>
+      <c r="BE229">
+        <v>6.4</v>
+      </c>
+      <c r="BF229">
+        <v>1.65</v>
+      </c>
+      <c r="BG229">
+        <v>1.38</v>
+      </c>
+      <c r="BH229">
+        <v>2.8</v>
+      </c>
+      <c r="BI229">
+        <v>1.65</v>
+      </c>
+      <c r="BJ229">
+        <v>2.08</v>
+      </c>
+      <c r="BK229">
+        <v>2.05</v>
+      </c>
+      <c r="BL229">
+        <v>1.68</v>
+      </c>
+      <c r="BM229">
+        <v>2.55</v>
+      </c>
+      <c r="BN229">
+        <v>1.43</v>
+      </c>
+      <c r="BO229">
+        <v>3.4</v>
+      </c>
+      <c r="BP229">
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="343">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -751,6 +751,12 @@
     <t>['44', '63']</t>
   </si>
   <si>
+    <t>['2', '22']</t>
+  </si>
+  <si>
+    <t>['20', '55', '82']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1031,6 +1037,12 @@
   </si>
   <si>
     <t>['63', '88']</t>
+  </si>
+  <si>
+    <t>['26', '34', '36']</t>
+  </si>
+  <si>
+    <t>['83']</t>
   </si>
 </sst>
 </file>
@@ -1392,7 +1404,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP229"/>
+  <dimension ref="A1:BP233"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1648,7 +1660,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2553,7 +2565,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ6">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2678,7 +2690,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2759,7 +2771,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ7">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3168,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ9">
         <v>0.79</v>
@@ -3374,7 +3386,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ10">
         <v>0.13</v>
@@ -3502,7 +3514,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3914,7 +3926,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4120,7 +4132,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4198,10 +4210,10 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ14">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4326,7 +4338,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4404,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ15">
         <v>0.43</v>
@@ -4613,7 +4625,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ16">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4738,7 +4750,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5356,7 +5368,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5434,7 +5446,7 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ20">
         <v>1.57</v>
@@ -5768,7 +5780,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5849,7 +5861,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ22">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR22">
         <v>1.58</v>
@@ -5974,7 +5986,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6052,7 +6064,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ23">
         <v>0.64</v>
@@ -6261,7 +6273,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ24">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR24">
         <v>1.65</v>
@@ -6386,7 +6398,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6464,7 +6476,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ25">
         <v>0.13</v>
@@ -6670,7 +6682,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ26">
         <v>1.07</v>
@@ -6798,7 +6810,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -7004,7 +7016,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7210,7 +7222,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7291,7 +7303,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ29">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR29">
         <v>0.96</v>
@@ -7909,7 +7921,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ32">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -8240,7 +8252,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8318,7 +8330,7 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ34">
         <v>0.6</v>
@@ -8524,7 +8536,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8652,7 +8664,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8733,7 +8745,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ36">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR36">
         <v>0.9399999999999999</v>
@@ -9682,7 +9694,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9888,7 +9900,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10175,7 +10187,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ43">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -10790,10 +10802,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ46">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR46">
         <v>1.58</v>
@@ -11124,7 +11136,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11205,7 +11217,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ48">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR48">
         <v>1.15</v>
@@ -11330,7 +11342,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11408,7 +11420,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ49">
         <v>1.8</v>
@@ -11536,7 +11548,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11617,7 +11629,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ50">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR50">
         <v>1.76</v>
@@ -11742,7 +11754,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12026,7 +12038,7 @@
         <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ52">
         <v>1.57</v>
@@ -12772,7 +12784,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13184,7 +13196,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13390,7 +13402,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13468,7 +13480,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ59">
         <v>1.29</v>
@@ -13802,7 +13814,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13883,7 +13895,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ61">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR61">
         <v>2.01</v>
@@ -14626,7 +14638,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14704,10 +14716,10 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ65">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR65">
         <v>1.79</v>
@@ -14913,7 +14925,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ66">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR66">
         <v>1.81</v>
@@ -15244,7 +15256,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15450,7 +15462,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15531,7 +15543,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ69">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR69">
         <v>1.21</v>
@@ -15734,7 +15746,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ70">
         <v>0.13</v>
@@ -15940,7 +15952,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ71">
         <v>0.43</v>
@@ -16352,7 +16364,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ73">
         <v>0.64</v>
@@ -16480,7 +16492,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16558,7 +16570,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ74">
         <v>0.13</v>
@@ -17385,7 +17397,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ78">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR78">
         <v>1.59</v>
@@ -17588,7 +17600,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ79">
         <v>0.79</v>
@@ -18003,7 +18015,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ81">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR81">
         <v>0.89</v>
@@ -18209,7 +18221,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ82">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR82">
         <v>0.92</v>
@@ -18334,7 +18346,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18412,10 +18424,10 @@
         <v>1.4</v>
       </c>
       <c r="AP83">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ83">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR83">
         <v>1.89</v>
@@ -18618,7 +18630,7 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ84">
         <v>1.07</v>
@@ -18824,10 +18836,10 @@
         <v>1.4</v>
       </c>
       <c r="AP85">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ85">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR85">
         <v>1.67</v>
@@ -18952,7 +18964,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19982,7 +19994,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20188,7 +20200,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20600,7 +20612,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20681,7 +20693,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ94">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR94">
         <v>2.03</v>
@@ -20884,10 +20896,10 @@
         <v>0.8</v>
       </c>
       <c r="AP95">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ95">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR95">
         <v>1.79</v>
@@ -21012,7 +21024,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21218,7 +21230,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21296,7 +21308,7 @@
         <v>0.2</v>
       </c>
       <c r="AP97">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ97">
         <v>0.79</v>
@@ -21502,7 +21514,7 @@
         <v>1.6</v>
       </c>
       <c r="AP98">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ98">
         <v>1.07</v>
@@ -21630,7 +21642,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21836,7 +21848,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21917,7 +21929,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ100">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR100">
         <v>1.3</v>
@@ -22042,7 +22054,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22532,7 +22544,7 @@
         <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ103">
         <v>1.07</v>
@@ -22947,7 +22959,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ105">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR105">
         <v>0.83</v>
@@ -23072,7 +23084,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23278,7 +23290,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23484,7 +23496,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23896,7 +23908,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -23974,10 +23986,10 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ110">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR110">
         <v>1.65</v>
@@ -24183,7 +24195,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ111">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR111">
         <v>1.55</v>
@@ -24386,7 +24398,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ112">
         <v>1.8</v>
@@ -24514,7 +24526,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24595,7 +24607,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ113">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR113">
         <v>0.88</v>
@@ -24798,7 +24810,7 @@
         <v>1.33</v>
       </c>
       <c r="AP114">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ114">
         <v>1.07</v>
@@ -25750,7 +25762,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26037,7 +26049,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ120">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR120">
         <v>1.64</v>
@@ -26240,7 +26252,7 @@
         <v>0.57</v>
       </c>
       <c r="AP121">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ121">
         <v>0.43</v>
@@ -26368,7 +26380,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26861,7 +26873,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ124">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR124">
         <v>1.8</v>
@@ -26986,7 +26998,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27273,7 +27285,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ126">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR126">
         <v>1.26</v>
@@ -27398,7 +27410,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27682,7 +27694,7 @@
         <v>1.57</v>
       </c>
       <c r="AP128">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ128">
         <v>1.29</v>
@@ -27810,7 +27822,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27888,10 +27900,10 @@
         <v>1.13</v>
       </c>
       <c r="AP129">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ129">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR129">
         <v>1.82</v>
@@ -28016,7 +28028,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28428,7 +28440,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28509,7 +28521,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ132">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR132">
         <v>1.55</v>
@@ -28840,7 +28852,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28918,7 +28930,7 @@
         <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ134">
         <v>1.07</v>
@@ -29124,7 +29136,7 @@
         <v>0.75</v>
       </c>
       <c r="AP135">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ135">
         <v>1.57</v>
@@ -29252,7 +29264,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29951,7 +29963,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ139">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR139">
         <v>1.07</v>
@@ -30282,7 +30294,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30694,7 +30706,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30772,7 +30784,7 @@
         <v>0.88</v>
       </c>
       <c r="AP143">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ143">
         <v>0.86</v>
@@ -30900,7 +30912,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -30981,7 +30993,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ144">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR144">
         <v>1.4</v>
@@ -31312,7 +31324,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31390,7 +31402,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ146">
         <v>1</v>
@@ -31724,7 +31736,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31930,7 +31942,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32217,7 +32229,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ150">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR150">
         <v>1.79</v>
@@ -32423,7 +32435,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ151">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR151">
         <v>1.23</v>
@@ -32548,7 +32560,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32626,10 +32638,10 @@
         <v>1.89</v>
       </c>
       <c r="AP152">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ152">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR152">
         <v>1.81</v>
@@ -32832,7 +32844,7 @@
         <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ153">
         <v>0.6</v>
@@ -32960,7 +32972,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33038,7 +33050,7 @@
         <v>1.44</v>
       </c>
       <c r="AP154">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ154">
         <v>1.8</v>
@@ -33166,7 +33178,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33372,7 +33384,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33659,7 +33671,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ157">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR157">
         <v>1.54</v>
@@ -33784,7 +33796,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34196,7 +34208,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34402,7 +34414,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34814,7 +34826,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34892,7 +34904,7 @@
         <v>0.5</v>
       </c>
       <c r="AP163">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ163">
         <v>0.64</v>
@@ -35226,7 +35238,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35432,7 +35444,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35719,7 +35731,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ167">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR167">
         <v>1.07</v>
@@ -35844,7 +35856,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -35925,7 +35937,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ168">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR168">
         <v>1.71</v>
@@ -36128,7 +36140,7 @@
         <v>1</v>
       </c>
       <c r="AP169">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ169">
         <v>1</v>
@@ -36462,7 +36474,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36668,7 +36680,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36874,7 +36886,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -37080,7 +37092,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37161,7 +37173,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ174">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR174">
         <v>1.38</v>
@@ -37364,7 +37376,7 @@
         <v>0.73</v>
       </c>
       <c r="AP175">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ175">
         <v>0.6</v>
@@ -37492,7 +37504,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37573,7 +37585,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ176">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR176">
         <v>1.54</v>
@@ -37698,7 +37710,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37776,7 +37788,7 @@
         <v>0.7</v>
       </c>
       <c r="AP177">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ177">
         <v>0.86</v>
@@ -38110,7 +38122,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38188,7 +38200,7 @@
         <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ179">
         <v>1.8</v>
@@ -38316,7 +38328,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38934,7 +38946,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39140,7 +39152,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39427,7 +39439,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ185">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR185">
         <v>1.29</v>
@@ -39964,7 +39976,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40042,10 +40054,10 @@
         <v>0.91</v>
       </c>
       <c r="AP188">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ188">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR188">
         <v>1.65</v>
@@ -40454,10 +40466,10 @@
         <v>1.91</v>
       </c>
       <c r="AP190">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ190">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR190">
         <v>1.72</v>
@@ -40582,7 +40594,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40660,7 +40672,7 @@
         <v>0.73</v>
       </c>
       <c r="AP191">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ191">
         <v>0.64</v>
@@ -40869,7 +40881,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ192">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR192">
         <v>1.52</v>
@@ -40994,7 +41006,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41200,7 +41212,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41281,7 +41293,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ194">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR194">
         <v>1.52</v>
@@ -42230,7 +42242,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42436,7 +42448,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42514,10 +42526,10 @@
         <v>0.92</v>
       </c>
       <c r="AP200">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ200">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR200">
         <v>1.89</v>
@@ -42848,7 +42860,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -43054,7 +43066,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43260,7 +43272,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43338,7 +43350,7 @@
         <v>0.5</v>
       </c>
       <c r="AP204">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ204">
         <v>0.43</v>
@@ -43466,7 +43478,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43547,7 +43559,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ205">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR205">
         <v>1.6</v>
@@ -43672,7 +43684,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -43956,7 +43968,7 @@
         <v>0.75</v>
       </c>
       <c r="AP207">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ207">
         <v>1</v>
@@ -44165,7 +44177,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ208">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR208">
         <v>1.72</v>
@@ -44368,7 +44380,7 @@
         <v>0.83</v>
       </c>
       <c r="AP209">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ209">
         <v>0.86</v>
@@ -44908,7 +44920,7 @@
         <v>227</v>
       </c>
       <c r="P212" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q212">
         <v>2.75</v>
@@ -44986,7 +44998,7 @@
         <v>0.92</v>
       </c>
       <c r="AP212">
-        <v>1.36</v>
+        <v>1.47</v>
       </c>
       <c r="AQ212">
         <v>1.07</v>
@@ -45114,7 +45126,7 @@
         <v>239</v>
       </c>
       <c r="P213" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -45192,7 +45204,7 @@
         <v>0.62</v>
       </c>
       <c r="AP213">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AQ213">
         <v>0.6</v>
@@ -45320,7 +45332,7 @@
         <v>86</v>
       </c>
       <c r="P214" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q214">
         <v>1.71</v>
@@ -45401,7 +45413,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ214">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="AR214">
         <v>2.08</v>
@@ -45607,7 +45619,7 @@
         <v>2.71</v>
       </c>
       <c r="AQ215">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="AR215">
         <v>1.77</v>
@@ -45732,7 +45744,7 @@
         <v>87</v>
       </c>
       <c r="P216" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q216">
         <v>3.25</v>
@@ -46350,7 +46362,7 @@
         <v>88</v>
       </c>
       <c r="P219" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46431,7 +46443,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ219">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="AR219">
         <v>1.58</v>
@@ -46634,7 +46646,7 @@
         <v>1.31</v>
       </c>
       <c r="AP220">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AQ220">
         <v>1.29</v>
@@ -46762,7 +46774,7 @@
         <v>241</v>
       </c>
       <c r="P221" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q221">
         <v>2.25</v>
@@ -47046,7 +47058,7 @@
         <v>1.15</v>
       </c>
       <c r="AP222">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ222">
         <v>1.07</v>
@@ -47380,7 +47392,7 @@
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q224">
         <v>4.33</v>
@@ -47461,7 +47473,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ224">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="AR224">
         <v>1.22</v>
@@ -48567,6 +48579,830 @@
       </c>
       <c r="BP229">
         <v>1.26</v>
+      </c>
+    </row>
+    <row r="230" spans="1:68">
+      <c r="A230" s="1">
+        <v>229</v>
+      </c>
+      <c r="B230">
+        <v>7453645</v>
+      </c>
+      <c r="C230" t="s">
+        <v>68</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230" s="2">
+        <v>45725.39583333334</v>
+      </c>
+      <c r="F230">
+        <v>29</v>
+      </c>
+      <c r="G230" t="s">
+        <v>83</v>
+      </c>
+      <c r="H230" t="s">
+        <v>70</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>3</v>
+      </c>
+      <c r="K230">
+        <v>3</v>
+      </c>
+      <c r="L230">
+        <v>1</v>
+      </c>
+      <c r="M230">
+        <v>3</v>
+      </c>
+      <c r="N230">
+        <v>4</v>
+      </c>
+      <c r="O230" t="s">
+        <v>174</v>
+      </c>
+      <c r="P230" t="s">
+        <v>341</v>
+      </c>
+      <c r="Q230">
+        <v>4.75</v>
+      </c>
+      <c r="R230">
+        <v>2.2</v>
+      </c>
+      <c r="S230">
+        <v>2.4</v>
+      </c>
+      <c r="T230">
+        <v>1.4</v>
+      </c>
+      <c r="U230">
+        <v>2.75</v>
+      </c>
+      <c r="V230">
+        <v>2.75</v>
+      </c>
+      <c r="W230">
+        <v>1.4</v>
+      </c>
+      <c r="X230">
+        <v>8</v>
+      </c>
+      <c r="Y230">
+        <v>1.08</v>
+      </c>
+      <c r="Z230">
+        <v>4.2</v>
+      </c>
+      <c r="AA230">
+        <v>3.55</v>
+      </c>
+      <c r="AB230">
+        <v>1.82</v>
+      </c>
+      <c r="AC230">
+        <v>1.05</v>
+      </c>
+      <c r="AD230">
+        <v>9</v>
+      </c>
+      <c r="AE230">
+        <v>1.3</v>
+      </c>
+      <c r="AF230">
+        <v>3.4</v>
+      </c>
+      <c r="AG230">
+        <v>1.92</v>
+      </c>
+      <c r="AH230">
+        <v>1.82</v>
+      </c>
+      <c r="AI230">
+        <v>1.8</v>
+      </c>
+      <c r="AJ230">
+        <v>1.95</v>
+      </c>
+      <c r="AK230">
+        <v>1.95</v>
+      </c>
+      <c r="AL230">
+        <v>1.27</v>
+      </c>
+      <c r="AM230">
+        <v>1.22</v>
+      </c>
+      <c r="AN230">
+        <v>1.5</v>
+      </c>
+      <c r="AO230">
+        <v>1.64</v>
+      </c>
+      <c r="AP230">
+        <v>1.4</v>
+      </c>
+      <c r="AQ230">
+        <v>1.73</v>
+      </c>
+      <c r="AR230">
+        <v>1.79</v>
+      </c>
+      <c r="AS230">
+        <v>1.67</v>
+      </c>
+      <c r="AT230">
+        <v>3.46</v>
+      </c>
+      <c r="AU230">
+        <v>5</v>
+      </c>
+      <c r="AV230">
+        <v>5</v>
+      </c>
+      <c r="AW230">
+        <v>14</v>
+      </c>
+      <c r="AX230">
+        <v>11</v>
+      </c>
+      <c r="AY230">
+        <v>22</v>
+      </c>
+      <c r="AZ230">
+        <v>18</v>
+      </c>
+      <c r="BA230">
+        <v>9</v>
+      </c>
+      <c r="BB230">
+        <v>4</v>
+      </c>
+      <c r="BC230">
+        <v>13</v>
+      </c>
+      <c r="BD230">
+        <v>2.7</v>
+      </c>
+      <c r="BE230">
+        <v>6.5</v>
+      </c>
+      <c r="BF230">
+        <v>1.56</v>
+      </c>
+      <c r="BG230">
+        <v>1.35</v>
+      </c>
+      <c r="BH230">
+        <v>2.9</v>
+      </c>
+      <c r="BI230">
+        <v>1.58</v>
+      </c>
+      <c r="BJ230">
+        <v>2.18</v>
+      </c>
+      <c r="BK230">
+        <v>1.96</v>
+      </c>
+      <c r="BL230">
+        <v>1.74</v>
+      </c>
+      <c r="BM230">
+        <v>2.48</v>
+      </c>
+      <c r="BN230">
+        <v>1.47</v>
+      </c>
+      <c r="BO230">
+        <v>3.25</v>
+      </c>
+      <c r="BP230">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="231" spans="1:68">
+      <c r="A231" s="1">
+        <v>230</v>
+      </c>
+      <c r="B231">
+        <v>7453647</v>
+      </c>
+      <c r="C231" t="s">
+        <v>68</v>
+      </c>
+      <c r="D231" t="s">
+        <v>69</v>
+      </c>
+      <c r="E231" s="2">
+        <v>45725.5</v>
+      </c>
+      <c r="F231">
+        <v>29</v>
+      </c>
+      <c r="G231" t="s">
+        <v>77</v>
+      </c>
+      <c r="H231" t="s">
+        <v>73</v>
+      </c>
+      <c r="I231">
+        <v>2</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>2</v>
+      </c>
+      <c r="L231">
+        <v>2</v>
+      </c>
+      <c r="M231">
+        <v>0</v>
+      </c>
+      <c r="N231">
+        <v>2</v>
+      </c>
+      <c r="O231" t="s">
+        <v>245</v>
+      </c>
+      <c r="P231" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q231">
+        <v>3.5</v>
+      </c>
+      <c r="R231">
+        <v>2.3</v>
+      </c>
+      <c r="S231">
+        <v>2.88</v>
+      </c>
+      <c r="T231">
+        <v>1.33</v>
+      </c>
+      <c r="U231">
+        <v>3.25</v>
+      </c>
+      <c r="V231">
+        <v>2.5</v>
+      </c>
+      <c r="W231">
+        <v>1.5</v>
+      </c>
+      <c r="X231">
+        <v>6.5</v>
+      </c>
+      <c r="Y231">
+        <v>1.11</v>
+      </c>
+      <c r="Z231">
+        <v>2.97</v>
+      </c>
+      <c r="AA231">
+        <v>3.57</v>
+      </c>
+      <c r="AB231">
+        <v>2.21</v>
+      </c>
+      <c r="AC231">
+        <v>1.04</v>
+      </c>
+      <c r="AD231">
+        <v>10</v>
+      </c>
+      <c r="AE231">
+        <v>1.2</v>
+      </c>
+      <c r="AF231">
+        <v>4.33</v>
+      </c>
+      <c r="AG231">
+        <v>1.65</v>
+      </c>
+      <c r="AH231">
+        <v>2.15</v>
+      </c>
+      <c r="AI231">
+        <v>1.57</v>
+      </c>
+      <c r="AJ231">
+        <v>2.25</v>
+      </c>
+      <c r="AK231">
+        <v>1.65</v>
+      </c>
+      <c r="AL231">
+        <v>1.27</v>
+      </c>
+      <c r="AM231">
+        <v>1.37</v>
+      </c>
+      <c r="AN231">
+        <v>1.36</v>
+      </c>
+      <c r="AO231">
+        <v>1.71</v>
+      </c>
+      <c r="AP231">
+        <v>1.47</v>
+      </c>
+      <c r="AQ231">
+        <v>1.6</v>
+      </c>
+      <c r="AR231">
+        <v>1.88</v>
+      </c>
+      <c r="AS231">
+        <v>1.34</v>
+      </c>
+      <c r="AT231">
+        <v>3.22</v>
+      </c>
+      <c r="AU231">
+        <v>5</v>
+      </c>
+      <c r="AV231">
+        <v>3</v>
+      </c>
+      <c r="AW231">
+        <v>5</v>
+      </c>
+      <c r="AX231">
+        <v>15</v>
+      </c>
+      <c r="AY231">
+        <v>11</v>
+      </c>
+      <c r="AZ231">
+        <v>18</v>
+      </c>
+      <c r="BA231">
+        <v>7</v>
+      </c>
+      <c r="BB231">
+        <v>9</v>
+      </c>
+      <c r="BC231">
+        <v>16</v>
+      </c>
+      <c r="BD231">
+        <v>1.98</v>
+      </c>
+      <c r="BE231">
+        <v>6.75</v>
+      </c>
+      <c r="BF231">
+        <v>1.97</v>
+      </c>
+      <c r="BG231">
+        <v>1.24</v>
+      </c>
+      <c r="BH231">
+        <v>3.55</v>
+      </c>
+      <c r="BI231">
+        <v>1.43</v>
+      </c>
+      <c r="BJ231">
+        <v>2.6</v>
+      </c>
+      <c r="BK231">
+        <v>1.68</v>
+      </c>
+      <c r="BL231">
+        <v>2.05</v>
+      </c>
+      <c r="BM231">
+        <v>2.05</v>
+      </c>
+      <c r="BN231">
+        <v>1.68</v>
+      </c>
+      <c r="BO231">
+        <v>2.55</v>
+      </c>
+      <c r="BP231">
+        <v>1.43</v>
+      </c>
+    </row>
+    <row r="232" spans="1:68">
+      <c r="A232" s="1">
+        <v>231</v>
+      </c>
+      <c r="B232">
+        <v>7453643</v>
+      </c>
+      <c r="C232" t="s">
+        <v>68</v>
+      </c>
+      <c r="D232" t="s">
+        <v>69</v>
+      </c>
+      <c r="E232" s="2">
+        <v>45725.60416666666</v>
+      </c>
+      <c r="F232">
+        <v>29</v>
+      </c>
+      <c r="G232" t="s">
+        <v>82</v>
+      </c>
+      <c r="H232" t="s">
+        <v>85</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+      <c r="M232">
+        <v>1</v>
+      </c>
+      <c r="N232">
+        <v>1</v>
+      </c>
+      <c r="O232" t="s">
+        <v>87</v>
+      </c>
+      <c r="P232" t="s">
+        <v>342</v>
+      </c>
+      <c r="Q232">
+        <v>2.88</v>
+      </c>
+      <c r="R232">
+        <v>2.25</v>
+      </c>
+      <c r="S232">
+        <v>3.5</v>
+      </c>
+      <c r="T232">
+        <v>1.33</v>
+      </c>
+      <c r="U232">
+        <v>3.25</v>
+      </c>
+      <c r="V232">
+        <v>2.63</v>
+      </c>
+      <c r="W232">
+        <v>1.44</v>
+      </c>
+      <c r="X232">
+        <v>7</v>
+      </c>
+      <c r="Y232">
+        <v>1.1</v>
+      </c>
+      <c r="Z232">
+        <v>2.27</v>
+      </c>
+      <c r="AA232">
+        <v>3.36</v>
+      </c>
+      <c r="AB232">
+        <v>3.01</v>
+      </c>
+      <c r="AC232">
+        <v>1.04</v>
+      </c>
+      <c r="AD232">
+        <v>10</v>
+      </c>
+      <c r="AE232">
+        <v>1.25</v>
+      </c>
+      <c r="AF232">
+        <v>3.85</v>
+      </c>
+      <c r="AG232">
+        <v>1.7</v>
+      </c>
+      <c r="AH232">
+        <v>2.05</v>
+      </c>
+      <c r="AI232">
+        <v>1.62</v>
+      </c>
+      <c r="AJ232">
+        <v>2.2</v>
+      </c>
+      <c r="AK232">
+        <v>1.39</v>
+      </c>
+      <c r="AL232">
+        <v>1.27</v>
+      </c>
+      <c r="AM232">
+        <v>1.62</v>
+      </c>
+      <c r="AN232">
+        <v>1.93</v>
+      </c>
+      <c r="AO232">
+        <v>1.21</v>
+      </c>
+      <c r="AP232">
+        <v>1.8</v>
+      </c>
+      <c r="AQ232">
+        <v>1.33</v>
+      </c>
+      <c r="AR232">
+        <v>1.76</v>
+      </c>
+      <c r="AS232">
+        <v>1.31</v>
+      </c>
+      <c r="AT232">
+        <v>3.07</v>
+      </c>
+      <c r="AU232">
+        <v>7</v>
+      </c>
+      <c r="AV232">
+        <v>6</v>
+      </c>
+      <c r="AW232">
+        <v>6</v>
+      </c>
+      <c r="AX232">
+        <v>7</v>
+      </c>
+      <c r="AY232">
+        <v>14</v>
+      </c>
+      <c r="AZ232">
+        <v>16</v>
+      </c>
+      <c r="BA232">
+        <v>8</v>
+      </c>
+      <c r="BB232">
+        <v>4</v>
+      </c>
+      <c r="BC232">
+        <v>12</v>
+      </c>
+      <c r="BD232">
+        <v>1.66</v>
+      </c>
+      <c r="BE232">
+        <v>7</v>
+      </c>
+      <c r="BF232">
+        <v>2.43</v>
+      </c>
+      <c r="BG232">
+        <v>1.25</v>
+      </c>
+      <c r="BH232">
+        <v>3.45</v>
+      </c>
+      <c r="BI232">
+        <v>1.44</v>
+      </c>
+      <c r="BJ232">
+        <v>2.55</v>
+      </c>
+      <c r="BK232">
+        <v>1.71</v>
+      </c>
+      <c r="BL232">
+        <v>2</v>
+      </c>
+      <c r="BM232">
+        <v>2.12</v>
+      </c>
+      <c r="BN232">
+        <v>1.64</v>
+      </c>
+      <c r="BO232">
+        <v>2.65</v>
+      </c>
+      <c r="BP232">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:68">
+      <c r="A233" s="1">
+        <v>232</v>
+      </c>
+      <c r="B233">
+        <v>7453642</v>
+      </c>
+      <c r="C233" t="s">
+        <v>68</v>
+      </c>
+      <c r="D233" t="s">
+        <v>69</v>
+      </c>
+      <c r="E233" s="2">
+        <v>45725.63541666666</v>
+      </c>
+      <c r="F233">
+        <v>29</v>
+      </c>
+      <c r="G233" t="s">
+        <v>78</v>
+      </c>
+      <c r="H233" t="s">
+        <v>84</v>
+      </c>
+      <c r="I233">
+        <v>1</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+      <c r="L233">
+        <v>3</v>
+      </c>
+      <c r="M233">
+        <v>0</v>
+      </c>
+      <c r="N233">
+        <v>3</v>
+      </c>
+      <c r="O233" t="s">
+        <v>246</v>
+      </c>
+      <c r="P233" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q233">
+        <v>1.83</v>
+      </c>
+      <c r="R233">
+        <v>2.5</v>
+      </c>
+      <c r="S233">
+        <v>7.5</v>
+      </c>
+      <c r="T233">
+        <v>1.33</v>
+      </c>
+      <c r="U233">
+        <v>3.25</v>
+      </c>
+      <c r="V233">
+        <v>2.5</v>
+      </c>
+      <c r="W233">
+        <v>1.5</v>
+      </c>
+      <c r="X233">
+        <v>6</v>
+      </c>
+      <c r="Y233">
+        <v>1.13</v>
+      </c>
+      <c r="Z233">
+        <v>1.33</v>
+      </c>
+      <c r="AA233">
+        <v>5.2</v>
+      </c>
+      <c r="AB233">
+        <v>8</v>
+      </c>
+      <c r="AC233">
+        <v>1.03</v>
+      </c>
+      <c r="AD233">
+        <v>11</v>
+      </c>
+      <c r="AE233">
+        <v>1.2</v>
+      </c>
+      <c r="AF233">
+        <v>4.5</v>
+      </c>
+      <c r="AG233">
+        <v>1.7</v>
+      </c>
+      <c r="AH233">
+        <v>2.05</v>
+      </c>
+      <c r="AI233">
+        <v>2</v>
+      </c>
+      <c r="AJ233">
+        <v>1.75</v>
+      </c>
+      <c r="AK233">
+        <v>1.09</v>
+      </c>
+      <c r="AL233">
+        <v>1.17</v>
+      </c>
+      <c r="AM233">
+        <v>2.95</v>
+      </c>
+      <c r="AN233">
+        <v>2.14</v>
+      </c>
+      <c r="AO233">
+        <v>1</v>
+      </c>
+      <c r="AP233">
+        <v>2.2</v>
+      </c>
+      <c r="AQ233">
+        <v>0.93</v>
+      </c>
+      <c r="AR233">
+        <v>1.88</v>
+      </c>
+      <c r="AS233">
+        <v>1.07</v>
+      </c>
+      <c r="AT233">
+        <v>2.95</v>
+      </c>
+      <c r="AU233">
+        <v>4</v>
+      </c>
+      <c r="AV233">
+        <v>4</v>
+      </c>
+      <c r="AW233">
+        <v>6</v>
+      </c>
+      <c r="AX233">
+        <v>4</v>
+      </c>
+      <c r="AY233">
+        <v>13</v>
+      </c>
+      <c r="AZ233">
+        <v>9</v>
+      </c>
+      <c r="BA233">
+        <v>1</v>
+      </c>
+      <c r="BB233">
+        <v>4</v>
+      </c>
+      <c r="BC233">
+        <v>5</v>
+      </c>
+      <c r="BD233">
+        <v>1.21</v>
+      </c>
+      <c r="BE233">
+        <v>8.5</v>
+      </c>
+      <c r="BF233">
+        <v>4.8</v>
+      </c>
+      <c r="BG233">
+        <v>1.23</v>
+      </c>
+      <c r="BH233">
+        <v>3.7</v>
+      </c>
+      <c r="BI233">
+        <v>1.38</v>
+      </c>
+      <c r="BJ233">
+        <v>2.7</v>
+      </c>
+      <c r="BK233">
+        <v>1.64</v>
+      </c>
+      <c r="BL233">
+        <v>2.12</v>
+      </c>
+      <c r="BM233">
+        <v>1.98</v>
+      </c>
+      <c r="BN233">
+        <v>1.74</v>
+      </c>
+      <c r="BO233">
+        <v>2.48</v>
+      </c>
+      <c r="BP233">
+        <v>1.47</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1460" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="344">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -757,6 +757,9 @@
     <t>['20', '55', '82']</t>
   </si>
   <si>
+    <t>['69', '83']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1404,7 +1407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP233"/>
+  <dimension ref="A1:BP234"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1660,7 +1663,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1947,7 +1950,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ3">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2562,7 +2565,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ6">
         <v>0.93</v>
@@ -2690,7 +2693,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3514,7 +3517,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3926,7 +3929,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4132,7 +4135,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4338,7 +4341,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4750,7 +4753,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5368,7 +5371,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5449,7 +5452,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ20">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR20">
         <v>1.27</v>
@@ -5780,7 +5783,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5858,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ22">
         <v>1.73</v>
@@ -5986,7 +5989,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6398,7 +6401,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6810,7 +6813,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -7016,7 +7019,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7222,7 +7225,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -8252,7 +8255,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8664,7 +8667,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8951,7 +8954,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ37">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR37">
         <v>1.03</v>
@@ -9566,7 +9569,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ40">
         <v>0.86</v>
@@ -9694,7 +9697,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9900,7 +9903,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -11136,7 +11139,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11342,7 +11345,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11548,7 +11551,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11754,7 +11757,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12041,7 +12044,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ52">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR52">
         <v>2.07</v>
@@ -12784,7 +12787,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13071,7 +13074,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ57">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR57">
         <v>1.08</v>
@@ -13196,7 +13199,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13402,7 +13405,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13814,7 +13817,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14304,7 +14307,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ63">
         <v>1.07</v>
@@ -14638,7 +14641,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15128,7 +15131,7 @@
         <v>1.25</v>
       </c>
       <c r="AP67">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -15256,7 +15259,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15462,7 +15465,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16492,7 +16495,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -17809,7 +17812,7 @@
         <v>2.14</v>
       </c>
       <c r="AQ80">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR80">
         <v>2.17</v>
@@ -18346,7 +18349,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18964,7 +18967,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19042,7 +19045,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ86">
         <v>0.64</v>
@@ -19994,7 +19997,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20200,7 +20203,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20612,7 +20615,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -21024,7 +21027,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21230,7 +21233,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21642,7 +21645,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21848,7 +21851,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -22054,7 +22057,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22135,7 +22138,7 @@
         <v>1.43</v>
       </c>
       <c r="AQ101">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR101">
         <v>1.52</v>
@@ -22338,7 +22341,7 @@
         <v>1.6</v>
       </c>
       <c r="AP102">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ102">
         <v>1.29</v>
@@ -23084,7 +23087,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23290,7 +23293,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23496,7 +23499,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23908,7 +23911,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24526,7 +24529,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -25428,7 +25431,7 @@
         <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ117">
         <v>1.07</v>
@@ -25762,7 +25765,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25843,7 +25846,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ119">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -26380,7 +26383,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26998,7 +27001,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27410,7 +27413,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27822,7 +27825,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -28028,7 +28031,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28106,7 +28109,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ130">
         <v>0.43</v>
@@ -28440,7 +28443,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28852,7 +28855,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29139,7 +29142,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ135">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR135">
         <v>1.6</v>
@@ -29264,7 +29267,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -30294,7 +30297,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30706,7 +30709,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30912,7 +30915,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31324,7 +31327,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31736,7 +31739,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31942,7 +31945,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32226,7 +32229,7 @@
         <v>1.67</v>
       </c>
       <c r="AP150">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ150">
         <v>1.6</v>
@@ -32560,7 +32563,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32972,7 +32975,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33178,7 +33181,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33384,7 +33387,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33796,7 +33799,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -33877,7 +33880,7 @@
         <v>1.79</v>
       </c>
       <c r="AQ158">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR158">
         <v>1.6</v>
@@ -34208,7 +34211,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34414,7 +34417,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34826,7 +34829,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35110,7 +35113,7 @@
         <v>0.8</v>
       </c>
       <c r="AP164">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ164">
         <v>0.6</v>
@@ -35238,7 +35241,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35319,7 +35322,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ165">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR165">
         <v>1.75</v>
@@ -35444,7 +35447,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35856,7 +35859,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36474,7 +36477,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36680,7 +36683,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36886,7 +36889,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -37092,7 +37095,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37504,7 +37507,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37710,7 +37713,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38122,7 +38125,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38328,7 +38331,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38946,7 +38949,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39027,7 +39030,7 @@
         <v>1.14</v>
       </c>
       <c r="AQ183">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR183">
         <v>1.3</v>
@@ -39152,7 +39155,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39976,7 +39979,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40260,7 +40263,7 @@
         <v>0.09</v>
       </c>
       <c r="AP189">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ189">
         <v>0.13</v>
@@ -40594,7 +40597,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -41006,7 +41009,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41212,7 +41215,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41908,7 +41911,7 @@
         <v>0.83</v>
       </c>
       <c r="AP197">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ197">
         <v>0.79</v>
@@ -42242,7 +42245,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42323,7 +42326,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ199">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR199">
         <v>1.34</v>
@@ -42448,7 +42451,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42860,7 +42863,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -43066,7 +43069,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43272,7 +43275,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43478,7 +43481,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43684,7 +43687,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -44920,7 +44923,7 @@
         <v>227</v>
       </c>
       <c r="P212" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q212">
         <v>2.75</v>
@@ -45126,7 +45129,7 @@
         <v>239</v>
       </c>
       <c r="P213" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -45332,7 +45335,7 @@
         <v>86</v>
       </c>
       <c r="P214" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q214">
         <v>1.71</v>
@@ -45616,7 +45619,7 @@
         <v>1.23</v>
       </c>
       <c r="AP215">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="AQ215">
         <v>1.33</v>
@@ -45744,7 +45747,7 @@
         <v>87</v>
       </c>
       <c r="P216" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q216">
         <v>3.25</v>
@@ -45825,7 +45828,7 @@
         <v>1.71</v>
       </c>
       <c r="AQ216">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="AR216">
         <v>1.66</v>
@@ -46362,7 +46365,7 @@
         <v>88</v>
       </c>
       <c r="P219" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46774,7 +46777,7 @@
         <v>241</v>
       </c>
       <c r="P221" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q221">
         <v>2.25</v>
@@ -47392,7 +47395,7 @@
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q224">
         <v>4.33</v>
@@ -48628,7 +48631,7 @@
         <v>174</v>
       </c>
       <c r="P230" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q230">
         <v>4.75</v>
@@ -49040,7 +49043,7 @@
         <v>87</v>
       </c>
       <c r="P232" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49403,6 +49406,212 @@
       </c>
       <c r="BP233">
         <v>1.47</v>
+      </c>
+    </row>
+    <row r="234" spans="1:68">
+      <c r="A234" s="1">
+        <v>233</v>
+      </c>
+      <c r="B234">
+        <v>7453652</v>
+      </c>
+      <c r="C234" t="s">
+        <v>68</v>
+      </c>
+      <c r="D234" t="s">
+        <v>69</v>
+      </c>
+      <c r="E234" s="2">
+        <v>45731.69791666666</v>
+      </c>
+      <c r="F234">
+        <v>30</v>
+      </c>
+      <c r="G234" t="s">
+        <v>74</v>
+      </c>
+      <c r="H234" t="s">
+        <v>78</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>0</v>
+      </c>
+      <c r="L234">
+        <v>2</v>
+      </c>
+      <c r="M234">
+        <v>1</v>
+      </c>
+      <c r="N234">
+        <v>3</v>
+      </c>
+      <c r="O234" t="s">
+        <v>247</v>
+      </c>
+      <c r="P234" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q234">
+        <v>3.2</v>
+      </c>
+      <c r="R234">
+        <v>2.25</v>
+      </c>
+      <c r="S234">
+        <v>3.2</v>
+      </c>
+      <c r="T234">
+        <v>1.36</v>
+      </c>
+      <c r="U234">
+        <v>3</v>
+      </c>
+      <c r="V234">
+        <v>2.63</v>
+      </c>
+      <c r="W234">
+        <v>1.44</v>
+      </c>
+      <c r="X234">
+        <v>7</v>
+      </c>
+      <c r="Y234">
+        <v>1.1</v>
+      </c>
+      <c r="Z234">
+        <v>2.63</v>
+      </c>
+      <c r="AA234">
+        <v>3.23</v>
+      </c>
+      <c r="AB234">
+        <v>2.63</v>
+      </c>
+      <c r="AC234">
+        <v>1.05</v>
+      </c>
+      <c r="AD234">
+        <v>9.5</v>
+      </c>
+      <c r="AE234">
+        <v>1.25</v>
+      </c>
+      <c r="AF234">
+        <v>3.75</v>
+      </c>
+      <c r="AG234">
+        <v>1.85</v>
+      </c>
+      <c r="AH234">
+        <v>1.89</v>
+      </c>
+      <c r="AI234">
+        <v>1.62</v>
+      </c>
+      <c r="AJ234">
+        <v>2.2</v>
+      </c>
+      <c r="AK234">
+        <v>1.48</v>
+      </c>
+      <c r="AL234">
+        <v>1.25</v>
+      </c>
+      <c r="AM234">
+        <v>1.48</v>
+      </c>
+      <c r="AN234">
+        <v>2.71</v>
+      </c>
+      <c r="AO234">
+        <v>1.57</v>
+      </c>
+      <c r="AP234">
+        <v>2.73</v>
+      </c>
+      <c r="AQ234">
+        <v>1.47</v>
+      </c>
+      <c r="AR234">
+        <v>1.77</v>
+      </c>
+      <c r="AS234">
+        <v>1.43</v>
+      </c>
+      <c r="AT234">
+        <v>3.2</v>
+      </c>
+      <c r="AU234">
+        <v>8</v>
+      </c>
+      <c r="AV234">
+        <v>3</v>
+      </c>
+      <c r="AW234">
+        <v>10</v>
+      </c>
+      <c r="AX234">
+        <v>6</v>
+      </c>
+      <c r="AY234">
+        <v>25</v>
+      </c>
+      <c r="AZ234">
+        <v>13</v>
+      </c>
+      <c r="BA234">
+        <v>4</v>
+      </c>
+      <c r="BB234">
+        <v>5</v>
+      </c>
+      <c r="BC234">
+        <v>9</v>
+      </c>
+      <c r="BD234">
+        <v>2</v>
+      </c>
+      <c r="BE234">
+        <v>6.55</v>
+      </c>
+      <c r="BF234">
+        <v>2.27</v>
+      </c>
+      <c r="BG234">
+        <v>1.21</v>
+      </c>
+      <c r="BH234">
+        <v>3.58</v>
+      </c>
+      <c r="BI234">
+        <v>1.41</v>
+      </c>
+      <c r="BJ234">
+        <v>2.6</v>
+      </c>
+      <c r="BK234">
+        <v>1.8</v>
+      </c>
+      <c r="BL234">
+        <v>1.91</v>
+      </c>
+      <c r="BM234">
+        <v>2.19</v>
+      </c>
+      <c r="BN234">
+        <v>1.57</v>
+      </c>
+      <c r="BO234">
+        <v>2.88</v>
+      </c>
+      <c r="BP234">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="353">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,6 +760,18 @@
     <t>['69', '83']</t>
   </si>
   <si>
+    <t>['54', '65']</t>
+  </si>
+  <si>
+    <t>['13', '66', '83']</t>
+  </si>
+  <si>
+    <t>['6', '87', '90+6']</t>
+  </si>
+  <si>
+    <t>['3', '49', '63', '80']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1046,6 +1058,21 @@
   </si>
   <si>
     <t>['83']</t>
+  </si>
+  <si>
+    <t>['73']</t>
+  </si>
+  <si>
+    <t>['44', '74']</t>
+  </si>
+  <si>
+    <t>['45+7', '86']</t>
+  </si>
+  <si>
+    <t>['45+5', '70']</t>
+  </si>
+  <si>
+    <t>['34', '77']</t>
   </si>
 </sst>
 </file>
@@ -1407,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP234"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1663,7 +1690,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1741,7 +1768,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -2153,7 +2180,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ4">
         <v>0.6</v>
@@ -2359,10 +2386,10 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ5">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2693,7 +2720,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2980,7 +3007,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ8">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3186,7 +3213,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ9">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3517,7 +3544,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3595,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ11">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3801,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ12">
         <v>1.8</v>
@@ -3929,7 +3956,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4010,7 +4037,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ13">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR13">
         <v>0</v>
@@ -4135,7 +4162,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4341,7 +4368,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4422,7 +4449,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ15">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4625,7 +4652,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ16">
         <v>1.73</v>
@@ -4753,7 +4780,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4831,10 +4858,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5037,7 +5064,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5246,7 +5273,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ19">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR19">
         <v>0.45</v>
@@ -5371,7 +5398,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5655,7 +5682,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ21">
         <v>0.6</v>
@@ -5783,7 +5810,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5989,7 +6016,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6070,7 +6097,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ23">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR23">
         <v>2.53</v>
@@ -6401,7 +6428,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6688,7 +6715,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ26">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR26">
         <v>1.53</v>
@@ -6813,7 +6840,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6891,7 +6918,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ27">
         <v>1.8</v>
@@ -7019,7 +7046,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7100,7 +7127,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ28">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR28">
         <v>0.79</v>
@@ -7225,7 +7252,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7303,7 +7330,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ29">
         <v>1.6</v>
@@ -7509,10 +7536,10 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ30">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR30">
         <v>2.35</v>
@@ -7715,10 +7742,10 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ31">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR31">
         <v>1.23</v>
@@ -8127,10 +8154,10 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR33">
         <v>1.52</v>
@@ -8255,7 +8282,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8667,7 +8694,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9157,7 +9184,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ38">
         <v>0.13</v>
@@ -9366,7 +9393,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ39">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR39">
         <v>1.72</v>
@@ -9572,7 +9599,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ40">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR40">
         <v>1.69</v>
@@ -9697,7 +9724,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9775,10 +9802,10 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ41">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR41">
         <v>1.62</v>
@@ -9903,7 +9930,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -9981,10 +10008,10 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ42">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR42">
         <v>0.95</v>
@@ -10187,7 +10214,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ43">
         <v>0.93</v>
@@ -10393,10 +10420,10 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ44">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR44">
         <v>1.89</v>
@@ -10599,10 +10626,10 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ45">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR45">
         <v>1.63</v>
@@ -11014,7 +11041,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ47">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR47">
         <v>1.76</v>
@@ -11139,7 +11166,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11345,7 +11372,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11551,7 +11578,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11757,7 +11784,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11835,10 +11862,10 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ51">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR51">
         <v>1.42</v>
@@ -12659,7 +12686,7 @@
         <v>1.67</v>
       </c>
       <c r="AP55">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -12787,7 +12814,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -12865,7 +12892,7 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ56">
         <v>1.8</v>
@@ -13071,7 +13098,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ57">
         <v>1.47</v>
@@ -13199,7 +13226,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13277,10 +13304,10 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ58">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR58">
         <v>0.9399999999999999</v>
@@ -13405,7 +13432,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13486,7 +13513,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ59">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13689,10 +13716,10 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ60">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR60">
         <v>1.66</v>
@@ -13817,7 +13844,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13895,7 +13922,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ61">
         <v>1.33</v>
@@ -14101,10 +14128,10 @@
         <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ62">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR62">
         <v>1.5</v>
@@ -14310,7 +14337,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ63">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR63">
         <v>1.69</v>
@@ -14513,10 +14540,10 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ64">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR64">
         <v>1.33</v>
@@ -14641,7 +14668,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15259,7 +15286,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15337,10 +15364,10 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ68">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR68">
         <v>1.04</v>
@@ -15465,7 +15492,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15958,7 +15985,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ71">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -16161,7 +16188,7 @@
         <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ72">
         <v>0.6</v>
@@ -16370,7 +16397,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ73">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR73">
         <v>1.73</v>
@@ -16495,7 +16522,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16779,7 +16806,7 @@
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ75">
         <v>0.6</v>
@@ -17194,7 +17221,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ77">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR77">
         <v>1.23</v>
@@ -17397,7 +17424,7 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ78">
         <v>0.93</v>
@@ -17606,7 +17633,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ79">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR79">
         <v>1.88</v>
@@ -17809,7 +17836,7 @@
         <v>0.6</v>
       </c>
       <c r="AP80">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ80">
         <v>1.47</v>
@@ -18221,7 +18248,7 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ82">
         <v>1.6</v>
@@ -18349,7 +18376,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18636,7 +18663,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ84">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR84">
         <v>1.61</v>
@@ -18967,7 +18994,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19048,7 +19075,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ86">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR86">
         <v>1.86</v>
@@ -19251,10 +19278,10 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ87">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR87">
         <v>1.36</v>
@@ -19457,10 +19484,10 @@
         <v>0.8</v>
       </c>
       <c r="AP88">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ88">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR88">
         <v>1.14</v>
@@ -19663,10 +19690,10 @@
         <v>0.8</v>
       </c>
       <c r="AP89">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ89">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -19997,7 +20024,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20203,7 +20230,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20490,7 +20517,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ93">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR93">
         <v>1.23</v>
@@ -20615,7 +20642,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20693,7 +20720,7 @@
         <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ94">
         <v>1.6</v>
@@ -21027,7 +21054,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21105,7 +21132,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ96">
         <v>1.8</v>
@@ -21233,7 +21260,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21314,7 +21341,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ97">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -21520,7 +21547,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ98">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR98">
         <v>1.83</v>
@@ -21645,7 +21672,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21723,10 +21750,10 @@
         <v>0.83</v>
       </c>
       <c r="AP99">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ99">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR99">
         <v>1.16</v>
@@ -21851,7 +21878,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -21929,7 +21956,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ100">
         <v>1.73</v>
@@ -22057,7 +22084,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22135,7 +22162,7 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ101">
         <v>1.47</v>
@@ -22344,7 +22371,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ102">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR102">
         <v>1.86</v>
@@ -22550,7 +22577,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ103">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR103">
         <v>1.64</v>
@@ -22753,10 +22780,10 @@
         <v>0.67</v>
       </c>
       <c r="AP104">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ104">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -22959,7 +22986,7 @@
         <v>1.33</v>
       </c>
       <c r="AP105">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ105">
         <v>1.33</v>
@@ -23087,7 +23114,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23293,7 +23320,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23374,7 +23401,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ107">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR107">
         <v>1.5</v>
@@ -23499,7 +23526,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23786,7 +23813,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ109">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR109">
         <v>1.75</v>
@@ -23911,7 +23938,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24195,7 +24222,7 @@
         <v>0.67</v>
       </c>
       <c r="AP111">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ111">
         <v>0.93</v>
@@ -24529,7 +24556,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24607,7 +24634,7 @@
         <v>1.86</v>
       </c>
       <c r="AP113">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ113">
         <v>1.73</v>
@@ -24816,7 +24843,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ114">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR114">
         <v>1.76</v>
@@ -25019,10 +25046,10 @@
         <v>0.71</v>
       </c>
       <c r="AP115">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ115">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR115">
         <v>2.07</v>
@@ -25225,10 +25252,10 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ116">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR116">
         <v>1.18</v>
@@ -25434,7 +25461,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ117">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR117">
         <v>1.85</v>
@@ -25637,7 +25664,7 @@
         <v>0.14</v>
       </c>
       <c r="AP118">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ118">
         <v>0.13</v>
@@ -25765,7 +25792,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25843,7 +25870,7 @@
         <v>0.71</v>
       </c>
       <c r="AP119">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ119">
         <v>1.47</v>
@@ -26049,7 +26076,7 @@
         <v>1.29</v>
       </c>
       <c r="AP120">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ120">
         <v>1.33</v>
@@ -26258,7 +26285,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ121">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR121">
         <v>1.8</v>
@@ -26383,7 +26410,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26667,10 +26694,10 @@
         <v>1.29</v>
       </c>
       <c r="AP123">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ123">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR123">
         <v>2.07</v>
@@ -27001,7 +27028,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27285,7 +27312,7 @@
         <v>1.57</v>
       </c>
       <c r="AP126">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ126">
         <v>1.6</v>
@@ -27413,7 +27440,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27491,10 +27518,10 @@
         <v>0.57</v>
       </c>
       <c r="AP127">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ127">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR127">
         <v>0.92</v>
@@ -27700,7 +27727,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ128">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR128">
         <v>1.7</v>
@@ -27825,7 +27852,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -28031,7 +28058,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28112,7 +28139,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ130">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR130">
         <v>1.84</v>
@@ -28315,7 +28342,7 @@
         <v>0.88</v>
       </c>
       <c r="AP131">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ131">
         <v>0.6</v>
@@ -28443,7 +28470,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28521,7 +28548,7 @@
         <v>1.75</v>
       </c>
       <c r="AP132">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ132">
         <v>1.73</v>
@@ -28727,10 +28754,10 @@
         <v>0.63</v>
       </c>
       <c r="AP133">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ133">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR133">
         <v>1.68</v>
@@ -28855,7 +28882,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -28936,7 +28963,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ134">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR134">
         <v>1.76</v>
@@ -29267,7 +29294,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29345,7 +29372,7 @@
         <v>0.13</v>
       </c>
       <c r="AP136">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ136">
         <v>0.13</v>
@@ -29554,7 +29581,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ137">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR137">
         <v>1.17</v>
@@ -29757,10 +29784,10 @@
         <v>1.38</v>
       </c>
       <c r="AP138">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ138">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR138">
         <v>1.55</v>
@@ -29963,7 +29990,7 @@
         <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ139">
         <v>0.93</v>
@@ -30169,10 +30196,10 @@
         <v>0.78</v>
       </c>
       <c r="AP140">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ140">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR140">
         <v>1.25</v>
@@ -30297,7 +30324,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30378,7 +30405,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ141">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR141">
         <v>1.44</v>
@@ -30581,7 +30608,7 @@
         <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ142">
         <v>1.8</v>
@@ -30709,7 +30736,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30790,7 +30817,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ143">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR143">
         <v>1.68</v>
@@ -30915,7 +30942,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31199,10 +31226,10 @@
         <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ145">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR145">
         <v>1.64</v>
@@ -31327,7 +31354,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31614,7 +31641,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ147">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR147">
         <v>1.75</v>
@@ -31739,7 +31766,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31820,7 +31847,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ148">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR148">
         <v>1.11</v>
@@ -31945,7 +31972,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32023,10 +32050,10 @@
         <v>0.44</v>
       </c>
       <c r="AP149">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ149">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR149">
         <v>1.18</v>
@@ -32435,7 +32462,7 @@
         <v>1.11</v>
       </c>
       <c r="AP151">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ151">
         <v>1.33</v>
@@ -32563,7 +32590,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32975,7 +33002,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33181,7 +33208,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33262,7 +33289,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ155">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR155">
         <v>1.43</v>
@@ -33387,7 +33414,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33465,10 +33492,10 @@
         <v>0.78</v>
       </c>
       <c r="AP156">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ156">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR156">
         <v>2.05</v>
@@ -33671,7 +33698,7 @@
         <v>0.67</v>
       </c>
       <c r="AP157">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ157">
         <v>0.93</v>
@@ -33799,7 +33826,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -33877,7 +33904,7 @@
         <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ158">
         <v>1.47</v>
@@ -34083,7 +34110,7 @@
         <v>0.11</v>
       </c>
       <c r="AP159">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ159">
         <v>0.13</v>
@@ -34211,7 +34238,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34292,7 +34319,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ160">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR160">
         <v>1.47</v>
@@ -34417,7 +34444,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34495,10 +34522,10 @@
         <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ161">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR161">
         <v>1.75</v>
@@ -34701,10 +34728,10 @@
         <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ162">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR162">
         <v>1.18</v>
@@ -34829,7 +34856,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34910,7 +34937,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ163">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR163">
         <v>1.85</v>
@@ -35241,7 +35268,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35447,7 +35474,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35525,10 +35552,10 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ166">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR166">
         <v>1.26</v>
@@ -35859,7 +35886,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -35937,7 +35964,7 @@
         <v>1.8</v>
       </c>
       <c r="AP168">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ168">
         <v>1.73</v>
@@ -36349,10 +36376,10 @@
         <v>0.91</v>
       </c>
       <c r="AP170">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ170">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR170">
         <v>1.54</v>
@@ -36477,7 +36504,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36558,7 +36585,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ171">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR171">
         <v>1.08</v>
@@ -36683,7 +36710,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36761,7 +36788,7 @@
         <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ172">
         <v>1.8</v>
@@ -36889,7 +36916,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36967,7 +36994,7 @@
         <v>0.1</v>
       </c>
       <c r="AP173">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ173">
         <v>0.13</v>
@@ -37095,7 +37122,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37507,7 +37534,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37713,7 +37740,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37794,7 +37821,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ177">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR177">
         <v>1.71</v>
@@ -38000,7 +38027,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ178">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR178">
         <v>1.57</v>
@@ -38125,7 +38152,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38331,7 +38358,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38412,7 +38439,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ180">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR180">
         <v>1.69</v>
@@ -38615,10 +38642,10 @@
         <v>0.45</v>
       </c>
       <c r="AP181">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ181">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR181">
         <v>2.05</v>
@@ -38821,10 +38848,10 @@
         <v>1.5</v>
       </c>
       <c r="AP182">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ182">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR182">
         <v>1.21</v>
@@ -38949,7 +38976,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39027,7 +39054,7 @@
         <v>1.18</v>
       </c>
       <c r="AP183">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ183">
         <v>1.47</v>
@@ -39155,7 +39182,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39233,7 +39260,7 @@
         <v>0.9</v>
       </c>
       <c r="AP184">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ184">
         <v>1</v>
@@ -39439,7 +39466,7 @@
         <v>1.27</v>
       </c>
       <c r="AP185">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ185">
         <v>1.33</v>
@@ -39645,7 +39672,7 @@
         <v>0.82</v>
       </c>
       <c r="AP186">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ186">
         <v>1</v>
@@ -39854,7 +39881,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ187">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR187">
         <v>1.65</v>
@@ -39979,7 +40006,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40597,7 +40624,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40678,7 +40705,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ191">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR191">
         <v>1.79</v>
@@ -40881,7 +40908,7 @@
         <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ192">
         <v>1.6</v>
@@ -41009,7 +41036,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41090,7 +41117,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ193">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR193">
         <v>1.37</v>
@@ -41215,7 +41242,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41293,7 +41320,7 @@
         <v>1.25</v>
       </c>
       <c r="AP194">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ194">
         <v>1.33</v>
@@ -41499,7 +41526,7 @@
         <v>0.67</v>
       </c>
       <c r="AP195">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ195">
         <v>0.6</v>
@@ -41708,7 +41735,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ196">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR196">
         <v>1.08</v>
@@ -41914,7 +41941,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ197">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR197">
         <v>1.75</v>
@@ -42117,10 +42144,10 @@
         <v>1.42</v>
       </c>
       <c r="AP198">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ198">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR198">
         <v>1.68</v>
@@ -42245,7 +42272,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42451,7 +42478,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42735,10 +42762,10 @@
         <v>0.92</v>
       </c>
       <c r="AP201">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ201">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR201">
         <v>1.28</v>
@@ -42863,7 +42890,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -42941,7 +42968,7 @@
         <v>1.67</v>
       </c>
       <c r="AP202">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ202">
         <v>1.8</v>
@@ -43069,7 +43096,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43147,10 +43174,10 @@
         <v>1.25</v>
       </c>
       <c r="AP203">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ203">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR203">
         <v>1.28</v>
@@ -43275,7 +43302,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43356,7 +43383,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ204">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR204">
         <v>1.66</v>
@@ -43481,7 +43508,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43687,7 +43714,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -43765,7 +43792,7 @@
         <v>0.08</v>
       </c>
       <c r="AP206">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ206">
         <v>0.13</v>
@@ -44386,7 +44413,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ209">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR209">
         <v>1.64</v>
@@ -44589,10 +44616,10 @@
         <v>0.62</v>
       </c>
       <c r="AP210">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="AQ210">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="AR210">
         <v>1.55</v>
@@ -44923,7 +44950,7 @@
         <v>227</v>
       </c>
       <c r="P212" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="Q212">
         <v>2.75</v>
@@ -45004,7 +45031,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ212">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR212">
         <v>1.93</v>
@@ -45129,7 +45156,7 @@
         <v>239</v>
       </c>
       <c r="P213" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -45335,7 +45362,7 @@
         <v>86</v>
       </c>
       <c r="P214" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q214">
         <v>1.71</v>
@@ -45413,7 +45440,7 @@
         <v>0.85</v>
       </c>
       <c r="AP214">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="AQ214">
         <v>0.93</v>
@@ -45747,7 +45774,7 @@
         <v>87</v>
       </c>
       <c r="P216" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="Q216">
         <v>3.25</v>
@@ -45825,7 +45852,7 @@
         <v>1.46</v>
       </c>
       <c r="AP216">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AQ216">
         <v>1.47</v>
@@ -46034,7 +46061,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ217">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="AR217">
         <v>1.34</v>
@@ -46365,7 +46392,7 @@
         <v>88</v>
       </c>
       <c r="P219" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46443,7 +46470,7 @@
         <v>1.69</v>
       </c>
       <c r="AP219">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="AQ219">
         <v>1.73</v>
@@ -46652,7 +46679,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ220">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AR220">
         <v>1.72</v>
@@ -46777,7 +46804,7 @@
         <v>241</v>
       </c>
       <c r="P221" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="Q221">
         <v>2.25</v>
@@ -46858,7 +46885,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ221">
-        <v>0.43</v>
+        <v>0.6</v>
       </c>
       <c r="AR221">
         <v>1.54</v>
@@ -47064,7 +47091,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ222">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AR222">
         <v>1.82</v>
@@ -47267,7 +47294,7 @@
         <v>0.92</v>
       </c>
       <c r="AP223">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="AQ223">
         <v>1</v>
@@ -47395,7 +47422,7 @@
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="Q224">
         <v>4.33</v>
@@ -47473,7 +47500,7 @@
         <v>1.62</v>
       </c>
       <c r="AP224">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ224">
         <v>1.6</v>
@@ -47679,10 +47706,10 @@
         <v>0.85</v>
       </c>
       <c r="AP225">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="AQ225">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AR225">
         <v>1.31</v>
@@ -48631,7 +48658,7 @@
         <v>174</v>
       </c>
       <c r="P230" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="Q230">
         <v>4.75</v>
@@ -49043,7 +49070,7 @@
         <v>87</v>
       </c>
       <c r="P232" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49612,6 +49639,1448 @@
       </c>
       <c r="BP234">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="235" spans="1:68">
+      <c r="A235" s="1">
+        <v>234</v>
+      </c>
+      <c r="B235">
+        <v>7453657</v>
+      </c>
+      <c r="C235" t="s">
+        <v>68</v>
+      </c>
+      <c r="D235" t="s">
+        <v>69</v>
+      </c>
+      <c r="E235" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F235">
+        <v>30</v>
+      </c>
+      <c r="G235" t="s">
+        <v>79</v>
+      </c>
+      <c r="H235" t="s">
+        <v>71</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>0</v>
+      </c>
+      <c r="L235">
+        <v>2</v>
+      </c>
+      <c r="M235">
+        <v>1</v>
+      </c>
+      <c r="N235">
+        <v>3</v>
+      </c>
+      <c r="O235" t="s">
+        <v>248</v>
+      </c>
+      <c r="P235" t="s">
+        <v>348</v>
+      </c>
+      <c r="Q235">
+        <v>2.5</v>
+      </c>
+      <c r="R235">
+        <v>2.25</v>
+      </c>
+      <c r="S235">
+        <v>4.5</v>
+      </c>
+      <c r="T235">
+        <v>1.36</v>
+      </c>
+      <c r="U235">
+        <v>3</v>
+      </c>
+      <c r="V235">
+        <v>2.75</v>
+      </c>
+      <c r="W235">
+        <v>1.4</v>
+      </c>
+      <c r="X235">
+        <v>7</v>
+      </c>
+      <c r="Y235">
+        <v>1.1</v>
+      </c>
+      <c r="Z235">
+        <v>1.72</v>
+      </c>
+      <c r="AA235">
+        <v>3.84</v>
+      </c>
+      <c r="AB235">
+        <v>4.4</v>
+      </c>
+      <c r="AC235">
+        <v>1.05</v>
+      </c>
+      <c r="AD235">
+        <v>9.5</v>
+      </c>
+      <c r="AE235">
+        <v>1.25</v>
+      </c>
+      <c r="AF235">
+        <v>3.7</v>
+      </c>
+      <c r="AG235">
+        <v>1.77</v>
+      </c>
+      <c r="AH235">
+        <v>1.98</v>
+      </c>
+      <c r="AI235">
+        <v>1.75</v>
+      </c>
+      <c r="AJ235">
+        <v>2</v>
+      </c>
+      <c r="AK235">
+        <v>1.22</v>
+      </c>
+      <c r="AL235">
+        <v>1.22</v>
+      </c>
+      <c r="AM235">
+        <v>1.91</v>
+      </c>
+      <c r="AN235">
+        <v>1.43</v>
+      </c>
+      <c r="AO235">
+        <v>1.07</v>
+      </c>
+      <c r="AP235">
+        <v>1.53</v>
+      </c>
+      <c r="AQ235">
+        <v>1</v>
+      </c>
+      <c r="AR235">
+        <v>1.5</v>
+      </c>
+      <c r="AS235">
+        <v>1.2</v>
+      </c>
+      <c r="AT235">
+        <v>2.7</v>
+      </c>
+      <c r="AU235">
+        <v>8</v>
+      </c>
+      <c r="AV235">
+        <v>6</v>
+      </c>
+      <c r="AW235">
+        <v>9</v>
+      </c>
+      <c r="AX235">
+        <v>11</v>
+      </c>
+      <c r="AY235">
+        <v>18</v>
+      </c>
+      <c r="AZ235">
+        <v>23</v>
+      </c>
+      <c r="BA235">
+        <v>5</v>
+      </c>
+      <c r="BB235">
+        <v>5</v>
+      </c>
+      <c r="BC235">
+        <v>10</v>
+      </c>
+      <c r="BD235">
+        <v>1.56</v>
+      </c>
+      <c r="BE235">
+        <v>8.9</v>
+      </c>
+      <c r="BF235">
+        <v>2.94</v>
+      </c>
+      <c r="BG235">
+        <v>1.23</v>
+      </c>
+      <c r="BH235">
+        <v>3.42</v>
+      </c>
+      <c r="BI235">
+        <v>1.46</v>
+      </c>
+      <c r="BJ235">
+        <v>2.45</v>
+      </c>
+      <c r="BK235">
+        <v>1.85</v>
+      </c>
+      <c r="BL235">
+        <v>1.85</v>
+      </c>
+      <c r="BM235">
+        <v>2.32</v>
+      </c>
+      <c r="BN235">
+        <v>1.51</v>
+      </c>
+      <c r="BO235">
+        <v>3.08</v>
+      </c>
+      <c r="BP235">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="236" spans="1:68">
+      <c r="A236" s="1">
+        <v>235</v>
+      </c>
+      <c r="B236">
+        <v>7453656</v>
+      </c>
+      <c r="C236" t="s">
+        <v>68</v>
+      </c>
+      <c r="D236" t="s">
+        <v>69</v>
+      </c>
+      <c r="E236" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F236">
+        <v>30</v>
+      </c>
+      <c r="G236" t="s">
+        <v>80</v>
+      </c>
+      <c r="H236" t="s">
+        <v>81</v>
+      </c>
+      <c r="I236">
+        <v>1</v>
+      </c>
+      <c r="J236">
+        <v>1</v>
+      </c>
+      <c r="K236">
+        <v>2</v>
+      </c>
+      <c r="L236">
+        <v>3</v>
+      </c>
+      <c r="M236">
+        <v>2</v>
+      </c>
+      <c r="N236">
+        <v>5</v>
+      </c>
+      <c r="O236" t="s">
+        <v>249</v>
+      </c>
+      <c r="P236" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q236">
+        <v>3.1</v>
+      </c>
+      <c r="R236">
+        <v>2.1</v>
+      </c>
+      <c r="S236">
+        <v>3.5</v>
+      </c>
+      <c r="T236">
+        <v>1.4</v>
+      </c>
+      <c r="U236">
+        <v>2.75</v>
+      </c>
+      <c r="V236">
+        <v>3</v>
+      </c>
+      <c r="W236">
+        <v>1.36</v>
+      </c>
+      <c r="X236">
+        <v>8</v>
+      </c>
+      <c r="Y236">
+        <v>1.08</v>
+      </c>
+      <c r="Z236">
+        <v>2.35</v>
+      </c>
+      <c r="AA236">
+        <v>2.98</v>
+      </c>
+      <c r="AB236">
+        <v>3.23</v>
+      </c>
+      <c r="AC236">
+        <v>1.06</v>
+      </c>
+      <c r="AD236">
+        <v>8.5</v>
+      </c>
+      <c r="AE236">
+        <v>1.3</v>
+      </c>
+      <c r="AF236">
+        <v>3.35</v>
+      </c>
+      <c r="AG236">
+        <v>1.89</v>
+      </c>
+      <c r="AH236">
+        <v>1.85</v>
+      </c>
+      <c r="AI236">
+        <v>1.67</v>
+      </c>
+      <c r="AJ236">
+        <v>2.1</v>
+      </c>
+      <c r="AK236">
+        <v>1.38</v>
+      </c>
+      <c r="AL236">
+        <v>1.3</v>
+      </c>
+      <c r="AM236">
+        <v>1.53</v>
+      </c>
+      <c r="AN236">
+        <v>1.79</v>
+      </c>
+      <c r="AO236">
+        <v>0.64</v>
+      </c>
+      <c r="AP236">
+        <v>1.87</v>
+      </c>
+      <c r="AQ236">
+        <v>0.6</v>
+      </c>
+      <c r="AR236">
+        <v>1.28</v>
+      </c>
+      <c r="AS236">
+        <v>1.25</v>
+      </c>
+      <c r="AT236">
+        <v>2.53</v>
+      </c>
+      <c r="AU236">
+        <v>5</v>
+      </c>
+      <c r="AV236">
+        <v>3</v>
+      </c>
+      <c r="AW236">
+        <v>6</v>
+      </c>
+      <c r="AX236">
+        <v>1</v>
+      </c>
+      <c r="AY236">
+        <v>12</v>
+      </c>
+      <c r="AZ236">
+        <v>4</v>
+      </c>
+      <c r="BA236">
+        <v>5</v>
+      </c>
+      <c r="BB236">
+        <v>2</v>
+      </c>
+      <c r="BC236">
+        <v>7</v>
+      </c>
+      <c r="BD236">
+        <v>1.92</v>
+      </c>
+      <c r="BE236">
+        <v>6.6</v>
+      </c>
+      <c r="BF236">
+        <v>2.38</v>
+      </c>
+      <c r="BG236">
+        <v>1.2</v>
+      </c>
+      <c r="BH236">
+        <v>3.68</v>
+      </c>
+      <c r="BI236">
+        <v>1.41</v>
+      </c>
+      <c r="BJ236">
+        <v>2.6</v>
+      </c>
+      <c r="BK236">
+        <v>1.73</v>
+      </c>
+      <c r="BL236">
+        <v>2</v>
+      </c>
+      <c r="BM236">
+        <v>2.19</v>
+      </c>
+      <c r="BN236">
+        <v>1.57</v>
+      </c>
+      <c r="BO236">
+        <v>2.88</v>
+      </c>
+      <c r="BP236">
+        <v>1.32</v>
+      </c>
+    </row>
+    <row r="237" spans="1:68">
+      <c r="A237" s="1">
+        <v>236</v>
+      </c>
+      <c r="B237">
+        <v>7453655</v>
+      </c>
+      <c r="C237" t="s">
+        <v>68</v>
+      </c>
+      <c r="D237" t="s">
+        <v>69</v>
+      </c>
+      <c r="E237" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F237">
+        <v>30</v>
+      </c>
+      <c r="G237" t="s">
+        <v>72</v>
+      </c>
+      <c r="H237" t="s">
+        <v>77</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>1</v>
+      </c>
+      <c r="K237">
+        <v>1</v>
+      </c>
+      <c r="L237">
+        <v>1</v>
+      </c>
+      <c r="M237">
+        <v>2</v>
+      </c>
+      <c r="N237">
+        <v>3</v>
+      </c>
+      <c r="O237" t="s">
+        <v>118</v>
+      </c>
+      <c r="P237" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q237">
+        <v>3.75</v>
+      </c>
+      <c r="R237">
+        <v>2.3</v>
+      </c>
+      <c r="S237">
+        <v>2.6</v>
+      </c>
+      <c r="T237">
+        <v>1.3</v>
+      </c>
+      <c r="U237">
+        <v>3.4</v>
+      </c>
+      <c r="V237">
+        <v>2.5</v>
+      </c>
+      <c r="W237">
+        <v>1.5</v>
+      </c>
+      <c r="X237">
+        <v>6</v>
+      </c>
+      <c r="Y237">
+        <v>1.13</v>
+      </c>
+      <c r="Z237">
+        <v>3.38</v>
+      </c>
+      <c r="AA237">
+        <v>3.75</v>
+      </c>
+      <c r="AB237">
+        <v>1.97</v>
+      </c>
+      <c r="AC237">
+        <v>1.04</v>
+      </c>
+      <c r="AD237">
+        <v>10</v>
+      </c>
+      <c r="AE237">
+        <v>1.2</v>
+      </c>
+      <c r="AF237">
+        <v>4.33</v>
+      </c>
+      <c r="AG237">
+        <v>1.59</v>
+      </c>
+      <c r="AH237">
+        <v>2.27</v>
+      </c>
+      <c r="AI237">
+        <v>1.57</v>
+      </c>
+      <c r="AJ237">
+        <v>2.25</v>
+      </c>
+      <c r="AK237">
+        <v>1.77</v>
+      </c>
+      <c r="AL237">
+        <v>1.22</v>
+      </c>
+      <c r="AM237">
+        <v>1.3</v>
+      </c>
+      <c r="AN237">
+        <v>1.14</v>
+      </c>
+      <c r="AO237">
+        <v>0.86</v>
+      </c>
+      <c r="AP237">
+        <v>1.07</v>
+      </c>
+      <c r="AQ237">
+        <v>1</v>
+      </c>
+      <c r="AR237">
+        <v>1.3</v>
+      </c>
+      <c r="AS237">
+        <v>1.58</v>
+      </c>
+      <c r="AT237">
+        <v>2.88</v>
+      </c>
+      <c r="AU237">
+        <v>2</v>
+      </c>
+      <c r="AV237">
+        <v>5</v>
+      </c>
+      <c r="AW237">
+        <v>6</v>
+      </c>
+      <c r="AX237">
+        <v>7</v>
+      </c>
+      <c r="AY237">
+        <v>10</v>
+      </c>
+      <c r="AZ237">
+        <v>16</v>
+      </c>
+      <c r="BA237">
+        <v>6</v>
+      </c>
+      <c r="BB237">
+        <v>4</v>
+      </c>
+      <c r="BC237">
+        <v>10</v>
+      </c>
+      <c r="BD237">
+        <v>2.34</v>
+      </c>
+      <c r="BE237">
+        <v>6.65</v>
+      </c>
+      <c r="BF237">
+        <v>1.94</v>
+      </c>
+      <c r="BG237">
+        <v>1.15</v>
+      </c>
+      <c r="BH237">
+        <v>4.25</v>
+      </c>
+      <c r="BI237">
+        <v>1.32</v>
+      </c>
+      <c r="BJ237">
+        <v>2.88</v>
+      </c>
+      <c r="BK237">
+        <v>1.58</v>
+      </c>
+      <c r="BL237">
+        <v>2.17</v>
+      </c>
+      <c r="BM237">
+        <v>1.93</v>
+      </c>
+      <c r="BN237">
+        <v>1.77</v>
+      </c>
+      <c r="BO237">
+        <v>2.57</v>
+      </c>
+      <c r="BP237">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="238" spans="1:68">
+      <c r="A238" s="1">
+        <v>237</v>
+      </c>
+      <c r="B238">
+        <v>7453654</v>
+      </c>
+      <c r="C238" t="s">
+        <v>68</v>
+      </c>
+      <c r="D238" t="s">
+        <v>69</v>
+      </c>
+      <c r="E238" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F238">
+        <v>30</v>
+      </c>
+      <c r="G238" t="s">
+        <v>84</v>
+      </c>
+      <c r="H238" t="s">
+        <v>82</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+      <c r="M238">
+        <v>0</v>
+      </c>
+      <c r="N238">
+        <v>0</v>
+      </c>
+      <c r="O238" t="s">
+        <v>87</v>
+      </c>
+      <c r="P238" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q238">
+        <v>0</v>
+      </c>
+      <c r="R238">
+        <v>0</v>
+      </c>
+      <c r="S238">
+        <v>0</v>
+      </c>
+      <c r="T238">
+        <v>0</v>
+      </c>
+      <c r="U238">
+        <v>0</v>
+      </c>
+      <c r="V238">
+        <v>0</v>
+      </c>
+      <c r="W238">
+        <v>0</v>
+      </c>
+      <c r="X238">
+        <v>0</v>
+      </c>
+      <c r="Y238">
+        <v>0</v>
+      </c>
+      <c r="Z238">
+        <v>2.9</v>
+      </c>
+      <c r="AA238">
+        <v>3.1</v>
+      </c>
+      <c r="AB238">
+        <v>2.4</v>
+      </c>
+      <c r="AC238">
+        <v>0</v>
+      </c>
+      <c r="AD238">
+        <v>0</v>
+      </c>
+      <c r="AE238">
+        <v>0</v>
+      </c>
+      <c r="AF238">
+        <v>0</v>
+      </c>
+      <c r="AG238">
+        <v>1.85</v>
+      </c>
+      <c r="AH238">
+        <v>1.85</v>
+      </c>
+      <c r="AI238">
+        <v>0</v>
+      </c>
+      <c r="AJ238">
+        <v>0</v>
+      </c>
+      <c r="AK238">
+        <v>0</v>
+      </c>
+      <c r="AL238">
+        <v>0</v>
+      </c>
+      <c r="AM238">
+        <v>0</v>
+      </c>
+      <c r="AN238">
+        <v>1.71</v>
+      </c>
+      <c r="AO238">
+        <v>1.29</v>
+      </c>
+      <c r="AP238">
+        <v>1.67</v>
+      </c>
+      <c r="AQ238">
+        <v>1.27</v>
+      </c>
+      <c r="AR238">
+        <v>1.24</v>
+      </c>
+      <c r="AS238">
+        <v>1.24</v>
+      </c>
+      <c r="AT238">
+        <v>2.48</v>
+      </c>
+      <c r="AU238">
+        <v>-1</v>
+      </c>
+      <c r="AV238">
+        <v>-1</v>
+      </c>
+      <c r="AW238">
+        <v>-1</v>
+      </c>
+      <c r="AX238">
+        <v>-1</v>
+      </c>
+      <c r="AY238">
+        <v>-1</v>
+      </c>
+      <c r="AZ238">
+        <v>-1</v>
+      </c>
+      <c r="BA238">
+        <v>-1</v>
+      </c>
+      <c r="BB238">
+        <v>-1</v>
+      </c>
+      <c r="BC238">
+        <v>-1</v>
+      </c>
+      <c r="BD238">
+        <v>0</v>
+      </c>
+      <c r="BE238">
+        <v>0</v>
+      </c>
+      <c r="BF238">
+        <v>0</v>
+      </c>
+      <c r="BG238">
+        <v>0</v>
+      </c>
+      <c r="BH238">
+        <v>0</v>
+      </c>
+      <c r="BI238">
+        <v>0</v>
+      </c>
+      <c r="BJ238">
+        <v>0</v>
+      </c>
+      <c r="BK238">
+        <v>0</v>
+      </c>
+      <c r="BL238">
+        <v>0</v>
+      </c>
+      <c r="BM238">
+        <v>0</v>
+      </c>
+      <c r="BN238">
+        <v>0</v>
+      </c>
+      <c r="BO238">
+        <v>0</v>
+      </c>
+      <c r="BP238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:68">
+      <c r="A239" s="1">
+        <v>238</v>
+      </c>
+      <c r="B239">
+        <v>7453653</v>
+      </c>
+      <c r="C239" t="s">
+        <v>68</v>
+      </c>
+      <c r="D239" t="s">
+        <v>69</v>
+      </c>
+      <c r="E239" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F239">
+        <v>30</v>
+      </c>
+      <c r="G239" t="s">
+        <v>85</v>
+      </c>
+      <c r="H239" t="s">
+        <v>75</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>1</v>
+      </c>
+      <c r="K239">
+        <v>1</v>
+      </c>
+      <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>2</v>
+      </c>
+      <c r="N239">
+        <v>3</v>
+      </c>
+      <c r="O239" t="s">
+        <v>105</v>
+      </c>
+      <c r="P239" t="s">
+        <v>351</v>
+      </c>
+      <c r="Q239">
+        <v>2.3</v>
+      </c>
+      <c r="R239">
+        <v>2.25</v>
+      </c>
+      <c r="S239">
+        <v>5</v>
+      </c>
+      <c r="T239">
+        <v>1.36</v>
+      </c>
+      <c r="U239">
+        <v>3</v>
+      </c>
+      <c r="V239">
+        <v>2.75</v>
+      </c>
+      <c r="W239">
+        <v>1.4</v>
+      </c>
+      <c r="X239">
+        <v>7</v>
+      </c>
+      <c r="Y239">
+        <v>1.1</v>
+      </c>
+      <c r="Z239">
+        <v>1.68</v>
+      </c>
+      <c r="AA239">
+        <v>3.81</v>
+      </c>
+      <c r="AB239">
+        <v>4.75</v>
+      </c>
+      <c r="AC239">
+        <v>1.05</v>
+      </c>
+      <c r="AD239">
+        <v>9.5</v>
+      </c>
+      <c r="AE239">
+        <v>1.28</v>
+      </c>
+      <c r="AF239">
+        <v>3.65</v>
+      </c>
+      <c r="AG239">
+        <v>1.82</v>
+      </c>
+      <c r="AH239">
+        <v>1.92</v>
+      </c>
+      <c r="AI239">
+        <v>1.8</v>
+      </c>
+      <c r="AJ239">
+        <v>1.95</v>
+      </c>
+      <c r="AK239">
+        <v>1.17</v>
+      </c>
+      <c r="AL239">
+        <v>1.22</v>
+      </c>
+      <c r="AM239">
+        <v>2.1</v>
+      </c>
+      <c r="AN239">
+        <v>1.79</v>
+      </c>
+      <c r="AO239">
+        <v>0.43</v>
+      </c>
+      <c r="AP239">
+        <v>1.67</v>
+      </c>
+      <c r="AQ239">
+        <v>0.6</v>
+      </c>
+      <c r="AR239">
+        <v>1.61</v>
+      </c>
+      <c r="AS239">
+        <v>1.22</v>
+      </c>
+      <c r="AT239">
+        <v>2.83</v>
+      </c>
+      <c r="AU239">
+        <v>3</v>
+      </c>
+      <c r="AV239">
+        <v>4</v>
+      </c>
+      <c r="AW239">
+        <v>3</v>
+      </c>
+      <c r="AX239">
+        <v>4</v>
+      </c>
+      <c r="AY239">
+        <v>6</v>
+      </c>
+      <c r="AZ239">
+        <v>10</v>
+      </c>
+      <c r="BA239">
+        <v>4</v>
+      </c>
+      <c r="BB239">
+        <v>3</v>
+      </c>
+      <c r="BC239">
+        <v>7</v>
+      </c>
+      <c r="BD239">
+        <v>1.54</v>
+      </c>
+      <c r="BE239">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF239">
+        <v>2.97</v>
+      </c>
+      <c r="BG239">
+        <v>1.15</v>
+      </c>
+      <c r="BH239">
+        <v>4.2</v>
+      </c>
+      <c r="BI239">
+        <v>1.32</v>
+      </c>
+      <c r="BJ239">
+        <v>2.88</v>
+      </c>
+      <c r="BK239">
+        <v>1.7</v>
+      </c>
+      <c r="BL239">
+        <v>2.05</v>
+      </c>
+      <c r="BM239">
+        <v>2.05</v>
+      </c>
+      <c r="BN239">
+        <v>1.7</v>
+      </c>
+      <c r="BO239">
+        <v>2.57</v>
+      </c>
+      <c r="BP239">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="240" spans="1:68">
+      <c r="A240" s="1">
+        <v>239</v>
+      </c>
+      <c r="B240">
+        <v>7453651</v>
+      </c>
+      <c r="C240" t="s">
+        <v>68</v>
+      </c>
+      <c r="D240" t="s">
+        <v>69</v>
+      </c>
+      <c r="E240" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F240">
+        <v>30</v>
+      </c>
+      <c r="G240" t="s">
+        <v>73</v>
+      </c>
+      <c r="H240" t="s">
+        <v>83</v>
+      </c>
+      <c r="I240">
+        <v>1</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>1</v>
+      </c>
+      <c r="L240">
+        <v>3</v>
+      </c>
+      <c r="M240">
+        <v>0</v>
+      </c>
+      <c r="N240">
+        <v>3</v>
+      </c>
+      <c r="O240" t="s">
+        <v>250</v>
+      </c>
+      <c r="P240" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q240">
+        <v>2.5</v>
+      </c>
+      <c r="R240">
+        <v>2.2</v>
+      </c>
+      <c r="S240">
+        <v>4.5</v>
+      </c>
+      <c r="T240">
+        <v>1.4</v>
+      </c>
+      <c r="U240">
+        <v>2.75</v>
+      </c>
+      <c r="V240">
+        <v>3</v>
+      </c>
+      <c r="W240">
+        <v>1.36</v>
+      </c>
+      <c r="X240">
+        <v>8</v>
+      </c>
+      <c r="Y240">
+        <v>1.08</v>
+      </c>
+      <c r="Z240">
+        <v>1.83</v>
+      </c>
+      <c r="AA240">
+        <v>3.47</v>
+      </c>
+      <c r="AB240">
+        <v>4.3</v>
+      </c>
+      <c r="AC240">
+        <v>1.06</v>
+      </c>
+      <c r="AD240">
+        <v>8.5</v>
+      </c>
+      <c r="AE240">
+        <v>1.33</v>
+      </c>
+      <c r="AF240">
+        <v>3.25</v>
+      </c>
+      <c r="AG240">
+        <v>1.94</v>
+      </c>
+      <c r="AH240">
+        <v>1.8</v>
+      </c>
+      <c r="AI240">
+        <v>1.8</v>
+      </c>
+      <c r="AJ240">
+        <v>1.95</v>
+      </c>
+      <c r="AK240">
+        <v>1.22</v>
+      </c>
+      <c r="AL240">
+        <v>1.25</v>
+      </c>
+      <c r="AM240">
+        <v>1.85</v>
+      </c>
+      <c r="AN240">
+        <v>1.71</v>
+      </c>
+      <c r="AO240">
+        <v>0.79</v>
+      </c>
+      <c r="AP240">
+        <v>1.8</v>
+      </c>
+      <c r="AQ240">
+        <v>0.73</v>
+      </c>
+      <c r="AR240">
+        <v>1.65</v>
+      </c>
+      <c r="AS240">
+        <v>1.4</v>
+      </c>
+      <c r="AT240">
+        <v>3.05</v>
+      </c>
+      <c r="AU240">
+        <v>7</v>
+      </c>
+      <c r="AV240">
+        <v>5</v>
+      </c>
+      <c r="AW240">
+        <v>5</v>
+      </c>
+      <c r="AX240">
+        <v>7</v>
+      </c>
+      <c r="AY240">
+        <v>17</v>
+      </c>
+      <c r="AZ240">
+        <v>14</v>
+      </c>
+      <c r="BA240">
+        <v>7</v>
+      </c>
+      <c r="BB240">
+        <v>7</v>
+      </c>
+      <c r="BC240">
+        <v>14</v>
+      </c>
+      <c r="BD240">
+        <v>1.5</v>
+      </c>
+      <c r="BE240">
+        <v>7.2</v>
+      </c>
+      <c r="BF240">
+        <v>3.48</v>
+      </c>
+      <c r="BG240">
+        <v>1.19</v>
+      </c>
+      <c r="BH240">
+        <v>3.78</v>
+      </c>
+      <c r="BI240">
+        <v>1.4</v>
+      </c>
+      <c r="BJ240">
+        <v>2.64</v>
+      </c>
+      <c r="BK240">
+        <v>1.8</v>
+      </c>
+      <c r="BL240">
+        <v>1.91</v>
+      </c>
+      <c r="BM240">
+        <v>2.15</v>
+      </c>
+      <c r="BN240">
+        <v>1.59</v>
+      </c>
+      <c r="BO240">
+        <v>2.83</v>
+      </c>
+      <c r="BP240">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7453650</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F241">
+        <v>30</v>
+      </c>
+      <c r="G241" t="s">
+        <v>70</v>
+      </c>
+      <c r="H241" t="s">
+        <v>76</v>
+      </c>
+      <c r="I241">
+        <v>1</v>
+      </c>
+      <c r="J241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>2</v>
+      </c>
+      <c r="L241">
+        <v>4</v>
+      </c>
+      <c r="M241">
+        <v>2</v>
+      </c>
+      <c r="N241">
+        <v>6</v>
+      </c>
+      <c r="O241" t="s">
+        <v>251</v>
+      </c>
+      <c r="P241" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q241">
+        <v>2.1</v>
+      </c>
+      <c r="R241">
+        <v>2.25</v>
+      </c>
+      <c r="S241">
+        <v>6.5</v>
+      </c>
+      <c r="T241">
+        <v>1.4</v>
+      </c>
+      <c r="U241">
+        <v>2.75</v>
+      </c>
+      <c r="V241">
+        <v>2.75</v>
+      </c>
+      <c r="W241">
+        <v>1.4</v>
+      </c>
+      <c r="X241">
+        <v>8</v>
+      </c>
+      <c r="Y241">
+        <v>1.08</v>
+      </c>
+      <c r="Z241">
+        <v>1.55</v>
+      </c>
+      <c r="AA241">
+        <v>3.98</v>
+      </c>
+      <c r="AB241">
+        <v>5.8</v>
+      </c>
+      <c r="AC241">
+        <v>1.05</v>
+      </c>
+      <c r="AD241">
+        <v>9.5</v>
+      </c>
+      <c r="AE241">
+        <v>1.28</v>
+      </c>
+      <c r="AF241">
+        <v>3.6</v>
+      </c>
+      <c r="AG241">
+        <v>1.87</v>
+      </c>
+      <c r="AH241">
+        <v>1.87</v>
+      </c>
+      <c r="AI241">
+        <v>2</v>
+      </c>
+      <c r="AJ241">
+        <v>1.75</v>
+      </c>
+      <c r="AK241">
+        <v>1.12</v>
+      </c>
+      <c r="AL241">
+        <v>1.18</v>
+      </c>
+      <c r="AM241">
+        <v>2.45</v>
+      </c>
+      <c r="AN241">
+        <v>2.14</v>
+      </c>
+      <c r="AO241">
+        <v>1.07</v>
+      </c>
+      <c r="AP241">
+        <v>2.2</v>
+      </c>
+      <c r="AQ241">
+        <v>1</v>
+      </c>
+      <c r="AR241">
+        <v>2.06</v>
+      </c>
+      <c r="AS241">
+        <v>1.44</v>
+      </c>
+      <c r="AT241">
+        <v>3.5</v>
+      </c>
+      <c r="AU241">
+        <v>10</v>
+      </c>
+      <c r="AV241">
+        <v>4</v>
+      </c>
+      <c r="AW241">
+        <v>10</v>
+      </c>
+      <c r="AX241">
+        <v>3</v>
+      </c>
+      <c r="AY241">
+        <v>24</v>
+      </c>
+      <c r="AZ241">
+        <v>8</v>
+      </c>
+      <c r="BA241">
+        <v>2</v>
+      </c>
+      <c r="BB241">
+        <v>3</v>
+      </c>
+      <c r="BC241">
+        <v>5</v>
+      </c>
+      <c r="BD241">
+        <v>1.42</v>
+      </c>
+      <c r="BE241">
+        <v>9.5</v>
+      </c>
+      <c r="BF241">
+        <v>3.52</v>
+      </c>
+      <c r="BG241">
+        <v>1.18</v>
+      </c>
+      <c r="BH241">
+        <v>3.9</v>
+      </c>
+      <c r="BI241">
+        <v>1.36</v>
+      </c>
+      <c r="BJ241">
+        <v>2.7</v>
+      </c>
+      <c r="BK241">
+        <v>1.85</v>
+      </c>
+      <c r="BL241">
+        <v>1.85</v>
+      </c>
+      <c r="BM241">
+        <v>2.11</v>
+      </c>
+      <c r="BN241">
+        <v>1.65</v>
+      </c>
+      <c r="BO241">
+        <v>2.75</v>
+      </c>
+      <c r="BP241">
+        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -49646,7 +49646,7 @@
         <v>234</v>
       </c>
       <c r="B235">
-        <v>7453657</v>
+        <v>7453654</v>
       </c>
       <c r="C235" t="s">
         <v>68</v>
@@ -49655,16 +49655,16 @@
         <v>69</v>
       </c>
       <c r="E235" s="2">
-        <v>45732.60416666666</v>
+        <v>45732.39583333334</v>
       </c>
       <c r="F235">
         <v>30</v>
       </c>
       <c r="G235" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="H235" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="I235">
         <v>0</v>
@@ -49676,175 +49676,175 @@
         <v>0</v>
       </c>
       <c r="L235">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N235">
+        <v>0</v>
+      </c>
+      <c r="O235" t="s">
+        <v>87</v>
+      </c>
+      <c r="P235" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q235">
+        <v>3.6</v>
+      </c>
+      <c r="R235">
+        <v>2.05</v>
+      </c>
+      <c r="S235">
+        <v>3.2</v>
+      </c>
+      <c r="T235">
+        <v>1.44</v>
+      </c>
+      <c r="U235">
+        <v>2.63</v>
+      </c>
+      <c r="V235">
+        <v>3.4</v>
+      </c>
+      <c r="W235">
+        <v>1.3</v>
+      </c>
+      <c r="X235">
+        <v>10</v>
+      </c>
+      <c r="Y235">
+        <v>1.06</v>
+      </c>
+      <c r="Z235">
+        <v>2.9</v>
+      </c>
+      <c r="AA235">
+        <v>3.1</v>
+      </c>
+      <c r="AB235">
+        <v>2.4</v>
+      </c>
+      <c r="AC235">
+        <v>1.07</v>
+      </c>
+      <c r="AD235">
+        <v>7.75</v>
+      </c>
+      <c r="AE235">
+        <v>1.35</v>
+      </c>
+      <c r="AF235">
+        <v>2.95</v>
+      </c>
+      <c r="AG235">
+        <v>1.85</v>
+      </c>
+      <c r="AH235">
+        <v>1.85</v>
+      </c>
+      <c r="AI235">
+        <v>1.91</v>
+      </c>
+      <c r="AJ235">
+        <v>1.91</v>
+      </c>
+      <c r="AK235">
+        <v>1.5</v>
+      </c>
+      <c r="AL235">
+        <v>1.3</v>
+      </c>
+      <c r="AM235">
+        <v>1.4</v>
+      </c>
+      <c r="AN235">
+        <v>1.71</v>
+      </c>
+      <c r="AO235">
+        <v>1.29</v>
+      </c>
+      <c r="AP235">
+        <v>1.67</v>
+      </c>
+      <c r="AQ235">
+        <v>1.27</v>
+      </c>
+      <c r="AR235">
+        <v>1.24</v>
+      </c>
+      <c r="AS235">
+        <v>1.24</v>
+      </c>
+      <c r="AT235">
+        <v>2.48</v>
+      </c>
+      <c r="AU235">
+        <v>5</v>
+      </c>
+      <c r="AV235">
+        <v>2</v>
+      </c>
+      <c r="AW235">
         <v>3</v>
       </c>
-      <c r="O235" t="s">
-        <v>248</v>
-      </c>
-      <c r="P235" t="s">
-        <v>348</v>
-      </c>
-      <c r="Q235">
-        <v>2.5</v>
-      </c>
-      <c r="R235">
-        <v>2.25</v>
-      </c>
-      <c r="S235">
-        <v>4.5</v>
-      </c>
-      <c r="T235">
-        <v>1.36</v>
-      </c>
-      <c r="U235">
+      <c r="AX235">
         <v>3</v>
       </c>
-      <c r="V235">
-        <v>2.75</v>
-      </c>
-      <c r="W235">
-        <v>1.4</v>
-      </c>
-      <c r="X235">
-        <v>7</v>
-      </c>
-      <c r="Y235">
-        <v>1.1</v>
-      </c>
-      <c r="Z235">
-        <v>1.72</v>
-      </c>
-      <c r="AA235">
-        <v>3.84</v>
-      </c>
-      <c r="AB235">
-        <v>4.4</v>
-      </c>
-      <c r="AC235">
-        <v>1.05</v>
-      </c>
-      <c r="AD235">
-        <v>9.5</v>
-      </c>
-      <c r="AE235">
-        <v>1.25</v>
-      </c>
-      <c r="AF235">
-        <v>3.7</v>
-      </c>
-      <c r="AG235">
-        <v>1.77</v>
-      </c>
-      <c r="AH235">
-        <v>1.98</v>
-      </c>
-      <c r="AI235">
-        <v>1.75</v>
-      </c>
-      <c r="AJ235">
-        <v>2</v>
-      </c>
-      <c r="AK235">
-        <v>1.22</v>
-      </c>
-      <c r="AL235">
-        <v>1.22</v>
-      </c>
-      <c r="AM235">
-        <v>1.91</v>
-      </c>
-      <c r="AN235">
-        <v>1.43</v>
-      </c>
-      <c r="AO235">
-        <v>1.07</v>
-      </c>
-      <c r="AP235">
-        <v>1.53</v>
-      </c>
-      <c r="AQ235">
-        <v>1</v>
-      </c>
-      <c r="AR235">
-        <v>1.5</v>
-      </c>
-      <c r="AS235">
-        <v>1.2</v>
-      </c>
-      <c r="AT235">
-        <v>2.7</v>
-      </c>
-      <c r="AU235">
+      <c r="AY235">
         <v>8</v>
       </c>
-      <c r="AV235">
-        <v>6</v>
-      </c>
-      <c r="AW235">
-        <v>9</v>
-      </c>
-      <c r="AX235">
-        <v>11</v>
-      </c>
-      <c r="AY235">
-        <v>18</v>
-      </c>
       <c r="AZ235">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="BA235">
         <v>5</v>
       </c>
       <c r="BB235">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BC235">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD235">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="BE235">
-        <v>8.9</v>
+        <v>6.3</v>
       </c>
       <c r="BF235">
-        <v>2.94</v>
+        <v>2.25</v>
       </c>
       <c r="BG235">
-        <v>1.23</v>
+        <v>1.31</v>
       </c>
       <c r="BH235">
-        <v>3.42</v>
+        <v>2.92</v>
       </c>
       <c r="BI235">
-        <v>1.46</v>
+        <v>1.6</v>
       </c>
       <c r="BJ235">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="BK235">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BL235">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="BM235">
-        <v>2.32</v>
+        <v>2.71</v>
       </c>
       <c r="BN235">
-        <v>1.51</v>
+        <v>1.38</v>
       </c>
       <c r="BO235">
-        <v>3.08</v>
+        <v>3.72</v>
       </c>
       <c r="BP235">
-        <v>1.28</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="236" spans="1:68">
@@ -49852,7 +49852,7 @@
         <v>235</v>
       </c>
       <c r="B236">
-        <v>7453656</v>
+        <v>7453657</v>
       </c>
       <c r="C236" t="s">
         <v>68</v>
@@ -49867,190 +49867,190 @@
         <v>30</v>
       </c>
       <c r="G236" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H236" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="I236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K236">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L236">
+        <v>2</v>
+      </c>
+      <c r="M236">
+        <v>1</v>
+      </c>
+      <c r="N236">
         <v>3</v>
       </c>
-      <c r="M236">
-        <v>2</v>
-      </c>
-      <c r="N236">
-        <v>5</v>
-      </c>
       <c r="O236" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="P236" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="Q236">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R236">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="S236">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T236">
+        <v>1.36</v>
+      </c>
+      <c r="U236">
+        <v>3</v>
+      </c>
+      <c r="V236">
+        <v>2.75</v>
+      </c>
+      <c r="W236">
         <v>1.4</v>
       </c>
-      <c r="U236">
-        <v>2.75</v>
-      </c>
-      <c r="V236">
-        <v>3</v>
-      </c>
-      <c r="W236">
-        <v>1.36</v>
-      </c>
       <c r="X236">
+        <v>7</v>
+      </c>
+      <c r="Y236">
+        <v>1.1</v>
+      </c>
+      <c r="Z236">
+        <v>1.72</v>
+      </c>
+      <c r="AA236">
+        <v>3.84</v>
+      </c>
+      <c r="AB236">
+        <v>4.4</v>
+      </c>
+      <c r="AC236">
+        <v>1.05</v>
+      </c>
+      <c r="AD236">
+        <v>9.5</v>
+      </c>
+      <c r="AE236">
+        <v>1.25</v>
+      </c>
+      <c r="AF236">
+        <v>3.7</v>
+      </c>
+      <c r="AG236">
+        <v>1.77</v>
+      </c>
+      <c r="AH236">
+        <v>1.98</v>
+      </c>
+      <c r="AI236">
+        <v>1.75</v>
+      </c>
+      <c r="AJ236">
+        <v>2</v>
+      </c>
+      <c r="AK236">
+        <v>1.22</v>
+      </c>
+      <c r="AL236">
+        <v>1.22</v>
+      </c>
+      <c r="AM236">
+        <v>1.91</v>
+      </c>
+      <c r="AN236">
+        <v>1.43</v>
+      </c>
+      <c r="AO236">
+        <v>1.07</v>
+      </c>
+      <c r="AP236">
+        <v>1.53</v>
+      </c>
+      <c r="AQ236">
+        <v>1</v>
+      </c>
+      <c r="AR236">
+        <v>1.5</v>
+      </c>
+      <c r="AS236">
+        <v>1.2</v>
+      </c>
+      <c r="AT236">
+        <v>2.7</v>
+      </c>
+      <c r="AU236">
         <v>8</v>
       </c>
-      <c r="Y236">
-        <v>1.08</v>
-      </c>
-      <c r="Z236">
-        <v>2.35</v>
-      </c>
-      <c r="AA236">
-        <v>2.98</v>
-      </c>
-      <c r="AB236">
-        <v>3.23</v>
-      </c>
-      <c r="AC236">
-        <v>1.06</v>
-      </c>
-      <c r="AD236">
-        <v>8.5</v>
-      </c>
-      <c r="AE236">
-        <v>1.3</v>
-      </c>
-      <c r="AF236">
-        <v>3.35</v>
-      </c>
-      <c r="AG236">
-        <v>1.89</v>
-      </c>
-      <c r="AH236">
-        <v>1.85</v>
-      </c>
-      <c r="AI236">
-        <v>1.67</v>
-      </c>
-      <c r="AJ236">
-        <v>2.1</v>
-      </c>
-      <c r="AK236">
-        <v>1.38</v>
-      </c>
-      <c r="AL236">
-        <v>1.3</v>
-      </c>
-      <c r="AM236">
-        <v>1.53</v>
-      </c>
-      <c r="AN236">
-        <v>1.79</v>
-      </c>
-      <c r="AO236">
-        <v>0.64</v>
-      </c>
-      <c r="AP236">
-        <v>1.87</v>
-      </c>
-      <c r="AQ236">
-        <v>0.6</v>
-      </c>
-      <c r="AR236">
-        <v>1.28</v>
-      </c>
-      <c r="AS236">
-        <v>1.25</v>
-      </c>
-      <c r="AT236">
-        <v>2.53</v>
-      </c>
-      <c r="AU236">
-        <v>5</v>
-      </c>
       <c r="AV236">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AW236">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AX236">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="AY236">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AZ236">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="BA236">
         <v>5</v>
       </c>
       <c r="BB236">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BC236">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD236">
-        <v>1.92</v>
+        <v>1.56</v>
       </c>
       <c r="BE236">
-        <v>6.6</v>
+        <v>8.9</v>
       </c>
       <c r="BF236">
-        <v>2.38</v>
+        <v>2.94</v>
       </c>
       <c r="BG236">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="BH236">
-        <v>3.68</v>
+        <v>3.42</v>
       </c>
       <c r="BI236">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="BJ236">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BK236">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="BL236">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BM236">
-        <v>2.19</v>
+        <v>2.32</v>
       </c>
       <c r="BN236">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="BO236">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="BP236">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="237" spans="1:68">
@@ -50058,7 +50058,7 @@
         <v>236</v>
       </c>
       <c r="B237">
-        <v>7453655</v>
+        <v>7453656</v>
       </c>
       <c r="C237" t="s">
         <v>68</v>
@@ -50073,190 +50073,190 @@
         <v>30</v>
       </c>
       <c r="G237" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H237" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J237">
         <v>1</v>
       </c>
       <c r="K237">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L237">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M237">
         <v>2</v>
       </c>
       <c r="N237">
+        <v>5</v>
+      </c>
+      <c r="O237" t="s">
+        <v>249</v>
+      </c>
+      <c r="P237" t="s">
+        <v>349</v>
+      </c>
+      <c r="Q237">
+        <v>3.1</v>
+      </c>
+      <c r="R237">
+        <v>2.1</v>
+      </c>
+      <c r="S237">
+        <v>3.5</v>
+      </c>
+      <c r="T237">
+        <v>1.4</v>
+      </c>
+      <c r="U237">
+        <v>2.75</v>
+      </c>
+      <c r="V237">
         <v>3</v>
       </c>
-      <c r="O237" t="s">
-        <v>118</v>
-      </c>
-      <c r="P237" t="s">
-        <v>350</v>
-      </c>
-      <c r="Q237">
-        <v>3.75</v>
-      </c>
-      <c r="R237">
-        <v>2.3</v>
-      </c>
-      <c r="S237">
-        <v>2.6</v>
-      </c>
-      <c r="T237">
+      <c r="W237">
+        <v>1.36</v>
+      </c>
+      <c r="X237">
+        <v>8</v>
+      </c>
+      <c r="Y237">
+        <v>1.08</v>
+      </c>
+      <c r="Z237">
+        <v>2.35</v>
+      </c>
+      <c r="AA237">
+        <v>2.98</v>
+      </c>
+      <c r="AB237">
+        <v>3.23</v>
+      </c>
+      <c r="AC237">
+        <v>1.06</v>
+      </c>
+      <c r="AD237">
+        <v>8.5</v>
+      </c>
+      <c r="AE237">
         <v>1.3</v>
       </c>
-      <c r="U237">
-        <v>3.4</v>
-      </c>
-      <c r="V237">
-        <v>2.5</v>
-      </c>
-      <c r="W237">
-        <v>1.5</v>
-      </c>
-      <c r="X237">
-        <v>6</v>
-      </c>
-      <c r="Y237">
-        <v>1.13</v>
-      </c>
-      <c r="Z237">
-        <v>3.38</v>
-      </c>
-      <c r="AA237">
-        <v>3.75</v>
-      </c>
-      <c r="AB237">
-        <v>1.97</v>
-      </c>
-      <c r="AC237">
-        <v>1.04</v>
-      </c>
-      <c r="AD237">
-        <v>10</v>
-      </c>
-      <c r="AE237">
-        <v>1.2</v>
-      </c>
       <c r="AF237">
-        <v>4.33</v>
+        <v>3.35</v>
       </c>
       <c r="AG237">
-        <v>1.59</v>
+        <v>1.89</v>
       </c>
       <c r="AH237">
-        <v>2.27</v>
+        <v>1.85</v>
       </c>
       <c r="AI237">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AJ237">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AK237">
-        <v>1.77</v>
+        <v>1.38</v>
       </c>
       <c r="AL237">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AM237">
-        <v>1.3</v>
+        <v>1.53</v>
       </c>
       <c r="AN237">
-        <v>1.14</v>
+        <v>1.79</v>
       </c>
       <c r="AO237">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="AP237">
-        <v>1.07</v>
+        <v>1.87</v>
       </c>
       <c r="AQ237">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AR237">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AS237">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AT237">
-        <v>2.88</v>
+        <v>2.53</v>
       </c>
       <c r="AU237">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV237">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AW237">
         <v>6</v>
       </c>
       <c r="AX237">
+        <v>1</v>
+      </c>
+      <c r="AY237">
+        <v>12</v>
+      </c>
+      <c r="AZ237">
+        <v>4</v>
+      </c>
+      <c r="BA237">
+        <v>5</v>
+      </c>
+      <c r="BB237">
+        <v>2</v>
+      </c>
+      <c r="BC237">
         <v>7</v>
       </c>
-      <c r="AY237">
-        <v>10</v>
-      </c>
-      <c r="AZ237">
-        <v>16</v>
-      </c>
-      <c r="BA237">
-        <v>6</v>
-      </c>
-      <c r="BB237">
-        <v>4</v>
-      </c>
-      <c r="BC237">
-        <v>10</v>
-      </c>
       <c r="BD237">
-        <v>2.34</v>
+        <v>1.92</v>
       </c>
       <c r="BE237">
-        <v>6.65</v>
+        <v>6.6</v>
       </c>
       <c r="BF237">
-        <v>1.94</v>
+        <v>2.38</v>
       </c>
       <c r="BG237">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BH237">
-        <v>4.25</v>
+        <v>3.68</v>
       </c>
       <c r="BI237">
+        <v>1.41</v>
+      </c>
+      <c r="BJ237">
+        <v>2.6</v>
+      </c>
+      <c r="BK237">
+        <v>1.73</v>
+      </c>
+      <c r="BL237">
+        <v>2</v>
+      </c>
+      <c r="BM237">
+        <v>2.19</v>
+      </c>
+      <c r="BN237">
+        <v>1.57</v>
+      </c>
+      <c r="BO237">
+        <v>2.88</v>
+      </c>
+      <c r="BP237">
         <v>1.32</v>
-      </c>
-      <c r="BJ237">
-        <v>2.88</v>
-      </c>
-      <c r="BK237">
-        <v>1.58</v>
-      </c>
-      <c r="BL237">
-        <v>2.17</v>
-      </c>
-      <c r="BM237">
-        <v>1.93</v>
-      </c>
-      <c r="BN237">
-        <v>1.77</v>
-      </c>
-      <c r="BO237">
-        <v>2.57</v>
-      </c>
-      <c r="BP237">
-        <v>1.42</v>
       </c>
     </row>
     <row r="238" spans="1:68">
@@ -50264,7 +50264,7 @@
         <v>237</v>
       </c>
       <c r="B238">
-        <v>7453654</v>
+        <v>7453655</v>
       </c>
       <c r="C238" t="s">
         <v>68</v>
@@ -50279,190 +50279,190 @@
         <v>30</v>
       </c>
       <c r="G238" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H238" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I238">
         <v>0</v>
       </c>
       <c r="J238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N238">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O238" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="P238" t="s">
-        <v>87</v>
+        <v>350</v>
       </c>
       <c r="Q238">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R238">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="S238">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T238">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U238">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V238">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="W238">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="X238">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Y238">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z238">
-        <v>2.9</v>
+        <v>3.38</v>
       </c>
       <c r="AA238">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="AB238">
-        <v>2.4</v>
+        <v>1.97</v>
       </c>
       <c r="AC238">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AD238">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AE238">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AF238">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AG238">
-        <v>1.85</v>
+        <v>1.59</v>
       </c>
       <c r="AH238">
-        <v>1.85</v>
+        <v>2.27</v>
       </c>
       <c r="AI238">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ238">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AK238">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AL238">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AM238">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN238">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="AO238">
-        <v>1.29</v>
+        <v>0.86</v>
       </c>
       <c r="AP238">
-        <v>1.67</v>
+        <v>1.07</v>
       </c>
       <c r="AQ238">
-        <v>1.27</v>
+        <v>1</v>
       </c>
       <c r="AR238">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AS238">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AT238">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="AU238">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AV238">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AW238">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AX238">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AY238">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AZ238">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="BA238">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="BB238">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="BC238">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="BD238">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BE238">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="BF238">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BG238">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BH238">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BI238">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BJ238">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="BK238">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BL238">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="BM238">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="BN238">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BO238">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="BP238">
-        <v>0</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="239" spans="1:68">

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="352">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,16 +760,16 @@
     <t>['69', '83']</t>
   </si>
   <si>
-    <t>['54', '65']</t>
-  </si>
-  <si>
-    <t>['13', '66', '83']</t>
+    <t>['3', '49', '63', '80']</t>
   </si>
   <si>
     <t>['6', '87', '90+6']</t>
   </si>
   <si>
-    <t>['3', '49', '63', '80']</t>
+    <t>['54', '65']</t>
+  </si>
+  <si>
+    <t>['13', '66', '83']</t>
   </si>
   <si>
     <t>['65']</t>
@@ -1045,9 +1045,6 @@
     <t>['33', '70']</t>
   </si>
   <si>
-    <t>['29']</t>
-  </si>
-  <si>
     <t>['45', '70']</t>
   </si>
   <si>
@@ -1060,6 +1057,12 @@
     <t>['83']</t>
   </si>
   <si>
+    <t>['45+5', '70']</t>
+  </si>
+  <si>
+    <t>['34', '77']</t>
+  </si>
+  <si>
     <t>['73']</t>
   </si>
   <si>
@@ -1067,12 +1070,6 @@
   </si>
   <si>
     <t>['45+7', '86']</t>
-  </si>
-  <si>
-    <t>['45+5', '70']</t>
-  </si>
-  <si>
-    <t>['34', '77']</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1431,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4655,7 +4652,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ16">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4858,7 +4855,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ17">
         <v>1</v>
@@ -5891,7 +5888,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ22">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR22">
         <v>1.58</v>
@@ -8154,7 +8151,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -8775,7 +8772,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ36">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR36">
         <v>0.9399999999999999</v>
@@ -10626,7 +10623,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ45">
         <v>1.27</v>
@@ -11659,7 +11656,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ50">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR50">
         <v>1.76</v>
@@ -12686,7 +12683,7 @@
         <v>1.67</v>
       </c>
       <c r="AP55">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -14955,7 +14952,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ66">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR66">
         <v>1.81</v>
@@ -16188,7 +16185,7 @@
         <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ72">
         <v>0.6</v>
@@ -18457,7 +18454,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ83">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR83">
         <v>1.89</v>
@@ -21132,7 +21129,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ96">
         <v>1.8</v>
@@ -21959,7 +21956,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ100">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR100">
         <v>1.3</v>
@@ -24222,7 +24219,7 @@
         <v>0.67</v>
       </c>
       <c r="AP111">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ111">
         <v>0.93</v>
@@ -24637,7 +24634,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ113">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR113">
         <v>0.88</v>
@@ -28551,7 +28548,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ132">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR132">
         <v>1.55</v>
@@ -28754,7 +28751,7 @@
         <v>0.63</v>
       </c>
       <c r="AP133">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ133">
         <v>0.6</v>
@@ -31226,7 +31223,7 @@
         <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ145">
         <v>0.73</v>
@@ -32671,7 +32668,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ152">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR152">
         <v>1.81</v>
@@ -33904,7 +33901,7 @@
         <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ158">
         <v>1.47</v>
@@ -35967,7 +35964,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ168">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR168">
         <v>1.71</v>
@@ -36376,7 +36373,7 @@
         <v>0.91</v>
       </c>
       <c r="AP170">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -40499,7 +40496,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ190">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR190">
         <v>1.72</v>
@@ -40908,7 +40905,7 @@
         <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ192">
         <v>1.6</v>
@@ -43589,7 +43586,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ205">
-        <v>1.73</v>
+        <v>1.79</v>
       </c>
       <c r="AR205">
         <v>1.6</v>
@@ -43792,7 +43789,7 @@
         <v>0.08</v>
       </c>
       <c r="AP206">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AQ206">
         <v>0.13</v>
@@ -46350,7 +46347,7 @@
         <v>218</v>
       </c>
       <c r="B219">
-        <v>7454763</v>
+        <v>7453638</v>
       </c>
       <c r="C219" t="s">
         <v>68</v>
@@ -46365,190 +46362,190 @@
         <v>28</v>
       </c>
       <c r="G219" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="H219" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="I219">
         <v>0</v>
       </c>
       <c r="J219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M219">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N219">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O219" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="P219" t="s">
-        <v>343</v>
+        <v>87</v>
       </c>
       <c r="Q219">
-        <v>4.33</v>
+        <v>2.95</v>
       </c>
       <c r="R219">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S219">
-        <v>2.38</v>
+        <v>3.3</v>
       </c>
       <c r="T219">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="U219">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="V219">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="W219">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="X219">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y219">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="Z219">
-        <v>3.56</v>
+        <v>2.35</v>
       </c>
       <c r="AA219">
-        <v>3.65</v>
+        <v>3.39</v>
       </c>
       <c r="AB219">
-        <v>1.94</v>
+        <v>2.86</v>
       </c>
       <c r="AC219">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AD219">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="AE219">
-        <v>1.22</v>
+        <v>1.33</v>
       </c>
       <c r="AF219">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="AG219">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AH219">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AI219">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AJ219">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AK219">
-        <v>1.98</v>
+        <v>1.41</v>
       </c>
       <c r="AL219">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AM219">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AN219">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="AO219">
-        <v>1.69</v>
+        <v>1.31</v>
       </c>
       <c r="AP219">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AQ219">
-        <v>1.73</v>
+        <v>1.27</v>
       </c>
       <c r="AR219">
-        <v>1.58</v>
+        <v>1.72</v>
       </c>
       <c r="AS219">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="AT219">
-        <v>3.29</v>
+        <v>2.96</v>
       </c>
       <c r="AU219">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AV219">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW219">
         <v>11</v>
       </c>
       <c r="AX219">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY219">
         <v>23</v>
       </c>
       <c r="AZ219">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA219">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="BB219">
+        <v>5</v>
+      </c>
+      <c r="BC219">
         <v>7</v>
       </c>
-      <c r="BC219">
-        <v>13</v>
-      </c>
       <c r="BD219">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="BE219">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF219">
-        <v>1.58</v>
+        <v>1.98</v>
       </c>
       <c r="BG219">
+        <v>1.29</v>
+      </c>
+      <c r="BH219">
+        <v>3.15</v>
+      </c>
+      <c r="BI219">
+        <v>1.5</v>
+      </c>
+      <c r="BJ219">
+        <v>2.35</v>
+      </c>
+      <c r="BK219">
+        <v>1.84</v>
+      </c>
+      <c r="BL219">
+        <v>1.84</v>
+      </c>
+      <c r="BM219">
+        <v>2.3</v>
+      </c>
+      <c r="BN219">
+        <v>1.54</v>
+      </c>
+      <c r="BO219">
+        <v>2.95</v>
+      </c>
+      <c r="BP219">
         <v>1.33</v>
-      </c>
-      <c r="BH219">
-        <v>2.95</v>
-      </c>
-      <c r="BI219">
-        <v>1.57</v>
-      </c>
-      <c r="BJ219">
-        <v>2.23</v>
-      </c>
-      <c r="BK219">
-        <v>1.94</v>
-      </c>
-      <c r="BL219">
-        <v>1.76</v>
-      </c>
-      <c r="BM219">
-        <v>2.43</v>
-      </c>
-      <c r="BN219">
-        <v>1.49</v>
-      </c>
-      <c r="BO219">
-        <v>3.15</v>
-      </c>
-      <c r="BP219">
-        <v>1.3</v>
       </c>
     </row>
     <row r="220" spans="1:68">
@@ -46556,7 +46553,7 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>7453638</v>
+        <v>7453640</v>
       </c>
       <c r="C220" t="s">
         <v>68</v>
@@ -46565,94 +46562,94 @@
         <v>69</v>
       </c>
       <c r="E220" s="2">
-        <v>45717.5</v>
+        <v>45717.59375</v>
       </c>
       <c r="F220">
         <v>28</v>
       </c>
       <c r="G220" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H220" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I220">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J220">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K220">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L220">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M220">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N220">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O220" t="s">
-        <v>87</v>
+        <v>241</v>
       </c>
       <c r="P220" t="s">
-        <v>87</v>
+        <v>343</v>
       </c>
       <c r="Q220">
+        <v>2.25</v>
+      </c>
+      <c r="R220">
+        <v>2.2</v>
+      </c>
+      <c r="S220">
+        <v>4.5</v>
+      </c>
+      <c r="T220">
+        <v>1.35</v>
+      </c>
+      <c r="U220">
         <v>2.95</v>
       </c>
-      <c r="R220">
-        <v>2.1</v>
-      </c>
-      <c r="S220">
-        <v>3.3</v>
-      </c>
-      <c r="T220">
-        <v>1.38</v>
-      </c>
-      <c r="U220">
-        <v>2.8</v>
-      </c>
       <c r="V220">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="W220">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="X220">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="Y220">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z220">
-        <v>2.35</v>
+        <v>1.77</v>
       </c>
       <c r="AA220">
-        <v>3.39</v>
+        <v>3.8</v>
       </c>
       <c r="AB220">
-        <v>2.86</v>
+        <v>4.1</v>
       </c>
       <c r="AC220">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD220">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AE220">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF220">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="AG220">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH220">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AI220">
         <v>1.73</v>
@@ -46661,100 +46658,100 @@
         <v>1.95</v>
       </c>
       <c r="AK220">
-        <v>1.41</v>
+        <v>1.2</v>
       </c>
       <c r="AL220">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AM220">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="AN220">
+        <v>1.23</v>
+      </c>
+      <c r="AO220">
+        <v>0.46</v>
+      </c>
+      <c r="AP220">
+        <v>1.47</v>
+      </c>
+      <c r="AQ220">
+        <v>0.6</v>
+      </c>
+      <c r="AR220">
         <v>1.54</v>
       </c>
-      <c r="AO220">
-        <v>1.31</v>
-      </c>
-      <c r="AP220">
-        <v>1.4</v>
-      </c>
-      <c r="AQ220">
-        <v>1.27</v>
-      </c>
-      <c r="AR220">
-        <v>1.72</v>
-      </c>
       <c r="AS220">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AT220">
-        <v>2.96</v>
+        <v>2.69</v>
       </c>
       <c r="AU220">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="AV220">
+        <v>8</v>
+      </c>
+      <c r="AW220">
         <v>5</v>
       </c>
-      <c r="AW220">
-        <v>11</v>
-      </c>
       <c r="AX220">
+        <v>8</v>
+      </c>
+      <c r="AY220">
+        <v>10</v>
+      </c>
+      <c r="AZ220">
+        <v>18</v>
+      </c>
+      <c r="BA220">
+        <v>3</v>
+      </c>
+      <c r="BB220">
         <v>4</v>
-      </c>
-      <c r="AY220">
-        <v>23</v>
-      </c>
-      <c r="AZ220">
-        <v>11</v>
-      </c>
-      <c r="BA220">
-        <v>2</v>
-      </c>
-      <c r="BB220">
-        <v>5</v>
       </c>
       <c r="BC220">
         <v>7</v>
       </c>
       <c r="BD220">
+        <v>1.47</v>
+      </c>
+      <c r="BE220">
+        <v>7</v>
+      </c>
+      <c r="BF220">
+        <v>2.95</v>
+      </c>
+      <c r="BG220">
+        <v>1.21</v>
+      </c>
+      <c r="BH220">
+        <v>3.9</v>
+      </c>
+      <c r="BI220">
+        <v>1.38</v>
+      </c>
+      <c r="BJ220">
+        <v>2.8</v>
+      </c>
+      <c r="BK220">
+        <v>1.63</v>
+      </c>
+      <c r="BL220">
+        <v>2.15</v>
+      </c>
+      <c r="BM220">
         <v>1.98</v>
       </c>
-      <c r="BE220">
-        <v>6.4</v>
-      </c>
-      <c r="BF220">
-        <v>1.98</v>
-      </c>
-      <c r="BG220">
-        <v>1.29</v>
-      </c>
-      <c r="BH220">
-        <v>3.15</v>
-      </c>
-      <c r="BI220">
-        <v>1.5</v>
-      </c>
-      <c r="BJ220">
-        <v>2.35</v>
-      </c>
-      <c r="BK220">
-        <v>1.84</v>
-      </c>
-      <c r="BL220">
-        <v>1.84</v>
-      </c>
-      <c r="BM220">
-        <v>2.3</v>
-      </c>
       <c r="BN220">
-        <v>1.54</v>
+        <v>1.73</v>
       </c>
       <c r="BO220">
-        <v>2.95</v>
+        <v>2.48</v>
       </c>
       <c r="BP220">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="221" spans="1:68">
@@ -46762,7 +46759,7 @@
         <v>220</v>
       </c>
       <c r="B221">
-        <v>7453640</v>
+        <v>7453635</v>
       </c>
       <c r="C221" t="s">
         <v>68</v>
@@ -46771,196 +46768,196 @@
         <v>69</v>
       </c>
       <c r="E221" s="2">
-        <v>45717.59375</v>
+        <v>45717.69791666666</v>
       </c>
       <c r="F221">
         <v>28</v>
       </c>
       <c r="G221" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H221" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="I221">
         <v>2</v>
       </c>
       <c r="J221">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K221">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L221">
         <v>4</v>
       </c>
       <c r="M221">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N221">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O221" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P221" t="s">
-        <v>344</v>
+        <v>196</v>
       </c>
       <c r="Q221">
-        <v>2.25</v>
+        <v>1.78</v>
       </c>
       <c r="R221">
+        <v>2.45</v>
+      </c>
+      <c r="S221">
+        <v>6.5</v>
+      </c>
+      <c r="T221">
+        <v>1.3</v>
+      </c>
+      <c r="U221">
+        <v>3.25</v>
+      </c>
+      <c r="V221">
+        <v>2.35</v>
+      </c>
+      <c r="W221">
+        <v>1.52</v>
+      </c>
+      <c r="X221">
+        <v>5.5</v>
+      </c>
+      <c r="Y221">
+        <v>1.13</v>
+      </c>
+      <c r="Z221">
+        <v>1.33</v>
+      </c>
+      <c r="AA221">
+        <v>5.2</v>
+      </c>
+      <c r="AB221">
+        <v>8.1</v>
+      </c>
+      <c r="AC221">
+        <v>1.03</v>
+      </c>
+      <c r="AD221">
+        <v>11</v>
+      </c>
+      <c r="AE221">
+        <v>1.2</v>
+      </c>
+      <c r="AF221">
+        <v>4.33</v>
+      </c>
+      <c r="AG221">
+        <v>1.66</v>
+      </c>
+      <c r="AH221">
+        <v>2.22</v>
+      </c>
+      <c r="AI221">
+        <v>1.95</v>
+      </c>
+      <c r="AJ221">
+        <v>1.73</v>
+      </c>
+      <c r="AK221">
+        <v>1.08</v>
+      </c>
+      <c r="AL221">
+        <v>1.16</v>
+      </c>
+      <c r="AM221">
+        <v>3.1</v>
+      </c>
+      <c r="AN221">
+        <v>2.08</v>
+      </c>
+      <c r="AO221">
+        <v>1.15</v>
+      </c>
+      <c r="AP221">
         <v>2.2</v>
       </c>
-      <c r="S221">
-        <v>4.5</v>
-      </c>
-      <c r="T221">
-        <v>1.35</v>
-      </c>
-      <c r="U221">
-        <v>2.95</v>
-      </c>
-      <c r="V221">
-        <v>2.5</v>
-      </c>
-      <c r="W221">
-        <v>1.46</v>
-      </c>
-      <c r="X221">
-        <v>6.25</v>
-      </c>
-      <c r="Y221">
-        <v>1.1</v>
-      </c>
-      <c r="Z221">
-        <v>1.77</v>
-      </c>
-      <c r="AA221">
-        <v>3.8</v>
-      </c>
-      <c r="AB221">
-        <v>4.1</v>
-      </c>
-      <c r="AC221">
-        <v>1.05</v>
-      </c>
-      <c r="AD221">
-        <v>9.5</v>
-      </c>
-      <c r="AE221">
-        <v>1.25</v>
-      </c>
-      <c r="AF221">
-        <v>3.75</v>
-      </c>
-      <c r="AG221">
-        <v>1.8</v>
-      </c>
-      <c r="AH221">
-        <v>1.94</v>
-      </c>
-      <c r="AI221">
-        <v>1.73</v>
-      </c>
-      <c r="AJ221">
-        <v>1.95</v>
-      </c>
-      <c r="AK221">
-        <v>1.2</v>
-      </c>
-      <c r="AL221">
-        <v>1.26</v>
-      </c>
-      <c r="AM221">
-        <v>2.05</v>
-      </c>
-      <c r="AN221">
-        <v>1.23</v>
-      </c>
-      <c r="AO221">
-        <v>0.46</v>
-      </c>
-      <c r="AP221">
-        <v>1.47</v>
-      </c>
       <c r="AQ221">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR221">
-        <v>1.54</v>
+        <v>1.82</v>
       </c>
       <c r="AS221">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AT221">
-        <v>2.69</v>
+        <v>3.06</v>
       </c>
       <c r="AU221">
+        <v>14</v>
+      </c>
+      <c r="AV221">
+        <v>3</v>
+      </c>
+      <c r="AW221">
+        <v>7</v>
+      </c>
+      <c r="AX221">
+        <v>2</v>
+      </c>
+      <c r="AY221">
+        <v>25</v>
+      </c>
+      <c r="AZ221">
         <v>5</v>
       </c>
-      <c r="AV221">
-        <v>8</v>
-      </c>
-      <c r="AW221">
+      <c r="BA221">
+        <v>2</v>
+      </c>
+      <c r="BB221">
         <v>5</v>
-      </c>
-      <c r="AX221">
-        <v>8</v>
-      </c>
-      <c r="AY221">
-        <v>10</v>
-      </c>
-      <c r="AZ221">
-        <v>18</v>
-      </c>
-      <c r="BA221">
-        <v>3</v>
-      </c>
-      <c r="BB221">
-        <v>4</v>
       </c>
       <c r="BC221">
         <v>7</v>
       </c>
       <c r="BD221">
-        <v>1.47</v>
+        <v>1.27</v>
       </c>
       <c r="BE221">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BF221">
-        <v>2.95</v>
+        <v>3.95</v>
       </c>
       <c r="BG221">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BH221">
-        <v>3.9</v>
+        <v>3.15</v>
       </c>
       <c r="BI221">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="BJ221">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="BK221">
-        <v>1.63</v>
+        <v>1.83</v>
       </c>
       <c r="BL221">
-        <v>2.15</v>
+        <v>1.85</v>
       </c>
       <c r="BM221">
-        <v>1.98</v>
+        <v>2.3</v>
       </c>
       <c r="BN221">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="BO221">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="BP221">
-        <v>1.47</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="222" spans="1:68">
@@ -46968,7 +46965,7 @@
         <v>221</v>
       </c>
       <c r="B222">
-        <v>7453635</v>
+        <v>7453637</v>
       </c>
       <c r="C222" t="s">
         <v>68</v>
@@ -46977,196 +46974,196 @@
         <v>69</v>
       </c>
       <c r="E222" s="2">
-        <v>45717.69791666666</v>
+        <v>45718.5</v>
       </c>
       <c r="F222">
         <v>28</v>
       </c>
       <c r="G222" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H222" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I222">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J222">
         <v>0</v>
       </c>
       <c r="K222">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L222">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M222">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N222">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O222" t="s">
-        <v>242</v>
+        <v>95</v>
       </c>
       <c r="P222" t="s">
-        <v>196</v>
+        <v>87</v>
       </c>
       <c r="Q222">
-        <v>1.78</v>
+        <v>4.33</v>
       </c>
       <c r="R222">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="S222">
-        <v>6.5</v>
+        <v>2.5</v>
       </c>
       <c r="T222">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U222">
         <v>3.25</v>
       </c>
       <c r="V222">
-        <v>2.35</v>
+        <v>2.63</v>
       </c>
       <c r="W222">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="X222">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="Y222">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="Z222">
-        <v>1.33</v>
+        <v>3.09</v>
       </c>
       <c r="AA222">
-        <v>5.2</v>
+        <v>3.39</v>
       </c>
       <c r="AB222">
-        <v>8.1</v>
+        <v>2.21</v>
       </c>
       <c r="AC222">
         <v>1.03</v>
       </c>
       <c r="AD222">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE222">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AF222">
-        <v>4.33</v>
+        <v>3.89</v>
       </c>
       <c r="AG222">
-        <v>1.66</v>
+        <v>1.8</v>
       </c>
       <c r="AH222">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="AI222">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AJ222">
+        <v>2.1</v>
+      </c>
+      <c r="AK222">
+        <v>1.87</v>
+      </c>
+      <c r="AL222">
+        <v>1.27</v>
+      </c>
+      <c r="AM222">
+        <v>1.25</v>
+      </c>
+      <c r="AN222">
+        <v>1</v>
+      </c>
+      <c r="AO222">
+        <v>0.92</v>
+      </c>
+      <c r="AP222">
+        <v>1.07</v>
+      </c>
+      <c r="AQ222">
+        <v>1</v>
+      </c>
+      <c r="AR222">
+        <v>1.28</v>
+      </c>
+      <c r="AS222">
+        <v>1.48</v>
+      </c>
+      <c r="AT222">
+        <v>2.76</v>
+      </c>
+      <c r="AU222">
+        <v>5</v>
+      </c>
+      <c r="AV222">
+        <v>8</v>
+      </c>
+      <c r="AW222">
+        <v>9</v>
+      </c>
+      <c r="AX222">
+        <v>9</v>
+      </c>
+      <c r="AY222">
+        <v>15</v>
+      </c>
+      <c r="AZ222">
+        <v>18</v>
+      </c>
+      <c r="BA222">
+        <v>4</v>
+      </c>
+      <c r="BB222">
+        <v>9</v>
+      </c>
+      <c r="BC222">
+        <v>13</v>
+      </c>
+      <c r="BD222">
+        <v>2.33</v>
+      </c>
+      <c r="BE222">
+        <v>6.75</v>
+      </c>
+      <c r="BF222">
         <v>1.73</v>
       </c>
-      <c r="AK222">
-        <v>1.08</v>
-      </c>
-      <c r="AL222">
-        <v>1.16</v>
-      </c>
-      <c r="AM222">
-        <v>3.1</v>
-      </c>
-      <c r="AN222">
-        <v>2.08</v>
-      </c>
-      <c r="AO222">
-        <v>1.15</v>
-      </c>
-      <c r="AP222">
-        <v>2.2</v>
-      </c>
-      <c r="AQ222">
-        <v>1</v>
-      </c>
-      <c r="AR222">
-        <v>1.82</v>
-      </c>
-      <c r="AS222">
+      <c r="BG222">
         <v>1.24</v>
       </c>
-      <c r="AT222">
-        <v>3.06</v>
-      </c>
-      <c r="AU222">
-        <v>14</v>
-      </c>
-      <c r="AV222">
-        <v>3</v>
-      </c>
-      <c r="AW222">
-        <v>7</v>
-      </c>
-      <c r="AX222">
-        <v>2</v>
-      </c>
-      <c r="AY222">
-        <v>25</v>
-      </c>
-      <c r="AZ222">
-        <v>5</v>
-      </c>
-      <c r="BA222">
-        <v>2</v>
-      </c>
-      <c r="BB222">
-        <v>5</v>
-      </c>
-      <c r="BC222">
-        <v>7</v>
-      </c>
-      <c r="BD222">
-        <v>1.27</v>
-      </c>
-      <c r="BE222">
-        <v>8</v>
-      </c>
-      <c r="BF222">
-        <v>3.95</v>
-      </c>
-      <c r="BG222">
-        <v>1.3</v>
-      </c>
       <c r="BH222">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="BI222">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BJ222">
-        <v>2.33</v>
+        <v>2.65</v>
       </c>
       <c r="BK222">
-        <v>1.83</v>
+        <v>1.68</v>
       </c>
       <c r="BL222">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="BM222">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="BN222">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="BO222">
-        <v>2.9</v>
+        <v>2.55</v>
       </c>
       <c r="BP222">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="223" spans="1:68">
@@ -47174,7 +47171,7 @@
         <v>222</v>
       </c>
       <c r="B223">
-        <v>7453637</v>
+        <v>7453636</v>
       </c>
       <c r="C223" t="s">
         <v>68</v>
@@ -47183,196 +47180,196 @@
         <v>69</v>
       </c>
       <c r="E223" s="2">
-        <v>45718.5</v>
+        <v>45718.60416666666</v>
       </c>
       <c r="F223">
         <v>28</v>
       </c>
       <c r="G223" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="H223" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="I223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J223">
         <v>0</v>
       </c>
       <c r="K223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M223">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N223">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O223" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="P223" t="s">
-        <v>87</v>
+        <v>344</v>
       </c>
       <c r="Q223">
         <v>4.33</v>
       </c>
       <c r="R223">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S223">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="T223">
+        <v>1.44</v>
+      </c>
+      <c r="U223">
+        <v>2.63</v>
+      </c>
+      <c r="V223">
+        <v>3.25</v>
+      </c>
+      <c r="W223">
         <v>1.33</v>
       </c>
-      <c r="U223">
-        <v>3.25</v>
-      </c>
-      <c r="V223">
-        <v>2.63</v>
-      </c>
-      <c r="W223">
-        <v>1.44</v>
-      </c>
       <c r="X223">
-        <v>6.5</v>
+        <v>9</v>
       </c>
       <c r="Y223">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Z223">
-        <v>3.09</v>
+        <v>3.95</v>
       </c>
       <c r="AA223">
-        <v>3.39</v>
+        <v>3.47</v>
       </c>
       <c r="AB223">
-        <v>2.21</v>
+        <v>1.89</v>
       </c>
       <c r="AC223">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="AD223">
-        <v>13</v>
+        <v>8.91</v>
       </c>
       <c r="AE223">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AF223">
-        <v>3.89</v>
+        <v>3.14</v>
       </c>
       <c r="AG223">
+        <v>1.91</v>
+      </c>
+      <c r="AH223">
+        <v>1.83</v>
+      </c>
+      <c r="AI223">
+        <v>1.95</v>
+      </c>
+      <c r="AJ223">
         <v>1.8</v>
       </c>
-      <c r="AH223">
-        <v>1.94</v>
-      </c>
-      <c r="AI223">
+      <c r="AK223">
+        <v>1.8</v>
+      </c>
+      <c r="AL223">
+        <v>1.3</v>
+      </c>
+      <c r="AM223">
+        <v>1.26</v>
+      </c>
+      <c r="AN223">
+        <v>1.85</v>
+      </c>
+      <c r="AO223">
+        <v>1.62</v>
+      </c>
+      <c r="AP223">
         <v>1.67</v>
       </c>
-      <c r="AJ223">
-        <v>2.1</v>
-      </c>
-      <c r="AK223">
-        <v>1.87</v>
-      </c>
-      <c r="AL223">
-        <v>1.27</v>
-      </c>
-      <c r="AM223">
-        <v>1.25</v>
-      </c>
-      <c r="AN223">
-        <v>1</v>
-      </c>
-      <c r="AO223">
-        <v>0.92</v>
-      </c>
-      <c r="AP223">
-        <v>1.07</v>
-      </c>
       <c r="AQ223">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AR223">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AS223">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AT223">
-        <v>2.76</v>
+        <v>2.57</v>
       </c>
       <c r="AU223">
         <v>5</v>
       </c>
       <c r="AV223">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AW223">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AX223">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="AY223">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ223">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA223">
+        <v>3</v>
+      </c>
+      <c r="BB223">
         <v>4</v>
       </c>
-      <c r="BB223">
-        <v>9</v>
-      </c>
       <c r="BC223">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BD223">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="BE223">
         <v>6.75</v>
       </c>
       <c r="BF223">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="BG223">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="BH223">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="BI223">
-        <v>1.42</v>
+        <v>1.58</v>
       </c>
       <c r="BJ223">
-        <v>2.65</v>
+        <v>2.18</v>
       </c>
       <c r="BK223">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="BL223">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="BM223">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="BN223">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="BO223">
-        <v>2.55</v>
+        <v>3.2</v>
       </c>
       <c r="BP223">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="224" spans="1:68">
@@ -47380,7 +47377,7 @@
         <v>223</v>
       </c>
       <c r="B224">
-        <v>7453636</v>
+        <v>7453639</v>
       </c>
       <c r="C224" t="s">
         <v>68</v>
@@ -47389,16 +47386,16 @@
         <v>69</v>
       </c>
       <c r="E224" s="2">
-        <v>45718.60416666666</v>
+        <v>45718.63541666666</v>
       </c>
       <c r="F224">
         <v>28</v>
       </c>
       <c r="G224" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="H224" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I224">
         <v>0</v>
@@ -47413,172 +47410,172 @@
         <v>0</v>
       </c>
       <c r="M224">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N224">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O224" t="s">
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>345</v>
+        <v>87</v>
       </c>
       <c r="Q224">
-        <v>4.33</v>
+        <v>3</v>
       </c>
       <c r="R224">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S224">
+        <v>3.2</v>
+      </c>
+      <c r="T224">
+        <v>1.3</v>
+      </c>
+      <c r="U224">
+        <v>3.4</v>
+      </c>
+      <c r="V224">
+        <v>2.5</v>
+      </c>
+      <c r="W224">
+        <v>1.5</v>
+      </c>
+      <c r="X224">
+        <v>6</v>
+      </c>
+      <c r="Y224">
+        <v>1.13</v>
+      </c>
+      <c r="Z224">
+        <v>2.46</v>
+      </c>
+      <c r="AA224">
+        <v>3.53</v>
+      </c>
+      <c r="AB224">
         <v>2.63</v>
       </c>
-      <c r="T224">
-        <v>1.44</v>
-      </c>
-      <c r="U224">
-        <v>2.63</v>
-      </c>
-      <c r="V224">
-        <v>3.25</v>
-      </c>
-      <c r="W224">
-        <v>1.33</v>
-      </c>
-      <c r="X224">
-        <v>9</v>
-      </c>
-      <c r="Y224">
-        <v>1.07</v>
-      </c>
-      <c r="Z224">
-        <v>3.95</v>
-      </c>
-      <c r="AA224">
-        <v>3.47</v>
-      </c>
-      <c r="AB224">
-        <v>1.89</v>
-      </c>
       <c r="AC224">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD224">
-        <v>8.91</v>
+        <v>15</v>
       </c>
       <c r="AE224">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="AF224">
-        <v>3.14</v>
+        <v>4.45</v>
       </c>
       <c r="AG224">
-        <v>1.91</v>
+        <v>1.61</v>
       </c>
       <c r="AH224">
-        <v>1.83</v>
+        <v>2.15</v>
       </c>
       <c r="AI224">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="AJ224">
-        <v>1.8</v>
+        <v>2.38</v>
       </c>
       <c r="AK224">
-        <v>1.8</v>
+        <v>1.46</v>
       </c>
       <c r="AL224">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AM224">
-        <v>1.26</v>
+        <v>1.52</v>
       </c>
       <c r="AN224">
         <v>1.85</v>
       </c>
       <c r="AO224">
-        <v>1.62</v>
+        <v>0.85</v>
       </c>
       <c r="AP224">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AQ224">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AR224">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AS224">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AT224">
-        <v>2.57</v>
+        <v>2.86</v>
       </c>
       <c r="AU224">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="AV224">
         <v>4</v>
       </c>
       <c r="AW224">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX224">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="AY224">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ224">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="BA224">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BB224">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="BC224">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="BD224">
-        <v>2.4</v>
+        <v>1.94</v>
       </c>
       <c r="BE224">
         <v>6.75</v>
       </c>
       <c r="BF224">
-        <v>1.68</v>
+        <v>2.05</v>
       </c>
       <c r="BG224">
-        <v>1.34</v>
+        <v>1.2</v>
       </c>
       <c r="BH224">
+        <v>3.95</v>
+      </c>
+      <c r="BI224">
+        <v>1.35</v>
+      </c>
+      <c r="BJ224">
         <v>2.9</v>
       </c>
-      <c r="BI224">
+      <c r="BK224">
         <v>1.58</v>
       </c>
-      <c r="BJ224">
+      <c r="BL224">
         <v>2.18</v>
       </c>
-      <c r="BK224">
-        <v>1.96</v>
-      </c>
-      <c r="BL224">
-        <v>1.74</v>
-      </c>
       <c r="BM224">
-        <v>2.48</v>
+        <v>1.93</v>
       </c>
       <c r="BN224">
-        <v>1.47</v>
+        <v>1.77</v>
       </c>
       <c r="BO224">
-        <v>3.2</v>
+        <v>2.4</v>
       </c>
       <c r="BP224">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="225" spans="1:68">
@@ -47586,7 +47583,7 @@
         <v>224</v>
       </c>
       <c r="B225">
-        <v>7453639</v>
+        <v>7453646</v>
       </c>
       <c r="C225" t="s">
         <v>68</v>
@@ -47595,196 +47592,196 @@
         <v>69</v>
       </c>
       <c r="E225" s="2">
-        <v>45718.63541666666</v>
+        <v>45723.69791666666</v>
       </c>
       <c r="F225">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G225" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H225" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="I225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J225">
         <v>0</v>
       </c>
       <c r="K225">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L225">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M225">
         <v>0</v>
       </c>
       <c r="N225">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O225" t="s">
-        <v>87</v>
+        <v>243</v>
       </c>
       <c r="P225" t="s">
         <v>87</v>
       </c>
       <c r="Q225">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R225">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="S225">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="T225">
         <v>1.3</v>
       </c>
       <c r="U225">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V225">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="W225">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X225">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="Y225">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="Z225">
-        <v>2.46</v>
+        <v>1.62</v>
       </c>
       <c r="AA225">
-        <v>3.53</v>
+        <v>4.2</v>
       </c>
       <c r="AB225">
-        <v>2.63</v>
+        <v>4.7</v>
       </c>
       <c r="AC225">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD225">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AE225">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AF225">
-        <v>4.45</v>
+        <v>4.33</v>
       </c>
       <c r="AG225">
         <v>1.61</v>
       </c>
       <c r="AH225">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AI225">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AJ225">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AK225">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AL225">
-        <v>1.27</v>
+        <v>1.18</v>
       </c>
       <c r="AM225">
+        <v>2.3</v>
+      </c>
+      <c r="AN225">
+        <v>1.36</v>
+      </c>
+      <c r="AO225">
+        <v>0.14</v>
+      </c>
+      <c r="AP225">
+        <v>1.47</v>
+      </c>
+      <c r="AQ225">
+        <v>0.13</v>
+      </c>
+      <c r="AR225">
         <v>1.52</v>
       </c>
-      <c r="AN225">
-        <v>1.85</v>
-      </c>
-      <c r="AO225">
-        <v>0.85</v>
-      </c>
-      <c r="AP225">
-        <v>1.87</v>
-      </c>
-      <c r="AQ225">
-        <v>1</v>
-      </c>
-      <c r="AR225">
-        <v>1.31</v>
-      </c>
       <c r="AS225">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="AT225">
-        <v>2.86</v>
+        <v>2.66</v>
       </c>
       <c r="AU225">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="AV225">
         <v>4</v>
       </c>
       <c r="AW225">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AX225">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AY225">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AZ225">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="BA225">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BB225">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BC225">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD225">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="BE225">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="BF225">
-        <v>2.05</v>
+        <v>3.4</v>
       </c>
       <c r="BG225">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="BH225">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="BI225">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BJ225">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="BK225">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="BL225">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="BM225">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="BN225">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="BO225">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="BP225">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="226" spans="1:68">
@@ -47792,7 +47789,7 @@
         <v>225</v>
       </c>
       <c r="B226">
-        <v>7453646</v>
+        <v>7453644</v>
       </c>
       <c r="C226" t="s">
         <v>68</v>
@@ -47801,16 +47798,16 @@
         <v>69</v>
       </c>
       <c r="E226" s="2">
-        <v>45723.69791666666</v>
+        <v>45724.5</v>
       </c>
       <c r="F226">
         <v>29</v>
       </c>
       <c r="G226" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H226" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="I226">
         <v>1</v>
@@ -47831,100 +47828,100 @@
         <v>2</v>
       </c>
       <c r="O226" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P226" t="s">
         <v>87</v>
       </c>
       <c r="Q226">
-        <v>2</v>
+        <v>2.75</v>
       </c>
       <c r="R226">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="S226">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="T226">
+        <v>1.37</v>
+      </c>
+      <c r="U226">
+        <v>2.85</v>
+      </c>
+      <c r="V226">
+        <v>2.7</v>
+      </c>
+      <c r="W226">
+        <v>1.4</v>
+      </c>
+      <c r="X226">
+        <v>6.75</v>
+      </c>
+      <c r="Y226">
+        <v>1.09</v>
+      </c>
+      <c r="Z226">
+        <v>2.71</v>
+      </c>
+      <c r="AA226">
+        <v>3.23</v>
+      </c>
+      <c r="AB226">
+        <v>2.55</v>
+      </c>
+      <c r="AC226">
+        <v>1.05</v>
+      </c>
+      <c r="AD226">
+        <v>9</v>
+      </c>
+      <c r="AE226">
         <v>1.3</v>
       </c>
-      <c r="U226">
-        <v>3.25</v>
-      </c>
-      <c r="V226">
-        <v>2.35</v>
-      </c>
-      <c r="W226">
-        <v>1.53</v>
-      </c>
-      <c r="X226">
-        <v>5.85</v>
-      </c>
-      <c r="Y226">
-        <v>1.07</v>
-      </c>
-      <c r="Z226">
+      <c r="AF226">
+        <v>3.45</v>
+      </c>
+      <c r="AG226">
+        <v>1.89</v>
+      </c>
+      <c r="AH226">
+        <v>1.85</v>
+      </c>
+      <c r="AI226">
+        <v>1.75</v>
+      </c>
+      <c r="AJ226">
+        <v>1.93</v>
+      </c>
+      <c r="AK226">
+        <v>1.36</v>
+      </c>
+      <c r="AL226">
+        <v>1.29</v>
+      </c>
+      <c r="AM226">
         <v>1.62</v>
       </c>
-      <c r="AA226">
-        <v>4.2</v>
-      </c>
-      <c r="AB226">
-        <v>4.7</v>
-      </c>
-      <c r="AC226">
-        <v>1.04</v>
-      </c>
-      <c r="AD226">
-        <v>10</v>
-      </c>
-      <c r="AE226">
-        <v>1.2</v>
-      </c>
-      <c r="AF226">
-        <v>4.33</v>
-      </c>
-      <c r="AG226">
-        <v>1.61</v>
-      </c>
-      <c r="AH226">
-        <v>2.2</v>
-      </c>
-      <c r="AI226">
-        <v>1.65</v>
-      </c>
-      <c r="AJ226">
-        <v>2.05</v>
-      </c>
-      <c r="AK226">
-        <v>1.15</v>
-      </c>
-      <c r="AL226">
-        <v>1.18</v>
-      </c>
-      <c r="AM226">
-        <v>2.3</v>
-      </c>
       <c r="AN226">
+        <v>1</v>
+      </c>
+      <c r="AO226">
+        <v>0.64</v>
+      </c>
+      <c r="AP226">
+        <v>1.13</v>
+      </c>
+      <c r="AQ226">
+        <v>0.6</v>
+      </c>
+      <c r="AR226">
         <v>1.36</v>
       </c>
-      <c r="AO226">
-        <v>0.14</v>
-      </c>
-      <c r="AP226">
-        <v>1.47</v>
-      </c>
-      <c r="AQ226">
-        <v>0.13</v>
-      </c>
-      <c r="AR226">
-        <v>1.52</v>
-      </c>
       <c r="AS226">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AT226">
-        <v>2.66</v>
+        <v>2.55</v>
       </c>
       <c r="AU226">
         <v>7</v>
@@ -47933,64 +47930,64 @@
         <v>4</v>
       </c>
       <c r="AW226">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AX226">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY226">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AZ226">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA226">
+        <v>5</v>
+      </c>
+      <c r="BB226">
         <v>4</v>
       </c>
-      <c r="BB226">
-        <v>8</v>
-      </c>
       <c r="BC226">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BD226">
-        <v>1.36</v>
+        <v>1.71</v>
       </c>
       <c r="BE226">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF226">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="BG226">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="BH226">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BI226">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="BJ226">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="BK226">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="BL226">
-        <v>2.12</v>
+        <v>2.02</v>
       </c>
       <c r="BM226">
-        <v>1.98</v>
+        <v>2.07</v>
       </c>
       <c r="BN226">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="BO226">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="BP226">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="227" spans="1:68">
@@ -47998,7 +47995,7 @@
         <v>226</v>
       </c>
       <c r="B227">
-        <v>7453644</v>
+        <v>7453648</v>
       </c>
       <c r="C227" t="s">
         <v>68</v>
@@ -48007,82 +48004,82 @@
         <v>69</v>
       </c>
       <c r="E227" s="2">
-        <v>45724.5</v>
+        <v>45724.59375</v>
       </c>
       <c r="F227">
         <v>29</v>
       </c>
       <c r="G227" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H227" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="I227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K227">
         <v>1</v>
       </c>
       <c r="L227">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N227">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O227" t="s">
-        <v>244</v>
+        <v>87</v>
       </c>
       <c r="P227" t="s">
-        <v>87</v>
+        <v>209</v>
       </c>
       <c r="Q227">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="R227">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="S227">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T227">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="U227">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="V227">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="W227">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="X227">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="Y227">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Z227">
-        <v>2.71</v>
+        <v>2.2</v>
       </c>
       <c r="AA227">
-        <v>3.23</v>
+        <v>3.36</v>
       </c>
       <c r="AB227">
-        <v>2.55</v>
+        <v>3.14</v>
       </c>
       <c r="AC227">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD227">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="AE227">
         <v>1.3</v>
@@ -48091,94 +48088,94 @@
         <v>3.45</v>
       </c>
       <c r="AG227">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="AH227">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AI227">
-        <v>1.75</v>
+        <v>1.66</v>
       </c>
       <c r="AJ227">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AK227">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AL227">
         <v>1.29</v>
       </c>
       <c r="AM227">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AN227">
-        <v>1</v>
+        <v>1.57</v>
       </c>
       <c r="AO227">
-        <v>0.64</v>
+        <v>0.86</v>
       </c>
       <c r="AP227">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AQ227">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="AR227">
-        <v>1.36</v>
+        <v>1.7</v>
       </c>
       <c r="AS227">
-        <v>1.19</v>
+        <v>1.52</v>
       </c>
       <c r="AT227">
-        <v>2.55</v>
+        <v>3.22</v>
       </c>
       <c r="AU227">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="AV227">
+        <v>6</v>
+      </c>
+      <c r="AW227">
+        <v>9</v>
+      </c>
+      <c r="AX227">
         <v>4</v>
       </c>
-      <c r="AW227">
-        <v>16</v>
-      </c>
-      <c r="AX227">
+      <c r="AY227">
+        <v>14</v>
+      </c>
+      <c r="AZ227">
+        <v>10</v>
+      </c>
+      <c r="BA227">
         <v>6</v>
       </c>
-      <c r="AY227">
-        <v>26</v>
-      </c>
-      <c r="AZ227">
-        <v>11</v>
-      </c>
-      <c r="BA227">
-        <v>5</v>
-      </c>
       <c r="BB227">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC227">
         <v>9</v>
       </c>
       <c r="BD227">
-        <v>1.71</v>
+        <v>1.77</v>
       </c>
       <c r="BE227">
         <v>6.75</v>
       </c>
       <c r="BF227">
-        <v>2.35</v>
+        <v>2.23</v>
       </c>
       <c r="BG227">
         <v>1.24</v>
       </c>
       <c r="BH227">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="BI227">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="BJ227">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="BK227">
         <v>1.7</v>
@@ -48190,13 +48187,13 @@
         <v>2.07</v>
       </c>
       <c r="BN227">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="BO227">
-        <v>2.6</v>
+        <v>2.65</v>
       </c>
       <c r="BP227">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="228" spans="1:68">
@@ -48204,7 +48201,7 @@
         <v>227</v>
       </c>
       <c r="B228">
-        <v>7453648</v>
+        <v>7453649</v>
       </c>
       <c r="C228" t="s">
         <v>68</v>
@@ -48213,25 +48210,25 @@
         <v>69</v>
       </c>
       <c r="E228" s="2">
-        <v>45724.59375</v>
+        <v>45724.69791666666</v>
       </c>
       <c r="F228">
         <v>29</v>
       </c>
       <c r="G228" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H228" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I228">
         <v>0</v>
       </c>
       <c r="J228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L228">
         <v>0</v>
@@ -48246,163 +48243,163 @@
         <v>87</v>
       </c>
       <c r="P228" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="Q228">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="R228">
+        <v>2.25</v>
+      </c>
+      <c r="S228">
+        <v>2.3</v>
+      </c>
+      <c r="T228">
+        <v>1.3</v>
+      </c>
+      <c r="U228">
+        <v>3.2</v>
+      </c>
+      <c r="V228">
+        <v>2.37</v>
+      </c>
+      <c r="W228">
+        <v>1.51</v>
+      </c>
+      <c r="X228">
+        <v>5.5</v>
+      </c>
+      <c r="Y228">
+        <v>1.12</v>
+      </c>
+      <c r="Z228">
+        <v>4.1</v>
+      </c>
+      <c r="AA228">
+        <v>3.87</v>
+      </c>
+      <c r="AB228">
+        <v>1.76</v>
+      </c>
+      <c r="AC228">
+        <v>1.04</v>
+      </c>
+      <c r="AD228">
+        <v>10</v>
+      </c>
+      <c r="AE228">
+        <v>1.22</v>
+      </c>
+      <c r="AF228">
+        <v>4.2</v>
+      </c>
+      <c r="AG228">
+        <v>1.85</v>
+      </c>
+      <c r="AH228">
+        <v>1.85</v>
+      </c>
+      <c r="AI228">
+        <v>1.62</v>
+      </c>
+      <c r="AJ228">
         <v>2.15</v>
       </c>
-      <c r="S228">
-        <v>3.5</v>
-      </c>
-      <c r="T228">
-        <v>1.35</v>
-      </c>
-      <c r="U228">
-        <v>2.9</v>
-      </c>
-      <c r="V228">
-        <v>2.6</v>
-      </c>
-      <c r="W228">
-        <v>1.43</v>
-      </c>
-      <c r="X228">
-        <v>6.5</v>
-      </c>
-      <c r="Y228">
-        <v>1.1</v>
-      </c>
-      <c r="Z228">
-        <v>2.2</v>
-      </c>
-      <c r="AA228">
-        <v>3.36</v>
-      </c>
-      <c r="AB228">
-        <v>3.14</v>
-      </c>
-      <c r="AC228">
-        <v>1.06</v>
-      </c>
-      <c r="AD228">
-        <v>8.5</v>
-      </c>
-      <c r="AE228">
-        <v>1.3</v>
-      </c>
-      <c r="AF228">
-        <v>3.45</v>
-      </c>
-      <c r="AG228">
-        <v>1.79</v>
-      </c>
-      <c r="AH228">
-        <v>1.95</v>
-      </c>
-      <c r="AI228">
-        <v>1.66</v>
-      </c>
-      <c r="AJ228">
-        <v>2.05</v>
-      </c>
       <c r="AK228">
-        <v>1.35</v>
+        <v>1.98</v>
       </c>
       <c r="AL228">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AM228">
-        <v>1.65</v>
+        <v>1.23</v>
       </c>
       <c r="AN228">
-        <v>1.57</v>
+        <v>1.21</v>
       </c>
       <c r="AO228">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="AP228">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AQ228">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="AR228">
-        <v>1.7</v>
+        <v>1.11</v>
       </c>
       <c r="AS228">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="AT228">
-        <v>3.22</v>
+        <v>2.78</v>
       </c>
       <c r="AU228">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AV228">
         <v>6</v>
       </c>
       <c r="AW228">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AX228">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="AY228">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AZ228">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="BA228">
+        <v>2</v>
+      </c>
+      <c r="BB228">
         <v>6</v>
       </c>
-      <c r="BB228">
-        <v>3</v>
-      </c>
       <c r="BC228">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD228">
-        <v>1.77</v>
+        <v>2.55</v>
       </c>
       <c r="BE228">
-        <v>6.75</v>
+        <v>6.4</v>
       </c>
       <c r="BF228">
-        <v>2.23</v>
+        <v>1.65</v>
       </c>
       <c r="BG228">
-        <v>1.24</v>
+        <v>1.38</v>
       </c>
       <c r="BH228">
-        <v>3.55</v>
+        <v>2.8</v>
       </c>
       <c r="BI228">
+        <v>1.65</v>
+      </c>
+      <c r="BJ228">
+        <v>2.08</v>
+      </c>
+      <c r="BK228">
+        <v>2.05</v>
+      </c>
+      <c r="BL228">
+        <v>1.68</v>
+      </c>
+      <c r="BM228">
+        <v>2.55</v>
+      </c>
+      <c r="BN228">
         <v>1.43</v>
       </c>
-      <c r="BJ228">
-        <v>2.55</v>
-      </c>
-      <c r="BK228">
-        <v>1.7</v>
-      </c>
-      <c r="BL228">
-        <v>2.02</v>
-      </c>
-      <c r="BM228">
-        <v>2.07</v>
-      </c>
-      <c r="BN228">
-        <v>1.66</v>
-      </c>
       <c r="BO228">
-        <v>2.65</v>
+        <v>3.4</v>
       </c>
       <c r="BP228">
-        <v>1.42</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="229" spans="1:68">
@@ -48410,7 +48407,7 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>7453649</v>
+        <v>7453645</v>
       </c>
       <c r="C229" t="s">
         <v>68</v>
@@ -48419,196 +48416,196 @@
         <v>69</v>
       </c>
       <c r="E229" s="2">
-        <v>45724.69791666666</v>
+        <v>45725.39583333334</v>
       </c>
       <c r="F229">
         <v>29</v>
       </c>
       <c r="G229" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="H229" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="I229">
         <v>0</v>
       </c>
       <c r="J229">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K229">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L229">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M229">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N229">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O229" t="s">
-        <v>87</v>
+        <v>174</v>
       </c>
       <c r="P229" t="s">
-        <v>201</v>
+        <v>345</v>
       </c>
       <c r="Q229">
-        <v>4.1</v>
+        <v>4.75</v>
       </c>
       <c r="R229">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S229">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T229">
+        <v>1.4</v>
+      </c>
+      <c r="U229">
+        <v>2.75</v>
+      </c>
+      <c r="V229">
+        <v>2.75</v>
+      </c>
+      <c r="W229">
+        <v>1.4</v>
+      </c>
+      <c r="X229">
+        <v>8</v>
+      </c>
+      <c r="Y229">
+        <v>1.08</v>
+      </c>
+      <c r="Z229">
+        <v>4.2</v>
+      </c>
+      <c r="AA229">
+        <v>3.55</v>
+      </c>
+      <c r="AB229">
+        <v>1.82</v>
+      </c>
+      <c r="AC229">
+        <v>1.05</v>
+      </c>
+      <c r="AD229">
+        <v>9</v>
+      </c>
+      <c r="AE229">
         <v>1.3</v>
       </c>
-      <c r="U229">
-        <v>3.2</v>
-      </c>
-      <c r="V229">
-        <v>2.37</v>
-      </c>
-      <c r="W229">
-        <v>1.51</v>
-      </c>
-      <c r="X229">
-        <v>5.5</v>
-      </c>
-      <c r="Y229">
-        <v>1.12</v>
-      </c>
-      <c r="Z229">
-        <v>4.1</v>
-      </c>
-      <c r="AA229">
-        <v>3.87</v>
-      </c>
-      <c r="AB229">
-        <v>1.76</v>
-      </c>
-      <c r="AC229">
-        <v>1.04</v>
-      </c>
-      <c r="AD229">
-        <v>10</v>
-      </c>
-      <c r="AE229">
+      <c r="AF229">
+        <v>3.4</v>
+      </c>
+      <c r="AG229">
+        <v>1.92</v>
+      </c>
+      <c r="AH229">
+        <v>1.82</v>
+      </c>
+      <c r="AI229">
+        <v>1.8</v>
+      </c>
+      <c r="AJ229">
+        <v>1.95</v>
+      </c>
+      <c r="AK229">
+        <v>1.95</v>
+      </c>
+      <c r="AL229">
+        <v>1.27</v>
+      </c>
+      <c r="AM229">
         <v>1.22</v>
       </c>
-      <c r="AF229">
-        <v>4.2</v>
-      </c>
-      <c r="AG229">
-        <v>1.85</v>
-      </c>
-      <c r="AH229">
-        <v>1.85</v>
-      </c>
-      <c r="AI229">
-        <v>1.62</v>
-      </c>
-      <c r="AJ229">
-        <v>2.15</v>
-      </c>
-      <c r="AK229">
-        <v>1.98</v>
-      </c>
-      <c r="AL229">
-        <v>1.24</v>
-      </c>
-      <c r="AM229">
-        <v>1.23</v>
-      </c>
       <c r="AN229">
-        <v>1.21</v>
+        <v>1.5</v>
       </c>
       <c r="AO229">
+        <v>1.69</v>
+      </c>
+      <c r="AP229">
+        <v>1.4</v>
+      </c>
+      <c r="AQ229">
+        <v>1.79</v>
+      </c>
+      <c r="AR229">
+        <v>1.79</v>
+      </c>
+      <c r="AS229">
         <v>1.71</v>
       </c>
-      <c r="AP229">
-        <v>1.13</v>
-      </c>
-      <c r="AQ229">
-        <v>1.8</v>
-      </c>
-      <c r="AR229">
-        <v>1.11</v>
-      </c>
-      <c r="AS229">
-        <v>1.67</v>
-      </c>
       <c r="AT229">
-        <v>2.78</v>
+        <v>3.5</v>
       </c>
       <c r="AU229">
         <v>5</v>
       </c>
       <c r="AV229">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW229">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AX229">
         <v>11</v>
       </c>
       <c r="AY229">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AZ229">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="BA229">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="BB229">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BC229">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="BD229">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="BE229">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="BF229">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="BG229">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BH229">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BI229">
-        <v>1.65</v>
+        <v>1.58</v>
       </c>
       <c r="BJ229">
-        <v>2.08</v>
+        <v>2.18</v>
       </c>
       <c r="BK229">
-        <v>2.05</v>
+        <v>1.96</v>
       </c>
       <c r="BL229">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="BM229">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="BN229">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BO229">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="BP229">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="230" spans="1:68">
@@ -48616,7 +48613,7 @@
         <v>229</v>
       </c>
       <c r="B230">
-        <v>7453645</v>
+        <v>7453647</v>
       </c>
       <c r="C230" t="s">
         <v>68</v>
@@ -48625,196 +48622,196 @@
         <v>69</v>
       </c>
       <c r="E230" s="2">
-        <v>45725.39583333334</v>
+        <v>45725.5</v>
       </c>
       <c r="F230">
         <v>29</v>
       </c>
       <c r="G230" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H230" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="I230">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J230">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K230">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L230">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M230">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N230">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O230" t="s">
-        <v>174</v>
+        <v>245</v>
       </c>
       <c r="P230" t="s">
-        <v>346</v>
+        <v>87</v>
       </c>
       <c r="Q230">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="R230">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="S230">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="T230">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="U230">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="V230">
-        <v>2.75</v>
+        <v>2.5</v>
       </c>
       <c r="W230">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="X230">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="Y230">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Z230">
-        <v>4.2</v>
+        <v>2.97</v>
       </c>
       <c r="AA230">
-        <v>3.55</v>
+        <v>3.57</v>
       </c>
       <c r="AB230">
-        <v>1.82</v>
+        <v>2.21</v>
       </c>
       <c r="AC230">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD230">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE230">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF230">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="AG230">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AH230">
-        <v>1.82</v>
+        <v>2.15</v>
       </c>
       <c r="AI230">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ230">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AK230">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AL230">
         <v>1.27</v>
       </c>
       <c r="AM230">
-        <v>1.22</v>
+        <v>1.37</v>
       </c>
       <c r="AN230">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AO230">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="AP230">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="AQ230">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AR230">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="AS230">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="AT230">
-        <v>3.46</v>
+        <v>3.22</v>
       </c>
       <c r="AU230">
         <v>5</v>
       </c>
       <c r="AV230">
+        <v>3</v>
+      </c>
+      <c r="AW230">
         <v>5</v>
       </c>
-      <c r="AW230">
-        <v>14</v>
-      </c>
       <c r="AX230">
+        <v>15</v>
+      </c>
+      <c r="AY230">
         <v>11</v>
-      </c>
-      <c r="AY230">
-        <v>22</v>
       </c>
       <c r="AZ230">
         <v>18</v>
       </c>
       <c r="BA230">
+        <v>7</v>
+      </c>
+      <c r="BB230">
         <v>9</v>
       </c>
-      <c r="BB230">
-        <v>4</v>
-      </c>
       <c r="BC230">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="BD230">
-        <v>2.7</v>
+        <v>1.98</v>
       </c>
       <c r="BE230">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF230">
-        <v>1.56</v>
+        <v>1.97</v>
       </c>
       <c r="BG230">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="BH230">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="BI230">
-        <v>1.58</v>
+        <v>1.43</v>
       </c>
       <c r="BJ230">
-        <v>2.18</v>
+        <v>2.6</v>
       </c>
       <c r="BK230">
-        <v>1.96</v>
+        <v>1.68</v>
       </c>
       <c r="BL230">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="BM230">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="BN230">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="BO230">
-        <v>3.25</v>
+        <v>2.55</v>
       </c>
       <c r="BP230">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="231" spans="1:68">
@@ -48822,7 +48819,7 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>7453647</v>
+        <v>7453643</v>
       </c>
       <c r="C231" t="s">
         <v>68</v>
@@ -48831,49 +48828,49 @@
         <v>69</v>
       </c>
       <c r="E231" s="2">
-        <v>45725.5</v>
+        <v>45725.60416666666</v>
       </c>
       <c r="F231">
         <v>29</v>
       </c>
       <c r="G231" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="H231" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="I231">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J231">
         <v>0</v>
       </c>
       <c r="K231">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L231">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N231">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O231" t="s">
-        <v>245</v>
+        <v>87</v>
       </c>
       <c r="P231" t="s">
-        <v>87</v>
+        <v>346</v>
       </c>
       <c r="Q231">
+        <v>2.88</v>
+      </c>
+      <c r="R231">
+        <v>2.25</v>
+      </c>
+      <c r="S231">
         <v>3.5</v>
-      </c>
-      <c r="R231">
-        <v>2.3</v>
-      </c>
-      <c r="S231">
-        <v>2.88</v>
       </c>
       <c r="T231">
         <v>1.33</v>
@@ -48882,25 +48879,25 @@
         <v>3.25</v>
       </c>
       <c r="V231">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="W231">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X231">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="Y231">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Z231">
-        <v>2.97</v>
+        <v>2.27</v>
       </c>
       <c r="AA231">
-        <v>3.57</v>
+        <v>3.36</v>
       </c>
       <c r="AB231">
-        <v>2.21</v>
+        <v>3.01</v>
       </c>
       <c r="AC231">
         <v>1.04</v>
@@ -48909,118 +48906,118 @@
         <v>10</v>
       </c>
       <c r="AE231">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF231">
-        <v>4.33</v>
+        <v>3.85</v>
       </c>
       <c r="AG231">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH231">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AI231">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AJ231">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AK231">
-        <v>1.65</v>
+        <v>1.39</v>
       </c>
       <c r="AL231">
         <v>1.27</v>
       </c>
       <c r="AM231">
-        <v>1.37</v>
+        <v>1.62</v>
       </c>
       <c r="AN231">
-        <v>1.36</v>
+        <v>1.93</v>
       </c>
       <c r="AO231">
+        <v>1.21</v>
+      </c>
+      <c r="AP231">
+        <v>1.8</v>
+      </c>
+      <c r="AQ231">
+        <v>1.33</v>
+      </c>
+      <c r="AR231">
+        <v>1.76</v>
+      </c>
+      <c r="AS231">
+        <v>1.31</v>
+      </c>
+      <c r="AT231">
+        <v>3.07</v>
+      </c>
+      <c r="AU231">
+        <v>7</v>
+      </c>
+      <c r="AV231">
+        <v>6</v>
+      </c>
+      <c r="AW231">
+        <v>6</v>
+      </c>
+      <c r="AX231">
+        <v>7</v>
+      </c>
+      <c r="AY231">
+        <v>14</v>
+      </c>
+      <c r="AZ231">
+        <v>16</v>
+      </c>
+      <c r="BA231">
+        <v>8</v>
+      </c>
+      <c r="BB231">
+        <v>4</v>
+      </c>
+      <c r="BC231">
+        <v>12</v>
+      </c>
+      <c r="BD231">
+        <v>1.66</v>
+      </c>
+      <c r="BE231">
+        <v>7</v>
+      </c>
+      <c r="BF231">
+        <v>2.43</v>
+      </c>
+      <c r="BG231">
+        <v>1.25</v>
+      </c>
+      <c r="BH231">
+        <v>3.45</v>
+      </c>
+      <c r="BI231">
+        <v>1.44</v>
+      </c>
+      <c r="BJ231">
+        <v>2.55</v>
+      </c>
+      <c r="BK231">
         <v>1.71</v>
       </c>
-      <c r="AP231">
-        <v>1.47</v>
-      </c>
-      <c r="AQ231">
-        <v>1.6</v>
-      </c>
-      <c r="AR231">
-        <v>1.88</v>
-      </c>
-      <c r="AS231">
-        <v>1.34</v>
-      </c>
-      <c r="AT231">
-        <v>3.22</v>
-      </c>
-      <c r="AU231">
-        <v>5</v>
-      </c>
-      <c r="AV231">
-        <v>3</v>
-      </c>
-      <c r="AW231">
-        <v>5</v>
-      </c>
-      <c r="AX231">
-        <v>15</v>
-      </c>
-      <c r="AY231">
-        <v>11</v>
-      </c>
-      <c r="AZ231">
-        <v>18</v>
-      </c>
-      <c r="BA231">
-        <v>7</v>
-      </c>
-      <c r="BB231">
-        <v>9</v>
-      </c>
-      <c r="BC231">
-        <v>16</v>
-      </c>
-      <c r="BD231">
-        <v>1.98</v>
-      </c>
-      <c r="BE231">
-        <v>6.75</v>
-      </c>
-      <c r="BF231">
-        <v>1.97</v>
-      </c>
-      <c r="BG231">
-        <v>1.24</v>
-      </c>
-      <c r="BH231">
-        <v>3.55</v>
-      </c>
-      <c r="BI231">
-        <v>1.43</v>
-      </c>
-      <c r="BJ231">
-        <v>2.6</v>
-      </c>
-      <c r="BK231">
-        <v>1.68</v>
-      </c>
       <c r="BL231">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BM231">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="BN231">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="BO231">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="BP231">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="232" spans="1:68">
@@ -49028,7 +49025,7 @@
         <v>231</v>
       </c>
       <c r="B232">
-        <v>7453643</v>
+        <v>7453642</v>
       </c>
       <c r="C232" t="s">
         <v>68</v>
@@ -49037,49 +49034,49 @@
         <v>69</v>
       </c>
       <c r="E232" s="2">
-        <v>45725.60416666666</v>
+        <v>45725.63541666666</v>
       </c>
       <c r="F232">
         <v>29</v>
       </c>
       <c r="G232" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H232" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="I232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J232">
         <v>0</v>
       </c>
       <c r="K232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L232">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N232">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O232" t="s">
+        <v>246</v>
+      </c>
+      <c r="P232" t="s">
         <v>87</v>
       </c>
-      <c r="P232" t="s">
-        <v>347</v>
-      </c>
       <c r="Q232">
-        <v>2.88</v>
+        <v>1.83</v>
       </c>
       <c r="R232">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S232">
-        <v>3.5</v>
+        <v>7.5</v>
       </c>
       <c r="T232">
         <v>1.33</v>
@@ -49088,37 +49085,37 @@
         <v>3.25</v>
       </c>
       <c r="V232">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="W232">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X232">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y232">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z232">
-        <v>2.27</v>
+        <v>1.33</v>
       </c>
       <c r="AA232">
-        <v>3.36</v>
+        <v>5.2</v>
       </c>
       <c r="AB232">
-        <v>3.01</v>
+        <v>8</v>
       </c>
       <c r="AC232">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD232">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE232">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF232">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AG232">
         <v>1.7</v>
@@ -49127,106 +49124,106 @@
         <v>2.05</v>
       </c>
       <c r="AI232">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AJ232">
+        <v>1.75</v>
+      </c>
+      <c r="AK232">
+        <v>1.09</v>
+      </c>
+      <c r="AL232">
+        <v>1.17</v>
+      </c>
+      <c r="AM232">
+        <v>2.95</v>
+      </c>
+      <c r="AN232">
+        <v>2.14</v>
+      </c>
+      <c r="AO232">
+        <v>1</v>
+      </c>
+      <c r="AP232">
         <v>2.2</v>
       </c>
-      <c r="AK232">
-        <v>1.39</v>
-      </c>
-      <c r="AL232">
-        <v>1.27</v>
-      </c>
-      <c r="AM232">
-        <v>1.62</v>
-      </c>
-      <c r="AN232">
-        <v>1.93</v>
-      </c>
-      <c r="AO232">
-        <v>1.21</v>
-      </c>
-      <c r="AP232">
-        <v>1.8</v>
-      </c>
       <c r="AQ232">
-        <v>1.33</v>
+        <v>0.93</v>
       </c>
       <c r="AR232">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AS232">
-        <v>1.31</v>
+        <v>1.07</v>
       </c>
       <c r="AT232">
-        <v>3.07</v>
+        <v>2.95</v>
       </c>
       <c r="AU232">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AV232">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AW232">
         <v>6</v>
       </c>
       <c r="AX232">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY232">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ232">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BA232">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="BB232">
         <v>4</v>
       </c>
       <c r="BC232">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="BD232">
-        <v>1.66</v>
+        <v>1.21</v>
       </c>
       <c r="BE232">
-        <v>7</v>
+        <v>8.5</v>
       </c>
       <c r="BF232">
-        <v>2.43</v>
+        <v>4.8</v>
       </c>
       <c r="BG232">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BH232">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BI232">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BJ232">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="BK232">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="BL232">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="BM232">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="BN232">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
       <c r="BO232">
-        <v>2.65</v>
+        <v>2.48</v>
       </c>
       <c r="BP232">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="233" spans="1:68">
@@ -49234,7 +49231,7 @@
         <v>232</v>
       </c>
       <c r="B233">
-        <v>7453642</v>
+        <v>7453652</v>
       </c>
       <c r="C233" t="s">
         <v>68</v>
@@ -49243,196 +49240,196 @@
         <v>69</v>
       </c>
       <c r="E233" s="2">
-        <v>45725.63541666666</v>
+        <v>45731.69791666666</v>
       </c>
       <c r="F233">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G233" t="s">
+        <v>74</v>
+      </c>
+      <c r="H233" t="s">
         <v>78</v>
       </c>
-      <c r="H233" t="s">
-        <v>84</v>
-      </c>
       <c r="I233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J233">
         <v>0</v>
       </c>
       <c r="K233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L233">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N233">
         <v>3</v>
       </c>
       <c r="O233" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="P233" t="s">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="Q233">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="R233">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S233">
-        <v>7.5</v>
+        <v>3.2</v>
       </c>
       <c r="T233">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U233">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="V233">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="W233">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X233">
+        <v>7</v>
+      </c>
+      <c r="Y233">
+        <v>1.1</v>
+      </c>
+      <c r="Z233">
+        <v>2.63</v>
+      </c>
+      <c r="AA233">
+        <v>3.23</v>
+      </c>
+      <c r="AB233">
+        <v>2.63</v>
+      </c>
+      <c r="AC233">
+        <v>1.05</v>
+      </c>
+      <c r="AD233">
+        <v>9.5</v>
+      </c>
+      <c r="AE233">
+        <v>1.25</v>
+      </c>
+      <c r="AF233">
+        <v>3.75</v>
+      </c>
+      <c r="AG233">
+        <v>1.85</v>
+      </c>
+      <c r="AH233">
+        <v>1.89</v>
+      </c>
+      <c r="AI233">
+        <v>1.62</v>
+      </c>
+      <c r="AJ233">
+        <v>2.2</v>
+      </c>
+      <c r="AK233">
+        <v>1.48</v>
+      </c>
+      <c r="AL233">
+        <v>1.25</v>
+      </c>
+      <c r="AM233">
+        <v>1.48</v>
+      </c>
+      <c r="AN233">
+        <v>2.71</v>
+      </c>
+      <c r="AO233">
+        <v>1.57</v>
+      </c>
+      <c r="AP233">
+        <v>2.73</v>
+      </c>
+      <c r="AQ233">
+        <v>1.47</v>
+      </c>
+      <c r="AR233">
+        <v>1.77</v>
+      </c>
+      <c r="AS233">
+        <v>1.43</v>
+      </c>
+      <c r="AT233">
+        <v>3.2</v>
+      </c>
+      <c r="AU233">
+        <v>8</v>
+      </c>
+      <c r="AV233">
+        <v>3</v>
+      </c>
+      <c r="AW233">
+        <v>10</v>
+      </c>
+      <c r="AX233">
         <v>6</v>
       </c>
-      <c r="Y233">
-        <v>1.13</v>
-      </c>
-      <c r="Z233">
-        <v>1.33</v>
-      </c>
-      <c r="AA233">
-        <v>5.2</v>
-      </c>
-      <c r="AB233">
-        <v>8</v>
-      </c>
-      <c r="AC233">
-        <v>1.03</v>
-      </c>
-      <c r="AD233">
-        <v>11</v>
-      </c>
-      <c r="AE233">
-        <v>1.2</v>
-      </c>
-      <c r="AF233">
-        <v>4.5</v>
-      </c>
-      <c r="AG233">
-        <v>1.7</v>
-      </c>
-      <c r="AH233">
-        <v>2.05</v>
-      </c>
-      <c r="AI233">
-        <v>2</v>
-      </c>
-      <c r="AJ233">
-        <v>1.75</v>
-      </c>
-      <c r="AK233">
-        <v>1.09</v>
-      </c>
-      <c r="AL233">
-        <v>1.17</v>
-      </c>
-      <c r="AM233">
-        <v>2.95</v>
-      </c>
-      <c r="AN233">
-        <v>2.14</v>
-      </c>
-      <c r="AO233">
-        <v>1</v>
-      </c>
-      <c r="AP233">
-        <v>2.2</v>
-      </c>
-      <c r="AQ233">
-        <v>0.93</v>
-      </c>
-      <c r="AR233">
-        <v>1.88</v>
-      </c>
-      <c r="AS233">
-        <v>1.07</v>
-      </c>
-      <c r="AT233">
-        <v>2.95</v>
-      </c>
-      <c r="AU233">
+      <c r="AY233">
+        <v>25</v>
+      </c>
+      <c r="AZ233">
+        <v>13</v>
+      </c>
+      <c r="BA233">
         <v>4</v>
       </c>
-      <c r="AV233">
-        <v>4</v>
-      </c>
-      <c r="AW233">
-        <v>6</v>
-      </c>
-      <c r="AX233">
-        <v>4</v>
-      </c>
-      <c r="AY233">
-        <v>13</v>
-      </c>
-      <c r="AZ233">
+      <c r="BB233">
+        <v>5</v>
+      </c>
+      <c r="BC233">
         <v>9</v>
       </c>
-      <c r="BA233">
-        <v>1</v>
-      </c>
-      <c r="BB233">
-        <v>4</v>
-      </c>
-      <c r="BC233">
-        <v>5</v>
-      </c>
       <c r="BD233">
+        <v>2</v>
+      </c>
+      <c r="BE233">
+        <v>6.55</v>
+      </c>
+      <c r="BF233">
+        <v>2.27</v>
+      </c>
+      <c r="BG233">
         <v>1.21</v>
       </c>
-      <c r="BE233">
-        <v>8.5</v>
-      </c>
-      <c r="BF233">
-        <v>4.8</v>
-      </c>
-      <c r="BG233">
-        <v>1.23</v>
-      </c>
       <c r="BH233">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="BI233">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BJ233">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="BK233">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="BL233">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="BM233">
-        <v>1.98</v>
+        <v>2.19</v>
       </c>
       <c r="BN233">
-        <v>1.74</v>
+        <v>1.57</v>
       </c>
       <c r="BO233">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="BP233">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="234" spans="1:68">
@@ -49440,7 +49437,7 @@
         <v>233</v>
       </c>
       <c r="B234">
-        <v>7453652</v>
+        <v>7453654</v>
       </c>
       <c r="C234" t="s">
         <v>68</v>
@@ -49449,16 +49446,16 @@
         <v>69</v>
       </c>
       <c r="E234" s="2">
-        <v>45731.69791666666</v>
+        <v>45732.39583333334</v>
       </c>
       <c r="F234">
         <v>30</v>
       </c>
       <c r="G234" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="H234" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I234">
         <v>0</v>
@@ -49470,175 +49467,175 @@
         <v>0</v>
       </c>
       <c r="L234">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N234">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O234" t="s">
-        <v>247</v>
+        <v>87</v>
       </c>
       <c r="P234" t="s">
-        <v>240</v>
+        <v>87</v>
       </c>
       <c r="Q234">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="R234">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S234">
         <v>3.2</v>
       </c>
       <c r="T234">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="U234">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="V234">
-        <v>2.63</v>
+        <v>3.4</v>
       </c>
       <c r="W234">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="X234">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y234">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z234">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="AA234">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="AB234">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AC234">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="AD234">
-        <v>9.5</v>
+        <v>7.75</v>
       </c>
       <c r="AE234">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AF234">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="AG234">
         <v>1.85</v>
       </c>
       <c r="AH234">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AI234">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="AJ234">
-        <v>2.2</v>
+        <v>1.91</v>
       </c>
       <c r="AK234">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AL234">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AM234">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="AN234">
+        <v>1.71</v>
+      </c>
+      <c r="AO234">
+        <v>1.29</v>
+      </c>
+      <c r="AP234">
+        <v>1.67</v>
+      </c>
+      <c r="AQ234">
+        <v>1.27</v>
+      </c>
+      <c r="AR234">
+        <v>1.24</v>
+      </c>
+      <c r="AS234">
+        <v>1.24</v>
+      </c>
+      <c r="AT234">
+        <v>2.48</v>
+      </c>
+      <c r="AU234">
+        <v>5</v>
+      </c>
+      <c r="AV234">
+        <v>2</v>
+      </c>
+      <c r="AW234">
+        <v>3</v>
+      </c>
+      <c r="AX234">
+        <v>3</v>
+      </c>
+      <c r="AY234">
+        <v>8</v>
+      </c>
+      <c r="AZ234">
+        <v>5</v>
+      </c>
+      <c r="BA234">
+        <v>5</v>
+      </c>
+      <c r="BB234">
+        <v>3</v>
+      </c>
+      <c r="BC234">
+        <v>8</v>
+      </c>
+      <c r="BD234">
+        <v>2.04</v>
+      </c>
+      <c r="BE234">
+        <v>6.3</v>
+      </c>
+      <c r="BF234">
+        <v>2.25</v>
+      </c>
+      <c r="BG234">
+        <v>1.31</v>
+      </c>
+      <c r="BH234">
+        <v>2.92</v>
+      </c>
+      <c r="BI234">
+        <v>1.6</v>
+      </c>
+      <c r="BJ234">
+        <v>2.14</v>
+      </c>
+      <c r="BK234">
+        <v>2.05</v>
+      </c>
+      <c r="BL234">
+        <v>1.7</v>
+      </c>
+      <c r="BM234">
         <v>2.71</v>
       </c>
-      <c r="AO234">
-        <v>1.57</v>
-      </c>
-      <c r="AP234">
-        <v>2.73</v>
-      </c>
-      <c r="AQ234">
-        <v>1.47</v>
-      </c>
-      <c r="AR234">
-        <v>1.77</v>
-      </c>
-      <c r="AS234">
-        <v>1.43</v>
-      </c>
-      <c r="AT234">
-        <v>3.2</v>
-      </c>
-      <c r="AU234">
-        <v>8</v>
-      </c>
-      <c r="AV234">
-        <v>3</v>
-      </c>
-      <c r="AW234">
-        <v>10</v>
-      </c>
-      <c r="AX234">
-        <v>6</v>
-      </c>
-      <c r="AY234">
-        <v>25</v>
-      </c>
-      <c r="AZ234">
-        <v>13</v>
-      </c>
-      <c r="BA234">
-        <v>4</v>
-      </c>
-      <c r="BB234">
-        <v>5</v>
-      </c>
-      <c r="BC234">
-        <v>9</v>
-      </c>
-      <c r="BD234">
-        <v>2</v>
-      </c>
-      <c r="BE234">
-        <v>6.55</v>
-      </c>
-      <c r="BF234">
-        <v>2.27</v>
-      </c>
-      <c r="BG234">
-        <v>1.21</v>
-      </c>
-      <c r="BH234">
-        <v>3.58</v>
-      </c>
-      <c r="BI234">
-        <v>1.41</v>
-      </c>
-      <c r="BJ234">
-        <v>2.6</v>
-      </c>
-      <c r="BK234">
-        <v>1.8</v>
-      </c>
-      <c r="BL234">
-        <v>1.91</v>
-      </c>
-      <c r="BM234">
-        <v>2.19</v>
-      </c>
       <c r="BN234">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="BO234">
-        <v>2.88</v>
+        <v>3.72</v>
       </c>
       <c r="BP234">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="235" spans="1:68">
@@ -49646,7 +49643,7 @@
         <v>234</v>
       </c>
       <c r="B235">
-        <v>7453654</v>
+        <v>7453653</v>
       </c>
       <c r="C235" t="s">
         <v>68</v>
@@ -49655,196 +49652,196 @@
         <v>69</v>
       </c>
       <c r="E235" s="2">
-        <v>45732.39583333334</v>
+        <v>45732.60416666666</v>
       </c>
       <c r="F235">
         <v>30</v>
       </c>
       <c r="G235" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H235" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="I235">
         <v>0</v>
       </c>
       <c r="J235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M235">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N235">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O235" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="P235" t="s">
-        <v>87</v>
+        <v>347</v>
       </c>
       <c r="Q235">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="R235">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S235">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="T235">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="U235">
-        <v>2.63</v>
+        <v>3</v>
       </c>
       <c r="V235">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="W235">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="X235">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y235">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Z235">
-        <v>2.9</v>
+        <v>1.68</v>
       </c>
       <c r="AA235">
-        <v>3.1</v>
+        <v>3.81</v>
       </c>
       <c r="AB235">
-        <v>2.4</v>
+        <v>4.75</v>
       </c>
       <c r="AC235">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AD235">
-        <v>7.75</v>
+        <v>9.5</v>
       </c>
       <c r="AE235">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AF235">
-        <v>2.95</v>
+        <v>3.65</v>
       </c>
       <c r="AG235">
+        <v>1.82</v>
+      </c>
+      <c r="AH235">
+        <v>1.92</v>
+      </c>
+      <c r="AI235">
+        <v>1.8</v>
+      </c>
+      <c r="AJ235">
+        <v>1.95</v>
+      </c>
+      <c r="AK235">
+        <v>1.17</v>
+      </c>
+      <c r="AL235">
+        <v>1.22</v>
+      </c>
+      <c r="AM235">
+        <v>2.1</v>
+      </c>
+      <c r="AN235">
         <v>1.85</v>
       </c>
-      <c r="AH235">
-        <v>1.85</v>
-      </c>
-      <c r="AI235">
-        <v>1.91</v>
-      </c>
-      <c r="AJ235">
-        <v>1.91</v>
-      </c>
-      <c r="AK235">
-        <v>1.5</v>
-      </c>
-      <c r="AL235">
-        <v>1.3</v>
-      </c>
-      <c r="AM235">
-        <v>1.4</v>
-      </c>
-      <c r="AN235">
+      <c r="AO235">
+        <v>0.43</v>
+      </c>
+      <c r="AP235">
         <v>1.71</v>
       </c>
-      <c r="AO235">
-        <v>1.29</v>
-      </c>
-      <c r="AP235">
-        <v>1.67</v>
-      </c>
       <c r="AQ235">
-        <v>1.27</v>
+        <v>0.6</v>
       </c>
       <c r="AR235">
-        <v>1.24</v>
+        <v>1.58</v>
       </c>
       <c r="AS235">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AT235">
-        <v>2.48</v>
+        <v>2.8</v>
       </c>
       <c r="AU235">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV235">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AW235">
         <v>3</v>
       </c>
       <c r="AX235">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY235">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AZ235">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="BA235">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB235">
         <v>3</v>
       </c>
       <c r="BC235">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD235">
-        <v>2.04</v>
+        <v>1.54</v>
       </c>
       <c r="BE235">
-        <v>6.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BF235">
-        <v>2.25</v>
+        <v>2.97</v>
       </c>
       <c r="BG235">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="BH235">
-        <v>2.92</v>
+        <v>4.2</v>
       </c>
       <c r="BI235">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="BJ235">
-        <v>2.14</v>
+        <v>2.88</v>
       </c>
       <c r="BK235">
+        <v>1.7</v>
+      </c>
+      <c r="BL235">
         <v>2.05</v>
       </c>
-      <c r="BL235">
+      <c r="BM235">
+        <v>2.05</v>
+      </c>
+      <c r="BN235">
         <v>1.7</v>
       </c>
-      <c r="BM235">
-        <v>2.71</v>
-      </c>
-      <c r="BN235">
-        <v>1.38</v>
-      </c>
       <c r="BO235">
-        <v>3.72</v>
+        <v>2.57</v>
       </c>
       <c r="BP235">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="236" spans="1:68">
@@ -49852,7 +49849,7 @@
         <v>235</v>
       </c>
       <c r="B236">
-        <v>7453657</v>
+        <v>7453650</v>
       </c>
       <c r="C236" t="s">
         <v>68</v>
@@ -49867,28 +49864,28 @@
         <v>30</v>
       </c>
       <c r="G236" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="H236" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J236">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K236">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L236">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M236">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N236">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O236" t="s">
         <v>248</v>
@@ -49897,19 +49894,19 @@
         <v>348</v>
       </c>
       <c r="Q236">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="R236">
         <v>2.25</v>
       </c>
       <c r="S236">
-        <v>4.5</v>
+        <v>6.5</v>
       </c>
       <c r="T236">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="U236">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V236">
         <v>2.75</v>
@@ -49918,19 +49915,19 @@
         <v>1.4</v>
       </c>
       <c r="X236">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y236">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z236">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="AA236">
-        <v>3.84</v>
+        <v>3.98</v>
       </c>
       <c r="AB236">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
       <c r="AC236">
         <v>1.05</v>
@@ -49939,100 +49936,100 @@
         <v>9.5</v>
       </c>
       <c r="AE236">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AF236">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AG236">
-        <v>1.77</v>
+        <v>1.87</v>
       </c>
       <c r="AH236">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="AI236">
+        <v>2</v>
+      </c>
+      <c r="AJ236">
         <v>1.75</v>
       </c>
-      <c r="AJ236">
-        <v>2</v>
-      </c>
       <c r="AK236">
-        <v>1.22</v>
+        <v>1.12</v>
       </c>
       <c r="AL236">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AM236">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="AN236">
-        <v>1.43</v>
+        <v>2.14</v>
       </c>
       <c r="AO236">
         <v>1.07</v>
       </c>
       <c r="AP236">
-        <v>1.53</v>
+        <v>2.2</v>
       </c>
       <c r="AQ236">
         <v>1</v>
       </c>
       <c r="AR236">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="AS236">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="AT236">
+        <v>3.5</v>
+      </c>
+      <c r="AU236">
+        <v>10</v>
+      </c>
+      <c r="AV236">
+        <v>4</v>
+      </c>
+      <c r="AW236">
+        <v>10</v>
+      </c>
+      <c r="AX236">
+        <v>3</v>
+      </c>
+      <c r="AY236">
+        <v>24</v>
+      </c>
+      <c r="AZ236">
+        <v>8</v>
+      </c>
+      <c r="BA236">
+        <v>2</v>
+      </c>
+      <c r="BB236">
+        <v>3</v>
+      </c>
+      <c r="BC236">
+        <v>5</v>
+      </c>
+      <c r="BD236">
+        <v>1.42</v>
+      </c>
+      <c r="BE236">
+        <v>9.5</v>
+      </c>
+      <c r="BF236">
+        <v>3.52</v>
+      </c>
+      <c r="BG236">
+        <v>1.18</v>
+      </c>
+      <c r="BH236">
+        <v>3.9</v>
+      </c>
+      <c r="BI236">
+        <v>1.36</v>
+      </c>
+      <c r="BJ236">
         <v>2.7</v>
-      </c>
-      <c r="AU236">
-        <v>8</v>
-      </c>
-      <c r="AV236">
-        <v>6</v>
-      </c>
-      <c r="AW236">
-        <v>9</v>
-      </c>
-      <c r="AX236">
-        <v>11</v>
-      </c>
-      <c r="AY236">
-        <v>18</v>
-      </c>
-      <c r="AZ236">
-        <v>23</v>
-      </c>
-      <c r="BA236">
-        <v>5</v>
-      </c>
-      <c r="BB236">
-        <v>5</v>
-      </c>
-      <c r="BC236">
-        <v>10</v>
-      </c>
-      <c r="BD236">
-        <v>1.56</v>
-      </c>
-      <c r="BE236">
-        <v>8.9</v>
-      </c>
-      <c r="BF236">
-        <v>2.94</v>
-      </c>
-      <c r="BG236">
-        <v>1.23</v>
-      </c>
-      <c r="BH236">
-        <v>3.42</v>
-      </c>
-      <c r="BI236">
-        <v>1.46</v>
-      </c>
-      <c r="BJ236">
-        <v>2.45</v>
       </c>
       <c r="BK236">
         <v>1.85</v>
@@ -50041,16 +50038,16 @@
         <v>1.85</v>
       </c>
       <c r="BM236">
-        <v>2.32</v>
+        <v>2.11</v>
       </c>
       <c r="BN236">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="BO236">
-        <v>3.08</v>
+        <v>2.75</v>
       </c>
       <c r="BP236">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="237" spans="1:68">
@@ -50058,7 +50055,7 @@
         <v>236</v>
       </c>
       <c r="B237">
-        <v>7453656</v>
+        <v>7453651</v>
       </c>
       <c r="C237" t="s">
         <v>68</v>
@@ -50073,43 +50070,43 @@
         <v>30</v>
       </c>
       <c r="G237" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="H237" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="I237">
         <v>1</v>
       </c>
       <c r="J237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K237">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L237">
         <v>3</v>
       </c>
       <c r="M237">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N237">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O237" t="s">
         <v>249</v>
       </c>
       <c r="P237" t="s">
-        <v>349</v>
+        <v>87</v>
       </c>
       <c r="Q237">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="R237">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="S237">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="T237">
         <v>1.4</v>
@@ -50130,13 +50127,13 @@
         <v>1.08</v>
       </c>
       <c r="Z237">
-        <v>2.35</v>
+        <v>1.83</v>
       </c>
       <c r="AA237">
-        <v>2.98</v>
+        <v>3.47</v>
       </c>
       <c r="AB237">
-        <v>3.23</v>
+        <v>4.3</v>
       </c>
       <c r="AC237">
         <v>1.06</v>
@@ -50145,118 +50142,118 @@
         <v>8.5</v>
       </c>
       <c r="AE237">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AF237">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AG237">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="AH237">
+        <v>1.8</v>
+      </c>
+      <c r="AI237">
+        <v>1.8</v>
+      </c>
+      <c r="AJ237">
+        <v>1.95</v>
+      </c>
+      <c r="AK237">
+        <v>1.22</v>
+      </c>
+      <c r="AL237">
+        <v>1.25</v>
+      </c>
+      <c r="AM237">
         <v>1.85</v>
       </c>
-      <c r="AI237">
-        <v>1.67</v>
-      </c>
-      <c r="AJ237">
-        <v>2.1</v>
-      </c>
-      <c r="AK237">
-        <v>1.38</v>
-      </c>
-      <c r="AL237">
-        <v>1.3</v>
-      </c>
-      <c r="AM237">
-        <v>1.53</v>
-      </c>
       <c r="AN237">
-        <v>1.79</v>
+        <v>1.71</v>
       </c>
       <c r="AO237">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="AP237">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AQ237">
-        <v>0.6</v>
+        <v>0.73</v>
       </c>
       <c r="AR237">
-        <v>1.28</v>
+        <v>1.65</v>
       </c>
       <c r="AS237">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AT237">
-        <v>2.53</v>
+        <v>3.05</v>
       </c>
       <c r="AU237">
+        <v>7</v>
+      </c>
+      <c r="AV237">
         <v>5</v>
       </c>
-      <c r="AV237">
-        <v>3</v>
-      </c>
       <c r="AW237">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX237">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AY237">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="AZ237">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="BA237">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BB237">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BC237">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="BD237">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="BE237">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BF237">
-        <v>2.38</v>
+        <v>3.48</v>
       </c>
       <c r="BG237">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BH237">
-        <v>3.68</v>
+        <v>3.78</v>
       </c>
       <c r="BI237">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BJ237">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BK237">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="BL237">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BM237">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="BN237">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="BO237">
-        <v>2.88</v>
+        <v>2.83</v>
       </c>
       <c r="BP237">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="238" spans="1:68">
@@ -50264,7 +50261,7 @@
         <v>237</v>
       </c>
       <c r="B238">
-        <v>7453655</v>
+        <v>7453657</v>
       </c>
       <c r="C238" t="s">
         <v>68</v>
@@ -50279,190 +50276,190 @@
         <v>30</v>
       </c>
       <c r="G238" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H238" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I238">
         <v>0</v>
       </c>
       <c r="J238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N238">
         <v>3</v>
       </c>
       <c r="O238" t="s">
-        <v>118</v>
+        <v>250</v>
       </c>
       <c r="P238" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="Q238">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="R238">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="S238">
-        <v>2.6</v>
+        <v>4.5</v>
       </c>
       <c r="T238">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="U238">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="V238">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="W238">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X238">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y238">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z238">
-        <v>3.38</v>
+        <v>1.72</v>
       </c>
       <c r="AA238">
-        <v>3.75</v>
+        <v>3.84</v>
       </c>
       <c r="AB238">
-        <v>1.97</v>
+        <v>4.4</v>
       </c>
       <c r="AC238">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD238">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AE238">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF238">
-        <v>4.33</v>
+        <v>3.7</v>
       </c>
       <c r="AG238">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="AH238">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
       <c r="AI238">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AJ238">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AK238">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="AL238">
         <v>1.22</v>
       </c>
       <c r="AM238">
-        <v>1.3</v>
+        <v>1.91</v>
       </c>
       <c r="AN238">
-        <v>1.14</v>
+        <v>1.43</v>
       </c>
       <c r="AO238">
-        <v>0.86</v>
+        <v>1.07</v>
       </c>
       <c r="AP238">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="AQ238">
         <v>1</v>
       </c>
       <c r="AR238">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AS238">
-        <v>1.58</v>
+        <v>1.2</v>
       </c>
       <c r="AT238">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AU238">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AV238">
+        <v>6</v>
+      </c>
+      <c r="AW238">
+        <v>9</v>
+      </c>
+      <c r="AX238">
+        <v>11</v>
+      </c>
+      <c r="AY238">
+        <v>18</v>
+      </c>
+      <c r="AZ238">
+        <v>23</v>
+      </c>
+      <c r="BA238">
         <v>5</v>
       </c>
-      <c r="AW238">
-        <v>6</v>
-      </c>
-      <c r="AX238">
-        <v>7</v>
-      </c>
-      <c r="AY238">
-        <v>10</v>
-      </c>
-      <c r="AZ238">
-        <v>16</v>
-      </c>
-      <c r="BA238">
-        <v>6</v>
-      </c>
       <c r="BB238">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC238">
         <v>10</v>
       </c>
       <c r="BD238">
-        <v>2.34</v>
+        <v>1.56</v>
       </c>
       <c r="BE238">
-        <v>6.65</v>
+        <v>8.9</v>
       </c>
       <c r="BF238">
-        <v>1.94</v>
+        <v>2.94</v>
       </c>
       <c r="BG238">
-        <v>1.15</v>
+        <v>1.23</v>
       </c>
       <c r="BH238">
-        <v>4.25</v>
+        <v>3.42</v>
       </c>
       <c r="BI238">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="BJ238">
-        <v>2.88</v>
+        <v>2.45</v>
       </c>
       <c r="BK238">
-        <v>1.58</v>
+        <v>1.85</v>
       </c>
       <c r="BL238">
-        <v>2.17</v>
+        <v>1.85</v>
       </c>
       <c r="BM238">
-        <v>1.93</v>
+        <v>2.32</v>
       </c>
       <c r="BN238">
-        <v>1.77</v>
+        <v>1.51</v>
       </c>
       <c r="BO238">
-        <v>2.57</v>
+        <v>3.08</v>
       </c>
       <c r="BP238">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="239" spans="1:68">
@@ -50470,7 +50467,7 @@
         <v>238</v>
       </c>
       <c r="B239">
-        <v>7453653</v>
+        <v>7453656</v>
       </c>
       <c r="C239" t="s">
         <v>68</v>
@@ -50485,190 +50482,190 @@
         <v>30</v>
       </c>
       <c r="G239" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="H239" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="I239">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J239">
         <v>1</v>
       </c>
       <c r="K239">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L239">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M239">
         <v>2</v>
       </c>
       <c r="N239">
+        <v>5</v>
+      </c>
+      <c r="O239" t="s">
+        <v>251</v>
+      </c>
+      <c r="P239" t="s">
+        <v>350</v>
+      </c>
+      <c r="Q239">
+        <v>3.1</v>
+      </c>
+      <c r="R239">
+        <v>2.1</v>
+      </c>
+      <c r="S239">
+        <v>3.5</v>
+      </c>
+      <c r="T239">
+        <v>1.4</v>
+      </c>
+      <c r="U239">
+        <v>2.75</v>
+      </c>
+      <c r="V239">
         <v>3</v>
       </c>
-      <c r="O239" t="s">
-        <v>105</v>
-      </c>
-      <c r="P239" t="s">
-        <v>351</v>
-      </c>
-      <c r="Q239">
-        <v>2.3</v>
-      </c>
-      <c r="R239">
-        <v>2.25</v>
-      </c>
-      <c r="S239">
-        <v>5</v>
-      </c>
-      <c r="T239">
+      <c r="W239">
         <v>1.36</v>
       </c>
-      <c r="U239">
-        <v>3</v>
-      </c>
-      <c r="V239">
-        <v>2.75</v>
-      </c>
-      <c r="W239">
-        <v>1.4</v>
-      </c>
       <c r="X239">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y239">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z239">
-        <v>1.68</v>
+        <v>2.35</v>
       </c>
       <c r="AA239">
-        <v>3.81</v>
+        <v>2.98</v>
       </c>
       <c r="AB239">
-        <v>4.75</v>
+        <v>3.23</v>
       </c>
       <c r="AC239">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD239">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AE239">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AF239">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="AG239">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="AH239">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AI239">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AJ239">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AK239">
-        <v>1.17</v>
+        <v>1.38</v>
       </c>
       <c r="AL239">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AM239">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AN239">
         <v>1.79</v>
       </c>
       <c r="AO239">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="AP239">
-        <v>1.67</v>
+        <v>1.87</v>
       </c>
       <c r="AQ239">
         <v>0.6</v>
       </c>
       <c r="AR239">
-        <v>1.61</v>
+        <v>1.28</v>
       </c>
       <c r="AS239">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AT239">
-        <v>2.83</v>
+        <v>2.53</v>
       </c>
       <c r="AU239">
+        <v>5</v>
+      </c>
+      <c r="AV239">
         <v>3</v>
       </c>
-      <c r="AV239">
+      <c r="AW239">
+        <v>6</v>
+      </c>
+      <c r="AX239">
+        <v>1</v>
+      </c>
+      <c r="AY239">
+        <v>12</v>
+      </c>
+      <c r="AZ239">
         <v>4</v>
       </c>
-      <c r="AW239">
-        <v>3</v>
-      </c>
-      <c r="AX239">
-        <v>4</v>
-      </c>
-      <c r="AY239">
-        <v>6</v>
-      </c>
-      <c r="AZ239">
-        <v>10</v>
-      </c>
       <c r="BA239">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB239">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BC239">
         <v>7</v>
       </c>
       <c r="BD239">
-        <v>1.54</v>
+        <v>1.92</v>
       </c>
       <c r="BE239">
-        <v>9.300000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BF239">
-        <v>2.97</v>
+        <v>2.38</v>
       </c>
       <c r="BG239">
-        <v>1.15</v>
+        <v>1.2</v>
       </c>
       <c r="BH239">
-        <v>4.2</v>
+        <v>3.68</v>
       </c>
       <c r="BI239">
+        <v>1.41</v>
+      </c>
+      <c r="BJ239">
+        <v>2.6</v>
+      </c>
+      <c r="BK239">
+        <v>1.73</v>
+      </c>
+      <c r="BL239">
+        <v>2</v>
+      </c>
+      <c r="BM239">
+        <v>2.19</v>
+      </c>
+      <c r="BN239">
+        <v>1.57</v>
+      </c>
+      <c r="BO239">
+        <v>2.88</v>
+      </c>
+      <c r="BP239">
         <v>1.32</v>
-      </c>
-      <c r="BJ239">
-        <v>2.88</v>
-      </c>
-      <c r="BK239">
-        <v>1.7</v>
-      </c>
-      <c r="BL239">
-        <v>2.05</v>
-      </c>
-      <c r="BM239">
-        <v>2.05</v>
-      </c>
-      <c r="BN239">
-        <v>1.7</v>
-      </c>
-      <c r="BO239">
-        <v>2.57</v>
-      </c>
-      <c r="BP239">
-        <v>1.42</v>
       </c>
     </row>
     <row r="240" spans="1:68">
@@ -50676,7 +50673,7 @@
         <v>239</v>
       </c>
       <c r="B240">
-        <v>7453651</v>
+        <v>7453655</v>
       </c>
       <c r="C240" t="s">
         <v>68</v>
@@ -50691,396 +50688,190 @@
         <v>30</v>
       </c>
       <c r="G240" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H240" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I240">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K240">
         <v>1</v>
       </c>
       <c r="L240">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M240">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N240">
         <v>3</v>
       </c>
       <c r="O240" t="s">
-        <v>250</v>
+        <v>118</v>
       </c>
       <c r="P240" t="s">
-        <v>87</v>
+        <v>351</v>
       </c>
       <c r="Q240">
+        <v>3.75</v>
+      </c>
+      <c r="R240">
+        <v>2.3</v>
+      </c>
+      <c r="S240">
+        <v>2.6</v>
+      </c>
+      <c r="T240">
+        <v>1.3</v>
+      </c>
+      <c r="U240">
+        <v>3.4</v>
+      </c>
+      <c r="V240">
         <v>2.5</v>
       </c>
-      <c r="R240">
-        <v>2.2</v>
-      </c>
-      <c r="S240">
-        <v>4.5</v>
-      </c>
-      <c r="T240">
-        <v>1.4</v>
-      </c>
-      <c r="U240">
-        <v>2.75</v>
-      </c>
-      <c r="V240">
-        <v>3</v>
-      </c>
       <c r="W240">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X240">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y240">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z240">
-        <v>1.83</v>
+        <v>3.38</v>
       </c>
       <c r="AA240">
-        <v>3.47</v>
+        <v>3.75</v>
       </c>
       <c r="AB240">
-        <v>4.3</v>
+        <v>1.97</v>
       </c>
       <c r="AC240">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AD240">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AE240">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AF240">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="AG240">
-        <v>1.94</v>
+        <v>1.59</v>
       </c>
       <c r="AH240">
-        <v>1.8</v>
+        <v>2.27</v>
       </c>
       <c r="AI240">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ240">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AK240">
+        <v>1.77</v>
+      </c>
+      <c r="AL240">
         <v>1.22</v>
       </c>
-      <c r="AL240">
-        <v>1.25</v>
-      </c>
       <c r="AM240">
-        <v>1.85</v>
+        <v>1.3</v>
       </c>
       <c r="AN240">
-        <v>1.71</v>
+        <v>1.14</v>
       </c>
       <c r="AO240">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="AP240">
-        <v>1.8</v>
+        <v>1.07</v>
       </c>
       <c r="AQ240">
-        <v>0.73</v>
+        <v>1</v>
       </c>
       <c r="AR240">
-        <v>1.65</v>
+        <v>1.3</v>
       </c>
       <c r="AS240">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AT240">
-        <v>3.05</v>
+        <v>2.88</v>
       </c>
       <c r="AU240">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AV240">
         <v>5</v>
       </c>
       <c r="AW240">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX240">
         <v>7</v>
       </c>
       <c r="AY240">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ240">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA240">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BB240">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BC240">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BD240">
-        <v>1.5</v>
+        <v>2.34</v>
       </c>
       <c r="BE240">
-        <v>7.2</v>
+        <v>6.65</v>
       </c>
       <c r="BF240">
-        <v>3.48</v>
+        <v>1.94</v>
       </c>
       <c r="BG240">
-        <v>1.19</v>
+        <v>1.15</v>
       </c>
       <c r="BH240">
-        <v>3.78</v>
+        <v>4.25</v>
       </c>
       <c r="BI240">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="BJ240">
-        <v>2.64</v>
+        <v>2.88</v>
       </c>
       <c r="BK240">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="BL240">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="BM240">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="BN240">
-        <v>1.59</v>
+        <v>1.77</v>
       </c>
       <c r="BO240">
-        <v>2.83</v>
+        <v>2.57</v>
       </c>
       <c r="BP240">
-        <v>1.33</v>
-      </c>
-    </row>
-    <row r="241" spans="1:68">
-      <c r="A241" s="1">
-        <v>240</v>
-      </c>
-      <c r="B241">
-        <v>7453650</v>
-      </c>
-      <c r="C241" t="s">
-        <v>68</v>
-      </c>
-      <c r="D241" t="s">
-        <v>69</v>
-      </c>
-      <c r="E241" s="2">
-        <v>45732.60416666666</v>
-      </c>
-      <c r="F241">
-        <v>30</v>
-      </c>
-      <c r="G241" t="s">
-        <v>70</v>
-      </c>
-      <c r="H241" t="s">
-        <v>76</v>
-      </c>
-      <c r="I241">
-        <v>1</v>
-      </c>
-      <c r="J241">
-        <v>1</v>
-      </c>
-      <c r="K241">
-        <v>2</v>
-      </c>
-      <c r="L241">
-        <v>4</v>
-      </c>
-      <c r="M241">
-        <v>2</v>
-      </c>
-      <c r="N241">
-        <v>6</v>
-      </c>
-      <c r="O241" t="s">
-        <v>251</v>
-      </c>
-      <c r="P241" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q241">
-        <v>2.1</v>
-      </c>
-      <c r="R241">
-        <v>2.25</v>
-      </c>
-      <c r="S241">
-        <v>6.5</v>
-      </c>
-      <c r="T241">
-        <v>1.4</v>
-      </c>
-      <c r="U241">
-        <v>2.75</v>
-      </c>
-      <c r="V241">
-        <v>2.75</v>
-      </c>
-      <c r="W241">
-        <v>1.4</v>
-      </c>
-      <c r="X241">
-        <v>8</v>
-      </c>
-      <c r="Y241">
-        <v>1.08</v>
-      </c>
-      <c r="Z241">
-        <v>1.55</v>
-      </c>
-      <c r="AA241">
-        <v>3.98</v>
-      </c>
-      <c r="AB241">
-        <v>5.8</v>
-      </c>
-      <c r="AC241">
-        <v>1.05</v>
-      </c>
-      <c r="AD241">
-        <v>9.5</v>
-      </c>
-      <c r="AE241">
-        <v>1.28</v>
-      </c>
-      <c r="AF241">
-        <v>3.6</v>
-      </c>
-      <c r="AG241">
-        <v>1.87</v>
-      </c>
-      <c r="AH241">
-        <v>1.87</v>
-      </c>
-      <c r="AI241">
-        <v>2</v>
-      </c>
-      <c r="AJ241">
-        <v>1.75</v>
-      </c>
-      <c r="AK241">
-        <v>1.12</v>
-      </c>
-      <c r="AL241">
-        <v>1.18</v>
-      </c>
-      <c r="AM241">
-        <v>2.45</v>
-      </c>
-      <c r="AN241">
-        <v>2.14</v>
-      </c>
-      <c r="AO241">
-        <v>1.07</v>
-      </c>
-      <c r="AP241">
-        <v>2.2</v>
-      </c>
-      <c r="AQ241">
-        <v>1</v>
-      </c>
-      <c r="AR241">
-        <v>2.06</v>
-      </c>
-      <c r="AS241">
-        <v>1.44</v>
-      </c>
-      <c r="AT241">
-        <v>3.5</v>
-      </c>
-      <c r="AU241">
-        <v>10</v>
-      </c>
-      <c r="AV241">
-        <v>4</v>
-      </c>
-      <c r="AW241">
-        <v>10</v>
-      </c>
-      <c r="AX241">
-        <v>3</v>
-      </c>
-      <c r="AY241">
-        <v>24</v>
-      </c>
-      <c r="AZ241">
-        <v>8</v>
-      </c>
-      <c r="BA241">
-        <v>2</v>
-      </c>
-      <c r="BB241">
-        <v>3</v>
-      </c>
-      <c r="BC241">
-        <v>5</v>
-      </c>
-      <c r="BD241">
         <v>1.42</v>
-      </c>
-      <c r="BE241">
-        <v>9.5</v>
-      </c>
-      <c r="BF241">
-        <v>3.52</v>
-      </c>
-      <c r="BG241">
-        <v>1.18</v>
-      </c>
-      <c r="BH241">
-        <v>3.9</v>
-      </c>
-      <c r="BI241">
-        <v>1.36</v>
-      </c>
-      <c r="BJ241">
-        <v>2.7</v>
-      </c>
-      <c r="BK241">
-        <v>1.85</v>
-      </c>
-      <c r="BL241">
-        <v>1.85</v>
-      </c>
-      <c r="BM241">
-        <v>2.11</v>
-      </c>
-      <c r="BN241">
-        <v>1.65</v>
-      </c>
-      <c r="BO241">
-        <v>2.75</v>
-      </c>
-      <c r="BP241">
-        <v>1.37</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1502" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="353">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -760,9 +760,6 @@
     <t>['69', '83']</t>
   </si>
   <si>
-    <t>['3', '49', '63', '80']</t>
-  </si>
-  <si>
     <t>['6', '87', '90+6']</t>
   </si>
   <si>
@@ -770,6 +767,9 @@
   </si>
   <si>
     <t>['13', '66', '83']</t>
+  </si>
+  <si>
+    <t>['3', '49', '63', '80']</t>
   </si>
   <si>
     <t>['65']</t>
@@ -1045,6 +1045,9 @@
     <t>['33', '70']</t>
   </si>
   <si>
+    <t>['29']</t>
+  </si>
+  <si>
     <t>['45', '70']</t>
   </si>
   <si>
@@ -1057,12 +1060,6 @@
     <t>['83']</t>
   </si>
   <si>
-    <t>['45+5', '70']</t>
-  </si>
-  <si>
-    <t>['34', '77']</t>
-  </si>
-  <si>
     <t>['73']</t>
   </si>
   <si>
@@ -1070,6 +1067,12 @@
   </si>
   <si>
     <t>['45+7', '86']</t>
+  </si>
+  <si>
+    <t>['34', '77']</t>
+  </si>
+  <si>
+    <t>['45+5', '70']</t>
   </si>
 </sst>
 </file>
@@ -1431,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP240"/>
+  <dimension ref="A1:BP241"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -4652,7 +4655,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ16">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4855,7 +4858,7 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ17">
         <v>1</v>
@@ -5888,7 +5891,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ22">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR22">
         <v>1.58</v>
@@ -8151,7 +8154,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ33">
         <v>1</v>
@@ -8772,7 +8775,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ36">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR36">
         <v>0.9399999999999999</v>
@@ -10623,7 +10626,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ45">
         <v>1.27</v>
@@ -11656,7 +11659,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ50">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR50">
         <v>1.76</v>
@@ -12683,7 +12686,7 @@
         <v>1.67</v>
       </c>
       <c r="AP55">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -14952,7 +14955,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ66">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR66">
         <v>1.81</v>
@@ -16185,7 +16188,7 @@
         <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ72">
         <v>0.6</v>
@@ -18454,7 +18457,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ83">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR83">
         <v>1.89</v>
@@ -21129,7 +21132,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ96">
         <v>1.8</v>
@@ -21956,7 +21959,7 @@
         <v>1.87</v>
       </c>
       <c r="AQ100">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR100">
         <v>1.3</v>
@@ -24219,7 +24222,7 @@
         <v>0.67</v>
       </c>
       <c r="AP111">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ111">
         <v>0.93</v>
@@ -24634,7 +24637,7 @@
         <v>1.07</v>
       </c>
       <c r="AQ113">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR113">
         <v>0.88</v>
@@ -28548,7 +28551,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ132">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR132">
         <v>1.55</v>
@@ -28751,7 +28754,7 @@
         <v>0.63</v>
       </c>
       <c r="AP133">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ133">
         <v>0.6</v>
@@ -31223,7 +31226,7 @@
         <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ145">
         <v>0.73</v>
@@ -32668,7 +32671,7 @@
         <v>2.2</v>
       </c>
       <c r="AQ152">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR152">
         <v>1.81</v>
@@ -33901,7 +33904,7 @@
         <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ158">
         <v>1.47</v>
@@ -35964,7 +35967,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ168">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR168">
         <v>1.71</v>
@@ -36373,7 +36376,7 @@
         <v>0.91</v>
       </c>
       <c r="AP170">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -40496,7 +40499,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ190">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR190">
         <v>1.72</v>
@@ -40905,7 +40908,7 @@
         <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ192">
         <v>1.6</v>
@@ -43586,7 +43589,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ205">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AR205">
         <v>1.6</v>
@@ -43789,7 +43792,7 @@
         <v>0.08</v>
       </c>
       <c r="AP206">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AQ206">
         <v>0.13</v>
@@ -46347,7 +46350,7 @@
         <v>218</v>
       </c>
       <c r="B219">
-        <v>7453638</v>
+        <v>7454763</v>
       </c>
       <c r="C219" t="s">
         <v>68</v>
@@ -46362,190 +46365,190 @@
         <v>28</v>
       </c>
       <c r="G219" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H219" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="I219">
         <v>0</v>
       </c>
       <c r="J219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M219">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N219">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O219" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P219" t="s">
-        <v>87</v>
+        <v>343</v>
       </c>
       <c r="Q219">
+        <v>4.33</v>
+      </c>
+      <c r="R219">
+        <v>2.38</v>
+      </c>
+      <c r="S219">
+        <v>2.38</v>
+      </c>
+      <c r="T219">
+        <v>1.3</v>
+      </c>
+      <c r="U219">
+        <v>3.4</v>
+      </c>
+      <c r="V219">
+        <v>2.5</v>
+      </c>
+      <c r="W219">
+        <v>1.5</v>
+      </c>
+      <c r="X219">
+        <v>6</v>
+      </c>
+      <c r="Y219">
+        <v>1.13</v>
+      </c>
+      <c r="Z219">
+        <v>3.56</v>
+      </c>
+      <c r="AA219">
+        <v>3.65</v>
+      </c>
+      <c r="AB219">
+        <v>1.94</v>
+      </c>
+      <c r="AC219">
+        <v>1.04</v>
+      </c>
+      <c r="AD219">
+        <v>10</v>
+      </c>
+      <c r="AE219">
+        <v>1.22</v>
+      </c>
+      <c r="AF219">
+        <v>4.2</v>
+      </c>
+      <c r="AG219">
+        <v>1.82</v>
+      </c>
+      <c r="AH219">
+        <v>1.92</v>
+      </c>
+      <c r="AI219">
+        <v>1.62</v>
+      </c>
+      <c r="AJ219">
+        <v>2.2</v>
+      </c>
+      <c r="AK219">
+        <v>1.98</v>
+      </c>
+      <c r="AL219">
+        <v>1.26</v>
+      </c>
+      <c r="AM219">
+        <v>1.22</v>
+      </c>
+      <c r="AN219">
+        <v>1.85</v>
+      </c>
+      <c r="AO219">
+        <v>1.69</v>
+      </c>
+      <c r="AP219">
+        <v>1.67</v>
+      </c>
+      <c r="AQ219">
+        <v>1.73</v>
+      </c>
+      <c r="AR219">
+        <v>1.58</v>
+      </c>
+      <c r="AS219">
+        <v>1.71</v>
+      </c>
+      <c r="AT219">
+        <v>3.29</v>
+      </c>
+      <c r="AU219">
+        <v>-1</v>
+      </c>
+      <c r="AV219">
+        <v>-1</v>
+      </c>
+      <c r="AW219">
+        <v>-1</v>
+      </c>
+      <c r="AX219">
+        <v>-1</v>
+      </c>
+      <c r="AY219">
+        <v>-1</v>
+      </c>
+      <c r="AZ219">
+        <v>-1</v>
+      </c>
+      <c r="BA219">
+        <v>6</v>
+      </c>
+      <c r="BB219">
+        <v>7</v>
+      </c>
+      <c r="BC219">
+        <v>13</v>
+      </c>
+      <c r="BD219">
+        <v>2.65</v>
+      </c>
+      <c r="BE219">
+        <v>6.75</v>
+      </c>
+      <c r="BF219">
+        <v>1.58</v>
+      </c>
+      <c r="BG219">
+        <v>1.33</v>
+      </c>
+      <c r="BH219">
         <v>2.95</v>
       </c>
-      <c r="R219">
-        <v>2.1</v>
-      </c>
-      <c r="S219">
-        <v>3.3</v>
-      </c>
-      <c r="T219">
-        <v>1.38</v>
-      </c>
-      <c r="U219">
-        <v>2.8</v>
-      </c>
-      <c r="V219">
-        <v>2.75</v>
-      </c>
-      <c r="W219">
-        <v>1.39</v>
-      </c>
-      <c r="X219">
-        <v>7</v>
-      </c>
-      <c r="Y219">
-        <v>1.08</v>
-      </c>
-      <c r="Z219">
-        <v>2.35</v>
-      </c>
-      <c r="AA219">
-        <v>3.39</v>
-      </c>
-      <c r="AB219">
-        <v>2.86</v>
-      </c>
-      <c r="AC219">
-        <v>1.06</v>
-      </c>
-      <c r="AD219">
-        <v>8.5</v>
-      </c>
-      <c r="AE219">
-        <v>1.33</v>
-      </c>
-      <c r="AF219">
-        <v>3.25</v>
-      </c>
-      <c r="AG219">
-        <v>1.89</v>
-      </c>
-      <c r="AH219">
-        <v>1.85</v>
-      </c>
-      <c r="AI219">
-        <v>1.73</v>
-      </c>
-      <c r="AJ219">
-        <v>1.95</v>
-      </c>
-      <c r="AK219">
-        <v>1.41</v>
-      </c>
-      <c r="AL219">
-        <v>1.31</v>
-      </c>
-      <c r="AM219">
-        <v>1.53</v>
-      </c>
-      <c r="AN219">
-        <v>1.54</v>
-      </c>
-      <c r="AO219">
-        <v>1.31</v>
-      </c>
-      <c r="AP219">
-        <v>1.4</v>
-      </c>
-      <c r="AQ219">
-        <v>1.27</v>
-      </c>
-      <c r="AR219">
-        <v>1.72</v>
-      </c>
-      <c r="AS219">
-        <v>1.24</v>
-      </c>
-      <c r="AT219">
-        <v>2.96</v>
-      </c>
-      <c r="AU219">
-        <v>11</v>
-      </c>
-      <c r="AV219">
-        <v>5</v>
-      </c>
-      <c r="AW219">
-        <v>11</v>
-      </c>
-      <c r="AX219">
-        <v>4</v>
-      </c>
-      <c r="AY219">
-        <v>23</v>
-      </c>
-      <c r="AZ219">
-        <v>11</v>
-      </c>
-      <c r="BA219">
-        <v>2</v>
-      </c>
-      <c r="BB219">
-        <v>5</v>
-      </c>
-      <c r="BC219">
-        <v>7</v>
-      </c>
-      <c r="BD219">
-        <v>1.98</v>
-      </c>
-      <c r="BE219">
-        <v>6.4</v>
-      </c>
-      <c r="BF219">
-        <v>1.98</v>
-      </c>
-      <c r="BG219">
-        <v>1.29</v>
-      </c>
-      <c r="BH219">
+      <c r="BI219">
+        <v>1.57</v>
+      </c>
+      <c r="BJ219">
+        <v>2.23</v>
+      </c>
+      <c r="BK219">
+        <v>1.94</v>
+      </c>
+      <c r="BL219">
+        <v>1.76</v>
+      </c>
+      <c r="BM219">
+        <v>2.43</v>
+      </c>
+      <c r="BN219">
+        <v>1.49</v>
+      </c>
+      <c r="BO219">
         <v>3.15</v>
       </c>
-      <c r="BI219">
-        <v>1.5</v>
-      </c>
-      <c r="BJ219">
-        <v>2.35</v>
-      </c>
-      <c r="BK219">
-        <v>1.84</v>
-      </c>
-      <c r="BL219">
-        <v>1.84</v>
-      </c>
-      <c r="BM219">
-        <v>2.3</v>
-      </c>
-      <c r="BN219">
-        <v>1.54</v>
-      </c>
-      <c r="BO219">
-        <v>2.95</v>
-      </c>
       <c r="BP219">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="220" spans="1:68">
@@ -46553,7 +46556,7 @@
         <v>219</v>
       </c>
       <c r="B220">
-        <v>7453640</v>
+        <v>7453638</v>
       </c>
       <c r="C220" t="s">
         <v>68</v>
@@ -46562,94 +46565,94 @@
         <v>69</v>
       </c>
       <c r="E220" s="2">
-        <v>45717.59375</v>
+        <v>45717.5</v>
       </c>
       <c r="F220">
         <v>28</v>
       </c>
       <c r="G220" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H220" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I220">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K220">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L220">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M220">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N220">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O220" t="s">
-        <v>241</v>
+        <v>87</v>
       </c>
       <c r="P220" t="s">
-        <v>343</v>
+        <v>87</v>
       </c>
       <c r="Q220">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="R220">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S220">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="T220">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="U220">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="V220">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="W220">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="X220">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="Y220">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="Z220">
-        <v>1.77</v>
+        <v>2.35</v>
       </c>
       <c r="AA220">
-        <v>3.8</v>
+        <v>3.39</v>
       </c>
       <c r="AB220">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="AC220">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD220">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AE220">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AF220">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="AG220">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AH220">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AI220">
         <v>1.73</v>
@@ -46658,100 +46661,100 @@
         <v>1.95</v>
       </c>
       <c r="AK220">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="AL220">
-        <v>1.26</v>
+        <v>1.31</v>
       </c>
       <c r="AM220">
-        <v>2.05</v>
+        <v>1.53</v>
       </c>
       <c r="AN220">
-        <v>1.23</v>
+        <v>1.54</v>
       </c>
       <c r="AO220">
-        <v>0.46</v>
+        <v>1.31</v>
       </c>
       <c r="AP220">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="AQ220">
-        <v>0.6</v>
+        <v>1.27</v>
       </c>
       <c r="AR220">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="AS220">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
       <c r="AT220">
-        <v>2.69</v>
+        <v>2.96</v>
       </c>
       <c r="AU220">
+        <v>11</v>
+      </c>
+      <c r="AV220">
         <v>5</v>
       </c>
-      <c r="AV220">
-        <v>8</v>
-      </c>
       <c r="AW220">
+        <v>11</v>
+      </c>
+      <c r="AX220">
+        <v>4</v>
+      </c>
+      <c r="AY220">
+        <v>23</v>
+      </c>
+      <c r="AZ220">
+        <v>11</v>
+      </c>
+      <c r="BA220">
+        <v>2</v>
+      </c>
+      <c r="BB220">
         <v>5</v>
-      </c>
-      <c r="AX220">
-        <v>8</v>
-      </c>
-      <c r="AY220">
-        <v>10</v>
-      </c>
-      <c r="AZ220">
-        <v>18</v>
-      </c>
-      <c r="BA220">
-        <v>3</v>
-      </c>
-      <c r="BB220">
-        <v>4</v>
       </c>
       <c r="BC220">
         <v>7</v>
       </c>
       <c r="BD220">
-        <v>1.47</v>
+        <v>1.98</v>
       </c>
       <c r="BE220">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="BF220">
+        <v>1.98</v>
+      </c>
+      <c r="BG220">
+        <v>1.29</v>
+      </c>
+      <c r="BH220">
+        <v>3.15</v>
+      </c>
+      <c r="BI220">
+        <v>1.5</v>
+      </c>
+      <c r="BJ220">
+        <v>2.35</v>
+      </c>
+      <c r="BK220">
+        <v>1.84</v>
+      </c>
+      <c r="BL220">
+        <v>1.84</v>
+      </c>
+      <c r="BM220">
+        <v>2.3</v>
+      </c>
+      <c r="BN220">
+        <v>1.54</v>
+      </c>
+      <c r="BO220">
         <v>2.95</v>
       </c>
-      <c r="BG220">
-        <v>1.21</v>
-      </c>
-      <c r="BH220">
-        <v>3.9</v>
-      </c>
-      <c r="BI220">
-        <v>1.38</v>
-      </c>
-      <c r="BJ220">
-        <v>2.8</v>
-      </c>
-      <c r="BK220">
-        <v>1.63</v>
-      </c>
-      <c r="BL220">
-        <v>2.15</v>
-      </c>
-      <c r="BM220">
-        <v>1.98</v>
-      </c>
-      <c r="BN220">
-        <v>1.73</v>
-      </c>
-      <c r="BO220">
-        <v>2.48</v>
-      </c>
       <c r="BP220">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="221" spans="1:68">
@@ -46759,7 +46762,7 @@
         <v>220</v>
       </c>
       <c r="B221">
-        <v>7453635</v>
+        <v>7453640</v>
       </c>
       <c r="C221" t="s">
         <v>68</v>
@@ -46768,196 +46771,196 @@
         <v>69</v>
       </c>
       <c r="E221" s="2">
-        <v>45717.69791666666</v>
+        <v>45717.59375</v>
       </c>
       <c r="F221">
         <v>28</v>
       </c>
       <c r="G221" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H221" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I221">
         <v>2</v>
       </c>
       <c r="J221">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K221">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L221">
         <v>4</v>
       </c>
       <c r="M221">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N221">
+        <v>6</v>
+      </c>
+      <c r="O221" t="s">
+        <v>241</v>
+      </c>
+      <c r="P221" t="s">
+        <v>344</v>
+      </c>
+      <c r="Q221">
+        <v>2.25</v>
+      </c>
+      <c r="R221">
+        <v>2.2</v>
+      </c>
+      <c r="S221">
+        <v>4.5</v>
+      </c>
+      <c r="T221">
+        <v>1.35</v>
+      </c>
+      <c r="U221">
+        <v>2.95</v>
+      </c>
+      <c r="V221">
+        <v>2.5</v>
+      </c>
+      <c r="W221">
+        <v>1.46</v>
+      </c>
+      <c r="X221">
+        <v>6.25</v>
+      </c>
+      <c r="Y221">
+        <v>1.1</v>
+      </c>
+      <c r="Z221">
+        <v>1.77</v>
+      </c>
+      <c r="AA221">
+        <v>3.8</v>
+      </c>
+      <c r="AB221">
+        <v>4.1</v>
+      </c>
+      <c r="AC221">
+        <v>1.05</v>
+      </c>
+      <c r="AD221">
+        <v>9.5</v>
+      </c>
+      <c r="AE221">
+        <v>1.25</v>
+      </c>
+      <c r="AF221">
+        <v>3.75</v>
+      </c>
+      <c r="AG221">
+        <v>1.8</v>
+      </c>
+      <c r="AH221">
+        <v>1.94</v>
+      </c>
+      <c r="AI221">
+        <v>1.73</v>
+      </c>
+      <c r="AJ221">
+        <v>1.95</v>
+      </c>
+      <c r="AK221">
+        <v>1.2</v>
+      </c>
+      <c r="AL221">
+        <v>1.26</v>
+      </c>
+      <c r="AM221">
+        <v>2.05</v>
+      </c>
+      <c r="AN221">
+        <v>1.23</v>
+      </c>
+      <c r="AO221">
+        <v>0.46</v>
+      </c>
+      <c r="AP221">
+        <v>1.47</v>
+      </c>
+      <c r="AQ221">
+        <v>0.6</v>
+      </c>
+      <c r="AR221">
+        <v>1.54</v>
+      </c>
+      <c r="AS221">
+        <v>1.15</v>
+      </c>
+      <c r="AT221">
+        <v>2.69</v>
+      </c>
+      <c r="AU221">
         <v>5</v>
       </c>
-      <c r="O221" t="s">
-        <v>242</v>
-      </c>
-      <c r="P221" t="s">
-        <v>196</v>
-      </c>
-      <c r="Q221">
-        <v>1.78</v>
-      </c>
-      <c r="R221">
-        <v>2.45</v>
-      </c>
-      <c r="S221">
-        <v>6.5</v>
-      </c>
-      <c r="T221">
-        <v>1.3</v>
-      </c>
-      <c r="U221">
-        <v>3.25</v>
-      </c>
-      <c r="V221">
-        <v>2.35</v>
-      </c>
-      <c r="W221">
-        <v>1.52</v>
-      </c>
-      <c r="X221">
-        <v>5.5</v>
-      </c>
-      <c r="Y221">
-        <v>1.13</v>
-      </c>
-      <c r="Z221">
-        <v>1.33</v>
-      </c>
-      <c r="AA221">
-        <v>5.2</v>
-      </c>
-      <c r="AB221">
-        <v>8.1</v>
-      </c>
-      <c r="AC221">
-        <v>1.03</v>
-      </c>
-      <c r="AD221">
-        <v>11</v>
-      </c>
-      <c r="AE221">
-        <v>1.2</v>
-      </c>
-      <c r="AF221">
-        <v>4.33</v>
-      </c>
-      <c r="AG221">
-        <v>1.66</v>
-      </c>
-      <c r="AH221">
-        <v>2.22</v>
-      </c>
-      <c r="AI221">
-        <v>1.95</v>
-      </c>
-      <c r="AJ221">
-        <v>1.73</v>
-      </c>
-      <c r="AK221">
-        <v>1.08</v>
-      </c>
-      <c r="AL221">
-        <v>1.16</v>
-      </c>
-      <c r="AM221">
-        <v>3.1</v>
-      </c>
-      <c r="AN221">
-        <v>2.08</v>
-      </c>
-      <c r="AO221">
-        <v>1.15</v>
-      </c>
-      <c r="AP221">
-        <v>2.2</v>
-      </c>
-      <c r="AQ221">
-        <v>1</v>
-      </c>
-      <c r="AR221">
-        <v>1.82</v>
-      </c>
-      <c r="AS221">
-        <v>1.24</v>
-      </c>
-      <c r="AT221">
-        <v>3.06</v>
-      </c>
-      <c r="AU221">
-        <v>14</v>
-      </c>
       <c r="AV221">
+        <v>8</v>
+      </c>
+      <c r="AW221">
+        <v>5</v>
+      </c>
+      <c r="AX221">
+        <v>8</v>
+      </c>
+      <c r="AY221">
+        <v>10</v>
+      </c>
+      <c r="AZ221">
+        <v>18</v>
+      </c>
+      <c r="BA221">
         <v>3</v>
       </c>
-      <c r="AW221">
-        <v>7</v>
-      </c>
-      <c r="AX221">
-        <v>2</v>
-      </c>
-      <c r="AY221">
-        <v>25</v>
-      </c>
-      <c r="AZ221">
-        <v>5</v>
-      </c>
-      <c r="BA221">
-        <v>2</v>
-      </c>
       <c r="BB221">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC221">
         <v>7</v>
       </c>
       <c r="BD221">
-        <v>1.27</v>
+        <v>1.47</v>
       </c>
       <c r="BE221">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BF221">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="BG221">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="BH221">
-        <v>3.15</v>
+        <v>3.9</v>
       </c>
       <c r="BI221">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BJ221">
-        <v>2.33</v>
+        <v>2.8</v>
       </c>
       <c r="BK221">
-        <v>1.83</v>
+        <v>1.63</v>
       </c>
       <c r="BL221">
-        <v>1.85</v>
+        <v>2.15</v>
       </c>
       <c r="BM221">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="BN221">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="BO221">
-        <v>2.9</v>
+        <v>2.48</v>
       </c>
       <c r="BP221">
-        <v>1.34</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="222" spans="1:68">
@@ -46965,7 +46968,7 @@
         <v>221</v>
       </c>
       <c r="B222">
-        <v>7453637</v>
+        <v>7453635</v>
       </c>
       <c r="C222" t="s">
         <v>68</v>
@@ -46974,196 +46977,196 @@
         <v>69</v>
       </c>
       <c r="E222" s="2">
-        <v>45718.5</v>
+        <v>45717.69791666666</v>
       </c>
       <c r="F222">
         <v>28</v>
       </c>
       <c r="G222" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="H222" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="I222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J222">
         <v>0</v>
       </c>
       <c r="K222">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L222">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M222">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N222">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="O222" t="s">
-        <v>95</v>
+        <v>242</v>
       </c>
       <c r="P222" t="s">
-        <v>87</v>
+        <v>196</v>
       </c>
       <c r="Q222">
-        <v>4.33</v>
+        <v>1.78</v>
       </c>
       <c r="R222">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="S222">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="T222">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U222">
         <v>3.25</v>
       </c>
       <c r="V222">
-        <v>2.63</v>
+        <v>2.35</v>
       </c>
       <c r="W222">
-        <v>1.44</v>
+        <v>1.52</v>
       </c>
       <c r="X222">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="Y222">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="Z222">
-        <v>3.09</v>
+        <v>1.33</v>
       </c>
       <c r="AA222">
-        <v>3.39</v>
+        <v>5.2</v>
       </c>
       <c r="AB222">
-        <v>2.21</v>
+        <v>8.1</v>
       </c>
       <c r="AC222">
         <v>1.03</v>
       </c>
       <c r="AD222">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AE222">
+        <v>1.2</v>
+      </c>
+      <c r="AF222">
+        <v>4.33</v>
+      </c>
+      <c r="AG222">
+        <v>1.66</v>
+      </c>
+      <c r="AH222">
+        <v>2.22</v>
+      </c>
+      <c r="AI222">
+        <v>1.95</v>
+      </c>
+      <c r="AJ222">
+        <v>1.73</v>
+      </c>
+      <c r="AK222">
+        <v>1.08</v>
+      </c>
+      <c r="AL222">
+        <v>1.16</v>
+      </c>
+      <c r="AM222">
+        <v>3.1</v>
+      </c>
+      <c r="AN222">
+        <v>2.08</v>
+      </c>
+      <c r="AO222">
+        <v>1.15</v>
+      </c>
+      <c r="AP222">
+        <v>2.2</v>
+      </c>
+      <c r="AQ222">
+        <v>1</v>
+      </c>
+      <c r="AR222">
+        <v>1.82</v>
+      </c>
+      <c r="AS222">
         <v>1.24</v>
       </c>
-      <c r="AF222">
-        <v>3.89</v>
-      </c>
-      <c r="AG222">
-        <v>1.8</v>
-      </c>
-      <c r="AH222">
-        <v>1.94</v>
-      </c>
-      <c r="AI222">
-        <v>1.67</v>
-      </c>
-      <c r="AJ222">
-        <v>2.1</v>
-      </c>
-      <c r="AK222">
-        <v>1.87</v>
-      </c>
-      <c r="AL222">
+      <c r="AT222">
+        <v>3.06</v>
+      </c>
+      <c r="AU222">
+        <v>14</v>
+      </c>
+      <c r="AV222">
+        <v>3</v>
+      </c>
+      <c r="AW222">
+        <v>7</v>
+      </c>
+      <c r="AX222">
+        <v>2</v>
+      </c>
+      <c r="AY222">
+        <v>25</v>
+      </c>
+      <c r="AZ222">
+        <v>5</v>
+      </c>
+      <c r="BA222">
+        <v>2</v>
+      </c>
+      <c r="BB222">
+        <v>5</v>
+      </c>
+      <c r="BC222">
+        <v>7</v>
+      </c>
+      <c r="BD222">
         <v>1.27</v>
       </c>
-      <c r="AM222">
-        <v>1.25</v>
-      </c>
-      <c r="AN222">
-        <v>1</v>
-      </c>
-      <c r="AO222">
-        <v>0.92</v>
-      </c>
-      <c r="AP222">
-        <v>1.07</v>
-      </c>
-      <c r="AQ222">
-        <v>1</v>
-      </c>
-      <c r="AR222">
-        <v>1.28</v>
-      </c>
-      <c r="AS222">
-        <v>1.48</v>
-      </c>
-      <c r="AT222">
-        <v>2.76</v>
-      </c>
-      <c r="AU222">
-        <v>5</v>
-      </c>
-      <c r="AV222">
+      <c r="BE222">
         <v>8</v>
       </c>
-      <c r="AW222">
-        <v>9</v>
-      </c>
-      <c r="AX222">
-        <v>9</v>
-      </c>
-      <c r="AY222">
-        <v>15</v>
-      </c>
-      <c r="AZ222">
-        <v>18</v>
-      </c>
-      <c r="BA222">
-        <v>4</v>
-      </c>
-      <c r="BB222">
-        <v>9</v>
-      </c>
-      <c r="BC222">
-        <v>13</v>
-      </c>
-      <c r="BD222">
+      <c r="BF222">
+        <v>3.95</v>
+      </c>
+      <c r="BG222">
+        <v>1.3</v>
+      </c>
+      <c r="BH222">
+        <v>3.15</v>
+      </c>
+      <c r="BI222">
+        <v>1.5</v>
+      </c>
+      <c r="BJ222">
         <v>2.33</v>
       </c>
-      <c r="BE222">
-        <v>6.75</v>
-      </c>
-      <c r="BF222">
-        <v>1.73</v>
-      </c>
-      <c r="BG222">
-        <v>1.24</v>
-      </c>
-      <c r="BH222">
-        <v>3.55</v>
-      </c>
-      <c r="BI222">
-        <v>1.42</v>
-      </c>
-      <c r="BJ222">
-        <v>2.65</v>
-      </c>
       <c r="BK222">
-        <v>1.68</v>
+        <v>1.83</v>
       </c>
       <c r="BL222">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="BM222">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="BN222">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="BO222">
-        <v>2.55</v>
+        <v>2.9</v>
       </c>
       <c r="BP222">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="223" spans="1:68">
@@ -47171,7 +47174,7 @@
         <v>222</v>
       </c>
       <c r="B223">
-        <v>7453636</v>
+        <v>7453637</v>
       </c>
       <c r="C223" t="s">
         <v>68</v>
@@ -47180,196 +47183,196 @@
         <v>69</v>
       </c>
       <c r="E223" s="2">
-        <v>45718.60416666666</v>
+        <v>45718.5</v>
       </c>
       <c r="F223">
         <v>28</v>
       </c>
       <c r="G223" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H223" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J223">
         <v>0</v>
       </c>
       <c r="K223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L223">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M223">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N223">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O223" t="s">
+        <v>95</v>
+      </c>
+      <c r="P223" t="s">
         <v>87</v>
-      </c>
-      <c r="P223" t="s">
-        <v>344</v>
       </c>
       <c r="Q223">
         <v>4.33</v>
       </c>
       <c r="R223">
+        <v>2.25</v>
+      </c>
+      <c r="S223">
+        <v>2.5</v>
+      </c>
+      <c r="T223">
+        <v>1.33</v>
+      </c>
+      <c r="U223">
+        <v>3.25</v>
+      </c>
+      <c r="V223">
+        <v>2.63</v>
+      </c>
+      <c r="W223">
+        <v>1.44</v>
+      </c>
+      <c r="X223">
+        <v>6.5</v>
+      </c>
+      <c r="Y223">
+        <v>1.11</v>
+      </c>
+      <c r="Z223">
+        <v>3.09</v>
+      </c>
+      <c r="AA223">
+        <v>3.39</v>
+      </c>
+      <c r="AB223">
+        <v>2.21</v>
+      </c>
+      <c r="AC223">
+        <v>1.03</v>
+      </c>
+      <c r="AD223">
+        <v>13</v>
+      </c>
+      <c r="AE223">
+        <v>1.24</v>
+      </c>
+      <c r="AF223">
+        <v>3.89</v>
+      </c>
+      <c r="AG223">
+        <v>1.8</v>
+      </c>
+      <c r="AH223">
+        <v>1.94</v>
+      </c>
+      <c r="AI223">
+        <v>1.67</v>
+      </c>
+      <c r="AJ223">
         <v>2.1</v>
       </c>
-      <c r="S223">
-        <v>2.63</v>
-      </c>
-      <c r="T223">
-        <v>1.44</v>
-      </c>
-      <c r="U223">
-        <v>2.63</v>
-      </c>
-      <c r="V223">
-        <v>3.25</v>
-      </c>
-      <c r="W223">
-        <v>1.33</v>
-      </c>
-      <c r="X223">
-        <v>9</v>
-      </c>
-      <c r="Y223">
+      <c r="AK223">
+        <v>1.87</v>
+      </c>
+      <c r="AL223">
+        <v>1.27</v>
+      </c>
+      <c r="AM223">
+        <v>1.25</v>
+      </c>
+      <c r="AN223">
+        <v>1</v>
+      </c>
+      <c r="AO223">
+        <v>0.92</v>
+      </c>
+      <c r="AP223">
         <v>1.07</v>
       </c>
-      <c r="Z223">
-        <v>3.95</v>
-      </c>
-      <c r="AA223">
-        <v>3.47</v>
-      </c>
-      <c r="AB223">
-        <v>1.89</v>
-      </c>
-      <c r="AC223">
-        <v>1.05</v>
-      </c>
-      <c r="AD223">
-        <v>8.91</v>
-      </c>
-      <c r="AE223">
-        <v>1.34</v>
-      </c>
-      <c r="AF223">
-        <v>3.14</v>
-      </c>
-      <c r="AG223">
-        <v>1.91</v>
-      </c>
-      <c r="AH223">
-        <v>1.83</v>
-      </c>
-      <c r="AI223">
-        <v>1.95</v>
-      </c>
-      <c r="AJ223">
-        <v>1.8</v>
-      </c>
-      <c r="AK223">
-        <v>1.8</v>
-      </c>
-      <c r="AL223">
-        <v>1.3</v>
-      </c>
-      <c r="AM223">
-        <v>1.26</v>
-      </c>
-      <c r="AN223">
-        <v>1.85</v>
-      </c>
-      <c r="AO223">
-        <v>1.62</v>
-      </c>
-      <c r="AP223">
-        <v>1.67</v>
-      </c>
       <c r="AQ223">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="AR223">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AS223">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="AT223">
-        <v>2.57</v>
+        <v>2.76</v>
       </c>
       <c r="AU223">
         <v>5</v>
       </c>
       <c r="AV223">
+        <v>8</v>
+      </c>
+      <c r="AW223">
+        <v>9</v>
+      </c>
+      <c r="AX223">
+        <v>9</v>
+      </c>
+      <c r="AY223">
+        <v>15</v>
+      </c>
+      <c r="AZ223">
+        <v>18</v>
+      </c>
+      <c r="BA223">
         <v>4</v>
       </c>
-      <c r="AW223">
-        <v>7</v>
-      </c>
-      <c r="AX223">
-        <v>5</v>
-      </c>
-      <c r="AY223">
+      <c r="BB223">
+        <v>9</v>
+      </c>
+      <c r="BC223">
         <v>13</v>
       </c>
-      <c r="AZ223">
-        <v>12</v>
-      </c>
-      <c r="BA223">
-        <v>3</v>
-      </c>
-      <c r="BB223">
-        <v>4</v>
-      </c>
-      <c r="BC223">
-        <v>7</v>
-      </c>
       <c r="BD223">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BE223">
         <v>6.75</v>
       </c>
       <c r="BF223">
+        <v>1.73</v>
+      </c>
+      <c r="BG223">
+        <v>1.24</v>
+      </c>
+      <c r="BH223">
+        <v>3.55</v>
+      </c>
+      <c r="BI223">
+        <v>1.42</v>
+      </c>
+      <c r="BJ223">
+        <v>2.65</v>
+      </c>
+      <c r="BK223">
         <v>1.68</v>
       </c>
-      <c r="BG223">
-        <v>1.34</v>
-      </c>
-      <c r="BH223">
-        <v>2.9</v>
-      </c>
-      <c r="BI223">
-        <v>1.58</v>
-      </c>
-      <c r="BJ223">
-        <v>2.18</v>
-      </c>
-      <c r="BK223">
-        <v>1.96</v>
-      </c>
       <c r="BL223">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="BM223">
-        <v>2.48</v>
+        <v>2.05</v>
       </c>
       <c r="BN223">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="BO223">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="BP223">
-        <v>1.28</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="224" spans="1:68">
@@ -47377,7 +47380,7 @@
         <v>223</v>
       </c>
       <c r="B224">
-        <v>7453639</v>
+        <v>7453636</v>
       </c>
       <c r="C224" t="s">
         <v>68</v>
@@ -47386,16 +47389,16 @@
         <v>69</v>
       </c>
       <c r="E224" s="2">
-        <v>45718.63541666666</v>
+        <v>45718.60416666666</v>
       </c>
       <c r="F224">
         <v>28</v>
       </c>
       <c r="G224" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H224" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="I224">
         <v>0</v>
@@ -47410,172 +47413,172 @@
         <v>0</v>
       </c>
       <c r="M224">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N224">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O224" t="s">
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>87</v>
+        <v>345</v>
       </c>
       <c r="Q224">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="R224">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S224">
-        <v>3.2</v>
+        <v>2.63</v>
       </c>
       <c r="T224">
+        <v>1.44</v>
+      </c>
+      <c r="U224">
+        <v>2.63</v>
+      </c>
+      <c r="V224">
+        <v>3.25</v>
+      </c>
+      <c r="W224">
+        <v>1.33</v>
+      </c>
+      <c r="X224">
+        <v>9</v>
+      </c>
+      <c r="Y224">
+        <v>1.07</v>
+      </c>
+      <c r="Z224">
+        <v>3.95</v>
+      </c>
+      <c r="AA224">
+        <v>3.47</v>
+      </c>
+      <c r="AB224">
+        <v>1.89</v>
+      </c>
+      <c r="AC224">
+        <v>1.05</v>
+      </c>
+      <c r="AD224">
+        <v>8.91</v>
+      </c>
+      <c r="AE224">
+        <v>1.34</v>
+      </c>
+      <c r="AF224">
+        <v>3.14</v>
+      </c>
+      <c r="AG224">
+        <v>1.91</v>
+      </c>
+      <c r="AH224">
+        <v>1.83</v>
+      </c>
+      <c r="AI224">
+        <v>1.95</v>
+      </c>
+      <c r="AJ224">
+        <v>1.8</v>
+      </c>
+      <c r="AK224">
+        <v>1.8</v>
+      </c>
+      <c r="AL224">
         <v>1.3</v>
       </c>
-      <c r="U224">
-        <v>3.4</v>
-      </c>
-      <c r="V224">
-        <v>2.5</v>
-      </c>
-      <c r="W224">
-        <v>1.5</v>
-      </c>
-      <c r="X224">
-        <v>6</v>
-      </c>
-      <c r="Y224">
-        <v>1.13</v>
-      </c>
-      <c r="Z224">
-        <v>2.46</v>
-      </c>
-      <c r="AA224">
-        <v>3.53</v>
-      </c>
-      <c r="AB224">
-        <v>2.63</v>
-      </c>
-      <c r="AC224">
-        <v>1.03</v>
-      </c>
-      <c r="AD224">
-        <v>15</v>
-      </c>
-      <c r="AE224">
-        <v>1.19</v>
-      </c>
-      <c r="AF224">
-        <v>4.45</v>
-      </c>
-      <c r="AG224">
-        <v>1.61</v>
-      </c>
-      <c r="AH224">
-        <v>2.15</v>
-      </c>
-      <c r="AI224">
-        <v>1.53</v>
-      </c>
-      <c r="AJ224">
-        <v>2.38</v>
-      </c>
-      <c r="AK224">
-        <v>1.46</v>
-      </c>
-      <c r="AL224">
-        <v>1.27</v>
-      </c>
       <c r="AM224">
-        <v>1.52</v>
+        <v>1.26</v>
       </c>
       <c r="AN224">
         <v>1.85</v>
       </c>
       <c r="AO224">
-        <v>0.85</v>
+        <v>1.62</v>
       </c>
       <c r="AP224">
-        <v>1.87</v>
+        <v>1.67</v>
       </c>
       <c r="AQ224">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="AR224">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AS224">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="AT224">
-        <v>2.86</v>
+        <v>2.57</v>
       </c>
       <c r="AU224">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AV224">
         <v>4</v>
       </c>
       <c r="AW224">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX224">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="AY224">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AZ224">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="BA224">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BB224">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BC224">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BD224">
-        <v>1.94</v>
+        <v>2.4</v>
       </c>
       <c r="BE224">
         <v>6.75</v>
       </c>
       <c r="BF224">
-        <v>2.05</v>
+        <v>1.68</v>
       </c>
       <c r="BG224">
-        <v>1.2</v>
+        <v>1.34</v>
       </c>
       <c r="BH224">
-        <v>3.95</v>
+        <v>2.9</v>
       </c>
       <c r="BI224">
-        <v>1.35</v>
+        <v>1.58</v>
       </c>
       <c r="BJ224">
-        <v>2.9</v>
+        <v>2.18</v>
       </c>
       <c r="BK224">
-        <v>1.58</v>
+        <v>1.96</v>
       </c>
       <c r="BL224">
-        <v>2.18</v>
+        <v>1.74</v>
       </c>
       <c r="BM224">
-        <v>1.93</v>
+        <v>2.48</v>
       </c>
       <c r="BN224">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="BO224">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="BP224">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="225" spans="1:68">
@@ -47583,7 +47586,7 @@
         <v>224</v>
       </c>
       <c r="B225">
-        <v>7453646</v>
+        <v>7453639</v>
       </c>
       <c r="C225" t="s">
         <v>68</v>
@@ -47592,196 +47595,196 @@
         <v>69</v>
       </c>
       <c r="E225" s="2">
-        <v>45723.69791666666</v>
+        <v>45718.63541666666</v>
       </c>
       <c r="F225">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G225" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H225" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="I225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J225">
         <v>0</v>
       </c>
       <c r="K225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L225">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M225">
         <v>0</v>
       </c>
       <c r="N225">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O225" t="s">
-        <v>243</v>
+        <v>87</v>
       </c>
       <c r="P225" t="s">
         <v>87</v>
       </c>
       <c r="Q225">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R225">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="S225">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="T225">
         <v>1.3</v>
       </c>
       <c r="U225">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V225">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="W225">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X225">
-        <v>5.85</v>
+        <v>6</v>
       </c>
       <c r="Y225">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Z225">
-        <v>1.62</v>
+        <v>2.46</v>
       </c>
       <c r="AA225">
-        <v>4.2</v>
+        <v>3.53</v>
       </c>
       <c r="AB225">
-        <v>4.7</v>
+        <v>2.63</v>
       </c>
       <c r="AC225">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AD225">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE225">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AF225">
-        <v>4.33</v>
+        <v>4.45</v>
       </c>
       <c r="AG225">
         <v>1.61</v>
       </c>
       <c r="AH225">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="AI225">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="AJ225">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AK225">
-        <v>1.15</v>
+        <v>1.46</v>
       </c>
       <c r="AL225">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
       <c r="AM225">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="AN225">
-        <v>1.36</v>
+        <v>1.85</v>
       </c>
       <c r="AO225">
-        <v>0.14</v>
+        <v>0.85</v>
       </c>
       <c r="AP225">
-        <v>1.47</v>
+        <v>1.87</v>
       </c>
       <c r="AQ225">
-        <v>0.13</v>
+        <v>1</v>
       </c>
       <c r="AR225">
-        <v>1.52</v>
+        <v>1.31</v>
       </c>
       <c r="AS225">
-        <v>1.14</v>
+        <v>1.55</v>
       </c>
       <c r="AT225">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="AU225">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AV225">
         <v>4</v>
       </c>
       <c r="AW225">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AX225">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AY225">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AZ225">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="BA225">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BB225">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC225">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD225">
-        <v>1.36</v>
+        <v>1.94</v>
       </c>
       <c r="BE225">
-        <v>7.5</v>
+        <v>6.75</v>
       </c>
       <c r="BF225">
-        <v>3.4</v>
+        <v>2.05</v>
       </c>
       <c r="BG225">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="BH225">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="BI225">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BJ225">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="BK225">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="BL225">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="BM225">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BN225">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="BO225">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="BP225">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="226" spans="1:68">
@@ -47789,7 +47792,7 @@
         <v>225</v>
       </c>
       <c r="B226">
-        <v>7453644</v>
+        <v>7453646</v>
       </c>
       <c r="C226" t="s">
         <v>68</v>
@@ -47798,16 +47801,16 @@
         <v>69</v>
       </c>
       <c r="E226" s="2">
-        <v>45724.5</v>
+        <v>45723.69791666666</v>
       </c>
       <c r="F226">
         <v>29</v>
       </c>
       <c r="G226" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H226" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="I226">
         <v>1</v>
@@ -47828,100 +47831,100 @@
         <v>2</v>
       </c>
       <c r="O226" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="P226" t="s">
         <v>87</v>
       </c>
       <c r="Q226">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="R226">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="S226">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="T226">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="U226">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="V226">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="W226">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="X226">
-        <v>6.75</v>
+        <v>5.85</v>
       </c>
       <c r="Y226">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="Z226">
-        <v>2.71</v>
+        <v>1.62</v>
       </c>
       <c r="AA226">
-        <v>3.23</v>
+        <v>4.2</v>
       </c>
       <c r="AB226">
-        <v>2.55</v>
+        <v>4.7</v>
       </c>
       <c r="AC226">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="AD226">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE226">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AF226">
-        <v>3.45</v>
+        <v>4.33</v>
       </c>
       <c r="AG226">
-        <v>1.89</v>
+        <v>1.61</v>
       </c>
       <c r="AH226">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AI226">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AJ226">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AK226">
+        <v>1.15</v>
+      </c>
+      <c r="AL226">
+        <v>1.18</v>
+      </c>
+      <c r="AM226">
+        <v>2.3</v>
+      </c>
+      <c r="AN226">
         <v>1.36</v>
       </c>
-      <c r="AL226">
-        <v>1.29</v>
-      </c>
-      <c r="AM226">
-        <v>1.62</v>
-      </c>
-      <c r="AN226">
-        <v>1</v>
-      </c>
       <c r="AO226">
-        <v>0.64</v>
+        <v>0.14</v>
       </c>
       <c r="AP226">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AQ226">
-        <v>0.6</v>
+        <v>0.13</v>
       </c>
       <c r="AR226">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AS226">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AT226">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="AU226">
         <v>7</v>
@@ -47930,64 +47933,64 @@
         <v>4</v>
       </c>
       <c r="AW226">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="AX226">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AY226">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AZ226">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA226">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB226">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="BC226">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="BD226">
-        <v>1.71</v>
+        <v>1.36</v>
       </c>
       <c r="BE226">
-        <v>6.75</v>
+        <v>7.5</v>
       </c>
       <c r="BF226">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="BG226">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="BH226">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BI226">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BJ226">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="BK226">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="BL226">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="BM226">
-        <v>2.07</v>
+        <v>1.98</v>
       </c>
       <c r="BN226">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="BO226">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="BP226">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="227" spans="1:68">
@@ -47995,7 +47998,7 @@
         <v>226</v>
       </c>
       <c r="B227">
-        <v>7453648</v>
+        <v>7453644</v>
       </c>
       <c r="C227" t="s">
         <v>68</v>
@@ -48004,82 +48007,82 @@
         <v>69</v>
       </c>
       <c r="E227" s="2">
-        <v>45724.59375</v>
+        <v>45724.5</v>
       </c>
       <c r="F227">
         <v>29</v>
       </c>
       <c r="G227" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H227" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K227">
         <v>1</v>
       </c>
       <c r="L227">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M227">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N227">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O227" t="s">
+        <v>244</v>
+      </c>
+      <c r="P227" t="s">
         <v>87</v>
       </c>
-      <c r="P227" t="s">
-        <v>209</v>
-      </c>
       <c r="Q227">
+        <v>2.75</v>
+      </c>
+      <c r="R227">
+        <v>2.1</v>
+      </c>
+      <c r="S227">
+        <v>3.4</v>
+      </c>
+      <c r="T227">
+        <v>1.37</v>
+      </c>
+      <c r="U227">
+        <v>2.85</v>
+      </c>
+      <c r="V227">
         <v>2.7</v>
       </c>
-      <c r="R227">
-        <v>2.15</v>
-      </c>
-      <c r="S227">
-        <v>3.5</v>
-      </c>
-      <c r="T227">
-        <v>1.35</v>
-      </c>
-      <c r="U227">
-        <v>2.9</v>
-      </c>
-      <c r="V227">
-        <v>2.6</v>
-      </c>
       <c r="W227">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="X227">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="Y227">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Z227">
-        <v>2.2</v>
+        <v>2.71</v>
       </c>
       <c r="AA227">
-        <v>3.36</v>
+        <v>3.23</v>
       </c>
       <c r="AB227">
-        <v>3.14</v>
+        <v>2.55</v>
       </c>
       <c r="AC227">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD227">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="AE227">
         <v>1.3</v>
@@ -48088,94 +48091,94 @@
         <v>3.45</v>
       </c>
       <c r="AG227">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="AH227">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AI227">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AJ227">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AK227">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AL227">
         <v>1.29</v>
       </c>
       <c r="AM227">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AN227">
-        <v>1.57</v>
+        <v>1</v>
       </c>
       <c r="AO227">
-        <v>0.86</v>
+        <v>0.64</v>
       </c>
       <c r="AP227">
-        <v>1.47</v>
+        <v>1.13</v>
       </c>
       <c r="AQ227">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="AR227">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="AS227">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="AT227">
-        <v>3.22</v>
+        <v>2.55</v>
       </c>
       <c r="AU227">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AV227">
+        <v>4</v>
+      </c>
+      <c r="AW227">
+        <v>16</v>
+      </c>
+      <c r="AX227">
         <v>6</v>
       </c>
-      <c r="AW227">
-        <v>9</v>
-      </c>
-      <c r="AX227">
+      <c r="AY227">
+        <v>26</v>
+      </c>
+      <c r="AZ227">
+        <v>11</v>
+      </c>
+      <c r="BA227">
+        <v>5</v>
+      </c>
+      <c r="BB227">
         <v>4</v>
-      </c>
-      <c r="AY227">
-        <v>14</v>
-      </c>
-      <c r="AZ227">
-        <v>10</v>
-      </c>
-      <c r="BA227">
-        <v>6</v>
-      </c>
-      <c r="BB227">
-        <v>3</v>
       </c>
       <c r="BC227">
         <v>9</v>
       </c>
       <c r="BD227">
-        <v>1.77</v>
+        <v>1.71</v>
       </c>
       <c r="BE227">
         <v>6.75</v>
       </c>
       <c r="BF227">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="BG227">
         <v>1.24</v>
       </c>
       <c r="BH227">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="BI227">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="BJ227">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="BK227">
         <v>1.7</v>
@@ -48187,13 +48190,13 @@
         <v>2.07</v>
       </c>
       <c r="BN227">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="BO227">
-        <v>2.65</v>
+        <v>2.6</v>
       </c>
       <c r="BP227">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="228" spans="1:68">
@@ -48201,7 +48204,7 @@
         <v>227</v>
       </c>
       <c r="B228">
-        <v>7453649</v>
+        <v>7453648</v>
       </c>
       <c r="C228" t="s">
         <v>68</v>
@@ -48210,25 +48213,25 @@
         <v>69</v>
       </c>
       <c r="E228" s="2">
-        <v>45724.69791666666</v>
+        <v>45724.59375</v>
       </c>
       <c r="F228">
         <v>29</v>
       </c>
       <c r="G228" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H228" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="I228">
         <v>0</v>
       </c>
       <c r="J228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L228">
         <v>0</v>
@@ -48243,163 +48246,163 @@
         <v>87</v>
       </c>
       <c r="P228" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="Q228">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="R228">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S228">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="T228">
+        <v>1.35</v>
+      </c>
+      <c r="U228">
+        <v>2.9</v>
+      </c>
+      <c r="V228">
+        <v>2.6</v>
+      </c>
+      <c r="W228">
+        <v>1.43</v>
+      </c>
+      <c r="X228">
+        <v>6.5</v>
+      </c>
+      <c r="Y228">
+        <v>1.1</v>
+      </c>
+      <c r="Z228">
+        <v>2.2</v>
+      </c>
+      <c r="AA228">
+        <v>3.36</v>
+      </c>
+      <c r="AB228">
+        <v>3.14</v>
+      </c>
+      <c r="AC228">
+        <v>1.06</v>
+      </c>
+      <c r="AD228">
+        <v>8.5</v>
+      </c>
+      <c r="AE228">
         <v>1.3</v>
       </c>
-      <c r="U228">
-        <v>3.2</v>
-      </c>
-      <c r="V228">
-        <v>2.37</v>
-      </c>
-      <c r="W228">
-        <v>1.51</v>
-      </c>
-      <c r="X228">
-        <v>5.5</v>
-      </c>
-      <c r="Y228">
-        <v>1.12</v>
-      </c>
-      <c r="Z228">
-        <v>4.1</v>
-      </c>
-      <c r="AA228">
-        <v>3.87</v>
-      </c>
-      <c r="AB228">
-        <v>1.76</v>
-      </c>
-      <c r="AC228">
-        <v>1.04</v>
-      </c>
-      <c r="AD228">
-        <v>10</v>
-      </c>
-      <c r="AE228">
-        <v>1.22</v>
-      </c>
       <c r="AF228">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="AG228">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="AH228">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AI228">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AJ228">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AK228">
-        <v>1.98</v>
+        <v>1.35</v>
       </c>
       <c r="AL228">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AM228">
-        <v>1.23</v>
+        <v>1.65</v>
       </c>
       <c r="AN228">
-        <v>1.21</v>
+        <v>1.57</v>
       </c>
       <c r="AO228">
-        <v>1.71</v>
+        <v>0.86</v>
       </c>
       <c r="AP228">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="AQ228">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="AR228">
-        <v>1.11</v>
+        <v>1.7</v>
       </c>
       <c r="AS228">
-        <v>1.67</v>
+        <v>1.52</v>
       </c>
       <c r="AT228">
-        <v>2.78</v>
+        <v>3.22</v>
       </c>
       <c r="AU228">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AV228">
         <v>6</v>
       </c>
       <c r="AW228">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX228">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="AY228">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="AZ228">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="BA228">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BB228">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BC228">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD228">
+        <v>1.77</v>
+      </c>
+      <c r="BE228">
+        <v>6.75</v>
+      </c>
+      <c r="BF228">
+        <v>2.23</v>
+      </c>
+      <c r="BG228">
+        <v>1.24</v>
+      </c>
+      <c r="BH228">
+        <v>3.55</v>
+      </c>
+      <c r="BI228">
+        <v>1.43</v>
+      </c>
+      <c r="BJ228">
         <v>2.55</v>
       </c>
-      <c r="BE228">
-        <v>6.4</v>
-      </c>
-      <c r="BF228">
-        <v>1.65</v>
-      </c>
-      <c r="BG228">
-        <v>1.38</v>
-      </c>
-      <c r="BH228">
-        <v>2.8</v>
-      </c>
-      <c r="BI228">
-        <v>1.65</v>
-      </c>
-      <c r="BJ228">
-        <v>2.08</v>
-      </c>
       <c r="BK228">
-        <v>2.05</v>
+        <v>1.7</v>
       </c>
       <c r="BL228">
-        <v>1.68</v>
+        <v>2.02</v>
       </c>
       <c r="BM228">
-        <v>2.55</v>
+        <v>2.07</v>
       </c>
       <c r="BN228">
-        <v>1.43</v>
+        <v>1.66</v>
       </c>
       <c r="BO228">
-        <v>3.4</v>
+        <v>2.65</v>
       </c>
       <c r="BP228">
-        <v>1.26</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="229" spans="1:68">
@@ -48407,7 +48410,7 @@
         <v>228</v>
       </c>
       <c r="B229">
-        <v>7453645</v>
+        <v>7453649</v>
       </c>
       <c r="C229" t="s">
         <v>68</v>
@@ -48416,196 +48419,196 @@
         <v>69</v>
       </c>
       <c r="E229" s="2">
-        <v>45725.39583333334</v>
+        <v>45724.69791666666</v>
       </c>
       <c r="F229">
         <v>29</v>
       </c>
       <c r="G229" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H229" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="I229">
         <v>0</v>
       </c>
       <c r="J229">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K229">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M229">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N229">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O229" t="s">
-        <v>174</v>
+        <v>87</v>
       </c>
       <c r="P229" t="s">
-        <v>345</v>
+        <v>201</v>
       </c>
       <c r="Q229">
-        <v>4.75</v>
+        <v>4.1</v>
       </c>
       <c r="R229">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S229">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="T229">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="U229">
-        <v>2.75</v>
+        <v>3.2</v>
       </c>
       <c r="V229">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="W229">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="X229">
-        <v>8</v>
+        <v>5.5</v>
       </c>
       <c r="Y229">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="Z229">
+        <v>4.1</v>
+      </c>
+      <c r="AA229">
+        <v>3.87</v>
+      </c>
+      <c r="AB229">
+        <v>1.76</v>
+      </c>
+      <c r="AC229">
+        <v>1.04</v>
+      </c>
+      <c r="AD229">
+        <v>10</v>
+      </c>
+      <c r="AE229">
+        <v>1.22</v>
+      </c>
+      <c r="AF229">
         <v>4.2</v>
       </c>
-      <c r="AA229">
-        <v>3.55</v>
-      </c>
-      <c r="AB229">
-        <v>1.82</v>
-      </c>
-      <c r="AC229">
-        <v>1.05</v>
-      </c>
-      <c r="AD229">
-        <v>9</v>
-      </c>
-      <c r="AE229">
-        <v>1.3</v>
-      </c>
-      <c r="AF229">
-        <v>3.4</v>
-      </c>
       <c r="AG229">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AH229">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="AI229">
+        <v>1.62</v>
+      </c>
+      <c r="AJ229">
+        <v>2.15</v>
+      </c>
+      <c r="AK229">
+        <v>1.98</v>
+      </c>
+      <c r="AL229">
+        <v>1.24</v>
+      </c>
+      <c r="AM229">
+        <v>1.23</v>
+      </c>
+      <c r="AN229">
+        <v>1.21</v>
+      </c>
+      <c r="AO229">
+        <v>1.71</v>
+      </c>
+      <c r="AP229">
+        <v>1.13</v>
+      </c>
+      <c r="AQ229">
         <v>1.8</v>
       </c>
-      <c r="AJ229">
-        <v>1.95</v>
-      </c>
-      <c r="AK229">
-        <v>1.95</v>
-      </c>
-      <c r="AL229">
-        <v>1.27</v>
-      </c>
-      <c r="AM229">
-        <v>1.22</v>
-      </c>
-      <c r="AN229">
-        <v>1.5</v>
-      </c>
-      <c r="AO229">
-        <v>1.69</v>
-      </c>
-      <c r="AP229">
-        <v>1.4</v>
-      </c>
-      <c r="AQ229">
-        <v>1.79</v>
-      </c>
       <c r="AR229">
-        <v>1.79</v>
+        <v>1.11</v>
       </c>
       <c r="AS229">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AT229">
-        <v>3.5</v>
+        <v>2.78</v>
       </c>
       <c r="AU229">
         <v>5</v>
       </c>
       <c r="AV229">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AW229">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX229">
         <v>11</v>
       </c>
       <c r="AY229">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AZ229">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="BA229">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="BB229">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BC229">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="BD229">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BE229">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF229">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="BG229">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="BH229">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="BI229">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="BJ229">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="BK229">
-        <v>1.96</v>
+        <v>2.05</v>
       </c>
       <c r="BL229">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="BM229">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="BN229">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="BO229">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="BP229">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="230" spans="1:68">
@@ -48613,7 +48616,7 @@
         <v>229</v>
       </c>
       <c r="B230">
-        <v>7453647</v>
+        <v>7453645</v>
       </c>
       <c r="C230" t="s">
         <v>68</v>
@@ -48622,196 +48625,196 @@
         <v>69</v>
       </c>
       <c r="E230" s="2">
-        <v>45725.5</v>
+        <v>45725.39583333334</v>
       </c>
       <c r="F230">
         <v>29</v>
       </c>
       <c r="G230" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H230" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="I230">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J230">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K230">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L230">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M230">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N230">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O230" t="s">
-        <v>245</v>
+        <v>174</v>
       </c>
       <c r="P230" t="s">
-        <v>87</v>
+        <v>346</v>
       </c>
       <c r="Q230">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="R230">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="S230">
-        <v>2.88</v>
+        <v>2.4</v>
       </c>
       <c r="T230">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U230">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="V230">
-        <v>2.5</v>
+        <v>2.75</v>
       </c>
       <c r="W230">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="X230">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="Y230">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Z230">
-        <v>2.97</v>
+        <v>4.2</v>
       </c>
       <c r="AA230">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="AB230">
-        <v>2.21</v>
+        <v>1.82</v>
       </c>
       <c r="AC230">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="AD230">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AE230">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AF230">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="AG230">
-        <v>1.65</v>
+        <v>1.92</v>
       </c>
       <c r="AH230">
-        <v>2.15</v>
+        <v>1.82</v>
       </c>
       <c r="AI230">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AJ230">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AK230">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AL230">
         <v>1.27</v>
       </c>
       <c r="AM230">
-        <v>1.37</v>
+        <v>1.22</v>
       </c>
       <c r="AN230">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="AO230">
+        <v>1.64</v>
+      </c>
+      <c r="AP230">
+        <v>1.4</v>
+      </c>
+      <c r="AQ230">
+        <v>1.73</v>
+      </c>
+      <c r="AR230">
+        <v>1.79</v>
+      </c>
+      <c r="AS230">
         <v>1.71</v>
       </c>
-      <c r="AP230">
-        <v>1.47</v>
-      </c>
-      <c r="AQ230">
-        <v>1.6</v>
-      </c>
-      <c r="AR230">
-        <v>1.88</v>
-      </c>
-      <c r="AS230">
-        <v>1.34</v>
-      </c>
       <c r="AT230">
-        <v>3.22</v>
+        <v>3.5</v>
       </c>
       <c r="AU230">
         <v>5</v>
       </c>
       <c r="AV230">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AW230">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AX230">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AY230">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="AZ230">
         <v>18</v>
       </c>
       <c r="BA230">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BB230">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="BC230">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BD230">
-        <v>1.98</v>
+        <v>2.7</v>
       </c>
       <c r="BE230">
-        <v>6.75</v>
+        <v>6.5</v>
       </c>
       <c r="BF230">
-        <v>1.97</v>
+        <v>1.56</v>
       </c>
       <c r="BG230">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="BH230">
-        <v>3.55</v>
+        <v>2.9</v>
       </c>
       <c r="BI230">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="BJ230">
-        <v>2.6</v>
+        <v>2.18</v>
       </c>
       <c r="BK230">
-        <v>1.68</v>
+        <v>1.96</v>
       </c>
       <c r="BL230">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="BM230">
-        <v>2.05</v>
+        <v>2.48</v>
       </c>
       <c r="BN230">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="BO230">
-        <v>2.55</v>
+        <v>3.25</v>
       </c>
       <c r="BP230">
-        <v>1.43</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="231" spans="1:68">
@@ -48819,7 +48822,7 @@
         <v>230</v>
       </c>
       <c r="B231">
-        <v>7453643</v>
+        <v>7453647</v>
       </c>
       <c r="C231" t="s">
         <v>68</v>
@@ -48828,49 +48831,49 @@
         <v>69</v>
       </c>
       <c r="E231" s="2">
-        <v>45725.60416666666</v>
+        <v>45725.5</v>
       </c>
       <c r="F231">
         <v>29</v>
       </c>
       <c r="G231" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H231" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="I231">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J231">
         <v>0</v>
       </c>
       <c r="K231">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L231">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N231">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O231" t="s">
+        <v>245</v>
+      </c>
+      <c r="P231" t="s">
         <v>87</v>
       </c>
-      <c r="P231" t="s">
-        <v>346</v>
-      </c>
       <c r="Q231">
+        <v>3.5</v>
+      </c>
+      <c r="R231">
+        <v>2.3</v>
+      </c>
+      <c r="S231">
         <v>2.88</v>
-      </c>
-      <c r="R231">
-        <v>2.25</v>
-      </c>
-      <c r="S231">
-        <v>3.5</v>
       </c>
       <c r="T231">
         <v>1.33</v>
@@ -48879,25 +48882,25 @@
         <v>3.25</v>
       </c>
       <c r="V231">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="W231">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X231">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="Y231">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Z231">
-        <v>2.27</v>
+        <v>2.97</v>
       </c>
       <c r="AA231">
-        <v>3.36</v>
+        <v>3.57</v>
       </c>
       <c r="AB231">
-        <v>3.01</v>
+        <v>2.21</v>
       </c>
       <c r="AC231">
         <v>1.04</v>
@@ -48906,118 +48909,118 @@
         <v>10</v>
       </c>
       <c r="AE231">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF231">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="AG231">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AH231">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AI231">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AJ231">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AK231">
-        <v>1.39</v>
+        <v>1.65</v>
       </c>
       <c r="AL231">
         <v>1.27</v>
       </c>
       <c r="AM231">
-        <v>1.62</v>
+        <v>1.37</v>
       </c>
       <c r="AN231">
-        <v>1.93</v>
+        <v>1.36</v>
       </c>
       <c r="AO231">
-        <v>1.21</v>
+        <v>1.71</v>
       </c>
       <c r="AP231">
-        <v>1.8</v>
+        <v>1.47</v>
       </c>
       <c r="AQ231">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AR231">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AS231">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AT231">
-        <v>3.07</v>
+        <v>3.22</v>
       </c>
       <c r="AU231">
+        <v>5</v>
+      </c>
+      <c r="AV231">
+        <v>3</v>
+      </c>
+      <c r="AW231">
+        <v>5</v>
+      </c>
+      <c r="AX231">
+        <v>15</v>
+      </c>
+      <c r="AY231">
+        <v>11</v>
+      </c>
+      <c r="AZ231">
+        <v>18</v>
+      </c>
+      <c r="BA231">
         <v>7</v>
       </c>
-      <c r="AV231">
-        <v>6</v>
-      </c>
-      <c r="AW231">
-        <v>6</v>
-      </c>
-      <c r="AX231">
-        <v>7</v>
-      </c>
-      <c r="AY231">
-        <v>14</v>
-      </c>
-      <c r="AZ231">
+      <c r="BB231">
+        <v>9</v>
+      </c>
+      <c r="BC231">
         <v>16</v>
       </c>
-      <c r="BA231">
-        <v>8</v>
-      </c>
-      <c r="BB231">
-        <v>4</v>
-      </c>
-      <c r="BC231">
-        <v>12</v>
-      </c>
       <c r="BD231">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="BE231">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="BF231">
-        <v>2.43</v>
+        <v>1.97</v>
       </c>
       <c r="BG231">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BH231">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BI231">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BJ231">
+        <v>2.6</v>
+      </c>
+      <c r="BK231">
+        <v>1.68</v>
+      </c>
+      <c r="BL231">
+        <v>2.05</v>
+      </c>
+      <c r="BM231">
+        <v>2.05</v>
+      </c>
+      <c r="BN231">
+        <v>1.68</v>
+      </c>
+      <c r="BO231">
         <v>2.55</v>
       </c>
-      <c r="BK231">
-        <v>1.71</v>
-      </c>
-      <c r="BL231">
-        <v>2</v>
-      </c>
-      <c r="BM231">
-        <v>2.12</v>
-      </c>
-      <c r="BN231">
-        <v>1.64</v>
-      </c>
-      <c r="BO231">
-        <v>2.65</v>
-      </c>
       <c r="BP231">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="232" spans="1:68">
@@ -49025,7 +49028,7 @@
         <v>231</v>
       </c>
       <c r="B232">
-        <v>7453642</v>
+        <v>7453643</v>
       </c>
       <c r="C232" t="s">
         <v>68</v>
@@ -49034,49 +49037,49 @@
         <v>69</v>
       </c>
       <c r="E232" s="2">
-        <v>45725.63541666666</v>
+        <v>45725.60416666666</v>
       </c>
       <c r="F232">
         <v>29</v>
       </c>
       <c r="G232" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="H232" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J232">
         <v>0</v>
       </c>
       <c r="K232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L232">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N232">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O232" t="s">
-        <v>246</v>
+        <v>87</v>
       </c>
       <c r="P232" t="s">
-        <v>87</v>
+        <v>347</v>
       </c>
       <c r="Q232">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="R232">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="S232">
-        <v>7.5</v>
+        <v>3.5</v>
       </c>
       <c r="T232">
         <v>1.33</v>
@@ -49085,37 +49088,37 @@
         <v>3.25</v>
       </c>
       <c r="V232">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="W232">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X232">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y232">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z232">
-        <v>1.33</v>
+        <v>2.27</v>
       </c>
       <c r="AA232">
-        <v>5.2</v>
+        <v>3.36</v>
       </c>
       <c r="AB232">
-        <v>8</v>
+        <v>3.01</v>
       </c>
       <c r="AC232">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AD232">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE232">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AF232">
-        <v>4.5</v>
+        <v>3.85</v>
       </c>
       <c r="AG232">
         <v>1.7</v>
@@ -49124,106 +49127,106 @@
         <v>2.05</v>
       </c>
       <c r="AI232">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="AJ232">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AK232">
-        <v>1.09</v>
+        <v>1.39</v>
       </c>
       <c r="AL232">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="AM232">
-        <v>2.95</v>
+        <v>1.62</v>
       </c>
       <c r="AN232">
-        <v>2.14</v>
+        <v>1.93</v>
       </c>
       <c r="AO232">
-        <v>1</v>
+        <v>1.21</v>
       </c>
       <c r="AP232">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ232">
-        <v>0.93</v>
+        <v>1.33</v>
       </c>
       <c r="AR232">
-        <v>1.88</v>
+        <v>1.76</v>
       </c>
       <c r="AS232">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="AT232">
-        <v>2.95</v>
+        <v>3.07</v>
       </c>
       <c r="AU232">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AV232">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AW232">
         <v>6</v>
       </c>
       <c r="AX232">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AY232">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ232">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="BA232">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="BB232">
         <v>4</v>
       </c>
       <c r="BC232">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="BD232">
-        <v>1.21</v>
+        <v>1.66</v>
       </c>
       <c r="BE232">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="BF232">
-        <v>4.8</v>
+        <v>2.43</v>
       </c>
       <c r="BG232">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BH232">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BI232">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="BJ232">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BK232">
+        <v>1.71</v>
+      </c>
+      <c r="BL232">
+        <v>2</v>
+      </c>
+      <c r="BM232">
+        <v>2.12</v>
+      </c>
+      <c r="BN232">
         <v>1.64</v>
       </c>
-      <c r="BL232">
-        <v>2.12</v>
-      </c>
-      <c r="BM232">
-        <v>1.98</v>
-      </c>
-      <c r="BN232">
-        <v>1.74</v>
-      </c>
       <c r="BO232">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="BP232">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="233" spans="1:68">
@@ -49231,7 +49234,7 @@
         <v>232</v>
       </c>
       <c r="B233">
-        <v>7453652</v>
+        <v>7453642</v>
       </c>
       <c r="C233" t="s">
         <v>68</v>
@@ -49240,196 +49243,196 @@
         <v>69</v>
       </c>
       <c r="E233" s="2">
-        <v>45731.69791666666</v>
+        <v>45725.63541666666</v>
       </c>
       <c r="F233">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G233" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H233" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J233">
         <v>0</v>
       </c>
       <c r="K233">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L233">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N233">
         <v>3</v>
       </c>
       <c r="O233" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P233" t="s">
-        <v>240</v>
+        <v>87</v>
       </c>
       <c r="Q233">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="R233">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="S233">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="T233">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="U233">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="V233">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="W233">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="X233">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y233">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Z233">
-        <v>2.63</v>
+        <v>1.33</v>
       </c>
       <c r="AA233">
-        <v>3.23</v>
+        <v>5.2</v>
       </c>
       <c r="AB233">
-        <v>2.63</v>
+        <v>8</v>
       </c>
       <c r="AC233">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="AD233">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="AE233">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AF233">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="AG233">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AH233">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AI233">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="AJ233">
+        <v>1.75</v>
+      </c>
+      <c r="AK233">
+        <v>1.09</v>
+      </c>
+      <c r="AL233">
+        <v>1.17</v>
+      </c>
+      <c r="AM233">
+        <v>2.95</v>
+      </c>
+      <c r="AN233">
+        <v>2.14</v>
+      </c>
+      <c r="AO233">
+        <v>1</v>
+      </c>
+      <c r="AP233">
         <v>2.2</v>
       </c>
-      <c r="AK233">
-        <v>1.48</v>
-      </c>
-      <c r="AL233">
-        <v>1.25</v>
-      </c>
-      <c r="AM233">
-        <v>1.48</v>
-      </c>
-      <c r="AN233">
-        <v>2.71</v>
-      </c>
-      <c r="AO233">
-        <v>1.57</v>
-      </c>
-      <c r="AP233">
-        <v>2.73</v>
-      </c>
       <c r="AQ233">
+        <v>0.93</v>
+      </c>
+      <c r="AR233">
+        <v>1.88</v>
+      </c>
+      <c r="AS233">
+        <v>1.07</v>
+      </c>
+      <c r="AT233">
+        <v>2.95</v>
+      </c>
+      <c r="AU233">
+        <v>4</v>
+      </c>
+      <c r="AV233">
+        <v>4</v>
+      </c>
+      <c r="AW233">
+        <v>6</v>
+      </c>
+      <c r="AX233">
+        <v>4</v>
+      </c>
+      <c r="AY233">
+        <v>13</v>
+      </c>
+      <c r="AZ233">
+        <v>9</v>
+      </c>
+      <c r="BA233">
+        <v>1</v>
+      </c>
+      <c r="BB233">
+        <v>4</v>
+      </c>
+      <c r="BC233">
+        <v>5</v>
+      </c>
+      <c r="BD233">
+        <v>1.21</v>
+      </c>
+      <c r="BE233">
+        <v>8.5</v>
+      </c>
+      <c r="BF233">
+        <v>4.8</v>
+      </c>
+      <c r="BG233">
+        <v>1.23</v>
+      </c>
+      <c r="BH233">
+        <v>3.7</v>
+      </c>
+      <c r="BI233">
+        <v>1.38</v>
+      </c>
+      <c r="BJ233">
+        <v>2.7</v>
+      </c>
+      <c r="BK233">
+        <v>1.64</v>
+      </c>
+      <c r="BL233">
+        <v>2.12</v>
+      </c>
+      <c r="BM233">
+        <v>1.98</v>
+      </c>
+      <c r="BN233">
+        <v>1.74</v>
+      </c>
+      <c r="BO233">
+        <v>2.48</v>
+      </c>
+      <c r="BP233">
         <v>1.47</v>
-      </c>
-      <c r="AR233">
-        <v>1.77</v>
-      </c>
-      <c r="AS233">
-        <v>1.43</v>
-      </c>
-      <c r="AT233">
-        <v>3.2</v>
-      </c>
-      <c r="AU233">
-        <v>8</v>
-      </c>
-      <c r="AV233">
-        <v>3</v>
-      </c>
-      <c r="AW233">
-        <v>10</v>
-      </c>
-      <c r="AX233">
-        <v>6</v>
-      </c>
-      <c r="AY233">
-        <v>25</v>
-      </c>
-      <c r="AZ233">
-        <v>13</v>
-      </c>
-      <c r="BA233">
-        <v>4</v>
-      </c>
-      <c r="BB233">
-        <v>5</v>
-      </c>
-      <c r="BC233">
-        <v>9</v>
-      </c>
-      <c r="BD233">
-        <v>2</v>
-      </c>
-      <c r="BE233">
-        <v>6.55</v>
-      </c>
-      <c r="BF233">
-        <v>2.27</v>
-      </c>
-      <c r="BG233">
-        <v>1.21</v>
-      </c>
-      <c r="BH233">
-        <v>3.58</v>
-      </c>
-      <c r="BI233">
-        <v>1.41</v>
-      </c>
-      <c r="BJ233">
-        <v>2.6</v>
-      </c>
-      <c r="BK233">
-        <v>1.8</v>
-      </c>
-      <c r="BL233">
-        <v>1.91</v>
-      </c>
-      <c r="BM233">
-        <v>2.19</v>
-      </c>
-      <c r="BN233">
-        <v>1.57</v>
-      </c>
-      <c r="BO233">
-        <v>2.88</v>
-      </c>
-      <c r="BP233">
-        <v>1.32</v>
       </c>
     </row>
     <row r="234" spans="1:68">
@@ -49437,7 +49440,7 @@
         <v>233</v>
       </c>
       <c r="B234">
-        <v>7453654</v>
+        <v>7453652</v>
       </c>
       <c r="C234" t="s">
         <v>68</v>
@@ -49446,16 +49449,16 @@
         <v>69</v>
       </c>
       <c r="E234" s="2">
-        <v>45732.39583333334</v>
+        <v>45731.69791666666</v>
       </c>
       <c r="F234">
         <v>30</v>
       </c>
       <c r="G234" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="H234" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="I234">
         <v>0</v>
@@ -49467,175 +49470,175 @@
         <v>0</v>
       </c>
       <c r="L234">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M234">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N234">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O234" t="s">
-        <v>87</v>
+        <v>247</v>
       </c>
       <c r="P234" t="s">
-        <v>87</v>
+        <v>240</v>
       </c>
       <c r="Q234">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="R234">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="S234">
         <v>3.2</v>
       </c>
       <c r="T234">
+        <v>1.36</v>
+      </c>
+      <c r="U234">
+        <v>3</v>
+      </c>
+      <c r="V234">
+        <v>2.63</v>
+      </c>
+      <c r="W234">
         <v>1.44</v>
       </c>
-      <c r="U234">
+      <c r="X234">
+        <v>7</v>
+      </c>
+      <c r="Y234">
+        <v>1.1</v>
+      </c>
+      <c r="Z234">
         <v>2.63</v>
       </c>
-      <c r="V234">
-        <v>3.4</v>
-      </c>
-      <c r="W234">
-        <v>1.3</v>
-      </c>
-      <c r="X234">
-        <v>10</v>
-      </c>
-      <c r="Y234">
-        <v>1.06</v>
-      </c>
-      <c r="Z234">
-        <v>2.9</v>
-      </c>
       <c r="AA234">
-        <v>3.1</v>
+        <v>3.23</v>
       </c>
       <c r="AB234">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="AC234">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AD234">
-        <v>7.75</v>
+        <v>9.5</v>
       </c>
       <c r="AE234">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AF234">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="AG234">
         <v>1.85</v>
       </c>
       <c r="AH234">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AI234">
+        <v>1.62</v>
+      </c>
+      <c r="AJ234">
+        <v>2.2</v>
+      </c>
+      <c r="AK234">
+        <v>1.48</v>
+      </c>
+      <c r="AL234">
+        <v>1.25</v>
+      </c>
+      <c r="AM234">
+        <v>1.48</v>
+      </c>
+      <c r="AN234">
+        <v>2.71</v>
+      </c>
+      <c r="AO234">
+        <v>1.57</v>
+      </c>
+      <c r="AP234">
+        <v>2.73</v>
+      </c>
+      <c r="AQ234">
+        <v>1.47</v>
+      </c>
+      <c r="AR234">
+        <v>1.77</v>
+      </c>
+      <c r="AS234">
+        <v>1.43</v>
+      </c>
+      <c r="AT234">
+        <v>3.2</v>
+      </c>
+      <c r="AU234">
+        <v>8</v>
+      </c>
+      <c r="AV234">
+        <v>3</v>
+      </c>
+      <c r="AW234">
+        <v>10</v>
+      </c>
+      <c r="AX234">
+        <v>6</v>
+      </c>
+      <c r="AY234">
+        <v>25</v>
+      </c>
+      <c r="AZ234">
+        <v>13</v>
+      </c>
+      <c r="BA234">
+        <v>4</v>
+      </c>
+      <c r="BB234">
+        <v>5</v>
+      </c>
+      <c r="BC234">
+        <v>9</v>
+      </c>
+      <c r="BD234">
+        <v>2</v>
+      </c>
+      <c r="BE234">
+        <v>6.55</v>
+      </c>
+      <c r="BF234">
+        <v>2.27</v>
+      </c>
+      <c r="BG234">
+        <v>1.21</v>
+      </c>
+      <c r="BH234">
+        <v>3.58</v>
+      </c>
+      <c r="BI234">
+        <v>1.41</v>
+      </c>
+      <c r="BJ234">
+        <v>2.6</v>
+      </c>
+      <c r="BK234">
+        <v>1.8</v>
+      </c>
+      <c r="BL234">
         <v>1.91</v>
       </c>
-      <c r="AJ234">
-        <v>1.91</v>
-      </c>
-      <c r="AK234">
-        <v>1.5</v>
-      </c>
-      <c r="AL234">
-        <v>1.3</v>
-      </c>
-      <c r="AM234">
-        <v>1.4</v>
-      </c>
-      <c r="AN234">
-        <v>1.71</v>
-      </c>
-      <c r="AO234">
-        <v>1.29</v>
-      </c>
-      <c r="AP234">
-        <v>1.67</v>
-      </c>
-      <c r="AQ234">
-        <v>1.27</v>
-      </c>
-      <c r="AR234">
-        <v>1.24</v>
-      </c>
-      <c r="AS234">
-        <v>1.24</v>
-      </c>
-      <c r="AT234">
-        <v>2.48</v>
-      </c>
-      <c r="AU234">
-        <v>5</v>
-      </c>
-      <c r="AV234">
-        <v>2</v>
-      </c>
-      <c r="AW234">
-        <v>3</v>
-      </c>
-      <c r="AX234">
-        <v>3</v>
-      </c>
-      <c r="AY234">
-        <v>8</v>
-      </c>
-      <c r="AZ234">
-        <v>5</v>
-      </c>
-      <c r="BA234">
-        <v>5</v>
-      </c>
-      <c r="BB234">
-        <v>3</v>
-      </c>
-      <c r="BC234">
-        <v>8</v>
-      </c>
-      <c r="BD234">
-        <v>2.04</v>
-      </c>
-      <c r="BE234">
-        <v>6.3</v>
-      </c>
-      <c r="BF234">
-        <v>2.25</v>
-      </c>
-      <c r="BG234">
-        <v>1.31</v>
-      </c>
-      <c r="BH234">
-        <v>2.92</v>
-      </c>
-      <c r="BI234">
-        <v>1.6</v>
-      </c>
-      <c r="BJ234">
-        <v>2.14</v>
-      </c>
-      <c r="BK234">
-        <v>2.05</v>
-      </c>
-      <c r="BL234">
-        <v>1.7</v>
-      </c>
       <c r="BM234">
-        <v>2.71</v>
+        <v>2.19</v>
       </c>
       <c r="BN234">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="BO234">
-        <v>3.72</v>
+        <v>2.88</v>
       </c>
       <c r="BP234">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="235" spans="1:68">
@@ -49643,7 +49646,7 @@
         <v>234</v>
       </c>
       <c r="B235">
-        <v>7453653</v>
+        <v>7453654</v>
       </c>
       <c r="C235" t="s">
         <v>68</v>
@@ -49652,196 +49655,196 @@
         <v>69</v>
       </c>
       <c r="E235" s="2">
-        <v>45732.60416666666</v>
+        <v>45732.39583333334</v>
       </c>
       <c r="F235">
         <v>30</v>
       </c>
       <c r="G235" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H235" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="I235">
         <v>0</v>
       </c>
       <c r="J235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L235">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M235">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N235">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O235" t="s">
-        <v>105</v>
+        <v>87</v>
       </c>
       <c r="P235" t="s">
-        <v>347</v>
+        <v>87</v>
       </c>
       <c r="Q235">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="R235">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="S235">
+        <v>3.2</v>
+      </c>
+      <c r="T235">
+        <v>1.44</v>
+      </c>
+      <c r="U235">
+        <v>2.63</v>
+      </c>
+      <c r="V235">
+        <v>3.4</v>
+      </c>
+      <c r="W235">
+        <v>1.3</v>
+      </c>
+      <c r="X235">
+        <v>10</v>
+      </c>
+      <c r="Y235">
+        <v>1.06</v>
+      </c>
+      <c r="Z235">
+        <v>2.9</v>
+      </c>
+      <c r="AA235">
+        <v>3.1</v>
+      </c>
+      <c r="AB235">
+        <v>2.4</v>
+      </c>
+      <c r="AC235">
+        <v>1.07</v>
+      </c>
+      <c r="AD235">
+        <v>7.75</v>
+      </c>
+      <c r="AE235">
+        <v>1.35</v>
+      </c>
+      <c r="AF235">
+        <v>2.95</v>
+      </c>
+      <c r="AG235">
+        <v>1.85</v>
+      </c>
+      <c r="AH235">
+        <v>1.85</v>
+      </c>
+      <c r="AI235">
+        <v>1.91</v>
+      </c>
+      <c r="AJ235">
+        <v>1.91</v>
+      </c>
+      <c r="AK235">
+        <v>1.5</v>
+      </c>
+      <c r="AL235">
+        <v>1.3</v>
+      </c>
+      <c r="AM235">
+        <v>1.4</v>
+      </c>
+      <c r="AN235">
+        <v>1.71</v>
+      </c>
+      <c r="AO235">
+        <v>1.29</v>
+      </c>
+      <c r="AP235">
+        <v>1.67</v>
+      </c>
+      <c r="AQ235">
+        <v>1.27</v>
+      </c>
+      <c r="AR235">
+        <v>1.24</v>
+      </c>
+      <c r="AS235">
+        <v>1.24</v>
+      </c>
+      <c r="AT235">
+        <v>2.48</v>
+      </c>
+      <c r="AU235">
         <v>5</v>
       </c>
-      <c r="T235">
-        <v>1.36</v>
-      </c>
-      <c r="U235">
-        <v>3</v>
-      </c>
-      <c r="V235">
-        <v>2.75</v>
-      </c>
-      <c r="W235">
-        <v>1.4</v>
-      </c>
-      <c r="X235">
-        <v>7</v>
-      </c>
-      <c r="Y235">
-        <v>1.1</v>
-      </c>
-      <c r="Z235">
-        <v>1.68</v>
-      </c>
-      <c r="AA235">
-        <v>3.81</v>
-      </c>
-      <c r="AB235">
-        <v>4.75</v>
-      </c>
-      <c r="AC235">
-        <v>1.05</v>
-      </c>
-      <c r="AD235">
-        <v>9.5</v>
-      </c>
-      <c r="AE235">
-        <v>1.28</v>
-      </c>
-      <c r="AF235">
-        <v>3.65</v>
-      </c>
-      <c r="AG235">
-        <v>1.82</v>
-      </c>
-      <c r="AH235">
-        <v>1.92</v>
-      </c>
-      <c r="AI235">
-        <v>1.8</v>
-      </c>
-      <c r="AJ235">
-        <v>1.95</v>
-      </c>
-      <c r="AK235">
-        <v>1.17</v>
-      </c>
-      <c r="AL235">
-        <v>1.22</v>
-      </c>
-      <c r="AM235">
-        <v>2.1</v>
-      </c>
-      <c r="AN235">
-        <v>1.85</v>
-      </c>
-      <c r="AO235">
-        <v>0.43</v>
-      </c>
-      <c r="AP235">
-        <v>1.71</v>
-      </c>
-      <c r="AQ235">
-        <v>0.6</v>
-      </c>
-      <c r="AR235">
-        <v>1.58</v>
-      </c>
-      <c r="AS235">
-        <v>1.22</v>
-      </c>
-      <c r="AT235">
-        <v>2.8</v>
-      </c>
-      <c r="AU235">
-        <v>3</v>
-      </c>
       <c r="AV235">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AW235">
         <v>3</v>
       </c>
       <c r="AX235">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY235">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ235">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="BA235">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB235">
         <v>3</v>
       </c>
       <c r="BC235">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BD235">
-        <v>1.54</v>
+        <v>2.04</v>
       </c>
       <c r="BE235">
-        <v>9.300000000000001</v>
+        <v>6.3</v>
       </c>
       <c r="BF235">
-        <v>2.97</v>
+        <v>2.25</v>
       </c>
       <c r="BG235">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="BH235">
-        <v>4.2</v>
+        <v>2.92</v>
       </c>
       <c r="BI235">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="BJ235">
-        <v>2.88</v>
+        <v>2.14</v>
       </c>
       <c r="BK235">
+        <v>2.05</v>
+      </c>
+      <c r="BL235">
         <v>1.7</v>
       </c>
-      <c r="BL235">
-        <v>2.05</v>
-      </c>
       <c r="BM235">
-        <v>2.05</v>
+        <v>2.71</v>
       </c>
       <c r="BN235">
-        <v>1.7</v>
+        <v>1.38</v>
       </c>
       <c r="BO235">
-        <v>2.57</v>
+        <v>3.72</v>
       </c>
       <c r="BP235">
-        <v>1.42</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="236" spans="1:68">
@@ -49849,7 +49852,7 @@
         <v>235</v>
       </c>
       <c r="B236">
-        <v>7453650</v>
+        <v>7453651</v>
       </c>
       <c r="C236" t="s">
         <v>68</v>
@@ -49864,43 +49867,43 @@
         <v>30</v>
       </c>
       <c r="G236" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H236" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I236">
         <v>1</v>
       </c>
       <c r="J236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K236">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L236">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M236">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N236">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O236" t="s">
         <v>248</v>
       </c>
       <c r="P236" t="s">
-        <v>348</v>
+        <v>87</v>
       </c>
       <c r="Q236">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="R236">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="S236">
-        <v>6.5</v>
+        <v>4.5</v>
       </c>
       <c r="T236">
         <v>1.4</v>
@@ -49909,10 +49912,10 @@
         <v>2.75</v>
       </c>
       <c r="V236">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="W236">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="X236">
         <v>8</v>
@@ -49921,133 +49924,133 @@
         <v>1.08</v>
       </c>
       <c r="Z236">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AA236">
-        <v>3.98</v>
+        <v>3.47</v>
       </c>
       <c r="AB236">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="AC236">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AD236">
-        <v>9.5</v>
+        <v>8.5</v>
       </c>
       <c r="AE236">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AF236">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AG236">
-        <v>1.87</v>
+        <v>1.94</v>
       </c>
       <c r="AH236">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AI236">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AJ236">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AK236">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AL236">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AM236">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="AN236">
-        <v>2.14</v>
+        <v>1.71</v>
       </c>
       <c r="AO236">
-        <v>1.07</v>
+        <v>0.79</v>
       </c>
       <c r="AP236">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AQ236">
-        <v>1</v>
+        <v>0.73</v>
       </c>
       <c r="AR236">
-        <v>2.06</v>
+        <v>1.65</v>
       </c>
       <c r="AS236">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AT236">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="AU236">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AV236">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AW236">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AX236">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="AY236">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AZ236">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="BA236">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="BB236">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="BC236">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="BD236">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="BE236">
-        <v>9.5</v>
+        <v>7.2</v>
       </c>
       <c r="BF236">
-        <v>3.52</v>
+        <v>3.48</v>
       </c>
       <c r="BG236">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="BH236">
-        <v>3.9</v>
+        <v>3.78</v>
       </c>
       <c r="BI236">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BJ236">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="BK236">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="BL236">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="BM236">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="BN236">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="BO236">
-        <v>2.75</v>
+        <v>2.83</v>
       </c>
       <c r="BP236">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="237" spans="1:68">
@@ -50055,7 +50058,7 @@
         <v>236</v>
       </c>
       <c r="B237">
-        <v>7453651</v>
+        <v>7453657</v>
       </c>
       <c r="C237" t="s">
         <v>68</v>
@@ -50070,25 +50073,25 @@
         <v>30</v>
       </c>
       <c r="G237" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="H237" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="I237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J237">
         <v>0</v>
       </c>
       <c r="K237">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L237">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M237">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N237">
         <v>3</v>
@@ -50097,163 +50100,163 @@
         <v>249</v>
       </c>
       <c r="P237" t="s">
-        <v>87</v>
+        <v>348</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
       </c>
       <c r="R237">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S237">
         <v>4.5</v>
       </c>
       <c r="T237">
+        <v>1.36</v>
+      </c>
+      <c r="U237">
+        <v>3</v>
+      </c>
+      <c r="V237">
+        <v>2.75</v>
+      </c>
+      <c r="W237">
         <v>1.4</v>
       </c>
-      <c r="U237">
-        <v>2.75</v>
-      </c>
-      <c r="V237">
-        <v>3</v>
-      </c>
-      <c r="W237">
-        <v>1.36</v>
-      </c>
       <c r="X237">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y237">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="Z237">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AA237">
-        <v>3.47</v>
+        <v>3.84</v>
       </c>
       <c r="AB237">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AC237">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AD237">
-        <v>8.5</v>
+        <v>9.5</v>
       </c>
       <c r="AE237">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AF237">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="AG237">
-        <v>1.94</v>
+        <v>1.77</v>
       </c>
       <c r="AH237">
-        <v>1.8</v>
+        <v>1.98</v>
       </c>
       <c r="AI237">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AJ237">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AK237">
         <v>1.22</v>
       </c>
       <c r="AL237">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AM237">
+        <v>1.91</v>
+      </c>
+      <c r="AN237">
+        <v>1.43</v>
+      </c>
+      <c r="AO237">
+        <v>1.07</v>
+      </c>
+      <c r="AP237">
+        <v>1.53</v>
+      </c>
+      <c r="AQ237">
+        <v>1</v>
+      </c>
+      <c r="AR237">
+        <v>1.5</v>
+      </c>
+      <c r="AS237">
+        <v>1.2</v>
+      </c>
+      <c r="AT237">
+        <v>2.7</v>
+      </c>
+      <c r="AU237">
+        <v>8</v>
+      </c>
+      <c r="AV237">
+        <v>6</v>
+      </c>
+      <c r="AW237">
+        <v>9</v>
+      </c>
+      <c r="AX237">
+        <v>11</v>
+      </c>
+      <c r="AY237">
+        <v>18</v>
+      </c>
+      <c r="AZ237">
+        <v>23</v>
+      </c>
+      <c r="BA237">
+        <v>5</v>
+      </c>
+      <c r="BB237">
+        <v>5</v>
+      </c>
+      <c r="BC237">
+        <v>10</v>
+      </c>
+      <c r="BD237">
+        <v>1.56</v>
+      </c>
+      <c r="BE237">
+        <v>8.9</v>
+      </c>
+      <c r="BF237">
+        <v>2.94</v>
+      </c>
+      <c r="BG237">
+        <v>1.23</v>
+      </c>
+      <c r="BH237">
+        <v>3.42</v>
+      </c>
+      <c r="BI237">
+        <v>1.46</v>
+      </c>
+      <c r="BJ237">
+        <v>2.45</v>
+      </c>
+      <c r="BK237">
         <v>1.85</v>
       </c>
-      <c r="AN237">
-        <v>1.71</v>
-      </c>
-      <c r="AO237">
-        <v>0.79</v>
-      </c>
-      <c r="AP237">
-        <v>1.8</v>
-      </c>
-      <c r="AQ237">
-        <v>0.73</v>
-      </c>
-      <c r="AR237">
-        <v>1.65</v>
-      </c>
-      <c r="AS237">
-        <v>1.4</v>
-      </c>
-      <c r="AT237">
-        <v>3.05</v>
-      </c>
-      <c r="AU237">
-        <v>7</v>
-      </c>
-      <c r="AV237">
-        <v>5</v>
-      </c>
-      <c r="AW237">
-        <v>5</v>
-      </c>
-      <c r="AX237">
-        <v>7</v>
-      </c>
-      <c r="AY237">
-        <v>17</v>
-      </c>
-      <c r="AZ237">
-        <v>14</v>
-      </c>
-      <c r="BA237">
-        <v>7</v>
-      </c>
-      <c r="BB237">
-        <v>7</v>
-      </c>
-      <c r="BC237">
-        <v>14</v>
-      </c>
-      <c r="BD237">
-        <v>1.5</v>
-      </c>
-      <c r="BE237">
-        <v>7.2</v>
-      </c>
-      <c r="BF237">
-        <v>3.48</v>
-      </c>
-      <c r="BG237">
-        <v>1.19</v>
-      </c>
-      <c r="BH237">
-        <v>3.78</v>
-      </c>
-      <c r="BI237">
-        <v>1.4</v>
-      </c>
-      <c r="BJ237">
-        <v>2.64</v>
-      </c>
-      <c r="BK237">
-        <v>1.8</v>
-      </c>
       <c r="BL237">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="BM237">
-        <v>2.15</v>
+        <v>2.32</v>
       </c>
       <c r="BN237">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="BO237">
-        <v>2.83</v>
+        <v>3.08</v>
       </c>
       <c r="BP237">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="238" spans="1:68">
@@ -50261,7 +50264,7 @@
         <v>237</v>
       </c>
       <c r="B238">
-        <v>7453657</v>
+        <v>7453656</v>
       </c>
       <c r="C238" t="s">
         <v>68</v>
@@ -50276,28 +50279,28 @@
         <v>30</v>
       </c>
       <c r="G238" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H238" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="I238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J238">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K238">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L238">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M238">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N238">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O238" t="s">
         <v>250</v>
@@ -50306,160 +50309,160 @@
         <v>349</v>
       </c>
       <c r="Q238">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
       <c r="R238">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="S238">
-        <v>4.5</v>
+        <v>3.5</v>
       </c>
       <c r="T238">
+        <v>1.4</v>
+      </c>
+      <c r="U238">
+        <v>2.75</v>
+      </c>
+      <c r="V238">
+        <v>3</v>
+      </c>
+      <c r="W238">
         <v>1.36</v>
       </c>
-      <c r="U238">
+      <c r="X238">
+        <v>8</v>
+      </c>
+      <c r="Y238">
+        <v>1.08</v>
+      </c>
+      <c r="Z238">
+        <v>2.35</v>
+      </c>
+      <c r="AA238">
+        <v>2.98</v>
+      </c>
+      <c r="AB238">
+        <v>3.23</v>
+      </c>
+      <c r="AC238">
+        <v>1.06</v>
+      </c>
+      <c r="AD238">
+        <v>8.5</v>
+      </c>
+      <c r="AE238">
+        <v>1.3</v>
+      </c>
+      <c r="AF238">
+        <v>3.35</v>
+      </c>
+      <c r="AG238">
+        <v>1.89</v>
+      </c>
+      <c r="AH238">
+        <v>1.85</v>
+      </c>
+      <c r="AI238">
+        <v>1.67</v>
+      </c>
+      <c r="AJ238">
+        <v>2.1</v>
+      </c>
+      <c r="AK238">
+        <v>1.38</v>
+      </c>
+      <c r="AL238">
+        <v>1.3</v>
+      </c>
+      <c r="AM238">
+        <v>1.53</v>
+      </c>
+      <c r="AN238">
+        <v>1.79</v>
+      </c>
+      <c r="AO238">
+        <v>0.64</v>
+      </c>
+      <c r="AP238">
+        <v>1.87</v>
+      </c>
+      <c r="AQ238">
+        <v>0.6</v>
+      </c>
+      <c r="AR238">
+        <v>1.28</v>
+      </c>
+      <c r="AS238">
+        <v>1.25</v>
+      </c>
+      <c r="AT238">
+        <v>2.53</v>
+      </c>
+      <c r="AU238">
+        <v>5</v>
+      </c>
+      <c r="AV238">
         <v>3</v>
       </c>
-      <c r="V238">
-        <v>2.75</v>
-      </c>
-      <c r="W238">
-        <v>1.4</v>
-      </c>
-      <c r="X238">
-        <v>7</v>
-      </c>
-      <c r="Y238">
-        <v>1.1</v>
-      </c>
-      <c r="Z238">
-        <v>1.72</v>
-      </c>
-      <c r="AA238">
-        <v>3.84</v>
-      </c>
-      <c r="AB238">
-        <v>4.4</v>
-      </c>
-      <c r="AC238">
-        <v>1.05</v>
-      </c>
-      <c r="AD238">
-        <v>9.5</v>
-      </c>
-      <c r="AE238">
-        <v>1.25</v>
-      </c>
-      <c r="AF238">
-        <v>3.7</v>
-      </c>
-      <c r="AG238">
-        <v>1.77</v>
-      </c>
-      <c r="AH238">
-        <v>1.98</v>
-      </c>
-      <c r="AI238">
-        <v>1.75</v>
-      </c>
-      <c r="AJ238">
-        <v>2</v>
-      </c>
-      <c r="AK238">
-        <v>1.22</v>
-      </c>
-      <c r="AL238">
-        <v>1.22</v>
-      </c>
-      <c r="AM238">
-        <v>1.91</v>
-      </c>
-      <c r="AN238">
-        <v>1.43</v>
-      </c>
-      <c r="AO238">
-        <v>1.07</v>
-      </c>
-      <c r="AP238">
-        <v>1.53</v>
-      </c>
-      <c r="AQ238">
-        <v>1</v>
-      </c>
-      <c r="AR238">
-        <v>1.5</v>
-      </c>
-      <c r="AS238">
-        <v>1.2</v>
-      </c>
-      <c r="AT238">
-        <v>2.7</v>
-      </c>
-      <c r="AU238">
-        <v>8</v>
-      </c>
-      <c r="AV238">
+      <c r="AW238">
         <v>6</v>
       </c>
-      <c r="AW238">
-        <v>9</v>
-      </c>
       <c r="AX238">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="AY238">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="AZ238">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="BA238">
         <v>5</v>
       </c>
       <c r="BB238">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BC238">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BD238">
-        <v>1.56</v>
+        <v>1.92</v>
       </c>
       <c r="BE238">
-        <v>8.9</v>
+        <v>6.6</v>
       </c>
       <c r="BF238">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="BG238">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="BH238">
-        <v>3.42</v>
+        <v>3.68</v>
       </c>
       <c r="BI238">
-        <v>1.46</v>
+        <v>1.41</v>
       </c>
       <c r="BJ238">
-        <v>2.45</v>
+        <v>2.6</v>
       </c>
       <c r="BK238">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="BL238">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="BM238">
-        <v>2.32</v>
+        <v>2.19</v>
       </c>
       <c r="BN238">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="BO238">
-        <v>3.08</v>
+        <v>2.88</v>
       </c>
       <c r="BP238">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="239" spans="1:68">
@@ -50467,7 +50470,7 @@
         <v>238</v>
       </c>
       <c r="B239">
-        <v>7453656</v>
+        <v>7453655</v>
       </c>
       <c r="C239" t="s">
         <v>68</v>
@@ -50482,190 +50485,190 @@
         <v>30</v>
       </c>
       <c r="G239" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H239" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="I239">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J239">
         <v>1</v>
       </c>
       <c r="K239">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L239">
+        <v>1</v>
+      </c>
+      <c r="M239">
+        <v>2</v>
+      </c>
+      <c r="N239">
         <v>3</v>
       </c>
-      <c r="M239">
-        <v>2</v>
-      </c>
-      <c r="N239">
-        <v>5</v>
-      </c>
       <c r="O239" t="s">
-        <v>251</v>
+        <v>118</v>
       </c>
       <c r="P239" t="s">
         <v>350</v>
       </c>
       <c r="Q239">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="R239">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="S239">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
       <c r="T239">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="U239">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="V239">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="W239">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="X239">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y239">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="Z239">
-        <v>2.35</v>
+        <v>3.38</v>
       </c>
       <c r="AA239">
-        <v>2.98</v>
+        <v>3.75</v>
       </c>
       <c r="AB239">
-        <v>3.23</v>
+        <v>1.97</v>
       </c>
       <c r="AC239">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AD239">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="AE239">
+        <v>1.2</v>
+      </c>
+      <c r="AF239">
+        <v>4.33</v>
+      </c>
+      <c r="AG239">
+        <v>1.59</v>
+      </c>
+      <c r="AH239">
+        <v>2.27</v>
+      </c>
+      <c r="AI239">
+        <v>1.57</v>
+      </c>
+      <c r="AJ239">
+        <v>2.25</v>
+      </c>
+      <c r="AK239">
+        <v>1.77</v>
+      </c>
+      <c r="AL239">
+        <v>1.22</v>
+      </c>
+      <c r="AM239">
         <v>1.3</v>
       </c>
-      <c r="AF239">
-        <v>3.35</v>
-      </c>
-      <c r="AG239">
-        <v>1.89</v>
-      </c>
-      <c r="AH239">
-        <v>1.85</v>
-      </c>
-      <c r="AI239">
-        <v>1.67</v>
-      </c>
-      <c r="AJ239">
-        <v>2.1</v>
-      </c>
-      <c r="AK239">
-        <v>1.38</v>
-      </c>
-      <c r="AL239">
+      <c r="AN239">
+        <v>1.14</v>
+      </c>
+      <c r="AO239">
+        <v>0.86</v>
+      </c>
+      <c r="AP239">
+        <v>1.07</v>
+      </c>
+      <c r="AQ239">
+        <v>1</v>
+      </c>
+      <c r="AR239">
         <v>1.3</v>
       </c>
-      <c r="AM239">
-        <v>1.53</v>
-      </c>
-      <c r="AN239">
-        <v>1.79</v>
-      </c>
-      <c r="AO239">
-        <v>0.64</v>
-      </c>
-      <c r="AP239">
-        <v>1.87</v>
-      </c>
-      <c r="AQ239">
-        <v>0.6</v>
-      </c>
-      <c r="AR239">
-        <v>1.28</v>
-      </c>
       <c r="AS239">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AT239">
-        <v>2.53</v>
+        <v>2.88</v>
       </c>
       <c r="AU239">
+        <v>2</v>
+      </c>
+      <c r="AV239">
         <v>5</v>
-      </c>
-      <c r="AV239">
-        <v>3</v>
       </c>
       <c r="AW239">
         <v>6</v>
       </c>
       <c r="AX239">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="AY239">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ239">
+        <v>16</v>
+      </c>
+      <c r="BA239">
+        <v>6</v>
+      </c>
+      <c r="BB239">
         <v>4</v>
       </c>
-      <c r="BA239">
-        <v>5</v>
-      </c>
-      <c r="BB239">
-        <v>2</v>
-      </c>
       <c r="BC239">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="BD239">
-        <v>1.92</v>
+        <v>2.34</v>
       </c>
       <c r="BE239">
-        <v>6.6</v>
+        <v>6.65</v>
       </c>
       <c r="BF239">
-        <v>2.38</v>
+        <v>1.94</v>
       </c>
       <c r="BG239">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="BH239">
-        <v>3.68</v>
+        <v>4.25</v>
       </c>
       <c r="BI239">
-        <v>1.41</v>
+        <v>1.32</v>
       </c>
       <c r="BJ239">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="BK239">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="BL239">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="BM239">
-        <v>2.19</v>
+        <v>1.93</v>
       </c>
       <c r="BN239">
-        <v>1.57</v>
+        <v>1.77</v>
       </c>
       <c r="BO239">
-        <v>2.88</v>
+        <v>2.57</v>
       </c>
       <c r="BP239">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="240" spans="1:68">
@@ -50673,7 +50676,7 @@
         <v>239</v>
       </c>
       <c r="B240">
-        <v>7453655</v>
+        <v>7453650</v>
       </c>
       <c r="C240" t="s">
         <v>68</v>
@@ -50688,189 +50691,395 @@
         <v>30</v>
       </c>
       <c r="G240" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H240" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J240">
         <v>1</v>
       </c>
       <c r="K240">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L240">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M240">
         <v>2</v>
       </c>
       <c r="N240">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O240" t="s">
-        <v>118</v>
+        <v>251</v>
       </c>
       <c r="P240" t="s">
         <v>351</v>
       </c>
       <c r="Q240">
-        <v>3.75</v>
+        <v>2.1</v>
       </c>
       <c r="R240">
+        <v>2.25</v>
+      </c>
+      <c r="S240">
+        <v>6.5</v>
+      </c>
+      <c r="T240">
+        <v>1.4</v>
+      </c>
+      <c r="U240">
+        <v>2.75</v>
+      </c>
+      <c r="V240">
+        <v>2.75</v>
+      </c>
+      <c r="W240">
+        <v>1.4</v>
+      </c>
+      <c r="X240">
+        <v>8</v>
+      </c>
+      <c r="Y240">
+        <v>1.08</v>
+      </c>
+      <c r="Z240">
+        <v>1.55</v>
+      </c>
+      <c r="AA240">
+        <v>3.98</v>
+      </c>
+      <c r="AB240">
+        <v>5.8</v>
+      </c>
+      <c r="AC240">
+        <v>1.05</v>
+      </c>
+      <c r="AD240">
+        <v>9.5</v>
+      </c>
+      <c r="AE240">
+        <v>1.28</v>
+      </c>
+      <c r="AF240">
+        <v>3.6</v>
+      </c>
+      <c r="AG240">
+        <v>1.87</v>
+      </c>
+      <c r="AH240">
+        <v>1.87</v>
+      </c>
+      <c r="AI240">
+        <v>2</v>
+      </c>
+      <c r="AJ240">
+        <v>1.75</v>
+      </c>
+      <c r="AK240">
+        <v>1.12</v>
+      </c>
+      <c r="AL240">
+        <v>1.18</v>
+      </c>
+      <c r="AM240">
+        <v>2.45</v>
+      </c>
+      <c r="AN240">
+        <v>2.14</v>
+      </c>
+      <c r="AO240">
+        <v>1.07</v>
+      </c>
+      <c r="AP240">
+        <v>2.2</v>
+      </c>
+      <c r="AQ240">
+        <v>1</v>
+      </c>
+      <c r="AR240">
+        <v>2.06</v>
+      </c>
+      <c r="AS240">
+        <v>1.44</v>
+      </c>
+      <c r="AT240">
+        <v>3.5</v>
+      </c>
+      <c r="AU240">
+        <v>10</v>
+      </c>
+      <c r="AV240">
+        <v>4</v>
+      </c>
+      <c r="AW240">
+        <v>10</v>
+      </c>
+      <c r="AX240">
+        <v>3</v>
+      </c>
+      <c r="AY240">
+        <v>24</v>
+      </c>
+      <c r="AZ240">
+        <v>8</v>
+      </c>
+      <c r="BA240">
+        <v>2</v>
+      </c>
+      <c r="BB240">
+        <v>3</v>
+      </c>
+      <c r="BC240">
+        <v>5</v>
+      </c>
+      <c r="BD240">
+        <v>1.42</v>
+      </c>
+      <c r="BE240">
+        <v>9.5</v>
+      </c>
+      <c r="BF240">
+        <v>3.52</v>
+      </c>
+      <c r="BG240">
+        <v>1.18</v>
+      </c>
+      <c r="BH240">
+        <v>3.9</v>
+      </c>
+      <c r="BI240">
+        <v>1.36</v>
+      </c>
+      <c r="BJ240">
+        <v>2.7</v>
+      </c>
+      <c r="BK240">
+        <v>1.85</v>
+      </c>
+      <c r="BL240">
+        <v>1.85</v>
+      </c>
+      <c r="BM240">
+        <v>2.11</v>
+      </c>
+      <c r="BN240">
+        <v>1.65</v>
+      </c>
+      <c r="BO240">
+        <v>2.75</v>
+      </c>
+      <c r="BP240">
+        <v>1.37</v>
+      </c>
+    </row>
+    <row r="241" spans="1:68">
+      <c r="A241" s="1">
+        <v>240</v>
+      </c>
+      <c r="B241">
+        <v>7453653</v>
+      </c>
+      <c r="C241" t="s">
+        <v>68</v>
+      </c>
+      <c r="D241" t="s">
+        <v>69</v>
+      </c>
+      <c r="E241" s="2">
+        <v>45732.60416666666</v>
+      </c>
+      <c r="F241">
+        <v>30</v>
+      </c>
+      <c r="G241" t="s">
+        <v>85</v>
+      </c>
+      <c r="H241" t="s">
+        <v>75</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>1</v>
+      </c>
+      <c r="L241">
+        <v>1</v>
+      </c>
+      <c r="M241">
+        <v>2</v>
+      </c>
+      <c r="N241">
+        <v>3</v>
+      </c>
+      <c r="O241" t="s">
+        <v>105</v>
+      </c>
+      <c r="P241" t="s">
+        <v>352</v>
+      </c>
+      <c r="Q241">
         <v>2.3</v>
       </c>
-      <c r="S240">
-        <v>2.6</v>
-      </c>
-      <c r="T240">
-        <v>1.3</v>
-      </c>
-      <c r="U240">
-        <v>3.4</v>
-      </c>
-      <c r="V240">
-        <v>2.5</v>
-      </c>
-      <c r="W240">
-        <v>1.5</v>
-      </c>
-      <c r="X240">
+      <c r="R241">
+        <v>2.25</v>
+      </c>
+      <c r="S241">
+        <v>5</v>
+      </c>
+      <c r="T241">
+        <v>1.36</v>
+      </c>
+      <c r="U241">
+        <v>3</v>
+      </c>
+      <c r="V241">
+        <v>2.75</v>
+      </c>
+      <c r="W241">
+        <v>1.4</v>
+      </c>
+      <c r="X241">
+        <v>7</v>
+      </c>
+      <c r="Y241">
+        <v>1.1</v>
+      </c>
+      <c r="Z241">
+        <v>1.68</v>
+      </c>
+      <c r="AA241">
+        <v>3.81</v>
+      </c>
+      <c r="AB241">
+        <v>4.75</v>
+      </c>
+      <c r="AC241">
+        <v>1.05</v>
+      </c>
+      <c r="AD241">
+        <v>9.5</v>
+      </c>
+      <c r="AE241">
+        <v>1.28</v>
+      </c>
+      <c r="AF241">
+        <v>3.65</v>
+      </c>
+      <c r="AG241">
+        <v>1.82</v>
+      </c>
+      <c r="AH241">
+        <v>1.92</v>
+      </c>
+      <c r="AI241">
+        <v>1.8</v>
+      </c>
+      <c r="AJ241">
+        <v>1.95</v>
+      </c>
+      <c r="AK241">
+        <v>1.17</v>
+      </c>
+      <c r="AL241">
+        <v>1.22</v>
+      </c>
+      <c r="AM241">
+        <v>2.1</v>
+      </c>
+      <c r="AN241">
+        <v>1.79</v>
+      </c>
+      <c r="AO241">
+        <v>0.43</v>
+      </c>
+      <c r="AP241">
+        <v>1.67</v>
+      </c>
+      <c r="AQ241">
+        <v>0.6</v>
+      </c>
+      <c r="AR241">
+        <v>1.58</v>
+      </c>
+      <c r="AS241">
+        <v>1.22</v>
+      </c>
+      <c r="AT241">
+        <v>2.8</v>
+      </c>
+      <c r="AU241">
+        <v>3</v>
+      </c>
+      <c r="AV241">
+        <v>4</v>
+      </c>
+      <c r="AW241">
+        <v>3</v>
+      </c>
+      <c r="AX241">
+        <v>4</v>
+      </c>
+      <c r="AY241">
         <v>6</v>
       </c>
-      <c r="Y240">
-        <v>1.13</v>
-      </c>
-      <c r="Z240">
-        <v>3.38</v>
-      </c>
-      <c r="AA240">
-        <v>3.75</v>
-      </c>
-      <c r="AB240">
-        <v>1.97</v>
-      </c>
-      <c r="AC240">
-        <v>1.04</v>
-      </c>
-      <c r="AD240">
+      <c r="AZ241">
         <v>10</v>
       </c>
-      <c r="AE240">
-        <v>1.2</v>
-      </c>
-      <c r="AF240">
-        <v>4.33</v>
-      </c>
-      <c r="AG240">
-        <v>1.59</v>
-      </c>
-      <c r="AH240">
-        <v>2.27</v>
-      </c>
-      <c r="AI240">
-        <v>1.57</v>
-      </c>
-      <c r="AJ240">
-        <v>2.25</v>
-      </c>
-      <c r="AK240">
-        <v>1.77</v>
-      </c>
-      <c r="AL240">
-        <v>1.22</v>
-      </c>
-      <c r="AM240">
-        <v>1.3</v>
-      </c>
-      <c r="AN240">
-        <v>1.14</v>
-      </c>
-      <c r="AO240">
-        <v>0.86</v>
-      </c>
-      <c r="AP240">
-        <v>1.07</v>
-      </c>
-      <c r="AQ240">
-        <v>1</v>
-      </c>
-      <c r="AR240">
-        <v>1.3</v>
-      </c>
-      <c r="AS240">
-        <v>1.58</v>
-      </c>
-      <c r="AT240">
+      <c r="BA241">
+        <v>4</v>
+      </c>
+      <c r="BB241">
+        <v>3</v>
+      </c>
+      <c r="BC241">
+        <v>7</v>
+      </c>
+      <c r="BD241">
+        <v>1.54</v>
+      </c>
+      <c r="BE241">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="BF241">
+        <v>2.97</v>
+      </c>
+      <c r="BG241">
+        <v>1.15</v>
+      </c>
+      <c r="BH241">
+        <v>4.2</v>
+      </c>
+      <c r="BI241">
+        <v>1.32</v>
+      </c>
+      <c r="BJ241">
         <v>2.88</v>
       </c>
-      <c r="AU240">
-        <v>2</v>
-      </c>
-      <c r="AV240">
-        <v>5</v>
-      </c>
-      <c r="AW240">
-        <v>6</v>
-      </c>
-      <c r="AX240">
-        <v>7</v>
-      </c>
-      <c r="AY240">
-        <v>10</v>
-      </c>
-      <c r="AZ240">
-        <v>16</v>
-      </c>
-      <c r="BA240">
-        <v>6</v>
-      </c>
-      <c r="BB240">
-        <v>4</v>
-      </c>
-      <c r="BC240">
-        <v>10</v>
-      </c>
-      <c r="BD240">
-        <v>2.34</v>
-      </c>
-      <c r="BE240">
-        <v>6.65</v>
-      </c>
-      <c r="BF240">
-        <v>1.94</v>
-      </c>
-      <c r="BG240">
-        <v>1.15</v>
-      </c>
-      <c r="BH240">
-        <v>4.25</v>
-      </c>
-      <c r="BI240">
-        <v>1.32</v>
-      </c>
-      <c r="BJ240">
-        <v>2.88</v>
-      </c>
-      <c r="BK240">
-        <v>1.58</v>
-      </c>
-      <c r="BL240">
-        <v>2.17</v>
-      </c>
-      <c r="BM240">
-        <v>1.93</v>
-      </c>
-      <c r="BN240">
-        <v>1.77</v>
-      </c>
-      <c r="BO240">
+      <c r="BK241">
+        <v>1.7</v>
+      </c>
+      <c r="BL241">
+        <v>2.05</v>
+      </c>
+      <c r="BM241">
+        <v>2.05</v>
+      </c>
+      <c r="BN241">
+        <v>1.7</v>
+      </c>
+      <c r="BO241">
         <v>2.57</v>
       </c>
-      <c r="BP240">
+      <c r="BP241">
         <v>1.42</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="353">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -1434,7 +1434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP241"/>
+  <dimension ref="A1:BP242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -3828,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="AP12">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ12">
         <v>1.8</v>
@@ -7742,7 +7742,7 @@
         <v>0</v>
       </c>
       <c r="AP31">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ31">
         <v>0.73</v>
@@ -10214,7 +10214,7 @@
         <v>0.5</v>
       </c>
       <c r="AP43">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ43">
         <v>0.93</v>
@@ -14540,7 +14540,7 @@
         <v>1</v>
       </c>
       <c r="AP64">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ64">
         <v>0.6</v>
@@ -19278,7 +19278,7 @@
         <v>1.75</v>
       </c>
       <c r="AP87">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ87">
         <v>1.27</v>
@@ -21956,7 +21956,7 @@
         <v>1.67</v>
       </c>
       <c r="AP100">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ100">
         <v>1.73</v>
@@ -25870,7 +25870,7 @@
         <v>0.71</v>
       </c>
       <c r="AP119">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ119">
         <v>1.47</v>
@@ -27312,7 +27312,7 @@
         <v>1.57</v>
       </c>
       <c r="AP126">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ126">
         <v>1.6</v>
@@ -30196,7 +30196,7 @@
         <v>0.78</v>
       </c>
       <c r="AP140">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ140">
         <v>1</v>
@@ -34110,7 +34110,7 @@
         <v>0.11</v>
       </c>
       <c r="AP159">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ159">
         <v>0.13</v>
@@ -39466,7 +39466,7 @@
         <v>1.27</v>
       </c>
       <c r="AP185">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ185">
         <v>1.33</v>
@@ -39672,7 +39672,7 @@
         <v>0.82</v>
       </c>
       <c r="AP186">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ186">
         <v>1</v>
@@ -43174,7 +43174,7 @@
         <v>1.25</v>
       </c>
       <c r="AP203">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ203">
         <v>1</v>
@@ -47706,7 +47706,7 @@
         <v>0.85</v>
       </c>
       <c r="AP225">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ225">
         <v>1</v>
@@ -50384,7 +50384,7 @@
         <v>0.64</v>
       </c>
       <c r="AP238">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AQ238">
         <v>0.6</v>
@@ -51081,6 +51081,212 @@
       </c>
       <c r="BP241">
         <v>1.42</v>
+      </c>
+    </row>
+    <row r="242" spans="1:68">
+      <c r="A242" s="1">
+        <v>241</v>
+      </c>
+      <c r="B242">
+        <v>7858307</v>
+      </c>
+      <c r="C242" t="s">
+        <v>68</v>
+      </c>
+      <c r="D242" t="s">
+        <v>69</v>
+      </c>
+      <c r="E242" s="2">
+        <v>45744.69791666666</v>
+      </c>
+      <c r="F242">
+        <v>1</v>
+      </c>
+      <c r="G242" t="s">
+        <v>80</v>
+      </c>
+      <c r="H242" t="s">
+        <v>76</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+      <c r="L242">
+        <v>0</v>
+      </c>
+      <c r="M242">
+        <v>0</v>
+      </c>
+      <c r="N242">
+        <v>0</v>
+      </c>
+      <c r="O242" t="s">
+        <v>87</v>
+      </c>
+      <c r="P242" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q242">
+        <v>3.75</v>
+      </c>
+      <c r="R242">
+        <v>2</v>
+      </c>
+      <c r="S242">
+        <v>3.2</v>
+      </c>
+      <c r="T242">
+        <v>1.5</v>
+      </c>
+      <c r="U242">
+        <v>2.5</v>
+      </c>
+      <c r="V242">
+        <v>3.5</v>
+      </c>
+      <c r="W242">
+        <v>1.29</v>
+      </c>
+      <c r="X242">
+        <v>10</v>
+      </c>
+      <c r="Y242">
+        <v>1.06</v>
+      </c>
+      <c r="Z242">
+        <v>2.99</v>
+      </c>
+      <c r="AA242">
+        <v>2.85</v>
+      </c>
+      <c r="AB242">
+        <v>2.6</v>
+      </c>
+      <c r="AC242">
+        <v>1.09</v>
+      </c>
+      <c r="AD242">
+        <v>7</v>
+      </c>
+      <c r="AE242">
+        <v>1.42</v>
+      </c>
+      <c r="AF242">
+        <v>2.8</v>
+      </c>
+      <c r="AG242">
+        <v>2.15</v>
+      </c>
+      <c r="AH242">
+        <v>1.61</v>
+      </c>
+      <c r="AI242">
+        <v>1.95</v>
+      </c>
+      <c r="AJ242">
+        <v>1.8</v>
+      </c>
+      <c r="AK242">
+        <v>1.53</v>
+      </c>
+      <c r="AL242">
+        <v>1.34</v>
+      </c>
+      <c r="AM242">
+        <v>1.37</v>
+      </c>
+      <c r="AN242">
+        <v>1.87</v>
+      </c>
+      <c r="AO242">
+        <v>1</v>
+      </c>
+      <c r="AP242">
+        <v>1.81</v>
+      </c>
+      <c r="AQ242">
+        <v>1</v>
+      </c>
+      <c r="AR242">
+        <v>1.3</v>
+      </c>
+      <c r="AS242">
+        <v>1.41</v>
+      </c>
+      <c r="AT242">
+        <v>2.71</v>
+      </c>
+      <c r="AU242">
+        <v>2</v>
+      </c>
+      <c r="AV242">
+        <v>7</v>
+      </c>
+      <c r="AW242">
+        <v>8</v>
+      </c>
+      <c r="AX242">
+        <v>19</v>
+      </c>
+      <c r="AY242">
+        <v>11</v>
+      </c>
+      <c r="AZ242">
+        <v>31</v>
+      </c>
+      <c r="BA242">
+        <v>4</v>
+      </c>
+      <c r="BB242">
+        <v>8</v>
+      </c>
+      <c r="BC242">
+        <v>12</v>
+      </c>
+      <c r="BD242">
+        <v>2.38</v>
+      </c>
+      <c r="BE242">
+        <v>6.6</v>
+      </c>
+      <c r="BF242">
+        <v>1.92</v>
+      </c>
+      <c r="BG242">
+        <v>1.17</v>
+      </c>
+      <c r="BH242">
+        <v>3.98</v>
+      </c>
+      <c r="BI242">
+        <v>1.35</v>
+      </c>
+      <c r="BJ242">
+        <v>2.74</v>
+      </c>
+      <c r="BK242">
+        <v>1.64</v>
+      </c>
+      <c r="BL242">
+        <v>2.07</v>
+      </c>
+      <c r="BM242">
+        <v>2.09</v>
+      </c>
+      <c r="BN242">
+        <v>1.66</v>
+      </c>
+      <c r="BO242">
+        <v>2.71</v>
+      </c>
+      <c r="BP242">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1514" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="357">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -772,6 +772,15 @@
     <t>['3', '49', '63', '80']</t>
   </si>
   <si>
+    <t>['21', '41']</t>
+  </si>
+  <si>
+    <t>['4', '14', '45+3', '71', '87']</t>
+  </si>
+  <si>
+    <t>['34', '70']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1073,6 +1082,9 @@
   </si>
   <si>
     <t>['45+5', '70']</t>
+  </si>
+  <si>
+    <t>['33', '68']</t>
   </si>
 </sst>
 </file>
@@ -1434,7 +1446,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP242"/>
+  <dimension ref="A1:BP246"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1690,7 +1702,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1768,7 +1780,7 @@
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ2">
         <v>1</v>
@@ -2180,7 +2192,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ4">
         <v>0.6</v>
@@ -2389,7 +2401,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ5">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR5">
         <v>0</v>
@@ -2720,7 +2732,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3007,7 +3019,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ8">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR8">
         <v>0</v>
@@ -3416,7 +3428,7 @@
         <v>0</v>
       </c>
       <c r="AP10">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ10">
         <v>0.13</v>
@@ -3544,7 +3556,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3956,7 +3968,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4162,7 +4174,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4243,7 +4255,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ14">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR14">
         <v>0</v>
@@ -4368,7 +4380,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4652,7 +4664,7 @@
         <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ16">
         <v>1.73</v>
@@ -4780,7 +4792,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5064,7 +5076,7 @@
         <v>1</v>
       </c>
       <c r="AP18">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ18">
         <v>1</v>
@@ -5398,7 +5410,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5810,7 +5822,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -6016,7 +6028,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6097,7 +6109,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ23">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR23">
         <v>2.53</v>
@@ -6428,7 +6440,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6712,7 +6724,7 @@
         <v>3</v>
       </c>
       <c r="AP26">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ26">
         <v>1</v>
@@ -6840,7 +6852,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6918,7 +6930,7 @@
         <v>0</v>
       </c>
       <c r="AP27">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ27">
         <v>1.8</v>
@@ -7046,7 +7058,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7252,7 +7264,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7333,7 +7345,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ29">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR29">
         <v>0.96</v>
@@ -7536,10 +7548,10 @@
         <v>3</v>
       </c>
       <c r="AP30">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ30">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR30">
         <v>2.35</v>
@@ -8282,7 +8294,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8694,7 +8706,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9184,7 +9196,7 @@
         <v>0</v>
       </c>
       <c r="AP38">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ38">
         <v>0.13</v>
@@ -9724,7 +9736,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9930,7 +9942,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10008,7 +10020,7 @@
         <v>2</v>
       </c>
       <c r="AP42">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ42">
         <v>1</v>
@@ -10420,7 +10432,7 @@
         <v>0.5</v>
       </c>
       <c r="AP44">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ44">
         <v>0.73</v>
@@ -10629,7 +10641,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ45">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR45">
         <v>1.63</v>
@@ -10832,10 +10844,10 @@
         <v>3</v>
       </c>
       <c r="AP46">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ46">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR46">
         <v>1.58</v>
@@ -11041,7 +11053,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ47">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR47">
         <v>1.76</v>
@@ -11166,7 +11178,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11372,7 +11384,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11578,7 +11590,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11784,7 +11796,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12814,7 +12826,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13098,7 +13110,7 @@
         <v>0.5</v>
       </c>
       <c r="AP57">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ57">
         <v>1.47</v>
@@ -13226,7 +13238,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13304,10 +13316,10 @@
         <v>0.33</v>
       </c>
       <c r="AP58">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ58">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR58">
         <v>0.9399999999999999</v>
@@ -13432,7 +13444,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13513,7 +13525,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ59">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR59">
         <v>1.61</v>
@@ -13844,7 +13856,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13922,7 +13934,7 @@
         <v>1.5</v>
       </c>
       <c r="AP61">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ61">
         <v>1.33</v>
@@ -14668,7 +14680,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15286,7 +15298,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15364,7 +15376,7 @@
         <v>1</v>
       </c>
       <c r="AP68">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ68">
         <v>1</v>
@@ -15492,7 +15504,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15573,7 +15585,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ69">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR69">
         <v>1.21</v>
@@ -15982,7 +15994,7 @@
         <v>1</v>
       </c>
       <c r="AP71">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ71">
         <v>0.6</v>
@@ -16397,7 +16409,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ73">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR73">
         <v>1.73</v>
@@ -16522,7 +16534,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -17836,7 +17848,7 @@
         <v>0.6</v>
       </c>
       <c r="AP80">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ80">
         <v>1.47</v>
@@ -18248,10 +18260,10 @@
         <v>2</v>
       </c>
       <c r="AP82">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ82">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR82">
         <v>0.92</v>
@@ -18376,7 +18388,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18866,7 +18878,7 @@
         <v>1.4</v>
       </c>
       <c r="AP85">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ85">
         <v>1.33</v>
@@ -18994,7 +19006,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19075,7 +19087,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ86">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR86">
         <v>1.86</v>
@@ -19281,7 +19293,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ87">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR87">
         <v>1.36</v>
@@ -19484,7 +19496,7 @@
         <v>0.8</v>
       </c>
       <c r="AP88">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ88">
         <v>1</v>
@@ -20024,7 +20036,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20230,7 +20242,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20642,7 +20654,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20720,10 +20732,10 @@
         <v>1.6</v>
       </c>
       <c r="AP94">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ94">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR94">
         <v>2.03</v>
@@ -21054,7 +21066,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21260,7 +21272,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21338,7 +21350,7 @@
         <v>0.2</v>
       </c>
       <c r="AP97">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ97">
         <v>0.73</v>
@@ -21672,7 +21684,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21750,10 +21762,10 @@
         <v>0.83</v>
       </c>
       <c r="AP99">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ99">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR99">
         <v>1.16</v>
@@ -21878,7 +21890,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -22084,7 +22096,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22371,7 +22383,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ102">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR102">
         <v>1.86</v>
@@ -22986,7 +22998,7 @@
         <v>1.33</v>
       </c>
       <c r="AP105">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ105">
         <v>1.33</v>
@@ -23114,7 +23126,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23320,7 +23332,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23401,7 +23413,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ107">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR107">
         <v>1.5</v>
@@ -23526,7 +23538,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23938,7 +23950,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24019,7 +24031,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ110">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR110">
         <v>1.65</v>
@@ -24428,7 +24440,7 @@
         <v>2</v>
       </c>
       <c r="AP112">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ112">
         <v>1.8</v>
@@ -24556,7 +24568,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24634,7 +24646,7 @@
         <v>1.86</v>
       </c>
       <c r="AP113">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ113">
         <v>1.73</v>
@@ -25046,10 +25058,10 @@
         <v>0.71</v>
       </c>
       <c r="AP115">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ115">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR115">
         <v>2.07</v>
@@ -25252,7 +25264,7 @@
         <v>0.67</v>
       </c>
       <c r="AP116">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ116">
         <v>0.73</v>
@@ -25792,7 +25804,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26410,7 +26422,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26694,7 +26706,7 @@
         <v>1.29</v>
       </c>
       <c r="AP123">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ123">
         <v>1</v>
@@ -27028,7 +27040,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27315,7 +27327,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ126">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR126">
         <v>1.26</v>
@@ -27440,7 +27452,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27518,7 +27530,7 @@
         <v>0.57</v>
       </c>
       <c r="AP127">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ127">
         <v>0.73</v>
@@ -27724,10 +27736,10 @@
         <v>1.57</v>
       </c>
       <c r="AP128">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ128">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR128">
         <v>1.7</v>
@@ -27852,7 +27864,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -28058,7 +28070,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28342,7 +28354,7 @@
         <v>0.88</v>
       </c>
       <c r="AP131">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ131">
         <v>0.6</v>
@@ -28470,7 +28482,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28757,7 +28769,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ133">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR133">
         <v>1.68</v>
@@ -28882,7 +28894,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29294,7 +29306,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29787,7 +29799,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ138">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR138">
         <v>1.55</v>
@@ -29990,7 +30002,7 @@
         <v>0.63</v>
       </c>
       <c r="AP139">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ139">
         <v>0.93</v>
@@ -30324,7 +30336,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30608,7 +30620,7 @@
         <v>1.63</v>
       </c>
       <c r="AP142">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ142">
         <v>1.8</v>
@@ -30736,7 +30748,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30814,7 +30826,7 @@
         <v>0.88</v>
       </c>
       <c r="AP143">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ143">
         <v>1</v>
@@ -30942,7 +30954,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31023,7 +31035,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ144">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR144">
         <v>1.4</v>
@@ -31354,7 +31366,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31641,7 +31653,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ147">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR147">
         <v>1.75</v>
@@ -31766,7 +31778,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31847,7 +31859,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ148">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR148">
         <v>1.11</v>
@@ -31972,7 +31984,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32050,7 +32062,7 @@
         <v>0.44</v>
       </c>
       <c r="AP149">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ149">
         <v>0.6</v>
@@ -32259,7 +32271,7 @@
         <v>2.73</v>
       </c>
       <c r="AQ150">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR150">
         <v>1.79</v>
@@ -32462,7 +32474,7 @@
         <v>1.11</v>
       </c>
       <c r="AP151">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ151">
         <v>1.33</v>
@@ -32590,7 +32602,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32668,7 +32680,7 @@
         <v>1.89</v>
       </c>
       <c r="AP152">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ152">
         <v>1.73</v>
@@ -33002,7 +33014,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33208,7 +33220,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33414,7 +33426,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33492,7 +33504,7 @@
         <v>0.78</v>
       </c>
       <c r="AP156">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ156">
         <v>1</v>
@@ -33826,7 +33838,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34238,7 +34250,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34444,7 +34456,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34728,7 +34740,7 @@
         <v>0.5</v>
       </c>
       <c r="AP162">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ162">
         <v>0.6</v>
@@ -34856,7 +34868,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34937,7 +34949,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ163">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR163">
         <v>1.85</v>
@@ -35268,7 +35280,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35474,7 +35486,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35552,10 +35564,10 @@
         <v>1.5</v>
       </c>
       <c r="AP166">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ166">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR166">
         <v>1.26</v>
@@ -35886,7 +35898,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36504,7 +36516,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36710,7 +36722,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36916,7 +36928,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -36994,7 +37006,7 @@
         <v>0.1</v>
       </c>
       <c r="AP173">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ173">
         <v>0.13</v>
@@ -37122,7 +37134,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37203,7 +37215,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ174">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR174">
         <v>1.38</v>
@@ -37406,7 +37418,7 @@
         <v>0.73</v>
       </c>
       <c r="AP175">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ175">
         <v>0.6</v>
@@ -37534,7 +37546,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37740,7 +37752,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38027,7 +38039,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ178">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR178">
         <v>1.57</v>
@@ -38152,7 +38164,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38358,7 +38370,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38642,7 +38654,7 @@
         <v>0.45</v>
       </c>
       <c r="AP181">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ181">
         <v>0.6</v>
@@ -38848,7 +38860,7 @@
         <v>1.5</v>
       </c>
       <c r="AP182">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ182">
         <v>1</v>
@@ -38976,7 +38988,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39054,7 +39066,7 @@
         <v>1.18</v>
       </c>
       <c r="AP183">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ183">
         <v>1.47</v>
@@ -39182,7 +39194,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40006,7 +40018,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40624,7 +40636,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40702,10 +40714,10 @@
         <v>0.73</v>
       </c>
       <c r="AP191">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ191">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR191">
         <v>1.79</v>
@@ -40911,7 +40923,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ192">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR192">
         <v>1.52</v>
@@ -41036,7 +41048,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41242,7 +41254,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41526,7 +41538,7 @@
         <v>0.67</v>
       </c>
       <c r="AP195">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ195">
         <v>0.6</v>
@@ -41735,7 +41747,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ196">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR196">
         <v>1.08</v>
@@ -42147,7 +42159,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ198">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR198">
         <v>1.68</v>
@@ -42272,7 +42284,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42478,7 +42490,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42762,7 +42774,7 @@
         <v>0.92</v>
       </c>
       <c r="AP201">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ201">
         <v>1</v>
@@ -42890,7 +42902,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -42968,7 +42980,7 @@
         <v>1.67</v>
       </c>
       <c r="AP202">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ202">
         <v>1.8</v>
@@ -43096,7 +43108,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43302,7 +43314,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43508,7 +43520,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43714,7 +43726,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -43998,7 +44010,7 @@
         <v>0.75</v>
       </c>
       <c r="AP207">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ207">
         <v>1</v>
@@ -44207,7 +44219,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ208">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR208">
         <v>1.72</v>
@@ -44619,7 +44631,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ210">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR210">
         <v>1.55</v>
@@ -44950,7 +44962,7 @@
         <v>227</v>
       </c>
       <c r="P212" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q212">
         <v>2.75</v>
@@ -45156,7 +45168,7 @@
         <v>239</v>
       </c>
       <c r="P213" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -45362,7 +45374,7 @@
         <v>86</v>
       </c>
       <c r="P214" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q214">
         <v>1.71</v>
@@ -45440,7 +45452,7 @@
         <v>0.85</v>
       </c>
       <c r="AP214">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ214">
         <v>0.93</v>
@@ -45774,7 +45786,7 @@
         <v>87</v>
       </c>
       <c r="P216" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q216">
         <v>3.25</v>
@@ -46392,7 +46404,7 @@
         <v>88</v>
       </c>
       <c r="P219" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46679,7 +46691,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ220">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR220">
         <v>1.72</v>
@@ -46804,7 +46816,7 @@
         <v>241</v>
       </c>
       <c r="P221" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q221">
         <v>2.25</v>
@@ -47088,7 +47100,7 @@
         <v>1.15</v>
       </c>
       <c r="AP222">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ222">
         <v>1</v>
@@ -47294,7 +47306,7 @@
         <v>0.92</v>
       </c>
       <c r="AP223">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ223">
         <v>1</v>
@@ -47422,7 +47434,7 @@
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q224">
         <v>4.33</v>
@@ -47500,10 +47512,10 @@
         <v>1.62</v>
       </c>
       <c r="AP224">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ224">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR224">
         <v>1.22</v>
@@ -48658,7 +48670,7 @@
         <v>174</v>
       </c>
       <c r="P230" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q230">
         <v>4.75</v>
@@ -48945,7 +48957,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ231">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AR231">
         <v>1.88</v>
@@ -49070,7 +49082,7 @@
         <v>87</v>
       </c>
       <c r="P232" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49354,7 +49366,7 @@
         <v>1</v>
       </c>
       <c r="AP233">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ233">
         <v>0.93</v>
@@ -49766,10 +49778,10 @@
         <v>1.29</v>
       </c>
       <c r="AP235">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AQ235">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="AR235">
         <v>1.24</v>
@@ -50100,7 +50112,7 @@
         <v>249</v>
       </c>
       <c r="P237" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50306,7 +50318,7 @@
         <v>250</v>
       </c>
       <c r="P238" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q238">
         <v>3.1</v>
@@ -50387,7 +50399,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ238">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR238">
         <v>1.28</v>
@@ -50512,7 +50524,7 @@
         <v>118</v>
       </c>
       <c r="P239" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q239">
         <v>3.75</v>
@@ -50590,7 +50602,7 @@
         <v>0.86</v>
       </c>
       <c r="AP239">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="AQ239">
         <v>1</v>
@@ -50718,7 +50730,7 @@
         <v>251</v>
       </c>
       <c r="P240" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -50796,7 +50808,7 @@
         <v>1.07</v>
       </c>
       <c r="AP240">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="AQ240">
         <v>1</v>
@@ -50924,7 +50936,7 @@
         <v>105</v>
       </c>
       <c r="P241" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q241">
         <v>2.3</v>
@@ -51287,6 +51299,830 @@
       </c>
       <c r="BP242">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="243" spans="1:68">
+      <c r="A243" s="1">
+        <v>242</v>
+      </c>
+      <c r="B243">
+        <v>7858308</v>
+      </c>
+      <c r="C243" t="s">
+        <v>68</v>
+      </c>
+      <c r="D243" t="s">
+        <v>69</v>
+      </c>
+      <c r="E243" s="2">
+        <v>45745.5</v>
+      </c>
+      <c r="F243">
+        <v>1</v>
+      </c>
+      <c r="G243" t="s">
+        <v>72</v>
+      </c>
+      <c r="H243" t="s">
+        <v>81</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>0</v>
+      </c>
+      <c r="L243">
+        <v>0</v>
+      </c>
+      <c r="M243">
+        <v>1</v>
+      </c>
+      <c r="N243">
+        <v>1</v>
+      </c>
+      <c r="O243" t="s">
+        <v>87</v>
+      </c>
+      <c r="P243" t="s">
+        <v>264</v>
+      </c>
+      <c r="Q243">
+        <v>3.75</v>
+      </c>
+      <c r="R243">
+        <v>2.25</v>
+      </c>
+      <c r="S243">
+        <v>2.75</v>
+      </c>
+      <c r="T243">
+        <v>1.36</v>
+      </c>
+      <c r="U243">
+        <v>3</v>
+      </c>
+      <c r="V243">
+        <v>2.63</v>
+      </c>
+      <c r="W243">
+        <v>1.44</v>
+      </c>
+      <c r="X243">
+        <v>7</v>
+      </c>
+      <c r="Y243">
+        <v>1.1</v>
+      </c>
+      <c r="Z243">
+        <v>3.14</v>
+      </c>
+      <c r="AA243">
+        <v>3.45</v>
+      </c>
+      <c r="AB243">
+        <v>2.16</v>
+      </c>
+      <c r="AC243">
+        <v>1.05</v>
+      </c>
+      <c r="AD243">
+        <v>9.5</v>
+      </c>
+      <c r="AE243">
+        <v>1.25</v>
+      </c>
+      <c r="AF243">
+        <v>3.75</v>
+      </c>
+      <c r="AG243">
+        <v>1.75</v>
+      </c>
+      <c r="AH243">
+        <v>1.95</v>
+      </c>
+      <c r="AI243">
+        <v>1.67</v>
+      </c>
+      <c r="AJ243">
+        <v>2.1</v>
+      </c>
+      <c r="AK243">
+        <v>1.65</v>
+      </c>
+      <c r="AL243">
+        <v>1.29</v>
+      </c>
+      <c r="AM243">
+        <v>1.34</v>
+      </c>
+      <c r="AN243">
+        <v>1.07</v>
+      </c>
+      <c r="AO243">
+        <v>0.6</v>
+      </c>
+      <c r="AP243">
+        <v>1</v>
+      </c>
+      <c r="AQ243">
+        <v>0.75</v>
+      </c>
+      <c r="AR243">
+        <v>1.29</v>
+      </c>
+      <c r="AS243">
+        <v>1.21</v>
+      </c>
+      <c r="AT243">
+        <v>2.5</v>
+      </c>
+      <c r="AU243">
+        <v>0</v>
+      </c>
+      <c r="AV243">
+        <v>11</v>
+      </c>
+      <c r="AW243">
+        <v>6</v>
+      </c>
+      <c r="AX243">
+        <v>17</v>
+      </c>
+      <c r="AY243">
+        <v>6</v>
+      </c>
+      <c r="AZ243">
+        <v>33</v>
+      </c>
+      <c r="BA243">
+        <v>0</v>
+      </c>
+      <c r="BB243">
+        <v>9</v>
+      </c>
+      <c r="BC243">
+        <v>9</v>
+      </c>
+      <c r="BD243">
+        <v>2.24</v>
+      </c>
+      <c r="BE243">
+        <v>6.7</v>
+      </c>
+      <c r="BF243">
+        <v>2.01</v>
+      </c>
+      <c r="BG243">
+        <v>1.14</v>
+      </c>
+      <c r="BH243">
+        <v>4.33</v>
+      </c>
+      <c r="BI243">
+        <v>1.3</v>
+      </c>
+      <c r="BJ243">
+        <v>2.97</v>
+      </c>
+      <c r="BK243">
+        <v>1.56</v>
+      </c>
+      <c r="BL243">
+        <v>2.21</v>
+      </c>
+      <c r="BM243">
+        <v>1.95</v>
+      </c>
+      <c r="BN243">
+        <v>1.77</v>
+      </c>
+      <c r="BO243">
+        <v>2.51</v>
+      </c>
+      <c r="BP243">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="244" spans="1:68">
+      <c r="A244" s="1">
+        <v>243</v>
+      </c>
+      <c r="B244">
+        <v>7858309</v>
+      </c>
+      <c r="C244" t="s">
+        <v>68</v>
+      </c>
+      <c r="D244" t="s">
+        <v>69</v>
+      </c>
+      <c r="E244" s="2">
+        <v>45745.59375</v>
+      </c>
+      <c r="F244">
+        <v>1</v>
+      </c>
+      <c r="G244" t="s">
+        <v>84</v>
+      </c>
+      <c r="H244" t="s">
+        <v>79</v>
+      </c>
+      <c r="I244">
+        <v>2</v>
+      </c>
+      <c r="J244">
+        <v>1</v>
+      </c>
+      <c r="K244">
+        <v>3</v>
+      </c>
+      <c r="L244">
+        <v>2</v>
+      </c>
+      <c r="M244">
+        <v>2</v>
+      </c>
+      <c r="N244">
+        <v>4</v>
+      </c>
+      <c r="O244" t="s">
+        <v>252</v>
+      </c>
+      <c r="P244" t="s">
+        <v>356</v>
+      </c>
+      <c r="Q244">
+        <v>3.4</v>
+      </c>
+      <c r="R244">
+        <v>2.05</v>
+      </c>
+      <c r="S244">
+        <v>3.25</v>
+      </c>
+      <c r="T244">
+        <v>1.44</v>
+      </c>
+      <c r="U244">
+        <v>2.63</v>
+      </c>
+      <c r="V244">
+        <v>3.25</v>
+      </c>
+      <c r="W244">
+        <v>1.33</v>
+      </c>
+      <c r="X244">
+        <v>10</v>
+      </c>
+      <c r="Y244">
+        <v>1.06</v>
+      </c>
+      <c r="Z244">
+        <v>2.73</v>
+      </c>
+      <c r="AA244">
+        <v>3.16</v>
+      </c>
+      <c r="AB244">
+        <v>2.58</v>
+      </c>
+      <c r="AC244">
+        <v>1.07</v>
+      </c>
+      <c r="AD244">
+        <v>7.75</v>
+      </c>
+      <c r="AE244">
+        <v>1.34</v>
+      </c>
+      <c r="AF244">
+        <v>3.22</v>
+      </c>
+      <c r="AG244">
+        <v>1.85</v>
+      </c>
+      <c r="AH244">
+        <v>1.85</v>
+      </c>
+      <c r="AI244">
+        <v>1.8</v>
+      </c>
+      <c r="AJ244">
+        <v>1.95</v>
+      </c>
+      <c r="AK244">
+        <v>1.47</v>
+      </c>
+      <c r="AL244">
+        <v>1.33</v>
+      </c>
+      <c r="AM244">
+        <v>1.44</v>
+      </c>
+      <c r="AN244">
+        <v>1.67</v>
+      </c>
+      <c r="AO244">
+        <v>1</v>
+      </c>
+      <c r="AP244">
+        <v>1.63</v>
+      </c>
+      <c r="AQ244">
+        <v>1</v>
+      </c>
+      <c r="AR244">
+        <v>1.24</v>
+      </c>
+      <c r="AS244">
+        <v>1.5</v>
+      </c>
+      <c r="AT244">
+        <v>2.74</v>
+      </c>
+      <c r="AU244">
+        <v>6</v>
+      </c>
+      <c r="AV244">
+        <v>7</v>
+      </c>
+      <c r="AW244">
+        <v>9</v>
+      </c>
+      <c r="AX244">
+        <v>8</v>
+      </c>
+      <c r="AY244">
+        <v>16</v>
+      </c>
+      <c r="AZ244">
+        <v>15</v>
+      </c>
+      <c r="BA244">
+        <v>8</v>
+      </c>
+      <c r="BB244">
+        <v>6</v>
+      </c>
+      <c r="BC244">
+        <v>14</v>
+      </c>
+      <c r="BD244">
+        <v>2.45</v>
+      </c>
+      <c r="BE244">
+        <v>6.65</v>
+      </c>
+      <c r="BF244">
+        <v>1.87</v>
+      </c>
+      <c r="BG244">
+        <v>1.16</v>
+      </c>
+      <c r="BH244">
+        <v>4.1</v>
+      </c>
+      <c r="BI244">
+        <v>1.33</v>
+      </c>
+      <c r="BJ244">
+        <v>2.83</v>
+      </c>
+      <c r="BK244">
+        <v>1.7</v>
+      </c>
+      <c r="BL244">
+        <v>2.05</v>
+      </c>
+      <c r="BM244">
+        <v>2.05</v>
+      </c>
+      <c r="BN244">
+        <v>1.7</v>
+      </c>
+      <c r="BO244">
+        <v>2.64</v>
+      </c>
+      <c r="BP244">
+        <v>1.4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:68">
+      <c r="A245" s="1">
+        <v>244</v>
+      </c>
+      <c r="B245">
+        <v>7858310</v>
+      </c>
+      <c r="C245" t="s">
+        <v>68</v>
+      </c>
+      <c r="D245" t="s">
+        <v>69</v>
+      </c>
+      <c r="E245" s="2">
+        <v>45745.69791666666</v>
+      </c>
+      <c r="F245">
+        <v>1</v>
+      </c>
+      <c r="G245" t="s">
+        <v>78</v>
+      </c>
+      <c r="H245" t="s">
+        <v>82</v>
+      </c>
+      <c r="I245">
+        <v>3</v>
+      </c>
+      <c r="J245">
+        <v>1</v>
+      </c>
+      <c r="K245">
+        <v>4</v>
+      </c>
+      <c r="L245">
+        <v>5</v>
+      </c>
+      <c r="M245">
+        <v>1</v>
+      </c>
+      <c r="N245">
+        <v>6</v>
+      </c>
+      <c r="O245" t="s">
+        <v>253</v>
+      </c>
+      <c r="P245" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q245">
+        <v>2.1</v>
+      </c>
+      <c r="R245">
+        <v>2.38</v>
+      </c>
+      <c r="S245">
+        <v>5.5</v>
+      </c>
+      <c r="T245">
+        <v>1.33</v>
+      </c>
+      <c r="U245">
+        <v>3.25</v>
+      </c>
+      <c r="V245">
+        <v>2.63</v>
+      </c>
+      <c r="W245">
+        <v>1.44</v>
+      </c>
+      <c r="X245">
+        <v>6.5</v>
+      </c>
+      <c r="Y245">
+        <v>1.11</v>
+      </c>
+      <c r="Z245">
+        <v>1.56</v>
+      </c>
+      <c r="AA245">
+        <v>4.1</v>
+      </c>
+      <c r="AB245">
+        <v>5.4</v>
+      </c>
+      <c r="AC245">
+        <v>1.03</v>
+      </c>
+      <c r="AD245">
+        <v>11.5</v>
+      </c>
+      <c r="AE245">
+        <v>1.24</v>
+      </c>
+      <c r="AF245">
+        <v>4.05</v>
+      </c>
+      <c r="AG245">
+        <v>1.67</v>
+      </c>
+      <c r="AH245">
+        <v>2.1</v>
+      </c>
+      <c r="AI245">
+        <v>1.8</v>
+      </c>
+      <c r="AJ245">
+        <v>1.95</v>
+      </c>
+      <c r="AK245">
+        <v>1.16</v>
+      </c>
+      <c r="AL245">
+        <v>1.22</v>
+      </c>
+      <c r="AM245">
+        <v>2.3</v>
+      </c>
+      <c r="AN245">
+        <v>2.2</v>
+      </c>
+      <c r="AO245">
+        <v>1.27</v>
+      </c>
+      <c r="AP245">
+        <v>2.25</v>
+      </c>
+      <c r="AQ245">
+        <v>1.19</v>
+      </c>
+      <c r="AR245">
+        <v>1.84</v>
+      </c>
+      <c r="AS245">
+        <v>1.2</v>
+      </c>
+      <c r="AT245">
+        <v>3.04</v>
+      </c>
+      <c r="AU245">
+        <v>10</v>
+      </c>
+      <c r="AV245">
+        <v>4</v>
+      </c>
+      <c r="AW245">
+        <v>6</v>
+      </c>
+      <c r="AX245">
+        <v>4</v>
+      </c>
+      <c r="AY245">
+        <v>16</v>
+      </c>
+      <c r="AZ245">
+        <v>8</v>
+      </c>
+      <c r="BA245">
+        <v>5</v>
+      </c>
+      <c r="BB245">
+        <v>4</v>
+      </c>
+      <c r="BC245">
+        <v>9</v>
+      </c>
+      <c r="BD245">
+        <v>1.43</v>
+      </c>
+      <c r="BE245">
+        <v>9.6</v>
+      </c>
+      <c r="BF245">
+        <v>3.45</v>
+      </c>
+      <c r="BG245">
+        <v>1.19</v>
+      </c>
+      <c r="BH245">
+        <v>3.78</v>
+      </c>
+      <c r="BI245">
+        <v>1.4</v>
+      </c>
+      <c r="BJ245">
+        <v>2.64</v>
+      </c>
+      <c r="BK245">
+        <v>1.7</v>
+      </c>
+      <c r="BL245">
+        <v>2.05</v>
+      </c>
+      <c r="BM245">
+        <v>2.14</v>
+      </c>
+      <c r="BN245">
+        <v>1.6</v>
+      </c>
+      <c r="BO245">
+        <v>2.81</v>
+      </c>
+      <c r="BP245">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="246" spans="1:68">
+      <c r="A246" s="1">
+        <v>245</v>
+      </c>
+      <c r="B246">
+        <v>7858311</v>
+      </c>
+      <c r="C246" t="s">
+        <v>68</v>
+      </c>
+      <c r="D246" t="s">
+        <v>69</v>
+      </c>
+      <c r="E246" s="2">
+        <v>45746.35416666666</v>
+      </c>
+      <c r="F246">
+        <v>1</v>
+      </c>
+      <c r="G246" t="s">
+        <v>70</v>
+      </c>
+      <c r="H246" t="s">
+        <v>73</v>
+      </c>
+      <c r="I246">
+        <v>1</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>1</v>
+      </c>
+      <c r="L246">
+        <v>2</v>
+      </c>
+      <c r="M246">
+        <v>0</v>
+      </c>
+      <c r="N246">
+        <v>2</v>
+      </c>
+      <c r="O246" t="s">
+        <v>254</v>
+      </c>
+      <c r="P246" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q246">
+        <v>2.2</v>
+      </c>
+      <c r="R246">
+        <v>2.3</v>
+      </c>
+      <c r="S246">
+        <v>5.5</v>
+      </c>
+      <c r="T246">
+        <v>1.36</v>
+      </c>
+      <c r="U246">
+        <v>3</v>
+      </c>
+      <c r="V246">
+        <v>2.63</v>
+      </c>
+      <c r="W246">
+        <v>1.44</v>
+      </c>
+      <c r="X246">
+        <v>7</v>
+      </c>
+      <c r="Y246">
+        <v>1.1</v>
+      </c>
+      <c r="Z246">
+        <v>1.64</v>
+      </c>
+      <c r="AA246">
+        <v>3.55</v>
+      </c>
+      <c r="AB246">
+        <v>5.6</v>
+      </c>
+      <c r="AC246">
+        <v>1.04</v>
+      </c>
+      <c r="AD246">
+        <v>10</v>
+      </c>
+      <c r="AE246">
+        <v>1.25</v>
+      </c>
+      <c r="AF246">
+        <v>3.91</v>
+      </c>
+      <c r="AG246">
+        <v>1.82</v>
+      </c>
+      <c r="AH246">
+        <v>1.92</v>
+      </c>
+      <c r="AI246">
+        <v>1.8</v>
+      </c>
+      <c r="AJ246">
+        <v>1.95</v>
+      </c>
+      <c r="AK246">
+        <v>1.14</v>
+      </c>
+      <c r="AL246">
+        <v>1.24</v>
+      </c>
+      <c r="AM246">
+        <v>2.25</v>
+      </c>
+      <c r="AN246">
+        <v>2.2</v>
+      </c>
+      <c r="AO246">
+        <v>1.6</v>
+      </c>
+      <c r="AP246">
+        <v>2.25</v>
+      </c>
+      <c r="AQ246">
+        <v>1.5</v>
+      </c>
+      <c r="AR246">
+        <v>2.09</v>
+      </c>
+      <c r="AS246">
+        <v>1.38</v>
+      </c>
+      <c r="AT246">
+        <v>3.47</v>
+      </c>
+      <c r="AU246">
+        <v>10</v>
+      </c>
+      <c r="AV246">
+        <v>2</v>
+      </c>
+      <c r="AW246">
+        <v>11</v>
+      </c>
+      <c r="AX246">
+        <v>3</v>
+      </c>
+      <c r="AY246">
+        <v>22</v>
+      </c>
+      <c r="AZ246">
+        <v>6</v>
+      </c>
+      <c r="BA246">
+        <v>7</v>
+      </c>
+      <c r="BB246">
+        <v>2</v>
+      </c>
+      <c r="BC246">
+        <v>9</v>
+      </c>
+      <c r="BD246">
+        <v>1.32</v>
+      </c>
+      <c r="BE246">
+        <v>9.9</v>
+      </c>
+      <c r="BF246">
+        <v>4.25</v>
+      </c>
+      <c r="BG246">
+        <v>1.27</v>
+      </c>
+      <c r="BH246">
+        <v>3.14</v>
+      </c>
+      <c r="BI246">
+        <v>1.52</v>
+      </c>
+      <c r="BJ246">
+        <v>2.3</v>
+      </c>
+      <c r="BK246">
+        <v>1.91</v>
+      </c>
+      <c r="BL246">
+        <v>1.8</v>
+      </c>
+      <c r="BM246">
+        <v>2.48</v>
+      </c>
+      <c r="BN246">
+        <v>1.45</v>
+      </c>
+      <c r="BO246">
+        <v>3.28</v>
+      </c>
+      <c r="BP246">
+        <v>1.25</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="360">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -781,6 +781,12 @@
     <t>['34', '70']</t>
   </si>
   <si>
+    <t>['14', '90']</t>
+  </si>
+  <si>
+    <t>['38', '50', '88', '90+1']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1085,6 +1091,9 @@
   </si>
   <si>
     <t>['33', '68']</t>
+  </si>
+  <si>
+    <t>['54', '80']</t>
   </si>
 </sst>
 </file>
@@ -1446,7 +1455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP246"/>
+  <dimension ref="A1:BP249"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1702,7 +1711,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1986,7 +1995,7 @@
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ3">
         <v>1.47</v>
@@ -2604,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="AP6">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ6">
         <v>0.93</v>
@@ -2732,7 +2741,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -2813,7 +2822,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ7">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR7">
         <v>0</v>
@@ -3225,7 +3234,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ9">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR9">
         <v>0</v>
@@ -3556,7 +3565,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3637,7 +3646,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ11">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR11">
         <v>0</v>
@@ -3968,7 +3977,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4174,7 +4183,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4380,7 +4389,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4792,7 +4801,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5282,7 +5291,7 @@
         <v>3</v>
       </c>
       <c r="AP19">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ19">
         <v>0.6</v>
@@ -5410,7 +5419,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5822,7 +5831,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5900,7 +5909,7 @@
         <v>0</v>
       </c>
       <c r="AP22">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ22">
         <v>1.73</v>
@@ -6028,7 +6037,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6315,7 +6324,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ24">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR24">
         <v>1.65</v>
@@ -6440,7 +6449,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6852,7 +6861,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -7058,7 +7067,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7264,7 +7273,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7757,7 +7766,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ31">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR31">
         <v>1.23</v>
@@ -8169,7 +8178,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ33">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR33">
         <v>1.52</v>
@@ -8294,7 +8303,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8706,7 +8715,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8784,7 +8793,7 @@
         <v>0</v>
       </c>
       <c r="AP36">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ36">
         <v>1.73</v>
@@ -9608,10 +9617,10 @@
         <v>1.5</v>
       </c>
       <c r="AP40">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ40">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR40">
         <v>1.69</v>
@@ -9736,7 +9745,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9942,7 +9951,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10435,7 +10444,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ44">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR44">
         <v>1.89</v>
@@ -11178,7 +11187,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11256,7 +11265,7 @@
         <v>0.33</v>
       </c>
       <c r="AP48">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ48">
         <v>0.93</v>
@@ -11384,7 +11393,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11590,7 +11599,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11796,7 +11805,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11877,7 +11886,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ51">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR51">
         <v>1.42</v>
@@ -12826,7 +12835,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13238,7 +13247,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13444,7 +13453,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13856,7 +13865,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -13937,7 +13946,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ61">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR61">
         <v>2.01</v>
@@ -14143,7 +14152,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ62">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR62">
         <v>1.5</v>
@@ -14346,7 +14355,7 @@
         <v>2.33</v>
       </c>
       <c r="AP63">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ63">
         <v>1</v>
@@ -14680,7 +14689,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14761,7 +14770,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ65">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR65">
         <v>1.79</v>
@@ -15170,7 +15179,7 @@
         <v>1.25</v>
       </c>
       <c r="AP67">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ67">
         <v>1</v>
@@ -15298,7 +15307,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15379,7 +15388,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ68">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR68">
         <v>1.04</v>
@@ -15504,7 +15513,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15582,7 +15591,7 @@
         <v>2.33</v>
       </c>
       <c r="AP69">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ69">
         <v>1.5</v>
@@ -16534,7 +16543,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -17230,7 +17239,7 @@
         <v>1</v>
       </c>
       <c r="AP77">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ77">
         <v>1</v>
@@ -17645,7 +17654,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ79">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR79">
         <v>1.88</v>
@@ -18057,7 +18066,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ81">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR81">
         <v>0.89</v>
@@ -18388,7 +18397,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18881,7 +18890,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ85">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR85">
         <v>1.67</v>
@@ -19006,7 +19015,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19084,7 +19093,7 @@
         <v>1</v>
       </c>
       <c r="AP86">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ86">
         <v>0.75</v>
@@ -20036,7 +20045,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20242,7 +20251,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20320,7 +20329,7 @@
         <v>1</v>
       </c>
       <c r="AP92">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ92">
         <v>1</v>
@@ -20529,7 +20538,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ93">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR93">
         <v>1.23</v>
@@ -20654,7 +20663,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -21066,7 +21075,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21272,7 +21281,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21353,7 +21362,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ97">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR97">
         <v>1.7</v>
@@ -21684,7 +21693,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21890,7 +21899,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -22096,7 +22105,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22380,7 +22389,7 @@
         <v>1.6</v>
       </c>
       <c r="AP102">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ102">
         <v>1.19</v>
@@ -23001,7 +23010,7 @@
         <v>1</v>
       </c>
       <c r="AQ105">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR105">
         <v>0.83</v>
@@ -23126,7 +23135,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23332,7 +23341,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23538,7 +23547,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23616,7 +23625,7 @@
         <v>0.86</v>
       </c>
       <c r="AP108">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ108">
         <v>0.6</v>
@@ -23825,7 +23834,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ109">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR109">
         <v>1.75</v>
@@ -23950,7 +23959,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24568,7 +24577,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -25267,7 +25276,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ116">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR116">
         <v>1.18</v>
@@ -25470,7 +25479,7 @@
         <v>0.57</v>
       </c>
       <c r="AP117">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ117">
         <v>1</v>
@@ -25804,7 +25813,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26091,7 +26100,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ120">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR120">
         <v>1.64</v>
@@ -26422,7 +26431,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -27040,7 +27049,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27452,7 +27461,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27533,7 +27542,7 @@
         <v>1</v>
       </c>
       <c r="AQ127">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR127">
         <v>0.92</v>
@@ -27864,7 +27873,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27945,7 +27954,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ129">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR129">
         <v>1.82</v>
@@ -28070,7 +28079,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28148,7 +28157,7 @@
         <v>0.5</v>
       </c>
       <c r="AP130">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ130">
         <v>0.6</v>
@@ -28482,7 +28491,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28894,7 +28903,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29306,7 +29315,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29590,10 +29599,10 @@
         <v>1</v>
       </c>
       <c r="AP137">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ137">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR137">
         <v>1.17</v>
@@ -30336,7 +30345,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30748,7 +30757,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30829,7 +30838,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ143">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR143">
         <v>1.68</v>
@@ -30954,7 +30963,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31241,7 +31250,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ145">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR145">
         <v>1.64</v>
@@ -31366,7 +31375,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31778,7 +31787,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31856,7 +31865,7 @@
         <v>1.33</v>
       </c>
       <c r="AP148">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ148">
         <v>1.19</v>
@@ -31984,7 +31993,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32268,7 +32277,7 @@
         <v>1.67</v>
       </c>
       <c r="AP150">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ150">
         <v>1.5</v>
@@ -32477,7 +32486,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ151">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR151">
         <v>1.23</v>
@@ -32602,7 +32611,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33014,7 +33023,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33220,7 +33229,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33426,7 +33435,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33507,7 +33516,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ156">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR156">
         <v>2.05</v>
@@ -33838,7 +33847,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34250,7 +34259,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34331,7 +34340,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ160">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR160">
         <v>1.47</v>
@@ -34456,7 +34465,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34868,7 +34877,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35152,7 +35161,7 @@
         <v>0.8</v>
       </c>
       <c r="AP164">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ164">
         <v>0.6</v>
@@ -35280,7 +35289,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35486,7 +35495,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35770,10 +35779,10 @@
         <v>1.3</v>
       </c>
       <c r="AP167">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ167">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR167">
         <v>1.07</v>
@@ -35898,7 +35907,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36516,7 +36525,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36594,10 +36603,10 @@
         <v>0.6</v>
       </c>
       <c r="AP171">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ171">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR171">
         <v>1.08</v>
@@ -36722,7 +36731,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36928,7 +36937,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -37134,7 +37143,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37546,7 +37555,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37752,7 +37761,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37833,7 +37842,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ177">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR177">
         <v>1.71</v>
@@ -38164,7 +38173,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38370,7 +38379,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38451,7 +38460,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ180">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR180">
         <v>1.69</v>
@@ -38988,7 +38997,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39194,7 +39203,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39481,7 +39490,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ185">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR185">
         <v>1.29</v>
@@ -40018,7 +40027,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40302,7 +40311,7 @@
         <v>0.09</v>
       </c>
       <c r="AP189">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ189">
         <v>0.13</v>
@@ -40636,7 +40645,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -41048,7 +41057,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41129,7 +41138,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ193">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR193">
         <v>1.37</v>
@@ -41254,7 +41263,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41335,7 +41344,7 @@
         <v>1.53</v>
       </c>
       <c r="AQ194">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR194">
         <v>1.52</v>
@@ -41744,7 +41753,7 @@
         <v>0.67</v>
       </c>
       <c r="AP196">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ196">
         <v>0.75</v>
@@ -41950,10 +41959,10 @@
         <v>0.83</v>
       </c>
       <c r="AP197">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ197">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR197">
         <v>1.75</v>
@@ -42284,7 +42293,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42490,7 +42499,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42902,7 +42911,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -43108,7 +43117,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43314,7 +43323,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43520,7 +43529,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43726,7 +43735,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -44425,7 +44434,7 @@
         <v>1.4</v>
       </c>
       <c r="AQ209">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR209">
         <v>1.64</v>
@@ -44834,7 +44843,7 @@
         <v>0.08</v>
       </c>
       <c r="AP211">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ211">
         <v>0.13</v>
@@ -44962,7 +44971,7 @@
         <v>227</v>
       </c>
       <c r="P212" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Q212">
         <v>2.75</v>
@@ -45168,7 +45177,7 @@
         <v>239</v>
       </c>
       <c r="P213" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -45374,7 +45383,7 @@
         <v>86</v>
       </c>
       <c r="P214" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q214">
         <v>1.71</v>
@@ -45658,10 +45667,10 @@
         <v>1.23</v>
       </c>
       <c r="AP215">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ215">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR215">
         <v>1.77</v>
@@ -45786,7 +45795,7 @@
         <v>87</v>
       </c>
       <c r="P216" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="Q216">
         <v>3.25</v>
@@ -46073,7 +46082,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ217">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR217">
         <v>1.34</v>
@@ -46404,7 +46413,7 @@
         <v>88</v>
       </c>
       <c r="P219" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46816,7 +46825,7 @@
         <v>241</v>
       </c>
       <c r="P221" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q221">
         <v>2.25</v>
@@ -47434,7 +47443,7 @@
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Q224">
         <v>4.33</v>
@@ -47721,7 +47730,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ225">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR225">
         <v>1.31</v>
@@ -48542,7 +48551,7 @@
         <v>1.71</v>
       </c>
       <c r="AP229">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="AQ229">
         <v>1.8</v>
@@ -48670,7 +48679,7 @@
         <v>174</v>
       </c>
       <c r="P230" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q230">
         <v>4.75</v>
@@ -49082,7 +49091,7 @@
         <v>87</v>
       </c>
       <c r="P232" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49163,7 +49172,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ232">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AR232">
         <v>1.76</v>
@@ -49572,7 +49581,7 @@
         <v>1.57</v>
       </c>
       <c r="AP234">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="AQ234">
         <v>1.47</v>
@@ -49987,7 +49996,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ236">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AR236">
         <v>1.65</v>
@@ -50112,7 +50121,7 @@
         <v>249</v>
       </c>
       <c r="P237" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50318,7 +50327,7 @@
         <v>250</v>
       </c>
       <c r="P238" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q238">
         <v>3.1</v>
@@ -50524,7 +50533,7 @@
         <v>118</v>
       </c>
       <c r="P239" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="Q239">
         <v>3.75</v>
@@ -50605,7 +50614,7 @@
         <v>1</v>
       </c>
       <c r="AQ239">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR239">
         <v>1.3</v>
@@ -50730,7 +50739,7 @@
         <v>251</v>
       </c>
       <c r="P240" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -50936,7 +50945,7 @@
         <v>105</v>
       </c>
       <c r="P241" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q241">
         <v>2.3</v>
@@ -51348,7 +51357,7 @@
         <v>87</v>
       </c>
       <c r="P243" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="Q243">
         <v>3.75</v>
@@ -51554,7 +51563,7 @@
         <v>252</v>
       </c>
       <c r="P244" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52123,6 +52132,624 @@
       </c>
       <c r="BP246">
         <v>1.25</v>
+      </c>
+    </row>
+    <row r="247" spans="1:68">
+      <c r="A247" s="1">
+        <v>246</v>
+      </c>
+      <c r="B247">
+        <v>7858312</v>
+      </c>
+      <c r="C247" t="s">
+        <v>68</v>
+      </c>
+      <c r="D247" t="s">
+        <v>69</v>
+      </c>
+      <c r="E247" s="2">
+        <v>45746.45833333334</v>
+      </c>
+      <c r="F247">
+        <v>1</v>
+      </c>
+      <c r="G247" t="s">
+        <v>75</v>
+      </c>
+      <c r="H247" t="s">
+        <v>83</v>
+      </c>
+      <c r="I247">
+        <v>1</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
+      </c>
+      <c r="L247">
+        <v>2</v>
+      </c>
+      <c r="M247">
+        <v>2</v>
+      </c>
+      <c r="N247">
+        <v>4</v>
+      </c>
+      <c r="O247" t="s">
+        <v>255</v>
+      </c>
+      <c r="P247" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q247">
+        <v>3.4</v>
+      </c>
+      <c r="R247">
+        <v>2.05</v>
+      </c>
+      <c r="S247">
+        <v>3.4</v>
+      </c>
+      <c r="T247">
+        <v>1.44</v>
+      </c>
+      <c r="U247">
+        <v>2.63</v>
+      </c>
+      <c r="V247">
+        <v>3.4</v>
+      </c>
+      <c r="W247">
+        <v>1.3</v>
+      </c>
+      <c r="X247">
+        <v>10</v>
+      </c>
+      <c r="Y247">
+        <v>1.06</v>
+      </c>
+      <c r="Z247">
+        <v>2.8</v>
+      </c>
+      <c r="AA247">
+        <v>3.06</v>
+      </c>
+      <c r="AB247">
+        <v>2.59</v>
+      </c>
+      <c r="AC247">
+        <v>1.08</v>
+      </c>
+      <c r="AD247">
+        <v>7.5</v>
+      </c>
+      <c r="AE247">
+        <v>1.42</v>
+      </c>
+      <c r="AF247">
+        <v>2.85</v>
+      </c>
+      <c r="AG247">
+        <v>1.91</v>
+      </c>
+      <c r="AH247">
+        <v>1.83</v>
+      </c>
+      <c r="AI247">
+        <v>1.8</v>
+      </c>
+      <c r="AJ247">
+        <v>1.95</v>
+      </c>
+      <c r="AK247">
+        <v>1.44</v>
+      </c>
+      <c r="AL247">
+        <v>1.35</v>
+      </c>
+      <c r="AM247">
+        <v>1.44</v>
+      </c>
+      <c r="AN247">
+        <v>1.13</v>
+      </c>
+      <c r="AO247">
+        <v>0.73</v>
+      </c>
+      <c r="AP247">
+        <v>1.13</v>
+      </c>
+      <c r="AQ247">
+        <v>0.75</v>
+      </c>
+      <c r="AR247">
+        <v>1.43</v>
+      </c>
+      <c r="AS247">
+        <v>1.41</v>
+      </c>
+      <c r="AT247">
+        <v>2.84</v>
+      </c>
+      <c r="AU247">
+        <v>4</v>
+      </c>
+      <c r="AV247">
+        <v>3</v>
+      </c>
+      <c r="AW247">
+        <v>3</v>
+      </c>
+      <c r="AX247">
+        <v>8</v>
+      </c>
+      <c r="AY247">
+        <v>9</v>
+      </c>
+      <c r="AZ247">
+        <v>14</v>
+      </c>
+      <c r="BA247">
+        <v>2</v>
+      </c>
+      <c r="BB247">
+        <v>4</v>
+      </c>
+      <c r="BC247">
+        <v>6</v>
+      </c>
+      <c r="BD247">
+        <v>1.88</v>
+      </c>
+      <c r="BE247">
+        <v>6.65</v>
+      </c>
+      <c r="BF247">
+        <v>2.43</v>
+      </c>
+      <c r="BG247">
+        <v>1.17</v>
+      </c>
+      <c r="BH247">
+        <v>3.98</v>
+      </c>
+      <c r="BI247">
+        <v>1.35</v>
+      </c>
+      <c r="BJ247">
+        <v>2.74</v>
+      </c>
+      <c r="BK247">
+        <v>1.64</v>
+      </c>
+      <c r="BL247">
+        <v>2.07</v>
+      </c>
+      <c r="BM247">
+        <v>2.05</v>
+      </c>
+      <c r="BN247">
+        <v>1.7</v>
+      </c>
+      <c r="BO247">
+        <v>2.71</v>
+      </c>
+      <c r="BP247">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="248" spans="1:68">
+      <c r="A248" s="1">
+        <v>247</v>
+      </c>
+      <c r="B248">
+        <v>7858313</v>
+      </c>
+      <c r="C248" t="s">
+        <v>68</v>
+      </c>
+      <c r="D248" t="s">
+        <v>69</v>
+      </c>
+      <c r="E248" s="2">
+        <v>45746.5625</v>
+      </c>
+      <c r="F248">
+        <v>1</v>
+      </c>
+      <c r="G248" t="s">
+        <v>74</v>
+      </c>
+      <c r="H248" t="s">
+        <v>85</v>
+      </c>
+      <c r="I248">
+        <v>1</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248">
+        <v>4</v>
+      </c>
+      <c r="M248">
+        <v>0</v>
+      </c>
+      <c r="N248">
+        <v>4</v>
+      </c>
+      <c r="O248" t="s">
+        <v>256</v>
+      </c>
+      <c r="P248" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q248">
+        <v>2.1</v>
+      </c>
+      <c r="R248">
+        <v>2.4</v>
+      </c>
+      <c r="S248">
+        <v>5</v>
+      </c>
+      <c r="T248">
+        <v>1.29</v>
+      </c>
+      <c r="U248">
+        <v>3.5</v>
+      </c>
+      <c r="V248">
+        <v>2.38</v>
+      </c>
+      <c r="W248">
+        <v>1.53</v>
+      </c>
+      <c r="X248">
+        <v>5.5</v>
+      </c>
+      <c r="Y248">
+        <v>1.14</v>
+      </c>
+      <c r="Z248">
+        <v>1.6</v>
+      </c>
+      <c r="AA248">
+        <v>3.85</v>
+      </c>
+      <c r="AB248">
+        <v>5.4</v>
+      </c>
+      <c r="AC248">
+        <v>1.04</v>
+      </c>
+      <c r="AD248">
+        <v>10</v>
+      </c>
+      <c r="AE248">
+        <v>1.2</v>
+      </c>
+      <c r="AF248">
+        <v>4.33</v>
+      </c>
+      <c r="AG248">
+        <v>1.6</v>
+      </c>
+      <c r="AH248">
+        <v>2.25</v>
+      </c>
+      <c r="AI248">
+        <v>1.62</v>
+      </c>
+      <c r="AJ248">
+        <v>2.2</v>
+      </c>
+      <c r="AK248">
+        <v>1.17</v>
+      </c>
+      <c r="AL248">
+        <v>1.23</v>
+      </c>
+      <c r="AM248">
+        <v>2.2</v>
+      </c>
+      <c r="AN248">
+        <v>2.73</v>
+      </c>
+      <c r="AO248">
+        <v>1.33</v>
+      </c>
+      <c r="AP248">
+        <v>2.75</v>
+      </c>
+      <c r="AQ248">
+        <v>1.25</v>
+      </c>
+      <c r="AR248">
+        <v>1.81</v>
+      </c>
+      <c r="AS248">
+        <v>1.33</v>
+      </c>
+      <c r="AT248">
+        <v>3.14</v>
+      </c>
+      <c r="AU248">
+        <v>10</v>
+      </c>
+      <c r="AV248">
+        <v>3</v>
+      </c>
+      <c r="AW248">
+        <v>6</v>
+      </c>
+      <c r="AX248">
+        <v>9</v>
+      </c>
+      <c r="AY248">
+        <v>16</v>
+      </c>
+      <c r="AZ248">
+        <v>21</v>
+      </c>
+      <c r="BA248">
+        <v>4</v>
+      </c>
+      <c r="BB248">
+        <v>5</v>
+      </c>
+      <c r="BC248">
+        <v>9</v>
+      </c>
+      <c r="BD248">
+        <v>1.44</v>
+      </c>
+      <c r="BE248">
+        <v>9.4</v>
+      </c>
+      <c r="BF248">
+        <v>3.4</v>
+      </c>
+      <c r="BG248">
+        <v>1.19</v>
+      </c>
+      <c r="BH248">
+        <v>3.74</v>
+      </c>
+      <c r="BI248">
+        <v>1.4</v>
+      </c>
+      <c r="BJ248">
+        <v>2.64</v>
+      </c>
+      <c r="BK248">
+        <v>1.77</v>
+      </c>
+      <c r="BL248">
+        <v>1.95</v>
+      </c>
+      <c r="BM248">
+        <v>2.15</v>
+      </c>
+      <c r="BN248">
+        <v>1.59</v>
+      </c>
+      <c r="BO248">
+        <v>2.83</v>
+      </c>
+      <c r="BP248">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="249" spans="1:68">
+      <c r="A249" s="1">
+        <v>248</v>
+      </c>
+      <c r="B249">
+        <v>7858314</v>
+      </c>
+      <c r="C249" t="s">
+        <v>68</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249" s="2">
+        <v>45746.59375</v>
+      </c>
+      <c r="F249">
+        <v>1</v>
+      </c>
+      <c r="G249" t="s">
+        <v>71</v>
+      </c>
+      <c r="H249" t="s">
+        <v>77</v>
+      </c>
+      <c r="I249">
+        <v>1</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+      <c r="L249">
+        <v>1</v>
+      </c>
+      <c r="M249">
+        <v>0</v>
+      </c>
+      <c r="N249">
+        <v>1</v>
+      </c>
+      <c r="O249" t="s">
+        <v>238</v>
+      </c>
+      <c r="P249" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q249">
+        <v>3.1</v>
+      </c>
+      <c r="R249">
+        <v>2.3</v>
+      </c>
+      <c r="S249">
+        <v>3.1</v>
+      </c>
+      <c r="T249">
+        <v>1.33</v>
+      </c>
+      <c r="U249">
+        <v>3.25</v>
+      </c>
+      <c r="V249">
+        <v>2.5</v>
+      </c>
+      <c r="W249">
+        <v>1.5</v>
+      </c>
+      <c r="X249">
+        <v>6.5</v>
+      </c>
+      <c r="Y249">
+        <v>1.11</v>
+      </c>
+      <c r="Z249">
+        <v>2.62</v>
+      </c>
+      <c r="AA249">
+        <v>3.59</v>
+      </c>
+      <c r="AB249">
+        <v>2.44</v>
+      </c>
+      <c r="AC249">
+        <v>1.04</v>
+      </c>
+      <c r="AD249">
+        <v>10</v>
+      </c>
+      <c r="AE249">
+        <v>1.22</v>
+      </c>
+      <c r="AF249">
+        <v>4.2</v>
+      </c>
+      <c r="AG249">
+        <v>1.65</v>
+      </c>
+      <c r="AH249">
+        <v>2.15</v>
+      </c>
+      <c r="AI249">
+        <v>1.57</v>
+      </c>
+      <c r="AJ249">
+        <v>2.25</v>
+      </c>
+      <c r="AK249">
+        <v>1.53</v>
+      </c>
+      <c r="AL249">
+        <v>1.28</v>
+      </c>
+      <c r="AM249">
+        <v>1.44</v>
+      </c>
+      <c r="AN249">
+        <v>1.13</v>
+      </c>
+      <c r="AO249">
+        <v>1</v>
+      </c>
+      <c r="AP249">
+        <v>1.25</v>
+      </c>
+      <c r="AQ249">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR249">
+        <v>1.15</v>
+      </c>
+      <c r="AS249">
+        <v>1.57</v>
+      </c>
+      <c r="AT249">
+        <v>2.72</v>
+      </c>
+      <c r="AU249">
+        <v>11</v>
+      </c>
+      <c r="AV249">
+        <v>5</v>
+      </c>
+      <c r="AW249">
+        <v>9</v>
+      </c>
+      <c r="AX249">
+        <v>9</v>
+      </c>
+      <c r="AY249">
+        <v>21</v>
+      </c>
+      <c r="AZ249">
+        <v>18</v>
+      </c>
+      <c r="BA249">
+        <v>8</v>
+      </c>
+      <c r="BB249">
+        <v>8</v>
+      </c>
+      <c r="BC249">
+        <v>16</v>
+      </c>
+      <c r="BD249">
+        <v>1.97</v>
+      </c>
+      <c r="BE249">
+        <v>6.55</v>
+      </c>
+      <c r="BF249">
+        <v>2.31</v>
+      </c>
+      <c r="BG249">
+        <v>1.21</v>
+      </c>
+      <c r="BH249">
+        <v>3.58</v>
+      </c>
+      <c r="BI249">
+        <v>1.42</v>
+      </c>
+      <c r="BJ249">
+        <v>2.57</v>
+      </c>
+      <c r="BK249">
+        <v>1.77</v>
+      </c>
+      <c r="BL249">
+        <v>1.95</v>
+      </c>
+      <c r="BM249">
+        <v>2.21</v>
+      </c>
+      <c r="BN249">
+        <v>1.56</v>
+      </c>
+      <c r="BO249">
+        <v>2.92</v>
+      </c>
+      <c r="BP249">
+        <v>1.31</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -52480,22 +52480,22 @@
         <v>3.14</v>
       </c>
       <c r="AU248">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV248">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AW248">
         <v>6</v>
       </c>
       <c r="AX248">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AY248">
         <v>16</v>
       </c>
       <c r="AZ248">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BA248">
         <v>4</v>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1556" uniqueCount="360">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="367">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -787,6 +787,15 @@
     <t>['38', '50', '88', '90+1']</t>
   </si>
   <si>
+    <t>['10', '14', '21', '42', '56']</t>
+  </si>
+  <si>
+    <t>['10', '90+5']</t>
+  </si>
+  <si>
+    <t>['62', '75']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1094,6 +1103,18 @@
   </si>
   <si>
     <t>['54', '80']</t>
+  </si>
+  <si>
+    <t>['59', '90']</t>
+  </si>
+  <si>
+    <t>['86']</t>
+  </si>
+  <si>
+    <t>['53', '58']</t>
+  </si>
+  <si>
+    <t>['31', '33', '39']</t>
   </si>
 </sst>
 </file>
@@ -1455,7 +1476,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP249"/>
+  <dimension ref="A1:BP253"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1711,7 +1732,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -1998,7 +2019,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ3">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR3">
         <v>0</v>
@@ -2204,7 +2225,7 @@
         <v>1</v>
       </c>
       <c r="AQ4">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR4">
         <v>0</v>
@@ -2741,7 +2762,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3231,7 +3252,7 @@
         <v>0</v>
       </c>
       <c r="AP9">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ9">
         <v>0.75</v>
@@ -3565,7 +3586,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3643,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="AP11">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ11">
         <v>0.9399999999999999</v>
@@ -3977,7 +3998,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4183,7 +4204,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4389,7 +4410,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4467,7 +4488,7 @@
         <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ15">
         <v>0.6</v>
@@ -4801,7 +4822,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -4879,10 +4900,10 @@
         <v>0</v>
       </c>
       <c r="AP17">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ17">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR17">
         <v>0</v>
@@ -5419,7 +5440,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5497,10 +5518,10 @@
         <v>1</v>
       </c>
       <c r="AP20">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ20">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR20">
         <v>1.27</v>
@@ -5706,7 +5727,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ21">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR21">
         <v>1.37</v>
@@ -5831,7 +5852,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -6037,7 +6058,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6449,7 +6470,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6527,7 +6548,7 @@
         <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ25">
         <v>0.13</v>
@@ -6861,7 +6882,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -7067,7 +7088,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7148,7 +7169,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ28">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR28">
         <v>0.79</v>
@@ -7273,7 +7294,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -7351,7 +7372,7 @@
         <v>3</v>
       </c>
       <c r="AP29">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ29">
         <v>1.5</v>
@@ -8175,7 +8196,7 @@
         <v>3</v>
       </c>
       <c r="AP33">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ33">
         <v>0.9399999999999999</v>
@@ -8303,7 +8324,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8381,10 +8402,10 @@
         <v>1</v>
       </c>
       <c r="AP34">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ34">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR34">
         <v>1.74</v>
@@ -8715,7 +8736,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9002,7 +9023,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ37">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR37">
         <v>1.03</v>
@@ -9745,7 +9766,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9823,7 +9844,7 @@
         <v>1.5</v>
       </c>
       <c r="AP41">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ41">
         <v>1</v>
@@ -9951,7 +9972,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10032,7 +10053,7 @@
         <v>1</v>
       </c>
       <c r="AQ42">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR42">
         <v>0.95</v>
@@ -10647,7 +10668,7 @@
         <v>1.5</v>
       </c>
       <c r="AP45">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ45">
         <v>1.19</v>
@@ -11187,7 +11208,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11393,7 +11414,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11471,7 +11492,7 @@
         <v>1.5</v>
       </c>
       <c r="AP49">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ49">
         <v>1.8</v>
@@ -11599,7 +11620,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11805,7 +11826,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12092,7 +12113,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ52">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR52">
         <v>2.07</v>
@@ -12298,7 +12319,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ53">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR53">
         <v>0.82</v>
@@ -12707,7 +12728,7 @@
         <v>1.67</v>
       </c>
       <c r="AP55">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ55">
         <v>1</v>
@@ -12835,7 +12856,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13122,7 +13143,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ57">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR57">
         <v>1.08</v>
@@ -13247,7 +13268,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13453,7 +13474,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13531,7 +13552,7 @@
         <v>1.33</v>
       </c>
       <c r="AP59">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ59">
         <v>1.19</v>
@@ -13865,7 +13886,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14149,7 +14170,7 @@
         <v>0.33</v>
       </c>
       <c r="AP62">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ62">
         <v>0.75</v>
@@ -14358,7 +14379,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ63">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR63">
         <v>1.69</v>
@@ -14689,7 +14710,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14767,7 +14788,7 @@
         <v>2</v>
       </c>
       <c r="AP65">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ65">
         <v>1.25</v>
@@ -15307,7 +15328,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15513,7 +15534,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16209,10 +16230,10 @@
         <v>0.75</v>
       </c>
       <c r="AP72">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ72">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR72">
         <v>1.82</v>
@@ -16415,7 +16436,7 @@
         <v>1</v>
       </c>
       <c r="AP73">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ73">
         <v>0.75</v>
@@ -16543,7 +16564,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -16621,7 +16642,7 @@
         <v>0</v>
       </c>
       <c r="AP74">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ74">
         <v>0.13</v>
@@ -16827,10 +16848,10 @@
         <v>0.6</v>
       </c>
       <c r="AP75">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ75">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR75">
         <v>1.41</v>
@@ -17860,7 +17881,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ80">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR80">
         <v>2.17</v>
@@ -18397,7 +18418,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18475,7 +18496,7 @@
         <v>1.4</v>
       </c>
       <c r="AP83">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ83">
         <v>1.73</v>
@@ -18681,10 +18702,10 @@
         <v>1.75</v>
       </c>
       <c r="AP84">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ84">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR84">
         <v>1.61</v>
@@ -19015,7 +19036,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19711,7 +19732,7 @@
         <v>0.8</v>
       </c>
       <c r="AP89">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ89">
         <v>0.6</v>
@@ -20045,7 +20066,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20126,7 +20147,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ91">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR91">
         <v>1.77</v>
@@ -20251,7 +20272,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20663,7 +20684,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -21075,7 +21096,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21153,7 +21174,7 @@
         <v>1.8</v>
       </c>
       <c r="AP96">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ96">
         <v>1.8</v>
@@ -21281,7 +21302,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21565,10 +21586,10 @@
         <v>1.6</v>
       </c>
       <c r="AP98">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ98">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR98">
         <v>1.83</v>
@@ -21693,7 +21714,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21899,7 +21920,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -22105,7 +22126,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22183,10 +22204,10 @@
         <v>0.67</v>
       </c>
       <c r="AP101">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ101">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR101">
         <v>1.52</v>
@@ -22595,7 +22616,7 @@
         <v>0.67</v>
       </c>
       <c r="AP103">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ103">
         <v>1</v>
@@ -23135,7 +23156,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23341,7 +23362,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23547,7 +23568,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23628,7 +23649,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ108">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR108">
         <v>1.16</v>
@@ -23959,7 +23980,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24037,7 +24058,7 @@
         <v>1.33</v>
       </c>
       <c r="AP110">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ110">
         <v>1.5</v>
@@ -24243,7 +24264,7 @@
         <v>0.67</v>
       </c>
       <c r="AP111">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ111">
         <v>0.93</v>
@@ -24577,7 +24598,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24864,7 +24885,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ114">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR114">
         <v>1.76</v>
@@ -25685,7 +25706,7 @@
         <v>0.14</v>
       </c>
       <c r="AP118">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ118">
         <v>0.13</v>
@@ -25813,7 +25834,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -25894,7 +25915,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ119">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR119">
         <v>1.33</v>
@@ -26303,7 +26324,7 @@
         <v>0.57</v>
       </c>
       <c r="AP121">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ121">
         <v>0.6</v>
@@ -26431,7 +26452,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26718,7 +26739,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ123">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR123">
         <v>2.07</v>
@@ -27049,7 +27070,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27461,7 +27482,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27873,7 +27894,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -27951,7 +27972,7 @@
         <v>1.13</v>
       </c>
       <c r="AP129">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ129">
         <v>1.25</v>
@@ -28079,7 +28100,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28366,7 +28387,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ131">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR131">
         <v>1.18</v>
@@ -28491,7 +28512,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28569,7 +28590,7 @@
         <v>1.75</v>
       </c>
       <c r="AP132">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ132">
         <v>1.73</v>
@@ -28775,7 +28796,7 @@
         <v>0.63</v>
       </c>
       <c r="AP133">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ133">
         <v>0.75</v>
@@ -28903,7 +28924,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29187,10 +29208,10 @@
         <v>0.75</v>
       </c>
       <c r="AP135">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ135">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR135">
         <v>1.6</v>
@@ -29315,7 +29336,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29805,7 +29826,7 @@
         <v>1.38</v>
       </c>
       <c r="AP138">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ138">
         <v>1.19</v>
@@ -30345,7 +30366,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30426,7 +30447,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ141">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR141">
         <v>1.44</v>
@@ -30757,7 +30778,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30963,7 +30984,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31247,7 +31268,7 @@
         <v>0.5</v>
       </c>
       <c r="AP145">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ145">
         <v>0.75</v>
@@ -31375,7 +31396,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31453,7 +31474,7 @@
         <v>1</v>
       </c>
       <c r="AP146">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ146">
         <v>1</v>
@@ -31787,7 +31808,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -31993,7 +32014,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32611,7 +32632,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32895,10 +32916,10 @@
         <v>0.89</v>
       </c>
       <c r="AP153">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ153">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR153">
         <v>1.62</v>
@@ -33023,7 +33044,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33229,7 +33250,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33435,7 +33456,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33719,7 +33740,7 @@
         <v>0.67</v>
       </c>
       <c r="AP157">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ157">
         <v>0.93</v>
@@ -33847,7 +33868,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -33925,10 +33946,10 @@
         <v>0.78</v>
       </c>
       <c r="AP158">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ158">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR158">
         <v>1.6</v>
@@ -34259,7 +34280,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34465,7 +34486,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34546,7 +34567,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ161">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR161">
         <v>1.75</v>
@@ -34877,7 +34898,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -34955,7 +34976,7 @@
         <v>0.5</v>
       </c>
       <c r="AP163">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ163">
         <v>0.75</v>
@@ -35164,7 +35185,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ164">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR164">
         <v>1.79</v>
@@ -35289,7 +35310,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35370,7 +35391,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ165">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR165">
         <v>1.75</v>
@@ -35495,7 +35516,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35907,7 +35928,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36191,7 +36212,7 @@
         <v>1</v>
       </c>
       <c r="AP169">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ169">
         <v>1</v>
@@ -36397,7 +36418,7 @@
         <v>0.91</v>
       </c>
       <c r="AP170">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ170">
         <v>1</v>
@@ -36525,7 +36546,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36731,7 +36752,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36809,7 +36830,7 @@
         <v>1.4</v>
       </c>
       <c r="AP172">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ172">
         <v>1.8</v>
@@ -36937,7 +36958,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -37143,7 +37164,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37430,7 +37451,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ175">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR175">
         <v>1.74</v>
@@ -37555,7 +37576,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37761,7 +37782,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38173,7 +38194,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38251,7 +38272,7 @@
         <v>1.55</v>
       </c>
       <c r="AP179">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ179">
         <v>1.8</v>
@@ -38379,7 +38400,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38872,7 +38893,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ182">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR182">
         <v>1.21</v>
@@ -38997,7 +39018,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39078,7 +39099,7 @@
         <v>1</v>
       </c>
       <c r="AQ183">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR183">
         <v>1.3</v>
@@ -39203,7 +39224,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39902,7 +39923,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ187">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR187">
         <v>1.65</v>
@@ -40027,7 +40048,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40105,7 +40126,7 @@
         <v>0.91</v>
       </c>
       <c r="AP188">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ188">
         <v>0.93</v>
@@ -40645,7 +40666,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -40929,7 +40950,7 @@
         <v>1.64</v>
       </c>
       <c r="AP192">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ192">
         <v>1.5</v>
@@ -41057,7 +41078,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41263,7 +41284,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -41341,7 +41362,7 @@
         <v>1.25</v>
       </c>
       <c r="AP194">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ194">
         <v>1.25</v>
@@ -41550,7 +41571,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ195">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR195">
         <v>2.09</v>
@@ -42293,7 +42314,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42374,7 +42395,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ199">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR199">
         <v>1.34</v>
@@ -42499,7 +42520,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42577,7 +42598,7 @@
         <v>0.92</v>
       </c>
       <c r="AP200">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ200">
         <v>0.93</v>
@@ -42911,7 +42932,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -43117,7 +43138,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43198,7 +43219,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ203">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR203">
         <v>1.28</v>
@@ -43323,7 +43344,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43529,7 +43550,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43735,7 +43756,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -43813,7 +43834,7 @@
         <v>0.08</v>
       </c>
       <c r="AP206">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ206">
         <v>0.13</v>
@@ -44431,7 +44452,7 @@
         <v>0.83</v>
       </c>
       <c r="AP209">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ209">
         <v>0.9399999999999999</v>
@@ -44637,7 +44658,7 @@
         <v>0.62</v>
       </c>
       <c r="AP210">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ210">
         <v>0.75</v>
@@ -44971,7 +44992,7 @@
         <v>227</v>
       </c>
       <c r="P212" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="Q212">
         <v>2.75</v>
@@ -45049,7 +45070,7 @@
         <v>0.92</v>
       </c>
       <c r="AP212">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ212">
         <v>1</v>
@@ -45177,7 +45198,7 @@
         <v>239</v>
       </c>
       <c r="P213" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -45258,7 +45279,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ213">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR213">
         <v>1.7</v>
@@ -45383,7 +45404,7 @@
         <v>86</v>
       </c>
       <c r="P214" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="Q214">
         <v>1.71</v>
@@ -45795,7 +45816,7 @@
         <v>87</v>
       </c>
       <c r="P216" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="Q216">
         <v>3.25</v>
@@ -45876,7 +45897,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ216">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR216">
         <v>1.66</v>
@@ -46413,7 +46434,7 @@
         <v>88</v>
       </c>
       <c r="P219" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46491,7 +46512,7 @@
         <v>1.69</v>
       </c>
       <c r="AP219">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ219">
         <v>1.73</v>
@@ -46697,7 +46718,7 @@
         <v>1.31</v>
       </c>
       <c r="AP220">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ220">
         <v>1.19</v>
@@ -46825,7 +46846,7 @@
         <v>241</v>
       </c>
       <c r="P221" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="Q221">
         <v>2.25</v>
@@ -47112,7 +47133,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ222">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR222">
         <v>1.82</v>
@@ -47443,7 +47464,7 @@
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="Q224">
         <v>4.33</v>
@@ -48142,7 +48163,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ227">
-        <v>0.6</v>
+        <v>0.63</v>
       </c>
       <c r="AR227">
         <v>1.36</v>
@@ -48679,7 +48700,7 @@
         <v>174</v>
       </c>
       <c r="P230" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="Q230">
         <v>4.75</v>
@@ -48757,7 +48778,7 @@
         <v>1.64</v>
       </c>
       <c r="AP230">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ230">
         <v>1.73</v>
@@ -48963,7 +48984,7 @@
         <v>1.71</v>
       </c>
       <c r="AP231">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="AQ231">
         <v>1.5</v>
@@ -49091,7 +49112,7 @@
         <v>87</v>
       </c>
       <c r="P232" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49584,7 +49605,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ234">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AR234">
         <v>1.77</v>
@@ -50121,7 +50142,7 @@
         <v>249</v>
       </c>
       <c r="P237" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50199,10 +50220,10 @@
         <v>1.07</v>
       </c>
       <c r="AP237">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AQ237">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AR237">
         <v>1.5</v>
@@ -50327,7 +50348,7 @@
         <v>250</v>
       </c>
       <c r="P238" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="Q238">
         <v>3.1</v>
@@ -50533,7 +50554,7 @@
         <v>118</v>
       </c>
       <c r="P239" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Q239">
         <v>3.75</v>
@@ -50739,7 +50760,7 @@
         <v>251</v>
       </c>
       <c r="P240" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -50945,7 +50966,7 @@
         <v>105</v>
       </c>
       <c r="P241" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="Q241">
         <v>2.3</v>
@@ -51023,7 +51044,7 @@
         <v>0.43</v>
       </c>
       <c r="AP241">
-        <v>1.67</v>
+        <v>1.56</v>
       </c>
       <c r="AQ241">
         <v>0.6</v>
@@ -51357,7 +51378,7 @@
         <v>87</v>
       </c>
       <c r="P243" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="Q243">
         <v>3.75</v>
@@ -51563,7 +51584,7 @@
         <v>252</v>
       </c>
       <c r="P244" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52181,7 +52202,7 @@
         <v>255</v>
       </c>
       <c r="P247" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="Q247">
         <v>3.4</v>
@@ -52750,6 +52771,830 @@
       </c>
       <c r="BP249">
         <v>1.31</v>
+      </c>
+    </row>
+    <row r="250" spans="1:68">
+      <c r="A250" s="1">
+        <v>249</v>
+      </c>
+      <c r="B250">
+        <v>7858315</v>
+      </c>
+      <c r="C250" t="s">
+        <v>68</v>
+      </c>
+      <c r="D250" t="s">
+        <v>69</v>
+      </c>
+      <c r="E250" s="2">
+        <v>45751.65625</v>
+      </c>
+      <c r="F250">
+        <v>2</v>
+      </c>
+      <c r="G250" t="s">
+        <v>79</v>
+      </c>
+      <c r="H250" t="s">
+        <v>71</v>
+      </c>
+      <c r="I250">
+        <v>4</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>4</v>
+      </c>
+      <c r="L250">
+        <v>5</v>
+      </c>
+      <c r="M250">
+        <v>2</v>
+      </c>
+      <c r="N250">
+        <v>7</v>
+      </c>
+      <c r="O250" t="s">
+        <v>257</v>
+      </c>
+      <c r="P250" t="s">
+        <v>363</v>
+      </c>
+      <c r="Q250">
+        <v>2.5</v>
+      </c>
+      <c r="R250">
+        <v>2.25</v>
+      </c>
+      <c r="S250">
+        <v>4.33</v>
+      </c>
+      <c r="T250">
+        <v>1.36</v>
+      </c>
+      <c r="U250">
+        <v>3</v>
+      </c>
+      <c r="V250">
+        <v>2.63</v>
+      </c>
+      <c r="W250">
+        <v>1.44</v>
+      </c>
+      <c r="X250">
+        <v>7</v>
+      </c>
+      <c r="Y250">
+        <v>1.1</v>
+      </c>
+      <c r="Z250">
+        <v>1.67</v>
+      </c>
+      <c r="AA250">
+        <v>3.91</v>
+      </c>
+      <c r="AB250">
+        <v>4.6</v>
+      </c>
+      <c r="AC250">
+        <v>1.05</v>
+      </c>
+      <c r="AD250">
+        <v>9.5</v>
+      </c>
+      <c r="AE250">
+        <v>1.25</v>
+      </c>
+      <c r="AF250">
+        <v>3.7</v>
+      </c>
+      <c r="AG250">
+        <v>1.77</v>
+      </c>
+      <c r="AH250">
+        <v>1.98</v>
+      </c>
+      <c r="AI250">
+        <v>1.7</v>
+      </c>
+      <c r="AJ250">
+        <v>2.05</v>
+      </c>
+      <c r="AK250">
+        <v>1.24</v>
+      </c>
+      <c r="AL250">
+        <v>1.27</v>
+      </c>
+      <c r="AM250">
+        <v>1.88</v>
+      </c>
+      <c r="AN250">
+        <v>1.53</v>
+      </c>
+      <c r="AO250">
+        <v>1</v>
+      </c>
+      <c r="AP250">
+        <v>1.63</v>
+      </c>
+      <c r="AQ250">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="AR250">
+        <v>1.54</v>
+      </c>
+      <c r="AS250">
+        <v>1.25</v>
+      </c>
+      <c r="AT250">
+        <v>2.79</v>
+      </c>
+      <c r="AU250">
+        <v>11</v>
+      </c>
+      <c r="AV250">
+        <v>6</v>
+      </c>
+      <c r="AW250">
+        <v>10</v>
+      </c>
+      <c r="AX250">
+        <v>5</v>
+      </c>
+      <c r="AY250">
+        <v>23</v>
+      </c>
+      <c r="AZ250">
+        <v>12</v>
+      </c>
+      <c r="BA250">
+        <v>4</v>
+      </c>
+      <c r="BB250">
+        <v>1</v>
+      </c>
+      <c r="BC250">
+        <v>5</v>
+      </c>
+      <c r="BD250">
+        <v>1.63</v>
+      </c>
+      <c r="BE250">
+        <v>6.75</v>
+      </c>
+      <c r="BF250">
+        <v>2.55</v>
+      </c>
+      <c r="BG250">
+        <v>1.3</v>
+      </c>
+      <c r="BH250">
+        <v>3.15</v>
+      </c>
+      <c r="BI250">
+        <v>1.52</v>
+      </c>
+      <c r="BJ250">
+        <v>2.33</v>
+      </c>
+      <c r="BK250">
+        <v>1.84</v>
+      </c>
+      <c r="BL250">
+        <v>1.84</v>
+      </c>
+      <c r="BM250">
+        <v>2.3</v>
+      </c>
+      <c r="BN250">
+        <v>1.53</v>
+      </c>
+      <c r="BO250">
+        <v>2.95</v>
+      </c>
+      <c r="BP250">
+        <v>1.33</v>
+      </c>
+    </row>
+    <row r="251" spans="1:68">
+      <c r="A251" s="1">
+        <v>250</v>
+      </c>
+      <c r="B251">
+        <v>7858316</v>
+      </c>
+      <c r="C251" t="s">
+        <v>68</v>
+      </c>
+      <c r="D251" t="s">
+        <v>69</v>
+      </c>
+      <c r="E251" s="2">
+        <v>45752.45833333334</v>
+      </c>
+      <c r="F251">
+        <v>2</v>
+      </c>
+      <c r="G251" t="s">
+        <v>83</v>
+      </c>
+      <c r="H251" t="s">
+        <v>72</v>
+      </c>
+      <c r="I251">
+        <v>1</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>1</v>
+      </c>
+      <c r="L251">
+        <v>2</v>
+      </c>
+      <c r="M251">
+        <v>1</v>
+      </c>
+      <c r="N251">
+        <v>3</v>
+      </c>
+      <c r="O251" t="s">
+        <v>258</v>
+      </c>
+      <c r="P251" t="s">
+        <v>364</v>
+      </c>
+      <c r="Q251">
+        <v>2.05</v>
+      </c>
+      <c r="R251">
+        <v>2.3</v>
+      </c>
+      <c r="S251">
+        <v>6.5</v>
+      </c>
+      <c r="T251">
+        <v>1.36</v>
+      </c>
+      <c r="U251">
+        <v>3</v>
+      </c>
+      <c r="V251">
+        <v>2.75</v>
+      </c>
+      <c r="W251">
+        <v>1.4</v>
+      </c>
+      <c r="X251">
+        <v>8</v>
+      </c>
+      <c r="Y251">
+        <v>1.08</v>
+      </c>
+      <c r="Z251">
+        <v>1.55</v>
+      </c>
+      <c r="AA251">
+        <v>4</v>
+      </c>
+      <c r="AB251">
+        <v>5.7</v>
+      </c>
+      <c r="AC251">
+        <v>1.05</v>
+      </c>
+      <c r="AD251">
+        <v>9.5</v>
+      </c>
+      <c r="AE251">
+        <v>1.28</v>
+      </c>
+      <c r="AF251">
+        <v>3.55</v>
+      </c>
+      <c r="AG251">
+        <v>1.89</v>
+      </c>
+      <c r="AH251">
+        <v>1.85</v>
+      </c>
+      <c r="AI251">
+        <v>2</v>
+      </c>
+      <c r="AJ251">
+        <v>1.75</v>
+      </c>
+      <c r="AK251">
+        <v>1.11</v>
+      </c>
+      <c r="AL251">
+        <v>1.21</v>
+      </c>
+      <c r="AM251">
+        <v>2.55</v>
+      </c>
+      <c r="AN251">
+        <v>1.4</v>
+      </c>
+      <c r="AO251">
+        <v>0.13</v>
+      </c>
+      <c r="AP251">
+        <v>1.5</v>
+      </c>
+      <c r="AQ251">
+        <v>0.13</v>
+      </c>
+      <c r="AR251">
+        <v>1.81</v>
+      </c>
+      <c r="AS251">
+        <v>1.17</v>
+      </c>
+      <c r="AT251">
+        <v>2.98</v>
+      </c>
+      <c r="AU251">
+        <v>10</v>
+      </c>
+      <c r="AV251">
+        <v>4</v>
+      </c>
+      <c r="AW251">
+        <v>12</v>
+      </c>
+      <c r="AX251">
+        <v>7</v>
+      </c>
+      <c r="AY251">
+        <v>25</v>
+      </c>
+      <c r="AZ251">
+        <v>11</v>
+      </c>
+      <c r="BA251">
+        <v>8</v>
+      </c>
+      <c r="BB251">
+        <v>6</v>
+      </c>
+      <c r="BC251">
+        <v>14</v>
+      </c>
+      <c r="BD251">
+        <v>1.23</v>
+      </c>
+      <c r="BE251">
+        <v>8.25</v>
+      </c>
+      <c r="BF251">
+        <v>5.5</v>
+      </c>
+      <c r="BG251">
+        <v>1.16</v>
+      </c>
+      <c r="BH251">
+        <v>4.1</v>
+      </c>
+      <c r="BI251">
+        <v>1.36</v>
+      </c>
+      <c r="BJ251">
+        <v>2.9</v>
+      </c>
+      <c r="BK251">
+        <v>1.63</v>
+      </c>
+      <c r="BL251">
+        <v>2.1</v>
+      </c>
+      <c r="BM251">
+        <v>2.1</v>
+      </c>
+      <c r="BN251">
+        <v>1.65</v>
+      </c>
+      <c r="BO251">
+        <v>2.8</v>
+      </c>
+      <c r="BP251">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="252" spans="1:68">
+      <c r="A252" s="1">
+        <v>251</v>
+      </c>
+      <c r="B252">
+        <v>7858317</v>
+      </c>
+      <c r="C252" t="s">
+        <v>68</v>
+      </c>
+      <c r="D252" t="s">
+        <v>69</v>
+      </c>
+      <c r="E252" s="2">
+        <v>45752.55208333334</v>
+      </c>
+      <c r="F252">
+        <v>2</v>
+      </c>
+      <c r="G252" t="s">
+        <v>77</v>
+      </c>
+      <c r="H252" t="s">
+        <v>80</v>
+      </c>
+      <c r="I252">
+        <v>0</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+      <c r="L252">
+        <v>2</v>
+      </c>
+      <c r="M252">
+        <v>2</v>
+      </c>
+      <c r="N252">
+        <v>4</v>
+      </c>
+      <c r="O252" t="s">
+        <v>259</v>
+      </c>
+      <c r="P252" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q252">
+        <v>2.63</v>
+      </c>
+      <c r="R252">
+        <v>2.2</v>
+      </c>
+      <c r="S252">
+        <v>4</v>
+      </c>
+      <c r="T252">
+        <v>1.36</v>
+      </c>
+      <c r="U252">
+        <v>3</v>
+      </c>
+      <c r="V252">
+        <v>2.75</v>
+      </c>
+      <c r="W252">
+        <v>1.4</v>
+      </c>
+      <c r="X252">
+        <v>7</v>
+      </c>
+      <c r="Y252">
+        <v>1.1</v>
+      </c>
+      <c r="Z252">
+        <v>1.97</v>
+      </c>
+      <c r="AA252">
+        <v>3.58</v>
+      </c>
+      <c r="AB252">
+        <v>3.55</v>
+      </c>
+      <c r="AC252">
+        <v>1.05</v>
+      </c>
+      <c r="AD252">
+        <v>9.5</v>
+      </c>
+      <c r="AE252">
+        <v>1.25</v>
+      </c>
+      <c r="AF252">
+        <v>3.7</v>
+      </c>
+      <c r="AG252">
+        <v>1.79</v>
+      </c>
+      <c r="AH252">
+        <v>1.95</v>
+      </c>
+      <c r="AI252">
+        <v>1.67</v>
+      </c>
+      <c r="AJ252">
+        <v>2.1</v>
+      </c>
+      <c r="AK252">
+        <v>1.3</v>
+      </c>
+      <c r="AL252">
+        <v>1.28</v>
+      </c>
+      <c r="AM252">
+        <v>1.75</v>
+      </c>
+      <c r="AN252">
+        <v>1.47</v>
+      </c>
+      <c r="AO252">
+        <v>0.6</v>
+      </c>
+      <c r="AP252">
+        <v>1.44</v>
+      </c>
+      <c r="AQ252">
+        <v>0.63</v>
+      </c>
+      <c r="AR252">
+        <v>1.83</v>
+      </c>
+      <c r="AS252">
+        <v>1.19</v>
+      </c>
+      <c r="AT252">
+        <v>3.02</v>
+      </c>
+      <c r="AU252">
+        <v>5</v>
+      </c>
+      <c r="AV252">
+        <v>6</v>
+      </c>
+      <c r="AW252">
+        <v>10</v>
+      </c>
+      <c r="AX252">
+        <v>13</v>
+      </c>
+      <c r="AY252">
+        <v>22</v>
+      </c>
+      <c r="AZ252">
+        <v>23</v>
+      </c>
+      <c r="BA252">
+        <v>6</v>
+      </c>
+      <c r="BB252">
+        <v>10</v>
+      </c>
+      <c r="BC252">
+        <v>16</v>
+      </c>
+      <c r="BD252">
+        <v>1.4</v>
+      </c>
+      <c r="BE252">
+        <v>7.25</v>
+      </c>
+      <c r="BF252">
+        <v>3.6</v>
+      </c>
+      <c r="BG252">
+        <v>1.21</v>
+      </c>
+      <c r="BH252">
+        <v>4</v>
+      </c>
+      <c r="BI252">
+        <v>1.39</v>
+      </c>
+      <c r="BJ252">
+        <v>2.75</v>
+      </c>
+      <c r="BK252">
+        <v>1.71</v>
+      </c>
+      <c r="BL252">
+        <v>2</v>
+      </c>
+      <c r="BM252">
+        <v>2.2</v>
+      </c>
+      <c r="BN252">
+        <v>1.58</v>
+      </c>
+      <c r="BO252">
+        <v>3</v>
+      </c>
+      <c r="BP252">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="253" spans="1:68">
+      <c r="A253" s="1">
+        <v>252</v>
+      </c>
+      <c r="B253">
+        <v>7858318</v>
+      </c>
+      <c r="C253" t="s">
+        <v>68</v>
+      </c>
+      <c r="D253" t="s">
+        <v>69</v>
+      </c>
+      <c r="E253" s="2">
+        <v>45752.65625</v>
+      </c>
+      <c r="F253">
+        <v>2</v>
+      </c>
+      <c r="G253" t="s">
+        <v>85</v>
+      </c>
+      <c r="H253" t="s">
+        <v>78</v>
+      </c>
+      <c r="I253">
+        <v>0</v>
+      </c>
+      <c r="J253">
+        <v>3</v>
+      </c>
+      <c r="K253">
+        <v>3</v>
+      </c>
+      <c r="L253">
+        <v>0</v>
+      </c>
+      <c r="M253">
+        <v>3</v>
+      </c>
+      <c r="N253">
+        <v>3</v>
+      </c>
+      <c r="O253" t="s">
+        <v>87</v>
+      </c>
+      <c r="P253" t="s">
+        <v>366</v>
+      </c>
+      <c r="Q253">
+        <v>4.33</v>
+      </c>
+      <c r="R253">
+        <v>2.3</v>
+      </c>
+      <c r="S253">
+        <v>2.4</v>
+      </c>
+      <c r="T253">
+        <v>1.33</v>
+      </c>
+      <c r="U253">
+        <v>3.25</v>
+      </c>
+      <c r="V253">
+        <v>2.63</v>
+      </c>
+      <c r="W253">
+        <v>1.44</v>
+      </c>
+      <c r="X253">
+        <v>6.5</v>
+      </c>
+      <c r="Y253">
+        <v>1.11</v>
+      </c>
+      <c r="Z253">
+        <v>3.98</v>
+      </c>
+      <c r="AA253">
+        <v>3.64</v>
+      </c>
+      <c r="AB253">
+        <v>1.84</v>
+      </c>
+      <c r="AC253">
+        <v>1.04</v>
+      </c>
+      <c r="AD253">
+        <v>10</v>
+      </c>
+      <c r="AE253">
+        <v>1.22</v>
+      </c>
+      <c r="AF253">
+        <v>4.2</v>
+      </c>
+      <c r="AG253">
+        <v>1.75</v>
+      </c>
+      <c r="AH253">
+        <v>1.95</v>
+      </c>
+      <c r="AI253">
+        <v>1.67</v>
+      </c>
+      <c r="AJ253">
+        <v>2.1</v>
+      </c>
+      <c r="AK253">
+        <v>1.98</v>
+      </c>
+      <c r="AL253">
+        <v>1.25</v>
+      </c>
+      <c r="AM253">
+        <v>1.23</v>
+      </c>
+      <c r="AN253">
+        <v>1.67</v>
+      </c>
+      <c r="AO253">
+        <v>1.47</v>
+      </c>
+      <c r="AP253">
+        <v>1.56</v>
+      </c>
+      <c r="AQ253">
+        <v>1.56</v>
+      </c>
+      <c r="AR253">
+        <v>1.54</v>
+      </c>
+      <c r="AS253">
+        <v>1.41</v>
+      </c>
+      <c r="AT253">
+        <v>2.95</v>
+      </c>
+      <c r="AU253">
+        <v>4</v>
+      </c>
+      <c r="AV253">
+        <v>7</v>
+      </c>
+      <c r="AW253">
+        <v>4</v>
+      </c>
+      <c r="AX253">
+        <v>10</v>
+      </c>
+      <c r="AY253">
+        <v>9</v>
+      </c>
+      <c r="AZ253">
+        <v>20</v>
+      </c>
+      <c r="BA253">
+        <v>4</v>
+      </c>
+      <c r="BB253">
+        <v>5</v>
+      </c>
+      <c r="BC253">
+        <v>9</v>
+      </c>
+      <c r="BD253">
+        <v>2.65</v>
+      </c>
+      <c r="BE253">
+        <v>6.5</v>
+      </c>
+      <c r="BF253">
+        <v>1.66</v>
+      </c>
+      <c r="BG253">
+        <v>1.22</v>
+      </c>
+      <c r="BH253">
+        <v>3.8</v>
+      </c>
+      <c r="BI253">
+        <v>1.42</v>
+      </c>
+      <c r="BJ253">
+        <v>2.65</v>
+      </c>
+      <c r="BK253">
+        <v>1.75</v>
+      </c>
+      <c r="BL253">
+        <v>1.95</v>
+      </c>
+      <c r="BM253">
+        <v>2.25</v>
+      </c>
+      <c r="BN253">
+        <v>1.55</v>
+      </c>
+      <c r="BO253">
+        <v>3.1</v>
+      </c>
+      <c r="BP253">
+        <v>1.32</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1580" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="370">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -796,6 +796,9 @@
     <t>['62', '75']</t>
   </si>
   <si>
+    <t>['63', '71']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1115,6 +1118,12 @@
   </si>
   <si>
     <t>['31', '33', '39']</t>
+  </si>
+  <si>
+    <t>['9', '29', '45+3']</t>
+  </si>
+  <si>
+    <t>['17', '22', '27']</t>
   </si>
 </sst>
 </file>
@@ -1476,7 +1485,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP253"/>
+  <dimension ref="A1:BP255"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1732,7 +1741,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2762,7 +2771,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3586,7 +3595,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3998,7 +4007,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4076,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="AP13">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ13">
         <v>1</v>
@@ -4204,7 +4213,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4282,7 +4291,7 @@
         <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ14">
         <v>1.5</v>
@@ -4410,7 +4419,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4491,7 +4500,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ15">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR15">
         <v>0</v>
@@ -4697,7 +4706,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ16">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR16">
         <v>0</v>
@@ -4822,7 +4831,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5315,7 +5324,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ19">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR19">
         <v>0.45</v>
@@ -5440,7 +5449,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5852,7 +5861,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -5933,7 +5942,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ22">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR22">
         <v>1.58</v>
@@ -6058,7 +6067,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6136,7 +6145,7 @@
         <v>0</v>
       </c>
       <c r="AP23">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ23">
         <v>0.75</v>
@@ -6470,7 +6479,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6882,7 +6891,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -7088,7 +7097,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7166,7 +7175,7 @@
         <v>3</v>
       </c>
       <c r="AP28">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ28">
         <v>0.9399999999999999</v>
@@ -7294,7 +7303,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -8324,7 +8333,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8608,7 +8617,7 @@
         <v>1</v>
       </c>
       <c r="AP35">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ35">
         <v>1</v>
@@ -8736,7 +8745,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -8817,7 +8826,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ36">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR36">
         <v>0.9399999999999999</v>
@@ -9020,7 +9029,7 @@
         <v>0.5</v>
       </c>
       <c r="AP37">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ37">
         <v>1.56</v>
@@ -9435,7 +9444,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ39">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR39">
         <v>1.72</v>
@@ -9766,7 +9775,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9972,7 +9981,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -11208,7 +11217,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11414,7 +11423,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11620,7 +11629,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11701,7 +11710,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ50">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR50">
         <v>1.76</v>
@@ -11826,7 +11835,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -12110,7 +12119,7 @@
         <v>0.67</v>
       </c>
       <c r="AP52">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ52">
         <v>1.56</v>
@@ -12316,7 +12325,7 @@
         <v>1</v>
       </c>
       <c r="AP53">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ53">
         <v>0.63</v>
@@ -12856,7 +12865,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -13268,7 +13277,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13474,7 +13483,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13886,7 +13895,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14585,7 +14594,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ64">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR64">
         <v>1.33</v>
@@ -14710,7 +14719,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -14997,7 +15006,7 @@
         <v>1.47</v>
       </c>
       <c r="AQ66">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR66">
         <v>1.81</v>
@@ -15328,7 +15337,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15534,7 +15543,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -15818,7 +15827,7 @@
         <v>0</v>
       </c>
       <c r="AP70">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ70">
         <v>0.13</v>
@@ -16027,7 +16036,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ71">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR71">
         <v>1.7</v>
@@ -16564,7 +16573,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -17672,7 +17681,7 @@
         <v>0.25</v>
       </c>
       <c r="AP79">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ79">
         <v>0.75</v>
@@ -18084,7 +18093,7 @@
         <v>1.5</v>
       </c>
       <c r="AP81">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ81">
         <v>1.25</v>
@@ -18418,7 +18427,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -18499,7 +18508,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ83">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR83">
         <v>1.89</v>
@@ -19036,7 +19045,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -19735,7 +19744,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ89">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR89">
         <v>1.48</v>
@@ -20066,7 +20075,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20272,7 +20281,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20556,7 +20565,7 @@
         <v>1.4</v>
       </c>
       <c r="AP93">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ93">
         <v>0.9399999999999999</v>
@@ -20684,7 +20693,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20968,7 +20977,7 @@
         <v>0.8</v>
       </c>
       <c r="AP95">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ95">
         <v>0.93</v>
@@ -21096,7 +21105,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21302,7 +21311,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21714,7 +21723,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21920,7 +21929,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -22001,7 +22010,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ100">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR100">
         <v>1.3</v>
@@ -22126,7 +22135,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22825,7 +22834,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ104">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR104">
         <v>1.57</v>
@@ -23156,7 +23165,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23234,7 +23243,7 @@
         <v>1.33</v>
       </c>
       <c r="AP106">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ106">
         <v>1</v>
@@ -23362,7 +23371,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23568,7 +23577,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23980,7 +23989,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24598,7 +24607,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -24679,7 +24688,7 @@
         <v>1</v>
       </c>
       <c r="AQ113">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR113">
         <v>0.88</v>
@@ -24882,7 +24891,7 @@
         <v>1.33</v>
       </c>
       <c r="AP114">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ114">
         <v>0.9399999999999999</v>
@@ -25834,7 +25843,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26327,7 +26336,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ121">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR121">
         <v>1.8</v>
@@ -26452,7 +26461,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -27070,7 +27079,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27148,7 +27157,7 @@
         <v>1.71</v>
       </c>
       <c r="AP125">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ125">
         <v>1.8</v>
@@ -27482,7 +27491,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27894,7 +27903,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -28100,7 +28109,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28181,7 +28190,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ130">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR130">
         <v>1.84</v>
@@ -28512,7 +28521,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28593,7 +28602,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ132">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR132">
         <v>1.55</v>
@@ -28924,7 +28933,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29002,7 +29011,7 @@
         <v>0.5</v>
       </c>
       <c r="AP134">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ134">
         <v>1</v>
@@ -29336,7 +29345,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -30366,7 +30375,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30778,7 +30787,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30984,7 +30993,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31062,7 +31071,7 @@
         <v>1.5</v>
       </c>
       <c r="AP144">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ144">
         <v>1.5</v>
@@ -31396,7 +31405,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31808,7 +31817,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -32014,7 +32023,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32095,7 +32104,7 @@
         <v>1</v>
       </c>
       <c r="AQ149">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR149">
         <v>1.18</v>
@@ -32632,7 +32641,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -32713,7 +32722,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ152">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR152">
         <v>1.81</v>
@@ -33044,7 +33053,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33122,7 +33131,7 @@
         <v>1.44</v>
       </c>
       <c r="AP154">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ154">
         <v>1.8</v>
@@ -33250,7 +33259,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33456,7 +33465,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33868,7 +33877,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34280,7 +34289,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34358,7 +34367,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP160">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ160">
         <v>0.75</v>
@@ -34486,7 +34495,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34773,7 +34782,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ162">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR162">
         <v>1.18</v>
@@ -34898,7 +34907,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35310,7 +35319,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35516,7 +35525,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35928,7 +35937,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36009,7 +36018,7 @@
         <v>1.8</v>
       </c>
       <c r="AQ168">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR168">
         <v>1.71</v>
@@ -36546,7 +36555,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36752,7 +36761,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36958,7 +36967,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -37164,7 +37173,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37576,7 +37585,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37654,7 +37663,7 @@
         <v>0.7</v>
       </c>
       <c r="AP176">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ176">
         <v>0.93</v>
@@ -37782,7 +37791,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -37860,7 +37869,7 @@
         <v>0.7</v>
       </c>
       <c r="AP177">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ177">
         <v>0.9399999999999999</v>
@@ -38066,7 +38075,7 @@
         <v>1.45</v>
       </c>
       <c r="AP178">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ178">
         <v>1.19</v>
@@ -38194,7 +38203,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38400,7 +38409,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38687,7 +38696,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ181">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR181">
         <v>2.05</v>
@@ -39018,7 +39027,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39224,7 +39233,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -40048,7 +40057,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40538,10 +40547,10 @@
         <v>1.91</v>
       </c>
       <c r="AP190">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ190">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR190">
         <v>1.72</v>
@@ -40666,7 +40675,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -41078,7 +41087,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41284,7 +41293,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -42314,7 +42323,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42520,7 +42529,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42932,7 +42941,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -43138,7 +43147,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43344,7 +43353,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43422,10 +43431,10 @@
         <v>0.5</v>
       </c>
       <c r="AP204">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ204">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR204">
         <v>1.66</v>
@@ -43550,7 +43559,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43628,10 +43637,10 @@
         <v>1.75</v>
       </c>
       <c r="AP205">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ205">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR205">
         <v>1.6</v>
@@ -43756,7 +43765,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -44992,7 +45001,7 @@
         <v>227</v>
       </c>
       <c r="P212" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q212">
         <v>2.75</v>
@@ -45198,7 +45207,7 @@
         <v>239</v>
       </c>
       <c r="P213" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -45276,7 +45285,7 @@
         <v>0.62</v>
       </c>
       <c r="AP213">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ213">
         <v>0.63</v>
@@ -45404,7 +45413,7 @@
         <v>86</v>
       </c>
       <c r="P214" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q214">
         <v>1.71</v>
@@ -45816,7 +45825,7 @@
         <v>87</v>
       </c>
       <c r="P216" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q216">
         <v>3.25</v>
@@ -46434,7 +46443,7 @@
         <v>88</v>
       </c>
       <c r="P219" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46515,7 +46524,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ219">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR219">
         <v>1.58</v>
@@ -46846,7 +46855,7 @@
         <v>241</v>
       </c>
       <c r="P221" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q221">
         <v>2.25</v>
@@ -46924,10 +46933,10 @@
         <v>0.46</v>
       </c>
       <c r="AP221">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ221">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR221">
         <v>1.54</v>
@@ -47464,7 +47473,7 @@
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q224">
         <v>4.33</v>
@@ -47954,7 +47963,7 @@
         <v>0.14</v>
       </c>
       <c r="AP226">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="AQ226">
         <v>0.13</v>
@@ -48700,7 +48709,7 @@
         <v>174</v>
       </c>
       <c r="P230" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q230">
         <v>4.75</v>
@@ -48781,7 +48790,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ230">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="AR230">
         <v>1.79</v>
@@ -49112,7 +49121,7 @@
         <v>87</v>
       </c>
       <c r="P232" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49190,7 +49199,7 @@
         <v>1.21</v>
       </c>
       <c r="AP232">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ232">
         <v>1.25</v>
@@ -50142,7 +50151,7 @@
         <v>249</v>
       </c>
       <c r="P237" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50348,7 +50357,7 @@
         <v>250</v>
       </c>
       <c r="P238" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q238">
         <v>3.1</v>
@@ -50554,7 +50563,7 @@
         <v>118</v>
       </c>
       <c r="P239" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q239">
         <v>3.75</v>
@@ -50760,7 +50769,7 @@
         <v>251</v>
       </c>
       <c r="P240" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -50966,7 +50975,7 @@
         <v>105</v>
       </c>
       <c r="P241" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q241">
         <v>2.3</v>
@@ -51047,7 +51056,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ241">
-        <v>0.6</v>
+        <v>0.75</v>
       </c>
       <c r="AR241">
         <v>1.58</v>
@@ -51378,7 +51387,7 @@
         <v>87</v>
       </c>
       <c r="P243" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q243">
         <v>3.75</v>
@@ -51584,7 +51593,7 @@
         <v>252</v>
       </c>
       <c r="P244" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52202,7 +52211,7 @@
         <v>255</v>
       </c>
       <c r="P247" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q247">
         <v>3.4</v>
@@ -52820,7 +52829,7 @@
         <v>257</v>
       </c>
       <c r="P250" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q250">
         <v>2.5</v>
@@ -53026,7 +53035,7 @@
         <v>258</v>
       </c>
       <c r="P251" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q251">
         <v>2.05</v>
@@ -53232,7 +53241,7 @@
         <v>259</v>
       </c>
       <c r="P252" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q252">
         <v>2.63</v>
@@ -53438,7 +53447,7 @@
         <v>87</v>
       </c>
       <c r="P253" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q253">
         <v>4.33</v>
@@ -53595,6 +53604,418 @@
       </c>
       <c r="BP253">
         <v>1.32</v>
+      </c>
+    </row>
+    <row r="254" spans="1:68">
+      <c r="A254" s="1">
+        <v>253</v>
+      </c>
+      <c r="B254">
+        <v>7858319</v>
+      </c>
+      <c r="C254" t="s">
+        <v>68</v>
+      </c>
+      <c r="D254" t="s">
+        <v>69</v>
+      </c>
+      <c r="E254" s="2">
+        <v>45753.35416666666</v>
+      </c>
+      <c r="F254">
+        <v>2</v>
+      </c>
+      <c r="G254" t="s">
+        <v>82</v>
+      </c>
+      <c r="H254" t="s">
+        <v>70</v>
+      </c>
+      <c r="I254">
+        <v>0</v>
+      </c>
+      <c r="J254">
+        <v>3</v>
+      </c>
+      <c r="K254">
+        <v>3</v>
+      </c>
+      <c r="L254">
+        <v>2</v>
+      </c>
+      <c r="M254">
+        <v>3</v>
+      </c>
+      <c r="N254">
+        <v>5</v>
+      </c>
+      <c r="O254" t="s">
+        <v>260</v>
+      </c>
+      <c r="P254" t="s">
+        <v>368</v>
+      </c>
+      <c r="Q254">
+        <v>4.75</v>
+      </c>
+      <c r="R254">
+        <v>2.3</v>
+      </c>
+      <c r="S254">
+        <v>2.3</v>
+      </c>
+      <c r="T254">
+        <v>1.33</v>
+      </c>
+      <c r="U254">
+        <v>3.25</v>
+      </c>
+      <c r="V254">
+        <v>2.63</v>
+      </c>
+      <c r="W254">
+        <v>1.44</v>
+      </c>
+      <c r="X254">
+        <v>6.5</v>
+      </c>
+      <c r="Y254">
+        <v>1.11</v>
+      </c>
+      <c r="Z254">
+        <v>3.83</v>
+      </c>
+      <c r="AA254">
+        <v>3.82</v>
+      </c>
+      <c r="AB254">
+        <v>1.83</v>
+      </c>
+      <c r="AC254">
+        <v>1.03</v>
+      </c>
+      <c r="AD254">
+        <v>11</v>
+      </c>
+      <c r="AE254">
+        <v>1.23</v>
+      </c>
+      <c r="AF254">
+        <v>4.19</v>
+      </c>
+      <c r="AG254">
+        <v>1.7</v>
+      </c>
+      <c r="AH254">
+        <v>2.05</v>
+      </c>
+      <c r="AI254">
+        <v>1.67</v>
+      </c>
+      <c r="AJ254">
+        <v>2.1</v>
+      </c>
+      <c r="AK254">
+        <v>2.05</v>
+      </c>
+      <c r="AL254">
+        <v>1.25</v>
+      </c>
+      <c r="AM254">
+        <v>1.2</v>
+      </c>
+      <c r="AN254">
+        <v>1.8</v>
+      </c>
+      <c r="AO254">
+        <v>1.73</v>
+      </c>
+      <c r="AP254">
+        <v>1.69</v>
+      </c>
+      <c r="AQ254">
+        <v>1.81</v>
+      </c>
+      <c r="AR254">
+        <v>1.75</v>
+      </c>
+      <c r="AS254">
+        <v>1.7</v>
+      </c>
+      <c r="AT254">
+        <v>3.45</v>
+      </c>
+      <c r="AU254">
+        <v>3</v>
+      </c>
+      <c r="AV254">
+        <v>10</v>
+      </c>
+      <c r="AW254">
+        <v>6</v>
+      </c>
+      <c r="AX254">
+        <v>7</v>
+      </c>
+      <c r="AY254">
+        <v>10</v>
+      </c>
+      <c r="AZ254">
+        <v>20</v>
+      </c>
+      <c r="BA254">
+        <v>2</v>
+      </c>
+      <c r="BB254">
+        <v>4</v>
+      </c>
+      <c r="BC254">
+        <v>6</v>
+      </c>
+      <c r="BD254">
+        <v>2.65</v>
+      </c>
+      <c r="BE254">
+        <v>6.75</v>
+      </c>
+      <c r="BF254">
+        <v>1.58</v>
+      </c>
+      <c r="BG254">
+        <v>1.33</v>
+      </c>
+      <c r="BH254">
+        <v>2.95</v>
+      </c>
+      <c r="BI254">
+        <v>1.56</v>
+      </c>
+      <c r="BJ254">
+        <v>2.23</v>
+      </c>
+      <c r="BK254">
+        <v>1.92</v>
+      </c>
+      <c r="BL254">
+        <v>1.78</v>
+      </c>
+      <c r="BM254">
+        <v>2.4</v>
+      </c>
+      <c r="BN254">
+        <v>1.49</v>
+      </c>
+      <c r="BO254">
+        <v>3.15</v>
+      </c>
+      <c r="BP254">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="255" spans="1:68">
+      <c r="A255" s="1">
+        <v>254</v>
+      </c>
+      <c r="B255">
+        <v>7858320</v>
+      </c>
+      <c r="C255" t="s">
+        <v>68</v>
+      </c>
+      <c r="D255" t="s">
+        <v>69</v>
+      </c>
+      <c r="E255" s="2">
+        <v>45753.45833333334</v>
+      </c>
+      <c r="F255">
+        <v>2</v>
+      </c>
+      <c r="G255" t="s">
+        <v>81</v>
+      </c>
+      <c r="H255" t="s">
+        <v>75</v>
+      </c>
+      <c r="I255">
+        <v>0</v>
+      </c>
+      <c r="J255">
+        <v>3</v>
+      </c>
+      <c r="K255">
+        <v>3</v>
+      </c>
+      <c r="L255">
+        <v>0</v>
+      </c>
+      <c r="M255">
+        <v>3</v>
+      </c>
+      <c r="N255">
+        <v>3</v>
+      </c>
+      <c r="O255" t="s">
+        <v>87</v>
+      </c>
+      <c r="P255" t="s">
+        <v>369</v>
+      </c>
+      <c r="Q255">
+        <v>2.5</v>
+      </c>
+      <c r="R255">
+        <v>2.25</v>
+      </c>
+      <c r="S255">
+        <v>4.33</v>
+      </c>
+      <c r="T255">
+        <v>1.36</v>
+      </c>
+      <c r="U255">
+        <v>3</v>
+      </c>
+      <c r="V255">
+        <v>2.63</v>
+      </c>
+      <c r="W255">
+        <v>1.44</v>
+      </c>
+      <c r="X255">
+        <v>7</v>
+      </c>
+      <c r="Y255">
+        <v>1.1</v>
+      </c>
+      <c r="Z255">
+        <v>1.87</v>
+      </c>
+      <c r="AA255">
+        <v>3.63</v>
+      </c>
+      <c r="AB255">
+        <v>3.86</v>
+      </c>
+      <c r="AC255">
+        <v>1.04</v>
+      </c>
+      <c r="AD255">
+        <v>9.75</v>
+      </c>
+      <c r="AE255">
+        <v>1.25</v>
+      </c>
+      <c r="AF255">
+        <v>3.82</v>
+      </c>
+      <c r="AG255">
+        <v>1.77</v>
+      </c>
+      <c r="AH255">
+        <v>1.98</v>
+      </c>
+      <c r="AI255">
+        <v>1.7</v>
+      </c>
+      <c r="AJ255">
+        <v>2.05</v>
+      </c>
+      <c r="AK255">
+        <v>1.25</v>
+      </c>
+      <c r="AL255">
+        <v>1.28</v>
+      </c>
+      <c r="AM255">
+        <v>1.83</v>
+      </c>
+      <c r="AN255">
+        <v>1.47</v>
+      </c>
+      <c r="AO255">
+        <v>0.6</v>
+      </c>
+      <c r="AP255">
+        <v>1.38</v>
+      </c>
+      <c r="AQ255">
+        <v>0.75</v>
+      </c>
+      <c r="AR255">
+        <v>1.53</v>
+      </c>
+      <c r="AS255">
+        <v>1.22</v>
+      </c>
+      <c r="AT255">
+        <v>2.75</v>
+      </c>
+      <c r="AU255">
+        <v>6</v>
+      </c>
+      <c r="AV255">
+        <v>4</v>
+      </c>
+      <c r="AW255">
+        <v>5</v>
+      </c>
+      <c r="AX255">
+        <v>7</v>
+      </c>
+      <c r="AY255">
+        <v>12</v>
+      </c>
+      <c r="AZ255">
+        <v>11</v>
+      </c>
+      <c r="BA255">
+        <v>4</v>
+      </c>
+      <c r="BB255">
+        <v>1</v>
+      </c>
+      <c r="BC255">
+        <v>5</v>
+      </c>
+      <c r="BD255">
+        <v>1.63</v>
+      </c>
+      <c r="BE255">
+        <v>6.75</v>
+      </c>
+      <c r="BF255">
+        <v>2.5</v>
+      </c>
+      <c r="BG255">
+        <v>1.2</v>
+      </c>
+      <c r="BH255">
+        <v>3.9</v>
+      </c>
+      <c r="BI255">
+        <v>1.35</v>
+      </c>
+      <c r="BJ255">
+        <v>2.9</v>
+      </c>
+      <c r="BK255">
+        <v>1.57</v>
+      </c>
+      <c r="BL255">
+        <v>2.2</v>
+      </c>
+      <c r="BM255">
+        <v>1.91</v>
+      </c>
+      <c r="BN255">
+        <v>1.79</v>
+      </c>
+      <c r="BO255">
+        <v>2.38</v>
+      </c>
+      <c r="BP255">
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1592" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1604" uniqueCount="372">
   <si>
     <t>Id_Jogo</t>
   </si>
@@ -799,6 +799,9 @@
     <t>['63', '71']</t>
   </si>
   <si>
+    <t>['78']</t>
+  </si>
+  <si>
     <t>['65']</t>
   </si>
   <si>
@@ -1124,6 +1127,9 @@
   </si>
   <si>
     <t>['17', '22', '27']</t>
+  </si>
+  <si>
+    <t>['32', '84']</t>
   </si>
 </sst>
 </file>
@@ -1485,7 +1491,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BP255"/>
+  <dimension ref="A1:BP257"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:68">
@@ -1741,7 +1747,7 @@
         <v>86</v>
       </c>
       <c r="P2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Q2">
         <v>1.91</v>
@@ -2437,7 +2443,7 @@
         <v>0</v>
       </c>
       <c r="AP5">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ5">
         <v>0.75</v>
@@ -2646,7 +2652,7 @@
         <v>2.75</v>
       </c>
       <c r="AQ6">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR6">
         <v>0</v>
@@ -2771,7 +2777,7 @@
         <v>87</v>
       </c>
       <c r="P7" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q7">
         <v>5</v>
@@ -3055,7 +3061,7 @@
         <v>0</v>
       </c>
       <c r="AP8">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ8">
         <v>1.19</v>
@@ -3595,7 +3601,7 @@
         <v>91</v>
       </c>
       <c r="P11" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Q11">
         <v>2.4</v>
@@ -3882,7 +3888,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ12">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR12">
         <v>0</v>
@@ -4007,7 +4013,7 @@
         <v>93</v>
       </c>
       <c r="P13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -4213,7 +4219,7 @@
         <v>94</v>
       </c>
       <c r="P14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q14">
         <v>3.25</v>
@@ -4419,7 +4425,7 @@
         <v>95</v>
       </c>
       <c r="P15" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Q15">
         <v>2.2</v>
@@ -4831,7 +4837,7 @@
         <v>97</v>
       </c>
       <c r="P17" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Q17">
         <v>1.75</v>
@@ -5449,7 +5455,7 @@
         <v>99</v>
       </c>
       <c r="P20" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q20">
         <v>4.1</v>
@@ -5733,7 +5739,7 @@
         <v>1</v>
       </c>
       <c r="AP21">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ21">
         <v>0.63</v>
@@ -5861,7 +5867,7 @@
         <v>101</v>
       </c>
       <c r="P22" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="Q22">
         <v>3.75</v>
@@ -6067,7 +6073,7 @@
         <v>102</v>
       </c>
       <c r="P23" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q23">
         <v>1.91</v>
@@ -6351,7 +6357,7 @@
         <v>3</v>
       </c>
       <c r="AP24">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ24">
         <v>1.25</v>
@@ -6479,7 +6485,7 @@
         <v>104</v>
       </c>
       <c r="P25" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="Q25">
         <v>1.93</v>
@@ -6891,7 +6897,7 @@
         <v>106</v>
       </c>
       <c r="P27" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="Q27">
         <v>3.9</v>
@@ -6972,7 +6978,7 @@
         <v>1</v>
       </c>
       <c r="AQ27">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR27">
         <v>0.45</v>
@@ -7097,7 +7103,7 @@
         <v>107</v>
       </c>
       <c r="P28" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="Q28">
         <v>3.06</v>
@@ -7303,7 +7309,7 @@
         <v>108</v>
       </c>
       <c r="P29" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="Q29">
         <v>3.75</v>
@@ -8002,7 +8008,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ32">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR32">
         <v>1.43</v>
@@ -8333,7 +8339,7 @@
         <v>113</v>
       </c>
       <c r="P34" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="Q34">
         <v>2.45</v>
@@ -8745,7 +8751,7 @@
         <v>114</v>
       </c>
       <c r="P36" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="Q36">
         <v>4.75</v>
@@ -9441,7 +9447,7 @@
         <v>1.5</v>
       </c>
       <c r="AP39">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ39">
         <v>0.75</v>
@@ -9775,7 +9781,7 @@
         <v>117</v>
       </c>
       <c r="P41" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="Q41">
         <v>3.2</v>
@@ -9981,7 +9987,7 @@
         <v>118</v>
       </c>
       <c r="P42" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="Q42">
         <v>3.4</v>
@@ -10268,7 +10274,7 @@
         <v>1.81</v>
       </c>
       <c r="AQ43">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR43">
         <v>1.33</v>
@@ -11217,7 +11223,7 @@
         <v>87</v>
       </c>
       <c r="P48" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="Q48">
         <v>2.6</v>
@@ -11298,7 +11304,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ48">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR48">
         <v>1.15</v>
@@ -11423,7 +11429,7 @@
         <v>122</v>
       </c>
       <c r="P49" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Q49">
         <v>3.1</v>
@@ -11504,7 +11510,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ49">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR49">
         <v>2.18</v>
@@ -11629,7 +11635,7 @@
         <v>87</v>
       </c>
       <c r="P50" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Q50">
         <v>5.85</v>
@@ -11835,7 +11841,7 @@
         <v>123</v>
       </c>
       <c r="P51" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="Q51">
         <v>2.2</v>
@@ -11913,7 +11919,7 @@
         <v>1</v>
       </c>
       <c r="AP51">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ51">
         <v>0.9399999999999999</v>
@@ -12531,7 +12537,7 @@
         <v>0</v>
       </c>
       <c r="AP54">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ54">
         <v>0.13</v>
@@ -12865,7 +12871,7 @@
         <v>87</v>
       </c>
       <c r="P56" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="Q56">
         <v>2.75</v>
@@ -12943,10 +12949,10 @@
         <v>2</v>
       </c>
       <c r="AP56">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ56">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR56">
         <v>1.68</v>
@@ -13277,7 +13283,7 @@
         <v>87</v>
       </c>
       <c r="P58" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="Q58">
         <v>3.1</v>
@@ -13483,7 +13489,7 @@
         <v>128</v>
       </c>
       <c r="P59" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="Q59">
         <v>3.52</v>
@@ -13767,7 +13773,7 @@
         <v>1</v>
       </c>
       <c r="AP60">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ60">
         <v>1</v>
@@ -13895,7 +13901,7 @@
         <v>129</v>
       </c>
       <c r="P61" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="Q61">
         <v>2.05</v>
@@ -14719,7 +14725,7 @@
         <v>133</v>
       </c>
       <c r="P65" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q65">
         <v>3.02</v>
@@ -15003,7 +15009,7 @@
         <v>1.5</v>
       </c>
       <c r="AP66">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ66">
         <v>1.81</v>
@@ -15337,7 +15343,7 @@
         <v>136</v>
       </c>
       <c r="P68" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="Q68">
         <v>3.2</v>
@@ -15543,7 +15549,7 @@
         <v>137</v>
       </c>
       <c r="P69" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q69">
         <v>3.76</v>
@@ -16573,7 +16579,7 @@
         <v>141</v>
       </c>
       <c r="P74" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="Q74">
         <v>1.91</v>
@@ -17066,7 +17072,7 @@
         <v>1.13</v>
       </c>
       <c r="AQ76">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR76">
         <v>1.57</v>
@@ -17475,10 +17481,10 @@
         <v>1</v>
       </c>
       <c r="AP78">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ78">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR78">
         <v>1.59</v>
@@ -18427,7 +18433,7 @@
         <v>150</v>
       </c>
       <c r="P83" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="Q83">
         <v>4.33</v>
@@ -19045,7 +19051,7 @@
         <v>151</v>
       </c>
       <c r="P86" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Q86">
         <v>1.91</v>
@@ -20075,7 +20081,7 @@
         <v>87</v>
       </c>
       <c r="P91" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="Q91">
         <v>2.88</v>
@@ -20153,7 +20159,7 @@
         <v>0.5</v>
       </c>
       <c r="AP91">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ91">
         <v>0.63</v>
@@ -20281,7 +20287,7 @@
         <v>155</v>
       </c>
       <c r="P92" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="Q92">
         <v>3.1</v>
@@ -20693,7 +20699,7 @@
         <v>157</v>
       </c>
       <c r="P94" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="Q94">
         <v>2.2</v>
@@ -20980,7 +20986,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ95">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR95">
         <v>1.79</v>
@@ -21105,7 +21111,7 @@
         <v>87</v>
       </c>
       <c r="P96" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="Q96">
         <v>3.5</v>
@@ -21186,7 +21192,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ96">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR96">
         <v>1.72</v>
@@ -21311,7 +21317,7 @@
         <v>159</v>
       </c>
       <c r="P97" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="Q97">
         <v>2</v>
@@ -21723,7 +21729,7 @@
         <v>161</v>
       </c>
       <c r="P99" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="Q99">
         <v>2.9</v>
@@ -21929,7 +21935,7 @@
         <v>87</v>
       </c>
       <c r="P100" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="Q100">
         <v>4.33</v>
@@ -22135,7 +22141,7 @@
         <v>162</v>
       </c>
       <c r="P101" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="Q101">
         <v>4.33</v>
@@ -22831,7 +22837,7 @@
         <v>0.67</v>
       </c>
       <c r="AP104">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ104">
         <v>0.75</v>
@@ -23165,7 +23171,7 @@
         <v>166</v>
       </c>
       <c r="P106" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="Q106">
         <v>3</v>
@@ -23371,7 +23377,7 @@
         <v>167</v>
       </c>
       <c r="P107" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="Q107">
         <v>4.33</v>
@@ -23577,7 +23583,7 @@
         <v>168</v>
       </c>
       <c r="P108" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="Q108">
         <v>3.5</v>
@@ -23861,7 +23867,7 @@
         <v>1.17</v>
       </c>
       <c r="AP109">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ109">
         <v>0.9399999999999999</v>
@@ -23989,7 +23995,7 @@
         <v>87</v>
       </c>
       <c r="P110" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="Q110">
         <v>3.2</v>
@@ -24276,7 +24282,7 @@
         <v>1.56</v>
       </c>
       <c r="AQ111">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR111">
         <v>1.55</v>
@@ -24482,7 +24488,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ112">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR112">
         <v>1.71</v>
@@ -24607,7 +24613,7 @@
         <v>171</v>
       </c>
       <c r="P113" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q113">
         <v>7.5</v>
@@ -25843,7 +25849,7 @@
         <v>150</v>
       </c>
       <c r="P119" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="Q119">
         <v>4.5</v>
@@ -26127,7 +26133,7 @@
         <v>1.29</v>
       </c>
       <c r="AP120">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ120">
         <v>1.25</v>
@@ -26461,7 +26467,7 @@
         <v>179</v>
       </c>
       <c r="P122" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="Q122">
         <v>3.5</v>
@@ -26951,10 +26957,10 @@
         <v>0.57</v>
       </c>
       <c r="AP124">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ124">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR124">
         <v>1.8</v>
@@ -27079,7 +27085,7 @@
         <v>181</v>
       </c>
       <c r="P125" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="Q125">
         <v>4.75</v>
@@ -27160,7 +27166,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ125">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR125">
         <v>1.37</v>
@@ -27491,7 +27497,7 @@
         <v>182</v>
       </c>
       <c r="P127" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="Q127">
         <v>4</v>
@@ -27903,7 +27909,7 @@
         <v>184</v>
       </c>
       <c r="P129" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="Q129">
         <v>2.75</v>
@@ -28109,7 +28115,7 @@
         <v>185</v>
       </c>
       <c r="P130" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="Q130">
         <v>1.72</v>
@@ -28521,7 +28527,7 @@
         <v>186</v>
       </c>
       <c r="P132" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="Q132">
         <v>4</v>
@@ -28933,7 +28939,7 @@
         <v>188</v>
       </c>
       <c r="P134" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="Q134">
         <v>2.55</v>
@@ -29345,7 +29351,7 @@
         <v>189</v>
       </c>
       <c r="P136" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="Q136">
         <v>1.7</v>
@@ -29423,7 +29429,7 @@
         <v>0.13</v>
       </c>
       <c r="AP136">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ136">
         <v>0.13</v>
@@ -30044,7 +30050,7 @@
         <v>1</v>
       </c>
       <c r="AQ139">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR139">
         <v>1.07</v>
@@ -30375,7 +30381,7 @@
         <v>87</v>
       </c>
       <c r="P141" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="Q141">
         <v>2.88</v>
@@ -30662,7 +30668,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ142">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR142">
         <v>2.07</v>
@@ -30787,7 +30793,7 @@
         <v>194</v>
       </c>
       <c r="P143" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q143">
         <v>1.95</v>
@@ -30993,7 +30999,7 @@
         <v>87</v>
       </c>
       <c r="P144" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q144">
         <v>3.75</v>
@@ -31405,7 +31411,7 @@
         <v>196</v>
       </c>
       <c r="P146" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q146">
         <v>2.7</v>
@@ -31689,7 +31695,7 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="AP147">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ147">
         <v>0.75</v>
@@ -31817,7 +31823,7 @@
         <v>167</v>
       </c>
       <c r="P148" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="Q148">
         <v>4</v>
@@ -32023,7 +32029,7 @@
         <v>198</v>
       </c>
       <c r="P149" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="Q149">
         <v>3.1</v>
@@ -32641,7 +32647,7 @@
         <v>200</v>
       </c>
       <c r="P152" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="Q152">
         <v>3.25</v>
@@ -33053,7 +33059,7 @@
         <v>202</v>
       </c>
       <c r="P154" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="Q154">
         <v>3</v>
@@ -33134,7 +33140,7 @@
         <v>1.69</v>
       </c>
       <c r="AQ154">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR154">
         <v>1.81</v>
@@ -33259,7 +33265,7 @@
         <v>87</v>
       </c>
       <c r="P155" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="Q155">
         <v>3.6</v>
@@ -33465,7 +33471,7 @@
         <v>203</v>
       </c>
       <c r="P156" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="Q156">
         <v>1.7</v>
@@ -33752,7 +33758,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ157">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR157">
         <v>1.54</v>
@@ -33877,7 +33883,7 @@
         <v>93</v>
       </c>
       <c r="P158" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="Q158">
         <v>3.7</v>
@@ -34289,7 +34295,7 @@
         <v>115</v>
       </c>
       <c r="P160" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="Q160">
         <v>3</v>
@@ -34495,7 +34501,7 @@
         <v>205</v>
       </c>
       <c r="P161" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="Q161">
         <v>1.9</v>
@@ -34573,7 +34579,7 @@
         <v>1.33</v>
       </c>
       <c r="AP161">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ161">
         <v>0.9399999999999999</v>
@@ -34907,7 +34913,7 @@
         <v>207</v>
       </c>
       <c r="P163" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="Q163">
         <v>2.45</v>
@@ -35319,7 +35325,7 @@
         <v>144</v>
       </c>
       <c r="P165" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="Q165">
         <v>3.5</v>
@@ -35397,7 +35403,7 @@
         <v>1</v>
       </c>
       <c r="AP165">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ165">
         <v>1.56</v>
@@ -35525,7 +35531,7 @@
         <v>209</v>
       </c>
       <c r="P166" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="Q166">
         <v>4.2</v>
@@ -35937,7 +35943,7 @@
         <v>87</v>
       </c>
       <c r="P168" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="Q168">
         <v>3.6</v>
@@ -36015,7 +36021,7 @@
         <v>1.8</v>
       </c>
       <c r="AP168">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ168">
         <v>1.81</v>
@@ -36555,7 +36561,7 @@
         <v>87</v>
       </c>
       <c r="P171" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Q171">
         <v>3.5</v>
@@ -36761,7 +36767,7 @@
         <v>159</v>
       </c>
       <c r="P172" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="Q172">
         <v>3.4</v>
@@ -36842,7 +36848,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ172">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR172">
         <v>1.56</v>
@@ -36967,7 +36973,7 @@
         <v>210</v>
       </c>
       <c r="P173" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="Q173">
         <v>1.5</v>
@@ -37173,7 +37179,7 @@
         <v>87</v>
       </c>
       <c r="P174" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="Q174">
         <v>4.33</v>
@@ -37585,7 +37591,7 @@
         <v>212</v>
       </c>
       <c r="P176" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="Q176">
         <v>2.63</v>
@@ -37666,7 +37672,7 @@
         <v>1.38</v>
       </c>
       <c r="AQ176">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR176">
         <v>1.54</v>
@@ -37791,7 +37797,7 @@
         <v>213</v>
       </c>
       <c r="P177" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="Q177">
         <v>2.3</v>
@@ -38203,7 +38209,7 @@
         <v>215</v>
       </c>
       <c r="P179" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="Q179">
         <v>3.5</v>
@@ -38284,7 +38290,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ179">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR179">
         <v>1.9</v>
@@ -38409,7 +38415,7 @@
         <v>216</v>
       </c>
       <c r="P180" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="Q180">
         <v>2.55</v>
@@ -38487,7 +38493,7 @@
         <v>0.82</v>
       </c>
       <c r="AP180">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ180">
         <v>0.75</v>
@@ -39027,7 +39033,7 @@
         <v>87</v>
       </c>
       <c r="P183" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="Q183">
         <v>5.5</v>
@@ -39233,7 +39239,7 @@
         <v>219</v>
       </c>
       <c r="P184" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="Q184">
         <v>2.5</v>
@@ -39311,7 +39317,7 @@
         <v>0.9</v>
       </c>
       <c r="AP184">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ184">
         <v>1</v>
@@ -39929,7 +39935,7 @@
         <v>1.36</v>
       </c>
       <c r="AP187">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ187">
         <v>0.9399999999999999</v>
@@ -40057,7 +40063,7 @@
         <v>96</v>
       </c>
       <c r="P188" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="Q188">
         <v>2.35</v>
@@ -40138,7 +40144,7 @@
         <v>1.5</v>
       </c>
       <c r="AQ188">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR188">
         <v>1.65</v>
@@ -40675,7 +40681,7 @@
         <v>224</v>
       </c>
       <c r="P191" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="Q191">
         <v>1.95</v>
@@ -41087,7 +41093,7 @@
         <v>225</v>
       </c>
       <c r="P193" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="Q193">
         <v>3.6</v>
@@ -41293,7 +41299,7 @@
         <v>226</v>
       </c>
       <c r="P194" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="Q194">
         <v>3</v>
@@ -42195,7 +42201,7 @@
         <v>1.42</v>
       </c>
       <c r="AP198">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ198">
         <v>1.19</v>
@@ -42323,7 +42329,7 @@
         <v>188</v>
       </c>
       <c r="P199" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="Q199">
         <v>6</v>
@@ -42529,7 +42535,7 @@
         <v>231</v>
       </c>
       <c r="P200" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="Q200">
         <v>2.25</v>
@@ -42610,7 +42616,7 @@
         <v>1.44</v>
       </c>
       <c r="AQ200">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR200">
         <v>1.89</v>
@@ -42941,7 +42947,7 @@
         <v>233</v>
       </c>
       <c r="P202" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="Q202">
         <v>5</v>
@@ -43022,7 +43028,7 @@
         <v>1.63</v>
       </c>
       <c r="AQ202">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR202">
         <v>1.22</v>
@@ -43147,7 +43153,7 @@
         <v>234</v>
       </c>
       <c r="P203" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Q203">
         <v>2.6</v>
@@ -43353,7 +43359,7 @@
         <v>235</v>
       </c>
       <c r="P204" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Q204">
         <v>2.15</v>
@@ -43559,7 +43565,7 @@
         <v>236</v>
       </c>
       <c r="P205" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Q205">
         <v>4.6</v>
@@ -43765,7 +43771,7 @@
         <v>237</v>
       </c>
       <c r="P206" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Q206">
         <v>1.95</v>
@@ -44255,7 +44261,7 @@
         <v>1.5</v>
       </c>
       <c r="AP208">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ208">
         <v>1.5</v>
@@ -45001,7 +45007,7 @@
         <v>227</v>
       </c>
       <c r="P212" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="Q212">
         <v>2.75</v>
@@ -45207,7 +45213,7 @@
         <v>239</v>
       </c>
       <c r="P213" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="Q213">
         <v>2.5</v>
@@ -45413,7 +45419,7 @@
         <v>86</v>
       </c>
       <c r="P214" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Q214">
         <v>1.71</v>
@@ -45494,7 +45500,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ214">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR214">
         <v>2.08</v>
@@ -45825,7 +45831,7 @@
         <v>87</v>
       </c>
       <c r="P216" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Q216">
         <v>3.25</v>
@@ -45903,7 +45909,7 @@
         <v>1.46</v>
       </c>
       <c r="AP216">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ216">
         <v>1.56</v>
@@ -46315,10 +46321,10 @@
         <v>1.77</v>
       </c>
       <c r="AP218">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ218">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR218">
         <v>1.71</v>
@@ -46443,7 +46449,7 @@
         <v>88</v>
       </c>
       <c r="P219" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="Q219">
         <v>4.33</v>
@@ -46855,7 +46861,7 @@
         <v>241</v>
       </c>
       <c r="P221" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="Q221">
         <v>2.25</v>
@@ -47473,7 +47479,7 @@
         <v>87</v>
       </c>
       <c r="P224" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="Q224">
         <v>4.33</v>
@@ -48375,7 +48381,7 @@
         <v>0.86</v>
       </c>
       <c r="AP228">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="AQ228">
         <v>1</v>
@@ -48584,7 +48590,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ229">
-        <v>1.8</v>
+        <v>1.88</v>
       </c>
       <c r="AR229">
         <v>1.11</v>
@@ -48709,7 +48715,7 @@
         <v>174</v>
       </c>
       <c r="P230" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Q230">
         <v>4.75</v>
@@ -49121,7 +49127,7 @@
         <v>87</v>
       </c>
       <c r="P232" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="Q232">
         <v>2.88</v>
@@ -49408,7 +49414,7 @@
         <v>2.25</v>
       </c>
       <c r="AQ233">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="AR233">
         <v>1.88</v>
@@ -50023,7 +50029,7 @@
         <v>0.79</v>
       </c>
       <c r="AP236">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="AQ236">
         <v>0.75</v>
@@ -50151,7 +50157,7 @@
         <v>249</v>
       </c>
       <c r="P237" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="Q237">
         <v>2.5</v>
@@ -50357,7 +50363,7 @@
         <v>250</v>
       </c>
       <c r="P238" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="Q238">
         <v>3.1</v>
@@ -50563,7 +50569,7 @@
         <v>118</v>
       </c>
       <c r="P239" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="Q239">
         <v>3.75</v>
@@ -50769,7 +50775,7 @@
         <v>251</v>
       </c>
       <c r="P240" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Q240">
         <v>2.1</v>
@@ -50975,7 +50981,7 @@
         <v>105</v>
       </c>
       <c r="P241" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Q241">
         <v>2.3</v>
@@ -51387,7 +51393,7 @@
         <v>87</v>
       </c>
       <c r="P243" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Q243">
         <v>3.75</v>
@@ -51593,7 +51599,7 @@
         <v>252</v>
       </c>
       <c r="P244" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Q244">
         <v>3.4</v>
@@ -52211,7 +52217,7 @@
         <v>255</v>
       </c>
       <c r="P247" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Q247">
         <v>3.4</v>
@@ -52829,7 +52835,7 @@
         <v>257</v>
       </c>
       <c r="P250" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="Q250">
         <v>2.5</v>
@@ -53035,7 +53041,7 @@
         <v>258</v>
       </c>
       <c r="P251" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="Q251">
         <v>2.05</v>
@@ -53241,7 +53247,7 @@
         <v>259</v>
       </c>
       <c r="P252" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="Q252">
         <v>2.63</v>
@@ -53447,7 +53453,7 @@
         <v>87</v>
       </c>
       <c r="P253" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="Q253">
         <v>4.33</v>
@@ -53653,7 +53659,7 @@
         <v>260</v>
       </c>
       <c r="P254" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="Q254">
         <v>4.75</v>
@@ -53859,7 +53865,7 @@
         <v>87</v>
       </c>
       <c r="P255" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Q255">
         <v>2.5</v>
@@ -54016,6 +54022,418 @@
       </c>
       <c r="BP255">
         <v>1.5</v>
+      </c>
+    </row>
+    <row r="256" spans="1:68">
+      <c r="A256" s="1">
+        <v>255</v>
+      </c>
+      <c r="B256">
+        <v>7858321</v>
+      </c>
+      <c r="C256" t="s">
+        <v>68</v>
+      </c>
+      <c r="D256" t="s">
+        <v>69</v>
+      </c>
+      <c r="E256" s="2">
+        <v>45753.5625</v>
+      </c>
+      <c r="F256">
+        <v>2</v>
+      </c>
+      <c r="G256" t="s">
+        <v>73</v>
+      </c>
+      <c r="H256" t="s">
+        <v>74</v>
+      </c>
+      <c r="I256">
+        <v>0</v>
+      </c>
+      <c r="J256">
+        <v>1</v>
+      </c>
+      <c r="K256">
+        <v>1</v>
+      </c>
+      <c r="L256">
+        <v>1</v>
+      </c>
+      <c r="M256">
+        <v>2</v>
+      </c>
+      <c r="N256">
+        <v>3</v>
+      </c>
+      <c r="O256" t="s">
+        <v>261</v>
+      </c>
+      <c r="P256" t="s">
+        <v>371</v>
+      </c>
+      <c r="Q256">
+        <v>3.4</v>
+      </c>
+      <c r="R256">
+        <v>2.2</v>
+      </c>
+      <c r="S256">
+        <v>3.1</v>
+      </c>
+      <c r="T256">
+        <v>1.4</v>
+      </c>
+      <c r="U256">
+        <v>2.75</v>
+      </c>
+      <c r="V256">
+        <v>2.75</v>
+      </c>
+      <c r="W256">
+        <v>1.4</v>
+      </c>
+      <c r="X256">
+        <v>8</v>
+      </c>
+      <c r="Y256">
+        <v>1.08</v>
+      </c>
+      <c r="Z256">
+        <v>2.7</v>
+      </c>
+      <c r="AA256">
+        <v>3.28</v>
+      </c>
+      <c r="AB256">
+        <v>2.54</v>
+      </c>
+      <c r="AC256">
+        <v>1.06</v>
+      </c>
+      <c r="AD256">
+        <v>9</v>
+      </c>
+      <c r="AE256">
+        <v>1.26</v>
+      </c>
+      <c r="AF256">
+        <v>3.8</v>
+      </c>
+      <c r="AG256">
+        <v>1.89</v>
+      </c>
+      <c r="AH256">
+        <v>1.85</v>
+      </c>
+      <c r="AI256">
+        <v>1.7</v>
+      </c>
+      <c r="AJ256">
+        <v>2.05</v>
+      </c>
+      <c r="AK256">
+        <v>1.53</v>
+      </c>
+      <c r="AL256">
+        <v>1.31</v>
+      </c>
+      <c r="AM256">
+        <v>1.41</v>
+      </c>
+      <c r="AN256">
+        <v>1.8</v>
+      </c>
+      <c r="AO256">
+        <v>1.8</v>
+      </c>
+      <c r="AP256">
+        <v>1.69</v>
+      </c>
+      <c r="AQ256">
+        <v>1.88</v>
+      </c>
+      <c r="AR256">
+        <v>1.65</v>
+      </c>
+      <c r="AS256">
+        <v>1.69</v>
+      </c>
+      <c r="AT256">
+        <v>3.34</v>
+      </c>
+      <c r="AU256">
+        <v>5</v>
+      </c>
+      <c r="AV256">
+        <v>5</v>
+      </c>
+      <c r="AW256">
+        <v>7</v>
+      </c>
+      <c r="AX256">
+        <v>7</v>
+      </c>
+      <c r="AY256">
+        <v>12</v>
+      </c>
+      <c r="AZ256">
+        <v>13</v>
+      </c>
+      <c r="BA256">
+        <v>4</v>
+      </c>
+      <c r="BB256">
+        <v>3</v>
+      </c>
+      <c r="BC256">
+        <v>7</v>
+      </c>
+      <c r="BD256">
+        <v>2.07</v>
+      </c>
+      <c r="BE256">
+        <v>6.4</v>
+      </c>
+      <c r="BF256">
+        <v>1.93</v>
+      </c>
+      <c r="BG256">
+        <v>1.36</v>
+      </c>
+      <c r="BH256">
+        <v>2.8</v>
+      </c>
+      <c r="BI256">
+        <v>1.61</v>
+      </c>
+      <c r="BJ256">
+        <v>2.15</v>
+      </c>
+      <c r="BK256">
+        <v>1.98</v>
+      </c>
+      <c r="BL256">
+        <v>1.72</v>
+      </c>
+      <c r="BM256">
+        <v>2.55</v>
+      </c>
+      <c r="BN256">
+        <v>1.45</v>
+      </c>
+      <c r="BO256">
+        <v>3.3</v>
+      </c>
+      <c r="BP256">
+        <v>1.27</v>
+      </c>
+    </row>
+    <row r="257" spans="1:68">
+      <c r="A257" s="1">
+        <v>256</v>
+      </c>
+      <c r="B257">
+        <v>7858322</v>
+      </c>
+      <c r="C257" t="s">
+        <v>68</v>
+      </c>
+      <c r="D257" t="s">
+        <v>69</v>
+      </c>
+      <c r="E257" s="2">
+        <v>45753.59375</v>
+      </c>
+      <c r="F257">
+        <v>2</v>
+      </c>
+      <c r="G257" t="s">
+        <v>76</v>
+      </c>
+      <c r="H257" t="s">
+        <v>84</v>
+      </c>
+      <c r="I257">
+        <v>1</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>1</v>
+      </c>
+      <c r="L257">
+        <v>1</v>
+      </c>
+      <c r="M257">
+        <v>0</v>
+      </c>
+      <c r="N257">
+        <v>1</v>
+      </c>
+      <c r="O257" t="s">
+        <v>95</v>
+      </c>
+      <c r="P257" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q257">
+        <v>2.6</v>
+      </c>
+      <c r="R257">
+        <v>2.1</v>
+      </c>
+      <c r="S257">
+        <v>4.75</v>
+      </c>
+      <c r="T257">
+        <v>1.44</v>
+      </c>
+      <c r="U257">
+        <v>2.63</v>
+      </c>
+      <c r="V257">
+        <v>3.25</v>
+      </c>
+      <c r="W257">
+        <v>1.33</v>
+      </c>
+      <c r="X257">
+        <v>10</v>
+      </c>
+      <c r="Y257">
+        <v>1.06</v>
+      </c>
+      <c r="Z257">
+        <v>1.85</v>
+      </c>
+      <c r="AA257">
+        <v>3.39</v>
+      </c>
+      <c r="AB257">
+        <v>4.3</v>
+      </c>
+      <c r="AC257">
+        <v>1.07</v>
+      </c>
+      <c r="AD257">
+        <v>7.75</v>
+      </c>
+      <c r="AE257">
+        <v>1.35</v>
+      </c>
+      <c r="AF257">
+        <v>3.09</v>
+      </c>
+      <c r="AG257">
+        <v>1.98</v>
+      </c>
+      <c r="AH257">
+        <v>1.77</v>
+      </c>
+      <c r="AI257">
+        <v>1.95</v>
+      </c>
+      <c r="AJ257">
+        <v>1.8</v>
+      </c>
+      <c r="AK257">
+        <v>1.22</v>
+      </c>
+      <c r="AL257">
+        <v>1.3</v>
+      </c>
+      <c r="AM257">
+        <v>1.9</v>
+      </c>
+      <c r="AN257">
+        <v>1.47</v>
+      </c>
+      <c r="AO257">
+        <v>0.93</v>
+      </c>
+      <c r="AP257">
+        <v>1.56</v>
+      </c>
+      <c r="AQ257">
+        <v>0.88</v>
+      </c>
+      <c r="AR257">
+        <v>1.68</v>
+      </c>
+      <c r="AS257">
+        <v>1.08</v>
+      </c>
+      <c r="AT257">
+        <v>2.76</v>
+      </c>
+      <c r="AU257">
+        <v>4</v>
+      </c>
+      <c r="AV257">
+        <v>3</v>
+      </c>
+      <c r="AW257">
+        <v>10</v>
+      </c>
+      <c r="AX257">
+        <v>6</v>
+      </c>
+      <c r="AY257">
+        <v>16</v>
+      </c>
+      <c r="AZ257">
+        <v>13</v>
+      </c>
+      <c r="BA257">
+        <v>3</v>
+      </c>
+      <c r="BB257">
+        <v>2</v>
+      </c>
+      <c r="BC257">
+        <v>5</v>
+      </c>
+      <c r="BD257">
+        <v>1.42</v>
+      </c>
+      <c r="BE257">
+        <v>7</v>
+      </c>
+      <c r="BF257">
+        <v>3.15</v>
+      </c>
+      <c r="BG257">
+        <v>1.32</v>
+      </c>
+      <c r="BH257">
+        <v>3.05</v>
+      </c>
+      <c r="BI257">
+        <v>1.55</v>
+      </c>
+      <c r="BJ257">
+        <v>2.25</v>
+      </c>
+      <c r="BK257">
+        <v>1.9</v>
+      </c>
+      <c r="BL257">
+        <v>1.79</v>
+      </c>
+      <c r="BM257">
+        <v>2.4</v>
+      </c>
+      <c r="BN257">
+        <v>1.5</v>
+      </c>
+      <c r="BO257">
+        <v>3.05</v>
+      </c>
+      <c r="BP257">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
+++ b/Bases_de_Dados/FootyStats/Bases_de_Dados_(2022-2025)/Belgium Pro League_20242025.xlsx
@@ -1279,7 +1279,7 @@
     <t>['2', '31']</t>
   </si>
   <si>
-    <t>['61', '90+5']</t>
+    <t>['61', '9005']</t>
   </si>
 </sst>
 </file>
@@ -2002,10 +2002,10 @@
         <v>2</v>
       </c>
       <c r="AY2">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AZ2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA2">
         <v>7</v>
@@ -2208,10 +2208,10 @@
         <v>5</v>
       </c>
       <c r="AY3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA3">
         <v>4</v>
@@ -2417,7 +2417,7 @@
         <v>2</v>
       </c>
       <c r="AZ4">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA4">
         <v>2</v>
@@ -2620,7 +2620,7 @@
         <v>3</v>
       </c>
       <c r="AY5">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ5">
         <v>3</v>
@@ -2826,7 +2826,7 @@
         <v>3</v>
       </c>
       <c r="AY6">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AZ6">
         <v>5</v>
@@ -3032,10 +3032,10 @@
         <v>5</v>
       </c>
       <c r="AY7">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AZ7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA7">
         <v>8</v>
@@ -3238,10 +3238,10 @@
         <v>6</v>
       </c>
       <c r="AY8">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA8">
         <v>5</v>
@@ -3444,10 +3444,10 @@
         <v>4</v>
       </c>
       <c r="AY9">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ9">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA9">
         <v>6</v>
@@ -3650,10 +3650,10 @@
         <v>1</v>
       </c>
       <c r="AY10">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ10">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BA10">
         <v>4</v>
@@ -3856,10 +3856,10 @@
         <v>6</v>
       </c>
       <c r="AY11">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ11">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="BA11">
         <v>8</v>
@@ -4062,10 +4062,10 @@
         <v>7</v>
       </c>
       <c r="AY12">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ12">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA12">
         <v>2</v>
@@ -4268,10 +4268,10 @@
         <v>8</v>
       </c>
       <c r="AY13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ13">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA13">
         <v>3</v>
@@ -4474,10 +4474,10 @@
         <v>4</v>
       </c>
       <c r="AY14">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="AZ14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA14">
         <v>7</v>
@@ -4680,10 +4680,10 @@
         <v>2</v>
       </c>
       <c r="AY15">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AZ15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA15">
         <v>14</v>
@@ -4886,10 +4886,10 @@
         <v>4</v>
       </c>
       <c r="AY16">
+        <v>8</v>
+      </c>
+      <c r="AZ16">
         <v>11</v>
-      </c>
-      <c r="AZ16">
-        <v>17</v>
       </c>
       <c r="BA16">
         <v>3</v>
@@ -5092,10 +5092,10 @@
         <v>8</v>
       </c>
       <c r="AY17">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ17">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA17">
         <v>6</v>
@@ -5298,10 +5298,10 @@
         <v>4</v>
       </c>
       <c r="AY18">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ18">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA18">
         <v>6</v>
@@ -5504,10 +5504,10 @@
         <v>5</v>
       </c>
       <c r="AY19">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA19">
         <v>3</v>
@@ -5710,10 +5710,10 @@
         <v>2</v>
       </c>
       <c r="AY20">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AZ20">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA20">
         <v>5</v>
@@ -5916,10 +5916,10 @@
         <v>4</v>
       </c>
       <c r="AY21">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="AZ21">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA21">
         <v>9</v>
@@ -6122,10 +6122,10 @@
         <v>5</v>
       </c>
       <c r="AY22">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ22">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA22">
         <v>5</v>
@@ -6328,10 +6328,10 @@
         <v>3</v>
       </c>
       <c r="AY23">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ23">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="BA23">
         <v>5</v>
@@ -6534,10 +6534,10 @@
         <v>4</v>
       </c>
       <c r="AY24">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AZ24">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA24">
         <v>4</v>
@@ -6740,10 +6740,10 @@
         <v>1</v>
       </c>
       <c r="AY25">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA25">
         <v>8</v>
@@ -6946,10 +6946,10 @@
         <v>4</v>
       </c>
       <c r="AY26">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA26">
         <v>5</v>
@@ -7152,10 +7152,10 @@
         <v>1</v>
       </c>
       <c r="AY27">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ27">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="BA27">
         <v>6</v>
@@ -7358,10 +7358,10 @@
         <v>5</v>
       </c>
       <c r="AY28">
+        <v>9</v>
+      </c>
+      <c r="AZ28">
         <v>13</v>
-      </c>
-      <c r="AZ28">
-        <v>15</v>
       </c>
       <c r="BA28">
         <v>3</v>
@@ -7564,10 +7564,10 @@
         <v>1</v>
       </c>
       <c r="AY29">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ29">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA29">
         <v>9</v>
@@ -7770,10 +7770,10 @@
         <v>5</v>
       </c>
       <c r="AY30">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ30">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA30">
         <v>7</v>
@@ -7976,10 +7976,10 @@
         <v>1</v>
       </c>
       <c r="AY31">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ31">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA31">
         <v>6</v>
@@ -8182,10 +8182,10 @@
         <v>3</v>
       </c>
       <c r="AY32">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ32">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BA32">
         <v>13</v>
@@ -8388,10 +8388,10 @@
         <v>3</v>
       </c>
       <c r="AY33">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ33">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA33">
         <v>7</v>
@@ -8594,10 +8594,10 @@
         <v>6</v>
       </c>
       <c r="AY34">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="AZ34">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA34">
         <v>7</v>
@@ -8800,10 +8800,10 @@
         <v>4</v>
       </c>
       <c r="AY35">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ35">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="BA35">
         <v>13</v>
@@ -9006,10 +9006,10 @@
         <v>6</v>
       </c>
       <c r="AY36">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ36">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA36">
         <v>6</v>
@@ -9212,10 +9212,10 @@
         <v>8</v>
       </c>
       <c r="AY37">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AZ37">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA37">
         <v>3</v>
@@ -9418,10 +9418,10 @@
         <v>6</v>
       </c>
       <c r="AY38">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ38">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA38">
         <v>2</v>
@@ -9624,7 +9624,7 @@
         <v>4</v>
       </c>
       <c r="AY39">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AZ39">
         <v>6</v>
@@ -9830,10 +9830,10 @@
         <v>4</v>
       </c>
       <c r="AY40">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ40">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="BA40">
         <v>0</v>
@@ -10036,10 +10036,10 @@
         <v>7</v>
       </c>
       <c r="AY41">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ41">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="BA41">
         <v>0</v>
@@ -10242,10 +10242,10 @@
         <v>4</v>
       </c>
       <c r="AY42">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ42">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="BA42">
         <v>4</v>
@@ -10448,10 +10448,10 @@
         <v>3</v>
       </c>
       <c r="AY43">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AZ43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA43">
         <v>11</v>
@@ -10654,19 +10654,19 @@
         <v>6</v>
       </c>
       <c r="AY44">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AZ44">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA44">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB44">
         <v>5</v>
       </c>
       <c r="BC44">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD44">
         <v>1.17</v>
@@ -10860,10 +10860,10 @@
         <v>3</v>
       </c>
       <c r="AY45">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ45">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="BA45">
         <v>1</v>
@@ -11066,10 +11066,10 @@
         <v>2</v>
       </c>
       <c r="AY46">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="AZ46">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA46">
         <v>8</v>
@@ -11272,10 +11272,10 @@
         <v>4</v>
       </c>
       <c r="AY47">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ47">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA47">
         <v>8</v>
@@ -11478,10 +11478,10 @@
         <v>0</v>
       </c>
       <c r="AY48">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="AZ48">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA48">
         <v>8</v>
@@ -11684,10 +11684,10 @@
         <v>8</v>
       </c>
       <c r="AY49">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ49">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="BA49">
         <v>6</v>
@@ -11890,10 +11890,10 @@
         <v>8</v>
       </c>
       <c r="AY50">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ50">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA50">
         <v>3</v>
@@ -12096,10 +12096,10 @@
         <v>7</v>
       </c>
       <c r="AY51">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AZ51">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA51">
         <v>3</v>
@@ -12302,10 +12302,10 @@
         <v>3</v>
       </c>
       <c r="AY52">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ52">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA52">
         <v>3</v>
@@ -12508,10 +12508,10 @@
         <v>4</v>
       </c>
       <c r="AY53">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AZ53">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="BA53">
         <v>8</v>
@@ -12714,10 +12714,10 @@
         <v>6</v>
       </c>
       <c r="AY54">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AZ54">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA54">
         <v>7</v>
@@ -12920,10 +12920,10 @@
         <v>3</v>
       </c>
       <c r="AY55">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AZ55">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA55">
         <v>7</v>
@@ -13126,10 +13126,10 @@
         <v>6</v>
       </c>
       <c r="AY56">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="AZ56">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA56">
         <v>4</v>
@@ -13332,10 +13332,10 @@
         <v>7</v>
       </c>
       <c r="AY57">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ57">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="BA57">
         <v>1</v>
@@ -13538,10 +13538,10 @@
         <v>7</v>
       </c>
       <c r="AY58">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ58">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA58">
         <v>4</v>
@@ -13744,10 +13744,10 @@
         <v>3</v>
       </c>
       <c r="AY59">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ59">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA59">
         <v>10</v>
@@ -13950,10 +13950,10 @@
         <v>4</v>
       </c>
       <c r="AY60">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ60">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA60">
         <v>6</v>
@@ -14156,7 +14156,7 @@
         <v>3</v>
       </c>
       <c r="AY61">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="AZ61">
         <v>7</v>
@@ -14362,10 +14362,10 @@
         <v>4</v>
       </c>
       <c r="AY62">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ62">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA62">
         <v>2</v>
@@ -14568,10 +14568,10 @@
         <v>2</v>
       </c>
       <c r="AY63">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="AZ63">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA63">
         <v>8</v>
@@ -14774,10 +14774,10 @@
         <v>6</v>
       </c>
       <c r="AY64">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ64">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA64">
         <v>10</v>
@@ -14980,10 +14980,10 @@
         <v>2</v>
       </c>
       <c r="AY65">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ65">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BA65">
         <v>6</v>
@@ -15186,10 +15186,10 @@
         <v>6</v>
       </c>
       <c r="AY66">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="AZ66">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BA66">
         <v>4</v>
@@ -15392,10 +15392,10 @@
         <v>4</v>
       </c>
       <c r="AY67">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AZ67">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="BA67">
         <v>6</v>
@@ -15598,10 +15598,10 @@
         <v>3</v>
       </c>
       <c r="AY68">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ68">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA68">
         <v>11</v>
@@ -15804,10 +15804,10 @@
         <v>4</v>
       </c>
       <c r="AY69">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="AZ69">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="BA69">
         <v>5</v>
@@ -16010,10 +16010,10 @@
         <v>2</v>
       </c>
       <c r="AY70">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ70">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA70">
         <v>10</v>
@@ -16216,7 +16216,7 @@
         <v>2</v>
       </c>
       <c r="AY71">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AZ71">
         <v>5</v>
@@ -16422,10 +16422,10 @@
         <v>7</v>
       </c>
       <c r="AY72">
+        <v>10</v>
+      </c>
+      <c r="AZ72">
         <v>11</v>
-      </c>
-      <c r="AZ72">
-        <v>13</v>
       </c>
       <c r="BA72">
         <v>4</v>
@@ -16628,10 +16628,10 @@
         <v>5</v>
       </c>
       <c r="AY73">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ73">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA73">
         <v>9</v>
@@ -16834,10 +16834,10 @@
         <v>3</v>
       </c>
       <c r="AY74">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AZ74">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA74">
         <v>13</v>
@@ -17040,10 +17040,10 @@
         <v>3</v>
       </c>
       <c r="AY75">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ75">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA75">
         <v>4</v>
@@ -17249,7 +17249,7 @@
         <v>10</v>
       </c>
       <c r="AZ76">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA76">
         <v>3</v>
@@ -17452,10 +17452,10 @@
         <v>7</v>
       </c>
       <c r="AY77">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AZ77">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA77">
         <v>0</v>
@@ -17658,10 +17658,10 @@
         <v>8</v>
       </c>
       <c r="AY78">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ78">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="BA78">
         <v>4</v>
@@ -17864,10 +17864,10 @@
         <v>5</v>
       </c>
       <c r="AY79">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ79">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA79">
         <v>4</v>
@@ -18070,10 +18070,10 @@
         <v>3</v>
       </c>
       <c r="AY80">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ80">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA80">
         <v>5</v>
@@ -18276,10 +18276,10 @@
         <v>6</v>
       </c>
       <c r="AY81">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="AZ81">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA81">
         <v>10</v>
@@ -18688,10 +18688,10 @@
         <v>5</v>
       </c>
       <c r="AY83">
+        <v>12</v>
+      </c>
+      <c r="AZ83">
         <v>14</v>
-      </c>
-      <c r="AZ83">
-        <v>16</v>
       </c>
       <c r="BA83">
         <v>3</v>
@@ -18897,7 +18897,7 @@
         <v>14</v>
       </c>
       <c r="AZ84">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BA84">
         <v>5</v>
@@ -19100,10 +19100,10 @@
         <v>2</v>
       </c>
       <c r="AY85">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AZ85">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA85">
         <v>5</v>
@@ -19924,10 +19924,10 @@
         <v>8</v>
       </c>
       <c r="AY89">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ89">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA89">
         <v>5</v>
@@ -20336,10 +20336,10 @@
         <v>0</v>
       </c>
       <c r="AY91">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ91">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA91">
         <v>9</v>
@@ -20542,10 +20542,10 @@
         <v>7</v>
       </c>
       <c r="AY92">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ92">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BA92">
         <v>5</v>
@@ -20748,10 +20748,10 @@
         <v>8</v>
       </c>
       <c r="AY93">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ93">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="BA93">
         <v>8</v>
@@ -20954,10 +20954,10 @@
         <v>4</v>
       </c>
       <c r="AY94">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ94">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA94">
         <v>8</v>
@@ -21160,10 +21160,10 @@
         <v>5</v>
       </c>
       <c r="AY95">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ95">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA95">
         <v>2</v>
@@ -21366,10 +21366,10 @@
         <v>7</v>
       </c>
       <c r="AY96">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AZ96">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="BA96">
         <v>1</v>
@@ -21572,10 +21572,10 @@
         <v>1</v>
       </c>
       <c r="AY97">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ97">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA97">
         <v>8</v>
@@ -21778,10 +21778,10 @@
         <v>11</v>
       </c>
       <c r="AY98">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ98">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="BA98">
         <v>4</v>
@@ -21984,10 +21984,10 @@
         <v>7</v>
       </c>
       <c r="AY99">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ99">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA99">
         <v>3</v>
@@ -22190,10 +22190,10 @@
         <v>2</v>
       </c>
       <c r="AY100">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ100">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA100">
         <v>8</v>
@@ -22396,10 +22396,10 @@
         <v>4</v>
       </c>
       <c r="AY101">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ101">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA101">
         <v>8</v>
@@ -22602,10 +22602,10 @@
         <v>6</v>
       </c>
       <c r="AY102">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ102">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA102">
         <v>3</v>
@@ -22808,10 +22808,10 @@
         <v>4</v>
       </c>
       <c r="AY103">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ103">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA103">
         <v>9</v>
@@ -23014,7 +23014,7 @@
         <v>1</v>
       </c>
       <c r="AY104">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="AZ104">
         <v>3</v>
@@ -23220,10 +23220,10 @@
         <v>2</v>
       </c>
       <c r="AY105">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ105">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA105">
         <v>4</v>
@@ -23426,10 +23426,10 @@
         <v>1</v>
       </c>
       <c r="AY106">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ106">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BA106">
         <v>10</v>
@@ -23632,10 +23632,10 @@
         <v>4</v>
       </c>
       <c r="AY107">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AZ107">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA107">
         <v>7</v>
@@ -23838,10 +23838,10 @@
         <v>8</v>
       </c>
       <c r="AY108">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ108">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="BA108">
         <v>6</v>
@@ -24044,10 +24044,10 @@
         <v>3</v>
       </c>
       <c r="AY109">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AZ109">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA109">
         <v>6</v>
@@ -24250,10 +24250,10 @@
         <v>4</v>
       </c>
       <c r="AY110">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AZ110">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="BA110">
         <v>5</v>
@@ -24456,10 +24456,10 @@
         <v>0</v>
       </c>
       <c r="AY111">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ111">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA111">
         <v>10</v>
@@ -24662,10 +24662,10 @@
         <v>6</v>
       </c>
       <c r="AY112">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="AZ112">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA112">
         <v>2</v>
@@ -24871,7 +24871,7 @@
         <v>7</v>
       </c>
       <c r="AZ113">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA113">
         <v>5</v>
@@ -25898,10 +25898,10 @@
         <v>7</v>
       </c>
       <c r="AY118">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AZ118">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA118">
         <v>5</v>
@@ -26310,10 +26310,10 @@
         <v>1</v>
       </c>
       <c r="AY120">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ120">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA120">
         <v>3</v>
@@ -26722,10 +26722,10 @@
         <v>4</v>
       </c>
       <c r="AY122">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="AZ122">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA122">
         <v>5</v>
@@ -26928,7 +26928,7 @@
         <v>2</v>
       </c>
       <c r="AY123">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AZ123">
         <v>5</v>
@@ -27134,10 +27134,10 @@
         <v>1</v>
       </c>
       <c r="AY124">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="AZ124">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BA124">
         <v>8</v>
@@ -27340,10 +27340,10 @@
         <v>9</v>
       </c>
       <c r="AY125">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ125">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="BA125">
         <v>5</v>
@@ -27546,10 +27546,10 @@
         <v>6</v>
       </c>
       <c r="AY126">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ126">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA126">
         <v>10</v>
@@ -27752,10 +27752,10 @@
         <v>3</v>
       </c>
       <c r="AY127">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="AZ127">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA127">
         <v>2</v>
@@ -27958,10 +27958,10 @@
         <v>6</v>
       </c>
       <c r="AY128">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ128">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA128">
         <v>5</v>
@@ -28164,10 +28164,10 @@
         <v>5</v>
       </c>
       <c r="AY129">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AZ129">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="BA129">
         <v>7</v>
@@ -28370,10 +28370,10 @@
         <v>8</v>
       </c>
       <c r="AY130">
+        <v>10</v>
+      </c>
+      <c r="AZ130">
         <v>13</v>
-      </c>
-      <c r="AZ130">
-        <v>17</v>
       </c>
       <c r="BA130">
         <v>1</v>
@@ -28576,10 +28576,10 @@
         <v>7</v>
       </c>
       <c r="AY131">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ131">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA131">
         <v>3</v>
@@ -28782,10 +28782,10 @@
         <v>5</v>
       </c>
       <c r="AY132">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="AZ132">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA132">
         <v>8</v>
@@ -28988,10 +28988,10 @@
         <v>8</v>
       </c>
       <c r="AY133">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ133">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA133">
         <v>5</v>
@@ -29194,10 +29194,10 @@
         <v>6</v>
       </c>
       <c r="AY134">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AZ134">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="BA134">
         <v>7</v>
@@ -29400,10 +29400,10 @@
         <v>6</v>
       </c>
       <c r="AY135">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ135">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA135">
         <v>3</v>
@@ -29606,10 +29606,10 @@
         <v>2</v>
       </c>
       <c r="AY136">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AZ136">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA136">
         <v>7</v>
@@ -29812,10 +29812,10 @@
         <v>5</v>
       </c>
       <c r="AY137">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AZ137">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="BA137">
         <v>3</v>
@@ -30018,10 +30018,10 @@
         <v>2</v>
       </c>
       <c r="AY138">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AZ138">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BA138">
         <v>4</v>
@@ -30224,10 +30224,10 @@
         <v>8</v>
       </c>
       <c r="AY139">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AZ139">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA139">
         <v>10</v>
@@ -30430,10 +30430,10 @@
         <v>4</v>
       </c>
       <c r="AY140">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="AZ140">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA140">
         <v>3</v>
@@ -30636,10 +30636,10 @@
         <v>1</v>
       </c>
       <c r="AY141">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AZ141">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA141">
         <v>5</v>
@@ -30842,10 +30842,10 @@
         <v>3</v>
       </c>
       <c r="AY142">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ142">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA142">
         <v>8</v>
@@ -31048,10 +31048,10 @@
         <v>2</v>
       </c>
       <c r="AY143">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AZ143">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA143">
         <v>15</v>
@@ -31254,10 +31254,10 @@
         <v>4</v>
       </c>
       <c r="AY144">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AZ144">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA144">
         <v>9</v>
@@ -31460,10 +31460,10 @@
         <v>9</v>
       </c>
       <c r="AY145">
+        <v>9</v>
+      </c>
+      <c r="AZ145">
         <v>16</v>
-      </c>
-      <c r="AZ145">
-        <v>19</v>
       </c>
       <c r="BA145">
         <v>9</v>
@@ -31666,10 +31666,10 @@
         <v>5</v>
       </c>
       <c r="AY146">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ146">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA146">
         <v>10</v>
@@ -31872,10 +31872,10 @@
         <v>5</v>
       </c>
       <c r="AY147">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="AZ147">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="BA147">
         <v>12</v>
@@ -32078,10 +32078,10 @@
         <v>2</v>
       </c>
       <c r="AY148">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ148">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="BA148">
         <v>5</v>
@@ -32284,10 +32284,10 @@
         <v>3</v>
       </c>
       <c r="AY149">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ149">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="BA149">
         <v>6</v>
@@ -32490,10 +32490,10 @@
         <v>3</v>
       </c>
       <c r="AY150">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ150">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA150">
         <v>10</v>
@@ -32696,10 +32696,10 @@
         <v>7</v>
       </c>
       <c r="AY151">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="AZ151">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA151">
         <v>4</v>
@@ -32902,10 +32902,10 @@
         <v>4</v>
       </c>
       <c r="AY152">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="AZ152">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA152">
         <v>5</v>
@@ -33108,10 +33108,10 @@
         <v>3</v>
       </c>
       <c r="AY153">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ153">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="BA153">
         <v>5</v>
@@ -33314,10 +33314,10 @@
         <v>11</v>
       </c>
       <c r="AY154">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AZ154">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="BA154">
         <v>5</v>
@@ -33520,10 +33520,10 @@
         <v>8</v>
       </c>
       <c r="AY155">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AZ155">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA155">
         <v>8</v>
@@ -33726,10 +33726,10 @@
         <v>6</v>
       </c>
       <c r="AY156">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ156">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA156">
         <v>1</v>
@@ -33932,10 +33932,10 @@
         <v>2</v>
       </c>
       <c r="AY157">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ157">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="BA157">
         <v>3</v>
@@ -34138,10 +34138,10 @@
         <v>5</v>
       </c>
       <c r="AY158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ158">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA158">
         <v>2</v>
@@ -34344,10 +34344,10 @@
         <v>2</v>
       </c>
       <c r="AY159">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="AZ159">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA159">
         <v>8</v>
@@ -34550,10 +34550,10 @@
         <v>6</v>
       </c>
       <c r="AY160">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="AZ160">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BA160">
         <v>2</v>
@@ -34756,10 +34756,10 @@
         <v>3</v>
       </c>
       <c r="AY161">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="AZ161">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA161">
         <v>7</v>
@@ -34962,10 +34962,10 @@
         <v>8</v>
       </c>
       <c r="AY162">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="AZ162">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="BA162">
         <v>3</v>
@@ -35168,10 +35168,10 @@
         <v>4</v>
       </c>
       <c r="AY163">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="AZ163">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA163">
         <v>10</v>
@@ -35374,10 +35374,10 @@
         <v>7</v>
       </c>
       <c r="AY164">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ164">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="BA164">
         <v>2</v>
@@ -35580,7 +35580,7 @@
         <v>3</v>
       </c>
       <c r="AY165">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ165">
         <v>8</v>
@@ -35786,19 +35786,19 @@
         <v>8</v>
       </c>
       <c r="AY166">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AZ166">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BA166">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB166">
         <v>6</v>
       </c>
       <c r="BC166">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BD166">
         <v>2.7</v>
@@ -35992,10 +35992,10 @@
         <v>5</v>
       </c>
       <c r="AY167">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ167">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA167">
         <v>5</v>
@@ -36198,10 +36198,10 @@
         <v>7</v>
       </c>
       <c r="AY168">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AZ168">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA168">
         <v>8</v>
@@ -36404,7 +36404,7 @@
         <v>5</v>
       </c>
       <c r="AY169">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ169">
         <v>11</v>
@@ -36610,7 +36610,7 @@
         <v>7</v>
       </c>
       <c r="AY170">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ170">
         <v>12</v>
@@ -36816,10 +36816,10 @@
         <v>10</v>
       </c>
       <c r="AY171">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ171">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="BA171">
         <v>3</v>
@@ -37025,7 +37025,7 @@
         <v>6</v>
       </c>
       <c r="AZ172">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA172">
         <v>2</v>
@@ -37231,7 +37231,7 @@
         <v>17</v>
       </c>
       <c r="AZ173">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA173">
         <v>5</v>
@@ -37434,10 +37434,10 @@
         <v>9</v>
       </c>
       <c r="AY174">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ174">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA174">
         <v>7</v>
@@ -37640,10 +37640,10 @@
         <v>3</v>
       </c>
       <c r="AY175">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ175">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA175">
         <v>6</v>
@@ -37846,10 +37846,10 @@
         <v>6</v>
       </c>
       <c r="AY176">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AZ176">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA176">
         <v>8</v>
@@ -38052,10 +38052,10 @@
         <v>9</v>
       </c>
       <c r="AY177">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ177">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BA177">
         <v>7</v>
@@ -38258,10 +38258,10 @@
         <v>14</v>
       </c>
       <c r="AY178">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AZ178">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA178">
         <v>3</v>
@@ -38464,7 +38464,7 @@
         <v>4</v>
       </c>
       <c r="AY179">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ179">
         <v>7</v>
@@ -38670,10 +38670,10 @@
         <v>6</v>
       </c>
       <c r="AY180">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ180">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA180">
         <v>2</v>
@@ -38876,10 +38876,10 @@
         <v>6</v>
       </c>
       <c r="AY181">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AZ181">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA181">
         <v>6</v>
@@ -39082,10 +39082,10 @@
         <v>10</v>
       </c>
       <c r="AY182">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ182">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="BA182">
         <v>3</v>
@@ -39494,10 +39494,10 @@
         <v>6</v>
       </c>
       <c r="AY184">
+        <v>12</v>
+      </c>
+      <c r="AZ184">
         <v>13</v>
-      </c>
-      <c r="AZ184">
-        <v>16</v>
       </c>
       <c r="BA184">
         <v>2</v>
@@ -39700,10 +39700,10 @@
         <v>19</v>
       </c>
       <c r="AY185">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AZ185">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="BA185">
         <v>1</v>
@@ -39906,10 +39906,10 @@
         <v>22</v>
       </c>
       <c r="AY186">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AZ186">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="BA186">
         <v>1</v>
@@ -40112,7 +40112,7 @@
         <v>1</v>
       </c>
       <c r="AY187">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ187">
         <v>4</v>
@@ -40318,10 +40318,10 @@
         <v>9</v>
       </c>
       <c r="AY188">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ188">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="BA188">
         <v>4</v>
@@ -40524,10 +40524,10 @@
         <v>7</v>
       </c>
       <c r="AY189">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AZ189">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BA189">
         <v>7</v>
@@ -40730,10 +40730,10 @@
         <v>9</v>
       </c>
       <c r="AY190">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="AZ190">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="BA190">
         <v>3</v>
@@ -40936,10 +40936,10 @@
         <v>5</v>
       </c>
       <c r="AY191">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AZ191">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA191">
         <v>6</v>
@@ -41142,10 +41142,10 @@
         <v>8</v>
       </c>
       <c r="AY192">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ192">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA192">
         <v>9</v>
@@ -41351,7 +41351,7 @@
         <v>10</v>
       </c>
       <c r="AZ193">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BA193">
         <v>5</v>
@@ -41557,7 +41557,7 @@
         <v>17</v>
       </c>
       <c r="AZ194">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA194">
         <v>9</v>
@@ -41760,10 +41760,10 @@
         <v>4</v>
       </c>
       <c r="AY195">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="AZ195">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="BA195">
         <v>8</v>
@@ -41966,10 +41966,10 @@
         <v>4</v>
       </c>
       <c r="AY196">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ196">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="BA196">
         <v>3</v>
@@ -42172,10 +42172,10 @@
         <v>7</v>
       </c>
       <c r="AY197">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ197">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA197">
         <v>2</v>
@@ -42378,19 +42378,19 @@
         <v>5</v>
       </c>
       <c r="AY198">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AZ198">
         <v>9</v>
       </c>
       <c r="BA198">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB198">
         <v>2</v>
       </c>
       <c r="BC198">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD198">
         <v>1.84</v>
@@ -42584,10 +42584,10 @@
         <v>8</v>
       </c>
       <c r="AY199">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ199">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BA199">
         <v>7</v>
@@ -42790,10 +42790,10 @@
         <v>10</v>
       </c>
       <c r="AY200">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AZ200">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BA200">
         <v>5</v>
@@ -42996,10 +42996,10 @@
         <v>6</v>
       </c>
       <c r="AY201">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="AZ201">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA201">
         <v>4</v>
@@ -43202,10 +43202,10 @@
         <v>12</v>
       </c>
       <c r="AY202">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AZ202">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="BA202">
         <v>6</v>
@@ -43408,10 +43408,10 @@
         <v>14</v>
       </c>
       <c r="AY203">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AZ203">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="BA203">
         <v>2</v>
@@ -43614,10 +43614,10 @@
         <v>9</v>
       </c>
       <c r="AY204">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ204">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA204">
         <v>4</v>
@@ -43820,10 +43820,10 @@
         <v>11</v>
       </c>
       <c r="AY205">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ205">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="BA205">
         <v>3</v>
@@ -44026,10 +44026,10 @@
         <v>8</v>
       </c>
       <c r="AY206">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AZ206">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA206">
         <v>8</v>
@@ -44438,10 +44438,10 @@
         <v>4</v>
       </c>
       <c r="AY208">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ208">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA208">
         <v>3</v>
@@ -44644,7 +44644,7 @@
         <v>3</v>
       </c>
       <c r="AY209">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="AZ209">
         <v>9</v>
@@ -44850,10 +44850,10 @@
         <v>6</v>
       </c>
       <c r="AY210">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ210">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BA210">
         <v>4</v>
@@ -45262,10 +45262,10 @@
         <v>9</v>
       </c>
       <c r="AY212">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AZ212">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA212">
         <v>2</v>
@@ -45468,10 +45468,10 @@
         <v>3</v>
       </c>
       <c r="AY213">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ213">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA213">
         <v>7</v>
@@ -45674,10 +45674,10 @@
         <v>9</v>
       </c>
       <c r="AY214">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ214">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA214">
         <v>7</v>
@@ -45880,10 +45880,10 @@
         <v>8</v>
       </c>
       <c r="AY215">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ215">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BA215">
         <v>7</v>
@@ -46086,10 +46086,10 @@
         <v>1</v>
       </c>
       <c r="AY216">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ216">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA216">
         <v>7</v>
@@ -46292,10 +46292,10 @@
         <v>2</v>
       </c>
       <c r="AY217">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AZ217">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA217">
         <v>5</v>
@@ -46501,7 +46501,7 @@
         <v>13</v>
       </c>
       <c r="AZ218">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA218">
         <v>3</v>
@@ -46704,10 +46704,10 @@
         <v>4</v>
       </c>
       <c r="AY219">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AZ219">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA219">
         <v>2</v>
@@ -46916,13 +46916,13 @@
         <v>-1</v>
       </c>
       <c r="BA220">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="BB220">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="BC220">
-        <v>13</v>
+        <v>-1</v>
       </c>
       <c r="BD220">
         <v>2.65</v>
@@ -47119,7 +47119,7 @@
         <v>10</v>
       </c>
       <c r="AZ221">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA221">
         <v>3</v>
@@ -47322,7 +47322,7 @@
         <v>2</v>
       </c>
       <c r="AY222">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="AZ222">
         <v>5</v>
@@ -47528,10 +47528,10 @@
         <v>9</v>
       </c>
       <c r="AY223">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ223">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BA223">
         <v>4</v>
@@ -47734,10 +47734,10 @@
         <v>5</v>
       </c>
       <c r="AY224">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ224">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BA224">
         <v>3</v>
@@ -47940,10 +47940,10 @@
         <v>15</v>
       </c>
       <c r="AY225">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ225">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA225">
         <v>2</v>
@@ -48146,10 +48146,10 @@
         <v>8</v>
       </c>
       <c r="AY226">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AZ226">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA226">
         <v>4</v>
@@ -48352,10 +48352,10 @@
         <v>6</v>
       </c>
       <c r="AY227">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AZ227">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BA227">
         <v>5</v>
@@ -48558,7 +48558,7 @@
         <v>4</v>
       </c>
       <c r="AY228">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AZ228">
         <v>10</v>
@@ -48764,10 +48764,10 @@
         <v>11</v>
       </c>
       <c r="AY229">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AZ229">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="BA229">
         <v>2</v>
@@ -48970,10 +48970,10 @@
         <v>11</v>
       </c>
       <c r="AY230">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AZ230">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA230">
         <v>9</v>
@@ -49176,7 +49176,7 @@
         <v>15</v>
       </c>
       <c r="AY231">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ231">
         <v>18</v>
@@ -49382,10 +49382,10 @@
         <v>7</v>
       </c>
       <c r="AY232">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AZ232">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="BA232">
         <v>8</v>
@@ -49588,10 +49588,10 @@
         <v>4</v>
       </c>
       <c r="AY233">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AZ233">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BA233">
         <v>1</v>
@@ -49794,10 +49794,10 @@
         <v>6</v>
       </c>
       <c r="AY234">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="AZ234">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA234">
         <v>4</v>
@@ -50209,7 +50209,7 @@
         <v>6</v>
       </c>
       <c r="AZ236">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BA236">
         <v>4</v>
@@ -50412,7 +50412,7 @@
         <v>1</v>
       </c>
       <c r="AY237">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ237">
         <v>4</v>
@@ -50618,10 +50618,10 @@
         <v>7</v>
       </c>
       <c r="AY238">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ238">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="BA238">
         <v>6</v>
@@ -50824,10 +50824,10 @@
         <v>11</v>
       </c>
       <c r="AY239">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AZ239">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="BA239">
         <v>5</v>
@@ -51030,10 +51030,10 @@
         <v>7</v>
       </c>
       <c r="AY240">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AZ240">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA240">
         <v>7</v>
@@ -51236,10 +51236,10 @@
         <v>3</v>
       </c>
       <c r="AY241">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="AZ241">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BA241">
         <v>2</v>
@@ -51442,10 +51442,10 @@
         <v>19</v>
       </c>
       <c r="AY242">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ242">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="BA242">
         <v>4</v>
@@ -51651,7 +51651,7 @@
         <v>6</v>
       </c>
       <c r="AZ243">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="BA243">
         <v>0</v>
@@ -51854,7 +51854,7 @@
         <v>8</v>
       </c>
       <c r="AY244">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ244">
         <v>15</v>
@@ -52266,10 +52266,10 @@
         <v>3</v>
       </c>
       <c r="AY246">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ246">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA246">
         <v>7</v>
@@ -52472,10 +52472,10 @@
         <v>8</v>
       </c>
       <c r="AY247">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ247">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BA247">
         <v>2</v>
@@ -52678,10 +52678,10 @@
         <v>0</v>
       </c>
       <c r="AY248">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AZ248">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="BA248">
         <v>4</v>
@@ -52884,10 +52884,10 @@
         <v>9</v>
       </c>
       <c r="AY249">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ249">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BA249">
         <v>8</v>
@@ -53090,10 +53090,10 @@
         <v>5</v>
       </c>
       <c r="AY250">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AZ250">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA250">
         <v>4</v>
@@ -53296,7 +53296,7 @@
         <v>7</v>
       </c>
       <c r="AY251">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AZ251">
         <v>11</v>
@@ -53502,10 +53502,10 @@
         <v>13</v>
       </c>
       <c r="AY252">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="AZ252">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="BA252">
         <v>6</v>
@@ -53708,10 +53708,10 @@
         <v>10</v>
       </c>
       <c r="AY253">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AZ253">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA253">
         <v>4</v>
@@ -53914,10 +53914,10 @@
         <v>7</v>
       </c>
       <c r="AY254">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ254">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BA254">
         <v>2</v>
@@ -54120,7 +54120,7 @@
         <v>7</v>
       </c>
       <c r="AY255">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ255">
         <v>11</v>
@@ -54329,7 +54329,7 @@
         <v>12</v>
       </c>
       <c r="AZ256">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA256">
         <v>4</v>
@@ -54532,10 +54532,10 @@
         <v>6</v>
       </c>
       <c r="AY257">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AZ257">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BA257">
         <v>3</v>
@@ -54738,10 +54738,10 @@
         <v>1</v>
       </c>
       <c r="AY258">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AZ258">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BA258">
         <v>6</v>
@@ -54944,7 +54944,7 @@
         <v>3</v>
       </c>
       <c r="AY259">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AZ259">
         <v>7</v>
@@ -55150,10 +55150,10 @@
         <v>4</v>
       </c>
       <c r="AY260">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AZ260">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA260">
         <v>5</v>
@@ -55356,10 +55356,10 @@
         <v>6</v>
       </c>
       <c r="AY261">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ261">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="BA261">
         <v>4</v>
@@ -55562,10 +55562,10 @@
         <v>11</v>
       </c>
       <c r="AY262">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AZ262">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BA262">
         <v>5</v>
@@ -55768,10 +55768,10 @@
         <v>9</v>
       </c>
       <c r="AY263">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AZ263">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="BA263">
         <v>8</v>
@@ -55974,7 +55974,7 @@
         <v>4</v>
       </c>
       <c r="AY264">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AZ264">
         <v>8</v>
@@ -56183,7 +56183,7 @@
         <v>6</v>
       </